--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="1870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="1871">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807556152344</t>
+    <t xml:space="preserve">15.1807546615601</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537845611572</t>
+    <t xml:space="preserve">14.8537855148315</t>
   </si>
   <si>
     <t xml:space="preserve">14.4801063537598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.171820640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476108551025</t>
+    <t xml:space="preserve">14.1718196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
     <t xml:space="preserve">13.9289264678955</t>
@@ -62,25 +62,25 @@
     <t xml:space="preserve">15.0406265258789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3208856582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022022247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389207839966</t>
+    <t xml:space="preserve">15.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022031784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389198303223</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0410308837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3212909698486</t>
+    <t xml:space="preserve">14.0410318374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
     <t xml:space="preserve">14.33997631073</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">14.3866853713989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943218231201</t>
+    <t xml:space="preserve">13.9943208694458</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240531921387</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">14.0036640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.433801651001</t>
+    <t xml:space="preserve">13.4338026046753</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155216217041</t>
+    <t xml:space="preserve">12.4155235290527</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061813354492</t>
@@ -122,25 +122,25 @@
     <t xml:space="preserve">12.8172292709351</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459051132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722249984741</t>
+    <t xml:space="preserve">13.5459041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722269058228</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645895004272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195852279663</t>
+    <t xml:space="preserve">13.4057750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.919584274292</t>
   </si>
   <si>
     <t xml:space="preserve">14.0316905975342</t>
@@ -152,103 +152,103 @@
     <t xml:space="preserve">13.8355093002319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.106427192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372131347656</t>
+    <t xml:space="preserve">14.1064262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372150421143</t>
   </si>
   <si>
     <t xml:space="preserve">14.4520797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2558975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011486053467</t>
+    <t xml:space="preserve">14.2558965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011447906494</t>
   </si>
   <si>
     <t xml:space="preserve">15.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769388198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4797010421753</t>
+    <t xml:space="preserve">15.1060190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.479700088501</t>
   </si>
   <si>
     <t xml:space="preserve">15.6385135650635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5450925827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873365402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939155578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302278518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3485069274902</t>
+    <t xml:space="preserve">15.5450954437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.993914604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202344894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302268981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253545761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017978668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858776092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3485088348389</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4139022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924556732178</t>
+    <t xml:space="preserve">16.4139003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924537658691</t>
   </si>
   <si>
     <t xml:space="preserve">16.3671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215339660645</t>
+    <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
     <t xml:space="preserve">16.2177181243896</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">16.1149578094482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2737693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100826263428</t>
+    <t xml:space="preserve">16.273775100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100845336914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6474494934082</t>
@@ -281,37 +281,37 @@
     <t xml:space="preserve">16.4419269561768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889888763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489810943604</t>
+    <t xml:space="preserve">16.4889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648983001709</t>
   </si>
   <si>
     <t xml:space="preserve">16.5548648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207466125488</t>
+    <t xml:space="preserve">16.6207427978516</t>
   </si>
   <si>
     <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6866283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054481506348</t>
+    <t xml:space="preserve">16.6866264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054500579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995662689209</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5454521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8277969360352</t>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8277988433838</t>
   </si>
   <si>
     <t xml:space="preserve">16.8183879852295</t>
@@ -320,40 +320,40 @@
     <t xml:space="preserve">16.2254638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6890048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725427627563</t>
+    <t xml:space="preserve">15.689003944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725399017334</t>
   </si>
   <si>
     <t xml:space="preserve">15.7078304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3407773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5830974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113357543945</t>
+    <t xml:space="preserve">15.3407783508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5831031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113338470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.4325122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2536964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290088653564</t>
+    <t xml:space="preserve">16.253698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642757415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290098190308</t>
   </si>
   <si>
     <t xml:space="preserve">14.8796157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0678462982178</t>
+    <t xml:space="preserve">15.0678453445435</t>
   </si>
   <si>
     <t xml:space="preserve">15.2748985290527</t>
@@ -362,61 +362,61 @@
     <t xml:space="preserve">15.2090177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7855005264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3149223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443281173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9172611236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513586044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301773071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.547833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337062835693</t>
+    <t xml:space="preserve">15.5101861953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.314923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9172620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384225845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348917007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054679870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.990177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478315353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337034225464</t>
   </si>
   <si>
     <t xml:space="preserve">15.6701831817627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3784255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007753372192</t>
+    <t xml:space="preserve">15.3784246444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007734298706</t>
   </si>
   <si>
     <t xml:space="preserve">15.6419506072998</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">15.9148836135864</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0278186798096</t>
+    <t xml:space="preserve">16.0278167724609</t>
   </si>
   <si>
     <t xml:space="preserve">16.2725200653076</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">16.1595821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.376049041748</t>
+    <t xml:space="preserve">16.3760452270508</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983959197998</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">16.4607486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301555633545</t>
+    <t xml:space="preserve">16.5078086853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301593780518</t>
   </si>
   <si>
     <t xml:space="preserve">16.4701633453369</t>
@@ -461,79 +461,79 @@
     <t xml:space="preserve">16.780740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8560314178467</t>
+    <t xml:space="preserve">16.8560333251953</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372116088867</t>
+    <t xml:space="preserve">17.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9783821105957</t>
+    <t xml:space="preserve">16.9783840179443</t>
   </si>
   <si>
     <t xml:space="preserve">16.846622467041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8936786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.912504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842716217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525043487549</t>
+    <t xml:space="preserve">16.8936824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960353851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9125022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713298797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231052398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525081634521</t>
   </si>
   <si>
     <t xml:space="preserve">16.9030895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0066223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9972057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8748550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.034854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654460906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619209289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0725002288818</t>
+    <t xml:space="preserve">17.0066184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9972038269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0536785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0348529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
     <t xml:space="preserve">17.2324962615967</t>
@@ -542,82 +542,82 @@
     <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.128963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2136726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642578125</t>
+    <t xml:space="preserve">17.1289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2136707305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548412322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642559051514</t>
   </si>
   <si>
     <t xml:space="preserve">17.3077869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2983741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724765777588</t>
+    <t xml:space="preserve">17.298376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724803924561</t>
   </si>
   <si>
     <t xml:space="preserve">18.738338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8230419158936</t>
+    <t xml:space="preserve">18.8230400085449</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3406734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3783206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2183246612549</t>
+    <t xml:space="preserve">18.804220199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2183265686035</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.423002243042</t>
+    <t xml:space="preserve">19.4159641265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724189758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4230003356934</t>
   </si>
   <si>
     <t xml:space="preserve">20.234769821167</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2535915374756</t>
+    <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982929229736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.357120513916</t>
+    <t xml:space="preserve">20.3571186065674</t>
   </si>
   <si>
     <t xml:space="preserve">20.893575668335</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">20.6676979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6959342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206596374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7453708648682</t>
+    <t xml:space="preserve">20.6959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7453689575195</t>
   </si>
   <si>
     <t xml:space="preserve">19.519495010376</t>
@@ -647,37 +647,37 @@
     <t xml:space="preserve">19.6889038085938</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.84889793396</t>
+    <t xml:space="preserve">19.7171382904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8488998413086</t>
   </si>
   <si>
     <t xml:space="preserve">19.5759620666504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4630279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2747936248779</t>
+    <t xml:space="preserve">19.4630260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2747955322266</t>
   </si>
   <si>
     <t xml:space="preserve">19.4442043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3877353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3500843048096</t>
+    <t xml:space="preserve">19.3877334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
     <t xml:space="preserve">19.3971462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0018615722656</t>
+    <t xml:space="preserve">19.0959758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.001859664917</t>
   </si>
   <si>
     <t xml:space="preserve">19.1053848266602</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936370849609</t>
+    <t xml:space="preserve">18.4936389923096</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2865829467773</t>
+    <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
     <t xml:space="preserve">18.6254024505615</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">19.2559700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5100803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2371482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547836303711</t>
+    <t xml:space="preserve">19.510082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2371463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547817230225</t>
   </si>
   <si>
     <t xml:space="preserve">19.7924289703369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5947875976562</t>
+    <t xml:space="preserve">19.594783782959</t>
   </si>
   <si>
     <t xml:space="preserve">20.6018180847168</t>
@@ -731,40 +731,40 @@
     <t xml:space="preserve">20.7335815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900505065918</t>
+    <t xml:space="preserve">20.7994632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900524139404</t>
   </si>
   <si>
     <t xml:space="preserve">20.9218120574951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3641548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2982730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853332519531</t>
+    <t xml:space="preserve">21.3641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2982692718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853370666504</t>
   </si>
   <si>
     <t xml:space="preserve">21.015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.279447555542</t>
+    <t xml:space="preserve">20.9029884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947460174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794513702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.1100406646729</t>
@@ -776,34 +776,34 @@
     <t xml:space="preserve">21.6088523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429706573486</t>
+    <t xml:space="preserve">21.2135677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429725646973</t>
   </si>
   <si>
     <t xml:space="preserve">21.8347301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0229568481445</t>
+    <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
     <t xml:space="preserve">21.8064937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0417804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582454681396</t>
+    <t xml:space="preserve">22.0417823791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582492828369</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817684173584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7476482391357</t>
+    <t xml:space="preserve">22.7476463317871</t>
   </si>
   <si>
     <t xml:space="preserve">22.6252975463867</t>
@@ -818,31 +818,31 @@
     <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5876483917236</t>
+    <t xml:space="preserve">22.5876502990723</t>
   </si>
   <si>
     <t xml:space="preserve">22.371187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9194355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7876720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3076820373535</t>
+    <t xml:space="preserve">22.0135498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464939117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.91943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7876682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0981216430664</t>
+    <t xml:space="preserve">22.098123550415</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">22.2686920166016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0507431030273</t>
+    <t xml:space="preserve">22.0507411956787</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">22.0886459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.756986618042</t>
+    <t xml:space="preserve">21.7569847106934</t>
   </si>
   <si>
     <t xml:space="preserve">21.8327941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6811752319336</t>
+    <t xml:space="preserve">21.6811771392822</t>
   </si>
   <si>
     <t xml:space="preserve">21.576940536499</t>
@@ -878,154 +878,154 @@
     <t xml:space="preserve">21.7285575866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7380313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1315670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4158458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4632244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.662223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5624485015869</t>
+    <t xml:space="preserve">21.7380352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4158477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8612232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.463228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6622257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5624504089355</t>
   </si>
   <si>
     <t xml:space="preserve">22.4013557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5529727935791</t>
+    <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
     <t xml:space="preserve">22.5813999176025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6761627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5908737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7948894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138408660889</t>
+    <t xml:space="preserve">22.6761608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5908756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.794885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">21.8422679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4676895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3255481719971</t>
+    <t xml:space="preserve">21.6716995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958957672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4676837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3255462646484</t>
   </si>
   <si>
     <t xml:space="preserve">22.5055923461914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0362510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2068195343018</t>
+    <t xml:space="preserve">22.6951160430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0362491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.998348236084</t>
+    <t xml:space="preserve">22.9983444213867</t>
   </si>
   <si>
     <t xml:space="preserve">23.1310081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5005741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900959014893</t>
+    <t xml:space="preserve">23.5005760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900939941406</t>
   </si>
   <si>
     <t xml:space="preserve">23.2731513977051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1404857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4058151245117</t>
+    <t xml:space="preserve">23.1404876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4058170318604</t>
   </si>
   <si>
     <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.770923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9509658813477</t>
+    <t xml:space="preserve">22.7709217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.950963973999</t>
   </si>
   <si>
     <t xml:space="preserve">23.0646781921387</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7235431671143</t>
+    <t xml:space="preserve">22.7519683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7235412597656</t>
   </si>
   <si>
     <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6477298736572</t>
+    <t xml:space="preserve">22.6477336883545</t>
   </si>
   <si>
     <t xml:space="preserve">22.477165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.87961769104</t>
+    <t xml:space="preserve">22.1834049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8796157836914</t>
   </si>
   <si>
     <t xml:space="preserve">24.1165199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6616687774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783905029297</t>
+    <t xml:space="preserve">23.6616649627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783924102783</t>
   </si>
   <si>
     <t xml:space="preserve">22.90358543396</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">24.0217590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6376991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.685079574585</t>
+    <t xml:space="preserve">24.4955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6850814819336</t>
   </si>
   <si>
     <t xml:space="preserve">24.5903224945068</t>
@@ -1061,37 +1061,37 @@
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1638984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8651275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558727264404</t>
+    <t xml:space="preserve">24.5429382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1639003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8651237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558746337891</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5473976135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915515899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052581787109</t>
+    <t xml:space="preserve">25.5474014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052600860596</t>
   </si>
   <si>
     <t xml:space="preserve">25.4431648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4905452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3863067626953</t>
+    <t xml:space="preserve">25.4905433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3863105773926</t>
   </si>
   <si>
     <t xml:space="preserve">25.3484039306641</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">25.0830745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.727445602417</t>
+    <t xml:space="preserve">25.7274436950684</t>
   </si>
   <si>
     <t xml:space="preserve">25.6611137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9643440246582</t>
+    <t xml:space="preserve">25.9643459320068</t>
   </si>
   <si>
     <t xml:space="preserve">26.3054847717285</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">27.3099422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119510650635</t>
+    <t xml:space="preserve">26.9119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">27.0635662078857</t>
@@ -1133,31 +1133,31 @@
     <t xml:space="preserve">26.9972343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1678047180176</t>
+    <t xml:space="preserve">27.1678009033203</t>
   </si>
   <si>
     <t xml:space="preserve">26.4665775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0591068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0451717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1778354644775</t>
+    <t xml:space="preserve">26.0591087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0451698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1778335571289</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5189743041992</t>
+    <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
     <t xml:space="preserve">25.1115016937256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5379257202148</t>
+    <t xml:space="preserve">25.5379238128662</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359188079834</t>
@@ -1166,58 +1166,58 @@
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9219818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.206262588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8601093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.333911895752</t>
+    <t xml:space="preserve">25.301025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683597564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9219799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2062606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8601112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3339138031006</t>
   </si>
   <si>
     <t xml:space="preserve">26.248628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4381484985352</t>
+    <t xml:space="preserve">26.4381465911865</t>
   </si>
   <si>
     <t xml:space="preserve">24.7987937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3673572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3578796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800651550293</t>
+    <t xml:space="preserve">25.3673553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3578815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800632476807</t>
   </si>
   <si>
     <t xml:space="preserve">25.6232089996338</t>
   </si>
   <si>
-    <t xml:space="preserve">25.774829864502</t>
+    <t xml:space="preserve">25.7748241424561</t>
   </si>
   <si>
     <t xml:space="preserve">25.5947799682617</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">25.7084903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1064853668213</t>
+    <t xml:space="preserve">26.1064872741699</t>
   </si>
   <si>
     <t xml:space="preserve">26.8171882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0540885925293</t>
+    <t xml:space="preserve">27.0540904998779</t>
   </si>
   <si>
     <t xml:space="preserve">27.3857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8695850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222064971924</t>
+    <t xml:space="preserve">25.8695812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222045898438</t>
   </si>
   <si>
     <t xml:space="preserve">25.9169673919678</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8272247314453</t>
+    <t xml:space="preserve">24.0691394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2586574554443</t>
+    <t xml:space="preserve">24.258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167427062988</t>
+    <t xml:space="preserve">25.0167407989502</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693641662598</t>
@@ -1298,46 +1298,46 @@
     <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4855308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5329093933105</t>
+    <t xml:space="preserve">26.4855289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5329055786133</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.769811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9492988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.617639541626</t>
+    <t xml:space="preserve">26.7698097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9492969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
     <t xml:space="preserve">28.8071575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6650199890137</t>
+    <t xml:space="preserve">28.665018081665</t>
   </si>
   <si>
     <t xml:space="preserve">29.3283405303955</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2335777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5394897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2086696624756</t>
+    <t xml:space="preserve">29.2335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5394916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2086715698242</t>
   </si>
   <si>
     <t xml:space="preserve">30.0652751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3042678833008</t>
+    <t xml:space="preserve">30.3042697906494</t>
   </si>
   <si>
     <t xml:space="preserve">29.9696769714355</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">31.2602386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7419929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803489685059</t>
+    <t xml:space="preserve">32.7419891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803527832031</t>
   </si>
   <si>
     <t xml:space="preserve">35.1797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4149398803711</t>
+    <t xml:space="preserve">36.135684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4149436950684</t>
   </si>
   <si>
     <t xml:space="preserve">33.936954498291</t>
@@ -1373,85 +1373,85 @@
     <t xml:space="preserve">34.1759452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9885177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7532997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922943115234</t>
+    <t xml:space="preserve">34.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.753303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922981262207</t>
   </si>
   <si>
     <t xml:space="preserve">35.2275161743164</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0841178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6577072143555</t>
+    <t xml:space="preserve">35.0841217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6576995849609</t>
   </si>
   <si>
     <t xml:space="preserve">35.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4224815368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.374683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4187126159668</t>
+    <t xml:space="preserve">36.422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4187088012695</t>
   </si>
   <si>
     <t xml:space="preserve">36.5658760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8526649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822532653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1168384552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036293029785</t>
+    <t xml:space="preserve">36.852668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822513580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1168441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036312103271</t>
   </si>
   <si>
     <t xml:space="preserve">31.5948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3558311462402</t>
+    <t xml:space="preserve">31.3558330535889</t>
   </si>
   <si>
     <t xml:space="preserve">31.2124404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0287818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935600280762</t>
+    <t xml:space="preserve">33.0287780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935523986816</t>
   </si>
   <si>
     <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7973251342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671379089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6539344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.036319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6061363220215</t>
+    <t xml:space="preserve">34.7973289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671417236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0363235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6061325073242</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627380371094</t>
@@ -1460,19 +1460,19 @@
     <t xml:space="preserve">33.8413543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7495307922363</t>
+    <t xml:space="preserve">34.7495269775391</t>
   </si>
   <si>
     <t xml:space="preserve">35.5621109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0400924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966941833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6614685058594</t>
+    <t xml:space="preserve">36.040096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6614723205566</t>
   </si>
   <si>
     <t xml:space="preserve">39.0035972595215</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">36.2790870666504</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2350616455078</t>
+    <t xml:space="preserve">37.2350540161133</t>
   </si>
   <si>
     <t xml:space="preserve">34.8929214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5583381652832</t>
+    <t xml:space="preserve">34.5583343505859</t>
   </si>
   <si>
     <t xml:space="preserve">33.6979637145996</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">33.2677726745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640075683594</t>
+    <t xml:space="preserve">32.2639999389648</t>
   </si>
   <si>
     <t xml:space="preserve">32.9809837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3633689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7897911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5985946655273</t>
+    <t xml:space="preserve">33.3633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7897872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.837589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5985984802246</t>
   </si>
   <si>
     <t xml:space="preserve">32.5029983520508</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2199783325195</t>
+    <t xml:space="preserve">33.2199745178223</t>
   </si>
   <si>
     <t xml:space="preserve">32.6463966369629</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.072811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7860240936279</t>
+    <t xml:space="preserve">32.0728149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7860202789307</t>
   </si>
   <si>
     <t xml:space="preserve">31.8338222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0690402984619</t>
+    <t xml:space="preserve">31.0690441131592</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250129699707</t>
@@ -1559,46 +1559,46 @@
     <t xml:space="preserve">31.0212459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8816165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357189178467</t>
+    <t xml:space="preserve">31.8816204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357227325439</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709426879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4401264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1055355072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2451629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9621410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3445281982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0137042999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181118011475</t>
+    <t xml:space="preserve">27.7709445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4401245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2489318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1055335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2451610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9621391296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3445262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0137100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181098937988</t>
   </si>
   <si>
     <t xml:space="preserve">29.2049007415771</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">30.4954605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5872898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4438915252686</t>
+    <t xml:space="preserve">29.587287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
     <t xml:space="preserve">29.6828861236572</t>
@@ -1625,31 +1625,31 @@
     <t xml:space="preserve">28.5835189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5759811401367</t>
+    <t xml:space="preserve">26.5759830474854</t>
   </si>
   <si>
     <t xml:space="preserve">26.3847885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2929573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4363574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6313190460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1017665863037</t>
+    <t xml:space="preserve">27.2929592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4363555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6313209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350860595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1017684936523</t>
   </si>
   <si>
     <t xml:space="preserve">26.8627738952637</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">27.4841556549072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0061702728271</t>
+    <t xml:space="preserve">27.0061683654785</t>
   </si>
   <si>
     <t xml:space="preserve">26.0979957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1935920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6237812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2891902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671775817871</t>
+    <t xml:space="preserve">25.6200103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1935939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6237831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.289192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671756744385</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
@@ -1700,34 +1700,34 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.388557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8225135803223</t>
+    <t xml:space="preserve">26.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3885555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
     <t xml:space="preserve">29.874080657959</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1608715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3520660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3080368041992</t>
+    <t xml:space="preserve">30.1608695983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3520641326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.308032989502</t>
   </si>
   <si>
     <t xml:space="preserve">31.4514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4551963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3118057250977</t>
+    <t xml:space="preserve">32.4552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3118019104004</t>
   </si>
   <si>
     <t xml:space="preserve">32.2162094116211</t>
@@ -1745,40 +1745,40 @@
     <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6388549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6484184265137</t>
+    <t xml:space="preserve">30.6388568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.648416519165</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9734497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2851505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4763412475586</t>
+    <t xml:space="preserve">30.9734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2851486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4763431549072</t>
   </si>
   <si>
     <t xml:space="preserve">30.2277908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9983577728271</t>
+    <t xml:space="preserve">29.9983558654785</t>
   </si>
   <si>
     <t xml:space="preserve">29.8262825012207</t>
@@ -1787,28 +1787,28 @@
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352073669434</t>
+    <t xml:space="preserve">30.438102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935209274292</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7115650177002</t>
+    <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
     <t xml:space="preserve">28.812952041626</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5203742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4879245758057</t>
+    <t xml:space="preserve">29.5203704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.487922668457</t>
   </si>
   <si>
     <t xml:space="preserve">28.717357635498</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">28.6533889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3058414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637676239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5182342529297</t>
+    <t xml:space="preserve">28.3058433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637657165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5182323455811</t>
   </si>
   <si>
     <t xml:space="preserve">27.8038291931152</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">27.6493625640869</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776020050049</t>
+    <t xml:space="preserve">27.9776039123535</t>
   </si>
   <si>
     <t xml:space="preserve">27.5142078399658</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">27.7845230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548343658447</t>
+    <t xml:space="preserve">28.0548362731934</t>
   </si>
   <si>
     <t xml:space="preserve">27.9969100952148</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">28.4989261627197</t>
   </si>
   <si>
-    <t xml:space="preserve">28.247917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3251514434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8424453735352</t>
+    <t xml:space="preserve">28.2479190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3251495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8424472808838</t>
   </si>
   <si>
     <t xml:space="preserve">27.900369644165</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">28.0934524536133</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6340808868408</t>
+    <t xml:space="preserve">28.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">29.1167869567871</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">28.8850898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2712535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8311901092529</t>
+    <t xml:space="preserve">29.2712554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8311920166016</t>
   </si>
   <si>
     <t xml:space="preserve">29.9084224700928</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8505001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2173538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9856548309326</t>
+    <t xml:space="preserve">29.8504981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2173557281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9856567382812</t>
   </si>
   <si>
     <t xml:space="preserve">30.6807556152344</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">29.3677959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4836463928223</t>
+    <t xml:space="preserve">29.4836444854736</t>
   </si>
   <si>
     <t xml:space="preserve">29.174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4257183074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2519454956055</t>
+    <t xml:space="preserve">29.4257202148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2519435882568</t>
   </si>
   <si>
     <t xml:space="preserve">29.464334487915</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">27.1666564941406</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542655944824</t>
+    <t xml:space="preserve">26.9542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2825050354004</t>
+    <t xml:space="preserve">27.282506942749</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">26.5101776123047</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8810615539551</t>
+    <t xml:space="preserve">27.8810596466064</t>
   </si>
   <si>
     <t xml:space="preserve">28.1899948120117</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">27.938985824585</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4369735717773</t>
+    <t xml:space="preserve">27.4369716644287</t>
   </si>
   <si>
     <t xml:space="preserve">27.2631988525391</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">26.6260280609131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.035530090332</t>
+    <t xml:space="preserve">27.4176654815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0355281829834</t>
   </si>
   <si>
     <t xml:space="preserve">27.0894260406494</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">27.0508079528809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4755897521973</t>
+    <t xml:space="preserve">27.4755878448486</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">27.591438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">27.610746383667</t>
+    <t xml:space="preserve">27.6107482910156</t>
   </si>
   <si>
     <t xml:space="preserve">27.6879806518555</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">25.9309349060059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8537006378174</t>
+    <t xml:space="preserve">25.8536987304688</t>
   </si>
   <si>
     <t xml:space="preserve">25.8730087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3018169403076</t>
+    <t xml:space="preserve">27.301815032959</t>
   </si>
   <si>
     <t xml:space="preserve">27.4562835693359</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">26.7032604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7459049224854</t>
+    <t xml:space="preserve">27.745906829834</t>
   </si>
   <si>
     <t xml:space="preserve">27.1087322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1320686340332</t>
+    <t xml:space="preserve">28.1320667266846</t>
   </si>
   <si>
     <t xml:space="preserve">28.3830757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9430122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4064102172852</t>
+    <t xml:space="preserve">28.9430141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4064083099365</t>
   </si>
   <si>
     <t xml:space="preserve">28.8078556060791</t>
@@ -2096,61 +2096,61 @@
     <t xml:space="preserve">28.9816303253174</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1360950469971</t>
+    <t xml:space="preserve">29.1360969543457</t>
   </si>
   <si>
     <t xml:space="preserve">28.7499313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8271656036377</t>
+    <t xml:space="preserve">28.8271636962891</t>
   </si>
   <si>
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6147727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133312225342</t>
+    <t xml:space="preserve">28.5954647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6147747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133293151855</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9357852935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4571113586426</t>
+    <t xml:space="preserve">31.9357891082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4571075439453</t>
   </si>
   <si>
     <t xml:space="preserve">31.8585548400879</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2213802337646</t>
+    <t xml:space="preserve">31.2213821411133</t>
   </si>
   <si>
     <t xml:space="preserve">31.1827659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">31.665470123291</t>
+    <t xml:space="preserve">31.6654739379883</t>
   </si>
   <si>
     <t xml:space="preserve">32.1674842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2600002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5882396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.047607421875</t>
+    <t xml:space="preserve">31.2600021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5882434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0476093292236</t>
   </si>
   <si>
     <t xml:space="preserve">30.9510707855225</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">31.1248435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3565406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8545265197754</t>
+    <t xml:space="preserve">31.356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.854528427124</t>
   </si>
   <si>
     <t xml:space="preserve">30.8931427001953</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">30.7000598907471</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0170478820801</t>
+    <t xml:space="preserve">33.0170440673828</t>
   </si>
   <si>
     <t xml:space="preserve">33.3645935058594</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">33.885913848877</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8899459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0251007080078</t>
+    <t xml:space="preserve">34.8899421691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0251045227051</t>
   </si>
   <si>
     <t xml:space="preserve">35.9712028503418</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">35.8167381286621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9864845275879</t>
+    <t xml:space="preserve">34.9864883422852</t>
   </si>
   <si>
     <t xml:space="preserve">33.2873611450195</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">31.8778629302979</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3605690002441</t>
+    <t xml:space="preserve">32.3605651855469</t>
   </si>
   <si>
     <t xml:space="preserve">33.3839073181152</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">32.901195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2447204589844</t>
+    <t xml:space="preserve">32.2447166442871</t>
   </si>
   <si>
     <t xml:space="preserve">32.5343437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4764137268066</t>
+    <t xml:space="preserve">32.4764175415039</t>
   </si>
   <si>
     <t xml:space="preserve">33.6928329467773</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">29.3871040344238</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8118839263916</t>
+    <t xml:space="preserve">29.811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9623222351074</t>
@@ -2291,22 +2291,22 @@
     <t xml:space="preserve">30.0049648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0274715423584</t>
+    <t xml:space="preserve">26.027473449707</t>
   </si>
   <si>
     <t xml:space="preserve">26.2784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2937622070312</t>
+    <t xml:space="preserve">25.2937602996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.1240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5407390594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931934356689</t>
+    <t xml:space="preserve">24.5407409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1931915283203</t>
   </si>
   <si>
     <t xml:space="preserve">22.9767761230469</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">25.8150844573975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1006774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7225685119629</t>
+    <t xml:space="preserve">25.100679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7225704193115</t>
   </si>
   <si>
     <t xml:space="preserve">26.8384170532227</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4442005157471</t>
+    <t xml:space="preserve">24.4441986083984</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075965881348</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">25.6220016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300582885742</t>
+    <t xml:space="preserve">26.3943309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300563812256</t>
   </si>
   <si>
     <t xml:space="preserve">27.8231353759766</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">26.2398624420166</t>
   </si>
   <si>
-    <t xml:space="preserve">25.718542098999</t>
+    <t xml:space="preserve">25.7185401916504</t>
   </si>
   <si>
     <t xml:space="preserve">25.4482288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.583381652832</t>
+    <t xml:space="preserve">25.5833835601807</t>
   </si>
   <si>
     <t xml:space="preserve">26.5487937927246</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">26.4522533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8923149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0660877227783</t>
+    <t xml:space="preserve">25.8923168182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.066089630127</t>
   </si>
   <si>
     <t xml:space="preserve">26.9735774993896</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">26.5681037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5061511993408</t>
+    <t xml:space="preserve">25.5061531066895</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903026580811</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5254592895508</t>
+    <t xml:space="preserve">25.5254573822021</t>
   </si>
   <si>
     <t xml:space="preserve">24.4055843353271</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">24.3283500671387</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8303623199463</t>
+    <t xml:space="preserve">24.8303604125977</t>
   </si>
   <si>
     <t xml:space="preserve">24.3862743377686</t>
@@ -2474,16 +2474,16 @@
     <t xml:space="preserve">24.154577255249</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0387287139893</t>
+    <t xml:space="preserve">24.0387268066406</t>
   </si>
   <si>
     <t xml:space="preserve">23.9035701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3822479248047</t>
+    <t xml:space="preserve">23.1505489349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3822460174561</t>
   </si>
   <si>
     <t xml:space="preserve">23.073314666748</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">23.7877197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2704257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6372833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.081371307373</t>
+    <t xml:space="preserve">24.2704238891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6372814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">24.3476600646973</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">25.119987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9462127685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.811056137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5986652374268</t>
+    <t xml:space="preserve">24.9462146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8110580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5986633300781</t>
   </si>
   <si>
     <t xml:space="preserve">24.7338237762451</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269065856934</t>
+    <t xml:space="preserve">24.9269046783447</t>
   </si>
   <si>
     <t xml:space="preserve">26.7611846923828</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">26.2205562591553</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6179733276367</t>
+    <t xml:space="preserve">24.6179752349854</t>
   </si>
   <si>
     <t xml:space="preserve">24.463508605957</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">25.2358360290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1392955780029</t>
+    <t xml:space="preserve">25.1392974853516</t>
   </si>
   <si>
     <t xml:space="preserve">25.6413078308105</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">26.7804927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6067199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0467834472656</t>
+    <t xml:space="preserve">26.6067180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.046781539917</t>
   </si>
   <si>
     <t xml:space="preserve">26.2591743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4136371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8343906402588</t>
+    <t xml:space="preserve">26.4136352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8343925476074</t>
   </si>
   <si>
     <t xml:space="preserve">25.7571582794189</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">24.5600509643555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7724361419678</t>
+    <t xml:space="preserve">24.8689823150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7724380493164</t>
   </si>
   <si>
     <t xml:space="preserve">30.1401233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7620143890381</t>
+    <t xml:space="preserve">31.7620182037354</t>
   </si>
   <si>
     <t xml:space="preserve">32.1481781005859</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">31.8392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9744033813477</t>
+    <t xml:space="preserve">31.9743995666504</t>
   </si>
   <si>
     <t xml:space="preserve">31.9550933837891</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">33.2680549621582</t>
   </si>
   <si>
-    <t xml:space="preserve">34.175537109375</t>
+    <t xml:space="preserve">34.1755409240723</t>
   </si>
   <si>
     <t xml:space="preserve">34.1562347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245338439941</t>
+    <t xml:space="preserve">33.9245300292969</t>
   </si>
   <si>
     <t xml:space="preserve">35.1795654296875</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">35.3726501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3879318237305</t>
+    <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
     <t xml:space="preserve">34.5810050964355</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">34.7547874450684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6429595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0444145202637</t>
+    <t xml:space="preserve">35.6429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0444107055664</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">32.2640228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">32.495719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0556640625</t>
+    <t xml:space="preserve">32.4957237243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0556678771973</t>
   </si>
   <si>
     <t xml:space="preserve">34.0596885681152</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5383682250977</t>
+    <t xml:space="preserve">33.5383720397949</t>
   </si>
   <si>
     <t xml:space="preserve">34.291389465332</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">33.7314529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3066673278809</t>
+    <t xml:space="preserve">33.3066711425781</t>
   </si>
   <si>
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908226013184</t>
+    <t xml:space="preserve">33.1908187866211</t>
   </si>
   <si>
     <t xml:space="preserve">32.9591217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8971748352051</t>
+    <t xml:space="preserve">31.8971710205078</t>
   </si>
   <si>
     <t xml:space="preserve">32.0709457397461</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">34.4458541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0983047485352</t>
+    <t xml:space="preserve">34.0983085632324</t>
   </si>
   <si>
     <t xml:space="preserve">33.5962905883789</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">33.4418296813965</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8818893432617</t>
+    <t xml:space="preserve">32.881893157959</t>
   </si>
   <si>
     <t xml:space="preserve">32.611572265625</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">35.8360443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4000129699707</t>
+    <t xml:space="preserve">37.4000091552734</t>
   </si>
   <si>
     <t xml:space="preserve">36.4925270080566</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043510437012</t>
+    <t xml:space="preserve">35.6043472290039</t>
   </si>
   <si>
     <t xml:space="preserve">35.565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3919563293457</t>
+    <t xml:space="preserve">35.391960144043</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">39.2149848937988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9527244567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1458015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7057418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4587631225586</t>
+    <t xml:space="preserve">40.9527206420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7057456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4587669372559</t>
   </si>
   <si>
     <t xml:space="preserve">41.9567489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5319671630859</t>
+    <t xml:space="preserve">41.5319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">41.3388862609863</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244850158691</t>
+    <t xml:space="preserve">40.6244812011719</t>
   </si>
   <si>
     <t xml:space="preserve">40.5665550231934</t>
@@ -2879,40 +2879,40 @@
     <t xml:space="preserve">41.0878791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2809638977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3236083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4008369445801</t>
+    <t xml:space="preserve">41.2809600830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3236045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4008331298828</t>
   </si>
   <si>
     <t xml:space="preserve">42.6711540222168</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8256187438965</t>
+    <t xml:space="preserve">42.8256225585938</t>
   </si>
   <si>
     <t xml:space="preserve">43.8875694274902</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5786399841309</t>
+    <t xml:space="preserve">43.5786437988281</t>
   </si>
   <si>
     <t xml:space="preserve">43.9841156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6172561645508</t>
+    <t xml:space="preserve">43.6172523498535</t>
   </si>
   <si>
     <t xml:space="preserve">43.8489532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3743057250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3244361877441</t>
+    <t xml:space="preserve">45.3743019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3244323730469</t>
   </si>
   <si>
     <t xml:space="preserve">49.7669219970703</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">48.463623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2665138244629</t>
+    <t xml:space="preserve">47.2665100097656</t>
   </si>
   <si>
     <t xml:space="preserve">48.7049713134766</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">47.4982109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4748687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8183898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0694007873535</t>
+    <t xml:space="preserve">46.4748725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8183937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0694046020508</t>
   </si>
   <si>
     <t xml:space="preserve">46.5521049499512</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">47.1120414733887</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4016647338867</t>
+    <t xml:space="preserve">47.401668548584</t>
   </si>
   <si>
     <t xml:space="preserve">48.01953125</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">48.3188056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1876754760742</t>
+    <t xml:space="preserve">49.1876792907715</t>
   </si>
   <si>
     <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6912879943848</t>
+    <t xml:space="preserve">47.691291809082</t>
   </si>
   <si>
     <t xml:space="preserve">47.7878303527832</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3051223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6140594482422</t>
+    <t xml:space="preserve">47.3051261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6140556335449</t>
   </si>
   <si>
     <t xml:space="preserve">48.2705345153809</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5392532348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8457565307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2842178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6221122741699</t>
+    <t xml:space="preserve">50.539249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.845760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">49.6703834533691</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4209747314453</t>
+    <t xml:space="preserve">47.420970916748</t>
   </si>
   <si>
     <t xml:space="preserve">47.9422950744629</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809150695801</t>
+    <t xml:space="preserve">47.9809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">49.3807563781738</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">50.2978935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4909820556641</t>
+    <t xml:space="preserve">50.4909782409668</t>
   </si>
   <si>
     <t xml:space="preserve">54.4974365234375</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">48.6567001342773</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0774574279785</t>
+    <t xml:space="preserve">48.0774536132812</t>
   </si>
   <si>
     <t xml:space="preserve">48.173999786377</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9616050720215</t>
+    <t xml:space="preserve">47.9616088867188</t>
   </si>
   <si>
     <t xml:space="preserve">47.903678894043</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996505737305</t>
+    <t xml:space="preserve">46.8996543884277</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590240478516</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">45.5287742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3011016845703</t>
+    <t xml:space="preserve">46.301097869873</t>
   </si>
   <si>
     <t xml:space="preserve">46.5907173156738</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">45.6446228027344</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8956298828125</t>
+    <t xml:space="preserve">45.8956260681152</t>
   </si>
   <si>
     <t xml:space="preserve">46.165943145752</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149322509766</t>
+    <t xml:space="preserve">45.9149360656738</t>
   </si>
   <si>
     <t xml:space="preserve">45.3163795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4129219055176</t>
+    <t xml:space="preserve">45.4129257202148</t>
   </si>
   <si>
     <t xml:space="preserve">45.4322319030762</t>
@@ -3140,22 +3140,22 @@
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699714660645</t>
+    <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9945983886719</t>
+    <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
     <t xml:space="preserve">49.429027557373</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5875244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1321754455566</t>
+    <t xml:space="preserve">50.5875205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1321792602539</t>
   </si>
   <si>
     <t xml:space="preserve">51.6977462768555</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">60.1450843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9174194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7106513977051</t>
+    <t xml:space="preserve">60.9174156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7106552124023</t>
   </si>
   <si>
     <t xml:space="preserve">60.6277923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">61.255313873291</t>
+    <t xml:space="preserve">61.2553100585938</t>
   </si>
   <si>
     <t xml:space="preserve">60.5312538146973</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">56.2834434509277</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4354858398438</t>
+    <t xml:space="preserve">53.4354820251465</t>
   </si>
   <si>
     <t xml:space="preserve">54.4491653442383</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">53.9664611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7870559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5802955627441</t>
+    <t xml:space="preserve">54.7870597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5802917480469</t>
   </si>
   <si>
     <t xml:space="preserve">54.0147323608398</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">54.9318733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4282608032227</t>
+    <t xml:space="preserve">56.4282569885254</t>
   </si>
   <si>
     <t xml:space="preserve">55.0284156799316</t>
@@ -3257,40 +3257,40 @@
     <t xml:space="preserve">57.345401763916</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5038909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6004295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.965690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0139579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3035850524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3864402770996</t>
+    <t xml:space="preserve">58.5038871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6004333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9656867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0139541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.303581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3864440917969</t>
   </si>
   <si>
     <t xml:space="preserve">58.6969680786133</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0420913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4073524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.221492767334</t>
+    <t xml:space="preserve">56.0420875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4073486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2214965820312</t>
   </si>
   <si>
     <t xml:space="preserve">54.0630035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2287178039551</t>
+    <t xml:space="preserve">52.2287216186523</t>
   </si>
   <si>
     <t xml:space="preserve">52.0839080810547</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">53.1458587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4427108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8288803100586</t>
+    <t xml:space="preserve">50.4427070617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8288764953613</t>
   </si>
   <si>
     <t xml:space="preserve">51.8908271789551</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">50.0565490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2359466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.483757019043</t>
+    <t xml:space="preserve">49.2359504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4837532043457</t>
   </si>
   <si>
     <t xml:space="preserve">51.8425559997559</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1184959411621</t>
+    <t xml:space="preserve">51.1184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">52.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1804466247559</t>
+    <t xml:space="preserve">52.1804504394531</t>
   </si>
   <si>
     <t xml:space="preserve">50.3461685180664</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">51.4563941955566</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9254188537598</t>
+    <t xml:space="preserve">50.9254150390625</t>
   </si>
   <si>
     <t xml:space="preserve">50.7806053161621</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">49.7186508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0074501037598</t>
+    <t xml:space="preserve">45.0074462890625</t>
   </si>
   <si>
     <t xml:space="preserve">46.3976440429688</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423439025879</t>
+    <t xml:space="preserve">41.2423477172852</t>
   </si>
   <si>
     <t xml:space="preserve">40.4893264770508</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">49.5738410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8771476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219573974609</t>
+    <t xml:space="preserve">50.8771438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219535827637</t>
   </si>
   <si>
     <t xml:space="preserve">49.9117393493652</t>
@@ -3425,22 +3425,22 @@
     <t xml:space="preserve">44.119270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6253089904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0348091125488</t>
+    <t xml:space="preserve">45.6253128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0348129272461</t>
   </si>
   <si>
     <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1578903198242</t>
+    <t xml:space="preserve">44.157886505127</t>
   </si>
   <si>
     <t xml:space="preserve">43.4627952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1254539489746</t>
+    <t xml:space="preserve">44.1254501342773</t>
   </si>
   <si>
     <t xml:space="preserve">42.3908386230469</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.444766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4312858581543</t>
+    <t xml:space="preserve">46.4447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.431282043457</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9380226135254</t>
+    <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
     <t xml:space="preserve">45.6456756591797</t>
@@ -3482,22 +3482,22 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9995727539062</t>
+    <t xml:space="preserve">41.0070457458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9995765686035</t>
   </si>
   <si>
     <t xml:space="preserve">40.3054046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1360054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7012176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766250610352</t>
+    <t xml:space="preserve">39.1360015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7012138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766212463379</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">41.9620590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8586006164551</t>
+    <t xml:space="preserve">42.8586044311523</t>
   </si>
   <si>
     <t xml:space="preserve">45.0025062561035</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">49.1636276245117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1381301879883</t>
+    <t xml:space="preserve">50.1381340026855</t>
   </si>
   <si>
     <t xml:space="preserve">50.8202819824219</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">51.7460556030273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9177322387695</t>
+    <t xml:space="preserve">50.9177284240723</t>
   </si>
   <si>
     <t xml:space="preserve">51.5511589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5488891601562</t>
+    <t xml:space="preserve">53.548885345459</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517150878906</t>
+    <t xml:space="preserve">55.3517189025879</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">55.8389663696289</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0338706970215</t>
+    <t xml:space="preserve">56.0338668823242</t>
   </si>
   <si>
     <t xml:space="preserve">54.3772125244141</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4004402160645</t>
+    <t xml:space="preserve">55.4004440307617</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">49.7970504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3562622070312</t>
+    <t xml:space="preserve">51.356258392334</t>
   </si>
   <si>
     <t xml:space="preserve">50.8690071105957</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">50.7715530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0151824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384140014648</t>
+    <t xml:space="preserve">51.0151786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384101867676</t>
   </si>
   <si>
     <t xml:space="preserve">51.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5998802185059</t>
+    <t xml:space="preserve">51.5998840332031</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
@@ -3665,10 +3665,10 @@
     <t xml:space="preserve">50.3817596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8015975952148</t>
+    <t xml:space="preserve">47.8480529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8015937805176</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">48.7738265991211</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7311096191406</t>
+    <t xml:space="preserve">47.7311134338379</t>
   </si>
   <si>
     <t xml:space="preserve">49.9919548034668</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483291625977</t>
+    <t xml:space="preserve">49.7483329772949</t>
   </si>
   <si>
     <t xml:space="preserve">48.4522399902344</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">49.3585319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">49.455982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3029899597168</t>
+    <t xml:space="preserve">49.4559783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3029937744141</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242240905762</t>
+    <t xml:space="preserve">60.2242279052734</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
@@ -3737,28 +3737,28 @@
     <t xml:space="preserve">55.1568145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6927909851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5698432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.152271270752</t>
+    <t xml:space="preserve">55.6927947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5698394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1522750854492</t>
   </si>
   <si>
     <t xml:space="preserve">60.8576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0038261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8111991882324</t>
+    <t xml:space="preserve">61.0038299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8111953735352</t>
   </si>
   <si>
     <t xml:space="preserve">59.6395263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8599281311035</t>
+    <t xml:space="preserve">58.8599243164062</t>
   </si>
   <si>
     <t xml:space="preserve">59.2497215270996</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">57.9828758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4213981628418</t>
+    <t xml:space="preserve">58.4214019775391</t>
   </si>
   <si>
     <t xml:space="preserve">59.6882514953613</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">62.319408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0502853393555</t>
+    <t xml:space="preserve">63.0502815246582</t>
   </si>
   <si>
     <t xml:space="preserve">61.3936309814453</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4842681884766</t>
+    <t xml:space="preserve">67.4842758178711</t>
   </si>
   <si>
     <t xml:space="preserve">68.1176910400391</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">69.8230743408203</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3590469360352</t>
+    <t xml:space="preserve">70.3590393066406</t>
   </si>
   <si>
     <t xml:space="preserve">68.9460220336914</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">68.410041809082</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8740692138672</t>
+    <t xml:space="preserve">67.8740615844727</t>
   </si>
   <si>
     <t xml:space="preserve">68.3125915527344</t>
   </si>
   <si>
-    <t xml:space="preserve">67.1919097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8973007202148</t>
+    <t xml:space="preserve">67.1919174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8972930908203</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">65.4865341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5817184448242</t>
+    <t xml:space="preserve">67.5817260742188</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3845,25 +3845,25 @@
     <t xml:space="preserve">66.509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1199569702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8995742797852</t>
+    <t xml:space="preserve">66.1199645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8995666503906</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6536712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0434646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6514053344727</t>
+    <t xml:space="preserve">66.5584869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6536636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0434722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6513977050781</t>
   </si>
   <si>
     <t xml:space="preserve">71.7233505249023</t>
@@ -3875,22 +3875,22 @@
     <t xml:space="preserve">71.528450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6978607177734</t>
+    <t xml:space="preserve">72.6978530883789</t>
   </si>
   <si>
     <t xml:space="preserve">75.6700897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">75.0366516113281</t>
+    <t xml:space="preserve">75.0366592407227</t>
   </si>
   <si>
     <t xml:space="preserve">74.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4032363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.7188110351562</t>
+    <t xml:space="preserve">74.4032287597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.7188034057617</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">77.3754653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">74.987922668457</t>
+    <t xml:space="preserve">74.9879302978516</t>
   </si>
   <si>
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627166748047</t>
+    <t xml:space="preserve">77.8627090454102</t>
   </si>
   <si>
     <t xml:space="preserve">79.3244705200195</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295623779297</t>
+    <t xml:space="preserve">78.0088958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295700073242</t>
   </si>
   <si>
     <t xml:space="preserve">77.424186706543</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.032112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4474105834961</t>
+    <t xml:space="preserve">78.3012313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0321197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
@@ -3962,25 +3962,25 @@
     <t xml:space="preserve">77.4729156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9647064208984</t>
+    <t xml:space="preserve">73.964714050293</t>
   </si>
   <si>
     <t xml:space="preserve">74.4519653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">71.82080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.9601669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8162689208984</t>
+    <t xml:space="preserve">71.8207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.9601593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8162612915039</t>
   </si>
   <si>
     <t xml:space="preserve">77.7165451049805</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964157104492</t>
+    <t xml:space="preserve">80.3964233398438</t>
   </si>
   <si>
     <t xml:space="preserve">80.2989730834961</t>
@@ -3992,16 +3992,16 @@
     <t xml:space="preserve">81.4683685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8581771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1924285888672</t>
+    <t xml:space="preserve">81.8581695556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7607192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2689361572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1924362182617</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">86.2434234619141</t>
   </si>
   <si>
-    <t xml:space="preserve">87.705192565918</t>
+    <t xml:space="preserve">87.7051849365234</t>
   </si>
   <si>
     <t xml:space="preserve">90.2876129150391</t>
@@ -4037,19 +4037,19 @@
     <t xml:space="preserve">89.3618392944336</t>
   </si>
   <si>
-    <t xml:space="preserve">86.0972518920898</t>
+    <t xml:space="preserve">86.0972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360580444336</t>
+    <t xml:space="preserve">88.4360656738281</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">84.4893264770508</t>
+    <t xml:space="preserve">84.4893341064453</t>
   </si>
   <si>
     <t xml:space="preserve">82.1017990112305</t>
@@ -4061,19 +4061,19 @@
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559112548828</t>
+    <t xml:space="preserve">83.8559036254883</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0043563842773</t>
+    <t xml:space="preserve">82.0043487548828</t>
   </si>
   <si>
     <t xml:space="preserve">81.4196472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2270202636719</t>
+    <t xml:space="preserve">79.2270278930664</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
@@ -4082,22 +4082,22 @@
     <t xml:space="preserve">79.9091720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5299453735352</t>
+    <t xml:space="preserve">81.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096496582031</t>
+    <t xml:space="preserve">77.1096420288086</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.632194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830841064453</t>
+    <t xml:space="preserve">78.6322021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618179321289</t>
+    <t xml:space="preserve">79.7618255615234</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370239257812</t>
+    <t xml:space="preserve">81.1370315551758</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909713745117</t>
+    <t xml:space="preserve">83.6909790039062</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.628173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317169189453</t>
+    <t xml:space="preserve">81.6281661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317092895508</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.07421875</t>
+    <t xml:space="preserve">79.0742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4184,22 +4184,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9268798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0959548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326644897461</t>
+    <t xml:space="preserve">78.926872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326721191406</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853256225586</t>
+    <t xml:space="preserve">75.6853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928970336914</t>
+    <t xml:space="preserve">72.4928894042969</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870895385742</t>
+    <t xml:space="preserve">75.5870971679688</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402282714844</t>
+    <t xml:space="preserve">72.6402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176910400391</t>
+    <t xml:space="preserve">71.1176834106445</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597076416016</t>
+    <t xml:space="preserve">71.5597152709961</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022247314453</t>
+    <t xml:space="preserve">72.3946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022171020508</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212265014648</t>
+    <t xml:space="preserve">70.9212188720703</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4295,16 +4295,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5419998168945</t>
+    <t xml:space="preserve">72.5420074462891</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389343261719</t>
+    <t xml:space="preserve">73.4260711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.827018737793</t>
+    <t xml:space="preserve">67.8270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247695922852</t>
+    <t xml:space="preserve">70.7247772216797</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.5460205078125</t>
+    <t xml:space="preserve">69.546028137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698593139648</t>
+    <t xml:space="preserve">73.7698669433594</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4361,19 +4361,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065841674805</t>
+    <t xml:space="preserve">77.6007919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065765380859</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481307983398</t>
+    <t xml:space="preserve">77.7481384277344</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4394,25 +4394,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.9309005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238143920898</t>
+    <t xml:space="preserve">75.930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238067626953</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344360351562</t>
+    <t xml:space="preserve">75.7344436645508</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.905143737793</t>
+    <t xml:space="preserve">82.9051513671875</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046737670898</t>
+    <t xml:space="preserve">85.7046661376953</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851791381836</t>
+    <t xml:space="preserve">86.7851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542541503906</t>
+    <t xml:space="preserve">82.9542617797852</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489471435547</t>
+    <t xml:space="preserve">83.2489547729492</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4484,16 +4484,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312393188477</t>
+    <t xml:space="preserve">84.2312316894531</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507186889648</t>
+    <t xml:space="preserve">82.5613479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507263183594</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338272094727</t>
+    <t xml:space="preserve">89.6338195800781</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581359863281</t>
+    <t xml:space="preserve">91.0581436157227</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.857666015625</t>
+    <t xml:space="preserve">93.8576736450195</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4547,16 +4547,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747375488281</t>
+    <t xml:space="preserve">102.845596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.827896118164</t>
+    <t xml:space="preserve">103.82788848877</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034027099609</t>
+    <t xml:space="preserve">109.034019470215</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525169372559</t>
+    <t xml:space="preserve">109.525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.631439208984</t>
+    <t xml:space="preserve">103.63143157959</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4625,16 +4625,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122573852539</t>
+    <t xml:space="preserve">102.158004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122581481934</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987426757812</t>
+    <t xml:space="preserve">99.8987350463867</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518661499023</t>
+    <t xml:space="preserve">96.3625030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518737792969</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2642669677734</t>
+    <t xml:space="preserve">96.264274597168</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5589599609375</t>
+    <t xml:space="preserve">96.558967590332</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4697,16 +4697,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890609741211</t>
+    <t xml:space="preserve">94.8890686035156</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488082885742</t>
+    <t xml:space="preserve">94.7417144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488159179688</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5622,6 +5622,9 @@
   </si>
   <si>
     <t xml:space="preserve">90.1600036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5</t>
   </si>
 </sst>
 </file>
@@ -70622,7 +70625,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495138889</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>341028</v>
@@ -70643,6 +70646,32 @@
         <v>1869</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.649525463</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>426505</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>90.0999984741211</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>87.5400009155273</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>89.620002746582</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="1871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1872">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807546615601</t>
+    <t xml:space="preserve">15.1807565689087</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537855148315</t>
+    <t xml:space="preserve">14.8537864685059</t>
   </si>
   <si>
     <t xml:space="preserve">14.4801063537598</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289264678955</t>
+    <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
     <t xml:space="preserve">15.0406265258789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3208837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022031784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.44273853302</t>
+    <t xml:space="preserve">15.3208856582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022012710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4427375793457</t>
   </si>
   <si>
     <t xml:space="preserve">14.6389198303223</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">14.0410318374634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3212919235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.33997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7697105407715</t>
+    <t xml:space="preserve">14.3212900161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3399753570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7697086334229</t>
   </si>
   <si>
     <t xml:space="preserve">14.3866853713989</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">13.9943208694458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240531921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036640167236</t>
+    <t xml:space="preserve">14.424054145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849786758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036630630493</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338026046753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7051248550415</t>
+    <t xml:space="preserve">12.7051258087158</t>
   </si>
   <si>
     <t xml:space="preserve">12.4155235290527</t>
@@ -122,31 +122,31 @@
     <t xml:space="preserve">12.8172292709351</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459041595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722269058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645895004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057750701904</t>
+    <t xml:space="preserve">13.5459051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057760238647</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777494430542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.919584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0316905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7607717514038</t>
+    <t xml:space="preserve">14.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195852279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0316896438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7607727050781</t>
   </si>
   <si>
     <t xml:space="preserve">13.8355093002319</t>
@@ -155,28 +155,28 @@
     <t xml:space="preserve">14.1064262390137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2372150421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2558965682983</t>
+    <t xml:space="preserve">14.2372140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558975219727</t>
   </si>
   <si>
     <t xml:space="preserve">15.4143056869507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2461490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769397735596</t>
+    <t xml:space="preserve">15.601146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060199737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769369125366</t>
   </si>
   <si>
     <t xml:space="preserve">15.479700088501</t>
@@ -188,43 +188,43 @@
     <t xml:space="preserve">15.5450954437256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945667266846</t>
+    <t xml:space="preserve">15.6945648193359</t>
   </si>
   <si>
     <t xml:space="preserve">15.6104888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983854293823</t>
+    <t xml:space="preserve">15.498384475708</t>
   </si>
   <si>
     <t xml:space="preserve">15.0873346328735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.993914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202344894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302268981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918064117432</t>
+    <t xml:space="preserve">14.99391746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918045043945</t>
   </si>
   <si>
     <t xml:space="preserve">15.7225923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7412776947021</t>
+    <t xml:space="preserve">15.7412757873535</t>
   </si>
   <si>
     <t xml:space="preserve">15.8253545761108</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3017978668213</t>
+    <t xml:space="preserve">16.3017959594727</t>
   </si>
   <si>
     <t xml:space="preserve">16.3952159881592</t>
@@ -242,64 +242,64 @@
     <t xml:space="preserve">16.4139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924537658691</t>
+    <t xml:space="preserve">16.2924556732178</t>
   </si>
   <si>
     <t xml:space="preserve">16.3671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2177181243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3765316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3391628265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.273775100708</t>
+    <t xml:space="preserve">16.0215377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2177200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3765335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3391647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737712860107</t>
   </si>
   <si>
     <t xml:space="preserve">16.4325847625732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6100845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4419269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889869689941</t>
+    <t xml:space="preserve">16.6100826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4419288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889888763428</t>
   </si>
   <si>
     <t xml:space="preserve">16.648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5548648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207427978516</t>
+    <t xml:space="preserve">16.5548686981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6866264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054500579834</t>
+    <t xml:space="preserve">16.6866245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054481506348</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995662689209</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">16.5454540252686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6583938598633</t>
+    <t xml:space="preserve">16.658390045166</t>
   </si>
   <si>
     <t xml:space="preserve">16.8277988433838</t>
@@ -317,37 +317,37 @@
     <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.689003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5831031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.253698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642757415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290098190308</t>
+    <t xml:space="preserve">16.2254619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407793045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.583101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2536964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290088653564</t>
   </si>
   <si>
     <t xml:space="preserve">14.8796157836914</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">15.2090177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101861953735</t>
+    <t xml:space="preserve">15.5101881027222</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854995727539</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">14.6443271636963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9172620773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384225845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348917007446</t>
+    <t xml:space="preserve">14.9172611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513586044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195989608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348926544189</t>
   </si>
   <si>
     <t xml:space="preserve">15.5854787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9054679870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.990177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478315353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337034225464</t>
+    <t xml:space="preserve">15.9054698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.547830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.933705329895</t>
   </si>
   <si>
     <t xml:space="preserve">15.6701831817627</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">15.6419506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9148836135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278167724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2725200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3195781707764</t>
+    <t xml:space="preserve">15.9148797988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2725219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3195762634277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819290161133</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">16.1595821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
+    <t xml:space="preserve">16.3760433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
   </si>
   <si>
     <t xml:space="preserve">16.4607486724854</t>
@@ -455,40 +455,40 @@
     <t xml:space="preserve">16.6301593780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4701633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9877948760986</t>
+    <t xml:space="preserve">16.4701614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7807388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9877967834473</t>
   </si>
   <si>
     <t xml:space="preserve">17.0160312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9407348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372097015381</t>
+    <t xml:space="preserve">16.9407367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9783840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.846622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960353851318</t>
+    <t xml:space="preserve">16.978385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8466186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960391998291</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
@@ -497,40 +497,40 @@
     <t xml:space="preserve">16.7713298797607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8089752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9030895233154</t>
+    <t xml:space="preserve">16.8089790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842678070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9030914306641</t>
   </si>
   <si>
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972038269043</t>
+    <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
     <t xml:space="preserve">17.0536785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748569488525</t>
+    <t xml:space="preserve">16.8748588562012</t>
   </si>
   <si>
     <t xml:space="preserve">17.0348529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8654441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619171142578</t>
+    <t xml:space="preserve">16.8654460906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619190216064</t>
   </si>
   <si>
     <t xml:space="preserve">17.0724983215332</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2136707305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548412322998</t>
+    <t xml:space="preserve">17.1289710998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2607288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2136745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548450469971</t>
   </si>
   <si>
     <t xml:space="preserve">17.3642559051514</t>
@@ -563,49 +563,49 @@
     <t xml:space="preserve">17.298376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6936569213867</t>
+    <t xml:space="preserve">17.6936588287354</t>
   </si>
   <si>
     <t xml:space="preserve">17.8724803924561</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230400085449</t>
+    <t xml:space="preserve">18.7383365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230419158936</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.804220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3406772613525</t>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
     <t xml:space="preserve">19.3783226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9359798431396</t>
+    <t xml:space="preserve">18.935977935791</t>
   </si>
   <si>
     <t xml:space="preserve">19.2183265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5571422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4159641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724189758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4230003356934</t>
+    <t xml:space="preserve">19.5571441650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4159660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4230041503906</t>
   </si>
   <si>
     <t xml:space="preserve">20.234769821167</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">20.3571186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">20.893575668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6676979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7453689575195</t>
+    <t xml:space="preserve">20.8935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6676998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7453708648682</t>
   </si>
   <si>
     <t xml:space="preserve">19.519495010376</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">19.7171382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8488998413086</t>
+    <t xml:space="preserve">19.84889793396</t>
   </si>
   <si>
     <t xml:space="preserve">19.5759620666504</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">19.2747955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4442043304443</t>
+    <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">19.3877334594727</t>
@@ -671,28 +671,28 @@
     <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3971462249756</t>
+    <t xml:space="preserve">19.397144317627</t>
   </si>
   <si>
     <t xml:space="preserve">19.0959758758545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.001859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0865650177002</t>
+    <t xml:space="preserve">19.0018615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171543121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0865669250488</t>
   </si>
   <si>
     <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936389923096</t>
+    <t xml:space="preserve">18.4936370849609</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524646759033</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">19.510082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2371463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.594783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018180847168</t>
+    <t xml:space="preserve">19.2371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018218994141</t>
   </si>
   <si>
     <t xml:space="preserve">20.7335815429688</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">20.7994632720947</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7900524139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641510009766</t>
+    <t xml:space="preserve">20.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641548156738</t>
   </si>
   <si>
     <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029884338379</t>
+    <t xml:space="preserve">21.1853351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0159244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029865264893</t>
   </si>
   <si>
     <t xml:space="preserve">21.0253372192383</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9876880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947460174561</t>
+    <t xml:space="preserve">20.9876918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947441101074</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794513702393</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">21.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112091064453</t>
+    <t xml:space="preserve">21.4112129211426</t>
   </si>
   <si>
     <t xml:space="preserve">21.6088523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135677337646</t>
+    <t xml:space="preserve">21.213565826416</t>
   </si>
   <si>
     <t xml:space="preserve">21.3829746246338</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">21.5429725646973</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8347301483154</t>
+    <t xml:space="preserve">21.8347320556641</t>
   </si>
   <si>
     <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8064937591553</t>
+    <t xml:space="preserve">21.8064918518066</t>
   </si>
   <si>
     <t xml:space="preserve">22.0417823791504</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">22.2582492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817684173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0394020080566</t>
+    <t xml:space="preserve">22.6817646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0394039154053</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288208007812</t>
@@ -821,28 +821,28 @@
     <t xml:space="preserve">22.5876502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">22.371187210083</t>
+    <t xml:space="preserve">22.3711833953857</t>
   </si>
   <si>
     <t xml:space="preserve">22.0135498046875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6464939117432</t>
+    <t xml:space="preserve">21.6464977264404</t>
   </si>
   <si>
     <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7876682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3076839447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1170749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.098123550415</t>
+    <t xml:space="preserve">21.7876720428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3076820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">22.1549777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2686920166016</t>
+    <t xml:space="preserve">22.2686901092529</t>
   </si>
   <si>
     <t xml:space="preserve">22.0507411956787</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">21.7380352020264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579872131348</t>
+    <t xml:space="preserve">21.5579891204834</t>
   </si>
   <si>
     <t xml:space="preserve">21.5200824737549</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612232208252</t>
+    <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
     <t xml:space="preserve">21.463228225708</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5813999176025</t>
+    <t xml:space="preserve">22.5813980102539</t>
   </si>
   <si>
     <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5908756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.794885635376</t>
+    <t xml:space="preserve">22.5908737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7948875427246</t>
   </si>
   <si>
     <t xml:space="preserve">21.8138446807861</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">21.8422679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6716995239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958957672119</t>
+    <t xml:space="preserve">21.6717014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958938598633</t>
   </si>
   <si>
     <t xml:space="preserve">22.4676837921143</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">22.5055923461914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6951160430908</t>
+    <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277797698975</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">23.5005760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6900939941406</t>
+    <t xml:space="preserve">23.6900959014893</t>
   </si>
   <si>
     <t xml:space="preserve">23.2731513977051</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7709217071533</t>
+    <t xml:space="preserve">22.7709197998047</t>
   </si>
   <si>
     <t xml:space="preserve">22.950963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0646781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7519683837891</t>
+    <t xml:space="preserve">23.0646800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.7235412597656</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">22.477165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1834049224854</t>
+    <t xml:space="preserve">22.183406829834</t>
   </si>
   <si>
     <t xml:space="preserve">23.8796157836914</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">24.1165199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6616649627686</t>
+    <t xml:space="preserve">23.6616668701172</t>
   </si>
   <si>
     <t xml:space="preserve">23.3868637084961</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">23.1783924102783</t>
   </si>
   <si>
-    <t xml:space="preserve">22.90358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0217590332031</t>
+    <t xml:space="preserve">22.9035835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0217609405518</t>
   </si>
   <si>
     <t xml:space="preserve">24.4955596923828</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377010345459</t>
+    <t xml:space="preserve">24.6377029418945</t>
   </si>
   <si>
     <t xml:space="preserve">24.6850814819336</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8082714080811</t>
+    <t xml:space="preserve">24.8082695007324</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5474014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915477752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052600860596</t>
+    <t xml:space="preserve">25.547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052581787109</t>
   </si>
   <si>
     <t xml:space="preserve">25.4431648254395</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">25.0830745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7274436950684</t>
+    <t xml:space="preserve">25.727445602417</t>
   </si>
   <si>
     <t xml:space="preserve">25.6611137390137</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">26.8645706176758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3099422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119491577148</t>
+    <t xml:space="preserve">27.309944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119472503662</t>
   </si>
   <si>
     <t xml:space="preserve">27.0635662078857</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">26.675048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9972343444824</t>
+    <t xml:space="preserve">26.9972362518311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1678009033203</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">25.5379238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359188079834</t>
+    <t xml:space="preserve">25.935920715332</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.301025390625</t>
+    <t xml:space="preserve">25.3010234832764</t>
   </si>
   <si>
     <t xml:space="preserve">25.2631225585938</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">24.9219799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2062606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8601112365723</t>
+    <t xml:space="preserve">25.206262588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8601093292236</t>
   </si>
   <si>
     <t xml:space="preserve">26.3339138031006</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">25.6232089996338</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7748241424561</t>
+    <t xml:space="preserve">25.7748260498047</t>
   </si>
   <si>
     <t xml:space="preserve">25.5947799682617</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">25.7084903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1064872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8171882629395</t>
+    <t xml:space="preserve">26.1064853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8171901702881</t>
   </si>
   <si>
     <t xml:space="preserve">27.0540904998779</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326847076416</t>
+    <t xml:space="preserve">25.6326866149902</t>
   </si>
   <si>
     <t xml:space="preserve">24.7324619293213</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9743766784668</t>
+    <t xml:space="preserve">23.9743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481792449951</t>
+    <t xml:space="preserve">24.0691375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481773376465</t>
   </si>
   <si>
     <t xml:space="preserve">24.8272228240967</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.258659362793</t>
+    <t xml:space="preserve">24.2586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">23.9269962310791</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433876037598</t>
+    <t xml:space="preserve">26.3433856964111</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012481689453</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4855289459229</t>
+    <t xml:space="preserve">26.4855270385742</t>
   </si>
   <si>
     <t xml:space="preserve">26.5329055786133</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">26.7698097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9492969512939</t>
+    <t xml:space="preserve">28.9492950439453</t>
   </si>
   <si>
     <t xml:space="preserve">28.6176376342773</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">29.9696769714355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.113073348999</t>
+    <t xml:space="preserve">30.1130714416504</t>
   </si>
   <si>
     <t xml:space="preserve">31.2602386474609</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">32.7419891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6501693725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803527832031</t>
+    <t xml:space="preserve">33.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803489685059</t>
   </si>
   <si>
     <t xml:space="preserve">35.1797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">36.135684967041</t>
+    <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
     <t xml:space="preserve">34.4149436950684</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">35.9922981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2275161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0841217041016</t>
+    <t xml:space="preserve">35.2275199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0841178894043</t>
   </si>
   <si>
     <t xml:space="preserve">35.6576995849609</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">30.7822513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168441772461</t>
+    <t xml:space="preserve">31.1168422698975</t>
   </si>
   <si>
     <t xml:space="preserve">31.4036312103271</t>
@@ -1433,22 +1433,22 @@
     <t xml:space="preserve">33.0287780761719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7935523986816</t>
+    <t xml:space="preserve">33.7935562133789</t>
   </si>
   <si>
     <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7973289489746</t>
+    <t xml:space="preserve">34.7973251342773</t>
   </si>
   <si>
     <t xml:space="preserve">34.3671417236328</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6539306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0363235473633</t>
+    <t xml:space="preserve">34.6539344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.036319732666</t>
   </si>
   <si>
     <t xml:space="preserve">34.6061325073242</t>
@@ -1457,31 +1457,31 @@
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413543701172</t>
+    <t xml:space="preserve">33.8413581848145</t>
   </si>
   <si>
     <t xml:space="preserve">34.7495269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5621109008789</t>
+    <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">36.040096282959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8966979980469</t>
+    <t xml:space="preserve">35.8966941833496</t>
   </si>
   <si>
     <t xml:space="preserve">36.6614723205566</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0035972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5180816650391</t>
+    <t xml:space="preserve">39.0036010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5180778503418</t>
   </si>
   <si>
     <t xml:space="preserve">37.4262504577637</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">33.2677726745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2639999389648</t>
+    <t xml:space="preserve">32.2640037536621</t>
   </si>
   <si>
     <t xml:space="preserve">32.9809837341309</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">32.837589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5985984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5029983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199745178223</t>
+    <t xml:space="preserve">32.5985946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5029945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199783325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.6463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3596000671387</t>
+    <t xml:space="preserve">32.3596038818359</t>
   </si>
   <si>
     <t xml:space="preserve">32.0728149414062</t>
@@ -1550,22 +1550,22 @@
     <t xml:space="preserve">31.8338222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0690441131592</t>
+    <t xml:space="preserve">31.0690422058105</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816204071045</t>
+    <t xml:space="preserve">31.0212440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816165924072</t>
   </si>
   <si>
     <t xml:space="preserve">28.8703117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5357227325439</t>
+    <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011318206787</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2489318847656</t>
+    <t xml:space="preserve">28.248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">27.5797519683838</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">27.9621391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3445262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0137100219727</t>
+    <t xml:space="preserve">28.3445281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.013708114624</t>
   </si>
   <si>
     <t xml:space="preserve">28.9181098937988</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">30.4954605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">29.587287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344532012939</t>
+    <t xml:space="preserve">29.5872898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344551086426</t>
   </si>
   <si>
     <t xml:space="preserve">30.0174732208252</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6828861236572</t>
+    <t xml:space="preserve">29.6828842163086</t>
   </si>
   <si>
     <t xml:space="preserve">28.5835189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5759830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3847885131836</t>
+    <t xml:space="preserve">26.5759811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.384786605835</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929592132568</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">27.4363555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231483459473</t>
+    <t xml:space="preserve">27.8187427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231464385986</t>
   </si>
   <si>
     <t xml:space="preserve">28.6313209533691</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">29.6350860595703</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017684936523</t>
+    <t xml:space="preserve">27.1017665863037</t>
   </si>
   <si>
     <t xml:space="preserve">26.8627738952637</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">26.1935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6237831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156066894531</t>
+    <t xml:space="preserve">26.6237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
     <t xml:space="preserve">26.289192199707</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659080505371</t>
+    <t xml:space="preserve">28.9659061431885</t>
   </si>
   <si>
     <t xml:space="preserve">28.6791172027588</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803848266602</t>
+    <t xml:space="preserve">26.4803867340088</t>
   </si>
   <si>
     <t xml:space="preserve">27.3885555267334</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">30.1608695983887</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3520641326904</t>
+    <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
     <t xml:space="preserve">31.308032989502</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">32.4552001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3118019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2162094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.602367401123</t>
+    <t xml:space="preserve">32.3118057250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2162055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6023635864258</t>
   </si>
   <si>
     <t xml:space="preserve">33.1721801757812</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9734477996826</t>
+    <t xml:space="preserve">30.9734497070312</t>
   </si>
   <si>
     <t xml:space="preserve">30.2851486206055</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">30.4763431549072</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2277908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9983558654785</t>
+    <t xml:space="preserve">30.2277889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9983577728271</t>
   </si>
   <si>
     <t xml:space="preserve">29.8262825012207</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.438102722168</t>
+    <t xml:space="preserve">30.4381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">30.7631340026855</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">29.7498054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7115669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.812952041626</t>
+    <t xml:space="preserve">29.7115688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8129539489746</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203704833984</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">28.487922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.717357635498</t>
+    <t xml:space="preserve">28.7173557281494</t>
   </si>
   <si>
     <t xml:space="preserve">29.4821319580078</t>
@@ -5625,6 +5625,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -70651,7 +70654,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.649525463</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>426505</v>
@@ -70672,6 +70675,32 @@
         <v>1870</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6516550926</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>793350</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>89.9400024414062</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>90.1399993896484</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="1877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1878">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">14.4801063537598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.171820640564</t>
+    <t xml:space="preserve">14.1718196868896</t>
   </si>
   <si>
     <t xml:space="preserve">13.9476127624512</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0406274795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208856582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022031784058</t>
+    <t xml:space="preserve">15.0406255722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208866119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022003173828</t>
   </si>
   <si>
     <t xml:space="preserve">14.44273853302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6389207839966</t>
+    <t xml:space="preserve">14.6389188766479</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877418518066</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">14.7697086334229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3866863250732</t>
+    <t xml:space="preserve">14.3866853713989</t>
   </si>
   <si>
     <t xml:space="preserve">13.9943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">14.424054145813</t>
+    <t xml:space="preserve">14.4240550994873</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9849805831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036640167236</t>
+    <t xml:space="preserve">13.9849815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036630630493</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338006973267</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">12.4155225753784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061794281006</t>
+    <t xml:space="preserve">12.4061813354492</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172292709351</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722249984741</t>
+    <t xml:space="preserve">13.5459051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722259521484</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645904541016</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">13.4057769775391</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0316896438599</t>
+    <t xml:space="preserve">13.3777484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251077651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195852279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
     <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8355073928833</t>
+    <t xml:space="preserve">13.835506439209</t>
   </si>
   <si>
     <t xml:space="preserve">14.1064252853394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2372150421143</t>
+    <t xml:space="preserve">14.2372140884399</t>
   </si>
   <si>
     <t xml:space="preserve">14.4520807266235</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">14.255898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4143075942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246148109436</t>
+    <t xml:space="preserve">15.4143037796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.601146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461500167847</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060199737549</t>
@@ -179,115 +179,115 @@
     <t xml:space="preserve">15.3769369125366</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4797029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.545093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104869842529</t>
+    <t xml:space="preserve">15.4797010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385145187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5450944900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104850769043</t>
   </si>
   <si>
     <t xml:space="preserve">15.498384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.993914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302268981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918035507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412776947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858737945557</t>
+    <t xml:space="preserve">15.0873365402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253564834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858776092529</t>
   </si>
   <si>
     <t xml:space="preserve">16.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550888061523</t>
+    <t xml:space="preserve">16.2550830841064</t>
   </si>
   <si>
     <t xml:space="preserve">16.4139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671894073486</t>
+    <t xml:space="preserve">16.2924537658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671875</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215339660645</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2177181243896</t>
+    <t xml:space="preserve">16.2177200317383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325847625732</t>
+    <t xml:space="preserve">16.3391666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325866699219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6474475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287631988525</t>
+    <t xml:space="preserve">16.6474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287670135498</t>
   </si>
   <si>
     <t xml:space="preserve">16.4419250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489849090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548648834229</t>
+    <t xml:space="preserve">16.4889812469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6489791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207466125488</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">16.6866245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583938598633</t>
+    <t xml:space="preserve">16.7054500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
   </si>
   <si>
     <t xml:space="preserve">16.8277988433838</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">16.8183898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078275680542</t>
+    <t xml:space="preserve">16.2254600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078294754028</t>
   </si>
   <si>
     <t xml:space="preserve">15.3407793045044</t>
   </si>
   <si>
-    <t xml:space="preserve">16.583101272583</t>
+    <t xml:space="preserve">16.5830993652344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113357543945</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">16.4325160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2536964416504</t>
+    <t xml:space="preserve">16.253698348999</t>
   </si>
   <si>
     <t xml:space="preserve">16.5642757415771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5290107727051</t>
+    <t xml:space="preserve">15.5290069580078</t>
   </si>
   <si>
     <t xml:space="preserve">14.8796148300171</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">15.0678453445435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2748994827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101852416992</t>
+    <t xml:space="preserve">15.2748985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101871490479</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854995727539</t>
@@ -374,82 +374,82 @@
     <t xml:space="preserve">14.6443271636963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9172611236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348936080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054670333862</t>
+    <t xml:space="preserve">14.9172601699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384187698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054708480835</t>
   </si>
   <si>
     <t xml:space="preserve">15.8301773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9901733398438</t>
+    <t xml:space="preserve">15.9901752471924</t>
   </si>
   <si>
     <t xml:space="preserve">15.7925329208374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5478324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.933705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.670184135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3784265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148836135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278224945068</t>
+    <t xml:space="preserve">15.547833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701831817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3784246444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.2725200653076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195762634277</t>
+    <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1595840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.376049041748</t>
+    <t xml:space="preserve">16.1595821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3760433197021</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.460750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078067779541</t>
+    <t xml:space="preserve">16.4607524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078105926514</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301574707031</t>
@@ -458,91 +458,91 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560314178467</t>
+    <t xml:space="preserve">16.7807426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560333251953</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372077941895</t>
+    <t xml:space="preserve">17.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9783878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8466205596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960391998291</t>
+    <t xml:space="preserve">16.978385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8466243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960372924805</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9030914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0066184997559</t>
+    <t xml:space="preserve">16.7713298797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9030895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0066165924072</t>
   </si>
   <si>
     <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8748588562012</t>
+    <t xml:space="preserve">17.0536766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0348529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8654460906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619190216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0725002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289672851562</t>
+    <t xml:space="preserve">16.8654479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0724983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2324924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289691925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2607307434082</t>
@@ -551,46 +551,46 @@
     <t xml:space="preserve">17.2136707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3548431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.307788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7383403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6818675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8042182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430320739746</t>
+    <t xml:space="preserve">17.3548450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642597198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.298376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.738338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.804220199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3783226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359836578369</t>
+    <t xml:space="preserve">19.3783187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359817504883</t>
   </si>
   <si>
     <t xml:space="preserve">19.2183265686035</t>
@@ -599,25 +599,25 @@
     <t xml:space="preserve">19.5571422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724151611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4230003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2347717285156</t>
+    <t xml:space="preserve">19.4159679412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.423002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2347679138184</t>
   </si>
   <si>
     <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4982948303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3571186065674</t>
+    <t xml:space="preserve">20.4982929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.357120513916</t>
   </si>
   <si>
     <t xml:space="preserve">20.8935775756836</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">20.6676998138428</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6959342956543</t>
+    <t xml:space="preserve">20.6959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3665313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1030101776123</t>
+    <t xml:space="preserve">20.103006362915</t>
   </si>
   <si>
     <t xml:space="preserve">19.8206634521484</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">19.7453708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">19.519495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6889038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171382904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8488960266113</t>
+    <t xml:space="preserve">19.5194931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6888999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.84889793396</t>
   </si>
   <si>
     <t xml:space="preserve">19.5759601593018</t>
@@ -662,43 +662,43 @@
     <t xml:space="preserve">19.2747936248779</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4442043304443</t>
+    <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">19.3877353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3500862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959796905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8701019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4936389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865829467773</t>
+    <t xml:space="preserve">19.3500881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3971462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0018615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8701000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4936408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2865867614746</t>
   </si>
   <si>
     <t xml:space="preserve">18.6254005432129</t>
@@ -707,130 +707,130 @@
     <t xml:space="preserve">19.2559700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5100841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2371501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218120574951</t>
+    <t xml:space="preserve">19.510082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218101501465</t>
   </si>
   <si>
     <t xml:space="preserve">21.3641529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2982711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853351593018</t>
+    <t xml:space="preserve">21.298267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">21.0159282684326</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253372192383</t>
+    <t xml:space="preserve">20.9029884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253353118896</t>
   </si>
   <si>
     <t xml:space="preserve">20.9876918792725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1947460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1100387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.608850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2135677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829765319824</t>
+    <t xml:space="preserve">21.1947441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112071990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6088485717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2135715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829746246338</t>
   </si>
   <si>
     <t xml:space="preserve">21.5429706573486</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8347301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0229606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8064937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.041784286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817684173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252975463867</t>
+    <t xml:space="preserve">21.8347263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0229587554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8064956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0417823791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582454681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252994537354</t>
   </si>
   <si>
     <t xml:space="preserve">23.0394039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7288227081299</t>
+    <t xml:space="preserve">22.7288246154785</t>
   </si>
   <si>
     <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135478973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9194316864014</t>
+    <t xml:space="preserve">22.5876522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3711814880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
@@ -839,124 +839,124 @@
     <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1170749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0981254577637</t>
+    <t xml:space="preserve">22.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.098123550415</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1549758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0507411956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7190780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.08864402771</t>
+    <t xml:space="preserve">22.1549777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0507431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7190799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0886459350586</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8327941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6811752319336</t>
+    <t xml:space="preserve">21.8327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6811771392822</t>
   </si>
   <si>
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285575866699</t>
+    <t xml:space="preserve">21.7285537719727</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380352020264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579872131348</t>
+    <t xml:space="preserve">21.5579853057861</t>
   </si>
   <si>
     <t xml:space="preserve">21.5200824737549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1315650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4158477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8612194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.463228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6622257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5624504089355</t>
+    <t xml:space="preserve">21.1315670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4158458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8612213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4632301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
     <t xml:space="preserve">22.4013557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5529708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5813980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6761608123779</t>
+    <t xml:space="preserve">22.5529727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5813999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6761627197266</t>
   </si>
   <si>
     <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7948875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6717014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958938598633</t>
+    <t xml:space="preserve">21.7948894500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.671703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958919525146</t>
   </si>
   <si>
     <t xml:space="preserve">22.4676876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3255462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951160430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277759552002</t>
+    <t xml:space="preserve">22.3255481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.0362491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2068176269531</t>
+    <t xml:space="preserve">23.2068195343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162952423096</t>
@@ -968,37 +968,37 @@
     <t xml:space="preserve">23.1310119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5005760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900978088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4531955718994</t>
+    <t xml:space="preserve">23.5005741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.405818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.453197479248</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9509658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0646781921387</t>
+    <t xml:space="preserve">22.9509620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0646800994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.7519702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7235412597656</t>
+    <t xml:space="preserve">22.723539352417</t>
   </si>
   <si>
     <t xml:space="preserve">22.9793949127197</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">22.6477317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">22.477165222168</t>
+    <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
     <t xml:space="preserve">22.183406829834</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">23.87961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6616687774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.90358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0217571258545</t>
+    <t xml:space="preserve">24.1165180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6616668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783924102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9035873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0217590332031</t>
   </si>
   <si>
     <t xml:space="preserve">24.4955615997314</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">24.6377010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6850814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903186798096</t>
+    <t xml:space="preserve">24.6850833892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903205871582</t>
   </si>
   <si>
     <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8082695007324</t>
+    <t xml:space="preserve">24.8082714080811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
@@ -1061,40 +1061,40 @@
     <t xml:space="preserve">24.7229843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1638965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8651256561279</t>
+    <t xml:space="preserve">24.5429401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1638984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8651237487793</t>
   </si>
   <si>
     <t xml:space="preserve">25.7558746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5474014282227</t>
+    <t xml:space="preserve">25.7653522491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5473976135254</t>
   </si>
   <si>
     <t xml:space="preserve">25.2915496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4052600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4431629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4905452728271</t>
+    <t xml:space="preserve">25.4052581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4431648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4905433654785</t>
   </si>
   <si>
     <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484039306641</t>
+    <t xml:space="preserve">25.3484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">25.3294506072998</t>
@@ -1103,43 +1103,43 @@
     <t xml:space="preserve">25.0830726623535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7274436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.661111831665</t>
+    <t xml:space="preserve">25.727445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6611137390137</t>
   </si>
   <si>
     <t xml:space="preserve">25.9643459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3054828643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645725250244</t>
+    <t xml:space="preserve">26.3054847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645706176758</t>
   </si>
   <si>
     <t xml:space="preserve">27.309944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0635681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.675048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678047180176</t>
+    <t xml:space="preserve">26.9119472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0635662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6750469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678066253662</t>
   </si>
   <si>
     <t xml:space="preserve">26.4665756225586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0591087341309</t>
+    <t xml:space="preserve">26.0591049194336</t>
   </si>
   <si>
     <t xml:space="preserve">25.0451698303223</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1115016937256</t>
+    <t xml:space="preserve">25.1115036010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.5379238128662</t>
@@ -1166,34 +1166,34 @@
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010234832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683559417725</t>
+    <t xml:space="preserve">25.301025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683597564697</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2062644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8601112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3339099884033</t>
+    <t xml:space="preserve">25.2062606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8601093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
     <t xml:space="preserve">26.248628616333</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">25.3673553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3578815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800670623779</t>
+    <t xml:space="preserve">25.3578796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.6232109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7748260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5947818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7084941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1064853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8171901702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0540885925293</t>
+    <t xml:space="preserve">25.7748279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5947799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7084903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1064872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8171882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540924072266</t>
   </si>
   <si>
     <t xml:space="preserve">27.3857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8695831298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222045898438</t>
+    <t xml:space="preserve">25.8695850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222026824951</t>
   </si>
   <si>
     <t xml:space="preserve">25.9169673919678</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">24.7324600219727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9743785858154</t>
+    <t xml:space="preserve">23.9743766784668</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481773376465</t>
+    <t xml:space="preserve">24.0691413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
   </si>
   <si>
     <t xml:space="preserve">24.8272228240967</t>
@@ -1271,28 +1271,28 @@
     <t xml:space="preserve">23.7848587036133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.258659362793</t>
+    <t xml:space="preserve">24.2586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167407989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9693622589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9269962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433895111084</t>
+    <t xml:space="preserve">25.0167427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9269981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0117282867432</t>
+    <t xml:space="preserve">26.0117263793945</t>
   </si>
   <si>
     <t xml:space="preserve">26.153865814209</t>
@@ -1304,76 +1304,76 @@
     <t xml:space="preserve">26.5329093933105</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9593296051025</t>
+    <t xml:space="preserve">26.9593315124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9492988586426</t>
+    <t xml:space="preserve">28.9492969512939</t>
   </si>
   <si>
     <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8071594238281</t>
+    <t xml:space="preserve">28.8071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">28.665018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3283405303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2335815429688</t>
+    <t xml:space="preserve">29.3283424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">29.5394897460938</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2086715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0652751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9696769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1130714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2602405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797142028809</t>
+    <t xml:space="preserve">30.2086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0652770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042640686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9696788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.113073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2602386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797180175781</t>
   </si>
   <si>
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149475097656</t>
+    <t xml:space="preserve">34.4149436950684</t>
   </si>
   <si>
     <t xml:space="preserve">33.936954498291</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.988525390625</t>
+    <t xml:space="preserve">34.1759452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
     <t xml:space="preserve">35.753303527832</t>
@@ -1397,118 +1397,118 @@
     <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3746795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268814086914</t>
+    <t xml:space="preserve">36.3746757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268775939941</t>
   </si>
   <si>
     <t xml:space="preserve">35.4187088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5658721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8526649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822551727295</t>
+    <t xml:space="preserve">36.5658760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822532653809</t>
   </si>
   <si>
     <t xml:space="preserve">31.1168422698975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4036331176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5948238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2124404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0287780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.984748840332</t>
+    <t xml:space="preserve">31.4036350250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5948257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.212438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0287857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9847564697266</t>
   </si>
   <si>
     <t xml:space="preserve">34.7973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3671493530273</t>
+    <t xml:space="preserve">34.3671417236328</t>
   </si>
   <si>
     <t xml:space="preserve">34.6539344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">35.036319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6061363220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4627342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.841365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7495269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5621109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0400924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6614723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0035972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306465148926</t>
+    <t xml:space="preserve">35.0363235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6061401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4627380371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8413581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7495307922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5621070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.040096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6614685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0036010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306541442871</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4262504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8564300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2790870666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2350578308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8929290771484</t>
+    <t xml:space="preserve">37.4262466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8564338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2790832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2350540161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8929252624512</t>
   </si>
   <si>
     <t xml:space="preserve">34.5583381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6979675292969</t>
+    <t xml:space="preserve">33.6979637145996</t>
   </si>
   <si>
     <t xml:space="preserve">33.5067672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2677764892578</t>
+    <t xml:space="preserve">33.2677726745605</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640075683594</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">32.9809875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3633728027344</t>
+    <t xml:space="preserve">33.3633766174316</t>
   </si>
   <si>
     <t xml:space="preserve">32.7897872924805</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">32.8375854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5985984802246</t>
+    <t xml:space="preserve">32.5985946655273</t>
   </si>
   <si>
     <t xml:space="preserve">32.503002166748</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2199821472168</t>
+    <t xml:space="preserve">33.2199783325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.6464004516602</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">32.0728149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7860202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338222503662</t>
+    <t xml:space="preserve">31.7860221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338203430176</t>
   </si>
   <si>
     <t xml:space="preserve">31.0690441131592</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">32.025016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0212440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357208251953</t>
+    <t xml:space="preserve">31.0212421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357227325439</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709445953369</t>
+    <t xml:space="preserve">27.7709426879883</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1055335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2451591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.96213722229</t>
+    <t xml:space="preserve">28.2489280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1055355072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2451610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9621391296387</t>
   </si>
   <si>
     <t xml:space="preserve">28.3445281982422</t>
@@ -1598,46 +1598,46 @@
     <t xml:space="preserve">29.0137062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9181098937988</t>
+    <t xml:space="preserve">28.9181118011475</t>
   </si>
   <si>
     <t xml:space="preserve">29.2049007415771</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4954624176025</t>
+    <t xml:space="preserve">30.4954605102539</t>
   </si>
   <si>
     <t xml:space="preserve">29.5872917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174770355225</t>
+    <t xml:space="preserve">30.7344532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174751281738</t>
   </si>
   <si>
     <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6828861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5835189819336</t>
+    <t xml:space="preserve">29.6828842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5835208892822</t>
   </si>
   <si>
     <t xml:space="preserve">26.5759830474854</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3847846984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2929592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4363574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187427520752</t>
+    <t xml:space="preserve">26.3847885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2929611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4363555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187446594238</t>
   </si>
   <si>
     <t xml:space="preserve">27.7231483459473</t>
@@ -1646,40 +1646,40 @@
     <t xml:space="preserve">28.6313209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6350879669189</t>
+    <t xml:space="preserve">29.6350898742676</t>
   </si>
   <si>
     <t xml:space="preserve">27.1017665863037</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8627738952637</t>
+    <t xml:space="preserve">26.8627758026123</t>
   </si>
   <si>
     <t xml:space="preserve">27.4841537475586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0061664581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200122833252</t>
+    <t xml:space="preserve">27.0061683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0979957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200103759766</t>
   </si>
   <si>
     <t xml:space="preserve">26.1935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">26.623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2891902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671775817871</t>
+    <t xml:space="preserve">26.6237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.289192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671756744385</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">28.9659080505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6791172027588</t>
+    <t xml:space="preserve">28.6791152954102</t>
   </si>
   <si>
     <t xml:space="preserve">29.1093044281006</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.388557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8225116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.874080657959</t>
+    <t xml:space="preserve">26.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3885555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8225135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8740825653076</t>
   </si>
   <si>
     <t xml:space="preserve">30.1608715057373</t>
@@ -1718,58 +1718,58 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.308032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4514350891113</t>
+    <t xml:space="preserve">31.3080348968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.45143699646</t>
   </si>
   <si>
     <t xml:space="preserve">32.4552040100098</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3118019104004</t>
+    <t xml:space="preserve">32.3118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">32.2162055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6023635864258</t>
+    <t xml:space="preserve">33.602367401123</t>
   </si>
   <si>
     <t xml:space="preserve">33.1721839904785</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5545654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2564678192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6388568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004989624023</t>
+    <t xml:space="preserve">33.5545692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2564697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6388549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910606384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004970550537</t>
   </si>
   <si>
     <t xml:space="preserve">29.9409980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6484184265137</t>
+    <t xml:space="preserve">30.6484203338623</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9734497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2851505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748329162598</t>
+    <t xml:space="preserve">30.9734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">30.4763412475586</t>
@@ -1784,16 +1784,16 @@
     <t xml:space="preserve">29.8262844085693</t>
   </si>
   <si>
-    <t xml:space="preserve">30.667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4381008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352073669434</t>
+    <t xml:space="preserve">30.6675395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.438102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9352111816406</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">28.812952041626</t>
+    <t xml:space="preserve">28.8129539489746</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203704833984</t>
@@ -1811,37 +1811,37 @@
     <t xml:space="preserve">28.487922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7173557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4821319580078</t>
+    <t xml:space="preserve">28.717357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4821357727051</t>
   </si>
   <si>
     <t xml:space="preserve">29.1762218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291797637939</t>
+    <t xml:space="preserve">29.3291759490967</t>
   </si>
   <si>
     <t xml:space="preserve">28.5761585235596</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9237060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6533908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058414459229</t>
+    <t xml:space="preserve">28.9237041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.653392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058433532715</t>
   </si>
   <si>
     <t xml:space="preserve">28.3637657165527</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5182323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8038291931152</t>
+    <t xml:space="preserve">28.5182342529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8038272857666</t>
   </si>
   <si>
     <t xml:space="preserve">28.0741443634033</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">27.2052745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3211212158203</t>
+    <t xml:space="preserve">27.3211231231689</t>
   </si>
   <si>
     <t xml:space="preserve">27.5335140228271</t>
@@ -1895,43 +1895,43 @@
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.900369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0934505462646</t>
+    <t xml:space="preserve">27.9003715515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0934524536133</t>
   </si>
   <si>
     <t xml:space="preserve">28.6340808868408</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1167888641357</t>
+    <t xml:space="preserve">29.1167869567871</t>
   </si>
   <si>
     <t xml:space="preserve">28.8850898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2712535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8311920166016</t>
+    <t xml:space="preserve">29.2712516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8311901092529</t>
   </si>
   <si>
     <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539596557617</t>
+    <t xml:space="preserve">29.8505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539577484131</t>
   </si>
   <si>
     <t xml:space="preserve">30.2173557281494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9856567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6807518005371</t>
+    <t xml:space="preserve">29.9856586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">29.3677959442139</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">29.2519454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4643363952637</t>
+    <t xml:space="preserve">29.464334487915</t>
   </si>
   <si>
     <t xml:space="preserve">29.0202465057373</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">28.9043979644775</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6920051574707</t>
+    <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
     <t xml:space="preserve">28.4796161651611</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542694091797</t>
+    <t xml:space="preserve">26.9542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1473503112793</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6839542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101795196533</t>
+    <t xml:space="preserve">26.683952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101776123047</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1899929046631</t>
+    <t xml:space="preserve">28.1899948120117</t>
   </si>
   <si>
     <t xml:space="preserve">28.3444595336914</t>
@@ -2009,25 +2009,25 @@
     <t xml:space="preserve">27.0314998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6260299682617</t>
+    <t xml:space="preserve">26.6260280609131</t>
   </si>
   <si>
     <t xml:space="preserve">27.4176635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0355281829834</t>
+    <t xml:space="preserve">28.035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">27.0894241333008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.992883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755878448486</t>
+    <t xml:space="preserve">26.9928817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0508117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755897521973</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2042,22 +2042,22 @@
     <t xml:space="preserve">27.6879806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3557109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9309329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8536987304688</t>
+    <t xml:space="preserve">26.355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8537006378174</t>
   </si>
   <si>
     <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3018169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4562835693359</t>
+    <t xml:space="preserve">27.301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4562816619873</t>
   </si>
   <si>
     <t xml:space="preserve">26.8577251434326</t>
@@ -2066,28 +2066,28 @@
     <t xml:space="preserve">25.7957725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9116249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7032623291016</t>
+    <t xml:space="preserve">25.9116230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7032604217529</t>
   </si>
   <si>
     <t xml:space="preserve">27.7459049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1087322235107</t>
+    <t xml:space="preserve">27.1087341308594</t>
   </si>
   <si>
     <t xml:space="preserve">28.1320686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3830738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9430122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4064102172852</t>
+    <t xml:space="preserve">28.3830757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9430141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4064083099365</t>
   </si>
   <si>
     <t xml:space="preserve">28.8078575134277</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">28.981632232666</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1360969543457</t>
+    <t xml:space="preserve">29.1360950469971</t>
   </si>
   <si>
     <t xml:space="preserve">28.7499313354492</t>
@@ -2117,28 +2117,28 @@
     <t xml:space="preserve">29.2133312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6228275299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.935791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026428222656</t>
+    <t xml:space="preserve">30.6228294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9357872009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026390075684</t>
   </si>
   <si>
     <t xml:space="preserve">32.4571075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8585548400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2213821411133</t>
+    <t xml:space="preserve">31.858549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2213802337646</t>
   </si>
   <si>
     <t xml:space="preserve">31.182767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6654720306396</t>
+    <t xml:space="preserve">31.6654739379883</t>
   </si>
   <si>
     <t xml:space="preserve">32.1674842834473</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">31.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5882396697998</t>
+    <t xml:space="preserve">31.5882415771484</t>
   </si>
   <si>
     <t xml:space="preserve">31.047607421875</t>
@@ -2156,25 +2156,25 @@
     <t xml:space="preserve">30.9510707855225</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1248455047607</t>
+    <t xml:space="preserve">31.1248435974121</t>
   </si>
   <si>
     <t xml:space="preserve">31.356538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8545246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8931427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8159084320068</t>
+    <t xml:space="preserve">30.8545265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8931446075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8159103393555</t>
   </si>
   <si>
     <t xml:space="preserve">31.3372325897217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4683609008789</t>
+    <t xml:space="preserve">30.4683628082275</t>
   </si>
   <si>
     <t xml:space="preserve">31.0089912414551</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">30.7000598907471</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0170478820801</t>
+    <t xml:space="preserve">33.0170516967773</t>
   </si>
   <si>
     <t xml:space="preserve">33.3645935058594</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">34.8899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0251045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9711990356445</t>
+    <t xml:space="preserve">35.0250968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9712028503418</t>
   </si>
   <si>
     <t xml:space="preserve">36.5311431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9559211730957</t>
+    <t xml:space="preserve">36.955924987793</t>
   </si>
   <si>
     <t xml:space="preserve">37.2069320678711</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6847801208496</t>
+    <t xml:space="preserve">31.9937133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6847839355469</t>
   </si>
   <si>
     <t xml:space="preserve">31.8778629302979</t>
@@ -2246,31 +2246,31 @@
     <t xml:space="preserve">33.383903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8432769775391</t>
+    <t xml:space="preserve">32.8432731628418</t>
   </si>
   <si>
     <t xml:space="preserve">31.7427062988281</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8239631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.901195526123</t>
+    <t xml:space="preserve">32.8239669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9011993408203</t>
   </si>
   <si>
     <t xml:space="preserve">32.2447166442871</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5343437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4764137268066</t>
+    <t xml:space="preserve">32.5343399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4764175415039</t>
   </si>
   <si>
     <t xml:space="preserve">33.6928367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7081146240234</t>
+    <t xml:space="preserve">32.7081184387207</t>
   </si>
   <si>
     <t xml:space="preserve">29.3871021270752</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">29.811882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9623222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8698101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7732677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0049648284912</t>
+    <t xml:space="preserve">28.9623203277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7732696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0049667358398</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784786224365</t>
+    <t xml:space="preserve">26.2784805297852</t>
   </si>
   <si>
     <t xml:space="preserve">25.2937622070312</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">26.1240119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5407428741455</t>
+    <t xml:space="preserve">24.5407409667969</t>
   </si>
   <si>
     <t xml:space="preserve">24.1931934356689</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">25.2744541168213</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7378482818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150825500488</t>
+    <t xml:space="preserve">25.737850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150844573975</t>
   </si>
   <si>
     <t xml:space="preserve">25.100679397583</t>
@@ -2330,25 +2330,25 @@
     <t xml:space="preserve">26.8384189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">24.791748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8263339996338</t>
+    <t xml:space="preserve">24.7917461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8263359069824</t>
   </si>
   <si>
     <t xml:space="preserve">24.019416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9614944458008</t>
+    <t xml:space="preserve">23.9614963531494</t>
   </si>
   <si>
     <t xml:space="preserve">24.4441986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9075946807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0427570343018</t>
+    <t xml:space="preserve">24.9075965881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">25.6220016479492</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">27.8231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6646461486816</t>
+    <t xml:space="preserve">26.664644241333</t>
   </si>
   <si>
     <t xml:space="preserve">26.645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2398624420166</t>
+    <t xml:space="preserve">26.2398643493652</t>
   </si>
   <si>
     <t xml:space="preserve">25.718542098999</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">26.5487957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9349594116211</t>
+    <t xml:space="preserve">26.9349575042725</t>
   </si>
   <si>
     <t xml:space="preserve">26.4522533416748</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">26.973575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.375020980835</t>
+    <t xml:space="preserve">26.3750228881836</t>
   </si>
   <si>
     <t xml:space="preserve">28.0162200927734</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">26.5681056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5061511993408</t>
+    <t xml:space="preserve">25.5061531066895</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903026580811</t>
@@ -2432,25 +2432,25 @@
     <t xml:space="preserve">25.5254592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4055843353271</t>
+    <t xml:space="preserve">24.4055862426758</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565914154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2511196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2897357940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5793571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8496723175049</t>
+    <t xml:space="preserve">24.6565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2511177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2897338867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5793552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8496704101562</t>
   </si>
   <si>
     <t xml:space="preserve">24.3283519744873</t>
@@ -2477,19 +2477,19 @@
     <t xml:space="preserve">24.0387268066406</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9035682678223</t>
+    <t xml:space="preserve">23.9035701751709</t>
   </si>
   <si>
     <t xml:space="preserve">23.1505470275879</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3822460174561</t>
+    <t xml:space="preserve">23.3822441101074</t>
   </si>
   <si>
     <t xml:space="preserve">23.0733165740967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7684116363525</t>
+    <t xml:space="preserve">23.7684135437012</t>
   </si>
   <si>
     <t xml:space="preserve">23.5946369171143</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">26.0853977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">25.119987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9462127685547</t>
+    <t xml:space="preserve">25.1199855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">24.811056137085</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269065856934</t>
+    <t xml:space="preserve">24.9269046783447</t>
   </si>
   <si>
     <t xml:space="preserve">26.7611846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2205543518066</t>
+    <t xml:space="preserve">26.2205562591553</t>
   </si>
   <si>
     <t xml:space="preserve">24.6179733276367</t>
@@ -2552,19 +2552,19 @@
     <t xml:space="preserve">24.463508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358341217041</t>
+    <t xml:space="preserve">25.2358360290527</t>
   </si>
   <si>
     <t xml:space="preserve">25.1392955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6413078308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3130683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977867126465</t>
+    <t xml:space="preserve">25.6413097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3130702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977886199951</t>
   </si>
   <si>
     <t xml:space="preserve">26.7804927825928</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4136371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8343925476074</t>
+    <t xml:space="preserve">26.4136390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8343906402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.7571582794189</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689823150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.772439956665</t>
+    <t xml:space="preserve">24.8689804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7724380493164</t>
   </si>
   <si>
     <t xml:space="preserve">30.1401214599609</t>
@@ -2609,37 +2609,37 @@
     <t xml:space="preserve">31.7620182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1481742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2061042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8392467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9744033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9550952911377</t>
+    <t xml:space="preserve">32.1481781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2061004638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8392448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.974401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9550933837891</t>
   </si>
   <si>
     <t xml:space="preserve">32.3798789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2680549621582</t>
+    <t xml:space="preserve">33.2680511474609</t>
   </si>
   <si>
     <t xml:space="preserve">34.1755409240723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1562309265137</t>
+    <t xml:space="preserve">34.1562347412109</t>
   </si>
   <si>
     <t xml:space="preserve">33.9245338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1795692443848</t>
+    <t xml:space="preserve">35.1795654296875</t>
   </si>
   <si>
     <t xml:space="preserve">35.3726501464844</t>
@@ -2651,34 +2651,34 @@
     <t xml:space="preserve">34.5810127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2761077880859</t>
+    <t xml:space="preserve">35.2761116027832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8706359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7547912597656</t>
+    <t xml:space="preserve">34.8706321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7547874450684</t>
   </si>
   <si>
     <t xml:space="preserve">35.6429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0444068908691</t>
+    <t xml:space="preserve">35.0444107055664</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4651641845703</t>
+    <t xml:space="preserve">34.465160369873</t>
   </si>
   <si>
     <t xml:space="preserve">34.6003227233887</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640266418457</t>
+    <t xml:space="preserve">32.2640228271484</t>
   </si>
   <si>
     <t xml:space="preserve">32.4957237243652</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">34.059684753418</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5383720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.291389465332</t>
+    <t xml:space="preserve">33.5383682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2913932800293</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7314491271973</t>
+    <t xml:space="preserve">32.9977378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7314529418945</t>
   </si>
   <si>
     <t xml:space="preserve">33.3066711425781</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8971710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0709419250488</t>
+    <t xml:space="preserve">33.1908187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8971748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0709457397461</t>
   </si>
   <si>
     <t xml:space="preserve">32.437801361084</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">33.3452911376953</t>
   </si>
   <si>
-    <t xml:space="preserve">33.210132598877</t>
+    <t xml:space="preserve">33.2101287841797</t>
   </si>
   <si>
     <t xml:space="preserve">33.7893753051758</t>
@@ -2759,16 +2759,16 @@
     <t xml:space="preserve">32.939811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4418296813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.881893157959</t>
+    <t xml:space="preserve">33.4418258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8818893432617</t>
   </si>
   <si>
     <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6775550842285</t>
+    <t xml:space="preserve">34.6775512695312</t>
   </si>
   <si>
     <t xml:space="preserve">37.5351676940918</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">36.2994422912598</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2801361083984</t>
+    <t xml:space="preserve">36.2801399230957</t>
   </si>
   <si>
     <t xml:space="preserve">35.7201957702637</t>
@@ -2798,64 +2798,64 @@
     <t xml:space="preserve">35.6043472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">35.565731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3919563293457</t>
+    <t xml:space="preserve">35.5657272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.391960144043</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510162353516</t>
+    <t xml:space="preserve">37.6510200500488</t>
   </si>
   <si>
     <t xml:space="preserve">37.0331573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3807067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5158615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5198936462402</t>
+    <t xml:space="preserve">37.3807029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5158653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5625305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.581844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9100761413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2383193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149810791016</t>
+    <t xml:space="preserve">39.5625343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5818405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9100799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2383232116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2149848937988</t>
   </si>
   <si>
     <t xml:space="preserve">40.9527206420898</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1458015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7057418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4587669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9567489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5319747924805</t>
+    <t xml:space="preserve">41.145809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7057456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4587631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9567451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">41.3388862609863</t>
@@ -2867,19 +2867,19 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5665550231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3429183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878868103027</t>
+    <t xml:space="preserve">40.6244812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5665588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3429145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">42.3236045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4008369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6711578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256149291992</t>
+    <t xml:space="preserve">42.4008407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6711540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256187438965</t>
   </si>
   <si>
     <t xml:space="preserve">43.8875694274902</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5786437988281</t>
+    <t xml:space="preserve">43.5786399841309</t>
   </si>
   <si>
     <t xml:space="preserve">43.9841156005859</t>
@@ -2912,19 +2912,19 @@
     <t xml:space="preserve">43.8489532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3743057250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3244361877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9600067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5601577758789</t>
+    <t xml:space="preserve">45.3743019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3244323730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9600028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5601615905762</t>
   </si>
   <si>
     <t xml:space="preserve">48.4636192321777</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4982109069824</t>
+    <t xml:space="preserve">47.4982070922852</t>
   </si>
   <si>
     <t xml:space="preserve">46.4748725891113</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">46.5521049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1120414733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4016647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.01953125</t>
+    <t xml:space="preserve">47.1120452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4016609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0195350646973</t>
   </si>
   <si>
     <t xml:space="preserve">48.3188056945801</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">49.1876754760742</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9229888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7878303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051223754883</t>
+    <t xml:space="preserve">47.9229927062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6912956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7878341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051261901855</t>
   </si>
   <si>
     <t xml:space="preserve">47.6140556335449</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.539249420166</t>
+    <t xml:space="preserve">50.5392456054688</t>
   </si>
   <si>
     <t xml:space="preserve">47.8457565307617</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">49.3807601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2978973388672</t>
+    <t xml:space="preserve">50.0082702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2979011535645</t>
   </si>
   <si>
     <t xml:space="preserve">50.4909782409668</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">54.4974365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8699188232422</t>
+    <t xml:space="preserve">53.8699150085449</t>
   </si>
   <si>
     <t xml:space="preserve">52.3252639770508</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">53.0975914001465</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0010528564453</t>
+    <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
     <t xml:space="preserve">52.8562393188477</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">52.0356369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">51.601203918457</t>
+    <t xml:space="preserve">51.6012077331543</t>
   </si>
   <si>
     <t xml:space="preserve">47.7105979919434</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">47.9616050720215</t>
   </si>
   <si>
-    <t xml:space="preserve">47.903678894043</t>
+    <t xml:space="preserve">47.9036827087402</t>
   </si>
   <si>
     <t xml:space="preserve">47.4402847290039</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996543884277</t>
+    <t xml:space="preserve">46.899658203125</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590278625488</t>
@@ -3104,46 +3104,46 @@
     <t xml:space="preserve">46.3010940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5907249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8031120300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8071365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6446151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.895622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1659469604492</t>
+    <t xml:space="preserve">46.5907211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8071403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6446189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8956260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1659393310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3163757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4129219055176</t>
+    <t xml:space="preserve">45.9149360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3163795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4129257202148</t>
   </si>
   <si>
     <t xml:space="preserve">45.4322280883789</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0887107849121</t>
+    <t xml:space="preserve">46.0887069702148</t>
   </si>
   <si>
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699714660645</t>
+    <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388336181641</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4290351867676</t>
+    <t xml:space="preserve">49.4290313720703</t>
   </si>
   <si>
     <t xml:space="preserve">50.5875244140625</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">51.6977424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1869010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1659927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.145092010498</t>
+    <t xml:space="preserve">56.1869049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1659965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1450881958008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">60.5312538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2899017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7589263916016</t>
+    <t xml:space="preserve">60.2899055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7589302062988</t>
   </si>
   <si>
     <t xml:space="preserve">58.021183013916</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">58.0694580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6213417053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.849006652832</t>
+    <t xml:space="preserve">56.621337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8490104675293</t>
   </si>
   <si>
     <t xml:space="preserve">56.283447265625</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5802993774414</t>
+    <t xml:space="preserve">53.5802955627441</t>
   </si>
   <si>
     <t xml:space="preserve">54.0147285461426</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">54.9318733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4282569885254</t>
+    <t xml:space="preserve">56.4282608032227</t>
   </si>
   <si>
     <t xml:space="preserve">55.0284118652344</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">54.2078170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3872108459473</t>
+    <t xml:space="preserve">53.3872146606445</t>
   </si>
   <si>
     <t xml:space="preserve">51.9873657226562</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7733764648438</t>
+    <t xml:space="preserve">53.773380279541</t>
   </si>
   <si>
     <t xml:space="preserve">54.9801406860352</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9656867980957</t>
+    <t xml:space="preserve">60.965690612793</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">58.6969718933105</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0420913696289</t>
+    <t xml:space="preserve">56.0420875549316</t>
   </si>
   <si>
     <t xml:space="preserve">58.4073524475098</t>
@@ -3296,19 +3296,19 @@
     <t xml:space="preserve">52.2287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0839080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1458587646484</t>
+    <t xml:space="preserve">52.083911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1458625793457</t>
   </si>
   <si>
     <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8288764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8908271789551</t>
+    <t xml:space="preserve">50.8288726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8908233642578</t>
   </si>
   <si>
     <t xml:space="preserve">50.0565452575684</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">49.2359466552734</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4837608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8425598144531</t>
+    <t xml:space="preserve">53.4837532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1184997558594</t>
+    <t xml:space="preserve">51.1185035705566</t>
   </si>
   <si>
     <t xml:space="preserve">52.37353515625</t>
@@ -3335,10 +3335,10 @@
     <t xml:space="preserve">52.1804504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3461685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4563941955566</t>
+    <t xml:space="preserve">50.3461723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4563903808594</t>
   </si>
   <si>
     <t xml:space="preserve">50.9254150390625</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">50.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7186508178711</t>
+    <t xml:space="preserve">49.7186546325684</t>
   </si>
   <si>
     <t xml:space="preserve">45.0074462890625</t>
@@ -3356,31 +3356,31 @@
     <t xml:space="preserve">46.3976402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763160705566</t>
+    <t xml:space="preserve">45.8763198852539</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4893226623535</t>
+    <t xml:space="preserve">41.2423477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4893264770508</t>
   </si>
   <si>
     <t xml:space="preserve">42.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">42.149829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5480766296387</t>
+    <t xml:space="preserve">42.1498336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5480804443359</t>
   </si>
   <si>
     <t xml:space="preserve">46.8224220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2633094787598</t>
+    <t xml:space="preserve">51.2633056640625</t>
   </si>
   <si>
     <t xml:space="preserve">51.7942886352539</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">49.5738410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8771476745605</t>
+    <t xml:space="preserve">50.8771438598633</t>
   </si>
   <si>
     <t xml:space="preserve">51.0219535827637</t>
@@ -3407,19 +3407,19 @@
     <t xml:space="preserve">47.5561294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9961929321289</t>
+    <t xml:space="preserve">46.9961967468262</t>
   </si>
   <si>
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9495239257812</t>
+    <t xml:space="preserve">44.949520111084</t>
   </si>
   <si>
     <t xml:space="preserve">43.6751823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.647819519043</t>
+    <t xml:space="preserve">41.6478157043457</t>
   </si>
   <si>
     <t xml:space="preserve">42.8063087463379</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">44.119270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6253051757812</t>
+    <t xml:space="preserve">45.6253089904785</t>
   </si>
   <si>
     <t xml:space="preserve">47.0348129272461</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">44.157886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4627914428711</t>
+    <t xml:space="preserve">44.1578903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4627876281738</t>
   </si>
   <si>
     <t xml:space="preserve">44.1254501342773</t>
@@ -3449,19 +3449,19 @@
     <t xml:space="preserve">42.3908386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0400161743164</t>
+    <t xml:space="preserve">42.0400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">43.4043235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">44.827091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.444766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.431282043457</t>
+    <t xml:space="preserve">44.8270950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.645679473877</t>
+    <t xml:space="preserve">45.6456756591797</t>
   </si>
   <si>
     <t xml:space="preserve">45.3923072814941</t>
@@ -3485,22 +3485,22 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070495605469</t>
+    <t xml:space="preserve">41.0070457458496</t>
   </si>
   <si>
     <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3054046630859</t>
+    <t xml:space="preserve">40.3054084777832</t>
   </si>
   <si>
     <t xml:space="preserve">39.1360054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7012176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766250610352</t>
+    <t xml:space="preserve">39.7012138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766212463379</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3509,22 +3509,22 @@
     <t xml:space="preserve">40.3248977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8706130981445</t>
+    <t xml:space="preserve">40.8706169128418</t>
   </si>
   <si>
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7806396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0924797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8841018676758</t>
+    <t xml:space="preserve">41.8646087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7806434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8840980529785</t>
   </si>
   <si>
     <t xml:space="preserve">41.9620628356934</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0025024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3593368530273</t>
+    <t xml:space="preserve">45.0025062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507789611816</t>
+    <t xml:space="preserve">45.4507751464844</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3566,19 +3566,19 @@
     <t xml:space="preserve">51.7460594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9177322387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5511589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5488891601562</t>
+    <t xml:space="preserve">50.9177284240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5511627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.548885345459</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517112731934</t>
+    <t xml:space="preserve">55.3517189025879</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3599,19 +3599,19 @@
     <t xml:space="preserve">53.7437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1335868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1080932617188</t>
+    <t xml:space="preserve">54.1335906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1080894470215</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4491691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4004364013672</t>
+    <t xml:space="preserve">55.4491653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4004402160645</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">55.5466156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4746704101562</t>
+    <t xml:space="preserve">54.474666595459</t>
   </si>
   <si>
     <t xml:space="preserve">53.0616416931152</t>
@@ -3629,31 +3629,31 @@
     <t xml:space="preserve">52.5743865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5256576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4792022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7970542907715</t>
+    <t xml:space="preserve">52.5256614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4792060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7970504760742</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8690071105957</t>
+    <t xml:space="preserve">50.869010925293</t>
   </si>
   <si>
     <t xml:space="preserve">50.771556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0151824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384101867676</t>
+    <t xml:space="preserve">51.0151786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384063720703</t>
   </si>
   <si>
     <t xml:space="preserve">51.4537086486816</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8015937805176</t>
+    <t xml:space="preserve">45.8015975952148</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">46.8345718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5362129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7738304138184</t>
+    <t xml:space="preserve">47.5362091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">47.7311096191406</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483291625977</t>
+    <t xml:space="preserve">49.7483329772949</t>
   </si>
   <si>
     <t xml:space="preserve">48.4522438049316</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494491577148</t>
+    <t xml:space="preserve">57.3494453430176</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698432922363</t>
+    <t xml:space="preserve">56.5698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3752,37 +3752,37 @@
     <t xml:space="preserve">60.8576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0038299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8111991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6395225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8599281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2497253417969</t>
+    <t xml:space="preserve">61.0038261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8111953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6395263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8599243164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2497215270996</t>
   </si>
   <si>
     <t xml:space="preserve">57.9828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4213981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6882476806641</t>
+    <t xml:space="preserve">58.4214019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6882514953613</t>
   </si>
   <si>
     <t xml:space="preserve">61.2961807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2684097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.319408416748</t>
+    <t xml:space="preserve">64.2684020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3194046020508</t>
   </si>
   <si>
     <t xml:space="preserve">63.0502815246582</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.484260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1176910400391</t>
+    <t xml:space="preserve">67.4842681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1176986694336</t>
   </si>
   <si>
     <t xml:space="preserve">69.8230819702148</t>
@@ -3824,16 +3824,16 @@
     <t xml:space="preserve">67.1919097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8972930908203</t>
+    <t xml:space="preserve">68.8972854614258</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4865341186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5817108154297</t>
+    <t xml:space="preserve">65.4865417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5817184448242</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8995742797852</t>
+    <t xml:space="preserve">66.8995666503906</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
@@ -3863,19 +3863,19 @@
     <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0434646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6514053344727</t>
+    <t xml:space="preserve">69.0434722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6513977050781</t>
   </si>
   <si>
     <t xml:space="preserve">71.7233505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4309997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5284576416016</t>
+    <t xml:space="preserve">71.4310073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.528450012207</t>
   </si>
   <si>
     <t xml:space="preserve">72.6978530883789</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.305778503418</t>
+    <t xml:space="preserve">74.3057861328125</t>
   </si>
   <si>
     <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7188110351562</t>
+    <t xml:space="preserve">75.7188034057617</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">76.839485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">77.2780227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.3754653930664</t>
+    <t xml:space="preserve">77.2780151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.3754577636719</t>
   </si>
   <si>
     <t xml:space="preserve">74.9879302978516</t>
@@ -3920,10 +3920,10 @@
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859329223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.5703659057617</t>
+    <t xml:space="preserve">78.8859405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.5703582763672</t>
   </si>
   <si>
     <t xml:space="preserve">77.1805572509766</t>
@@ -3932,28 +3932,28 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.424186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0831069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6678161621094</t>
+    <t xml:space="preserve">78.0088958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.4241790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6678085327148</t>
   </si>
   <si>
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.032112121582</t>
+    <t xml:space="preserve">78.3012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0321197509766</t>
   </si>
   <si>
     <t xml:space="preserve">78.4474182128906</t>
@@ -3962,16 +3962,16 @@
     <t xml:space="preserve">77.8139877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">77.4729156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9647064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4519653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.82080078125</t>
+    <t xml:space="preserve">77.4729080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.964714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">77.9601593017578</t>
@@ -3983,34 +3983,34 @@
     <t xml:space="preserve">77.7165374755859</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2989730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7119903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4683685302734</t>
+    <t xml:space="preserve">80.3964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2989654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7119979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.468376159668</t>
   </si>
   <si>
     <t xml:space="preserve">81.8581695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1924362182617</t>
+    <t xml:space="preserve">81.7607192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2689361572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1924438476562</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488143920898</t>
+    <t xml:space="preserve">87.9488067626953</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">87.9000854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">86.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434387207031</t>
+    <t xml:space="preserve">86.3408737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434234619141</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2876129150391</t>
+    <t xml:space="preserve">90.2876205444336</t>
   </si>
   <si>
     <t xml:space="preserve">87.8513641357422</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">89.3618316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">86.0972518920898</t>
+    <t xml:space="preserve">86.0972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360656738281</t>
+    <t xml:space="preserve">88.4360580444336</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1017990112305</t>
+    <t xml:space="preserve">82.1017913818359</t>
   </si>
   <si>
     <t xml:space="preserve">83.1250305175781</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559036254883</t>
+    <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0043487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4196472167969</t>
+    <t xml:space="preserve">82.0043411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4196548461914</t>
   </si>
   <si>
     <t xml:space="preserve">79.2270278930664</t>
@@ -4082,25 +4082,25 @@
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5299453735352</t>
+    <t xml:space="preserve">79.9091720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096496582031</t>
+    <t xml:space="preserve">77.1096420288086</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.632194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830841064453</t>
+    <t xml:space="preserve">78.6322021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618179321289</t>
+    <t xml:space="preserve">79.7618255615234</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370239257812</t>
+    <t xml:space="preserve">81.1370315551758</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909713745117</t>
+    <t xml:space="preserve">83.6909790039062</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.628173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317169189453</t>
+    <t xml:space="preserve">81.6281661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317092895508</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.07421875</t>
+    <t xml:space="preserve">79.0742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9268798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0959548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326644897461</t>
+    <t xml:space="preserve">78.926872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326721191406</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853256225586</t>
+    <t xml:space="preserve">75.6853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928970336914</t>
+    <t xml:space="preserve">72.4928894042969</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870895385742</t>
+    <t xml:space="preserve">75.5870971679688</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402282714844</t>
+    <t xml:space="preserve">72.6402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176910400391</t>
+    <t xml:space="preserve">71.1176834106445</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597076416016</t>
+    <t xml:space="preserve">71.5597152709961</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4253,19 +4253,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022247314453</t>
+    <t xml:space="preserve">72.3946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022171020508</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212265014648</t>
+    <t xml:space="preserve">70.9212188720703</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5419998168945</t>
+    <t xml:space="preserve">72.5420074462891</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389343261719</t>
+    <t xml:space="preserve">73.4260711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.827018737793</t>
+    <t xml:space="preserve">67.8270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247695922852</t>
+    <t xml:space="preserve">70.7247772216797</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.5460205078125</t>
+    <t xml:space="preserve">69.546028137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698593139648</t>
+    <t xml:space="preserve">73.7698669433594</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4364,19 +4364,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065841674805</t>
+    <t xml:space="preserve">77.6007919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065765380859</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481307983398</t>
+    <t xml:space="preserve">77.7481384277344</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4397,25 +4397,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.9309005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238143920898</t>
+    <t xml:space="preserve">75.930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238067626953</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344360351562</t>
+    <t xml:space="preserve">75.7344436645508</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4445,19 +4445,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.905143737793</t>
+    <t xml:space="preserve">82.9051513671875</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046737670898</t>
+    <t xml:space="preserve">85.7046661376953</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851791381836</t>
+    <t xml:space="preserve">86.7851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4469,13 +4469,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542541503906</t>
+    <t xml:space="preserve">82.9542617797852</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489471435547</t>
+    <t xml:space="preserve">83.2489547729492</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4487,16 +4487,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312393188477</t>
+    <t xml:space="preserve">84.2312316894531</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507186889648</t>
+    <t xml:space="preserve">82.5613479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507263183594</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338272094727</t>
+    <t xml:space="preserve">89.6338195800781</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581359863281</t>
+    <t xml:space="preserve">91.0581436157227</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.857666015625</t>
+    <t xml:space="preserve">93.8576736450195</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747375488281</t>
+    <t xml:space="preserve">102.845596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.827896118164</t>
+    <t xml:space="preserve">103.82788848877</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034027099609</t>
+    <t xml:space="preserve">109.034019470215</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525169372559</t>
+    <t xml:space="preserve">109.525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.631439208984</t>
+    <t xml:space="preserve">103.63143157959</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122573852539</t>
+    <t xml:space="preserve">102.158004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122581481934</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987426757812</t>
+    <t xml:space="preserve">99.8987350463867</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518661499023</t>
+    <t xml:space="preserve">96.3625030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518737792969</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4670,13 +4670,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2642669677734</t>
+    <t xml:space="preserve">96.264274597168</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5589599609375</t>
+    <t xml:space="preserve">96.558967590332</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890609741211</t>
+    <t xml:space="preserve">94.8890686035156</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488082885742</t>
+    <t xml:space="preserve">94.7417144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488159179688</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5643,6 +5643,9 @@
   </si>
   <si>
     <t xml:space="preserve">89.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3600006103516</t>
   </si>
 </sst>
 </file>
@@ -70825,7 +70828,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494328704</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>491856</v>
@@ -70846,6 +70849,32 @@
         <v>1876</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6495717593</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>415439</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>91.8000030517578</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>89.379997253418</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>89.379997253418</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>90.3600006103516</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1877</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="1879">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537855148315</t>
+    <t xml:space="preserve">14.8537864685059</t>
   </si>
   <si>
     <t xml:space="preserve">14.4801063537598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1718196868896</t>
+    <t xml:space="preserve">14.1718187332153</t>
   </si>
   <si>
     <t xml:space="preserve">13.9476127624512</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0406255722046</t>
+    <t xml:space="preserve">15.0406284332275</t>
   </si>
   <si>
     <t xml:space="preserve">15.3208866119385</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">15.3022003173828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.44273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389188766479</t>
+    <t xml:space="preserve">14.4427375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389198303223</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0410308837891</t>
+    <t xml:space="preserve">14.0410318374634</t>
   </si>
   <si>
     <t xml:space="preserve">14.3212928771973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3399772644043</t>
+    <t xml:space="preserve">14.33997631073</t>
   </si>
   <si>
     <t xml:space="preserve">14.7697086334229</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">14.3866853713989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240550994873</t>
+    <t xml:space="preserve">13.9943208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240531921387</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9849815368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036630630493</t>
+    <t xml:space="preserve">13.9849796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036640167236</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338006973267</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">12.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155225753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4061813354492</t>
+    <t xml:space="preserve">12.4155235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4061803817749</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172292709351</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">13.1722259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5645904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057769775391</t>
+    <t xml:space="preserve">13.5645895004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057750701904</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777484893799</t>
@@ -146,34 +146,34 @@
     <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7607707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.835506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1064252853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372140884399</t>
+    <t xml:space="preserve">13.7607727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8355073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.106424331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372131347656</t>
   </si>
   <si>
     <t xml:space="preserve">14.4520807266235</t>
   </si>
   <si>
-    <t xml:space="preserve">14.255898475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4143037796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.601146697998</t>
+    <t xml:space="preserve">14.2558994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011476516724</t>
   </si>
   <si>
     <t xml:space="preserve">15.2461500167847</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1060199737549</t>
+    <t xml:space="preserve">15.1060209274292</t>
   </si>
   <si>
     <t xml:space="preserve">15.3769369125366</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">15.4797010421753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6385145187378</t>
+    <t xml:space="preserve">15.6385154724121</t>
   </si>
   <si>
     <t xml:space="preserve">15.5450944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873365402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939155578613</t>
+    <t xml:space="preserve">15.6945657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983835220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">14.6202354431152</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">15.1527299880981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3302297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225904464722</t>
+    <t xml:space="preserve">15.330228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225923538208</t>
   </si>
   <si>
     <t xml:space="preserve">15.7412757873535</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">15.8253564834595</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3017959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858776092529</t>
+    <t xml:space="preserve">16.3017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858757019043</t>
   </si>
   <si>
     <t xml:space="preserve">16.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4139003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924537658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0215339660645</t>
+    <t xml:space="preserve">16.2550868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4138984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671894073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0215377807617</t>
   </si>
   <si>
     <t xml:space="preserve">16.2177200317383</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">16.3765316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391666412354</t>
+    <t xml:space="preserve">16.3391647338867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1149578094482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2737712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325866699219</t>
+    <t xml:space="preserve">16.2737731933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325847625732</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100845336914</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">16.6287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4419250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889812469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489791870117</t>
+    <t xml:space="preserve">16.4419288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6489810943604</t>
   </si>
   <si>
     <t xml:space="preserve">16.5548667907715</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6866245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995643615723</t>
+    <t xml:space="preserve">16.6866264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995624542236</t>
   </si>
   <si>
     <t xml:space="preserve">16.5454540252686</t>
@@ -311,43 +311,43 @@
     <t xml:space="preserve">16.6583919525146</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8277988433838</t>
+    <t xml:space="preserve">16.8278007507324</t>
   </si>
   <si>
     <t xml:space="preserve">16.8183898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725427627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078294754028</t>
+    <t xml:space="preserve">16.2254619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725408554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078285217285</t>
   </si>
   <si>
     <t xml:space="preserve">15.3407793045044</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5830993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.253698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642757415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290069580078</t>
+    <t xml:space="preserve">16.5830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2536964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290088653564</t>
   </si>
   <si>
     <t xml:space="preserve">14.8796148300171</t>
@@ -356,28 +356,28 @@
     <t xml:space="preserve">15.0678453445435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2748985290527</t>
+    <t xml:space="preserve">15.2748975753784</t>
   </si>
   <si>
     <t xml:space="preserve">15.2090167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101871490479</t>
+    <t xml:space="preserve">15.5101842880249</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.314923286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9172601699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384187698364</t>
+    <t xml:space="preserve">14.3149242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.644326210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9172611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384197235107</t>
   </si>
   <si>
     <t xml:space="preserve">15.6513595581055</t>
@@ -386,49 +386,49 @@
     <t xml:space="preserve">15.5195980072021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4348945617676</t>
+    <t xml:space="preserve">15.4348955154419</t>
   </si>
   <si>
     <t xml:space="preserve">15.5854787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9054708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301773071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.547833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701831817627</t>
+    <t xml:space="preserve">15.9054698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901723861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337034225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701822280884</t>
   </si>
   <si>
     <t xml:space="preserve">15.3784246444702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5007743835449</t>
+    <t xml:space="preserve">15.5007734298706</t>
   </si>
   <si>
     <t xml:space="preserve">15.6419467926025</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9148817062378</t>
+    <t xml:space="preserve">15.9148826599121</t>
   </si>
   <si>
     <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2725200653076</t>
+    <t xml:space="preserve">16.2725219726562</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195781707764</t>
@@ -440,37 +440,37 @@
     <t xml:space="preserve">16.1595821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607524871826</t>
+    <t xml:space="preserve">16.3760471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.460750579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.5078105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6301574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4701614379883</t>
+    <t xml:space="preserve">16.6301593780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4701595306396</t>
   </si>
   <si>
     <t xml:space="preserve">16.7807426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8560333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9877948760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407367706299</t>
+    <t xml:space="preserve">16.8560352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9877967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0160293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407405853271</t>
   </si>
   <si>
     <t xml:space="preserve">16.8372097015381</t>
@@ -482,25 +482,25 @@
     <t xml:space="preserve">16.978385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8466243743896</t>
+    <t xml:space="preserve">16.846622467041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8936805725098</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6960372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9125022888184</t>
+    <t xml:space="preserve">16.6960391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.912504196167</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713298797607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8089752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231033325195</t>
+    <t xml:space="preserve">16.8089790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231052398682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8842697143555</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">17.0536766052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0348529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619152069092</t>
+    <t xml:space="preserve">16.8748588562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.034854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654460906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619209289551</t>
   </si>
   <si>
     <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2324924468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2136707305908</t>
+    <t xml:space="preserve">17.232494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2607326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2136726379395</t>
   </si>
   <si>
     <t xml:space="preserve">17.3548450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3642597198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3077850341797</t>
+    <t xml:space="preserve">17.3642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077869415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.298376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724765777588</t>
+    <t xml:space="preserve">17.6936569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724784851074</t>
   </si>
   <si>
     <t xml:space="preserve">18.738338470459</t>
@@ -575,100 +575,100 @@
     <t xml:space="preserve">18.8230400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6818695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.804220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3406753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3783187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359817504883</t>
+    <t xml:space="preserve">18.6818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3406715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
     <t xml:space="preserve">19.2183265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5571422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4159679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.423002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2347679138184</t>
+    <t xml:space="preserve">19.5571403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4159660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724151611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4230003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.234769821167</t>
   </si>
   <si>
     <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4982929229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.357120513916</t>
+    <t xml:space="preserve">20.498291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3571186065674</t>
   </si>
   <si>
     <t xml:space="preserve">20.8935775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.103006362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206634521484</t>
+    <t xml:space="preserve">20.6677017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206615447998</t>
   </si>
   <si>
     <t xml:space="preserve">19.7453708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5194931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6888999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171363830566</t>
+    <t xml:space="preserve">19.519495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6889019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171382904053</t>
   </si>
   <si>
     <t xml:space="preserve">19.84889793396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5759601593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2747936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4442024230957</t>
+    <t xml:space="preserve">19.575963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2747917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4442043304443</t>
   </si>
   <si>
     <t xml:space="preserve">19.3877353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3500881195068</t>
+    <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
     <t xml:space="preserve">19.3971462249756</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">19.0959777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0018615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171581268311</t>
+    <t xml:space="preserve">19.0018634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171562194824</t>
   </si>
   <si>
     <t xml:space="preserve">19.0865650177002</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936408996582</t>
+    <t xml:space="preserve">18.4936389923096</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524684906006</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">19.2559700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.510082244873</t>
+    <t xml:space="preserve">19.5100841522217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371482849121</t>
@@ -716,46 +716,46 @@
     <t xml:space="preserve">19.5006713867188</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7547855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994632720947</t>
+    <t xml:space="preserve">19.7547817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924289703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947856903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335834503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994613647461</t>
   </si>
   <si>
     <t xml:space="preserve">20.7900505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9218101501465</t>
+    <t xml:space="preserve">20.9218120574951</t>
   </si>
   <si>
     <t xml:space="preserve">21.3641529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.298267364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0159282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253353118896</t>
+    <t xml:space="preserve">21.2982711791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.015926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253391265869</t>
   </si>
   <si>
     <t xml:space="preserve">20.9876918792725</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6088485717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2135715484619</t>
+    <t xml:space="preserve">21.1100406646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.608850479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2135696411133</t>
   </si>
   <si>
     <t xml:space="preserve">21.3829746246338</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">21.5429706573486</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8347263336182</t>
+    <t xml:space="preserve">21.8347282409668</t>
   </si>
   <si>
     <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8064956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0417823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582454681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252994537354</t>
+    <t xml:space="preserve">21.8064937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0417804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252975463867</t>
   </si>
   <si>
     <t xml:space="preserve">23.0394039154053</t>
@@ -818,52 +818,52 @@
     <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5876522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3711814880371</t>
+    <t xml:space="preserve">22.5876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.371187210083</t>
   </si>
   <si>
     <t xml:space="preserve">22.0135459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6464996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.91943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.787670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3076839447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.117073059082</t>
+    <t xml:space="preserve">21.6464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9194316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7876720428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3076877593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
     <t xml:space="preserve">22.098123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1455039978027</t>
+    <t xml:space="preserve">22.1455059051514</t>
   </si>
   <si>
     <t xml:space="preserve">22.1549777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2686901092529</t>
+    <t xml:space="preserve">22.2686920166016</t>
   </si>
   <si>
     <t xml:space="preserve">22.0507431030273</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190799713135</t>
+    <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
     <t xml:space="preserve">22.0886459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7569828033447</t>
+    <t xml:space="preserve">21.7569808959961</t>
   </si>
   <si>
     <t xml:space="preserve">21.8327922821045</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200824737549</t>
+    <t xml:space="preserve">21.7285575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200843811035</t>
   </si>
   <si>
     <t xml:space="preserve">21.1315670013428</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4158458709717</t>
+    <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
     <t xml:space="preserve">21.8612213134766</t>
@@ -902,22 +902,22 @@
     <t xml:space="preserve">21.662223815918</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5674629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5624485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4013557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5813999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6761627197266</t>
+    <t xml:space="preserve">21.5674648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5624465942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
     <t xml:space="preserve">22.590877532959</t>
@@ -932,31 +932,31 @@
     <t xml:space="preserve">21.8422679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.671703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958919525146</t>
+    <t xml:space="preserve">21.6716995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958938598633</t>
   </si>
   <si>
     <t xml:space="preserve">22.4676876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3255481719971</t>
+    <t xml:space="preserve">22.3255500793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.5055923461914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6951141357422</t>
+    <t xml:space="preserve">22.6951122283936</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0362491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2068195343018</t>
+    <t xml:space="preserve">23.0362510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162952423096</t>
@@ -965,37 +965,37 @@
     <t xml:space="preserve">22.9983463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1310119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5005741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.405818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.453197479248</t>
+    <t xml:space="preserve">23.131010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5005760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404838562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4058170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9509620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0646800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7519702911377</t>
+    <t xml:space="preserve">22.9509658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7519721984863</t>
   </si>
   <si>
     <t xml:space="preserve">22.723539352417</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6477317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4771633148193</t>
+    <t xml:space="preserve">22.6477336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4771614074707</t>
   </si>
   <si>
     <t xml:space="preserve">22.183406829834</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">23.87961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1165180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6616668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783924102783</t>
+    <t xml:space="preserve">24.1165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6616687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783905029297</t>
   </si>
   <si>
     <t xml:space="preserve">22.9035873413086</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">24.0217590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145130157471</t>
+    <t xml:space="preserve">24.4955577850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145111083984</t>
   </si>
   <si>
     <t xml:space="preserve">24.6377010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6850833892822</t>
+    <t xml:space="preserve">24.6850814819336</t>
   </si>
   <si>
     <t xml:space="preserve">24.5903205871582</t>
@@ -1058,49 +1058,49 @@
     <t xml:space="preserve">24.7798404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7229843139648</t>
+    <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">24.5429401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1638984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8651237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5473976135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052581787109</t>
+    <t xml:space="preserve">24.1639003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8651256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5474014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052600860596</t>
   </si>
   <si>
     <t xml:space="preserve">25.4431648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4905433654785</t>
+    <t xml:space="preserve">25.4905452728271</t>
   </si>
   <si>
     <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3294506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0830726623535</t>
+    <t xml:space="preserve">25.3484039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3294525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">25.727445602417</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">25.6611137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9643459320068</t>
+    <t xml:space="preserve">25.9643421173096</t>
   </si>
   <si>
     <t xml:space="preserve">26.3054847717285</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">26.9119472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0635662078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6750469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678066253662</t>
+    <t xml:space="preserve">27.0635681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.675048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678047180176</t>
   </si>
   <si>
     <t xml:space="preserve">26.4665756225586</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">26.0591049194336</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0451698303223</t>
+    <t xml:space="preserve">25.0451717376709</t>
   </si>
   <si>
     <t xml:space="preserve">25.1778354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1967868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5189723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1115036010742</t>
+    <t xml:space="preserve">25.1967849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1115055084229</t>
   </si>
   <si>
     <t xml:space="preserve">25.5379238128662</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.301025390625</t>
+    <t xml:space="preserve">25.3010215759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.2631187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1683597564697</t>
+    <t xml:space="preserve">25.1683578491211</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219818115234</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">25.2062606811523</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042575836182</t>
+    <t xml:space="preserve">25.1020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042556762695</t>
   </si>
   <si>
     <t xml:space="preserve">25.8601093292236</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">26.248628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4381465911865</t>
+    <t xml:space="preserve">26.4381504058838</t>
   </si>
   <si>
     <t xml:space="preserve">24.7987937927246</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">25.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232109069824</t>
+    <t xml:space="preserve">25.6232089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.7748279571533</t>
@@ -1223,64 +1223,64 @@
     <t xml:space="preserve">25.5947799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7084903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1064872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8171882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0540924072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3857517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222026824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9169673919678</t>
+    <t xml:space="preserve">25.7084941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1064853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8171863555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540904998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9169654846191</t>
   </si>
   <si>
     <t xml:space="preserve">25.6326847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7324600219727</t>
+    <t xml:space="preserve">24.7324619293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.9743766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008007049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0691413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481792449951</t>
+    <t xml:space="preserve">24.4007987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0691375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481773376465</t>
   </si>
   <si>
     <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7848587036133</t>
+    <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
     <t xml:space="preserve">24.2586612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0641231536865</t>
+    <t xml:space="preserve">25.0641250610352</t>
   </si>
   <si>
     <t xml:space="preserve">25.0167427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9693603515625</t>
+    <t xml:space="preserve">24.9693641662598</t>
   </si>
   <si>
     <t xml:space="preserve">23.9269981384277</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">26.153865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4855270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5329093933105</t>
+    <t xml:space="preserve">26.4855289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5329113006592</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593315124512</t>
@@ -1316,28 +1316,28 @@
     <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8071556091309</t>
+    <t xml:space="preserve">28.8071575164795</t>
   </si>
   <si>
     <t xml:space="preserve">28.665018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3283424377441</t>
+    <t xml:space="preserve">29.3283405303955</t>
   </si>
   <si>
     <t xml:space="preserve">29.2335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5394897460938</t>
+    <t xml:space="preserve">29.5394916534424</t>
   </si>
   <si>
     <t xml:space="preserve">30.2086696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0652770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042640686035</t>
+    <t xml:space="preserve">30.0652751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042678833008</t>
   </si>
   <si>
     <t xml:space="preserve">29.9696788787842</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602386474609</t>
+    <t xml:space="preserve">31.2602405548096</t>
   </si>
   <si>
     <t xml:space="preserve">32.7419929504395</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">33.6501617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0803565979004</t>
+    <t xml:space="preserve">34.0803527832031</t>
   </si>
   <si>
     <t xml:space="preserve">35.1797180175781</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149436950684</t>
+    <t xml:space="preserve">34.4149475097656</t>
   </si>
   <si>
     <t xml:space="preserve">33.936954498291</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">35.753303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2275161743164</t>
+    <t xml:space="preserve">35.7532997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2275123596191</t>
   </si>
   <si>
     <t xml:space="preserve">35.0841217041016</t>
@@ -1397,37 +1397,37 @@
     <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3746757507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4187088012695</t>
+    <t xml:space="preserve">36.3746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4187049865723</t>
   </si>
   <si>
     <t xml:space="preserve">36.5658760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8526611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822532653809</t>
+    <t xml:space="preserve">36.8526649475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822551727295</t>
   </si>
   <si>
     <t xml:space="preserve">31.1168422698975</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4036350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5948257446289</t>
+    <t xml:space="preserve">31.4036331176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5948276519775</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">31.212438583374</t>
+    <t xml:space="preserve">31.2124404907227</t>
   </si>
   <si>
     <t xml:space="preserve">33.0287857055664</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">33.7935562133789</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9847564697266</t>
+    <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
     <t xml:space="preserve">34.7973289489746</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">34.6061401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4627380371094</t>
+    <t xml:space="preserve">34.4627418518066</t>
   </si>
   <si>
     <t xml:space="preserve">33.8413581848145</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.040096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966941833496</t>
+    <t xml:space="preserve">36.0400886535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966903686523</t>
   </si>
   <si>
     <t xml:space="preserve">36.6614685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306541442871</t>
+    <t xml:space="preserve">39.0035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4262466430664</t>
+    <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
     <t xml:space="preserve">37.8564338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2790832519531</t>
+    <t xml:space="preserve">36.2790870666504</t>
   </si>
   <si>
     <t xml:space="preserve">37.2350540161133</t>
@@ -1508,22 +1508,22 @@
     <t xml:space="preserve">33.5067672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2677726745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9809875488281</t>
+    <t xml:space="preserve">33.2677764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9809837341309</t>
   </si>
   <si>
     <t xml:space="preserve">33.3633766174316</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7897872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8375854492188</t>
+    <t xml:space="preserve">32.7897911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.837589263916</t>
   </si>
   <si>
     <t xml:space="preserve">32.5985946655273</t>
@@ -1532,55 +1532,55 @@
     <t xml:space="preserve">32.503002166748</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2199783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6464004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3596000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7860221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690441131592</t>
+    <t xml:space="preserve">33.2199821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6463928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3596038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.072811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7860202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690422058105</t>
   </si>
   <si>
     <t xml:space="preserve">32.025016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0212421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357227325439</t>
+    <t xml:space="preserve">31.0212440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709426879883</t>
+    <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2489280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797519683838</t>
+    <t xml:space="preserve">28.248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797500610352</t>
   </si>
   <si>
     <t xml:space="preserve">28.1055355072021</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">27.2451610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9621391296387</t>
+    <t xml:space="preserve">27.96213722229</t>
   </si>
   <si>
     <t xml:space="preserve">28.3445281982422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0137062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181118011475</t>
+    <t xml:space="preserve">29.013708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181098937988</t>
   </si>
   <si>
     <t xml:space="preserve">29.2049007415771</t>
@@ -1607,46 +1607,46 @@
     <t xml:space="preserve">30.4954605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5872917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344532012939</t>
+    <t xml:space="preserve">29.5872898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344551086426</t>
   </si>
   <si>
     <t xml:space="preserve">30.0174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4438934326172</t>
+    <t xml:space="preserve">29.4438915252686</t>
   </si>
   <si>
     <t xml:space="preserve">29.6828842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3847885131836</t>
+    <t xml:space="preserve">28.5835189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.384786605835</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4363555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187446594238</t>
+    <t xml:space="preserve">27.4363574981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187427520752</t>
   </si>
   <si>
     <t xml:space="preserve">27.7231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350898742676</t>
+    <t xml:space="preserve">28.6313190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
     <t xml:space="preserve">27.1017665863037</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">27.4841537475586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0061683654785</t>
+    <t xml:space="preserve">27.0061664581299</t>
   </si>
   <si>
     <t xml:space="preserve">26.0979957580566</t>
@@ -1667,28 +1667,28 @@
     <t xml:space="preserve">25.6200103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1935939788818</t>
+    <t xml:space="preserve">26.1935920715332</t>
   </si>
   <si>
     <t xml:space="preserve">26.6237812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7156066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.289192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671756744385</t>
+    <t xml:space="preserve">25.7156085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2891902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671775817871</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6791152954102</t>
+    <t xml:space="preserve">28.9659099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6791172027588</t>
   </si>
   <si>
     <t xml:space="preserve">29.1093044281006</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3885555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8225135803223</t>
+    <t xml:space="preserve">26.4803867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.388557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
     <t xml:space="preserve">29.8740825653076</t>
@@ -1718,64 +1718,64 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080348968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.45143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4552040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3118057250977</t>
+    <t xml:space="preserve">31.3080368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4514350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3118019104004</t>
   </si>
   <si>
     <t xml:space="preserve">32.2162055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">33.602367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1721839904785</t>
+    <t xml:space="preserve">33.6023635864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1721801757812</t>
   </si>
   <si>
     <t xml:space="preserve">33.5545692443848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2564697265625</t>
+    <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
     <t xml:space="preserve">30.6388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5910606384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409980773926</t>
+    <t xml:space="preserve">30.5910587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409961700439</t>
   </si>
   <si>
     <t xml:space="preserve">30.6484203338623</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8204936981201</t>
+    <t xml:space="preserve">30.8204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">30.9734477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2851467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748310089111</t>
+    <t xml:space="preserve">30.2851486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748348236084</t>
   </si>
   <si>
     <t xml:space="preserve">30.4763412475586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2277889251709</t>
+    <t xml:space="preserve">30.2277908325195</t>
   </si>
   <si>
     <t xml:space="preserve">29.9983558654785</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">30.438102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352111816406</t>
+    <t xml:space="preserve">30.7631340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935209274292</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8129539489746</t>
+    <t xml:space="preserve">28.812952041626</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203704833984</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">28.717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821357727051</t>
+    <t xml:space="preserve">29.4821319580078</t>
   </si>
   <si>
     <t xml:space="preserve">29.1762218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291759490967</t>
+    <t xml:space="preserve">29.3291778564453</t>
   </si>
   <si>
     <t xml:space="preserve">28.5761585235596</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">28.5182342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8038272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0741443634033</t>
+    <t xml:space="preserve">27.8038291931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0741424560547</t>
   </si>
   <si>
     <t xml:space="preserve">27.1859664916992</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">27.8617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7845230102539</t>
+    <t xml:space="preserve">27.7845211029053</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548343658447</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">28.8850898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2712516784668</t>
+    <t xml:space="preserve">29.2712535858154</t>
   </si>
   <si>
     <t xml:space="preserve">29.8311901092529</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8505001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539577484131</t>
+    <t xml:space="preserve">29.8504981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539596557617</t>
   </si>
   <si>
     <t xml:space="preserve">30.2173557281494</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">29.9856586456299</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6807556152344</t>
+    <t xml:space="preserve">30.6807537078857</t>
   </si>
   <si>
     <t xml:space="preserve">29.3677959442139</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">29.4257202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2519454956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.464334487915</t>
+    <t xml:space="preserve">29.2519435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4643363952637</t>
   </si>
   <si>
     <t xml:space="preserve">29.0202465057373</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4796161651611</t>
+    <t xml:space="preserve">28.4796180725098</t>
   </si>
   <si>
     <t xml:space="preserve">27.7652111053467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1666584014893</t>
+    <t xml:space="preserve">27.1666564941406</t>
   </si>
   <si>
     <t xml:space="preserve">26.9542675018311</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">27.1473503112793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2825088500977</t>
+    <t xml:space="preserve">27.282506942749</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">26.683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5101776123047</t>
+    <t xml:space="preserve">26.5101795196533</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
@@ -2009,25 +2009,25 @@
     <t xml:space="preserve">27.0314998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6260280609131</t>
+    <t xml:space="preserve">26.6260299682617</t>
   </si>
   <si>
     <t xml:space="preserve">27.4176635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0894241333008</t>
+    <t xml:space="preserve">28.0355281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0894222259521</t>
   </si>
   <si>
     <t xml:space="preserve">26.9928817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0508117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755897521973</t>
+    <t xml:space="preserve">27.0508098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755878448486</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">27.591438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">27.610746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6879806518555</t>
+    <t xml:space="preserve">27.6107482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6879825592041</t>
   </si>
   <si>
     <t xml:space="preserve">26.355712890625</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.301815032959</t>
+    <t xml:space="preserve">27.3018169403076</t>
   </si>
   <si>
     <t xml:space="preserve">27.4562816619873</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">28.3830757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9430141448975</t>
+    <t xml:space="preserve">28.9430122375488</t>
   </si>
   <si>
     <t xml:space="preserve">29.4064083099365</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">28.7499313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8271656036377</t>
+    <t xml:space="preserve">28.8271636962891</t>
   </si>
   <si>
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954666137695</t>
+    <t xml:space="preserve">28.5954685211182</t>
   </si>
   <si>
     <t xml:space="preserve">28.6147727966309</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">29.2133312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6228294372559</t>
+    <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
     <t xml:space="preserve">31.9357872009277</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">32.3026390075684</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4571075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.858549118042</t>
+    <t xml:space="preserve">32.457103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8585529327393</t>
   </si>
   <si>
     <t xml:space="preserve">31.2213802337646</t>
@@ -2138,19 +2138,19 @@
     <t xml:space="preserve">31.182767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6654739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1674842834473</t>
+    <t xml:space="preserve">31.6654720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1674880981445</t>
   </si>
   <si>
     <t xml:space="preserve">31.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5882415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.047607421875</t>
+    <t xml:space="preserve">31.5882396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0476093292236</t>
   </si>
   <si>
     <t xml:space="preserve">30.9510707855225</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">30.7000598907471</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0170516967773</t>
+    <t xml:space="preserve">33.0170478820801</t>
   </si>
   <si>
     <t xml:space="preserve">33.3645935058594</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">34.8899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0250968933105</t>
+    <t xml:space="preserve">35.0251007080078</t>
   </si>
   <si>
     <t xml:space="preserve">35.9712028503418</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">36.5311431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.955924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2069320678711</t>
+    <t xml:space="preserve">36.9559211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2069282531738</t>
   </si>
   <si>
     <t xml:space="preserve">35.7008895874023</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">33.0363578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9205055236816</t>
+    <t xml:space="preserve">32.9205017089844</t>
   </si>
   <si>
     <t xml:space="preserve">31.9937133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6847839355469</t>
+    <t xml:space="preserve">31.6847801208496</t>
   </si>
   <si>
     <t xml:space="preserve">31.8778629302979</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">32.8239669799805</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9011993408203</t>
+    <t xml:space="preserve">32.901195526123</t>
   </si>
   <si>
     <t xml:space="preserve">32.2447166442871</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">32.5343399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4764175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6928367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081184387207</t>
+    <t xml:space="preserve">32.4764137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081146240234</t>
   </si>
   <si>
     <t xml:space="preserve">29.3871021270752</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">28.9623203277588</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8698081970215</t>
+    <t xml:space="preserve">29.8698101043701</t>
   </si>
   <si>
     <t xml:space="preserve">29.7732696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0049667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0274715423584</t>
+    <t xml:space="preserve">30.0049648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.027473449707</t>
   </si>
   <si>
     <t xml:space="preserve">26.2784805297852</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">26.1240119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5407409667969</t>
+    <t xml:space="preserve">24.5407428741455</t>
   </si>
   <si>
     <t xml:space="preserve">24.1931934356689</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">25.737850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150844573975</t>
+    <t xml:space="preserve">25.8150825500488</t>
   </si>
   <si>
     <t xml:space="preserve">25.100679397583</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">24.4441986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9075965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0427551269531</t>
+    <t xml:space="preserve">24.9075946807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">25.6220016479492</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">25.718542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4482269287109</t>
+    <t xml:space="preserve">25.4482288360596</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833854675293</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">26.5487957000732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9349575042725</t>
+    <t xml:space="preserve">26.9349594116211</t>
   </si>
   <si>
     <t xml:space="preserve">26.4522533416748</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">25.8923149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.066089630127</t>
+    <t xml:space="preserve">26.0660915374756</t>
   </si>
   <si>
     <t xml:space="preserve">26.973575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3750228881836</t>
+    <t xml:space="preserve">26.375020980835</t>
   </si>
   <si>
     <t xml:space="preserve">28.0162200927734</t>
@@ -2423,25 +2423,25 @@
     <t xml:space="preserve">26.5681056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5061531066895</t>
+    <t xml:space="preserve">25.5061511993408</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903026580811</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5254592895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4055862426758</t>
+    <t xml:space="preserve">25.5254611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4055843353271</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2511177062988</t>
+    <t xml:space="preserve">24.6565914154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2511196136475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2897338867188</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">24.5793552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8496704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3283519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8303642272949</t>
+    <t xml:space="preserve">24.8496723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3283500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8303623199463</t>
   </si>
   <si>
     <t xml:space="preserve">24.3862762451172</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">24.1352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1545753479004</t>
+    <t xml:space="preserve">24.154577255249</t>
   </si>
   <si>
     <t xml:space="preserve">24.0387268066406</t>
@@ -2483,10 +2483,10 @@
     <t xml:space="preserve">23.1505470275879</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3822441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0733165740967</t>
+    <t xml:space="preserve">23.3822460174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0733184814453</t>
   </si>
   <si>
     <t xml:space="preserve">23.7684135437012</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">24.2704257965088</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6372833251953</t>
+    <t xml:space="preserve">24.6372814178467</t>
   </si>
   <si>
     <t xml:space="preserve">25.081371307373</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">25.6413097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3130702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977886199951</t>
+    <t xml:space="preserve">25.3130683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977867126465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7804927825928</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">26.4136390686035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8343906402588</t>
+    <t xml:space="preserve">25.8343925476074</t>
   </si>
   <si>
     <t xml:space="preserve">25.7571582794189</t>
@@ -2600,25 +2600,25 @@
     <t xml:space="preserve">24.8689804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7724380493164</t>
+    <t xml:space="preserve">24.772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">30.1401214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7620182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1481781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2061004638672</t>
+    <t xml:space="preserve">31.7620143890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1481742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2061042785645</t>
   </si>
   <si>
     <t xml:space="preserve">31.8392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">31.974401473999</t>
+    <t xml:space="preserve">31.9744052886963</t>
   </si>
   <si>
     <t xml:space="preserve">31.9550933837891</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">34.1562347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245338439941</t>
+    <t xml:space="preserve">33.9245300292969</t>
   </si>
   <si>
     <t xml:space="preserve">35.1795654296875</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5810127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2761116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1216430664062</t>
+    <t xml:space="preserve">34.5810165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2761077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1216468811035</t>
   </si>
   <si>
     <t xml:space="preserve">34.8706321716309</t>
@@ -2666,16 +2666,16 @@
     <t xml:space="preserve">35.6429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0444107055664</t>
+    <t xml:space="preserve">35.0444068908691</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.465160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6003227233887</t>
+    <t xml:space="preserve">34.4651641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6003189086914</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640228271484</t>
@@ -2693,16 +2693,16 @@
     <t xml:space="preserve">33.5383682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2913932800293</t>
+    <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9977378845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7314529418945</t>
+    <t xml:space="preserve">32.9977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7314491271973</t>
   </si>
   <si>
     <t xml:space="preserve">33.3066711425781</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8971748352051</t>
+    <t xml:space="preserve">33.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8971710205078</t>
   </si>
   <si>
     <t xml:space="preserve">32.0709457397461</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">33.3452911376953</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2101287841797</t>
+    <t xml:space="preserve">33.210132598877</t>
   </si>
   <si>
     <t xml:space="preserve">33.7893753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.557674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9824562072754</t>
+    <t xml:space="preserve">33.5576782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9824600219727</t>
   </si>
   <si>
     <t xml:space="preserve">33.9631500244141</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">33.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">32.939811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4418258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8818893432617</t>
+    <t xml:space="preserve">32.9398078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4418296813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.881893157959</t>
   </si>
   <si>
     <t xml:space="preserve">32.6115760803223</t>
@@ -2774,58 +2774,58 @@
     <t xml:space="preserve">37.5351676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8360481262207</t>
+    <t xml:space="preserve">35.8360443115234</t>
   </si>
   <si>
     <t xml:space="preserve">37.4000129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4925270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1490058898926</t>
+    <t xml:space="preserve">36.4925308227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1490097045898</t>
   </si>
   <si>
     <t xml:space="preserve">36.2994422912598</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2801399230957</t>
+    <t xml:space="preserve">36.2801361083984</t>
   </si>
   <si>
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5657272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.391960144043</t>
+    <t xml:space="preserve">35.6043434143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.565731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3919563293457</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510200500488</t>
+    <t xml:space="preserve">37.6510162353516</t>
   </si>
   <si>
     <t xml:space="preserve">37.0331573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3807029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5158653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.519889831543</t>
+    <t xml:space="preserve">37.3807067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198936462402</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5625343322754</t>
+    <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
     <t xml:space="preserve">39.5818405151367</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">40.2383232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2149848937988</t>
+    <t xml:space="preserve">39.2149810791016</t>
   </si>
   <si>
     <t xml:space="preserve">40.9527206420898</t>
   </si>
   <si>
-    <t xml:space="preserve">41.145809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7057456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4587631225586</t>
+    <t xml:space="preserve">41.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7057418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4587669372559</t>
   </si>
   <si>
     <t xml:space="preserve">41.9567451477051</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5665588378906</t>
+    <t xml:space="preserve">40.6244850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5665550231934</t>
   </si>
   <si>
     <t xml:space="preserve">42.3429145812988</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">42.4780731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0878829956055</t>
+    <t xml:space="preserve">41.0878868103027</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">42.4008407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6711540222168</t>
+    <t xml:space="preserve">42.6711578369141</t>
   </si>
   <si>
     <t xml:space="preserve">42.8256187438965</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">43.8875694274902</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5786399841309</t>
+    <t xml:space="preserve">43.5786437988281</t>
   </si>
   <si>
     <t xml:space="preserve">43.9841156005859</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">43.8489532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3743019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3244323730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7669258117676</t>
+    <t xml:space="preserve">45.3743057250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3244361877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7669219970703</t>
   </si>
   <si>
     <t xml:space="preserve">49.9600028991699</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">48.5601615905762</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4636192321777</t>
+    <t xml:space="preserve">48.4636154174805</t>
   </si>
   <si>
     <t xml:space="preserve">47.2665100097656</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">46.4748725891113</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8183898925781</t>
+    <t xml:space="preserve">45.8183937072754</t>
   </si>
   <si>
     <t xml:space="preserve">46.0693969726562</t>
@@ -2957,28 +2957,28 @@
     <t xml:space="preserve">47.1120452880859</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4016609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0195350646973</t>
+    <t xml:space="preserve">47.4016647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.01953125</t>
   </si>
   <si>
     <t xml:space="preserve">48.3188056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1876754760742</t>
+    <t xml:space="preserve">49.1876792907715</t>
   </si>
   <si>
     <t xml:space="preserve">47.9229927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6912956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7878341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051261901855</t>
+    <t xml:space="preserve">47.691291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051223754883</t>
   </si>
   <si>
     <t xml:space="preserve">47.6140556335449</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">47.9422988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0734252929688</t>
+    <t xml:space="preserve">47.0734214782715</t>
   </si>
   <si>
     <t xml:space="preserve">47.9809112548828</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">54.4974365234375</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8699150085449</t>
+    <t xml:space="preserve">53.8699188232422</t>
   </si>
   <si>
     <t xml:space="preserve">52.3252639770508</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">47.7105979919434</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6567039489746</t>
+    <t xml:space="preserve">48.6567001342773</t>
   </si>
   <si>
     <t xml:space="preserve">48.0774536132812</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">48.173999786377</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9616050720215</t>
+    <t xml:space="preserve">47.9616088867188</t>
   </si>
   <si>
     <t xml:space="preserve">47.9036827087402</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.899658203125</t>
+    <t xml:space="preserve">46.8996543884277</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590278625488</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287704467773</t>
+    <t xml:space="preserve">45.5287666320801</t>
   </si>
   <si>
     <t xml:space="preserve">46.3010940551758</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">47.8071403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6446189880371</t>
+    <t xml:space="preserve">45.6446151733398</t>
   </si>
   <si>
     <t xml:space="preserve">45.8956260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1659393310547</t>
+    <t xml:space="preserve">46.165943145752</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">45.9149360656738</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3163795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4129257202148</t>
+    <t xml:space="preserve">45.3163757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4129219055176</t>
   </si>
   <si>
     <t xml:space="preserve">45.4322280883789</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">46.0887069702148</t>
   </si>
   <si>
-    <t xml:space="preserve">46.957576751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1699676513672</t>
+    <t xml:space="preserve">46.9575805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1699714660645</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388336181641</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">50.5875244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1321792602539</t>
+    <t xml:space="preserve">52.1321830749512</t>
   </si>
   <si>
     <t xml:space="preserve">51.6977424621582</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">56.1869049072266</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1659965515137</t>
+    <t xml:space="preserve">58.1659927368164</t>
   </si>
   <si>
     <t xml:space="preserve">60.1450881958008</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">60.6277923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">61.2553100585938</t>
+    <t xml:space="preserve">61.255313873291</t>
   </si>
   <si>
     <t xml:space="preserve">60.5312538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2899055480957</t>
+    <t xml:space="preserve">60.2899017333984</t>
   </si>
   <si>
     <t xml:space="preserve">59.7589302062988</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">56.621337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8490104675293</t>
+    <t xml:space="preserve">55.849006652832</t>
   </si>
   <si>
     <t xml:space="preserve">56.283447265625</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">54.9318733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4282608032227</t>
+    <t xml:space="preserve">56.4282569885254</t>
   </si>
   <si>
     <t xml:space="preserve">55.0284118652344</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">54.2078170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3872146606445</t>
+    <t xml:space="preserve">53.3872108459473</t>
   </si>
   <si>
     <t xml:space="preserve">51.9873657226562</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.773380279541</t>
+    <t xml:space="preserve">53.7733764648438</t>
   </si>
   <si>
     <t xml:space="preserve">54.9801406860352</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">56.2351760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3453979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5038909912109</t>
+    <t xml:space="preserve">57.345401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5038871765137</t>
   </si>
   <si>
     <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">60.965690612793</t>
+    <t xml:space="preserve">60.9656867980957</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
   </si>
   <si>
-    <t xml:space="preserve">61.303581237793</t>
+    <t xml:space="preserve">61.3035850524902</t>
   </si>
   <si>
     <t xml:space="preserve">60.3864402770996</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">58.4073524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">55.221492767334</t>
+    <t xml:space="preserve">55.2214965820312</t>
   </si>
   <si>
     <t xml:space="preserve">54.0629997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2287178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.083911895752</t>
+    <t xml:space="preserve">52.2287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0839080810547</t>
   </si>
   <si>
     <t xml:space="preserve">53.1458625793457</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8288726806641</t>
+    <t xml:space="preserve">50.8288764953613</t>
   </si>
   <si>
     <t xml:space="preserve">51.8908233642578</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">49.2359466552734</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4837532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8425559997559</t>
+    <t xml:space="preserve">53.483757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8425598144531</t>
   </si>
   <si>
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1185035705566</t>
+    <t xml:space="preserve">51.1184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">52.37353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1804504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3461723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4563903808594</t>
+    <t xml:space="preserve">52.1804542541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3461685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4563941955566</t>
   </si>
   <si>
     <t xml:space="preserve">50.9254150390625</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">46.3976402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763198852539</t>
+    <t xml:space="preserve">45.8763160705566</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">42.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1498336791992</t>
+    <t xml:space="preserve">42.149829864502</t>
   </si>
   <si>
     <t xml:space="preserve">45.5480804443359</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">46.8224220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2633056640625</t>
+    <t xml:space="preserve">51.2633094787598</t>
   </si>
   <si>
     <t xml:space="preserve">51.7942886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5738410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8771438598633</t>
+    <t xml:space="preserve">49.573844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8771476745605</t>
   </si>
   <si>
     <t xml:space="preserve">51.0219535827637</t>
@@ -3407,19 +3407,19 @@
     <t xml:space="preserve">47.5561294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9961967468262</t>
+    <t xml:space="preserve">46.9961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.949520111084</t>
+    <t xml:space="preserve">44.9495239257812</t>
   </si>
   <si>
     <t xml:space="preserve">43.6751823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6478157043457</t>
+    <t xml:space="preserve">41.647819519043</t>
   </si>
   <si>
     <t xml:space="preserve">42.8063087463379</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1578903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4627876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1254501342773</t>
+    <t xml:space="preserve">44.157886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4627914428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1254539489746</t>
   </si>
   <si>
     <t xml:space="preserve">42.3908386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0400199890137</t>
+    <t xml:space="preserve">42.0400161743164</t>
   </si>
   <si>
     <t xml:space="preserve">43.4043235778809</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4447708129883</t>
+    <t xml:space="preserve">46.444766998291</t>
   </si>
   <si>
     <t xml:space="preserve">45.4312858581543</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6456756591797</t>
+    <t xml:space="preserve">45.645679473877</t>
   </si>
   <si>
     <t xml:space="preserve">45.3923072814941</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3054084777832</t>
+    <t xml:space="preserve">40.3054046630859</t>
   </si>
   <si>
     <t xml:space="preserve">39.1360054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7012138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766212463379</t>
+    <t xml:space="preserve">39.7012176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766250610352</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646087646484</t>
+    <t xml:space="preserve">41.8646049499512</t>
   </si>
   <si>
     <t xml:space="preserve">42.7806434631348</t>
@@ -3527,22 +3527,22 @@
     <t xml:space="preserve">41.8840980529785</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9620628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8586006164551</t>
+    <t xml:space="preserve">41.9620590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8585968017578</t>
   </si>
   <si>
     <t xml:space="preserve">45.0025062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3593330383301</t>
+    <t xml:space="preserve">44.3593368530273</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507751464844</t>
+    <t xml:space="preserve">45.4507789611816</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">50.9177284240723</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5511627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.548885345459</t>
+    <t xml:space="preserve">51.5511589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5488891601562</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517189025879</t>
+    <t xml:space="preserve">55.3517150878906</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3602,16 +3602,16 @@
     <t xml:space="preserve">54.1335906982422</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1080894470215</t>
+    <t xml:space="preserve">55.1080932617188</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4491653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4004402160645</t>
+    <t xml:space="preserve">55.4491691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4004364013672</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">50.4792060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7970504760742</t>
+    <t xml:space="preserve">49.7970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">51.0151786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5024337768555</t>
+    <t xml:space="preserve">51.5024299621582</t>
   </si>
   <si>
     <t xml:space="preserve">52.0384063720703</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8015975952148</t>
+    <t xml:space="preserve">45.8015937805176</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">47.7311096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9919548034668</t>
+    <t xml:space="preserve">49.9919509887695</t>
   </si>
   <si>
     <t xml:space="preserve">49.8945045471191</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494453430176</t>
+    <t xml:space="preserve">57.3494491577148</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698394775391</t>
+    <t xml:space="preserve">56.5698432922363</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">61.0038261413574</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8111953735352</t>
+    <t xml:space="preserve">58.8111991882324</t>
   </si>
   <si>
     <t xml:space="preserve">59.6395263671875</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">58.8599243164062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2497215270996</t>
+    <t xml:space="preserve">59.2497253417969</t>
   </si>
   <si>
     <t xml:space="preserve">57.9828720092773</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">64.2684020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3194046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0502815246582</t>
+    <t xml:space="preserve">62.319408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0502853393555</t>
   </si>
   <si>
     <t xml:space="preserve">61.3936309814453</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">68.1176986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8230819702148</t>
+    <t xml:space="preserve">69.8230743408203</t>
   </si>
   <si>
     <t xml:space="preserve">70.3590469360352</t>
@@ -3812,43 +3812,43 @@
     <t xml:space="preserve">68.9460220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">68.410041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8740692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3125915527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.1919097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8972854614258</t>
+    <t xml:space="preserve">68.4100341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8740768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3125839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.1919174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8972930908203</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4865417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5817184448242</t>
+    <t xml:space="preserve">65.4865341186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5817108154297</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">69.6768951416016</t>
+    <t xml:space="preserve">69.6769027709961</t>
   </si>
   <si>
     <t xml:space="preserve">69.1409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">66.509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1199645996094</t>
+    <t xml:space="preserve">66.5097579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1199569702148</t>
   </si>
   <si>
     <t xml:space="preserve">66.8995666503906</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">66.5584869384766</t>
   </si>
   <si>
-    <t xml:space="preserve">68.6536636352539</t>
+    <t xml:space="preserve">68.6536712646484</t>
   </si>
   <si>
     <t xml:space="preserve">69.0434722900391</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">71.7233505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4310073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.528450012207</t>
+    <t xml:space="preserve">71.4309997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5284576416016</t>
   </si>
   <si>
     <t xml:space="preserve">72.6978530883789</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.3057861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4032287597656</t>
+    <t xml:space="preserve">74.305778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4032363891602</t>
   </si>
   <si>
     <t xml:space="preserve">75.7188034057617</t>
@@ -3905,19 +3905,19 @@
     <t xml:space="preserve">77.2780151367188</t>
   </si>
   <si>
-    <t xml:space="preserve">77.3754577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9879302978516</t>
+    <t xml:space="preserve">77.3754653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.987922668457</t>
   </si>
   <si>
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3244705200195</t>
+    <t xml:space="preserve">77.8627166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3244781494141</t>
   </si>
   <si>
     <t xml:space="preserve">78.8859405517578</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.4241790771484</t>
+    <t xml:space="preserve">78.0088882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.424186706543</t>
   </si>
   <si>
     <t xml:space="preserve">77.0831146240234</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">78.3012390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0321197509766</t>
+    <t xml:space="preserve">79.032112121582</t>
   </si>
   <si>
     <t xml:space="preserve">78.4474182128906</t>
@@ -3962,16 +3962,16 @@
     <t xml:space="preserve">77.8139877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">77.4729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.964714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8207931518555</t>
+    <t xml:space="preserve">77.4729156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9647064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.82080078125</t>
   </si>
   <si>
     <t xml:space="preserve">77.9601593017578</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">77.7165374755859</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7119979858398</t>
+    <t xml:space="preserve">80.3964233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2989730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7119903564453</t>
   </si>
   <si>
     <t xml:space="preserve">81.468376159668</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">81.7607192993164</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2689361572266</t>
+    <t xml:space="preserve">85.268928527832</t>
   </si>
   <si>
     <t xml:space="preserve">88.1924438476562</t>
@@ -4010,22 +4010,22 @@
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488067626953</t>
+    <t xml:space="preserve">87.9488143920898</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6796875</t>
+    <t xml:space="preserve">88.6796798706055</t>
   </si>
   <si>
     <t xml:space="preserve">87.9000854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">86.3408737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434234619141</t>
+    <t xml:space="preserve">86.3408813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434310913086</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">86.0972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">88.9720458984375</t>
+    <t xml:space="preserve">88.972038269043</t>
   </si>
   <si>
     <t xml:space="preserve">88.4360580444336</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1017913818359</t>
+    <t xml:space="preserve">82.1017990112305</t>
   </si>
   <si>
     <t xml:space="preserve">83.1250305175781</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559112548828</t>
+    <t xml:space="preserve">83.8559036254883</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091720581055</t>
+    <t xml:space="preserve">79.9091644287109</t>
   </si>
   <si>
     <t xml:space="preserve">81.5299377441406</t>
@@ -5646,6 +5646,9 @@
   </si>
   <si>
     <t xml:space="preserve">90.3600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
   </si>
 </sst>
 </file>
@@ -70854,7 +70857,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6495717593</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>415439</v>
@@ -70875,6 +70878,32 @@
         <v>1877</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494791667</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>296212</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>91.2200012207031</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>89.7200012207031</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>90.6999969482422</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>90</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="1879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1880">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">14.8537855148315</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4801063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1718196868896</t>
+    <t xml:space="preserve">14.4801044464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1718187332153</t>
   </si>
   <si>
     <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289274215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406274795532</t>
+    <t xml:space="preserve">13.9289283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406255722046</t>
   </si>
   <si>
     <t xml:space="preserve">15.3208856582642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3022012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.087742805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0410318374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3212928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.33997631073</t>
+    <t xml:space="preserve">15.3022003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0877408981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0410327911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3212909698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3399772644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.7697076797485</t>
@@ -95,61 +95,61 @@
     <t xml:space="preserve">13.9943208694458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240550994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.003662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051248550415</t>
+    <t xml:space="preserve">14.424054145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051258087158</t>
   </si>
   <si>
     <t xml:space="preserve">12.4155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172292709351</t>
+    <t xml:space="preserve">12.4061784744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172302246094</t>
   </si>
   <si>
     <t xml:space="preserve">13.5459051132202</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1722269058228</t>
+    <t xml:space="preserve">13.1722259521484</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057760238647</t>
+    <t xml:space="preserve">13.4057750701904</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777494430542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251096725464</t>
+    <t xml:space="preserve">14.1251106262207</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195852279663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0316905975342</t>
+    <t xml:space="preserve">14.0316896438599</t>
   </si>
   <si>
     <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8355083465576</t>
+    <t xml:space="preserve">13.8355073928833</t>
   </si>
   <si>
     <t xml:space="preserve">14.1064262390137</t>
@@ -158,115 +158,115 @@
     <t xml:space="preserve">14.2372140884399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4520797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.255898475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4143085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011457443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2461500167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060190200806</t>
+    <t xml:space="preserve">14.4520807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.414306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060180664062</t>
   </si>
   <si>
     <t xml:space="preserve">15.3769378662109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4797010421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
+    <t xml:space="preserve">15.4796991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385116577148</t>
   </si>
   <si>
     <t xml:space="preserve">15.5450944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104869842529</t>
+    <t xml:space="preserve">15.6945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104879379272</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983835220337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873365402222</t>
+    <t xml:space="preserve">15.0873355865479</t>
   </si>
   <si>
     <t xml:space="preserve">14.993914604187</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6202363967896</t>
+    <t xml:space="preserve">14.6202383041382</t>
   </si>
   <si>
     <t xml:space="preserve">15.1527290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3302268981934</t>
+    <t xml:space="preserve">15.330228805542</t>
   </si>
   <si>
     <t xml:space="preserve">15.5918064117432</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7225933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253564834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017978668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858737945557</t>
+    <t xml:space="preserve">15.7225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858776092529</t>
   </si>
   <si>
     <t xml:space="preserve">16.3485050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550868988037</t>
+    <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
     <t xml:space="preserve">16.4139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924537658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671894073486</t>
+    <t xml:space="preserve">16.2924575805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2177200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3765335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3391609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325885772705</t>
+    <t xml:space="preserve">16.2177181243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3765354156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3391628265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325847625732</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100826263428</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">16.6474494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6287670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4419288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889831542969</t>
+    <t xml:space="preserve">16.6287651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4419250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889850616455</t>
   </si>
   <si>
     <t xml:space="preserve">16.6489810943604</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207447052002</t>
+    <t xml:space="preserve">16.6207485198975</t>
   </si>
   <si>
     <t xml:space="preserve">16.601921081543</t>
@@ -299,40 +299,40 @@
     <t xml:space="preserve">16.6866283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.705451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454540252686</t>
+    <t xml:space="preserve">16.7054500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454521179199</t>
   </si>
   <si>
     <t xml:space="preserve">16.6583938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8277969360352</t>
+    <t xml:space="preserve">16.8278007507324</t>
   </si>
   <si>
     <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890029907227</t>
+    <t xml:space="preserve">16.2254619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890068054199</t>
   </si>
   <si>
     <t xml:space="preserve">15.4725399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7078285217285</t>
+    <t xml:space="preserve">15.7078304290771</t>
   </si>
   <si>
     <t xml:space="preserve">15.3407793045044</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5831031799316</t>
+    <t xml:space="preserve">16.5830974578857</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113338470459</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">16.4325160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2536964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642795562744</t>
+    <t xml:space="preserve">16.2536945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642757415771</t>
   </si>
   <si>
     <t xml:space="preserve">15.5290107727051</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">14.8796138763428</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0678434371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090177536011</t>
+    <t xml:space="preserve">15.0678443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090187072754</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101861953735</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">14.7854995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.314923286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.644326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9172620773315</t>
+    <t xml:space="preserve">14.3149223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9172611236572</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384206771851</t>
@@ -383,52 +383,52 @@
     <t xml:space="preserve">15.6513586044312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5195980072021</t>
+    <t xml:space="preserve">15.5195989608765</t>
   </si>
   <si>
     <t xml:space="preserve">15.4348936080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854787826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054679870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301773071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478324890137</t>
+    <t xml:space="preserve">15.5854768753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301801681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.547833442688</t>
   </si>
   <si>
     <t xml:space="preserve">15.933705329895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.670184135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3784265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419477462769</t>
+    <t xml:space="preserve">15.6701812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3784246444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148817062378</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0278186798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2725200653076</t>
+    <t xml:space="preserve">16.0278224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2725219726562</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195781707764</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">16.2819309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1595821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3760452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078067779541</t>
+    <t xml:space="preserve">16.1595840454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3760433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078105926514</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301574707031</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7807426452637</t>
+    <t xml:space="preserve">16.780740737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.8560333251953</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">17.0160293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9407386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9313278198242</t>
+    <t xml:space="preserve">16.9407367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
     <t xml:space="preserve">16.978385925293</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">16.846622467041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8936805725098</t>
+    <t xml:space="preserve">16.8936824798584</t>
   </si>
   <si>
     <t xml:space="preserve">16.6960391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713279724121</t>
+    <t xml:space="preserve">16.9125022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713298797607</t>
   </si>
   <si>
     <t xml:space="preserve">16.8089771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4231052398682</t>
+    <t xml:space="preserve">16.4231033325195</t>
   </si>
   <si>
     <t xml:space="preserve">16.8842678070068</t>
@@ -509,61 +509,61 @@
     <t xml:space="preserve">16.7525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9030933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0066204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9972057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0536785125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8748550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0348529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0724983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2324924468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289710998535</t>
+    <t xml:space="preserve">16.9030914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0066165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9972095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.053674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.034854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654460906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0725002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.232494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289672851562</t>
   </si>
   <si>
     <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136707305908</t>
+    <t xml:space="preserve">17.2136726379395</t>
   </si>
   <si>
     <t xml:space="preserve">17.3548450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3077850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936588287354</t>
+    <t xml:space="preserve">17.3642559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077869415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.298376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936569213867</t>
   </si>
   <si>
     <t xml:space="preserve">17.8724784851074</t>
@@ -575,79 +575,79 @@
     <t xml:space="preserve">18.8230419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6818695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.804220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3406753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3783226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359798431396</t>
+    <t xml:space="preserve">18.6818675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.378324508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.935977935791</t>
   </si>
   <si>
     <t xml:space="preserve">19.2183246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5571422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4159641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724151611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.423002243042</t>
+    <t xml:space="preserve">19.5571403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4159660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4230041503906</t>
   </si>
   <si>
     <t xml:space="preserve">20.2347679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2535934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4982929229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.357120513916</t>
+    <t xml:space="preserve">20.2535953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4982948303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3571224212646</t>
   </si>
   <si>
     <t xml:space="preserve">20.893575668335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030101776123</t>
+    <t xml:space="preserve">20.6676998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.103006362915</t>
   </si>
   <si>
     <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7453708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.519495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6889019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171382904053</t>
+    <t xml:space="preserve">19.7453689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5194931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6889038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171401977539</t>
   </si>
   <si>
     <t xml:space="preserve">19.8488960266113</t>
@@ -659,28 +659,28 @@
     <t xml:space="preserve">19.4630260467529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2747955322266</t>
+    <t xml:space="preserve">19.2747936248779</t>
   </si>
   <si>
     <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3877353668213</t>
+    <t xml:space="preserve">19.387731552124</t>
   </si>
   <si>
     <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3971462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053848266602</t>
+    <t xml:space="preserve">19.397144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0018615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053867340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.9171600341797</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">18.8700981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936389923096</t>
+    <t xml:space="preserve">18.4936370849609</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524646759033</t>
@@ -701,46 +701,46 @@
     <t xml:space="preserve">18.2865829467773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100841522217</t>
+    <t xml:space="preserve">18.6254005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5100860595703</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5006694793701</t>
+    <t xml:space="preserve">19.5006713867188</t>
   </si>
   <si>
     <t xml:space="preserve">19.7547836303711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7924289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994632720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641529083252</t>
+    <t xml:space="preserve">19.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.594783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018199920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641510009766</t>
   </si>
   <si>
     <t xml:space="preserve">21.2982711791992</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">21.1853332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">21.015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029865264893</t>
+    <t xml:space="preserve">21.0159244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029846191406</t>
   </si>
   <si>
     <t xml:space="preserve">21.0253372192383</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9876899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794532775879</t>
+    <t xml:space="preserve">20.9876918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
     <t xml:space="preserve">21.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112091064453</t>
+    <t xml:space="preserve">21.4112110137939</t>
   </si>
   <si>
     <t xml:space="preserve">21.6088523864746</t>
@@ -779,28 +779,28 @@
     <t xml:space="preserve">21.2135677337646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3829746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429725646973</t>
+    <t xml:space="preserve">21.3829765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429706573486</t>
   </si>
   <si>
     <t xml:space="preserve">21.8347320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0229568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8064918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.041784286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817684173584</t>
+    <t xml:space="preserve">22.0229587554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8064937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0417823791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817665100098</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476482391357</t>
@@ -809,40 +809,40 @@
     <t xml:space="preserve">22.6252975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0394058227539</t>
+    <t xml:space="preserve">23.0394039154053</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0582256317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3711853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
+    <t xml:space="preserve">23.0582275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135478973389</t>
   </si>
   <si>
     <t xml:space="preserve">21.6464977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9194316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.787670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3076801300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.117073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0981216430664</t>
+    <t xml:space="preserve">21.91943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7876720428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3076858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1170749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.098123550415</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455020904541</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">22.2686901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0507431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7190818786621</t>
+    <t xml:space="preserve">22.0507411956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7190799713135</t>
   </si>
   <si>
     <t xml:space="preserve">22.0886459350586</t>
@@ -872,19 +872,19 @@
     <t xml:space="preserve">21.6811752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5769386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7285556793213</t>
+    <t xml:space="preserve">21.576940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7285575866699</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380332946777</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200824737549</t>
+    <t xml:space="preserve">21.5579891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200843811035</t>
   </si>
   <si>
     <t xml:space="preserve">21.1315650939941</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4632263183594</t>
+    <t xml:space="preserve">21.4632301330566</t>
   </si>
   <si>
     <t xml:space="preserve">21.6622257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5674648284912</t>
+    <t xml:space="preserve">21.5674667358398</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624504089355</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">22.4013557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5529727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5813999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6761608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5908756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7948894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422698974609</t>
+    <t xml:space="preserve">22.5529708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6761627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.590877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7948875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">21.6717014312744</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">21.5958938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4676876068115</t>
+    <t xml:space="preserve">22.4676856994629</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277797698975</t>
+    <t xml:space="preserve">22.5055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951160430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.0362491607666</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2162933349609</t>
+    <t xml:space="preserve">23.2162952423096</t>
   </si>
   <si>
     <t xml:space="preserve">22.9983444213867</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">23.5005760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6900959014893</t>
+    <t xml:space="preserve">23.6900978088379</t>
   </si>
   <si>
     <t xml:space="preserve">23.2731513977051</t>
@@ -983,46 +983,46 @@
     <t xml:space="preserve">23.4058170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4531955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.770923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9509658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.06467628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7519702911377</t>
+    <t xml:space="preserve">23.4531936645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7709197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.950963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7519683837891</t>
   </si>
   <si>
     <t xml:space="preserve">22.723539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9793949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6477298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.477165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.87961769104</t>
+    <t xml:space="preserve">22.9793930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6477317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4771633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1834049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8796157836914</t>
   </si>
   <si>
     <t xml:space="preserve">24.1165199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6616706848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868637084961</t>
+    <t xml:space="preserve">23.6616668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868656158447</t>
   </si>
   <si>
     <t xml:space="preserve">23.1783924102783</t>
@@ -1031,34 +1031,34 @@
     <t xml:space="preserve">22.9035873413086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0217609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6376991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6850814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040328979492</t>
+    <t xml:space="preserve">24.0217590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6377029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903186798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040309906006</t>
   </si>
   <si>
     <t xml:space="preserve">24.8082695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7798404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7229881286621</t>
+    <t xml:space="preserve">24.779842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">24.5429382324219</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651256561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5474014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4431629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4905452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3863067626953</t>
+    <t xml:space="preserve">24.8651275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4431648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4905433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">25.3484039306641</t>
@@ -1100,49 +1100,49 @@
     <t xml:space="preserve">25.3294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0830783843994</t>
+    <t xml:space="preserve">25.0830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">25.7274436950684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.661111831665</t>
+    <t xml:space="preserve">25.6611137390137</t>
   </si>
   <si>
     <t xml:space="preserve">25.9643459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3054828643799</t>
+    <t xml:space="preserve">26.3054809570312</t>
   </si>
   <si>
     <t xml:space="preserve">26.8645687103271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.309944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0635681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.675048828125</t>
+    <t xml:space="preserve">27.3099422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0635662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6750507354736</t>
   </si>
   <si>
     <t xml:space="preserve">26.9972343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1678028106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4665775299072</t>
+    <t xml:space="preserve">27.1678047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4665756225586</t>
   </si>
   <si>
     <t xml:space="preserve">26.0591068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0451717376709</t>
+    <t xml:space="preserve">25.0451698303223</t>
   </si>
   <si>
     <t xml:space="preserve">25.1778354644775</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1115016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5379257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9359188079834</t>
+    <t xml:space="preserve">25.1115036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5379276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.935920715332</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010234832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683578491211</t>
+    <t xml:space="preserve">25.301025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683559417725</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219799041748</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">25.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1020259857178</t>
+    <t xml:space="preserve">25.1020278930664</t>
   </si>
   <si>
     <t xml:space="preserve">25.5853023529053</t>
@@ -1193,31 +1193,31 @@
     <t xml:space="preserve">25.8601112365723</t>
   </si>
   <si>
-    <t xml:space="preserve">26.333911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4381465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7987957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3673553466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3578815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6232089996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748279571533</t>
+    <t xml:space="preserve">26.3339138031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2486305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4381484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7987937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3673572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3578796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6232109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748260498047</t>
   </si>
   <si>
     <t xml:space="preserve">25.5947799682617</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">25.7084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1064853668213</t>
+    <t xml:space="preserve">26.1064872741699</t>
   </si>
   <si>
     <t xml:space="preserve">26.8171901702881</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">25.8695850372314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8222064971924</t>
+    <t xml:space="preserve">25.8222045898438</t>
   </si>
   <si>
     <t xml:space="preserve">25.9169673919678</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">25.6326847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7324638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9743766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4007987976074</t>
+    <t xml:space="preserve">24.7324619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
     <t xml:space="preserve">24.0691375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4481792449951</t>
+    <t xml:space="preserve">24.4481773376465</t>
   </si>
   <si>
     <t xml:space="preserve">24.8272228240967</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">25.0167407989502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9693622589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9269962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433895111084</t>
+    <t xml:space="preserve">24.9693641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9269981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433856964111</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012481689453</t>
@@ -1295,25 +1295,25 @@
     <t xml:space="preserve">26.0117263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1538639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4855308532715</t>
+    <t xml:space="preserve">26.153865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4855270385742</t>
   </si>
   <si>
     <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9593334197998</t>
+    <t xml:space="preserve">26.9593315124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9492988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.617639541626</t>
+    <t xml:space="preserve">28.9493007659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
     <t xml:space="preserve">28.8071575164795</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">29.3283424377441</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5394916534424</t>
+    <t xml:space="preserve">29.2335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5394897460938</t>
   </si>
   <si>
     <t xml:space="preserve">30.2086696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0652770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9696769714355</t>
+    <t xml:space="preserve">30.0652732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042678833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9696788787842</t>
   </si>
   <si>
     <t xml:space="preserve">30.1130714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501693725586</t>
+    <t xml:space="preserve">31.2602386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501617431641</t>
   </si>
   <si>
     <t xml:space="preserve">34.0803527832031</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9369583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759452819824</t>
+    <t xml:space="preserve">34.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.936954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759414672852</t>
   </si>
   <si>
     <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7532997131348</t>
+    <t xml:space="preserve">35.753303527832</t>
   </si>
   <si>
     <t xml:space="preserve">35.9922981262207</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">35.2275161743164</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0841255187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6576957702637</t>
+    <t xml:space="preserve">35.0841178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6577033996582</t>
   </si>
   <si>
     <t xml:space="preserve">35.275318145752</t>
@@ -1403,25 +1403,25 @@
     <t xml:space="preserve">36.3268814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4187088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5658721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8526611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5948257446289</t>
+    <t xml:space="preserve">35.4187126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5658760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.852668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5948276519775</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558330535889</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">33.7935600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9847526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7973327636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671455383301</t>
+    <t xml:space="preserve">33.9847564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7973251342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671417236328</t>
   </si>
   <si>
     <t xml:space="preserve">34.6539344787598</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">35.036319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6061363220215</t>
+    <t xml:space="preserve">34.6061325073242</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627342224121</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.040096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966941833496</t>
+    <t xml:space="preserve">36.0400924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966979980469</t>
   </si>
   <si>
     <t xml:space="preserve">36.6614723205566</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">39.0036010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3306465148926</t>
+    <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180740356445</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8564338684082</t>
+    <t xml:space="preserve">37.8564376831055</t>
   </si>
   <si>
     <t xml:space="preserve">36.2790870666504</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">37.2350578308105</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8929290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5583381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6979675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.506763458252</t>
+    <t xml:space="preserve">34.8929214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5583343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5067672729492</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677726745605</t>
@@ -1514,73 +1514,73 @@
     <t xml:space="preserve">32.2640075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9809875488281</t>
+    <t xml:space="preserve">32.9809837341309</t>
   </si>
   <si>
     <t xml:space="preserve">33.3633728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7897911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.837589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5985946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.503002166748</t>
+    <t xml:space="preserve">32.7897872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8375854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5985908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5029945373535</t>
   </si>
   <si>
     <t xml:space="preserve">33.2199783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6463966369629</t>
+    <t xml:space="preserve">32.6463928222656</t>
   </si>
   <si>
     <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.072811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7860202789307</t>
+    <t xml:space="preserve">32.0728149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7860240936279</t>
   </si>
   <si>
     <t xml:space="preserve">31.8338222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0690441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0212440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703136444092</t>
+    <t xml:space="preserve">31.0690422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0212421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703117370605</t>
   </si>
   <si>
     <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2011337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7709465026855</t>
+    <t xml:space="preserve">28.2011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797500610352</t>
+    <t xml:space="preserve">28.2489280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797519683838</t>
   </si>
   <si>
     <t xml:space="preserve">28.1055335998535</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">28.3445281982422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0137062072754</t>
+    <t xml:space="preserve">29.013708114624</t>
   </si>
   <si>
     <t xml:space="preserve">28.9181098937988</t>
@@ -1604,31 +1604,31 @@
     <t xml:space="preserve">29.2049007415771</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4954624176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5872917175293</t>
+    <t xml:space="preserve">30.4954605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5872898101807</t>
   </si>
   <si>
     <t xml:space="preserve">30.7344570159912</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0174770355225</t>
+    <t xml:space="preserve">30.0174732208252</t>
   </si>
   <si>
     <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6828861236572</t>
+    <t xml:space="preserve">29.6828842163086</t>
   </si>
   <si>
     <t xml:space="preserve">28.5835189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5759830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3847846984863</t>
+    <t xml:space="preserve">26.5759811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.384786605835</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929592132568</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.862771987915</t>
+    <t xml:space="preserve">27.1017665863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8627738952637</t>
   </si>
   <si>
     <t xml:space="preserve">27.4841537475586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0061664581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0979957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200103759766</t>
+    <t xml:space="preserve">27.0061683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0979976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200122833252</t>
   </si>
   <si>
     <t xml:space="preserve">26.1935939788818</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2891902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671756744385</t>
+    <t xml:space="preserve">26.289192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671775817871</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">28.9659080505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6791152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1093063354492</t>
+    <t xml:space="preserve">28.6791172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.109302520752</t>
   </si>
   <si>
     <t xml:space="preserve">26.6715774536133</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">28.8225135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8740787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1608715057373</t>
+    <t xml:space="preserve">29.874080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1608695983887</t>
   </si>
   <si>
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080348968506</t>
+    <t xml:space="preserve">31.308032989502</t>
   </si>
   <si>
     <t xml:space="preserve">31.4514331817627</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">32.2162094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">33.602367401123</t>
+    <t xml:space="preserve">33.6023635864258</t>
   </si>
   <si>
     <t xml:space="preserve">33.1721801757812</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">33.5545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2564659118652</t>
+    <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
     <t xml:space="preserve">30.6388568878174</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">29.3004970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9409999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.648416519165</t>
+    <t xml:space="preserve">29.9409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6484184265137</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
@@ -1769,34 +1769,34 @@
     <t xml:space="preserve">30.2851505279541</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0748310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.47633934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2277889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9983558654785</t>
+    <t xml:space="preserve">30.0748329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4763431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2277908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9983577728271</t>
   </si>
   <si>
     <t xml:space="preserve">29.8262825012207</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6675395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.438102722168</t>
+    <t xml:space="preserve">30.667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">30.7631340026855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9352073669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7498035430908</t>
+    <t xml:space="preserve">30.935209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7498054504395</t>
   </si>
   <si>
     <t xml:space="preserve">29.7115669250488</t>
@@ -1814,19 +1814,19 @@
     <t xml:space="preserve">28.7173557281494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821300506592</t>
+    <t xml:space="preserve">29.4821319580078</t>
   </si>
   <si>
     <t xml:space="preserve">29.1762218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9237060546875</t>
+    <t xml:space="preserve">29.3291797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9237041473389</t>
   </si>
   <si>
     <t xml:space="preserve">28.6533908843994</t>
@@ -1838,19 +1838,19 @@
     <t xml:space="preserve">28.3637657165527</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5182342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8038291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0741424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2245845794678</t>
+    <t xml:space="preserve">28.5182323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8038311004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0741443634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1859645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2245826721191</t>
   </si>
   <si>
     <t xml:space="preserve">27.2052745819092</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">27.6493625640869</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776020050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5142040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8617534637451</t>
+    <t xml:space="preserve">27.9776039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5142059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8617553710938</t>
   </si>
   <si>
     <t xml:space="preserve">27.7845211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548343658447</t>
+    <t xml:space="preserve">28.0548362731934</t>
   </si>
   <si>
     <t xml:space="preserve">27.9969100952148</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">28.4989261627197</t>
   </si>
   <si>
-    <t xml:space="preserve">28.247917175293</t>
+    <t xml:space="preserve">28.2479190826416</t>
   </si>
   <si>
     <t xml:space="preserve">28.3251514434814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8424453735352</t>
+    <t xml:space="preserve">27.8424472808838</t>
   </si>
   <si>
     <t xml:space="preserve">27.900369644165</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">28.0934524536133</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6340808868408</t>
+    <t xml:space="preserve">28.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">29.1167888641357</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">28.8850898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2712535858154</t>
+    <t xml:space="preserve">29.2712554931641</t>
   </si>
   <si>
     <t xml:space="preserve">29.8311920166016</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9084224700928</t>
+    <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
     <t xml:space="preserve">29.8505001068115</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">30.2173538208008</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9856567382812</t>
+    <t xml:space="preserve">29.9856548309326</t>
   </si>
   <si>
     <t xml:space="preserve">30.6807537078857</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">29.3677940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4836463928223</t>
+    <t xml:space="preserve">29.4836444854736</t>
   </si>
   <si>
     <t xml:space="preserve">29.174711227417</t>
@@ -1946,34 +1946,34 @@
     <t xml:space="preserve">29.4257183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2519474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4643363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0202445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9043998718262</t>
+    <t xml:space="preserve">29.2519454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.464334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9043979644775</t>
   </si>
   <si>
     <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4796161651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7652130126953</t>
+    <t xml:space="preserve">28.4796180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7652111053467</t>
   </si>
   <si>
     <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542694091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1473522186279</t>
+    <t xml:space="preserve">26.9542675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1473503112793</t>
   </si>
   <si>
     <t xml:space="preserve">27.282506942749</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6839542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101795196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8810615539551</t>
+    <t xml:space="preserve">26.683952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8810596466064</t>
   </si>
   <si>
     <t xml:space="preserve">28.1899948120117</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">28.3444595336914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9389877319336</t>
+    <t xml:space="preserve">27.938985824585</t>
   </si>
   <si>
     <t xml:space="preserve">27.4369735717773</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">27.2631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0314998626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6260280609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4176635742188</t>
+    <t xml:space="preserve">27.0315017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6260299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4176654815674</t>
   </si>
   <si>
     <t xml:space="preserve">28.0355281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0894260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9928855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755878448486</t>
+    <t xml:space="preserve">27.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9928798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0508079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755897521973</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">27.591438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">27.610746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6879787445068</t>
+    <t xml:space="preserve">27.6107482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6879806518555</t>
   </si>
   <si>
     <t xml:space="preserve">26.3557109832764</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3018169403076</t>
+    <t xml:space="preserve">27.301815032959</t>
   </si>
   <si>
     <t xml:space="preserve">27.4562816619873</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">26.7032604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7459049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1087322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1320686340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3830738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9430141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4064102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8078575134277</t>
+    <t xml:space="preserve">27.745906829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1087341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1320667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3830757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9430122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4064083099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8078556060791</t>
   </si>
   <si>
     <t xml:space="preserve">28.9816303253174</t>
@@ -2099,37 +2099,37 @@
     <t xml:space="preserve">29.1360969543457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7499313354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8271656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.000940322876</t>
+    <t xml:space="preserve">28.7499332427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8271636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0009384155273</t>
   </si>
   <si>
     <t xml:space="preserve">28.5954666137695</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6147708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133293151855</t>
+    <t xml:space="preserve">28.6147747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133274078369</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9357872009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026466369629</t>
+    <t xml:space="preserve">31.9357891082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026390075684</t>
   </si>
   <si>
     <t xml:space="preserve">32.4571075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8585548400879</t>
+    <t xml:space="preserve">31.8585510253906</t>
   </si>
   <si>
     <t xml:space="preserve">31.2213821411133</t>
@@ -2141,28 +2141,28 @@
     <t xml:space="preserve">31.6654720306396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2600002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5882434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.047607421875</t>
+    <t xml:space="preserve">32.1674880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2600021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5882415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0476093292236</t>
   </si>
   <si>
     <t xml:space="preserve">30.9510688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1248455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3565406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8545246124268</t>
+    <t xml:space="preserve">31.1248435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.854528427124</t>
   </si>
   <si>
     <t xml:space="preserve">30.8931427001953</t>
@@ -2171,40 +2171,40 @@
     <t xml:space="preserve">30.8159103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3372344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4683609008789</t>
+    <t xml:space="preserve">31.337230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4683628082275</t>
   </si>
   <si>
     <t xml:space="preserve">31.0089912414551</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7000579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0170478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3645973205566</t>
+    <t xml:space="preserve">30.7000617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0170440673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3645935058594</t>
   </si>
   <si>
     <t xml:space="preserve">33.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8859176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8899459838867</t>
+    <t xml:space="preserve">33.885913848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8899421691895</t>
   </si>
   <si>
     <t xml:space="preserve">35.0251007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9712028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5311431884766</t>
+    <t xml:space="preserve">35.9712066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5311393737793</t>
   </si>
   <si>
     <t xml:space="preserve">36.9559211730957</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">37.2069320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8167343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9864845275879</t>
+    <t xml:space="preserve">35.7008934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9864883422852</t>
   </si>
   <si>
     <t xml:space="preserve">33.2873611450195</t>
@@ -2228,19 +2228,19 @@
     <t xml:space="preserve">33.0363578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9205093383789</t>
+    <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
     <t xml:space="preserve">31.9937114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6847801208496</t>
+    <t xml:space="preserve">31.684778213501</t>
   </si>
   <si>
     <t xml:space="preserve">31.8778629302979</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3605690002441</t>
+    <t xml:space="preserve">32.3605651855469</t>
   </si>
   <si>
     <t xml:space="preserve">33.3839073181152</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">32.8432731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7427062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8239669799805</t>
+    <t xml:space="preserve">31.7427024841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8239631652832</t>
   </si>
   <si>
     <t xml:space="preserve">32.901195526123</t>
@@ -2270,34 +2270,34 @@
     <t xml:space="preserve">33.6928367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7081146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3871040344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8118839263916</t>
+    <t xml:space="preserve">32.7081184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3871059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9623222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8698101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.773265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0049667358398</t>
+    <t xml:space="preserve">29.8698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7732677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0049648284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.027473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784786224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2937622070312</t>
+    <t xml:space="preserve">26.2784805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2937602996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.1240139007568</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">24.5407409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1931934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9767742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2744541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378482818604</t>
+    <t xml:space="preserve">24.1931915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9767761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2744522094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.737850189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150825500488</t>
@@ -2339,22 +2339,22 @@
     <t xml:space="preserve">24.019416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9614944458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4442005157471</t>
+    <t xml:space="preserve">23.9614925384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4441986083984</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0427551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6220016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3943290710449</t>
+    <t xml:space="preserve">25.0427570343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6220035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3943309783936</t>
   </si>
   <si>
     <t xml:space="preserve">27.6300563812256</t>
@@ -2366,31 +2366,31 @@
     <t xml:space="preserve">26.6646461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6453380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2398643493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.718542098999</t>
+    <t xml:space="preserve">26.645336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2398624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7185401916504</t>
   </si>
   <si>
     <t xml:space="preserve">25.4482288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5833835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5487957000732</t>
+    <t xml:space="preserve">25.5833854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5487937927246</t>
   </si>
   <si>
     <t xml:space="preserve">26.9349575042725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4522514343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8923149108887</t>
+    <t xml:space="preserve">26.4522533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8923168182373</t>
   </si>
   <si>
     <t xml:space="preserve">26.066089630127</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3750190734863</t>
+    <t xml:space="preserve">26.375020980835</t>
   </si>
   <si>
     <t xml:space="preserve">28.0162200927734</t>
@@ -2426,25 +2426,25 @@
     <t xml:space="preserve">25.5061511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903007507324</t>
+    <t xml:space="preserve">25.3903026580811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5254592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4055843353271</t>
+    <t xml:space="preserve">24.4055862426758</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565914154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2511196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2897357940674</t>
+    <t xml:space="preserve">24.6565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2511177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2897338867188</t>
   </si>
   <si>
     <t xml:space="preserve">24.5793571472168</t>
@@ -2453,43 +2453,43 @@
     <t xml:space="preserve">24.8496723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3283519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8303642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3862762451172</t>
+    <t xml:space="preserve">24.3283500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8303623199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3862743377686</t>
   </si>
   <si>
     <t xml:space="preserve">23.8842601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9421863555908</t>
+    <t xml:space="preserve">23.9421844482422</t>
   </si>
   <si>
     <t xml:space="preserve">24.1352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1545753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0387268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035682678223</t>
+    <t xml:space="preserve">24.154577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0387287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035701751709</t>
   </si>
   <si>
     <t xml:space="preserve">23.1505489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3822479248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0733165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7684135437012</t>
+    <t xml:space="preserve">23.3822460174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.073314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7684116363525</t>
   </si>
   <si>
     <t xml:space="preserve">23.5946388244629</t>
@@ -2501,64 +2501,64 @@
     <t xml:space="preserve">24.2704257965088</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6372814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.081371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3476600646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5447673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1047058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0853977203369</t>
+    <t xml:space="preserve">24.6372833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0813694000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3476581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5447654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1047077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0853996276855</t>
   </si>
   <si>
     <t xml:space="preserve">25.119987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9462127685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.811056137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5986652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7338256835938</t>
+    <t xml:space="preserve">24.9462146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8110580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5986633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7338237762451</t>
   </si>
   <si>
     <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269065856934</t>
+    <t xml:space="preserve">24.9269046783447</t>
   </si>
   <si>
     <t xml:space="preserve">26.7611846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2205543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6179733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4635066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358360290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1392974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6413097381592</t>
+    <t xml:space="preserve">26.2205581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6179752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.463508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1392955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6413078308105</t>
   </si>
   <si>
     <t xml:space="preserve">25.3130702972412</t>
@@ -2567,31 +2567,31 @@
     <t xml:space="preserve">26.2977867126465</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7804946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067218780518</t>
+    <t xml:space="preserve">26.7804927825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067180633545</t>
   </si>
   <si>
     <t xml:space="preserve">26.046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2591724395752</t>
+    <t xml:space="preserve">26.2591743469238</t>
   </si>
   <si>
     <t xml:space="preserve">26.4136371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8343906402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7571582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4675350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5600509643555</t>
+    <t xml:space="preserve">25.8343925476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7571601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4675331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689804077148</t>
@@ -2600,28 +2600,28 @@
     <t xml:space="preserve">24.7724380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1401214599609</t>
+    <t xml:space="preserve">30.1401233673096</t>
   </si>
   <si>
     <t xml:space="preserve">31.7620143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1481742858887</t>
+    <t xml:space="preserve">32.1481781005859</t>
   </si>
   <si>
     <t xml:space="preserve">32.2061042785645</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8392467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9744033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9550952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3798789978027</t>
+    <t xml:space="preserve">31.8392448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9743995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9550933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">33.2680549621582</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">35.1795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3726501464844</t>
+    <t xml:space="preserve">35.3726463317871</t>
   </si>
   <si>
     <t xml:space="preserve">34.3879280090332</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">34.5810089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2761077880859</t>
+    <t xml:space="preserve">35.2761116027832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8706359863281</t>
+    <t xml:space="preserve">34.8706398010254</t>
   </si>
   <si>
     <t xml:space="preserve">34.7547874450684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6429595947266</t>
+    <t xml:space="preserve">35.6429634094238</t>
   </si>
   <si>
     <t xml:space="preserve">35.0444107055664</t>
@@ -2669,58 +2669,58 @@
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4651641845703</t>
+    <t xml:space="preserve">34.465160369873</t>
   </si>
   <si>
     <t xml:space="preserve">34.6003227233887</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640266418457</t>
+    <t xml:space="preserve">32.2640228271484</t>
   </si>
   <si>
     <t xml:space="preserve">32.4957237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0556602478027</t>
+    <t xml:space="preserve">33.0556678771973</t>
   </si>
   <si>
     <t xml:space="preserve">34.0596885681152</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5383720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.291389465332</t>
+    <t xml:space="preserve">33.5383682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2913856506348</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542167663574</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7314529418945</t>
+    <t xml:space="preserve">32.9977378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7314491271973</t>
   </si>
   <si>
     <t xml:space="preserve">33.3066711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6349105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591255187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8971710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0709419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4377975463867</t>
+    <t xml:space="preserve">33.6349067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1908187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8971748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0709457397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.437801361084</t>
   </si>
   <si>
     <t xml:space="preserve">33.345287322998</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9631462097168</t>
+    <t xml:space="preserve">33.9824562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
     <t xml:space="preserve">34.4458541870117</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">34.0983047485352</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5962905883789</t>
+    <t xml:space="preserve">33.5962944030762</t>
   </si>
   <si>
     <t xml:space="preserve">33.0749702453613</t>
@@ -2759,31 +2759,31 @@
     <t xml:space="preserve">33.4418258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8818893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6115760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6775550842285</t>
+    <t xml:space="preserve">32.881893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.611572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6775512695312</t>
   </si>
   <si>
     <t xml:space="preserve">37.5351715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8360481262207</t>
+    <t xml:space="preserve">35.8360443115234</t>
   </si>
   <si>
     <t xml:space="preserve">37.4000129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4925231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1490020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2994422912598</t>
+    <t xml:space="preserve">36.4925270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1490058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2994384765625</t>
   </si>
   <si>
     <t xml:space="preserve">36.2801361083984</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">35.6043510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5657348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3919563293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4346008300781</t>
+    <t xml:space="preserve">35.565731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.391960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4346046447754</t>
   </si>
   <si>
     <t xml:space="preserve">37.6510200500488</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5158653259277</t>
+    <t xml:space="preserve">37.5158576965332</t>
   </si>
   <si>
     <t xml:space="preserve">38.519889831543</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.581844329834</t>
+    <t xml:space="preserve">39.5818405151367</t>
   </si>
   <si>
     <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2383193969727</t>
+    <t xml:space="preserve">40.2383155822754</t>
   </si>
   <si>
     <t xml:space="preserve">39.2149848937988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9527206420898</t>
+    <t xml:space="preserve">40.9527168273926</t>
   </si>
   <si>
     <t xml:space="preserve">41.1458015441895</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">41.3388862609863</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8948020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7017211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6244850158691</t>
+    <t xml:space="preserve">40.8947982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.701717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6244812011719</t>
   </si>
   <si>
     <t xml:space="preserve">40.5665588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3429145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780731201172</t>
+    <t xml:space="preserve">42.3429107666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780769348145</t>
   </si>
   <si>
     <t xml:space="preserve">41.0878829956055</t>
@@ -2882,19 +2882,19 @@
     <t xml:space="preserve">41.2809600830078</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3236083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4008369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6711540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8875732421875</t>
+    <t xml:space="preserve">42.3236045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4008331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8875694274902</t>
   </si>
   <si>
     <t xml:space="preserve">43.5786399841309</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">43.9841156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6172561645508</t>
+    <t xml:space="preserve">43.6172523498535</t>
   </si>
   <si>
     <t xml:space="preserve">43.8489532470703</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">45.3743057250977</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3244361877441</t>
+    <t xml:space="preserve">47.3244323730469</t>
   </si>
   <si>
     <t xml:space="preserve">49.7669219970703</t>
@@ -2933,25 +2933,25 @@
     <t xml:space="preserve">48.7049713134766</t>
   </si>
   <si>
-    <t xml:space="preserve">48.367073059082</t>
+    <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
     <t xml:space="preserve">47.4982070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4748725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8183898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0694007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1120452880859</t>
+    <t xml:space="preserve">46.4748687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8183937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0694046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5521049499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1120376586914</t>
   </si>
   <si>
     <t xml:space="preserve">47.4016647338867</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">48.01953125</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3188018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1876754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9229888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6912879943848</t>
+    <t xml:space="preserve">48.3188056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1876792907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9229850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.691291809082</t>
   </si>
   <si>
     <t xml:space="preserve">47.7878341674805</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">47.3051223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6140594482422</t>
+    <t xml:space="preserve">47.6140556335449</t>
   </si>
   <si>
     <t xml:space="preserve">48.2705345153809</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">50.539249420166</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8457527160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2842140197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6221122741699</t>
+    <t xml:space="preserve">47.8457565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">49.6703834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5255661010742</t>
+    <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
     <t xml:space="preserve">47.420970916748</t>
@@ -3017,67 +3017,67 @@
     <t xml:space="preserve">47.9809150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3807601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0082778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2978935241699</t>
+    <t xml:space="preserve">49.3807563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0082740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2978973388672</t>
   </si>
   <si>
     <t xml:space="preserve">50.4909782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4974403381348</t>
+    <t xml:space="preserve">54.4974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">53.8699150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3252601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9527740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9045028686523</t>
+    <t xml:space="preserve">52.3252639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9527778625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9045066833496</t>
   </si>
   <si>
     <t xml:space="preserve">53.6768379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0975914001465</t>
+    <t xml:space="preserve">53.0975875854492</t>
   </si>
   <si>
     <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8562393188477</t>
+    <t xml:space="preserve">52.8562355041504</t>
   </si>
   <si>
     <t xml:space="preserve">52.0356407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">51.601203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7105979919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0774536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.173999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.903678894043</t>
+    <t xml:space="preserve">51.6012001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7105941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6567001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0774574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1740036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9616088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9036827087402</t>
   </si>
   <si>
     <t xml:space="preserve">47.4402847290039</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287704467773</t>
+    <t xml:space="preserve">45.5287742614746</t>
   </si>
   <si>
     <t xml:space="preserve">46.301097869873</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">46.5907211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8031120300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8071365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6446189880371</t>
+    <t xml:space="preserve">46.8031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8071403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6446228027344</t>
   </si>
   <si>
     <t xml:space="preserve">45.8956260681152</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3163757324219</t>
+    <t xml:space="preserve">45.9149360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3163795471191</t>
   </si>
   <si>
     <t xml:space="preserve">45.4129219055176</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699714660645</t>
+    <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9945983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4290313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5875244140625</t>
+    <t xml:space="preserve">48.9945945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.429027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5875205993652</t>
   </si>
   <si>
     <t xml:space="preserve">52.1321792602539</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">58.1659965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">60.145092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9174194335938</t>
+    <t xml:space="preserve">60.1450843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9174156188965</t>
   </si>
   <si>
     <t xml:space="preserve">59.7106552124023</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">61.255313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5312538146973</t>
+    <t xml:space="preserve">60.53125</t>
   </si>
   <si>
     <t xml:space="preserve">60.2899017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7589225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.021183013916</t>
+    <t xml:space="preserve">59.7589263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0211868286133</t>
   </si>
   <si>
     <t xml:space="preserve">58.0694580078125</t>
@@ -3200,46 +3200,46 @@
     <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">55.849006652832</t>
+    <t xml:space="preserve">55.8490104675293</t>
   </si>
   <si>
     <t xml:space="preserve">56.2834434509277</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4354858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4491691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9664573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7870559692383</t>
+    <t xml:space="preserve">53.4354820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4491653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
     <t xml:space="preserve">53.5802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0147285461426</t>
+    <t xml:space="preserve">54.0147323608398</t>
   </si>
   <si>
     <t xml:space="preserve">54.9318695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4282608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0284080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2078170776367</t>
+    <t xml:space="preserve">56.4282569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0284118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2078132629395</t>
   </si>
   <si>
     <t xml:space="preserve">53.3872146606445</t>
   </si>
   <si>
-    <t xml:space="preserve">51.987361907959</t>
+    <t xml:space="preserve">51.9873657226562</t>
   </si>
   <si>
     <t xml:space="preserve">55.4145774841309</t>
@@ -3257,13 +3257,13 @@
     <t xml:space="preserve">57.3453979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5038948059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6004295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9656867980957</t>
+    <t xml:space="preserve">58.5038909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6004333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.965690612793</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
@@ -3272,34 +3272,34 @@
     <t xml:space="preserve">61.3035850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3864364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6969718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420913696289</t>
+    <t xml:space="preserve">60.3864402770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6969680786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420875549316</t>
   </si>
   <si>
     <t xml:space="preserve">58.4073486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">55.221492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0629997253418</t>
+    <t xml:space="preserve">55.2214965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0630035400391</t>
   </si>
   <si>
     <t xml:space="preserve">52.2287216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">52.083911895752</t>
+    <t xml:space="preserve">52.0839080810547</t>
   </si>
   <si>
     <t xml:space="preserve">53.1458587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4427108764648</t>
+    <t xml:space="preserve">50.4427070617676</t>
   </si>
   <si>
     <t xml:space="preserve">50.8288764953613</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">51.8908271789551</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2359466552734</t>
+    <t xml:space="preserve">50.0565452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2359504699707</t>
   </si>
   <si>
     <t xml:space="preserve">53.483757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8425598144531</t>
+    <t xml:space="preserve">51.8425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1184959411621</t>
+    <t xml:space="preserve">51.1185035705566</t>
   </si>
   <si>
     <t xml:space="preserve">52.3735313415527</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">52.1804504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3461685180664</t>
+    <t xml:space="preserve">50.3461723327637</t>
   </si>
   <si>
     <t xml:space="preserve">51.4563941955566</t>
@@ -3341,22 +3341,22 @@
     <t xml:space="preserve">50.9254150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7806015014648</t>
+    <t xml:space="preserve">50.7806053161621</t>
   </si>
   <si>
     <t xml:space="preserve">49.7186508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0074424743652</t>
+    <t xml:space="preserve">45.0074501037598</t>
   </si>
   <si>
     <t xml:space="preserve">46.3976440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0919036865234</t>
+    <t xml:space="preserve">45.8763198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
     <t xml:space="preserve">41.2423477172852</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">42.1498336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5480766296387</t>
+    <t xml:space="preserve">45.5480804443359</t>
   </si>
   <si>
     <t xml:space="preserve">46.8224220275879</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">51.2633094787598</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7942886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5738372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8771476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219612121582</t>
+    <t xml:space="preserve">51.7942848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8771438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219573974609</t>
   </si>
   <si>
     <t xml:space="preserve">49.911735534668</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">45.2970695495605</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5561294555664</t>
+    <t xml:space="preserve">47.5561332702637</t>
   </si>
   <si>
     <t xml:space="preserve">46.9961929321289</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9495277404785</t>
+    <t xml:space="preserve">44.9495239257812</t>
   </si>
   <si>
     <t xml:space="preserve">43.675178527832</t>
@@ -3422,22 +3422,22 @@
     <t xml:space="preserve">42.8063125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">44.119270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0348091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.837703704834</t>
+    <t xml:space="preserve">44.1192665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6253089904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0348129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
     <t xml:space="preserve">44.1578903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4627914428711</t>
+    <t xml:space="preserve">43.4627952575684</t>
   </si>
   <si>
     <t xml:space="preserve">44.1254501342773</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">42.3908386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0400161743164</t>
+    <t xml:space="preserve">42.0400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">43.4043235778809</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.444766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.431282043457</t>
+    <t xml:space="preserve">46.4447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070495605469</t>
+    <t xml:space="preserve">41.0070457458496</t>
   </si>
   <si>
     <t xml:space="preserve">38.9995727539062</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">39.1360054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7012176513672</t>
+    <t xml:space="preserve">39.7012138366699</t>
   </si>
   <si>
     <t xml:space="preserve">39.8766212463379</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">40.0325469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">40.324893951416</t>
+    <t xml:space="preserve">40.3248977661133</t>
   </si>
   <si>
     <t xml:space="preserve">40.8706169128418</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646049499512</t>
+    <t xml:space="preserve">41.8646087646484</t>
   </si>
   <si>
     <t xml:space="preserve">42.7806434631348</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.269359588623</t>
+    <t xml:space="preserve">45.4507751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">47.4387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">49.163631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1381301879883</t>
+    <t xml:space="preserve">49.1636276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1381340026855</t>
   </si>
   <si>
     <t xml:space="preserve">50.8202857971191</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">51.2100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7460556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9177322387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5511589050293</t>
+    <t xml:space="preserve">51.7460594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9177284240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5511627197266</t>
   </si>
   <si>
     <t xml:space="preserve">53.548885345459</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517112731934</t>
+    <t xml:space="preserve">55.3517189025879</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3590,22 +3590,22 @@
     <t xml:space="preserve">54.3772125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9131927490234</t>
+    <t xml:space="preserve">54.9131889343262</t>
   </si>
   <si>
     <t xml:space="preserve">53.7437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1335868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1080932617188</t>
+    <t xml:space="preserve">54.1335906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1080894470215</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4491691589355</t>
+    <t xml:space="preserve">55.4491653442383</t>
   </si>
   <si>
     <t xml:space="preserve">55.4004402160645</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">54.474666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">53.061637878418</t>
+    <t xml:space="preserve">53.0616416931152</t>
   </si>
   <si>
     <t xml:space="preserve">52.5743865966797</t>
@@ -3632,40 +3632,40 @@
     <t xml:space="preserve">50.4792060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7970542907715</t>
+    <t xml:space="preserve">49.7970504760742</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8690071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7715530395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0151824951172</t>
+    <t xml:space="preserve">50.869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.771556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0151786804199</t>
   </si>
   <si>
     <t xml:space="preserve">51.5024337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0384140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4537124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5998840332031</t>
+    <t xml:space="preserve">52.0384063720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4537086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5998878479004</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3817596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8480453491211</t>
+    <t xml:space="preserve">50.3817558288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
     <t xml:space="preserve">45.8015975952148</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483291625977</t>
+    <t xml:space="preserve">49.7483329772949</t>
   </si>
   <si>
     <t xml:space="preserve">48.4522438049316</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8712768554688</t>
+    <t xml:space="preserve">48.871280670166</t>
   </si>
   <si>
     <t xml:space="preserve">49.3098030090332</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">49.4559783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3029899597168</t>
+    <t xml:space="preserve">55.3029937744141</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242240905762</t>
+    <t xml:space="preserve">60.2242279052734</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4468955993652</t>
+    <t xml:space="preserve">57.4468994140625</t>
   </si>
   <si>
     <t xml:space="preserve">57.1545486450195</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698432922363</t>
+    <t xml:space="preserve">56.5698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">59.6395263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8599281311035</t>
+    <t xml:space="preserve">58.8599243164062</t>
   </si>
   <si>
     <t xml:space="preserve">59.2497215270996</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">57.9828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4213981628418</t>
+    <t xml:space="preserve">58.4214019775391</t>
   </si>
   <si>
     <t xml:space="preserve">59.6882514953613</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">64.2684020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.319408416748</t>
+    <t xml:space="preserve">62.3194046020508</t>
   </si>
   <si>
     <t xml:space="preserve">63.0502815246582</t>
@@ -3794,43 +3794,43 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.484260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1176910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8230743408203</t>
+    <t xml:space="preserve">67.4842681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1176986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8230819702148</t>
   </si>
   <si>
     <t xml:space="preserve">70.3590469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9460296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4100494384766</t>
+    <t xml:space="preserve">68.9460220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.410041809082</t>
   </si>
   <si>
     <t xml:space="preserve">67.8740692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3125991821289</t>
+    <t xml:space="preserve">68.3125915527344</t>
   </si>
   <si>
     <t xml:space="preserve">67.1919097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8972930908203</t>
+    <t xml:space="preserve">68.8972854614258</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4865341186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5817108154297</t>
+    <t xml:space="preserve">65.4865417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5817184448242</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3848,28 +3848,28 @@
     <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8995742797852</t>
+    <t xml:space="preserve">66.8995666503906</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584945678711</t>
+    <t xml:space="preserve">66.5584869384766</t>
   </si>
   <si>
     <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0434646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6514053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7233428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4309997558594</t>
+    <t xml:space="preserve">69.0434722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6513977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7233505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4310073852539</t>
   </si>
   <si>
     <t xml:space="preserve">71.528450012207</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">72.6978530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6700820922852</t>
+    <t xml:space="preserve">75.6700897216797</t>
   </si>
   <si>
     <t xml:space="preserve">75.0366516113281</t>
@@ -3890,13 +3890,13 @@
     <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7188110351562</t>
+    <t xml:space="preserve">75.7188034057617</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8394775390625</t>
+    <t xml:space="preserve">76.839485168457</t>
   </si>
   <si>
     <t xml:space="preserve">77.2780151367188</t>
@@ -3911,49 +3911,49 @@
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627166748047</t>
+    <t xml:space="preserve">77.8627090454102</t>
   </si>
   <si>
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859329223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.5703659057617</t>
+    <t xml:space="preserve">78.8859405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.5703582763672</t>
   </si>
   <si>
     <t xml:space="preserve">77.1805572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">78.1550674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0088882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.424186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0831069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6678161621094</t>
+    <t xml:space="preserve">78.1550598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0088958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.4241790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6678085327148</t>
   </si>
   <si>
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.032112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4474105834961</t>
+    <t xml:space="preserve">78.3012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0321197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
@@ -3962,16 +3962,16 @@
     <t xml:space="preserve">77.4729080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9647064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4519653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.82080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.9601669311523</t>
+    <t xml:space="preserve">73.964714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.9601593017578</t>
   </si>
   <si>
     <t xml:space="preserve">75.8162612915039</t>
@@ -3983,25 +3983,25 @@
     <t xml:space="preserve">80.3964157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">80.2989730834961</t>
+    <t xml:space="preserve">80.2989654541016</t>
   </si>
   <si>
     <t xml:space="preserve">81.7119979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4683685302734</t>
+    <t xml:space="preserve">81.468376159668</t>
   </si>
   <si>
     <t xml:space="preserve">81.8581695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1924362182617</t>
+    <t xml:space="preserve">81.7607192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2689361572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1924438476562</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
@@ -4022,28 +4022,28 @@
     <t xml:space="preserve">86.3408737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2434310913086</t>
+    <t xml:space="preserve">86.2434234619141</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2876129150391</t>
+    <t xml:space="preserve">90.2876205444336</t>
   </si>
   <si>
     <t xml:space="preserve">87.8513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3618392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0972518920898</t>
+    <t xml:space="preserve">89.3618316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360656738281</t>
+    <t xml:space="preserve">88.4360580444336</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1017990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1250228881836</t>
+    <t xml:space="preserve">82.1017913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">85.6100082397461</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6887664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0043563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4196472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2270202636719</t>
+    <t xml:space="preserve">80.6887741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0043411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4196548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2270278930664</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
@@ -4082,22 +4082,22 @@
     <t xml:space="preserve">79.9091720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5299453735352</t>
+    <t xml:space="preserve">81.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096496582031</t>
+    <t xml:space="preserve">77.1096420288086</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.632194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830841064453</t>
+    <t xml:space="preserve">78.6322021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618179321289</t>
+    <t xml:space="preserve">79.7618255615234</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370239257812</t>
+    <t xml:space="preserve">81.1370315551758</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909713745117</t>
+    <t xml:space="preserve">83.6909790039062</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.628173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317169189453</t>
+    <t xml:space="preserve">81.6281661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317092895508</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.07421875</t>
+    <t xml:space="preserve">79.0742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4184,22 +4184,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9268798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0959548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326644897461</t>
+    <t xml:space="preserve">78.926872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326721191406</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853256225586</t>
+    <t xml:space="preserve">75.6853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928970336914</t>
+    <t xml:space="preserve">72.4928894042969</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870895385742</t>
+    <t xml:space="preserve">75.5870971679688</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402282714844</t>
+    <t xml:space="preserve">72.6402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176910400391</t>
+    <t xml:space="preserve">71.1176834106445</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597076416016</t>
+    <t xml:space="preserve">71.5597152709961</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022247314453</t>
+    <t xml:space="preserve">72.3946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022171020508</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212265014648</t>
+    <t xml:space="preserve">70.9212188720703</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4295,16 +4295,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5419998168945</t>
+    <t xml:space="preserve">72.5420074462891</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389343261719</t>
+    <t xml:space="preserve">73.4260711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.827018737793</t>
+    <t xml:space="preserve">67.8270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247695922852</t>
+    <t xml:space="preserve">70.7247772216797</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.5460205078125</t>
+    <t xml:space="preserve">69.546028137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698593139648</t>
+    <t xml:space="preserve">73.7698669433594</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4361,19 +4361,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065841674805</t>
+    <t xml:space="preserve">77.6007919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065765380859</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481307983398</t>
+    <t xml:space="preserve">77.7481384277344</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4394,25 +4394,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.9309005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238143920898</t>
+    <t xml:space="preserve">75.930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238067626953</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344360351562</t>
+    <t xml:space="preserve">75.7344436645508</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.905143737793</t>
+    <t xml:space="preserve">82.9051513671875</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046737670898</t>
+    <t xml:space="preserve">85.7046661376953</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851791381836</t>
+    <t xml:space="preserve">86.7851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542541503906</t>
+    <t xml:space="preserve">82.9542617797852</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489471435547</t>
+    <t xml:space="preserve">83.2489547729492</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4484,16 +4484,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312393188477</t>
+    <t xml:space="preserve">84.2312316894531</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507186889648</t>
+    <t xml:space="preserve">82.5613479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507263183594</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338272094727</t>
+    <t xml:space="preserve">89.6338195800781</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581359863281</t>
+    <t xml:space="preserve">91.0581436157227</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.857666015625</t>
+    <t xml:space="preserve">93.8576736450195</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4547,16 +4547,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747375488281</t>
+    <t xml:space="preserve">102.845596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.827896118164</t>
+    <t xml:space="preserve">103.82788848877</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034027099609</t>
+    <t xml:space="preserve">109.034019470215</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525169372559</t>
+    <t xml:space="preserve">109.525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.631439208984</t>
+    <t xml:space="preserve">103.63143157959</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4625,16 +4625,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122573852539</t>
+    <t xml:space="preserve">102.158004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122581481934</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987426757812</t>
+    <t xml:space="preserve">99.8987350463867</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518661499023</t>
+    <t xml:space="preserve">96.3625030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518737792969</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2642669677734</t>
+    <t xml:space="preserve">96.264274597168</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5589599609375</t>
+    <t xml:space="preserve">96.558967590332</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4697,16 +4697,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890609741211</t>
+    <t xml:space="preserve">94.8890686035156</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488082885742</t>
+    <t xml:space="preserve">94.7417144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488159179688</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5649,6 +5649,9 @@
   </si>
   <si>
     <t xml:space="preserve">90.4199981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -70909,7 +70912,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6910069444</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>233588</v>
@@ -70930,6 +70933,32 @@
         <v>1878</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.693587963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>310749</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>91.4800033569336</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>89.8399963378906</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>90.4000015258789</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>90.8199996948242</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1881">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,76 +38,76 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807565689087</t>
+    <t xml:space="preserve">15.1807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537855148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1718187332153</t>
+    <t xml:space="preserve">14.8537845611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.171820640564</t>
   </si>
   <si>
     <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208856582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022003173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.44273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0877408981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0410327911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3212909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3399772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7697076797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3866853713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.424054145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849805831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433801651001</t>
+    <t xml:space="preserve">13.9289255142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208866119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022022247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4427375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0877418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0410318374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3212919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.33997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7697086334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3866863250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240550994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.003662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338006973267</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051258087158</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">12.4155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061784744263</t>
+    <t xml:space="preserve">12.4061822891235</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459051132202</t>
+    <t xml:space="preserve">13.5459060668945</t>
   </si>
   <si>
     <t xml:space="preserve">13.1722259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5645904541016</t>
+    <t xml:space="preserve">13.5645895004272</t>
   </si>
   <si>
     <t xml:space="preserve">13.4057750701904</t>
@@ -137,55 +137,55 @@
     <t xml:space="preserve">13.3777494430542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251106262207</t>
+    <t xml:space="preserve">14.1251096725464</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195852279663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0316896438599</t>
+    <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
     <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8355073928833</t>
+    <t xml:space="preserve">13.8355083465576</t>
   </si>
   <si>
     <t xml:space="preserve">14.1064262390137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2372140884399</t>
+    <t xml:space="preserve">14.2372150421143</t>
   </si>
   <si>
     <t xml:space="preserve">14.4520807266235</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2558965682983</t>
+    <t xml:space="preserve">14.255898475647</t>
   </si>
   <si>
     <t xml:space="preserve">15.414306640625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011476516724</t>
+    <t xml:space="preserve">15.6011457443237</t>
   </si>
   <si>
     <t xml:space="preserve">15.246150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1060180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5450944900513</t>
+    <t xml:space="preserve">15.1060190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769388198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.479700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5450925827026</t>
   </si>
   <si>
     <t xml:space="preserve">15.6945667266846</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">15.6104879379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.993914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202383041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.330228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412776947021</t>
+    <t xml:space="preserve">15.4983825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873365402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918035507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412738800049</t>
   </si>
   <si>
     <t xml:space="preserve">15.8253555297852</t>
@@ -227,85 +227,85 @@
     <t xml:space="preserve">16.3017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3952178955078</t>
+    <t xml:space="preserve">16.3952159881592</t>
   </si>
   <si>
     <t xml:space="preserve">16.3858776092529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3485050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4139003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924575805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671913146973</t>
+    <t xml:space="preserve">16.3485088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4139022827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671932220459</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2177181243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3765354156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3391628265381</t>
+    <t xml:space="preserve">16.2177200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3765316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3391647338867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1149559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2737693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100826263428</t>
+    <t xml:space="preserve">16.2737712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100845336914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6474494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6287651062012</t>
+    <t xml:space="preserve">16.6287670135498</t>
   </si>
   <si>
     <t xml:space="preserve">16.4419250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889850616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489810943604</t>
+    <t xml:space="preserve">16.4889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648983001709</t>
   </si>
   <si>
     <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.601921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6866283416748</t>
+    <t xml:space="preserve">16.6207447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6019229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6866245269775</t>
   </si>
   <si>
     <t xml:space="preserve">16.7054500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7995643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454521179199</t>
+    <t xml:space="preserve">16.7995662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454559326172</t>
   </si>
   <si>
     <t xml:space="preserve">16.6583938598633</t>
@@ -320,46 +320,46 @@
     <t xml:space="preserve">16.2254619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6890068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407793045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5830974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113338470459</t>
+    <t xml:space="preserve">15.6890048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725408554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407783508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.583101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113357543945</t>
   </si>
   <si>
     <t xml:space="preserve">16.4325160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2536945343018</t>
+    <t xml:space="preserve">16.2536964416504</t>
   </si>
   <si>
     <t xml:space="preserve">16.5642757415771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5290107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090187072754</t>
+    <t xml:space="preserve">15.5290098190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748975753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090177536011</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101861953735</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">14.7854995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3149223327637</t>
+    <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443271636963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9172611236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513586044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195989608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348936080933</t>
+    <t xml:space="preserve">14.9172620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348945617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.5854768753052</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">15.9054698944092</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8301801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.547833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.933705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701812744141</t>
+    <t xml:space="preserve">15.8301782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901723861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478315353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337034225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701822280884</t>
   </si>
   <si>
     <t xml:space="preserve">15.3784246444702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419486999512</t>
+    <t xml:space="preserve">15.5007753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419496536255</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148817062378</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0278224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2725219726562</t>
+    <t xml:space="preserve">16.0278205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2725200653076</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195781707764</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">16.2819309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1595840454102</t>
+    <t xml:space="preserve">16.1595802307129</t>
   </si>
   <si>
     <t xml:space="preserve">16.3760433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4983978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607467651367</t>
+    <t xml:space="preserve">16.4983959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.460750579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.5078105926514</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">16.6301574707031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4701614379883</t>
+    <t xml:space="preserve">16.4701633453369</t>
   </si>
   <si>
     <t xml:space="preserve">16.780740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8560333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9877948760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407367706299</t>
+    <t xml:space="preserve">16.8560352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.98779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407348632812</t>
   </si>
   <si>
     <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9313259124756</t>
+    <t xml:space="preserve">16.931324005127</t>
   </si>
   <si>
     <t xml:space="preserve">16.978385925293</t>
@@ -506,40 +506,40 @@
     <t xml:space="preserve">16.8842678070068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9030914306641</t>
+    <t xml:space="preserve">16.7525081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9030933380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.0066165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.053674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8748569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.034854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654460906982</t>
+    <t xml:space="preserve">16.9972057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0536766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8748588562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0348529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654441833496</t>
   </si>
   <si>
     <t xml:space="preserve">16.7619190216064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0725002288818</t>
+    <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
     <t xml:space="preserve">17.232494354248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1007347106934</t>
+    <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289672851562</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548450469971</t>
+    <t xml:space="preserve">17.2136745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">17.3642559051514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3077869415283</t>
+    <t xml:space="preserve">17.3077850341797</t>
   </si>
   <si>
     <t xml:space="preserve">17.298376083374</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">17.6936569213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8724784851074</t>
+    <t xml:space="preserve">17.8724765777588</t>
   </si>
   <si>
     <t xml:space="preserve">18.738338470459</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">18.8230419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6818675994873</t>
+    <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042182922363</t>
@@ -584,61 +584,61 @@
     <t xml:space="preserve">19.1430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3406772613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.378324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.935977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2183246612549</t>
+    <t xml:space="preserve">19.3406734466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2183227539062</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159660339355</t>
+    <t xml:space="preserve">19.4159641265869</t>
   </si>
   <si>
     <t xml:space="preserve">20.2724170684814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4230041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2347679138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4982948303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3571224212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.893575668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959323883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.103006362915</t>
+    <t xml:space="preserve">20.423002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.234769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4982929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3571186065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8935775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6676959991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030101776123</t>
   </si>
   <si>
     <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7453689575195</t>
+    <t xml:space="preserve">19.7453727722168</t>
   </si>
   <si>
     <t xml:space="preserve">19.5194931030273</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">19.6889038085938</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8488960266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.575963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2747936248779</t>
+    <t xml:space="preserve">19.7171382904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.84889793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5759620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2747955322266</t>
   </si>
   <si>
     <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.387731552124</t>
+    <t xml:space="preserve">19.3877334594727</t>
   </si>
   <si>
     <t xml:space="preserve">19.3500862121582</t>
@@ -677,43 +677,43 @@
     <t xml:space="preserve">19.0959739685059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0018615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171600341797</t>
+    <t xml:space="preserve">19.001859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171562194824</t>
   </si>
   <si>
     <t xml:space="preserve">19.0865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8700981140137</t>
+    <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
     <t xml:space="preserve">18.4936370849609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3524646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6254005432129</t>
+    <t xml:space="preserve">18.352466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2865867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6254024505615</t>
   </si>
   <si>
     <t xml:space="preserve">19.2559700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5100860595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2371520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006713867188</t>
+    <t xml:space="preserve">19.5100803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006694793701</t>
   </si>
   <si>
     <t xml:space="preserve">19.7547836303711</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">19.7924308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.594783782959</t>
+    <t xml:space="preserve">19.5947856903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6018199920654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7335815429688</t>
+    <t xml:space="preserve">20.7335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994613647461</t>
@@ -737,49 +737,49 @@
     <t xml:space="preserve">20.7900485992432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9218139648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2982711791992</t>
+    <t xml:space="preserve">20.9218101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1853332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0159244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794494628906</t>
+    <t xml:space="preserve">21.015926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.279447555542</t>
   </si>
   <si>
     <t xml:space="preserve">21.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6088523864746</t>
+    <t xml:space="preserve">21.4112129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6088542938232</t>
   </si>
   <si>
     <t xml:space="preserve">21.2135677337646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3829765319824</t>
+    <t xml:space="preserve">21.3829746246338</t>
   </si>
   <si>
     <t xml:space="preserve">21.5429706573486</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">21.8347320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0229587554932</t>
+    <t xml:space="preserve">22.0229606628418</t>
   </si>
   <si>
     <t xml:space="preserve">21.8064937591553</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">22.2582473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817665100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0394039154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7288227081299</t>
+    <t xml:space="preserve">22.6817646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0394020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7288208007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.0582275390625</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">22.5876502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">22.371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135478973389</t>
+    <t xml:space="preserve">22.3711853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135459899902</t>
   </si>
   <si>
     <t xml:space="preserve">21.6464977264404</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7876720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3076858520508</t>
+    <t xml:space="preserve">21.787670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3076820373535</t>
   </si>
   <si>
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.098123550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1455020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1549758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686901092529</t>
+    <t xml:space="preserve">22.0981216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1455039978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1549777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686920166016</t>
   </si>
   <si>
     <t xml:space="preserve">22.0507411956787</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0886459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7569847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327941894531</t>
+    <t xml:space="preserve">21.7190818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0886478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327960968018</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811752319336</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380332946777</t>
+    <t xml:space="preserve">21.7285594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380352020264</t>
   </si>
   <si>
     <t xml:space="preserve">21.5579891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5200843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1315650939941</t>
+    <t xml:space="preserve">21.5200824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1315631866455</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158496856689</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4632301330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6622257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674667358398</t>
+    <t xml:space="preserve">21.463228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674648284912</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624504089355</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013557434082</t>
+    <t xml:space="preserve">22.4013538360596</t>
   </si>
   <si>
     <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5814018249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6761627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.590877532959</t>
+    <t xml:space="preserve">22.5813999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6761608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5908756256104</t>
   </si>
   <si>
     <t xml:space="preserve">21.7948875427246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8138427734375</t>
+    <t xml:space="preserve">21.8138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">21.8422660827637</t>
@@ -935,58 +935,58 @@
     <t xml:space="preserve">21.6717014312744</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5958938598633</t>
+    <t xml:space="preserve">21.5958919525146</t>
   </si>
   <si>
     <t xml:space="preserve">22.4676856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3255462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5055923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951160430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0362491607666</t>
+    <t xml:space="preserve">22.3255481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5055904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.036247253418</t>
   </si>
   <si>
     <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2162952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9983444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1310119628906</t>
+    <t xml:space="preserve">23.2162914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.998348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1310081481934</t>
   </si>
   <si>
     <t xml:space="preserve">23.5005760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6900978088379</t>
+    <t xml:space="preserve">23.6900959014893</t>
   </si>
   <si>
     <t xml:space="preserve">23.2731513977051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1404857635498</t>
+    <t xml:space="preserve">23.1404876708984</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4531936645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7709197998047</t>
+    <t xml:space="preserve">23.4531955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
     <t xml:space="preserve">22.950963973999</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">22.7519683837891</t>
   </si>
   <si>
-    <t xml:space="preserve">22.723539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9793930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6477317810059</t>
+    <t xml:space="preserve">22.7235412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9793949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6477355957031</t>
   </si>
   <si>
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1834049224854</t>
+    <t xml:space="preserve">22.1834087371826</t>
   </si>
   <si>
     <t xml:space="preserve">23.8796157836914</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">23.6616668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3868656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783924102783</t>
+    <t xml:space="preserve">23.3868637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783905029297</t>
   </si>
   <si>
     <t xml:space="preserve">22.9035873413086</t>
@@ -1034,112 +1034,112 @@
     <t xml:space="preserve">24.0217590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145168304443</t>
+    <t xml:space="preserve">24.4955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145149230957</t>
   </si>
   <si>
     <t xml:space="preserve">24.6377029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.685079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903186798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040309906006</t>
+    <t xml:space="preserve">24.6850814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
     <t xml:space="preserve">24.8082695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">24.779842376709</t>
+    <t xml:space="preserve">24.7798404693604</t>
   </si>
   <si>
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1638984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8651275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.547399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915477752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4431648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4905433654785</t>
+    <t xml:space="preserve">24.5429401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1639003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8651256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5474014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4431667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4905452728271</t>
   </si>
   <si>
     <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3294506072998</t>
+    <t xml:space="preserve">25.3484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3294525146484</t>
   </si>
   <si>
     <t xml:space="preserve">25.0830745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7274436950684</t>
+    <t xml:space="preserve">25.727445602417</t>
   </si>
   <si>
     <t xml:space="preserve">25.6611137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9643459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3099422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119510650635</t>
+    <t xml:space="preserve">25.9643478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.309944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972343444824</t>
+    <t xml:space="preserve">26.675048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972324371338</t>
   </si>
   <si>
     <t xml:space="preserve">27.1678047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4665756225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0591068267822</t>
+    <t xml:space="preserve">26.4665775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0591087341309</t>
   </si>
   <si>
     <t xml:space="preserve">25.0451698303223</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">25.1778354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1967868804932</t>
+    <t xml:space="preserve">25.1967849731445</t>
   </si>
   <si>
     <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1115036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5379276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.935920715332</t>
+    <t xml:space="preserve">25.111499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5379257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9359188079834</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588821411133</t>
@@ -1172,49 +1172,49 @@
     <t xml:space="preserve">25.2631206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1683559417725</t>
+    <t xml:space="preserve">25.1683597564697</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.206262588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853023529053</t>
+    <t xml:space="preserve">25.2062606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853042602539</t>
   </si>
   <si>
     <t xml:space="preserve">25.6042575836182</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8601112365723</t>
+    <t xml:space="preserve">25.8601093292236</t>
   </si>
   <si>
     <t xml:space="preserve">26.3339138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4381484985352</t>
+    <t xml:space="preserve">26.248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4381465911865</t>
   </si>
   <si>
     <t xml:space="preserve">24.7987937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3673572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3578796386719</t>
+    <t xml:space="preserve">25.3673553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3578815460205</t>
   </si>
   <si>
     <t xml:space="preserve">25.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232109069824</t>
+    <t xml:space="preserve">25.6232089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.7748260498047</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">25.7084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1064872741699</t>
+    <t xml:space="preserve">26.1064853668213</t>
   </si>
   <si>
     <t xml:space="preserve">26.8171901702881</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">27.0540904998779</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3857536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695850372314</t>
+    <t xml:space="preserve">27.3857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695831298828</t>
   </si>
   <si>
     <t xml:space="preserve">25.8222045898438</t>
@@ -1247,31 +1247,31 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7324619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9743785858154</t>
+    <t xml:space="preserve">25.6326866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7324638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8272228240967</t>
+    <t xml:space="preserve">24.0691394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.827220916748</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.258659362793</t>
+    <t xml:space="preserve">24.2586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">25.0167407989502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9693641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9269981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433856964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012481689453</t>
+    <t xml:space="preserve">24.9693622589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
     <t xml:space="preserve">26.0117263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855270385742</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7698078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9493007659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6176376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8071575164795</t>
+    <t xml:space="preserve">26.9593334197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7698097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9492969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.617639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8071594238281</t>
   </si>
   <si>
     <t xml:space="preserve">28.665018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3283424377441</t>
+    <t xml:space="preserve">29.3283405303955</t>
   </si>
   <si>
     <t xml:space="preserve">29.2335815429688</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">30.2086696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0652732849121</t>
+    <t xml:space="preserve">30.0652751922607</t>
   </si>
   <si>
     <t xml:space="preserve">30.3042678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9696788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1130714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2602386474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419891357422</t>
+    <t xml:space="preserve">29.9696750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.113073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419929504395</t>
   </si>
   <si>
     <t xml:space="preserve">33.6501617431641</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">33.936954498291</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1759414672852</t>
+    <t xml:space="preserve">34.1759452819824</t>
   </si>
   <si>
     <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">35.753303527832</t>
+    <t xml:space="preserve">35.7532997131348</t>
   </si>
   <si>
     <t xml:space="preserve">35.9922981262207</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">35.2275161743164</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0841178894043</t>
+    <t xml:space="preserve">35.0841217041016</t>
   </si>
   <si>
     <t xml:space="preserve">35.6577033996582</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">35.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">36.422477722168</t>
+    <t xml:space="preserve">36.4224815368652</t>
   </si>
   <si>
     <t xml:space="preserve">36.3746795654297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3268814086914</t>
+    <t xml:space="preserve">36.3268852233887</t>
   </si>
   <si>
     <t xml:space="preserve">35.4187126159668</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5658760070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.852668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822532653809</t>
+    <t xml:space="preserve">36.5658798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822551727295</t>
   </si>
   <si>
     <t xml:space="preserve">31.1168403625488</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">31.4036312103271</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5948276519775</t>
+    <t xml:space="preserve">31.5948257446289</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558330535889</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2124404907227</t>
+    <t xml:space="preserve">31.212438583374</t>
   </si>
   <si>
     <t xml:space="preserve">33.0287818908691</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">33.7935600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9847564697266</t>
+    <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
     <t xml:space="preserve">34.7973251342773</t>
@@ -1445,49 +1445,49 @@
     <t xml:space="preserve">34.3671417236328</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6539344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.036319732666</t>
+    <t xml:space="preserve">34.6539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0363235473633</t>
   </si>
   <si>
     <t xml:space="preserve">34.6061325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4627342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8413619995117</t>
+    <t xml:space="preserve">34.4627380371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8413581848145</t>
   </si>
   <si>
     <t xml:space="preserve">34.7495269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0400924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966979980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6614723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5180740356445</t>
+    <t xml:space="preserve">35.5621109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.040096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6614685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5180816650391</t>
   </si>
   <si>
     <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8564376831055</t>
+    <t xml:space="preserve">37.8564300537109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2790870666504</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">34.8929214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5583343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6979637145996</t>
+    <t xml:space="preserve">34.5583381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6979598999023</t>
   </si>
   <si>
     <t xml:space="preserve">33.5067672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2677726745605</t>
+    <t xml:space="preserve">33.2677764892578</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640075683594</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">33.3633728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7897872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5985908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5029945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199783325195</t>
+    <t xml:space="preserve">32.7897911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.837589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5985946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5029983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199745178223</t>
   </si>
   <si>
     <t xml:space="preserve">32.6463928222656</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0728149414062</t>
+    <t xml:space="preserve">32.072811126709</t>
   </si>
   <si>
     <t xml:space="preserve">31.7860240936279</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8338222503662</t>
+    <t xml:space="preserve">31.8338260650635</t>
   </si>
   <si>
     <t xml:space="preserve">31.0690422058105</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">32.0250129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0212421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816165924072</t>
+    <t xml:space="preserve">31.0212459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816204071045</t>
   </si>
   <si>
     <t xml:space="preserve">28.8703117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5357208251953</t>
+    <t xml:space="preserve">28.5357227325439</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011318206787</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2489280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797519683838</t>
+    <t xml:space="preserve">28.4401264190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797500610352</t>
   </si>
   <si>
     <t xml:space="preserve">28.1055335998535</t>
@@ -1589,34 +1589,34 @@
     <t xml:space="preserve">27.2451610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9621391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3445281982422</t>
+    <t xml:space="preserve">27.9621410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3445262908936</t>
   </si>
   <si>
     <t xml:space="preserve">29.013708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9181098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2049007415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4954605102539</t>
+    <t xml:space="preserve">28.9181079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2048988342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4954586029053</t>
   </si>
   <si>
     <t xml:space="preserve">29.5872898101807</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4438934326172</t>
+    <t xml:space="preserve">30.7344551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174770355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4438896179199</t>
   </si>
   <si>
     <t xml:space="preserve">29.6828842163086</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">26.5759811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">26.384786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2929592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4363555908203</t>
+    <t xml:space="preserve">26.3847904205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2929573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4363574981689</t>
   </si>
   <si>
     <t xml:space="preserve">27.8187427520752</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">27.1017665863037</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8627738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4841537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0061683654785</t>
+    <t xml:space="preserve">26.8627758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4841556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0061702728271</t>
   </si>
   <si>
     <t xml:space="preserve">26.0979976654053</t>
@@ -1667,82 +1667,82 @@
     <t xml:space="preserve">25.6200122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1935939788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6237812042236</t>
+    <t xml:space="preserve">26.1935920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6237831115723</t>
   </si>
   <si>
     <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
-    <t xml:space="preserve">26.289192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671775817871</t>
+    <t xml:space="preserve">26.2891902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671756744385</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6791172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.109302520752</t>
+    <t xml:space="preserve">28.9659099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6791152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1093044281006</t>
   </si>
   <si>
     <t xml:space="preserve">26.6715774536133</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8149738311768</t>
+    <t xml:space="preserve">26.8149719238281</t>
   </si>
   <si>
     <t xml:space="preserve">26.4803867340088</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3885555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8225135803223</t>
+    <t xml:space="preserve">27.3885593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
     <t xml:space="preserve">29.874080657959</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1608695983887</t>
+    <t xml:space="preserve">30.1608715057373</t>
   </si>
   <si>
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.308032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4514331817627</t>
+    <t xml:space="preserve">31.3080348968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4514312744141</t>
   </si>
   <si>
     <t xml:space="preserve">32.4552001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3118019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2162094116211</t>
+    <t xml:space="preserve">32.3118057250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2162055969238</t>
   </si>
   <si>
     <t xml:space="preserve">33.6023635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1721801757812</t>
+    <t xml:space="preserve">33.172176361084</t>
   </si>
   <si>
     <t xml:space="preserve">33.5545654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2564678192139</t>
+    <t xml:space="preserve">30.2564697265625</t>
   </si>
   <si>
     <t xml:space="preserve">30.6388568878174</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">29.9409980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6484184265137</t>
+    <t xml:space="preserve">30.648416519165</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">30.9734477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2851505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4763431549072</t>
+    <t xml:space="preserve">30.2851486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4763412475586</t>
   </si>
   <si>
     <t xml:space="preserve">30.2277908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9983577728271</t>
+    <t xml:space="preserve">29.9983558654785</t>
   </si>
   <si>
     <t xml:space="preserve">29.8262825012207</t>
@@ -1802,31 +1802,31 @@
     <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8129539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5203723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.487922668457</t>
+    <t xml:space="preserve">28.812952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5203704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4879245758057</t>
   </si>
   <si>
     <t xml:space="preserve">28.7173557281494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1762218475342</t>
+    <t xml:space="preserve">29.4821300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1762237548828</t>
   </si>
   <si>
     <t xml:space="preserve">29.3291797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5761547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9237041473389</t>
+    <t xml:space="preserve">28.5761585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9237060546875</t>
   </si>
   <si>
     <t xml:space="preserve">28.6533908843994</t>
@@ -1835,16 +1835,16 @@
     <t xml:space="preserve">28.3058414459229</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3637657165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5182323455811</t>
+    <t xml:space="preserve">28.3637676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5182342529297</t>
   </si>
   <si>
     <t xml:space="preserve">27.8038311004639</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0741443634033</t>
+    <t xml:space="preserve">28.0741424560547</t>
   </si>
   <si>
     <t xml:space="preserve">27.1859645843506</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">27.3211231231689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5335159301758</t>
+    <t xml:space="preserve">27.5335140228271</t>
   </si>
   <si>
     <t xml:space="preserve">27.6493625640869</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776039123535</t>
+    <t xml:space="preserve">27.9776020050049</t>
   </si>
   <si>
     <t xml:space="preserve">27.5142059326172</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">27.7845211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548362731934</t>
+    <t xml:space="preserve">28.0548324584961</t>
   </si>
   <si>
     <t xml:space="preserve">27.9969100952148</t>
@@ -1886,40 +1886,40 @@
     <t xml:space="preserve">28.4989261627197</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2479190826416</t>
+    <t xml:space="preserve">28.247917175293</t>
   </si>
   <si>
     <t xml:space="preserve">28.3251514434814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8424472808838</t>
+    <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
     <t xml:space="preserve">27.900369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0934524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1167888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8850898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2712554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8311920166016</t>
+    <t xml:space="preserve">28.0934543609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1167869567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8850879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2712535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8311901092529</t>
   </si>
   <si>
     <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8505001068115</t>
+    <t xml:space="preserve">29.8505020141602</t>
   </si>
   <si>
     <t xml:space="preserve">29.7539577484131</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">29.9856548309326</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6807537078857</t>
+    <t xml:space="preserve">30.6807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">29.3677940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4836444854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.174711227417</t>
+    <t xml:space="preserve">29.4836463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1747093200684</t>
   </si>
   <si>
     <t xml:space="preserve">29.4257183074951</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4796180725098</t>
+    <t xml:space="preserve">28.4796161651611</t>
   </si>
   <si>
     <t xml:space="preserve">27.7652111053467</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542675018311</t>
+    <t xml:space="preserve">26.9542655944824</t>
   </si>
   <si>
     <t xml:space="preserve">27.1473503112793</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">26.683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5101776123047</t>
+    <t xml:space="preserve">26.5101795196533</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810596466064</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">28.1899948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3444595336914</t>
+    <t xml:space="preserve">28.3444576263428</t>
   </si>
   <si>
     <t xml:space="preserve">27.938985824585</t>
@@ -2006,43 +2006,43 @@
     <t xml:space="preserve">27.2631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0315017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6260299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4176654815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0355281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0894241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9928798675537</t>
+    <t xml:space="preserve">27.0314998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6260280609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4176616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0894260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.992883682251</t>
   </si>
   <si>
     <t xml:space="preserve">27.0508079528809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4755897521973</t>
+    <t xml:space="preserve">27.4755878448486</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">27.591438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6107482910156</t>
+    <t xml:space="preserve">27.5914363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.610746383667</t>
   </si>
   <si>
     <t xml:space="preserve">27.6879806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3557109832764</t>
+    <t xml:space="preserve">26.355712890625</t>
   </si>
   <si>
     <t xml:space="preserve">25.9309329986572</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">25.8537006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8730068206787</t>
+    <t xml:space="preserve">25.8730087280273</t>
   </si>
   <si>
     <t xml:space="preserve">27.301815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4562816619873</t>
+    <t xml:space="preserve">27.4562835693359</t>
   </si>
   <si>
     <t xml:space="preserve">26.8577251434326</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">26.7032604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.745906829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1087341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1320667266846</t>
+    <t xml:space="preserve">27.7459049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1087322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1320686340332</t>
   </si>
   <si>
     <t xml:space="preserve">28.3830757141113</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">28.9430122375488</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4064083099365</t>
+    <t xml:space="preserve">29.4064102172852</t>
   </si>
   <si>
     <t xml:space="preserve">28.8078556060791</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">28.7499332427979</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8271636962891</t>
+    <t xml:space="preserve">28.8271656036377</t>
   </si>
   <si>
     <t xml:space="preserve">29.0009384155273</t>
@@ -2111,28 +2111,28 @@
     <t xml:space="preserve">28.5954666137695</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6147747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133274078369</t>
+    <t xml:space="preserve">28.6147727966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133312225342</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9357891082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4571075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8585510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2213821411133</t>
+    <t xml:space="preserve">31.9357852935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4571113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8585548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2213802337646</t>
   </si>
   <si>
     <t xml:space="preserve">31.1827659606934</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">31.6654720306396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1674880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2600021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5882415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0476093292236</t>
+    <t xml:space="preserve">32.1674842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5882396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.047607421875</t>
   </si>
   <si>
     <t xml:space="preserve">30.9510688781738</t>
@@ -2159,43 +2159,43 @@
     <t xml:space="preserve">31.1248435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.854528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8931427001953</t>
+    <t xml:space="preserve">31.3565406799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8545246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">30.8159103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">31.337230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4683628082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0089912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7000617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0170440673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3645935058594</t>
+    <t xml:space="preserve">31.3372325897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4683609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0089931488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7000598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0170478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3645973205566</t>
   </si>
   <si>
     <t xml:space="preserve">33.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">33.885913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8899421691895</t>
+    <t xml:space="preserve">33.8859176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8899459838867</t>
   </si>
   <si>
     <t xml:space="preserve">35.0251007080078</t>
@@ -2204,22 +2204,22 @@
     <t xml:space="preserve">35.9712066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5311393737793</t>
+    <t xml:space="preserve">36.5311431884766</t>
   </si>
   <si>
     <t xml:space="preserve">36.9559211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2069320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7008934020996</t>
+    <t xml:space="preserve">37.2069282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7008857727051</t>
   </si>
   <si>
     <t xml:space="preserve">35.8167381286621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9864883422852</t>
+    <t xml:space="preserve">34.9864845275879</t>
   </si>
   <si>
     <t xml:space="preserve">33.2873611450195</t>
@@ -2234,13 +2234,13 @@
     <t xml:space="preserve">31.9937114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">31.684778213501</t>
+    <t xml:space="preserve">31.6847820281982</t>
   </si>
   <si>
     <t xml:space="preserve">31.8778629302979</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3605651855469</t>
+    <t xml:space="preserve">32.3605690002441</t>
   </si>
   <si>
     <t xml:space="preserve">33.3839073181152</t>
@@ -2249,25 +2249,25 @@
     <t xml:space="preserve">32.8432731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7427024841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8239631652832</t>
+    <t xml:space="preserve">31.7427062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8239669799805</t>
   </si>
   <si>
     <t xml:space="preserve">32.901195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2447204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5343437194824</t>
+    <t xml:space="preserve">32.2447242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5343399047852</t>
   </si>
   <si>
     <t xml:space="preserve">32.4764175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6928367614746</t>
+    <t xml:space="preserve">33.6928329467773</t>
   </si>
   <si>
     <t xml:space="preserve">32.7081184387207</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">30.0049648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">26.027473449707</t>
+    <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
     <t xml:space="preserve">26.2784805297852</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">26.1240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5407409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931915283203</t>
+    <t xml:space="preserve">24.5407390594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1931934356689</t>
   </si>
   <si>
     <t xml:space="preserve">22.9767761230469</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">25.2744522094727</t>
   </si>
   <si>
-    <t xml:space="preserve">25.737850189209</t>
+    <t xml:space="preserve">25.7378482818604</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150825500488</t>
   </si>
   <si>
-    <t xml:space="preserve">25.100679397583</t>
+    <t xml:space="preserve">25.1006774902344</t>
   </si>
   <si>
     <t xml:space="preserve">26.7225685119629</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8384189605713</t>
+    <t xml:space="preserve">26.8384170532227</t>
   </si>
   <si>
     <t xml:space="preserve">24.791748046875</t>
@@ -2336,49 +2336,49 @@
     <t xml:space="preserve">23.8263359069824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.019416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9614925384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4441986083984</t>
+    <t xml:space="preserve">24.0194187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9614944458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4442005157471</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0427570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6220035552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300563812256</t>
+    <t xml:space="preserve">25.0427551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6220016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3943290710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300582885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.8231353759766</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6646461486816</t>
+    <t xml:space="preserve">26.664644241333</t>
   </si>
   <si>
     <t xml:space="preserve">26.645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2398624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7185401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4482288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5833854675293</t>
+    <t xml:space="preserve">26.2398643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.718542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4482269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5833835601807</t>
   </si>
   <si>
     <t xml:space="preserve">26.5487937927246</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">26.4522533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8923168182373</t>
+    <t xml:space="preserve">25.8923149108887</t>
   </si>
   <si>
     <t xml:space="preserve">26.066089630127</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">26.375020980835</t>
+    <t xml:space="preserve">26.3750190734863</t>
   </si>
   <si>
     <t xml:space="preserve">28.0162200927734</t>
@@ -2432,34 +2432,34 @@
     <t xml:space="preserve">25.5254592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4055862426758</t>
+    <t xml:space="preserve">24.4055843353271</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565895080566</t>
+    <t xml:space="preserve">24.6565914154053</t>
   </si>
   <si>
     <t xml:space="preserve">24.2511177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2897338867188</t>
+    <t xml:space="preserve">24.2897357940674</t>
   </si>
   <si>
     <t xml:space="preserve">24.5793571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8496723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3283500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8303623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3862743377686</t>
+    <t xml:space="preserve">24.8496742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3283519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8303642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3862762451172</t>
   </si>
   <si>
     <t xml:space="preserve">23.8842601776123</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">23.1505489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3822460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.073314666748</t>
+    <t xml:space="preserve">23.3822479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0733165740967</t>
   </si>
   <si>
     <t xml:space="preserve">23.7684116363525</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5946388244629</t>
+    <t xml:space="preserve">23.5946369171143</t>
   </si>
   <si>
     <t xml:space="preserve">23.7877197265625</t>
@@ -2501,34 +2501,34 @@
     <t xml:space="preserve">24.2704257965088</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6372833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0813694000244</t>
+    <t xml:space="preserve">24.6372814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.081371307373</t>
   </si>
   <si>
     <t xml:space="preserve">24.3476581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5447654724121</t>
+    <t xml:space="preserve">25.5447673797607</t>
   </si>
   <si>
     <t xml:space="preserve">26.1047077178955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0853996276855</t>
+    <t xml:space="preserve">26.0853977203369</t>
   </si>
   <si>
     <t xml:space="preserve">25.119987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9462146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8110580444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5986633300781</t>
+    <t xml:space="preserve">24.9462127685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.811056137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5986652374268</t>
   </si>
   <si>
     <t xml:space="preserve">24.7338237762451</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269046783447</t>
+    <t xml:space="preserve">24.9269065856934</t>
   </si>
   <si>
     <t xml:space="preserve">26.7611846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2205581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6179752349854</t>
+    <t xml:space="preserve">26.2205543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6179733276367</t>
   </si>
   <si>
     <t xml:space="preserve">24.463508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1392955780029</t>
+    <t xml:space="preserve">25.2358360290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1392974853516</t>
   </si>
   <si>
     <t xml:space="preserve">25.6413078308105</t>
@@ -2570,28 +2570,28 @@
     <t xml:space="preserve">26.7804927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6067180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.046781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2591743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4136371612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8343925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7571601867676</t>
+    <t xml:space="preserve">26.6067199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0467834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2591724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4136390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8343906402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7571582794189</t>
   </si>
   <si>
     <t xml:space="preserve">25.4675331115723</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5600490570068</t>
+    <t xml:space="preserve">24.5600509643555</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689804077148</t>
@@ -2609,10 +2609,10 @@
     <t xml:space="preserve">32.1481781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2061042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8392448425293</t>
+    <t xml:space="preserve">32.2061004638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8392486572266</t>
   </si>
   <si>
     <t xml:space="preserve">31.9743995666504</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">34.175537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1562347412109</t>
+    <t xml:space="preserve">34.1562309265137</t>
   </si>
   <si>
     <t xml:space="preserve">33.9245338439941</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">35.1795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3726463317871</t>
+    <t xml:space="preserve">35.3726501464844</t>
   </si>
   <si>
     <t xml:space="preserve">34.3879280090332</t>
@@ -2654,43 +2654,43 @@
     <t xml:space="preserve">35.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8706398010254</t>
+    <t xml:space="preserve">34.8706359863281</t>
   </si>
   <si>
     <t xml:space="preserve">34.7547874450684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0444107055664</t>
+    <t xml:space="preserve">35.6429595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0444145202637</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.465160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6003227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640228271484</t>
+    <t xml:space="preserve">34.4651641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6003189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640266418457</t>
   </si>
   <si>
     <t xml:space="preserve">32.4957237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0556678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0596885681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5383682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2913856506348</t>
+    <t xml:space="preserve">33.0556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.059684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5383720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542167663574</t>
@@ -2699,19 +2699,19 @@
     <t xml:space="preserve">32.9977378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7314491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3066711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6349067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1908187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591217041016</t>
+    <t xml:space="preserve">33.7314529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3066673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6349105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591255187988</t>
   </si>
   <si>
     <t xml:space="preserve">31.8971748352051</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">32.0709457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">32.437801361084</t>
+    <t xml:space="preserve">32.4377975463867</t>
   </si>
   <si>
     <t xml:space="preserve">33.345287322998</t>
@@ -2735,19 +2735,19 @@
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824562072754</t>
+    <t xml:space="preserve">33.9824600219727</t>
   </si>
   <si>
     <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4458541870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0983047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5962944030762</t>
+    <t xml:space="preserve">34.445858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0983085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5962905883789</t>
   </si>
   <si>
     <t xml:space="preserve">33.0749702453613</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">33.4418258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">32.881893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.611572265625</t>
+    <t xml:space="preserve">32.8818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
     <t xml:space="preserve">34.6775512695312</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">35.8360443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4000129699707</t>
+    <t xml:space="preserve">37.4000091552734</t>
   </si>
   <si>
     <t xml:space="preserve">36.4925270080566</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">37.1490058898926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2994384765625</t>
+    <t xml:space="preserve">36.2994422912598</t>
   </si>
   <si>
     <t xml:space="preserve">36.2801361083984</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">35.6043510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.565731048584</t>
+    <t xml:space="preserve">35.5657348632812</t>
   </si>
   <si>
     <t xml:space="preserve">35.391960144043</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2383155822754</t>
+    <t xml:space="preserve">40.2383232116699</t>
   </si>
   <si>
     <t xml:space="preserve">39.2149848937988</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9527168273926</t>
+    <t xml:space="preserve">40.9527244567871</t>
   </si>
   <si>
     <t xml:space="preserve">41.1458015441895</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">41.5319709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3388862609863</t>
+    <t xml:space="preserve">41.3388900756836</t>
   </si>
   <si>
     <t xml:space="preserve">40.8947982788086</t>
@@ -2864,31 +2864,31 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244812011719</t>
+    <t xml:space="preserve">40.6244850158691</t>
   </si>
   <si>
     <t xml:space="preserve">40.5665588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3429107666016</t>
+    <t xml:space="preserve">42.3429145812988</t>
   </si>
   <si>
     <t xml:space="preserve">42.4780769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0878829956055</t>
+    <t xml:space="preserve">41.0878791809082</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3236045837402</t>
+    <t xml:space="preserve">42.3236083984375</t>
   </si>
   <si>
     <t xml:space="preserve">42.4008331298828</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6711502075195</t>
+    <t xml:space="preserve">42.6711540222168</t>
   </si>
   <si>
     <t xml:space="preserve">42.8256225585938</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">43.9841156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6172523498535</t>
+    <t xml:space="preserve">43.6172561645508</t>
   </si>
   <si>
     <t xml:space="preserve">43.8489532470703</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">45.3743057250977</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3244323730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9600067138672</t>
+    <t xml:space="preserve">47.3244361877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9600105285645</t>
   </si>
   <si>
     <t xml:space="preserve">48.5601577758789</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">48.4636192321777</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2665100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7049713134766</t>
+    <t xml:space="preserve">47.2665138244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7049751281738</t>
   </si>
   <si>
     <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4982070922852</t>
+    <t xml:space="preserve">47.4982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">46.4748687744141</t>
@@ -2945,40 +2945,40 @@
     <t xml:space="preserve">45.8183937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0694046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5521049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1120376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4016647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.01953125</t>
+    <t xml:space="preserve">46.0694007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1120452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4016609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0195350646973</t>
   </si>
   <si>
     <t xml:space="preserve">48.3188056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1876792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9229850769043</t>
+    <t xml:space="preserve">49.1876754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
     <t xml:space="preserve">47.691291809082</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7878341674805</t>
+    <t xml:space="preserve">47.7878303527832</t>
   </si>
   <si>
     <t xml:space="preserve">47.3051223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6140556335449</t>
+    <t xml:space="preserve">47.6140594482422</t>
   </si>
   <si>
     <t xml:space="preserve">48.2705345153809</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.539249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8457565307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2842216491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6221160888672</t>
+    <t xml:space="preserve">50.5392532348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.845760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2842178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6221122741699</t>
   </si>
   <si>
     <t xml:space="preserve">49.6703834533691</t>
@@ -3014,19 +3014,19 @@
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809150695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3807563781738</t>
+    <t xml:space="preserve">47.9809112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3807601928711</t>
   </si>
   <si>
     <t xml:space="preserve">50.0082740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2978973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4909782409668</t>
+    <t xml:space="preserve">50.2978935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4909820556641</t>
   </si>
   <si>
     <t xml:space="preserve">54.4974365234375</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">52.9045066833496</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6768379211426</t>
+    <t xml:space="preserve">53.6768341064453</t>
   </si>
   <si>
     <t xml:space="preserve">53.0975875854492</t>
@@ -3053,31 +3053,31 @@
     <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8562355041504</t>
+    <t xml:space="preserve">52.8562393188477</t>
   </si>
   <si>
     <t xml:space="preserve">52.0356407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6012001037598</t>
+    <t xml:space="preserve">51.601203918457</t>
   </si>
   <si>
     <t xml:space="preserve">47.7105941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6567001342773</t>
+    <t xml:space="preserve">48.6567039489746</t>
   </si>
   <si>
     <t xml:space="preserve">48.0774574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1740036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9616088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9036827087402</t>
+    <t xml:space="preserve">48.173999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9616050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
     <t xml:space="preserve">47.4402847290039</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287742614746</t>
+    <t xml:space="preserve">45.5287704467773</t>
   </si>
   <si>
     <t xml:space="preserve">46.301097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5907211303711</t>
+    <t xml:space="preserve">46.5907173156738</t>
   </si>
   <si>
     <t xml:space="preserve">46.8031158447266</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">47.8071403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6446228027344</t>
+    <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
     <t xml:space="preserve">45.8956260681152</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149360656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3163795471191</t>
+    <t xml:space="preserve">45.9149322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3163757324219</t>
   </si>
   <si>
     <t xml:space="preserve">45.4129219055176</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0388336181641</t>
+    <t xml:space="preserve">48.0388374328613</t>
   </si>
   <si>
     <t xml:space="preserve">48.9945945739746</t>
@@ -3158,25 +3158,25 @@
     <t xml:space="preserve">52.1321792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6977424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1869049072266</t>
+    <t xml:space="preserve">51.6977462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1869087219238</t>
   </si>
   <si>
     <t xml:space="preserve">58.1659965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1450843811035</t>
+    <t xml:space="preserve">60.1450881958008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6277923583984</t>
+    <t xml:space="preserve">59.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6277961730957</t>
   </si>
   <si>
     <t xml:space="preserve">61.255313873291</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">58.0211868286133</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0694580078125</t>
+    <t xml:space="preserve">58.0694541931152</t>
   </si>
   <si>
     <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8490104675293</t>
+    <t xml:space="preserve">55.849006652832</t>
   </si>
   <si>
     <t xml:space="preserve">56.2834434509277</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">53.9664611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7870597839355</t>
+    <t xml:space="preserve">54.7870559692383</t>
   </si>
   <si>
     <t xml:space="preserve">53.5802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0147323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9318695068359</t>
+    <t xml:space="preserve">54.0147285461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9318733215332</t>
   </si>
   <si>
     <t xml:space="preserve">56.4282569885254</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.773380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9801406860352</t>
+    <t xml:space="preserve">53.7733840942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9801445007324</t>
   </si>
   <si>
     <t xml:space="preserve">56.2351722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3453979492188</t>
+    <t xml:space="preserve">57.345401763916</t>
   </si>
   <si>
     <t xml:space="preserve">58.5038909912109</t>
@@ -3278,19 +3278,19 @@
     <t xml:space="preserve">58.6969680786133</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0420875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4073486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2214965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0630035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2287216186523</t>
+    <t xml:space="preserve">56.0420913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4073524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.221492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2287178039551</t>
   </si>
   <si>
     <t xml:space="preserve">52.0839080810547</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">53.1458587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4427070617676</t>
+    <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
     <t xml:space="preserve">50.8288764953613</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">50.0565452575684</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2359504699707</t>
+    <t xml:space="preserve">49.2359466552734</t>
   </si>
   <si>
     <t xml:space="preserve">53.483757019043</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1185035705566</t>
+    <t xml:space="preserve">51.1184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">52.3735313415527</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">51.4563941955566</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9254150390625</t>
+    <t xml:space="preserve">50.9254188537598</t>
   </si>
   <si>
     <t xml:space="preserve">50.7806053161621</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">49.7186508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0074501037598</t>
+    <t xml:space="preserve">45.0074462890625</t>
   </si>
   <si>
     <t xml:space="preserve">46.3976440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763198852539</t>
+    <t xml:space="preserve">45.8763160705566</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423477172852</t>
+    <t xml:space="preserve">41.2423439025879</t>
   </si>
   <si>
     <t xml:space="preserve">40.4893264770508</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">42.1498336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5480804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2633094787598</t>
+    <t xml:space="preserve">45.5480766296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8224182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2633056640625</t>
   </si>
   <si>
     <t xml:space="preserve">51.7942848205566</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">51.0219573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">49.911735534668</t>
+    <t xml:space="preserve">49.9117393493652</t>
   </si>
   <si>
     <t xml:space="preserve">46.6486473083496</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">45.2970695495605</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5561332702637</t>
+    <t xml:space="preserve">47.5561294555664</t>
   </si>
   <si>
     <t xml:space="preserve">46.9961929321289</t>
@@ -3416,13 +3416,13 @@
     <t xml:space="preserve">43.675178527832</t>
   </si>
   <si>
-    <t xml:space="preserve">41.647819519043</t>
+    <t xml:space="preserve">41.6478157043457</t>
   </si>
   <si>
     <t xml:space="preserve">42.8063125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1192665100098</t>
+    <t xml:space="preserve">44.1192741394043</t>
   </si>
   <si>
     <t xml:space="preserve">45.6253089904785</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">47.0348129272461</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8376998901367</t>
+    <t xml:space="preserve">45.837703704834</t>
   </si>
   <si>
     <t xml:space="preserve">44.1578903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4627952575684</t>
+    <t xml:space="preserve">43.4627914428711</t>
   </si>
   <si>
     <t xml:space="preserve">44.1254501342773</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">42.3908386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0400199890137</t>
+    <t xml:space="preserve">42.0400161743164</t>
   </si>
   <si>
     <t xml:space="preserve">43.4043235778809</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4312858581543</t>
+    <t xml:space="preserve">46.444766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.431282043457</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070457458496</t>
+    <t xml:space="preserve">41.0070495605469</t>
   </si>
   <si>
     <t xml:space="preserve">38.9995727539062</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">39.1360054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7012138366699</t>
+    <t xml:space="preserve">39.7012176513672</t>
   </si>
   <si>
     <t xml:space="preserve">39.8766212463379</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">40.0325469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3248977661133</t>
+    <t xml:space="preserve">40.324893951416</t>
   </si>
   <si>
     <t xml:space="preserve">40.8706169128418</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646087646484</t>
+    <t xml:space="preserve">41.8646049499512</t>
   </si>
   <si>
     <t xml:space="preserve">42.7806434631348</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2693557739258</t>
+    <t xml:space="preserve">45.4507789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.269359588623</t>
   </si>
   <si>
     <t xml:space="preserve">47.4387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1636276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1381340026855</t>
+    <t xml:space="preserve">49.163631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1381301879883</t>
   </si>
   <si>
     <t xml:space="preserve">50.8202857971191</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">51.2100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7460594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9177284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5511627197266</t>
+    <t xml:space="preserve">51.7460556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9177322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5511589050293</t>
   </si>
   <si>
     <t xml:space="preserve">53.548885345459</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517189025879</t>
+    <t xml:space="preserve">55.3517112731934</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3590,22 +3590,22 @@
     <t xml:space="preserve">54.3772125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9131889343262</t>
+    <t xml:space="preserve">54.9131927490234</t>
   </si>
   <si>
     <t xml:space="preserve">53.7437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1335906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1080894470215</t>
+    <t xml:space="preserve">54.1335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1080932617188</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4491653442383</t>
+    <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
     <t xml:space="preserve">55.4004402160645</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">54.474666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0616416931152</t>
+    <t xml:space="preserve">53.061637878418</t>
   </si>
   <si>
     <t xml:space="preserve">52.5743865966797</t>
@@ -3632,40 +3632,40 @@
     <t xml:space="preserve">50.4792060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7970504760742</t>
+    <t xml:space="preserve">49.7970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
   </si>
   <si>
-    <t xml:space="preserve">50.869010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.771556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0151786804199</t>
+    <t xml:space="preserve">50.8690071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7715530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0151824951172</t>
   </si>
   <si>
     <t xml:space="preserve">51.5024337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0384063720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4537086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5998878479004</t>
+    <t xml:space="preserve">52.0384140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4537124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5998840332031</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3817558288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8480491638184</t>
+    <t xml:space="preserve">50.3817596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8480453491211</t>
   </si>
   <si>
     <t xml:space="preserve">45.8015975952148</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483329772949</t>
+    <t xml:space="preserve">49.7483291625977</t>
   </si>
   <si>
     <t xml:space="preserve">48.4522438049316</t>
   </si>
   <si>
-    <t xml:space="preserve">48.871280670166</t>
+    <t xml:space="preserve">48.8712768554688</t>
   </si>
   <si>
     <t xml:space="preserve">49.3098030090332</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">49.4559783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3029937744141</t>
+    <t xml:space="preserve">55.3029899597168</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242279052734</t>
+    <t xml:space="preserve">60.2242240905762</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4468994140625</t>
+    <t xml:space="preserve">57.4468955993652</t>
   </si>
   <si>
     <t xml:space="preserve">57.1545486450195</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698394775391</t>
+    <t xml:space="preserve">56.5698432922363</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">59.6395263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8599243164062</t>
+    <t xml:space="preserve">58.8599281311035</t>
   </si>
   <si>
     <t xml:space="preserve">59.2497215270996</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">57.9828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4214019775391</t>
+    <t xml:space="preserve">58.4213981628418</t>
   </si>
   <si>
     <t xml:space="preserve">59.6882514953613</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">64.2684020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3194046020508</t>
+    <t xml:space="preserve">62.319408416748</t>
   </si>
   <si>
     <t xml:space="preserve">63.0502815246582</t>
@@ -3794,43 +3794,43 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4842681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1176986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8230819702148</t>
+    <t xml:space="preserve">67.484260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1176910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8230743408203</t>
   </si>
   <si>
     <t xml:space="preserve">70.3590469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9460220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.410041809082</t>
+    <t xml:space="preserve">68.9460296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4100494384766</t>
   </si>
   <si>
     <t xml:space="preserve">67.8740692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3125915527344</t>
+    <t xml:space="preserve">68.3125991821289</t>
   </si>
   <si>
     <t xml:space="preserve">67.1919097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8972854614258</t>
+    <t xml:space="preserve">68.8972930908203</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4865417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5817184448242</t>
+    <t xml:space="preserve">65.4865341186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5817108154297</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3848,28 +3848,28 @@
     <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8995666503906</t>
+    <t xml:space="preserve">66.8995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584869384766</t>
+    <t xml:space="preserve">66.5584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0434722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6513977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7233505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4310073852539</t>
+    <t xml:space="preserve">69.0434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6514053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7233428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4309997558594</t>
   </si>
   <si>
     <t xml:space="preserve">71.528450012207</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">72.6978530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6700897216797</t>
+    <t xml:space="preserve">75.6700820922852</t>
   </si>
   <si>
     <t xml:space="preserve">75.0366516113281</t>
@@ -3890,13 +3890,13 @@
     <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7188034057617</t>
+    <t xml:space="preserve">75.7188110351562</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">76.839485168457</t>
+    <t xml:space="preserve">76.8394775390625</t>
   </si>
   <si>
     <t xml:space="preserve">77.2780151367188</t>
@@ -3911,49 +3911,49 @@
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627090454102</t>
+    <t xml:space="preserve">77.8627166748047</t>
   </si>
   <si>
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.5703582763672</t>
+    <t xml:space="preserve">78.8859329223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.5703659057617</t>
   </si>
   <si>
     <t xml:space="preserve">77.1805572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">78.1550598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0088958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.4241790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6678085327148</t>
+    <t xml:space="preserve">78.1550674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0088882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.424186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0831069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6678161621094</t>
   </si>
   <si>
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0321197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4474182128906</t>
+    <t xml:space="preserve">78.3012466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.032112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4474105834961</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
@@ -3962,16 +3962,16 @@
     <t xml:space="preserve">77.4729080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">73.964714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.9601593017578</t>
+    <t xml:space="preserve">73.9647064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.82080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.9601669311523</t>
   </si>
   <si>
     <t xml:space="preserve">75.8162612915039</t>
@@ -3983,25 +3983,25 @@
     <t xml:space="preserve">80.3964157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">80.2989654541016</t>
+    <t xml:space="preserve">80.2989730834961</t>
   </si>
   <si>
     <t xml:space="preserve">81.7119979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">81.468376159668</t>
+    <t xml:space="preserve">81.4683685302734</t>
   </si>
   <si>
     <t xml:space="preserve">81.8581695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7607192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2689361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1924438476562</t>
+    <t xml:space="preserve">81.7607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.268928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1924362182617</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
@@ -4022,28 +4022,28 @@
     <t xml:space="preserve">86.3408737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2434234619141</t>
+    <t xml:space="preserve">86.2434310913086</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2876205444336</t>
+    <t xml:space="preserve">90.2876129150391</t>
   </si>
   <si>
     <t xml:space="preserve">87.8513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3618316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0972595214844</t>
+    <t xml:space="preserve">89.3618392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360580444336</t>
+    <t xml:space="preserve">88.4360656738281</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1017913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1250305175781</t>
+    <t xml:space="preserve">82.1017990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1250228881836</t>
   </si>
   <si>
     <t xml:space="preserve">85.6100082397461</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6887741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0043411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4196548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2270278930664</t>
+    <t xml:space="preserve">80.6887664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0043563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4196472167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2270202636719</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
@@ -4082,22 +4082,22 @@
     <t xml:space="preserve">79.9091720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5299377441406</t>
+    <t xml:space="preserve">81.5299453735352</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096420288086</t>
+    <t xml:space="preserve">77.1096496582031</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6322021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830764770508</t>
+    <t xml:space="preserve">78.632194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830841064453</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618255615234</t>
+    <t xml:space="preserve">79.7618179321289</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370315551758</t>
+    <t xml:space="preserve">81.1370239257812</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909790039062</t>
+    <t xml:space="preserve">83.6909713745117</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6281661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317092895508</t>
+    <t xml:space="preserve">81.628173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317169189453</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0742263793945</t>
+    <t xml:space="preserve">79.07421875</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4184,22 +4184,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.926872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326721191406</t>
+    <t xml:space="preserve">78.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0959548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326644897461</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853332519531</t>
+    <t xml:space="preserve">75.6853256225586</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928894042969</t>
+    <t xml:space="preserve">72.4928970336914</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870971679688</t>
+    <t xml:space="preserve">75.5870895385742</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402359008789</t>
+    <t xml:space="preserve">72.6402282714844</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176834106445</t>
+    <t xml:space="preserve">71.1176910400391</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597152709961</t>
+    <t xml:space="preserve">71.5597076416016</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3946533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022171020508</t>
+    <t xml:space="preserve">72.394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022247314453</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212188720703</t>
+    <t xml:space="preserve">70.9212265014648</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4295,16 +4295,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5420074462891</t>
+    <t xml:space="preserve">72.5419998168945</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389419555664</t>
+    <t xml:space="preserve">73.4260635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389343261719</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8270263671875</t>
+    <t xml:space="preserve">67.827018737793</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247772216797</t>
+    <t xml:space="preserve">70.7247695922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.546028137207</t>
+    <t xml:space="preserve">69.5460205078125</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698669433594</t>
+    <t xml:space="preserve">73.7698593139648</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4361,19 +4361,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065765380859</t>
+    <t xml:space="preserve">77.6007843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481384277344</t>
+    <t xml:space="preserve">77.7481307983398</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4394,25 +4394,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273498535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238067626953</t>
+    <t xml:space="preserve">75.9309005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238143920898</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344436645508</t>
+    <t xml:space="preserve">75.7344360351562</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9051513671875</t>
+    <t xml:space="preserve">82.905143737793</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046661376953</t>
+    <t xml:space="preserve">85.7046737670898</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851867675781</t>
+    <t xml:space="preserve">86.7851791381836</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542617797852</t>
+    <t xml:space="preserve">82.9542541503906</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489547729492</t>
+    <t xml:space="preserve">83.2489471435547</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4484,16 +4484,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312316894531</t>
+    <t xml:space="preserve">84.2312393188477</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507263183594</t>
+    <t xml:space="preserve">82.5613555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507186889648</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338195800781</t>
+    <t xml:space="preserve">89.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581436157227</t>
+    <t xml:space="preserve">91.0581359863281</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8576736450195</t>
+    <t xml:space="preserve">93.857666015625</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4547,16 +4547,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747367858887</t>
+    <t xml:space="preserve">102.845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747375488281</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.82788848877</t>
+    <t xml:space="preserve">103.827896118164</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034019470215</t>
+    <t xml:space="preserve">109.034027099609</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525161743164</t>
+    <t xml:space="preserve">109.525169372559</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.63143157959</t>
+    <t xml:space="preserve">103.631439208984</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4625,16 +4625,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.158004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122581481934</t>
+    <t xml:space="preserve">102.157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122573852539</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987350463867</t>
+    <t xml:space="preserve">99.8987426757812</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3625030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518737792969</t>
+    <t xml:space="preserve">96.3624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518661499023</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.264274597168</t>
+    <t xml:space="preserve">96.2642669677734</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.558967590332</t>
+    <t xml:space="preserve">96.5589599609375</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4697,16 +4697,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890686035156</t>
+    <t xml:space="preserve">94.8890609741211</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488159179688</t>
+    <t xml:space="preserve">94.7417221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488082885742</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5652,6 +5652,9 @@
   </si>
   <si>
     <t xml:space="preserve">90.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.6399993896484</t>
   </si>
 </sst>
 </file>
@@ -70938,7 +70941,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.693587963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>310749</v>
@@ -70959,6 +70962,32 @@
         <v>1879</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.69125</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>410982</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>91.3000030517578</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>88.5800018310547</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>90.1999969482422</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>88.6399993896484</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1880</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="1882">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537845611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801054000854</t>
+    <t xml:space="preserve">14.8537864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801063537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.171820640564</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289255142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022022247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389188766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0877418518066</t>
+    <t xml:space="preserve">13.9289274215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406255722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208856582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022012710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.087742805481</t>
   </si>
   <si>
     <t xml:space="preserve">14.0410318374634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3212919235229</t>
+    <t xml:space="preserve">14.3212909698486</t>
   </si>
   <si>
     <t xml:space="preserve">14.33997631073</t>
@@ -89,58 +89,58 @@
     <t xml:space="preserve">14.7697086334229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3866863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240550994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849815368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.003662109375</t>
+    <t xml:space="preserve">14.3866853713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240531921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036640167236</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338006973267</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7051258087158</t>
+    <t xml:space="preserve">12.7051248550415</t>
   </si>
   <si>
     <t xml:space="preserve">12.4155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061822891235</t>
+    <t xml:space="preserve">12.4061813354492</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645895004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195852279663</t>
+    <t xml:space="preserve">13.5459070205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0316905975342</t>
@@ -152,49 +152,49 @@
     <t xml:space="preserve">13.8355083465576</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372150421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.255898475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011457443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060190200806</t>
+    <t xml:space="preserve">14.106427192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372121810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.601146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060199737549</t>
   </si>
   <si>
     <t xml:space="preserve">15.3769388198853</t>
   </si>
   <si>
-    <t xml:space="preserve">15.479700088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
+    <t xml:space="preserve">15.4797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385145187378</t>
   </si>
   <si>
     <t xml:space="preserve">15.5450925827026</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945667266846</t>
+    <t xml:space="preserve">15.6945648193359</t>
   </si>
   <si>
     <t xml:space="preserve">15.6104879379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983825683594</t>
+    <t xml:space="preserve">15.4983863830566</t>
   </si>
   <si>
     <t xml:space="preserve">15.0873365402222</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">14.9939155578613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6202354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527299880981</t>
+    <t xml:space="preserve">14.6202344894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527309417725</t>
   </si>
   <si>
     <t xml:space="preserve">15.3302278518677</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">15.7225904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7412738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253555297852</t>
+    <t xml:space="preserve">15.7412748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253536224365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3017959594727</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">16.3485088348389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550830841064</t>
+    <t xml:space="preserve">16.2550868988037</t>
   </si>
   <si>
     <t xml:space="preserve">16.4139022827148</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">16.2924556732178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3671932220459</t>
+    <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215358734131</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">16.3765316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391647338867</t>
+    <t xml:space="preserve">16.3391628265381</t>
   </si>
   <si>
     <t xml:space="preserve">16.1149559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2737712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4419250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889869689941</t>
+    <t xml:space="preserve">16.2737693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4419269561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889850616455</t>
   </si>
   <si>
     <t xml:space="preserve">16.648983001709</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207447052002</t>
+    <t xml:space="preserve">16.6207427978516</t>
   </si>
   <si>
     <t xml:space="preserve">16.6019229888916</t>
@@ -299,85 +299,85 @@
     <t xml:space="preserve">16.6866245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054500579834</t>
+    <t xml:space="preserve">16.7054481506348</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995662689209</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5454559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8278007507324</t>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8277969360352</t>
   </si>
   <si>
     <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725408554077</t>
+    <t xml:space="preserve">16.2254638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725427627563</t>
   </si>
   <si>
     <t xml:space="preserve">15.7078275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3407783508301</t>
+    <t xml:space="preserve">15.3407793045044</t>
   </si>
   <si>
     <t xml:space="preserve">16.583101272583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2536964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642757415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796148300171</t>
+    <t xml:space="preserve">16.6113338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.253698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796157836914</t>
   </si>
   <si>
     <t xml:space="preserve">15.0678462982178</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2748975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090177536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101861953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854995727539</t>
+    <t xml:space="preserve">15.2748985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854986190796</t>
   </si>
   <si>
     <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443271636963</t>
+    <t xml:space="preserve">14.644326210022</t>
   </si>
   <si>
     <t xml:space="preserve">14.9172620773315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384197235107</t>
+    <t xml:space="preserve">15.5384216308594</t>
   </si>
   <si>
     <t xml:space="preserve">15.6513595581055</t>
@@ -389,37 +389,37 @@
     <t xml:space="preserve">15.4348945617676</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854768753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054698944092</t>
+    <t xml:space="preserve">15.5854787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054689407349</t>
   </si>
   <si>
     <t xml:space="preserve">15.8301782608032</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9901723861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925310134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478315353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337034225464</t>
+    <t xml:space="preserve">15.990177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.933705329895</t>
   </si>
   <si>
     <t xml:space="preserve">15.6701822280884</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3784246444702</t>
+    <t xml:space="preserve">15.3784236907959</t>
   </si>
   <si>
     <t xml:space="preserve">15.5007753372192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6419496536255</t>
+    <t xml:space="preserve">15.6419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148817062378</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2725200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3195781707764</t>
+    <t xml:space="preserve">16.2725219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.319580078125</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819309234619</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">16.1595802307129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760433197021</t>
+    <t xml:space="preserve">16.3760452270508</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.460750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078105926514</t>
+    <t xml:space="preserve">16.4607486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078086853027</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301574707031</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">16.8560352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.98779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.931324005127</t>
+    <t xml:space="preserve">16.9877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0160274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
     <t xml:space="preserve">16.978385925293</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">16.846622467041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960391998291</t>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960372924805</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
@@ -497,58 +497,58 @@
     <t xml:space="preserve">16.7713298797607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8089771270752</t>
+    <t xml:space="preserve">16.8089809417725</t>
   </si>
   <si>
     <t xml:space="preserve">16.4231033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8842678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525081634521</t>
+    <t xml:space="preserve">16.8842697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525043487549</t>
   </si>
   <si>
     <t xml:space="preserve">16.9030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0066165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9972057342529</t>
+    <t xml:space="preserve">17.0066184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9972076416016</t>
   </si>
   <si>
     <t xml:space="preserve">17.0536766052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748588562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0348529815674</t>
+    <t xml:space="preserve">16.8748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0348510742188</t>
   </si>
   <si>
     <t xml:space="preserve">16.8654441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7619190216064</t>
+    <t xml:space="preserve">16.7619209289551</t>
   </si>
   <si>
     <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289672851562</t>
+    <t xml:space="preserve">17.2324962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289691925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136745452881</t>
+    <t xml:space="preserve">17.2136726379395</t>
   </si>
   <si>
     <t xml:space="preserve">17.3548431396484</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">17.3642559051514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3077850341797</t>
+    <t xml:space="preserve">17.3077869415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.298376083374</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">17.6936569213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8724765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.738338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230419158936</t>
+    <t xml:space="preserve">17.8724784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7383365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230438232422</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818695068359</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">18.8042182922363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3406734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3783226013184</t>
+    <t xml:space="preserve">19.1430339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3406753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783206939697</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183227539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5571403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4159641265869</t>
+    <t xml:space="preserve">19.2183246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5571422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4159660339355</t>
   </si>
   <si>
     <t xml:space="preserve">20.2724170684814</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4982929229736</t>
+    <t xml:space="preserve">20.498291015625</t>
   </si>
   <si>
     <t xml:space="preserve">20.3571186065674</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">20.8935775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676959991455</t>
+    <t xml:space="preserve">20.6676979064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.6959362030029</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7453727722168</t>
+    <t xml:space="preserve">19.7453708648682</t>
   </si>
   <si>
     <t xml:space="preserve">19.5194931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6889038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171382904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.84889793396</t>
+    <t xml:space="preserve">19.6889057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8488960266113</t>
   </si>
   <si>
     <t xml:space="preserve">19.5759620666504</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">19.2747955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3877334594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3500862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959739685059</t>
+    <t xml:space="preserve">19.4442043304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.387731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3500881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3971462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959758758545</t>
   </si>
   <si>
     <t xml:space="preserve">19.001859664917</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">19.1053886413574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9171562194824</t>
+    <t xml:space="preserve">18.9171581268311</t>
   </si>
   <si>
     <t xml:space="preserve">19.0865650177002</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.352466583252</t>
+    <t xml:space="preserve">18.4936408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524646759033</t>
   </si>
   <si>
     <t xml:space="preserve">18.2865867614746</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">18.6254024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2559700012207</t>
+    <t xml:space="preserve">19.2559680938721</t>
   </si>
   <si>
     <t xml:space="preserve">19.5100803375244</t>
@@ -713,31 +713,31 @@
     <t xml:space="preserve">19.2371482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5006694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
+    <t xml:space="preserve">19.5006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924289703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018218994141</t>
   </si>
   <si>
     <t xml:space="preserve">20.7335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218101501465</t>
+    <t xml:space="preserve">20.7994632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218120574951</t>
   </si>
   <si>
     <t xml:space="preserve">21.3641529083252</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853332519531</t>
+    <t xml:space="preserve">21.1853351593018</t>
   </si>
   <si>
     <t xml:space="preserve">21.015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029884338379</t>
+    <t xml:space="preserve">20.902982711792</t>
   </si>
   <si>
     <t xml:space="preserve">21.0253391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9876899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947479248047</t>
+    <t xml:space="preserve">20.9876918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947441101074</t>
   </si>
   <si>
     <t xml:space="preserve">21.279447555542</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">21.1100406646729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6088542938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2135677337646</t>
+    <t xml:space="preserve">21.4112091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6088523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2135696411133</t>
   </si>
   <si>
     <t xml:space="preserve">21.3829746246338</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">21.5429706573486</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8347320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0229606628418</t>
+    <t xml:space="preserve">21.8347282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
     <t xml:space="preserve">21.8064937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0417823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817646026611</t>
+    <t xml:space="preserve">22.041784286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582454681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817665100098</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476463317871</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">23.0394020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7288208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0582275390625</t>
+    <t xml:space="preserve">22.7288227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
     <t xml:space="preserve">22.5876502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3711853027344</t>
+    <t xml:space="preserve">22.371187210083</t>
   </si>
   <si>
     <t xml:space="preserve">22.0135459899902</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">21.3076820373535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1170749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0981216430664</t>
+    <t xml:space="preserve">22.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.098123550415</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
@@ -851,61 +851,61 @@
     <t xml:space="preserve">22.1549777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2686920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0507411956787</t>
+    <t xml:space="preserve">22.2686901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0507431030273</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0886478424072</t>
+    <t xml:space="preserve">22.08864402771</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8327960968018</t>
+    <t xml:space="preserve">21.8327941894531</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.576940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7285594940186</t>
+    <t xml:space="preserve">21.5769424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7285575866699</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380352020264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579891204834</t>
+    <t xml:space="preserve">21.5579872131348</t>
   </si>
   <si>
     <t xml:space="preserve">21.5200824737549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1315631866455</t>
+    <t xml:space="preserve">21.1315650939941</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.463228225708</t>
+    <t xml:space="preserve">21.8612232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4632263183594</t>
   </si>
   <si>
     <t xml:space="preserve">21.662223815918</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5674648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5624504089355</t>
+    <t xml:space="preserve">21.5674667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
     <t xml:space="preserve">22.4013538360596</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5908756256104</t>
+    <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
     <t xml:space="preserve">21.7948875427246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8138446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422660827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6717014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3255481719971</t>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.671703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4676876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3255500793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.5055904388428</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8277797698975</t>
+    <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.036247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2068176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2162914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.998348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1310081481934</t>
+    <t xml:space="preserve">23.2068157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2162952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9983463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.131010055542</t>
   </si>
   <si>
     <t xml:space="preserve">23.5005760192871</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">23.6900959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2731513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404876708984</t>
+    <t xml:space="preserve">23.2731494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404857635498</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4531955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7709217071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.950963973999</t>
+    <t xml:space="preserve">23.453197479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7709197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9509658813477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0646781921387</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7519683837891</t>
+    <t xml:space="preserve">22.7519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.7235412597656</t>
@@ -1004,55 +1004,55 @@
     <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6477355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4771633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1834087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8796157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1165199279785</t>
+    <t xml:space="preserve">22.6477317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.477165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.183406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8796195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1165180206299</t>
   </si>
   <si>
     <t xml:space="preserve">23.6616668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3868637084961</t>
+    <t xml:space="preserve">23.3868656158447</t>
   </si>
   <si>
     <t xml:space="preserve">23.1783905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9035873413086</t>
+    <t xml:space="preserve">22.90358543396</t>
   </si>
   <si>
     <t xml:space="preserve">24.0217590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955596923828</t>
+    <t xml:space="preserve">24.4955615997314</t>
   </si>
   <si>
     <t xml:space="preserve">24.5145149230957</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6850814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903205871582</t>
+    <t xml:space="preserve">24.6377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6850776672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903186798096</t>
   </si>
   <si>
     <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8082695007324</t>
+    <t xml:space="preserve">24.8082714080811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1639003753662</t>
+    <t xml:space="preserve">24.5429382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
     <t xml:space="preserve">24.8651256561279</t>
@@ -1076,52 +1076,52 @@
     <t xml:space="preserve">25.7653484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5474014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915458679199</t>
+    <t xml:space="preserve">25.5474033355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
   </si>
   <si>
     <t xml:space="preserve">25.4052600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4431667327881</t>
+    <t xml:space="preserve">25.4431648254395</t>
   </si>
   <si>
     <t xml:space="preserve">25.4905452728271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3863086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3294525146484</t>
+    <t xml:space="preserve">25.3863105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3484020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3294506072998</t>
   </si>
   <si>
     <t xml:space="preserve">25.0830745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.727445602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6611137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645706176758</t>
+    <t xml:space="preserve">25.7274475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.661111831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645687103271</t>
   </si>
   <si>
     <t xml:space="preserve">27.309944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119491577148</t>
+    <t xml:space="preserve">26.9119472503662</t>
   </si>
   <si>
     <t xml:space="preserve">27.0635662078857</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">26.675048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9972324371338</t>
+    <t xml:space="preserve">26.9972362518311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1678047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4665775299072</t>
+    <t xml:space="preserve">26.4665794372559</t>
   </si>
   <si>
     <t xml:space="preserve">26.0591087341309</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">25.0451698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1778354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1967849731445</t>
+    <t xml:space="preserve">25.1778335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
     <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.111499786377</t>
+    <t xml:space="preserve">25.1115016937256</t>
   </si>
   <si>
     <t xml:space="preserve">25.5379257202148</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">25.301025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2631206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9219799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2062606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042575836182</t>
+    <t xml:space="preserve">25.2631187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9219818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.206262588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042556762695</t>
   </si>
   <si>
     <t xml:space="preserve">25.8601093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3339138031006</t>
+    <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
     <t xml:space="preserve">26.248628616333</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">26.4381465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7987937927246</t>
+    <t xml:space="preserve">24.7987957000732</t>
   </si>
   <si>
     <t xml:space="preserve">25.3673553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3578815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800651550293</t>
+    <t xml:space="preserve">25.3578796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800670623779</t>
   </si>
   <si>
     <t xml:space="preserve">25.6232089996338</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">25.7748260498047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5947799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7084922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1064853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8171901702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0540904998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3857517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695831298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222045898438</t>
+    <t xml:space="preserve">25.5947818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7084903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1064872741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8171882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222064971924</t>
   </si>
   <si>
     <t xml:space="preserve">25.9169673919678</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">25.6326866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7324638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9743804931641</t>
+    <t xml:space="preserve">24.7324600219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008007049561</t>
@@ -1262,28 +1262,28 @@
     <t xml:space="preserve">24.0691394805908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4481792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.827220916748</t>
+    <t xml:space="preserve">24.4481773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2586612701416</t>
+    <t xml:space="preserve">24.2586574554443</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167407989502</t>
+    <t xml:space="preserve">25.0167388916016</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693622589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9269962310791</t>
+    <t xml:space="preserve">23.9269981384277</t>
   </si>
   <si>
     <t xml:space="preserve">26.3433876037598</t>
@@ -1292,19 +1292,19 @@
     <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0117263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1538677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4855270385742</t>
+    <t xml:space="preserve">26.0117282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4855289459229</t>
   </si>
   <si>
     <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9593334197998</t>
+    <t xml:space="preserve">26.9593315124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698097229004</t>
@@ -1313,28 +1313,28 @@
     <t xml:space="preserve">28.9492969512939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.617639541626</t>
+    <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
     <t xml:space="preserve">28.8071594238281</t>
   </si>
   <si>
-    <t xml:space="preserve">28.665018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3283405303955</t>
+    <t xml:space="preserve">28.6650161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3283386230469</t>
   </si>
   <si>
     <t xml:space="preserve">29.2335815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5394897460938</t>
+    <t xml:space="preserve">29.5394916534424</t>
   </si>
   <si>
     <t xml:space="preserve">30.2086696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0652751922607</t>
+    <t xml:space="preserve">30.0652770996094</t>
   </si>
   <si>
     <t xml:space="preserve">30.3042678833008</t>
@@ -1349,82 +1349,82 @@
     <t xml:space="preserve">31.2602367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7419929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.936954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9885215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7532997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2275161743164</t>
+    <t xml:space="preserve">32.7419967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797142028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.135684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4149436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9369583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9885177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.753303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2275123596191</t>
   </si>
   <si>
     <t xml:space="preserve">35.0841217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6577033996582</t>
+    <t xml:space="preserve">35.6576995849609</t>
   </si>
   <si>
     <t xml:space="preserve">35.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4224815368652</t>
+    <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
     <t xml:space="preserve">36.3746795654297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3268852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4187126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5658798217773</t>
+    <t xml:space="preserve">36.3268814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4187049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5658760070801</t>
   </si>
   <si>
     <t xml:space="preserve">36.8526611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7822551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036312103271</t>
+    <t xml:space="preserve">30.7822532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036331176758</t>
   </si>
   <si>
     <t xml:space="preserve">31.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3558330535889</t>
+    <t xml:space="preserve">31.3558349609375</t>
   </si>
   <si>
     <t xml:space="preserve">31.212438583374</t>
@@ -1436,34 +1436,34 @@
     <t xml:space="preserve">33.7935600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9847526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7973251342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671417236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6539306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0363235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6061325073242</t>
+    <t xml:space="preserve">33.984748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7973289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.653938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.036319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6061401367188</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413581848145</t>
+    <t xml:space="preserve">33.8413619995117</t>
   </si>
   <si>
     <t xml:space="preserve">34.7495269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5621109008789</t>
+    <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">36.040096282959</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">35.8966941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6614685058594</t>
+    <t xml:space="preserve">36.6614723205566</t>
   </si>
   <si>
     <t xml:space="preserve">39.0035972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3306541442871</t>
+    <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4262504577637</t>
+    <t xml:space="preserve">37.4262542724609</t>
   </si>
   <si>
     <t xml:space="preserve">37.8564300537109</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">37.2350578308105</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8929214477539</t>
+    <t xml:space="preserve">34.8929252624512</t>
   </si>
   <si>
     <t xml:space="preserve">34.5583381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6979598999023</t>
+    <t xml:space="preserve">33.6979675292969</t>
   </si>
   <si>
     <t xml:space="preserve">33.5067672729492</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">33.2677764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9809837341309</t>
+    <t xml:space="preserve">32.2640113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9809875488281</t>
   </si>
   <si>
     <t xml:space="preserve">33.3633728027344</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">32.5985946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5029983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6463928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3596000671387</t>
+    <t xml:space="preserve">32.503002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6463966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3596038818359</t>
   </si>
   <si>
     <t xml:space="preserve">32.072811126709</t>
@@ -1547,34 +1547,34 @@
     <t xml:space="preserve">31.7860240936279</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8338260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357227325439</t>
+    <t xml:space="preserve">31.8338222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.025016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816146850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4401264190674</t>
+    <t xml:space="preserve">27.7709465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
     <t xml:space="preserve">28.248929977417</t>
@@ -1589,25 +1589,25 @@
     <t xml:space="preserve">27.2451610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9621410369873</t>
+    <t xml:space="preserve">27.9621391296387</t>
   </si>
   <si>
     <t xml:space="preserve">28.3445262908936</t>
   </si>
   <si>
-    <t xml:space="preserve">29.013708114624</t>
+    <t xml:space="preserve">29.0137042999268</t>
   </si>
   <si>
     <t xml:space="preserve">28.9181079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2048988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4954586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5872898101807</t>
+    <t xml:space="preserve">29.2049026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5872936248779</t>
   </si>
   <si>
     <t xml:space="preserve">30.7344551086426</t>
@@ -1616,52 +1616,52 @@
     <t xml:space="preserve">30.0174770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4438896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6828842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5835189819336</t>
+    <t xml:space="preserve">29.4438934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6828861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.583517074585</t>
   </si>
   <si>
     <t xml:space="preserve">26.5759811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3847904205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2929573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4363574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6313190460205</t>
+    <t xml:space="preserve">26.3847885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2929611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4363594055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6313209533691</t>
   </si>
   <si>
     <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017665863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8627758026123</t>
+    <t xml:space="preserve">27.1017646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.862771987915</t>
   </si>
   <si>
     <t xml:space="preserve">27.4841556549072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0061702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0979976654053</t>
+    <t xml:space="preserve">27.0061683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0979957580566</t>
   </si>
   <si>
     <t xml:space="preserve">25.6200122833252</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">26.1935920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6237831115723</t>
+    <t xml:space="preserve">26.623779296875</t>
   </si>
   <si>
     <t xml:space="preserve">25.7156085968018</t>
@@ -1685,25 +1685,25 @@
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6791152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1093044281006</t>
+    <t xml:space="preserve">28.9659061431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6791172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1093063354492</t>
   </si>
   <si>
     <t xml:space="preserve">26.6715774536133</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8149719238281</t>
+    <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
     <t xml:space="preserve">26.4803867340088</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3885593414307</t>
+    <t xml:space="preserve">27.388557434082</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
@@ -1715,28 +1715,28 @@
     <t xml:space="preserve">30.1608715057373</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3520660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3080348968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4514312744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4552001953125</t>
+    <t xml:space="preserve">30.3520641326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3080368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4514331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4552040100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.3118057250977</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2162055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6023635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.172176361084</t>
+    <t xml:space="preserve">32.2162094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1721801757812</t>
   </si>
   <si>
     <t xml:space="preserve">33.5545654296875</t>
@@ -1751,49 +1751,49 @@
     <t xml:space="preserve">30.5910587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3004970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.648416519165</t>
+    <t xml:space="preserve">29.3004989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6484203338623</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9734477996826</t>
+    <t xml:space="preserve">30.9734497070312</t>
   </si>
   <si>
     <t xml:space="preserve">30.2851486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0748348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4763412475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2277908325195</t>
+    <t xml:space="preserve">30.0748310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.47633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2277889251709</t>
   </si>
   <si>
     <t xml:space="preserve">29.9983558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8262825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.935209274292</t>
+    <t xml:space="preserve">29.8262844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6675395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.438102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9352073669434</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
@@ -1808,49 +1808,49 @@
     <t xml:space="preserve">29.5203704833984</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4879245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7173557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4821300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1762237548828</t>
+    <t xml:space="preserve">28.487922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.717357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4821319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1762218475342</t>
   </si>
   <si>
     <t xml:space="preserve">29.3291797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5761585235596</t>
+    <t xml:space="preserve">28.5761566162109</t>
   </si>
   <si>
     <t xml:space="preserve">28.9237060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6533908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637676239014</t>
+    <t xml:space="preserve">28.6533889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637657165527</t>
   </si>
   <si>
     <t xml:space="preserve">28.5182342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8038311004639</t>
+    <t xml:space="preserve">27.8038272857666</t>
   </si>
   <si>
     <t xml:space="preserve">28.0741424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1859645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2245826721191</t>
+    <t xml:space="preserve">27.1859664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2245845794678</t>
   </si>
   <si>
     <t xml:space="preserve">27.2052745819092</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">27.3211231231689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5335140228271</t>
+    <t xml:space="preserve">27.5335159301758</t>
   </si>
   <si>
     <t xml:space="preserve">27.6493625640869</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">28.0548324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9969100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4989261627197</t>
+    <t xml:space="preserve">27.9969120025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4989242553711</t>
   </si>
   <si>
     <t xml:space="preserve">28.247917175293</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.900369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0934543609619</t>
+    <t xml:space="preserve">27.9003677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0934524536133</t>
   </si>
   <si>
     <t xml:space="preserve">28.6340808868408</t>
@@ -1907,58 +1907,58 @@
     <t xml:space="preserve">29.1167869567871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8850879669189</t>
+    <t xml:space="preserve">28.8850898742676</t>
   </si>
   <si>
     <t xml:space="preserve">29.2712535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8311901092529</t>
+    <t xml:space="preserve">29.8311920166016</t>
   </si>
   <si>
     <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8505020141602</t>
+    <t xml:space="preserve">29.8504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">29.7539577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2173538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9856548309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6807556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3677940368652</t>
+    <t xml:space="preserve">30.2173557281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9856567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6807537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3677959442139</t>
   </si>
   <si>
     <t xml:space="preserve">29.4836463928223</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1747093200684</t>
+    <t xml:space="preserve">29.1747131347656</t>
   </si>
   <si>
     <t xml:space="preserve">29.4257183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2519454956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.464334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0202465057373</t>
+    <t xml:space="preserve">29.2519435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4643363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0202484130859</t>
   </si>
   <si>
     <t xml:space="preserve">28.9043979644775</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6920070648193</t>
+    <t xml:space="preserve">28.6920051574707</t>
   </si>
   <si>
     <t xml:space="preserve">28.4796161651611</t>
@@ -1967,34 +1967,34 @@
     <t xml:space="preserve">27.7652111053467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1666584014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9542655944824</t>
+    <t xml:space="preserve">27.1666564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1473503112793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.282506942749</t>
+    <t xml:space="preserve">27.2825088500977</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.683952331543</t>
+    <t xml:space="preserve">26.6839542388916</t>
   </si>
   <si>
     <t xml:space="preserve">26.5101795196533</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8810596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1899948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3444576263428</t>
+    <t xml:space="preserve">27.8810634613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1899929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3444595336914</t>
   </si>
   <si>
     <t xml:space="preserve">27.938985824585</t>
@@ -2006,31 +2006,31 @@
     <t xml:space="preserve">27.2631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0314998626709</t>
+    <t xml:space="preserve">27.0315017700195</t>
   </si>
   <si>
     <t xml:space="preserve">26.6260280609131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4176616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0894260406494</t>
+    <t xml:space="preserve">27.4176635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0355281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0894241333008</t>
   </si>
   <si>
     <t xml:space="preserve">26.992883682251</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0508079528809</t>
+    <t xml:space="preserve">27.0508098602295</t>
   </si>
   <si>
     <t xml:space="preserve">27.4755878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7072887420654</t>
+    <t xml:space="preserve">27.7072906494141</t>
   </si>
   <si>
     <t xml:space="preserve">27.5914363861084</t>
@@ -2042,70 +2042,70 @@
     <t xml:space="preserve">27.6879806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.355712890625</t>
+    <t xml:space="preserve">26.3557109832764</t>
   </si>
   <si>
     <t xml:space="preserve">25.9309329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8537006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8730087280273</t>
+    <t xml:space="preserve">25.8536987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
     <t xml:space="preserve">27.301815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4562835693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8577251434326</t>
+    <t xml:space="preserve">27.4562816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8577270507812</t>
   </si>
   <si>
     <t xml:space="preserve">25.7957744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9116230010986</t>
+    <t xml:space="preserve">25.9116249084473</t>
   </si>
   <si>
     <t xml:space="preserve">26.7032604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7459049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1087322235107</t>
+    <t xml:space="preserve">27.7459030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1087341308594</t>
   </si>
   <si>
     <t xml:space="preserve">28.1320686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3830757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9430122375488</t>
+    <t xml:space="preserve">28.3830738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9430141448975</t>
   </si>
   <si>
     <t xml:space="preserve">29.4064102172852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8078556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9816303253174</t>
+    <t xml:space="preserve">28.8078575134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.981632232666</t>
   </si>
   <si>
     <t xml:space="preserve">29.1360969543457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7499332427979</t>
+    <t xml:space="preserve">28.7499313354492</t>
   </si>
   <si>
     <t xml:space="preserve">28.8271656036377</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0009384155273</t>
+    <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
     <t xml:space="preserve">28.5954666137695</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">28.6147727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2133312225342</t>
+    <t xml:space="preserve">29.2133293151855</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9357852935791</t>
+    <t xml:space="preserve">31.935791015625</t>
   </si>
   <si>
     <t xml:space="preserve">32.3026428222656</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">31.8585548400879</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2213802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1827659606934</t>
+    <t xml:space="preserve">31.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.182767868042</t>
   </si>
   <si>
     <t xml:space="preserve">31.6654720306396</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">31.2600002288818</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5882396697998</t>
+    <t xml:space="preserve">31.5882415771484</t>
   </si>
   <si>
     <t xml:space="preserve">31.047607421875</t>
@@ -2156,52 +2156,52 @@
     <t xml:space="preserve">30.9510688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1248435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3565406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8545246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8931446075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8159103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3372325897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4683609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0089931488037</t>
+    <t xml:space="preserve">31.1248455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3565425872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8545265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8931427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8159084320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.337230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4683628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0089912414551</t>
   </si>
   <si>
     <t xml:space="preserve">30.7000598907471</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0170478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3645973205566</t>
+    <t xml:space="preserve">33.0170440673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3645935058594</t>
   </si>
   <si>
     <t xml:space="preserve">33.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8859176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8899459838867</t>
+    <t xml:space="preserve">33.885913848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8899421691895</t>
   </si>
   <si>
     <t xml:space="preserve">35.0251007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9712066650391</t>
+    <t xml:space="preserve">35.9712028503418</t>
   </si>
   <si>
     <t xml:space="preserve">36.5311431884766</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">36.9559211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7008857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8167381286621</t>
+    <t xml:space="preserve">37.2069320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7008895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8167343139648</t>
   </si>
   <si>
     <t xml:space="preserve">34.9864845275879</t>
@@ -2228,55 +2228,55 @@
     <t xml:space="preserve">33.0363578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9205055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6847820281982</t>
+    <t xml:space="preserve">32.9205017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9937076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6847801208496</t>
   </si>
   <si>
     <t xml:space="preserve">31.8778629302979</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3605690002441</t>
+    <t xml:space="preserve">32.3605651855469</t>
   </si>
   <si>
     <t xml:space="preserve">33.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8432731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7427062988281</t>
+    <t xml:space="preserve">32.8432769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7427024841309</t>
   </si>
   <si>
     <t xml:space="preserve">32.8239669799805</t>
   </si>
   <si>
-    <t xml:space="preserve">32.901195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2447242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5343399047852</t>
+    <t xml:space="preserve">32.9011993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2447204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5343437194824</t>
   </si>
   <si>
     <t xml:space="preserve">32.4764175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6928329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3871059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.811882019043</t>
+    <t xml:space="preserve">33.6928367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3871021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8118839263916</t>
   </si>
   <si>
     <t xml:space="preserve">28.9623222351074</t>
@@ -2294,40 +2294,40 @@
     <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784805297852</t>
+    <t xml:space="preserve">26.2784767150879</t>
   </si>
   <si>
     <t xml:space="preserve">25.2937602996826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5407390594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931934356689</t>
+    <t xml:space="preserve">26.1240119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5407409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1931915283203</t>
   </si>
   <si>
     <t xml:space="preserve">22.9767761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2744522094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378482818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1006774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7225685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8384170532227</t>
+    <t xml:space="preserve">25.2744541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.737850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.100679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7225704193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8384189605713</t>
   </si>
   <si>
     <t xml:space="preserve">24.791748046875</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">24.4442005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9075965881348</t>
+    <t xml:space="preserve">24.9075984954834</t>
   </si>
   <si>
     <t xml:space="preserve">25.0427551269531</t>
@@ -2354,40 +2354,40 @@
     <t xml:space="preserve">25.6220016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8231353759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.664644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.645336151123</t>
+    <t xml:space="preserve">26.3943309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.630054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8231372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6646461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6453380584717</t>
   </si>
   <si>
     <t xml:space="preserve">26.2398643493652</t>
   </si>
   <si>
-    <t xml:space="preserve">25.718542098999</t>
+    <t xml:space="preserve">25.7185401916504</t>
   </si>
   <si>
     <t xml:space="preserve">25.4482269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5833835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5487937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9349575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4522533416748</t>
+    <t xml:space="preserve">25.5833854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5487957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9349594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4522514343262</t>
   </si>
   <si>
     <t xml:space="preserve">25.8923149108887</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3750190734863</t>
+    <t xml:space="preserve">26.375020980835</t>
   </si>
   <si>
     <t xml:space="preserve">28.0162200927734</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0242748260498</t>
+    <t xml:space="preserve">30.0242729187012</t>
   </si>
   <si>
     <t xml:space="preserve">32.283332824707</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">25.5061511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903026580811</t>
+    <t xml:space="preserve">25.3903007507324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5254592895508</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565914154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2511177062988</t>
+    <t xml:space="preserve">24.6565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2511196136475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2897357940674</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">24.5793571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8496742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3283519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8303642272949</t>
+    <t xml:space="preserve">24.8496723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3283500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8303623199463</t>
   </si>
   <si>
     <t xml:space="preserve">24.3862762451172</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">23.9421844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1352672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.154577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0387287139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035701751709</t>
+    <t xml:space="preserve">24.1352691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1545753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.038724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035682678223</t>
   </si>
   <si>
     <t xml:space="preserve">23.1505489349365</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">23.7877197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2704257965088</t>
+    <t xml:space="preserve">24.2704277038574</t>
   </si>
   <si>
     <t xml:space="preserve">24.6372814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">25.081371307373</t>
+    <t xml:space="preserve">25.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">24.3476581573486</t>
@@ -2513,55 +2513,55 @@
     <t xml:space="preserve">25.5447673797607</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1047077178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0853977203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.119987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9462127685547</t>
+    <t xml:space="preserve">26.1047039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0853996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1199893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">24.811056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5986652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7338237762451</t>
+    <t xml:space="preserve">24.5986671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7338256835938</t>
   </si>
   <si>
     <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269065856934</t>
+    <t xml:space="preserve">24.9269046783447</t>
   </si>
   <si>
     <t xml:space="preserve">26.7611846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2205543518066</t>
+    <t xml:space="preserve">26.2205562591553</t>
   </si>
   <si>
     <t xml:space="preserve">24.6179733276367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.463508605957</t>
+    <t xml:space="preserve">24.4635105133057</t>
   </si>
   <si>
     <t xml:space="preserve">25.2358360290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1392974853516</t>
+    <t xml:space="preserve">25.1392955780029</t>
   </si>
   <si>
     <t xml:space="preserve">25.6413078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3130702972412</t>
+    <t xml:space="preserve">25.3130683898926</t>
   </si>
   <si>
     <t xml:space="preserve">26.2977867126465</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">26.6067199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0467834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2591724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4136390686035</t>
+    <t xml:space="preserve">26.046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2591705322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4136371612549</t>
   </si>
   <si>
     <t xml:space="preserve">25.8343906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7571582794189</t>
+    <t xml:space="preserve">25.7571601867676</t>
   </si>
   <si>
     <t xml:space="preserve">25.4675331115723</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">24.8689804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7724380493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1401233673096</t>
+    <t xml:space="preserve">24.772439956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1401214599609</t>
   </si>
   <si>
     <t xml:space="preserve">31.7620143890381</t>
@@ -2609,25 +2609,25 @@
     <t xml:space="preserve">32.1481781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2061004638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8392486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9743995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9550933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2680549621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.175537109375</t>
+    <t xml:space="preserve">32.2061042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8392467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9744071960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3798789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2680511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1755409240723</t>
   </si>
   <si>
     <t xml:space="preserve">34.1562309265137</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">33.9245338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1795654296875</t>
+    <t xml:space="preserve">35.1795692443848</t>
   </si>
   <si>
     <t xml:space="preserve">35.3726501464844</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5810089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2761116027832</t>
+    <t xml:space="preserve">34.5810127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2761077880859</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8706359863281</t>
+    <t xml:space="preserve">34.8706398010254</t>
   </si>
   <si>
     <t xml:space="preserve">34.7547874450684</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">35.6429595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0444145202637</t>
+    <t xml:space="preserve">35.0444068908691</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
@@ -2672,52 +2672,52 @@
     <t xml:space="preserve">34.4651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6003189086914</t>
+    <t xml:space="preserve">34.6003265380859</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4957237243652</t>
+    <t xml:space="preserve">32.4957275390625</t>
   </si>
   <si>
     <t xml:space="preserve">33.0556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.059684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5383720397949</t>
+    <t xml:space="preserve">34.0596885681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5383682250977</t>
   </si>
   <si>
     <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6542167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9977378845215</t>
+    <t xml:space="preserve">33.6542205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9977416992188</t>
   </si>
   <si>
     <t xml:space="preserve">33.7314529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3066673278809</t>
+    <t xml:space="preserve">33.3066711425781</t>
   </si>
   <si>
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591255187988</t>
+    <t xml:space="preserve">33.1908187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591217041016</t>
   </si>
   <si>
     <t xml:space="preserve">31.8971748352051</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0709457397461</t>
+    <t xml:space="preserve">32.0709419250488</t>
   </si>
   <si>
     <t xml:space="preserve">32.4377975463867</t>
@@ -2726,31 +2726,31 @@
     <t xml:space="preserve">33.345287322998</t>
   </si>
   <si>
-    <t xml:space="preserve">33.210132598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7893753051758</t>
+    <t xml:space="preserve">33.2101287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7893714904785</t>
   </si>
   <si>
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824600219727</t>
+    <t xml:space="preserve">33.9824562072754</t>
   </si>
   <si>
     <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">34.445858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0983085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5962905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0749702453613</t>
+    <t xml:space="preserve">34.4458541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0983047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5962944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0749740600586</t>
   </si>
   <si>
     <t xml:space="preserve">32.939811706543</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">32.8818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6115760803223</t>
+    <t xml:space="preserve">32.611572265625</t>
   </si>
   <si>
     <t xml:space="preserve">34.6775512695312</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">37.5351715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8360443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4000091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4925270080566</t>
+    <t xml:space="preserve">35.8360481262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4000129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">37.1490058898926</t>
@@ -2789,22 +2789,22 @@
     <t xml:space="preserve">36.2801361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7201957702637</t>
+    <t xml:space="preserve">35.7201995849609</t>
   </si>
   <si>
     <t xml:space="preserve">35.6043510437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5657348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.391960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4346046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6510200500488</t>
+    <t xml:space="preserve">35.565731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3919563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4346008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6510162353516</t>
   </si>
   <si>
     <t xml:space="preserve">37.0331573486328</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5158576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.519889831543</t>
+    <t xml:space="preserve">37.5158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198936462402</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
@@ -2831,19 +2831,19 @@
     <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2383232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9527244567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1458015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7057418823242</t>
+    <t xml:space="preserve">40.2383193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2149810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9527206420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7057456970215</t>
   </si>
   <si>
     <t xml:space="preserve">42.4587631225586</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">41.5319709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3388900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8947982788086</t>
+    <t xml:space="preserve">41.3388824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8948020935059</t>
   </si>
   <si>
     <t xml:space="preserve">40.701717376709</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">40.5665588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3429145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878791809082</t>
+    <t xml:space="preserve">42.3429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">42.3236083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4008331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6711540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256225585938</t>
+    <t xml:space="preserve">42.4008369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6711578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256187438965</t>
   </si>
   <si>
     <t xml:space="preserve">43.8875694274902</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">43.6172561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8489532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3743057250977</t>
+    <t xml:space="preserve">43.8489570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3743019104004</t>
   </si>
   <si>
     <t xml:space="preserve">47.3244361877441</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">49.7669258117676</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9600105285645</t>
+    <t xml:space="preserve">49.9600028991699</t>
   </si>
   <si>
     <t xml:space="preserve">48.5601577758789</t>
@@ -2927,19 +2927,19 @@
     <t xml:space="preserve">48.4636192321777</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2665138244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7049751281738</t>
+    <t xml:space="preserve">47.2665100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7049674987793</t>
   </si>
   <si>
     <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4982109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4748687744141</t>
+    <t xml:space="preserve">47.4982070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4748764038086</t>
   </si>
   <si>
     <t xml:space="preserve">45.8183937072754</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">46.5521087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1120452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4016609191895</t>
+    <t xml:space="preserve">47.1120414733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.401668548584</t>
   </si>
   <si>
     <t xml:space="preserve">48.0195350646973</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3188056945801</t>
+    <t xml:space="preserve">48.3188095092773</t>
   </si>
   <si>
     <t xml:space="preserve">49.1876754760742</t>
@@ -2975,46 +2975,46 @@
     <t xml:space="preserve">47.7878303527832</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3051223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6140594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2705345153809</t>
+    <t xml:space="preserve">47.3051261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6140556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2705383300781</t>
   </si>
   <si>
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5392532348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.845760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2842178344727</t>
+    <t xml:space="preserve">50.539249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8457565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2842140197754</t>
   </si>
   <si>
     <t xml:space="preserve">49.6221122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6703834533691</t>
+    <t xml:space="preserve">49.6703872680664</t>
   </si>
   <si>
     <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9422950744629</t>
+    <t xml:space="preserve">47.4209747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9422988891602</t>
   </si>
   <si>
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809112548828</t>
+    <t xml:space="preserve">47.9809150695801</t>
   </si>
   <si>
     <t xml:space="preserve">49.3807601928711</t>
@@ -3023,55 +3023,55 @@
     <t xml:space="preserve">50.0082740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2978935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4974365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8699150085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3252639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9527778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9045066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6768341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0975875854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.001049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8562393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0356407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.601203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7105941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0774574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.173999786377</t>
+    <t xml:space="preserve">50.2978973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4909782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4974403381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8699188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3252601623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9527740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6768379211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0975914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0010528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8562355041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0356369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7105979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6567001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.077449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1739959716797</t>
   </si>
   <si>
     <t xml:space="preserve">47.9616050720215</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4402847290039</t>
+    <t xml:space="preserve">47.4402885437012</t>
   </si>
   <si>
     <t xml:space="preserve">47.7685203552246</t>
@@ -3101,37 +3101,37 @@
     <t xml:space="preserve">46.301097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5907173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8031158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8071403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6446189880371</t>
+    <t xml:space="preserve">46.5907211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8071365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6446228027344</t>
   </si>
   <si>
     <t xml:space="preserve">45.8956260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">46.165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6639251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9149322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3163757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4129219055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4322319030762</t>
+    <t xml:space="preserve">46.1659469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6639213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9149360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3163795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4129180908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4322280883789</t>
   </si>
   <si>
     <t xml:space="preserve">46.0887107849121</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.429027557373</t>
+    <t xml:space="preserve">49.4290313720703</t>
   </si>
   <si>
     <t xml:space="preserve">50.5875205993652</t>
@@ -3158,31 +3158,31 @@
     <t xml:space="preserve">52.1321792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6977462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1869087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1659965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1450881958008</t>
+    <t xml:space="preserve">51.6977424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1869049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1659927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.145092010498</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.255313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.53125</t>
+    <t xml:space="preserve">59.7106552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6277923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2553100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5312538146973</t>
   </si>
   <si>
     <t xml:space="preserve">60.2899017333984</t>
@@ -3191,40 +3191,40 @@
     <t xml:space="preserve">59.7589263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0211868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0694541931152</t>
+    <t xml:space="preserve">58.021183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0694580078125</t>
   </si>
   <si>
     <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">55.849006652832</t>
+    <t xml:space="preserve">55.8490104675293</t>
   </si>
   <si>
     <t xml:space="preserve">56.2834434509277</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4354820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4491653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7870559692383</t>
+    <t xml:space="preserve">53.4354782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4491691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9664649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
     <t xml:space="preserve">53.5802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0147285461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9318733215332</t>
+    <t xml:space="preserve">54.0147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9318695068359</t>
   </si>
   <si>
     <t xml:space="preserve">56.4282569885254</t>
@@ -3242,58 +3242,58 @@
     <t xml:space="preserve">51.9873657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4145774841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7733840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9801445007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2351722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.345401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5038909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6004333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.965690612793</t>
+    <t xml:space="preserve">55.4145812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7733764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9801406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2351760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3453979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5038871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6004295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9656867980957</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
   </si>
   <si>
-    <t xml:space="preserve">61.3035850524902</t>
+    <t xml:space="preserve">61.303581237793</t>
   </si>
   <si>
     <t xml:space="preserve">60.3864402770996</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6969680786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4073524475098</t>
+    <t xml:space="preserve">58.6969757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4073486328125</t>
   </si>
   <si>
     <t xml:space="preserve">55.221492767334</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0629997253418</t>
+    <t xml:space="preserve">54.0630035400391</t>
   </si>
   <si>
     <t xml:space="preserve">52.2287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0839080810547</t>
+    <t xml:space="preserve">52.083911895752</t>
   </si>
   <si>
     <t xml:space="preserve">53.1458587646484</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">50.8288764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8908271789551</t>
+    <t xml:space="preserve">51.8908309936523</t>
   </si>
   <si>
     <t xml:space="preserve">50.0565452575684</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">53.483757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8425559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6840629577637</t>
+    <t xml:space="preserve">51.8425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6840667724609</t>
   </si>
   <si>
     <t xml:space="preserve">51.1184997558594</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">50.3461723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4563941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9254188537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7186508178711</t>
+    <t xml:space="preserve">51.4563903808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9254150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7806015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7186546325684</t>
   </si>
   <si>
     <t xml:space="preserve">45.0074462890625</t>
@@ -3353,16 +3353,16 @@
     <t xml:space="preserve">46.3976440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763160705566</t>
+    <t xml:space="preserve">45.8763198852539</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4893264770508</t>
+    <t xml:space="preserve">41.2423477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4893226623535</t>
   </si>
   <si>
     <t xml:space="preserve">42.555305480957</t>
@@ -3374,31 +3374,31 @@
     <t xml:space="preserve">45.5480766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8224182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2633056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5738410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8771438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9117393493652</t>
+    <t xml:space="preserve">46.8224258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.263313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7942886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5738372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8771476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9117317199707</t>
   </si>
   <si>
     <t xml:space="preserve">46.6486473083496</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2970695495605</t>
+    <t xml:space="preserve">45.2970733642578</t>
   </si>
   <si>
     <t xml:space="preserve">47.5561294555664</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9495239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.675178527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6478157043457</t>
+    <t xml:space="preserve">44.9495277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6751823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.647819519043</t>
   </si>
   <si>
     <t xml:space="preserve">42.8063125610352</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">45.6253089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0348129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.837703704834</t>
+    <t xml:space="preserve">47.0348091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
     <t xml:space="preserve">44.1578903198242</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">43.4043235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8270950317383</t>
+    <t xml:space="preserve">44.827091217041</t>
   </si>
   <si>
     <t xml:space="preserve">46.444766998291</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6456756591797</t>
+    <t xml:space="preserve">45.645679473877</t>
   </si>
   <si>
     <t xml:space="preserve">45.3923072814941</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3054084777832</t>
+    <t xml:space="preserve">40.3054046630859</t>
   </si>
   <si>
     <t xml:space="preserve">39.1360054016113</t>
@@ -3497,16 +3497,16 @@
     <t xml:space="preserve">39.7012176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8766212463379</t>
+    <t xml:space="preserve">39.8766250610352</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">40.324893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8706169128418</t>
+    <t xml:space="preserve">40.3248977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8706130981445</t>
   </si>
   <si>
     <t xml:space="preserve">42.3713493347168</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">41.8646049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7806434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0924835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8840980529785</t>
+    <t xml:space="preserve">42.7806396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8841018676758</t>
   </si>
   <si>
     <t xml:space="preserve">41.9620628356934</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0025062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3593330383301</t>
+    <t xml:space="preserve">45.0025024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3593368530273</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">45.4507789611816</t>
   </si>
   <si>
-    <t xml:space="preserve">46.269359588623</t>
+    <t xml:space="preserve">46.2693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">47.4387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">49.163631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1381301879883</t>
+    <t xml:space="preserve">49.1636276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1381340026855</t>
   </si>
   <si>
     <t xml:space="preserve">50.8202857971191</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">51.2100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7460556030273</t>
+    <t xml:space="preserve">51.7460594177246</t>
   </si>
   <si>
     <t xml:space="preserve">50.9177322387695</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">51.5511589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">53.548885345459</t>
+    <t xml:space="preserve">53.5488891601562</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">54.3772125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9131927490234</t>
+    <t xml:space="preserve">54.9131889343262</t>
   </si>
   <si>
     <t xml:space="preserve">53.7437896728516</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4004402160645</t>
+    <t xml:space="preserve">55.4004364013672</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3617,19 +3617,19 @@
     <t xml:space="preserve">55.5466156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">54.474666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.061637878418</t>
+    <t xml:space="preserve">54.4746704101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0616416931152</t>
   </si>
   <si>
     <t xml:space="preserve">52.5743865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5256614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4792060852051</t>
+    <t xml:space="preserve">52.5256576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4792022705078</t>
   </si>
   <si>
     <t xml:space="preserve">49.7970542907715</t>
@@ -3641,34 +3641,34 @@
     <t xml:space="preserve">50.8690071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7715530395508</t>
+    <t xml:space="preserve">50.771556854248</t>
   </si>
   <si>
     <t xml:space="preserve">51.0151824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5024337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4537124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5998840332031</t>
+    <t xml:space="preserve">51.5024299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384101867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4537086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5998878479004</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3817596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8480453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8015975952148</t>
+    <t xml:space="preserve">50.3817558288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8015937805176</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">46.8345718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5362091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7738265991211</t>
+    <t xml:space="preserve">47.5362129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7738304138184</t>
   </si>
   <si>
     <t xml:space="preserve">47.7311096191406</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">48.4522438049316</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8712768554688</t>
+    <t xml:space="preserve">48.871280670166</t>
   </si>
   <si>
     <t xml:space="preserve">49.3098030090332</t>
@@ -3710,25 +3710,25 @@
     <t xml:space="preserve">49.4559783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3029899597168</t>
+    <t xml:space="preserve">55.3029937744141</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242240905762</t>
+    <t xml:space="preserve">60.2242279052734</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4468955993652</t>
+    <t xml:space="preserve">57.4468994140625</t>
   </si>
   <si>
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494453430176</t>
+    <t xml:space="preserve">57.3494491577148</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3749,19 +3749,19 @@
     <t xml:space="preserve">60.8576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0038261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8111953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6395263671875</t>
+    <t xml:space="preserve">61.0038299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8111991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6395225524902</t>
   </si>
   <si>
     <t xml:space="preserve">58.8599281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2497215270996</t>
+    <t xml:space="preserve">59.2497253417969</t>
   </si>
   <si>
     <t xml:space="preserve">57.9828720092773</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">58.4213981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6882514953613</t>
+    <t xml:space="preserve">59.6882476806641</t>
   </si>
   <si>
     <t xml:space="preserve">61.2961807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2684020996094</t>
+    <t xml:space="preserve">64.2684097290039</t>
   </si>
   <si>
     <t xml:space="preserve">62.319408416748</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">68.1176910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8230743408203</t>
+    <t xml:space="preserve">69.8230819702148</t>
   </si>
   <si>
     <t xml:space="preserve">70.3590469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9460296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4100494384766</t>
+    <t xml:space="preserve">68.9460220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.410041809082</t>
   </si>
   <si>
     <t xml:space="preserve">67.8740692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3125991821289</t>
+    <t xml:space="preserve">68.3125915527344</t>
   </si>
   <si>
     <t xml:space="preserve">67.1919097900391</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584945678711</t>
+    <t xml:space="preserve">66.5584869384766</t>
   </si>
   <si>
     <t xml:space="preserve">68.6536636352539</t>
@@ -3866,25 +3866,25 @@
     <t xml:space="preserve">70.6514053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7233428955078</t>
+    <t xml:space="preserve">71.7233505249023</t>
   </si>
   <si>
     <t xml:space="preserve">71.4309997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">71.528450012207</t>
+    <t xml:space="preserve">71.5284576416016</t>
   </si>
   <si>
     <t xml:space="preserve">72.6978530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6700820922852</t>
+    <t xml:space="preserve">75.6700897216797</t>
   </si>
   <si>
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.3057861328125</t>
+    <t xml:space="preserve">74.305778503418</t>
   </si>
   <si>
     <t xml:space="preserve">74.4032287597656</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">78.8372192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8394775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.2780151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.3754577636719</t>
+    <t xml:space="preserve">76.839485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.2780227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.3754653930664</t>
   </si>
   <si>
     <t xml:space="preserve">74.9879302978516</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627166748047</t>
+    <t xml:space="preserve">77.8627090454102</t>
   </si>
   <si>
     <t xml:space="preserve">79.3244705200195</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">77.1805572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">78.1550674438477</t>
+    <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
     <t xml:space="preserve">78.0088882446289</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">79.032112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4474105834961</t>
+    <t xml:space="preserve">78.4474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">77.4729080200195</t>
+    <t xml:space="preserve">77.4729156494141</t>
   </si>
   <si>
     <t xml:space="preserve">73.9647064208984</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">71.82080078125</t>
   </si>
   <si>
-    <t xml:space="preserve">77.9601669311523</t>
+    <t xml:space="preserve">77.9601593017578</t>
   </si>
   <si>
     <t xml:space="preserve">75.8162612915039</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">77.7165374755859</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964157104492</t>
+    <t xml:space="preserve">80.3964233398438</t>
   </si>
   <si>
     <t xml:space="preserve">80.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7119979858398</t>
+    <t xml:space="preserve">81.7119903564453</t>
   </si>
   <si>
     <t xml:space="preserve">81.4683685302734</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488067626953</t>
+    <t xml:space="preserve">87.9488143920898</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
@@ -4019,10 +4019,10 @@
     <t xml:space="preserve">87.9000854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">86.3408737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434310913086</t>
+    <t xml:space="preserve">86.3408813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434387207031</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">87.8513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3618392944336</t>
+    <t xml:space="preserve">89.3618316650391</t>
   </si>
   <si>
     <t xml:space="preserve">86.0972518920898</t>
@@ -4055,31 +4055,31 @@
     <t xml:space="preserve">82.1017990112305</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1250228881836</t>
+    <t xml:space="preserve">83.1250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6887664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0043563842773</t>
+    <t xml:space="preserve">83.8559036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6887741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0043487548828</t>
   </si>
   <si>
     <t xml:space="preserve">81.4196472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2270202636719</t>
+    <t xml:space="preserve">79.2270278930664</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091720581055</t>
+    <t xml:space="preserve">79.9091644287109</t>
   </si>
   <si>
     <t xml:space="preserve">81.5299453735352</t>
@@ -5655,6 +5655,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.6399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7799987792969</t>
   </si>
 </sst>
 </file>
@@ -70967,7 +70970,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.69125</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>410982</v>
@@ -70988,6 +70991,32 @@
         <v>1880</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6912268518</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>269570</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>89.0599975585938</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>87.7799987792969</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>88.7799987792969</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1881</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807546615601</t>
+    <t xml:space="preserve">15.1807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537845611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801054000854</t>
+    <t xml:space="preserve">14.8537855148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801063537598</t>
   </si>
   <si>
     <t xml:space="preserve">14.171820640564</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">13.9289264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0406274795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208856582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022003173828</t>
+    <t xml:space="preserve">15.0406255722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022012710571</t>
   </si>
   <si>
     <t xml:space="preserve">14.44273853302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6389198303223</t>
+    <t xml:space="preserve">14.6389188766479</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877418518066</t>
@@ -83,40 +83,40 @@
     <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3399782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7697086334229</t>
+    <t xml:space="preserve">14.33997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7697076797485</t>
   </si>
   <si>
     <t xml:space="preserve">14.3866853713989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.424054145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4155216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4061803817749</t>
+    <t xml:space="preserve">13.9943227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240531921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338006973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4155225753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4061813354492</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172302246094</t>
@@ -131,97 +131,97 @@
     <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057760238647</t>
+    <t xml:space="preserve">13.4057750701904</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777503967285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251096725464</t>
+    <t xml:space="preserve">14.1251106262207</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195852279663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0316905975342</t>
+    <t xml:space="preserve">14.0316915512085</t>
   </si>
   <si>
     <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8355083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.106427192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372140884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2558975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2461490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060199737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
+    <t xml:space="preserve">13.8355073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1064252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372121810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.255898475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.479700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385145187378</t>
   </si>
   <si>
     <t xml:space="preserve">15.545093536377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945638656616</t>
+    <t xml:space="preserve">15.6945657730103</t>
   </si>
   <si>
     <t xml:space="preserve">15.6104879379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983825683594</t>
+    <t xml:space="preserve">15.4983835220337</t>
   </si>
   <si>
     <t xml:space="preserve">15.0873355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.99391746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202344894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527290344238</t>
+    <t xml:space="preserve">14.9939155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527299880981</t>
   </si>
   <si>
     <t xml:space="preserve">15.3302297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253545761108</t>
+    <t xml:space="preserve">15.5918035507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412767410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253555297852</t>
   </si>
   <si>
     <t xml:space="preserve">16.3017978668213</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">16.3952159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3858737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3485088348389</t>
+    <t xml:space="preserve">16.3858757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3485107421875</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550868988037</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">16.4139022827148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671913146973</t>
+    <t xml:space="preserve">16.2924537658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671932220459</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2177219390869</t>
+    <t xml:space="preserve">16.2177181243896</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391666412354</t>
+    <t xml:space="preserve">16.3391628265381</t>
   </si>
   <si>
     <t xml:space="preserve">16.1149559020996</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">16.2737712860107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4325866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287670135498</t>
+    <t xml:space="preserve">16.4325847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287651062012</t>
   </si>
   <si>
     <t xml:space="preserve">16.4419269561768</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">16.5548648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207466125488</t>
+    <t xml:space="preserve">16.6207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6866283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054500579834</t>
+    <t xml:space="preserve">16.6866264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054462432861</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995643615723</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">16.5454540252686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6583938598633</t>
+    <t xml:space="preserve">16.6583919525146</t>
   </si>
   <si>
     <t xml:space="preserve">16.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183898925781</t>
+    <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254619598389</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">15.6890048980713</t>
   </si>
   <si>
-    <t xml:space="preserve">15.472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5830993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113338470459</t>
+    <t xml:space="preserve">15.4725427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407793045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5831031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113357543945</t>
   </si>
   <si>
     <t xml:space="preserve">16.4325141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2536964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290098190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678462982178</t>
+    <t xml:space="preserve">16.253698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642757415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678453445435</t>
   </si>
   <si>
     <t xml:space="preserve">15.2748985290527</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">15.5101852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7854995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.314923286438</t>
+    <t xml:space="preserve">14.7854986190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3149242401123</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443271636963</t>
@@ -389,37 +389,37 @@
     <t xml:space="preserve">15.4348936080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854778289795</t>
+    <t xml:space="preserve">15.5854787826538</t>
   </si>
   <si>
     <t xml:space="preserve">15.9054689407349</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8301773071289</t>
+    <t xml:space="preserve">15.8301801681519</t>
   </si>
   <si>
     <t xml:space="preserve">15.9901733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.792534828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.547833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337034225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3784236907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419496536255</t>
+    <t xml:space="preserve">15.7925310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.933705329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.670184135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3784255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148836135864</t>
@@ -428,67 +428,67 @@
     <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2725219726562</t>
+    <t xml:space="preserve">16.2725200653076</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2819328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1595821380615</t>
+    <t xml:space="preserve">16.2819309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1595802307129</t>
   </si>
   <si>
     <t xml:space="preserve">16.3760452270508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4983978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607524871826</t>
+    <t xml:space="preserve">16.4983959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607486724854</t>
   </si>
   <si>
     <t xml:space="preserve">16.5078086853027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6301593780518</t>
+    <t xml:space="preserve">16.6301574707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.4701633453369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560333251953</t>
+    <t xml:space="preserve">16.7807426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560314178467</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0160293579102</t>
+    <t xml:space="preserve">17.0160274505615</t>
   </si>
   <si>
     <t xml:space="preserve">16.9407386779785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8372116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.931324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9783821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8466186523438</t>
+    <t xml:space="preserve">16.8372135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9783878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8466205596924</t>
   </si>
   <si>
     <t xml:space="preserve">16.8936824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6960391998291</t>
+    <t xml:space="preserve">16.6960353851318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">17.0536766052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748569488525</t>
+    <t xml:space="preserve">16.8748588562012</t>
   </si>
   <si>
     <t xml:space="preserve">17.034854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8654460906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619209289551</t>
+    <t xml:space="preserve">16.8654441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619171142578</t>
   </si>
   <si>
     <t xml:space="preserve">17.0724983215332</t>
@@ -539,43 +539,43 @@
     <t xml:space="preserve">17.2324962615967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1007347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289672851562</t>
+    <t xml:space="preserve">17.1007328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289691925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2607307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3077850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983741760254</t>
+    <t xml:space="preserve">17.2136707305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077869415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.298376083374</t>
   </si>
   <si>
     <t xml:space="preserve">17.6936588287354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8724765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7383365631104</t>
+    <t xml:space="preserve">17.8724784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.738338470459</t>
   </si>
   <si>
     <t xml:space="preserve">18.8230438232422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6818714141846</t>
+    <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042182922363</t>
@@ -584,46 +584,46 @@
     <t xml:space="preserve">19.1430339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3406734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3783206939697</t>
+    <t xml:space="preserve">19.3406753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783226013184</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183265686035</t>
+    <t xml:space="preserve">19.2183246612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159698486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724170684814</t>
+    <t xml:space="preserve">19.4159660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724189758301</t>
   </si>
   <si>
     <t xml:space="preserve">20.4230003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2347717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.498291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.357120513916</t>
+    <t xml:space="preserve">20.234769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4982929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3571186065674</t>
   </si>
   <si>
     <t xml:space="preserve">20.893575668335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676998138428</t>
+    <t xml:space="preserve">20.6676979064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.6959342956543</t>
@@ -632,58 +632,58 @@
     <t xml:space="preserve">20.3665313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1030082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5194931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6889019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171382904053</t>
+    <t xml:space="preserve">20.1030101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7453708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.519495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6889057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">19.84889793396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5759601593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630260467529</t>
+    <t xml:space="preserve">19.5759620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630279541016</t>
   </si>
   <si>
     <t xml:space="preserve">19.2747936248779</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4442005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3877334594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3500862121582</t>
+    <t xml:space="preserve">19.4442024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.387731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3500881195068</t>
   </si>
   <si>
     <t xml:space="preserve">19.397144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959758758545</t>
+    <t xml:space="preserve">19.0959777832031</t>
   </si>
   <si>
     <t xml:space="preserve">19.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1053848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171581268311</t>
+    <t xml:space="preserve">19.1053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171543121338</t>
   </si>
   <si>
     <t xml:space="preserve">19.0865650177002</t>
@@ -692,22 +692,22 @@
     <t xml:space="preserve">18.8700981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.352466583252</t>
+    <t xml:space="preserve">18.4936370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524646759033</t>
   </si>
   <si>
     <t xml:space="preserve">18.2865867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254043579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100784301758</t>
+    <t xml:space="preserve">18.6254024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.510082244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371482849121</t>
@@ -716,52 +716,52 @@
     <t xml:space="preserve">19.5006694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7547817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335815429688</t>
+    <t xml:space="preserve">19.7547836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924289703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947856903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018199920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7900485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641490936279</t>
+    <t xml:space="preserve">20.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641529083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0159244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947441101074</t>
+    <t xml:space="preserve">21.1853370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.015926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947479248047</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794494628906</t>
@@ -770,55 +770,55 @@
     <t xml:space="preserve">21.1100425720215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.608850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.213565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429725646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8347282409668</t>
+    <t xml:space="preserve">21.4112091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6088523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2135677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.54296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8347320556641</t>
   </si>
   <si>
     <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8064956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0417823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582454681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476463317871</t>
+    <t xml:space="preserve">21.8064937591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.041784286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
   </si>
   <si>
     <t xml:space="preserve">22.6252956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0394039154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7288227081299</t>
+    <t xml:space="preserve">23.0394020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7288208007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5876502990723</t>
+    <t xml:space="preserve">22.5876522064209</t>
   </si>
   <si>
     <t xml:space="preserve">22.3711853027344</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">22.0135459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6465015411377</t>
+    <t xml:space="preserve">21.6464977264404</t>
   </si>
   <si>
     <t xml:space="preserve">21.91943359375</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.098123550415</t>
+    <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
@@ -857,52 +857,52 @@
     <t xml:space="preserve">22.0507411956787</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.08864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7569847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327922821045</t>
+    <t xml:space="preserve">21.7190799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0886459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327960968018</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.576940536499</t>
+    <t xml:space="preserve">21.5769424438477</t>
   </si>
   <si>
     <t xml:space="preserve">21.7285575866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7380313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579853057861</t>
+    <t xml:space="preserve">21.7380352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579872131348</t>
   </si>
   <si>
     <t xml:space="preserve">21.5200824737549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1315670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4158477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8612194061279</t>
+    <t xml:space="preserve">21.1315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4158496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
     <t xml:space="preserve">21.4632263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6622257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674629211426</t>
+    <t xml:space="preserve">21.662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674648284912</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624485015869</t>
@@ -920,64 +920,64 @@
     <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5908756256104</t>
+    <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
     <t xml:space="preserve">21.7948875427246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8138408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6717014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4676876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3255481719971</t>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.671703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3255500793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.5055904388428</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6951122283936</t>
+    <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0362491607666</t>
+    <t xml:space="preserve">23.036247253418</t>
   </si>
   <si>
     <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2162952423096</t>
+    <t xml:space="preserve">23.2162933349609</t>
   </si>
   <si>
     <t xml:space="preserve">22.998348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1310119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5005779266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900978088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404876708984</t>
+    <t xml:space="preserve">23.131010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5005760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404857635498</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058151245117</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.770923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.950963973999</t>
+    <t xml:space="preserve">22.7709217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9509658813477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0646781921387</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">22.7235412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9793949127197</t>
+    <t xml:space="preserve">22.9793930053711</t>
   </si>
   <si>
     <t xml:space="preserve">22.6477336883545</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1834087371826</t>
+    <t xml:space="preserve">22.183406829834</t>
   </si>
   <si>
     <t xml:space="preserve">23.87961769104</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">24.1165199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6616668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783885955811</t>
+    <t xml:space="preserve">23.6616687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783905029297</t>
   </si>
   <si>
     <t xml:space="preserve">22.9035873413086</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">24.0217590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955596923828</t>
+    <t xml:space="preserve">24.4955615997314</t>
   </si>
   <si>
     <t xml:space="preserve">24.5145149230957</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">24.6377010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6850814819336</t>
+    <t xml:space="preserve">24.685079574585</t>
   </si>
   <si>
     <t xml:space="preserve">24.5903205871582</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8082714080811</t>
+    <t xml:space="preserve">24.8082695007324</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651237487793</t>
+    <t xml:space="preserve">24.8651256561279</t>
   </si>
   <si>
     <t xml:space="preserve">25.7558727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.547399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915496826172</t>
+    <t xml:space="preserve">25.7653484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5474014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
   </si>
   <si>
     <t xml:space="preserve">25.4052600860596</t>
@@ -1088,43 +1088,43 @@
     <t xml:space="preserve">25.4431648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4905433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3863086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3484058380127</t>
+    <t xml:space="preserve">25.4905452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3863105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3484039306641</t>
   </si>
   <si>
     <t xml:space="preserve">25.3294525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0830707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7274436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.661111831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054847717285</t>
+    <t xml:space="preserve">25.0830726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.727445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6611137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054866790771</t>
   </si>
   <si>
     <t xml:space="preserve">26.8645706176758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3099422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0635662078857</t>
+    <t xml:space="preserve">27.309944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0635681152344</t>
   </si>
   <si>
     <t xml:space="preserve">26.675048828125</t>
@@ -1133,19 +1133,19 @@
     <t xml:space="preserve">26.9972343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1678028106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4665794372559</t>
+    <t xml:space="preserve">27.1678047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4665775299072</t>
   </si>
   <si>
     <t xml:space="preserve">26.0591087341309</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0451717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1778354644775</t>
+    <t xml:space="preserve">25.0451698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1778335571289</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">25.5189743041992</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1115016937256</t>
+    <t xml:space="preserve">25.111499786377</t>
   </si>
   <si>
     <t xml:space="preserve">25.5379238128662</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">25.9359188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1588840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3010234832764</t>
+    <t xml:space="preserve">25.1588821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.301025390625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2631187438965</t>
@@ -1196,37 +1196,37 @@
     <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2486305236816</t>
+    <t xml:space="preserve">26.248628616333</t>
   </si>
   <si>
     <t xml:space="preserve">26.4381465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">24.798791885376</t>
+    <t xml:space="preserve">24.7987937927246</t>
   </si>
   <si>
     <t xml:space="preserve">25.3673553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3578796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6232109069824</t>
+    <t xml:space="preserve">25.3578815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6232089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.7748260498047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5947818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7084922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1064853668213</t>
+    <t xml:space="preserve">25.5947799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7084903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1064872741699</t>
   </si>
   <si>
     <t xml:space="preserve">26.8171901702881</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">27.0540904998779</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3857498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695869445801</t>
+    <t xml:space="preserve">27.3857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695831298828</t>
   </si>
   <si>
     <t xml:space="preserve">25.8222064971924</t>
@@ -1247,43 +1247,43 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7324600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9743785858154</t>
+    <t xml:space="preserve">25.6326866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7324619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008026123047</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.827220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7848587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2586612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641212463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0167427062988</t>
+    <t xml:space="preserve">24.0691394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8272228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7848567962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0167407989502</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693622589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9270000457764</t>
+    <t xml:space="preserve">23.9269981384277</t>
   </si>
   <si>
     <t xml:space="preserve">26.3433876037598</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">26.0117263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.153865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4855289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5329093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9593315124512</t>
+    <t xml:space="preserve">26.1538677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5329074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9593334197998</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698097229004</t>
@@ -1313,40 +1313,40 @@
     <t xml:space="preserve">28.9492969512939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6176414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8071575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.665018081665</t>
+    <t xml:space="preserve">28.6176376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8071613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6650161743164</t>
   </si>
   <si>
     <t xml:space="preserve">29.3283386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2335796356201</t>
+    <t xml:space="preserve">29.2335815429688</t>
   </si>
   <si>
     <t xml:space="preserve">29.5394916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2086734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0652751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9696769714355</t>
+    <t xml:space="preserve">30.2086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0652770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9696750640869</t>
   </si>
   <si>
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602367401123</t>
+    <t xml:space="preserve">31.2602386474609</t>
   </si>
   <si>
     <t xml:space="preserve">32.7419967651367</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">34.0803527832031</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1797218322754</t>
+    <t xml:space="preserve">35.1797142028809</t>
   </si>
   <si>
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149398803711</t>
+    <t xml:space="preserve">34.4149436950684</t>
   </si>
   <si>
     <t xml:space="preserve">33.9369583129883</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7532958984375</t>
+    <t xml:space="preserve">35.7532997131348</t>
   </si>
   <si>
     <t xml:space="preserve">35.9922981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2275161743164</t>
+    <t xml:space="preserve">35.2275123596191</t>
   </si>
   <si>
     <t xml:space="preserve">35.0841217041016</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">35.6576995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">35.275318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.374683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268852233887</t>
+    <t xml:space="preserve">35.2753143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4224815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268814086914</t>
   </si>
   <si>
     <t xml:space="preserve">35.4187088012695</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">30.7822551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036331176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5948276519775</t>
+    <t xml:space="preserve">31.1168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5948257446289</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558349609375</t>
@@ -1460,28 +1460,28 @@
     <t xml:space="preserve">33.8413581848145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7495307922363</t>
+    <t xml:space="preserve">34.7495269775391</t>
   </si>
   <si>
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0400924682617</t>
+    <t xml:space="preserve">36.040096282959</t>
   </si>
   <si>
     <t xml:space="preserve">35.8966941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6614646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0035972595215</t>
+    <t xml:space="preserve">36.6614685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0035934448242</t>
   </si>
   <si>
     <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5180778503418</t>
+    <t xml:space="preserve">36.5180816650391</t>
   </si>
   <si>
     <t xml:space="preserve">37.4262504577637</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">36.2790870666504</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2350540161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8929214477539</t>
+    <t xml:space="preserve">37.2350578308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8929252624512</t>
   </si>
   <si>
     <t xml:space="preserve">34.5583381652832</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">33.5067672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2677726745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640075683594</t>
+    <t xml:space="preserve">33.2677764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640113830566</t>
   </si>
   <si>
     <t xml:space="preserve">32.9809875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3633728027344</t>
+    <t xml:space="preserve">33.3633766174316</t>
   </si>
   <si>
     <t xml:space="preserve">32.7897911071777</t>
@@ -1529,37 +1529,37 @@
     <t xml:space="preserve">32.5985946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5029983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199745178223</t>
+    <t xml:space="preserve">32.503002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199783325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.6463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3596000671387</t>
+    <t xml:space="preserve">32.3596038818359</t>
   </si>
   <si>
     <t xml:space="preserve">32.072811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7860221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0250129699707</t>
+    <t xml:space="preserve">31.7860202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.025016784668</t>
   </si>
   <si>
     <t xml:space="preserve">31.0212478637695</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8816165924072</t>
+    <t xml:space="preserve">31.8816184997559</t>
   </si>
   <si>
     <t xml:space="preserve">28.8703117370605</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2011299133301</t>
+    <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
     <t xml:space="preserve">27.7709445953369</t>
@@ -1592,16 +1592,16 @@
     <t xml:space="preserve">27.9621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3445281982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.013708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2048988342285</t>
+    <t xml:space="preserve">28.3445262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0137062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2049007415771</t>
   </si>
   <si>
     <t xml:space="preserve">30.4954586029053</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">29.5872917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174751281738</t>
+    <t xml:space="preserve">30.7344551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174770355225</t>
   </si>
   <si>
     <t xml:space="preserve">29.4438915252686</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">27.2929592132568</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4363574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187446594238</t>
+    <t xml:space="preserve">27.4363594055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187427520752</t>
   </si>
   <si>
     <t xml:space="preserve">27.7231464385986</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017684936523</t>
+    <t xml:space="preserve">27.1017646789551</t>
   </si>
   <si>
     <t xml:space="preserve">26.8627738952637</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">26.0979976654053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6200103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1935901641846</t>
+    <t xml:space="preserve">25.6200122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1935920715332</t>
   </si>
   <si>
     <t xml:space="preserve">26.6237812042236</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2891902923584</t>
+    <t xml:space="preserve">26.2891883850098</t>
   </si>
   <si>
     <t xml:space="preserve">26.7671737670898</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">28.9659099578857</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6791172027588</t>
+    <t xml:space="preserve">28.6791152954102</t>
   </si>
   <si>
     <t xml:space="preserve">29.1093044281006</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6715793609619</t>
+    <t xml:space="preserve">26.6715774536133</t>
   </si>
   <si>
     <t xml:space="preserve">26.8149719238281</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">26.4803867340088</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3885555267334</t>
+    <t xml:space="preserve">27.3885593414307</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080348968506</t>
+    <t xml:space="preserve">31.3080368041992</t>
   </si>
   <si>
     <t xml:space="preserve">31.4514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4552001953125</t>
+    <t xml:space="preserve">32.4552040100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.3118057250977</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">33.602367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">33.172176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5545692443848</t>
+    <t xml:space="preserve">33.1721801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5545654296875</t>
   </si>
   <si>
     <t xml:space="preserve">30.2564697265625</t>
@@ -1748,52 +1748,52 @@
     <t xml:space="preserve">30.6388568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5910606384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004970550537</t>
+    <t xml:space="preserve">30.5910587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004989624023</t>
   </si>
   <si>
     <t xml:space="preserve">29.9409999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">30.648416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8204936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9734497070312</t>
+    <t xml:space="preserve">30.6484184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8204917907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9734477996826</t>
   </si>
   <si>
     <t xml:space="preserve">30.2851486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0748348236084</t>
+    <t xml:space="preserve">30.0748329162598</t>
   </si>
   <si>
     <t xml:space="preserve">30.47633934021</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2277889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9983558654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8262825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6675357818604</t>
+    <t xml:space="preserve">30.2277908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9983539581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8262844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
     <t xml:space="preserve">30.438102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7631340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352111816406</t>
+    <t xml:space="preserve">30.7631359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935209274292</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
@@ -1814,28 +1814,28 @@
     <t xml:space="preserve">28.717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1762237548828</t>
+    <t xml:space="preserve">29.4821300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1762218475342</t>
   </si>
   <si>
     <t xml:space="preserve">29.3291797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5761566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9237041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6533908843994</t>
+    <t xml:space="preserve">28.5761585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9237079620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6533889770508</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058414459229</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3637676239014</t>
+    <t xml:space="preserve">28.3637657165527</t>
   </si>
   <si>
     <t xml:space="preserve">28.5182342529297</t>
@@ -1847,10 +1847,10 @@
     <t xml:space="preserve">28.0741424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2245826721191</t>
+    <t xml:space="preserve">27.1859645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2245845794678</t>
   </si>
   <si>
     <t xml:space="preserve">27.2052745819092</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">27.5142059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8617534637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7845230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0548343658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9969120025635</t>
+    <t xml:space="preserve">27.8617553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7845211029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0548324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9969100952148</t>
   </si>
   <si>
     <t xml:space="preserve">28.4989242553711</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">27.9003677368164</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0934505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1167888641357</t>
+    <t xml:space="preserve">28.0934524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1167869567871</t>
   </si>
   <si>
     <t xml:space="preserve">28.8850898742676</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">29.8311901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9084224700928</t>
+    <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
     <t xml:space="preserve">29.8505001068115</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">30.6807537078857</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3677940368652</t>
+    <t xml:space="preserve">29.3677959442139</t>
   </si>
   <si>
     <t xml:space="preserve">29.4836463928223</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">29.174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4257164001465</t>
+    <t xml:space="preserve">29.4257183074951</t>
   </si>
   <si>
     <t xml:space="preserve">29.2519454956055</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">29.4643363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0202445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9043979644775</t>
+    <t xml:space="preserve">29.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9043998718262</t>
   </si>
   <si>
     <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4796180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7652130126953</t>
+    <t xml:space="preserve">28.4796161651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7652111053467</t>
   </si>
   <si>
     <t xml:space="preserve">27.1666584014893</t>
@@ -1973,31 +1973,31 @@
     <t xml:space="preserve">26.9542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1473522186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.282506942749</t>
+    <t xml:space="preserve">27.1473503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2825088500977</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101776123047</t>
+    <t xml:space="preserve">26.6839542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101795196533</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1899948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3444595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9389877319336</t>
+    <t xml:space="preserve">28.1899929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3444576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.938985824585</t>
   </si>
   <si>
     <t xml:space="preserve">27.4369735717773</t>
@@ -2015,46 +2015,46 @@
     <t xml:space="preserve">27.4176635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0894241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.992883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0508079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755897521973</t>
+    <t xml:space="preserve">28.0355281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0894260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9928855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0508098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755878448486</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">27.591438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6107482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6879787445068</t>
+    <t xml:space="preserve">27.5914363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.610746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6879806518555</t>
   </si>
   <si>
     <t xml:space="preserve">26.355712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9309349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8537006378174</t>
+    <t xml:space="preserve">25.9309329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8536987304688</t>
   </si>
   <si>
     <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3018169403076</t>
+    <t xml:space="preserve">27.301815032959</t>
   </si>
   <si>
     <t xml:space="preserve">27.4562816619873</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">28.8078575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9816303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1360950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7499313354492</t>
+    <t xml:space="preserve">28.981632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1360969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7499332427979</t>
   </si>
   <si>
     <t xml:space="preserve">28.8271656036377</t>
@@ -2114,19 +2114,19 @@
     <t xml:space="preserve">28.6147727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2133293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6228275299072</t>
+    <t xml:space="preserve">29.2133312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6228256225586</t>
   </si>
   <si>
     <t xml:space="preserve">31.9357872009277</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3026466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4571075439453</t>
+    <t xml:space="preserve">32.3026428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4571113586426</t>
   </si>
   <si>
     <t xml:space="preserve">31.8585548400879</t>
@@ -2138,25 +2138,25 @@
     <t xml:space="preserve">31.1827659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">31.665470123291</t>
+    <t xml:space="preserve">31.6654720306396</t>
   </si>
   <si>
     <t xml:space="preserve">32.1674842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2599983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5882396697998</t>
+    <t xml:space="preserve">31.2600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5882415771484</t>
   </si>
   <si>
     <t xml:space="preserve">31.047607421875</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9510707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1248435974121</t>
+    <t xml:space="preserve">30.9510688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1248455047607</t>
   </si>
   <si>
     <t xml:space="preserve">31.3565406799316</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">30.8931427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8159122467041</t>
+    <t xml:space="preserve">30.8159103393555</t>
   </si>
   <si>
     <t xml:space="preserve">31.3372325897217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4683628082275</t>
+    <t xml:space="preserve">30.4683609008789</t>
   </si>
   <si>
     <t xml:space="preserve">31.0089931488037</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">33.0170478820801</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3645935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9052238464355</t>
+    <t xml:space="preserve">33.3645973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9052200317383</t>
   </si>
   <si>
     <t xml:space="preserve">33.8859176635742</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">34.8899459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0250968933105</t>
+    <t xml:space="preserve">35.0251007080078</t>
   </si>
   <si>
     <t xml:space="preserve">35.9712028503418</t>
@@ -2210,19 +2210,19 @@
     <t xml:space="preserve">36.9559211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8167343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9864807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2873573303223</t>
+    <t xml:space="preserve">37.2069320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7008857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9864845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2873611450195</t>
   </si>
   <si>
     <t xml:space="preserve">33.0363578796387</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.993709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6847801208496</t>
+    <t xml:space="preserve">31.9937114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6847839355469</t>
   </si>
   <si>
     <t xml:space="preserve">31.8778629302979</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">32.3605690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.383903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8432693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7427082061768</t>
+    <t xml:space="preserve">33.3839073181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8432769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7427062988281</t>
   </si>
   <si>
     <t xml:space="preserve">32.8239669799805</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">32.901195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2447204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5343399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4764137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6928329467773</t>
+    <t xml:space="preserve">32.2447242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5343437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4764175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6928367614746</t>
   </si>
   <si>
     <t xml:space="preserve">32.7081184387207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3871021270752</t>
+    <t xml:space="preserve">29.3871040344238</t>
   </si>
   <si>
     <t xml:space="preserve">29.8118839263916</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">29.8698081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">29.773265838623</t>
+    <t xml:space="preserve">29.7732677459717</t>
   </si>
   <si>
     <t xml:space="preserve">30.0049648284912</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2937641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1240158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5407390594482</t>
+    <t xml:space="preserve">26.2784786224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2937622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5407409667969</t>
   </si>
   <si>
     <t xml:space="preserve">24.1931934356689</t>
@@ -2312,28 +2312,28 @@
     <t xml:space="preserve">22.9767761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2744541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.737850189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.100679397583</t>
+    <t xml:space="preserve">25.2744522094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7378482818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1006774902344</t>
   </si>
   <si>
     <t xml:space="preserve">26.7225685119629</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8384170532227</t>
+    <t xml:space="preserve">26.8384189605713</t>
   </si>
   <si>
     <t xml:space="preserve">24.791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8263378143311</t>
+    <t xml:space="preserve">23.8263359069824</t>
   </si>
   <si>
     <t xml:space="preserve">24.0194187164307</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">24.4442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9075946807861</t>
+    <t xml:space="preserve">24.9075984954834</t>
   </si>
   <si>
     <t xml:space="preserve">25.0427551269531</t>
@@ -2354,52 +2354,52 @@
     <t xml:space="preserve">25.6220016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3943271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8231372833252</t>
+    <t xml:space="preserve">26.3943290710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8231353759766</t>
   </si>
   <si>
     <t xml:space="preserve">26.6646461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.645336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2398624420166</t>
+    <t xml:space="preserve">26.6453380584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2398643493652</t>
   </si>
   <si>
     <t xml:space="preserve">25.718542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4482288360596</t>
+    <t xml:space="preserve">25.4482269287109</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5487937927246</t>
+    <t xml:space="preserve">26.5487957000732</t>
   </si>
   <si>
     <t xml:space="preserve">26.9349594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4522533416748</t>
+    <t xml:space="preserve">26.4522514343262</t>
   </si>
   <si>
     <t xml:space="preserve">25.8923149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0660877227783</t>
+    <t xml:space="preserve">26.066089630127</t>
   </si>
   <si>
     <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">26.375020980835</t>
+    <t xml:space="preserve">26.3750190734863</t>
   </si>
   <si>
     <t xml:space="preserve">28.0162200927734</t>
@@ -2408,16 +2408,16 @@
     <t xml:space="preserve">30.0242748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">32.283332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.410436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5994911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5721282958984</t>
+    <t xml:space="preserve">32.2833290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4104385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5994930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5721302032471</t>
   </si>
   <si>
     <t xml:space="preserve">26.5681037902832</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">25.3903007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5254611968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4055824279785</t>
+    <t xml:space="preserve">25.5254592895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4055843353271</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
@@ -2444,28 +2444,28 @@
     <t xml:space="preserve">24.2511196136475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2897338867188</t>
+    <t xml:space="preserve">24.2897357940674</t>
   </si>
   <si>
     <t xml:space="preserve">24.5793571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8496723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3283500671387</t>
+    <t xml:space="preserve">24.8496742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3283519744873</t>
   </si>
   <si>
     <t xml:space="preserve">24.8303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3862743377686</t>
+    <t xml:space="preserve">24.3862762451172</t>
   </si>
   <si>
     <t xml:space="preserve">23.8842601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9421863555908</t>
+    <t xml:space="preserve">23.9421844482422</t>
   </si>
   <si>
     <t xml:space="preserve">24.1352672576904</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">24.154577255249</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0387287139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1505508422852</t>
+    <t xml:space="preserve">24.0387268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1505489349365</t>
   </si>
   <si>
     <t xml:space="preserve">23.3822479248047</t>
@@ -2489,34 +2489,34 @@
     <t xml:space="preserve">23.0733165740967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7684135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5946407318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2704257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6372833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0813732147217</t>
+    <t xml:space="preserve">23.7684116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7877197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2704277038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6372814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.081371307373</t>
   </si>
   <si>
     <t xml:space="preserve">24.3476581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5447654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1047077178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0853996276855</t>
+    <t xml:space="preserve">25.5447673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1047058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0853977203369</t>
   </si>
   <si>
     <t xml:space="preserve">25.119987487793</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">24.5986671447754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7338218688965</t>
+    <t xml:space="preserve">24.7338256835938</t>
   </si>
   <si>
     <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9269065856934</t>
+    <t xml:space="preserve">24.9269046783447</t>
   </si>
   <si>
     <t xml:space="preserve">26.7611865997314</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">25.2358360290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1392955780029</t>
+    <t xml:space="preserve">25.1392974853516</t>
   </si>
   <si>
     <t xml:space="preserve">25.6413097381592</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">25.3130702972412</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2977886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7804946899414</t>
+    <t xml:space="preserve">26.2977867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7804927825928</t>
   </si>
   <si>
     <t xml:space="preserve">26.6067199707031</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">26.046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2591743469238</t>
+    <t xml:space="preserve">26.2591705322266</t>
   </si>
   <si>
     <t xml:space="preserve">26.4136371612549</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">25.4675350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5600490570068</t>
+    <t xml:space="preserve">24.5600509643555</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689804077148</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">24.7724380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1401233673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7620124816895</t>
+    <t xml:space="preserve">30.1401214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7620143890381</t>
   </si>
   <si>
     <t xml:space="preserve">32.1481781005859</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">31.8392467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9744052886963</t>
+    <t xml:space="preserve">31.9744033813477</t>
   </si>
   <si>
     <t xml:space="preserve">31.9550952911377</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">34.1562309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245376586914</t>
+    <t xml:space="preserve">33.9245338439941</t>
   </si>
   <si>
     <t xml:space="preserve">35.1795654296875</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">35.3726501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3879318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5810089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2761116027832</t>
+    <t xml:space="preserve">34.3879280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5810127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2761077880859</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
@@ -2672,22 +2672,22 @@
     <t xml:space="preserve">34.4651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6003189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.495719909668</t>
+    <t xml:space="preserve">34.6003227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.264030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4957275390625</t>
   </si>
   <si>
     <t xml:space="preserve">33.0556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0596923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5383682250977</t>
+    <t xml:space="preserve">34.0596885681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5383720397949</t>
   </si>
   <si>
     <t xml:space="preserve">34.291389465332</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">32.9977378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7314491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3066673278809</t>
+    <t xml:space="preserve">33.7314529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3066711425781</t>
   </si>
   <si>
     <t xml:space="preserve">33.6349105834961</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">33.1908226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9591217041016</t>
+    <t xml:space="preserve">32.9591255187988</t>
   </si>
   <si>
     <t xml:space="preserve">31.8971748352051</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">33.345287322998</t>
   </si>
   <si>
-    <t xml:space="preserve">33.210132598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7893753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.557674407959</t>
+    <t xml:space="preserve">33.2101287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7893714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5576705932617</t>
   </si>
   <si>
     <t xml:space="preserve">33.9824600219727</t>
@@ -2741,22 +2741,22 @@
     <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">34.445858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0983085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5962944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0749702453613</t>
+    <t xml:space="preserve">34.4458541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0983047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5962905883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0749740600586</t>
   </si>
   <si>
     <t xml:space="preserve">32.939811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4418296813965</t>
+    <t xml:space="preserve">33.4418258666992</t>
   </si>
   <si>
     <t xml:space="preserve">32.8818893432617</t>
@@ -2765,31 +2765,31 @@
     <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">34.677547454834</t>
+    <t xml:space="preserve">34.6775512695312</t>
   </si>
   <si>
     <t xml:space="preserve">37.5351715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8360443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.400016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4925270080566</t>
+    <t xml:space="preserve">35.8360481262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4000129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4925231933594</t>
   </si>
   <si>
     <t xml:space="preserve">37.1490058898926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2994384765625</t>
+    <t xml:space="preserve">36.2994422912598</t>
   </si>
   <si>
     <t xml:space="preserve">36.2801361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7201957702637</t>
+    <t xml:space="preserve">35.7201995849609</t>
   </si>
   <si>
     <t xml:space="preserve">35.6043510437012</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">35.565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3919525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4346008300781</t>
+    <t xml:space="preserve">35.3919563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4346046447754</t>
   </si>
   <si>
     <t xml:space="preserve">37.6510162353516</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5158576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.519889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8481292724609</t>
+    <t xml:space="preserve">37.5158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198936462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8481254577637</t>
   </si>
   <si>
     <t xml:space="preserve">39.5625305175781</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2383193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9527244567871</t>
+    <t xml:space="preserve">40.2383232116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2149848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9527206420898</t>
   </si>
   <si>
     <t xml:space="preserve">41.1458015441895</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">41.9567489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5319671630859</t>
+    <t xml:space="preserve">41.5319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">41.3388862609863</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8947982788086</t>
+    <t xml:space="preserve">40.8948020935059</t>
   </si>
   <si>
     <t xml:space="preserve">40.701717376709</t>
@@ -2867,43 +2867,43 @@
     <t xml:space="preserve">40.6244850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5665550231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3429145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2809638977051</t>
+    <t xml:space="preserve">40.5665588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2809600830078</t>
   </si>
   <si>
     <t xml:space="preserve">42.3236083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4008369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6711502075195</t>
+    <t xml:space="preserve">42.4008331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6711540222168</t>
   </si>
   <si>
     <t xml:space="preserve">42.8256187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.887565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5786361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9841117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.617259979248</t>
+    <t xml:space="preserve">43.8875694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5786399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9841156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6172561645508</t>
   </si>
   <si>
     <t xml:space="preserve">43.8489570617676</t>
@@ -2933,25 +2933,25 @@
     <t xml:space="preserve">48.7049713134766</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3670768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4982109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4748687744141</t>
+    <t xml:space="preserve">48.367073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4982070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4748725891113</t>
   </si>
   <si>
     <t xml:space="preserve">45.8183898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0693969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5521049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1120414733887</t>
+    <t xml:space="preserve">46.0694007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1120452880859</t>
   </si>
   <si>
     <t xml:space="preserve">47.4016647338867</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">48.3188056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1876754760742</t>
+    <t xml:space="preserve">49.1876792907715</t>
   </si>
   <si>
     <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6912879943848</t>
+    <t xml:space="preserve">47.691291809082</t>
   </si>
   <si>
     <t xml:space="preserve">47.7878303527832</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5392532348633</t>
+    <t xml:space="preserve">50.539249420166</t>
   </si>
   <si>
     <t xml:space="preserve">47.8457565307617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2842178344727</t>
+    <t xml:space="preserve">49.2842140197754</t>
   </si>
   <si>
     <t xml:space="preserve">49.6221122741699</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">47.4209747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9422950744629</t>
+    <t xml:space="preserve">47.9422988891602</t>
   </si>
   <si>
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809188842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3807563781738</t>
+    <t xml:space="preserve">47.9809150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3807601928711</t>
   </si>
   <si>
     <t xml:space="preserve">50.0082778930664</t>
@@ -3026,28 +3026,28 @@
     <t xml:space="preserve">50.2978935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4974365234375</t>
+    <t xml:space="preserve">50.4909782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4974403381348</t>
   </si>
   <si>
     <t xml:space="preserve">53.8699188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3252639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9527778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9045066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6768341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0975875854492</t>
+    <t xml:space="preserve">52.3252601623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9527740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6768379211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0975914001465</t>
   </si>
   <si>
     <t xml:space="preserve">53.001049041748</t>
@@ -3059,19 +3059,19 @@
     <t xml:space="preserve">52.0356407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">51.601203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7105941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6567001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0774574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1739959716797</t>
+    <t xml:space="preserve">51.6012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7105979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6567039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.173999786377</t>
   </si>
   <si>
     <t xml:space="preserve">47.9616050720215</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4402809143066</t>
+    <t xml:space="preserve">47.4402847290039</t>
   </si>
   <si>
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3590278625488</t>
+    <t xml:space="preserve">46.8996543884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3590240478516</t>
   </si>
   <si>
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3011016845703</t>
+    <t xml:space="preserve">45.5287704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.301097869873</t>
   </si>
   <si>
     <t xml:space="preserve">46.5907173156738</t>
@@ -3107,40 +3107,40 @@
     <t xml:space="preserve">46.8031158447266</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8071403503418</t>
+    <t xml:space="preserve">47.8071365356445</t>
   </si>
   <si>
     <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8956298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1659393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6639251708984</t>
+    <t xml:space="preserve">45.8956260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6639213562012</t>
   </si>
   <si>
     <t xml:space="preserve">45.9149360656738</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3163795471191</t>
+    <t xml:space="preserve">45.3163757324219</t>
   </si>
   <si>
     <t xml:space="preserve">45.4129180908203</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4322319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0887107849121</t>
+    <t xml:space="preserve">45.4322280883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0887145996094</t>
   </si>
   <si>
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699714660645</t>
+    <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388374328613</t>
@@ -3149,25 +3149,25 @@
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.429027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5875282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1321754455566</t>
+    <t xml:space="preserve">49.4290313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5875244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1321792602539</t>
   </si>
   <si>
     <t xml:space="preserve">51.6977424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1869010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1659965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1450881958008</t>
+    <t xml:space="preserve">56.1869049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1659927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.145092010498</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">60.6277923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">61.2553100585938</t>
+    <t xml:space="preserve">61.255313873291</t>
   </si>
   <si>
     <t xml:space="preserve">60.5312538146973</t>
@@ -3188,46 +3188,46 @@
     <t xml:space="preserve">60.2899017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7589263916016</t>
+    <t xml:space="preserve">59.7589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">58.021183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0694541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6213417053223</t>
+    <t xml:space="preserve">58.0694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6213455200195</t>
   </si>
   <si>
     <t xml:space="preserve">55.849006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2834434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4354858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4491653442383</t>
+    <t xml:space="preserve">56.283447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4354820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4491691589355</t>
   </si>
   <si>
     <t xml:space="preserve">53.9664611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7870597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5802993774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0147323608398</t>
+    <t xml:space="preserve">54.7870559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5802955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0147285461426</t>
   </si>
   <si>
     <t xml:space="preserve">54.9318695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4282608032227</t>
+    <t xml:space="preserve">56.4282569885254</t>
   </si>
   <si>
     <t xml:space="preserve">55.0284118652344</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">53.3872146606445</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9873657226562</t>
+    <t xml:space="preserve">51.987361907959</t>
   </si>
   <si>
     <t xml:space="preserve">55.4145774841309</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">54.9801406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2351722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.345401763916</t>
+    <t xml:space="preserve">56.2351760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3453979492188</t>
   </si>
   <si>
     <t xml:space="preserve">58.5038909912109</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">60.965690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0139617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.303581237793</t>
+    <t xml:space="preserve">60.9656867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0139579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3035850524902</t>
   </si>
   <si>
     <t xml:space="preserve">60.3864364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6969680786133</t>
+    <t xml:space="preserve">58.6969718933105</t>
   </si>
   <si>
     <t xml:space="preserve">56.0420951843262</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">58.4073524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2214965820312</t>
+    <t xml:space="preserve">55.221492767334</t>
   </si>
   <si>
     <t xml:space="preserve">54.0629997253418</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">52.2287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0839080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1458587646484</t>
+    <t xml:space="preserve">52.083911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1458549499512</t>
   </si>
   <si>
     <t xml:space="preserve">50.4427108764648</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">51.8425598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6840629577637</t>
+    <t xml:space="preserve">50.6840667724609</t>
   </si>
   <si>
     <t xml:space="preserve">51.1184959411621</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">52.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1804466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3461685180664</t>
+    <t xml:space="preserve">52.1804504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3461723327637</t>
   </si>
   <si>
     <t xml:space="preserve">51.4563941955566</t>
@@ -3344,28 +3344,28 @@
     <t xml:space="preserve">50.7806015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7186546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0074501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3976402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8763198852539</t>
+    <t xml:space="preserve">49.7186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0074462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3976440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8763160705566</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4893226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5553092956543</t>
+    <t xml:space="preserve">41.2423439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4893264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.555305480957</t>
   </si>
   <si>
     <t xml:space="preserve">42.1498336791992</t>
@@ -3374,22 +3374,22 @@
     <t xml:space="preserve">45.5480766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8224182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2633056640625</t>
+    <t xml:space="preserve">46.8224220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2633094787598</t>
   </si>
   <si>
     <t xml:space="preserve">51.7942886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5738410949707</t>
+    <t xml:space="preserve">49.5738372802734</t>
   </si>
   <si>
     <t xml:space="preserve">50.8771476745605</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0219612121582</t>
+    <t xml:space="preserve">51.0219573974609</t>
   </si>
   <si>
     <t xml:space="preserve">49.911735534668</t>
@@ -3407,13 +3407,13 @@
     <t xml:space="preserve">46.9961929321289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4169464111328</t>
+    <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
     <t xml:space="preserve">44.9495239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6751823425293</t>
+    <t xml:space="preserve">43.675178527832</t>
   </si>
   <si>
     <t xml:space="preserve">41.647819519043</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">42.8063125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">44.119270324707</t>
+    <t xml:space="preserve">44.1192741394043</t>
   </si>
   <si>
     <t xml:space="preserve">45.6253089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0348091125488</t>
+    <t xml:space="preserve">47.0348129272461</t>
   </si>
   <si>
     <t xml:space="preserve">45.837703704834</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">43.4627914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1254539489746</t>
+    <t xml:space="preserve">44.1254501342773</t>
   </si>
   <si>
     <t xml:space="preserve">42.3908386230469</t>
@@ -3458,22 +3458,22 @@
     <t xml:space="preserve">46.444766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4312858581543</t>
+    <t xml:space="preserve">45.431282043457</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9380226135254</t>
+    <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
     <t xml:space="preserve">45.6456756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3923110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5092506408691</t>
+    <t xml:space="preserve">45.3923072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5092468261719</t>
   </si>
   <si>
     <t xml:space="preserve">44.3983154296875</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3054046630859</t>
+    <t xml:space="preserve">40.3054084777832</t>
   </si>
   <si>
     <t xml:space="preserve">39.1360054016113</t>
@@ -3497,13 +3497,13 @@
     <t xml:space="preserve">39.7012176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8766250610352</t>
+    <t xml:space="preserve">39.8766212463379</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3248977661133</t>
+    <t xml:space="preserve">40.324893951416</t>
   </si>
   <si>
     <t xml:space="preserve">40.8706169128418</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646087646484</t>
+    <t xml:space="preserve">41.8646049499512</t>
   </si>
   <si>
     <t xml:space="preserve">42.7806434631348</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">41.8840980529785</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9620590209961</t>
+    <t xml:space="preserve">41.9620628356934</t>
   </si>
   <si>
     <t xml:space="preserve">42.8586006164551</t>
@@ -3539,22 +3539,22 @@
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2693557739258</t>
+    <t xml:space="preserve">45.4507789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.269359588623</t>
   </si>
   <si>
     <t xml:space="preserve">47.4387588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1636276245117</t>
+    <t xml:space="preserve">49.163631439209</t>
   </si>
   <si>
     <t xml:space="preserve">50.1381301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8202819824219</t>
+    <t xml:space="preserve">50.8202857971191</t>
   </si>
   <si>
     <t xml:space="preserve">51.2100830078125</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">51.5511589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5488891601562</t>
+    <t xml:space="preserve">53.548885345459</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517150878906</t>
+    <t xml:space="preserve">55.3517112731934</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">54.3772125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9131889343262</t>
+    <t xml:space="preserve">54.9131927490234</t>
   </si>
   <si>
     <t xml:space="preserve">53.7437896728516</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">54.1335868835449</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1080894470215</t>
+    <t xml:space="preserve">55.1080932617188</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">56.3262176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5466194152832</t>
+    <t xml:space="preserve">55.5466156005859</t>
   </si>
   <si>
     <t xml:space="preserve">54.474666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0616416931152</t>
+    <t xml:space="preserve">53.061637878418</t>
   </si>
   <si>
     <t xml:space="preserve">52.5743865966797</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">52.5256614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4792098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7970504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3562622070312</t>
+    <t xml:space="preserve">50.4792060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7970542907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.356258392334</t>
   </si>
   <si>
     <t xml:space="preserve">50.8690071105957</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">52.0384140014648</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4537086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5998802185059</t>
+    <t xml:space="preserve">51.4537124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5998840332031</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">50.3817596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8480491638184</t>
+    <t xml:space="preserve">47.8480453491211</t>
   </si>
   <si>
     <t xml:space="preserve">45.8015975952148</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">49.7483291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4522399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.871280670166</t>
+    <t xml:space="preserve">48.4522438049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8712768554688</t>
   </si>
   <si>
     <t xml:space="preserve">49.3098030090332</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">49.3585319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">49.455982208252</t>
+    <t xml:space="preserve">49.4559783935547</t>
   </si>
   <si>
     <t xml:space="preserve">55.3029899597168</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494415283203</t>
+    <t xml:space="preserve">57.3494453430176</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">55.1568145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6927909851074</t>
+    <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
     <t xml:space="preserve">56.5698432922363</t>
   </si>
   <si>
-    <t xml:space="preserve">59.152271270752</t>
+    <t xml:space="preserve">59.1522750854492</t>
   </si>
   <si>
     <t xml:space="preserve">60.8576545715332</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">61.0038261413574</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8111991882324</t>
+    <t xml:space="preserve">58.8111953735352</t>
   </si>
   <si>
     <t xml:space="preserve">59.6395263671875</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">59.2497215270996</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9828758239746</t>
+    <t xml:space="preserve">57.9828720092773</t>
   </si>
   <si>
     <t xml:space="preserve">58.4213981628418</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">61.2961807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2684097290039</t>
+    <t xml:space="preserve">64.2684020996094</t>
   </si>
   <si>
     <t xml:space="preserve">62.319408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0502853393555</t>
+    <t xml:space="preserve">63.0502815246582</t>
   </si>
   <si>
     <t xml:space="preserve">61.3936309814453</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4842681884766</t>
+    <t xml:space="preserve">67.484260559082</t>
   </si>
   <si>
     <t xml:space="preserve">68.1176910400391</t>
@@ -3806,22 +3806,22 @@
     <t xml:space="preserve">70.3590469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9460220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.410041809082</t>
+    <t xml:space="preserve">68.9460296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4100494384766</t>
   </si>
   <si>
     <t xml:space="preserve">67.8740692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3125915527344</t>
+    <t xml:space="preserve">68.3125991821289</t>
   </si>
   <si>
     <t xml:space="preserve">67.1919097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8973007202148</t>
+    <t xml:space="preserve">68.8972930908203</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">65.4865341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5817184448242</t>
+    <t xml:space="preserve">67.5817108154297</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">66.509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1199569702148</t>
+    <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
     <t xml:space="preserve">66.8995742797852</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">66.5584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">68.6536712646484</t>
+    <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
     <t xml:space="preserve">69.0434646606445</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">70.6514053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7233505249023</t>
+    <t xml:space="preserve">71.7233428955078</t>
   </si>
   <si>
     <t xml:space="preserve">71.4309997558594</t>
@@ -3875,10 +3875,10 @@
     <t xml:space="preserve">71.528450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6978607177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6700897216797</t>
+    <t xml:space="preserve">72.6978530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6700820922852</t>
   </si>
   <si>
     <t xml:space="preserve">75.0366516113281</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">74.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4032363891602</t>
+    <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
     <t xml:space="preserve">75.7188110351562</t>
@@ -3896,16 +3896,16 @@
     <t xml:space="preserve">78.8372192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">76.839485168457</t>
+    <t xml:space="preserve">76.8394775390625</t>
   </si>
   <si>
     <t xml:space="preserve">77.2780151367188</t>
   </si>
   <si>
-    <t xml:space="preserve">77.3754653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.987922668457</t>
+    <t xml:space="preserve">77.3754577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9879302978516</t>
   </si>
   <si>
     <t xml:space="preserve">76.9369354248047</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859405517578</t>
+    <t xml:space="preserve">78.8859329223633</t>
   </si>
   <si>
     <t xml:space="preserve">77.5703659057617</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">77.1805572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">78.1550598144531</t>
+    <t xml:space="preserve">78.1550674438477</t>
   </si>
   <si>
     <t xml:space="preserve">78.0088882446289</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012390136719</t>
+    <t xml:space="preserve">78.3012466430664</t>
   </si>
   <si>
     <t xml:space="preserve">79.032112121582</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">77.8139877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">77.4729156494141</t>
+    <t xml:space="preserve">77.4729080200195</t>
   </si>
   <si>
     <t xml:space="preserve">73.9647064208984</t>
@@ -3974,10 +3974,10 @@
     <t xml:space="preserve">77.9601669311523</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8162689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7165451049805</t>
+    <t xml:space="preserve">75.8162612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7165374755859</t>
   </si>
   <si>
     <t xml:space="preserve">80.3964157104492</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">81.4683685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8581771850586</t>
+    <t xml:space="preserve">81.8581695556641</t>
   </si>
   <si>
     <t xml:space="preserve">81.7607269287109</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">85.268928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1924285888672</t>
+    <t xml:space="preserve">88.1924362182617</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
@@ -4016,16 +4016,16 @@
     <t xml:space="preserve">88.6796875</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9000778198242</t>
+    <t xml:space="preserve">87.9000854492188</t>
   </si>
   <si>
     <t xml:space="preserve">86.3408737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2434234619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.705192565918</t>
+    <t xml:space="preserve">86.2434310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7051849365234</t>
   </si>
   <si>
     <t xml:space="preserve">90.2876129150391</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360580444336</t>
+    <t xml:space="preserve">88.4360656738281</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6887741088867</t>
+    <t xml:space="preserve">80.6887664794922</t>
   </si>
   <si>
     <t xml:space="preserve">82.0043563842773</t>
@@ -5669,7 +5669,7 @@
     <t xml:space="preserve">87.2799987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.7399978637695</t>
+    <t xml:space="preserve">87.3199996948242</t>
   </si>
 </sst>
 </file>
@@ -71112,22 +71112,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6913078704</v>
+        <v>45967.6910532407</v>
       </c>
       <c r="B2505" t="n">
-        <v>218305</v>
+        <v>254735</v>
       </c>
       <c r="C2505" t="n">
-        <v>89.0999984741211</v>
+        <v>89.2799987792969</v>
       </c>
       <c r="D2505" t="n">
-        <v>85.5999984741211</v>
+        <v>86.8000030517578</v>
       </c>
       <c r="E2505" t="n">
-        <v>86.7200012207031</v>
+        <v>88.3199996948242</v>
       </c>
       <c r="F2505" t="n">
-        <v>88.7399978637695</v>
+        <v>87.3199996948242</v>
       </c>
       <c r="G2505" t="s">
         <v>1885</v>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="1887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1890">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801073074341</t>
+    <t xml:space="preserve">14.8537845611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801054000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.1718196868896</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">13.9476127624512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289283752441</t>
+    <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
     <t xml:space="preserve">15.0406255722046</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">14.44273853302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6389198303223</t>
+    <t xml:space="preserve">14.6389207839966</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0410318374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3212928771973</t>
+    <t xml:space="preserve">14.0410308837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
     <t xml:space="preserve">14.3399772644043</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">14.3866853713989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240522384644</t>
+    <t xml:space="preserve">13.9943227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.424054145813</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">13.9849805831909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0036640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433801651001</t>
+    <t xml:space="preserve">14.0036630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338006973267</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155225753784</t>
+    <t xml:space="preserve">12.4155216217041</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061813354492</t>
@@ -122,31 +122,31 @@
     <t xml:space="preserve">12.8172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722259521484</t>
+    <t xml:space="preserve">13.5459051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722249984741</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.919584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0316905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7607707977295</t>
+    <t xml:space="preserve">13.4057769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0316896438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7607717514038</t>
   </si>
   <si>
     <t xml:space="preserve">13.8355083465576</t>
@@ -155,79 +155,79 @@
     <t xml:space="preserve">14.106427192688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2372131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520807266235</t>
+    <t xml:space="preserve">14.2372140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520788192749</t>
   </si>
   <si>
     <t xml:space="preserve">14.2558975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4143047332764</t>
+    <t xml:space="preserve">15.414306640625</t>
   </si>
   <si>
     <t xml:space="preserve">15.6011476516724</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2461500167847</t>
+    <t xml:space="preserve">15.246148109436</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385145187378</t>
+    <t xml:space="preserve">15.3769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385126113892</t>
   </si>
   <si>
     <t xml:space="preserve">15.545093536377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939155578613</t>
+    <t xml:space="preserve">15.6945657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873355865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">14.6202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1527309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302268981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412767410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017978668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952159881592</t>
+    <t xml:space="preserve">15.1527280807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952140808105</t>
   </si>
   <si>
     <t xml:space="preserve">16.3858737945557</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">16.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4139003753662</t>
+    <t xml:space="preserve">16.2550888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4139022827148</t>
   </si>
   <si>
     <t xml:space="preserve">16.2924575805664</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2177200317383</t>
+    <t xml:space="preserve">16.0215358734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2177219390869</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391647338867</t>
+    <t xml:space="preserve">16.3391666412354</t>
   </si>
   <si>
     <t xml:space="preserve">16.1149578094482</t>
@@ -266,55 +266,55 @@
     <t xml:space="preserve">16.2737693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4325847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100826263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474494934082</t>
+    <t xml:space="preserve">16.4325828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.61008644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474514007568</t>
   </si>
   <si>
     <t xml:space="preserve">16.6287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4419250488281</t>
+    <t xml:space="preserve">16.4419288635254</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889850616455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6489772796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548648834229</t>
+    <t xml:space="preserve">16.6489810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548629760742</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6019229888916</t>
+    <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6866264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054500579834</t>
+    <t xml:space="preserve">16.7054462432861</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995624542236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5454521179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8277988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8183898925781</t>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8277969360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254600524902</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">15.6890048980713</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5830993652344</t>
+    <t xml:space="preserve">15.4725437164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407773971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.583101272583</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113357543945</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">16.4325141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2537002563477</t>
+    <t xml:space="preserve">16.253698348999</t>
   </si>
   <si>
     <t xml:space="preserve">16.5642795562744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5290107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090177536011</t>
+    <t xml:space="preserve">15.5290088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678453445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090167999268</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101861953735</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">14.7854995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3149242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.644326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9172611236572</t>
+    <t xml:space="preserve">14.314923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443281173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9172620773315</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384206771851</t>
@@ -389,43 +389,43 @@
     <t xml:space="preserve">15.4348936080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854768753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925338745117</t>
+    <t xml:space="preserve">15.5854787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301773071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925329208374</t>
   </si>
   <si>
     <t xml:space="preserve">15.5478343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9337072372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701803207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3784246444702</t>
+    <t xml:space="preserve">15.933705329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701831817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3784255981445</t>
   </si>
   <si>
     <t xml:space="preserve">15.5007743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6419486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148826599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278186798096</t>
+    <t xml:space="preserve">15.6419477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.2725200653076</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2819290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1595821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.376049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301593780518</t>
+    <t xml:space="preserve">16.2819309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1595802307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3760471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301574707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7807426452637</t>
+    <t xml:space="preserve">16.780740737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.8560333251953</t>
@@ -470,64 +470,64 @@
     <t xml:space="preserve">17.0160293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9407405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372097015381</t>
+    <t xml:space="preserve">16.9407386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.931324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9783840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8466205596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960391998291</t>
+    <t xml:space="preserve">16.9783821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.846622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960353851318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713279724121</t>
+    <t xml:space="preserve">16.7713317871094</t>
   </si>
   <si>
     <t xml:space="preserve">16.8089790344238</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4231052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842716217041</t>
+    <t xml:space="preserve">16.4231033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842697143555</t>
   </si>
   <si>
     <t xml:space="preserve">16.7525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9030895233154</t>
+    <t xml:space="preserve">16.9030876159668</t>
   </si>
   <si>
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0536766052246</t>
+    <t xml:space="preserve">16.9972057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.053674697876</t>
   </si>
   <si>
     <t xml:space="preserve">16.8748588562012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0348529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654441833496</t>
+    <t xml:space="preserve">17.034854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654460906982</t>
   </si>
   <si>
     <t xml:space="preserve">16.7619209289551</t>
@@ -536,31 +536,31 @@
     <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2324924468994</t>
+    <t xml:space="preserve">17.2324962615967</t>
   </si>
   <si>
     <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2607288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2136745452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3077869415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.298376083374</t>
+    <t xml:space="preserve">17.1289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2136726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642597198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983722686768</t>
   </si>
   <si>
     <t xml:space="preserve">17.6936569213867</t>
@@ -569,52 +569,52 @@
     <t xml:space="preserve">17.8724784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230438232422</t>
+    <t xml:space="preserve">18.7383365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230457305908</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.804220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430320739746</t>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406734466553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3783206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2183246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5571384429932</t>
+    <t xml:space="preserve">19.3783187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2183265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5571403503418</t>
   </si>
   <si>
     <t xml:space="preserve">19.4159679412842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2724189758301</t>
+    <t xml:space="preserve">20.2724170684814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4230003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2347679138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4982948303223</t>
+    <t xml:space="preserve">20.2347717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4982967376709</t>
   </si>
   <si>
     <t xml:space="preserve">20.357120513916</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">20.6676979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6959362030029</t>
+    <t xml:space="preserve">20.6959342956543</t>
   </si>
   <si>
     <t xml:space="preserve">20.3665313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1030082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206634521484</t>
+    <t xml:space="preserve">20.1030120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206615447998</t>
   </si>
   <si>
     <t xml:space="preserve">19.7453708648682</t>
@@ -644,43 +644,43 @@
     <t xml:space="preserve">19.5194969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6888980865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.84889793396</t>
+    <t xml:space="preserve">19.6889038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171382904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8488998413086</t>
   </si>
   <si>
     <t xml:space="preserve">19.5759620666504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4630241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2747917175293</t>
+    <t xml:space="preserve">19.4630260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2747936248779</t>
   </si>
   <si>
     <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3877353668213</t>
+    <t xml:space="preserve">19.3877334594727</t>
   </si>
   <si>
     <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3971462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959758758545</t>
+    <t xml:space="preserve">19.3971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959777832031</t>
   </si>
   <si>
     <t xml:space="preserve">19.0018615722656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1053886413574</t>
+    <t xml:space="preserve">19.1053867340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.9171600341797</t>
@@ -692,55 +692,55 @@
     <t xml:space="preserve">18.8700981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936408996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.352466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6254005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2371501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018218994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994632720947</t>
+    <t xml:space="preserve">18.4936370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.286584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6254043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5100803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2371463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994594573975</t>
   </si>
   <si>
     <t xml:space="preserve">20.7900505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9218101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641567230225</t>
+    <t xml:space="preserve">20.9218082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641529083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.2982692718506</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">21.0159244537354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029884338379</t>
+    <t xml:space="preserve">20.9029865264893</t>
   </si>
   <si>
     <t xml:space="preserve">21.0253391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9876899719238</t>
+    <t xml:space="preserve">20.9876937866211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1947422027588</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">21.1100425720215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112071990967</t>
+    <t xml:space="preserve">21.4112091064453</t>
   </si>
   <si>
     <t xml:space="preserve">21.608850479126</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829746246338</t>
+    <t xml:space="preserve">21.2135677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829765319824</t>
   </si>
   <si>
     <t xml:space="preserve">21.54296875</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">21.8347282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0229606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8064956665039</t>
+    <t xml:space="preserve">22.0229587554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8064937591553</t>
   </si>
   <si>
     <t xml:space="preserve">22.0417823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2582454681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476444244385</t>
+    <t xml:space="preserve">22.2582473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476463317871</t>
   </si>
   <si>
     <t xml:space="preserve">22.6252956390381</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">23.0394058227539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7288265228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0582256317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3711891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464977264404</t>
+    <t xml:space="preserve">22.7288208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0582275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876483917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135478973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464996337891</t>
   </si>
   <si>
     <t xml:space="preserve">21.9194316864014</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
-    <t xml:space="preserve">22.117073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.098123550415</t>
+    <t xml:space="preserve">22.1170749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1549777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686901092529</t>
+    <t xml:space="preserve">22.1549797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686920166016</t>
   </si>
   <si>
     <t xml:space="preserve">22.0507411956787</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0886459350586</t>
+    <t xml:space="preserve">22.08864402771</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569847106934</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">21.6811752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5769424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7285575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380332946777</t>
+    <t xml:space="preserve">21.576940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7285594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380313873291</t>
   </si>
   <si>
     <t xml:space="preserve">21.5579872131348</t>
@@ -887,49 +887,49 @@
     <t xml:space="preserve">21.5200843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1315650939941</t>
+    <t xml:space="preserve">21.1315670013428</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.463228225708</t>
+    <t xml:space="preserve">21.8612194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4632244110107</t>
   </si>
   <si>
     <t xml:space="preserve">21.6622257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5674667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5624465942383</t>
+    <t xml:space="preserve">21.5674629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5624504089355</t>
   </si>
   <si>
     <t xml:space="preserve">22.4013538360596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5529670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5813999176025</t>
+    <t xml:space="preserve">22.5529708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5813980102539</t>
   </si>
   <si>
     <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.590877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7948875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422698974609</t>
+    <t xml:space="preserve">22.5908756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7948894500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138408660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422679901123</t>
   </si>
   <si>
     <t xml:space="preserve">21.6717014312744</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">21.5958938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4676856994629</t>
+    <t xml:space="preserve">22.4676876068115</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255462646484</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">22.5055923461914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6951122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277797698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0362510681152</t>
+    <t xml:space="preserve">22.6951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277778625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0362491607666</t>
   </si>
   <si>
     <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2162952423096</t>
+    <t xml:space="preserve">23.2162971496582</t>
   </si>
   <si>
     <t xml:space="preserve">22.998348236084</t>
@@ -968,25 +968,25 @@
     <t xml:space="preserve">23.131010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5005741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900978088379</t>
+    <t xml:space="preserve">23.5005760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900959014893</t>
   </si>
   <si>
     <t xml:space="preserve">23.2731513977051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1404876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.405818939209</t>
+    <t xml:space="preserve">23.1404857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4058170318604</t>
   </si>
   <si>
     <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.770923614502</t>
+    <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
     <t xml:space="preserve">22.9509658813477</t>
@@ -995,58 +995,58 @@
     <t xml:space="preserve">23.0646800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7519721984863</t>
+    <t xml:space="preserve">22.7519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.7235412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9793949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6477336883545</t>
+    <t xml:space="preserve">22.9793930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6477317810059</t>
   </si>
   <si>
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.183406829834</t>
+    <t xml:space="preserve">22.1834087371826</t>
   </si>
   <si>
     <t xml:space="preserve">23.87961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1165180206299</t>
+    <t xml:space="preserve">24.1165199279785</t>
   </si>
   <si>
     <t xml:space="preserve">23.6616668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3868656158447</t>
+    <t xml:space="preserve">23.3868618011475</t>
   </si>
   <si>
     <t xml:space="preserve">23.1783885955811</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9035873413086</t>
+    <t xml:space="preserve">22.90358543396</t>
   </si>
   <si>
     <t xml:space="preserve">24.0217571258545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6376991271973</t>
+    <t xml:space="preserve">24.4955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6377010345459</t>
   </si>
   <si>
     <t xml:space="preserve">24.685079574585</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5903186798096</t>
+    <t xml:space="preserve">24.5903205871582</t>
   </si>
   <si>
     <t xml:space="preserve">24.7040328979492</t>
@@ -1055,34 +1055,34 @@
     <t xml:space="preserve">24.8082714080811</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7798404693604</t>
+    <t xml:space="preserve">24.779842376709</t>
   </si>
   <si>
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1639003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8651275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558746337891</t>
+    <t xml:space="preserve">24.5429401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1638965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8651256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558727264404</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5474014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915477752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052581787109</t>
+    <t xml:space="preserve">25.547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052600860596</t>
   </si>
   <si>
     <t xml:space="preserve">25.4431648254395</t>
@@ -1091,40 +1091,40 @@
     <t xml:space="preserve">25.4905452728271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3863105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3294525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0830745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7274475097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.661111831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054828643799</t>
+    <t xml:space="preserve">25.3863067626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3484039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3294506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0830707550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.727445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6611137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054847717285</t>
   </si>
   <si>
     <t xml:space="preserve">26.8645687103271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3099460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0635681152344</t>
+    <t xml:space="preserve">27.309944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
     <t xml:space="preserve">26.6750469207764</t>
@@ -1148,79 +1148,79 @@
     <t xml:space="preserve">25.1778335571289</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1967887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5189723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1115055084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5379238128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9359188079834</t>
+    <t xml:space="preserve">25.1967868804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5189743041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1115016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5379257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.935920715332</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.301025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683578491211</t>
+    <t xml:space="preserve">25.3010234832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683597564697</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219799041748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2062644958496</t>
+    <t xml:space="preserve">25.206262588501</t>
   </si>
   <si>
     <t xml:space="preserve">25.1020278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5853061676025</t>
+    <t xml:space="preserve">25.5853004455566</t>
   </si>
   <si>
     <t xml:space="preserve">25.6042575836182</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8601093292236</t>
+    <t xml:space="preserve">25.860107421875</t>
   </si>
   <si>
     <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.248628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4381465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7987937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3673553466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3578796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6232089996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.594783782959</t>
+    <t xml:space="preserve">26.2486305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4381484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.798791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3673572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3578777313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6232109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5947818756104</t>
   </si>
   <si>
     <t xml:space="preserve">25.7084903717041</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">26.1064853668213</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8171882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0540904998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3857536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695850372314</t>
+    <t xml:space="preserve">26.8171901702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695869445801</t>
   </si>
   <si>
     <t xml:space="preserve">25.8222045898438</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7324600219727</t>
+    <t xml:space="preserve">25.632682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7324619293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.9743785858154</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">24.4007987976074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8272247314453</t>
+    <t xml:space="preserve">24.0691394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0167407989502</t>
+    <t xml:space="preserve">24.2586612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0167446136475</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693641662598</t>
@@ -1286,1303 +1286,1303 @@
     <t xml:space="preserve">23.9269981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433837890625</t>
+    <t xml:space="preserve">26.3433856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2012481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5329093933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7698097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9492969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.617639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8071575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6650161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3283386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2335777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5394897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2086734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0652751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9696788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1130714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2602386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1356887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.936954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7532997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2275123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0841217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6577033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4187126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5658760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5948295593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2124404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0287818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.984748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7973251342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671417236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6539344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.036319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6061401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4627380371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8413543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7495346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5621070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0400886535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6614723205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5180778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4262504577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8564338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2790870666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2350540161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8929214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5583419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6979675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5067672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2677764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9809799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7897911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.837589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5985946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.503002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6463966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3596000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.072811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7860221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7709445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4401245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1055335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2451610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9621429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3445281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0137062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2049007415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4954605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5872898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4438934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6828861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.384786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2929592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4363555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6313190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1017684936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8627738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4841556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0061683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0979976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1935920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2891902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7269153594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9659099578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6791172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1093044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6715793609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8149719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4803867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3885555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8225135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8740825653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1608715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3520660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3080368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4514312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3118057250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2162094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.172176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5545692443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2564678192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6388568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6484184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8204936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2851486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4763412475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2277908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9983558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8262825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.438102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7498054504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7115650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8129501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5203723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4879245758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.717357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4821319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1762237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9237041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6533908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5182342529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8038291931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0741424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1859664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2245826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2052745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3211231231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5335140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6493625640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9776020050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5142059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8617534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7845230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0548343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9969120025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4989242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.247917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3251514434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8424453735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9003677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0934505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1167888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8850898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2712535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8311901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9084224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2173538208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6807537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3677940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4836463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.174711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4257164001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2519454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4643363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0202445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9043979644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6920070648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4796180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7652130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1666584014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9542675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1473522186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.282506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5528240203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.683952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8810615539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1899948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3444595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9389877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4369735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2631988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0314998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6260280609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4176635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.992883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0508079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755897521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7072887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.591438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6107482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6879787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8537006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8730068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3018169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4562816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8577251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7957744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9116230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7032604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7459030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1087341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1320686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3830738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9430122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4064102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8078575134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9816303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1360950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7499313354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8271656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.000940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6147727966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6228275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9357872009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4571075439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8585548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1827659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.665470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1674842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2599983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5882396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.047607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9510707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1248435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3565406799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8545246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8931427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8159122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3372325897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4683628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0089931488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7000598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0170478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9052238464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8859176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8899459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0250968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9712028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5311431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9559211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2069282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7008895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8167343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9864807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2873573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0363578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9205055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.993709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6847801208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8778629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3605690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.383903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8432693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7427082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8239669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.901195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2447204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5343399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4764137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3871021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8118839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9623222351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.773265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0049648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0274715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2784805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2937641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1240158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5407390594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1931934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9767761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2744541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.737850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.100679397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7225685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8384170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.791748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0194187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9614944458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4442024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9075946807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0427551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6220016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3943271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8231372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6646461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.645336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2398624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.718542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4482288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5833835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5487937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9349594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4522533416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8923149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0660877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735774993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.375020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0162200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0242748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.283332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.410436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5994911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5721282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5681037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5061511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3903007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5254611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4055824279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.482816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6565914154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2511196136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2897338867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5793571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8496723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3283500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8303642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3862743377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8842601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9421863555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1352672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.154577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0387287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1505508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3822479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0733165740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7684135437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5946407318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7877216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2704257965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6372833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0813732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3476581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5447654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1047077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0853996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.119987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9462127685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.811056137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5986671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7338218688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9848289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7611865997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2205543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.463508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358360290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1392955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6413097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3130702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7804946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2591743469238</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0117282867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1538677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4855270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5329074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7698078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9492950439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6176376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8071556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6650142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3283386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.539493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0652770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9696769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.113073348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2602386474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.936954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9885177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7532997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2275161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0841217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6577033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.275318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4224739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.374683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4187049865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5658760070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8526649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822532653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5948276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.212438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0287818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9847526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7973327636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671417236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6539344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.036319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6061363220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4627380371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8413581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7495346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0400886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6614723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0035972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5180778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4262542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8564338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2790832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2350540161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8929214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5583343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6979637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.506763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9809799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7897872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5985946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.503002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6463928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3596038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.072811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7860240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2011337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7709426879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4401245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.248929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1055335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2451610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9621391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3445262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.013708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2049007415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4954624176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.587287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174770355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4438934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6828842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3847885131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2929592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4363574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231483459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6313190460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350879669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1017646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8627758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4841556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0061683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0979976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1935939788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6237812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.289192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7269153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9659080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6791172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1093063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6715793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8149738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4803867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.388557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.822509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.874080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1608695983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3520641326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3080387115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4514350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4552001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3118019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2162094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.602367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.172176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5545654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2564697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6388549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6484184265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8204956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2851467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4763431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2277908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9983577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8262825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6675395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.438102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.935209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7498035430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7115650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.812952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5203704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.487922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.717357635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4821338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1762218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3291778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761566162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9237041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6533908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637657165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5182342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8038272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0741443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1859683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2245826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2052745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3211231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6493625640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9776039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5142059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8617534637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7845211029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0548343658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9969120025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4989242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.247917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3251514434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8424453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.900369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0934524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1167888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8850898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2712535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8311920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9084243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8505001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2173557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9856586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6807537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3677959442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4836444854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1747131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4257202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2519435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4643363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0202484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9043960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6920070648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4796180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7652111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1666564941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9542675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1473503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.282506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5528240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8810634613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1899948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3444595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.938985824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4369735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2631988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0315017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6260280609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0894241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.992883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7072887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.591438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.610746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6879806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9309329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8537006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8730068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.301815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4562797546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8577270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7957744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9116249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7032623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7459049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1087341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1320686340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3830757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9430141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4064083099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8078556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9816303253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1360950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7499313354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8271656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.000940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6147727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133274078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6228294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9357872009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4571075439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2213802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6654720306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2600002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5882434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0476093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9510688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1248455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3565425872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8545246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8931446075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8159103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.337230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4683647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0089912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7000598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0170478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3645896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9052238464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.885913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8899421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0250968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9712028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5311431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9559211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8167343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9864845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2873649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0363578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9205055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.993709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6847801208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8778629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.383903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8432769775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7427024841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8239669799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9011993408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2447166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5343437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4764175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6928329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3871021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8118839263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9623222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7732677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0049648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0274715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2784786224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2937622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5407428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9767742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2744522094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1006813049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7225685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8384189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.791748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8263359069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.019416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9614963531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4442005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9075965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0427551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6219997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300563812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8231391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.664644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.645336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2398643493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.718542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4482269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5833854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5487957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9349594116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4522533416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8923168182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0660915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.973575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.375020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0162181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0242729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2833366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4104404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5994930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5681037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5061531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3903026580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5254592895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4055843353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4828147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6565895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2511196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2897338867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5793552398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8496723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3283500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8303623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3862762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8842601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9421844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1352691650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1545753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0387268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3822460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0733165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7684135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7877197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2704257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.637279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.081371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3476581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5447673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1047058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0853996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.119987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.946216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.811056137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5986671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7338237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.984827041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7611846923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2205562591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6179752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4635105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358360290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1392955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3130683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7804946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.046781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2591705322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4136390686035</t>
+    <t xml:space="preserve">26.4136371612549</t>
   </si>
   <si>
     <t xml:space="preserve">25.8343906402588</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">25.7571582794189</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4675331115723</t>
+    <t xml:space="preserve">25.4675350189209</t>
   </si>
   <si>
     <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.772439956665</t>
+    <t xml:space="preserve">24.8689804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7724380493164</t>
   </si>
   <si>
     <t xml:space="preserve">30.1401233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7620143890381</t>
+    <t xml:space="preserve">31.7620124816895</t>
   </si>
   <si>
     <t xml:space="preserve">32.1481781005859</t>
@@ -2615,28 +2615,28 @@
     <t xml:space="preserve">32.2061042785645</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8392486572266</t>
+    <t xml:space="preserve">31.8392467498779</t>
   </si>
   <si>
     <t xml:space="preserve">31.9744052886963</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9550933837891</t>
+    <t xml:space="preserve">31.9550952911377</t>
   </si>
   <si>
     <t xml:space="preserve">32.3798789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2680511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1755409240723</t>
+    <t xml:space="preserve">33.2680549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.175537109375</t>
   </si>
   <si>
     <t xml:space="preserve">34.1562309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245338439941</t>
+    <t xml:space="preserve">33.9245376586914</t>
   </si>
   <si>
     <t xml:space="preserve">35.1795654296875</t>
@@ -2645,13 +2645,13 @@
     <t xml:space="preserve">35.3726501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3879280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5810127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2761077880859</t>
+    <t xml:space="preserve">34.3879318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5810089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2761116027832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">34.8706359863281</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7547836303711</t>
+    <t xml:space="preserve">34.7547874450684</t>
   </si>
   <si>
     <t xml:space="preserve">35.6429595947266</t>
@@ -2672,28 +2672,28 @@
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4651679992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6003227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4957275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0556602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.059684753418</t>
+    <t xml:space="preserve">34.4651641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6003189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.495719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0596923828125</t>
   </si>
   <si>
     <t xml:space="preserve">33.5383682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2913932800293</t>
+    <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542205810547</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">32.9977378845215</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7314529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3066711425781</t>
+    <t xml:space="preserve">33.7314491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3066673278809</t>
   </si>
   <si>
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908187866211</t>
+    <t xml:space="preserve">33.1908226013184</t>
   </si>
   <si>
     <t xml:space="preserve">32.9591217041016</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">31.8971748352051</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0709457397461</t>
+    <t xml:space="preserve">32.0709419250488</t>
   </si>
   <si>
     <t xml:space="preserve">32.4377975463867</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">33.345287322998</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2101287841797</t>
+    <t xml:space="preserve">33.210132598877</t>
   </si>
   <si>
     <t xml:space="preserve">33.7893753051758</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4458541870117</t>
+    <t xml:space="preserve">34.445858001709</t>
   </si>
   <si>
     <t xml:space="preserve">34.0983085632324</t>
@@ -2759,31 +2759,31 @@
     <t xml:space="preserve">32.939811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4418258666992</t>
+    <t xml:space="preserve">33.4418296813965</t>
   </si>
   <si>
     <t xml:space="preserve">32.8818893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">32.611572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6775512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5351676940918</t>
+    <t xml:space="preserve">32.6115760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.677547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5351715087891</t>
   </si>
   <si>
     <t xml:space="preserve">35.8360443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4000129699707</t>
+    <t xml:space="preserve">37.400016784668</t>
   </si>
   <si>
     <t xml:space="preserve">36.4925270080566</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1490097045898</t>
+    <t xml:space="preserve">37.1490058898926</t>
   </si>
   <si>
     <t xml:space="preserve">36.2994384765625</t>
@@ -2795,19 +2795,19 @@
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5657348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3919563293457</t>
+    <t xml:space="preserve">35.6043510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.565731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3919525146484</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510200500488</t>
+    <t xml:space="preserve">37.6510162353516</t>
   </si>
   <si>
     <t xml:space="preserve">37.0331573486328</t>
@@ -2816,34 +2816,34 @@
     <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5158653259277</t>
+    <t xml:space="preserve">37.5158576965332</t>
   </si>
   <si>
     <t xml:space="preserve">38.519889831543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8481330871582</t>
+    <t xml:space="preserve">38.8481292724609</t>
   </si>
   <si>
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.910083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2383232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9527206420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1458053588867</t>
+    <t xml:space="preserve">39.581844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9100799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2383193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2149810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9527244567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1458015441895</t>
   </si>
   <si>
     <t xml:space="preserve">41.7057418823242</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">42.4587631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9567451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5319709777832</t>
+    <t xml:space="preserve">41.9567489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">41.3388862609863</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5665588378906</t>
+    <t xml:space="preserve">40.6244850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5665550231934</t>
   </si>
   <si>
     <t xml:space="preserve">42.3429145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4780731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2809600830078</t>
+    <t xml:space="preserve">42.4780769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2809638977051</t>
   </si>
   <si>
     <t xml:space="preserve">42.3236083984375</t>
@@ -2891,43 +2891,43 @@
     <t xml:space="preserve">42.4008369445801</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6711540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8875732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5786399841309</t>
+    <t xml:space="preserve">42.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.887565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5786361694336</t>
   </si>
   <si>
     <t xml:space="preserve">43.9841117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8489532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3743019104004</t>
+    <t xml:space="preserve">43.617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8489570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3743057250977</t>
   </si>
   <si>
     <t xml:space="preserve">47.3244361877441</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9600028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5601615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4636154174805</t>
+    <t xml:space="preserve">49.7669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9600067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5601577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4636192321777</t>
   </si>
   <si>
     <t xml:space="preserve">47.2665100097656</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4982070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4748764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8183937072754</t>
+    <t xml:space="preserve">47.4982109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4748687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8183898925781</t>
   </si>
   <si>
     <t xml:space="preserve">46.0693969726562</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">46.5521049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1120452880859</t>
+    <t xml:space="preserve">47.1120414733887</t>
   </si>
   <si>
     <t xml:space="preserve">47.4016647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">48.01953125</t>
+    <t xml:space="preserve">48.0195350646973</t>
   </si>
   <si>
     <t xml:space="preserve">48.3188056945801</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">49.1876754760742</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9229927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7878341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051300048828</t>
+    <t xml:space="preserve">47.9229888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6912879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051223754883</t>
   </si>
   <si>
     <t xml:space="preserve">47.6140594482422</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2705383300781</t>
+    <t xml:space="preserve">48.2705345153809</t>
   </si>
   <si>
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.539249420166</t>
+    <t xml:space="preserve">50.5392532348633</t>
   </si>
   <si>
     <t xml:space="preserve">47.8457565307617</t>
@@ -3002,34 +3002,34 @@
     <t xml:space="preserve">49.6221122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6703872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5255661010742</t>
+    <t xml:space="preserve">49.6703834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
     <t xml:space="preserve">47.4209747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9422988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0734214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9809112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3807601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2978973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4909782409668</t>
+    <t xml:space="preserve">47.9422950744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0734252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3807563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0082778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2978935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4909820556641</t>
   </si>
   <si>
     <t xml:space="preserve">54.4974365234375</t>
@@ -3038,58 +3038,58 @@
     <t xml:space="preserve">53.8699188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3252601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9527740478516</t>
+    <t xml:space="preserve">52.3252639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9527778625488</t>
   </si>
   <si>
     <t xml:space="preserve">52.9045066833496</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6768379211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0975914001465</t>
+    <t xml:space="preserve">53.6768341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0975875854492</t>
   </si>
   <si>
     <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8562355041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0356369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6012077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7105979919434</t>
+    <t xml:space="preserve">52.8562393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0356407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.601203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7105941772461</t>
   </si>
   <si>
     <t xml:space="preserve">48.6567001342773</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0774536132812</t>
+    <t xml:space="preserve">48.0774574279785</t>
   </si>
   <si>
     <t xml:space="preserve">48.1739959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9616088867188</t>
+    <t xml:space="preserve">47.9616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4402885437012</t>
+    <t xml:space="preserve">47.4402809143066</t>
   </si>
   <si>
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996543884277</t>
+    <t xml:space="preserve">46.8996505737305</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590278625488</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287704467773</t>
+    <t xml:space="preserve">45.5287742614746</t>
   </si>
   <si>
     <t xml:space="preserve">46.3011016845703</t>
@@ -3110,64 +3110,64 @@
     <t xml:space="preserve">46.8031158447266</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8071441650391</t>
+    <t xml:space="preserve">47.8071403503418</t>
   </si>
   <si>
     <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8956260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6639289855957</t>
+    <t xml:space="preserve">45.8956298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1659393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
     <t xml:space="preserve">45.9149360656738</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3163757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4129219055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4322280883789</t>
+    <t xml:space="preserve">45.3163795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4129180908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4322319030762</t>
   </si>
   <si>
     <t xml:space="preserve">46.0887107849121</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9575805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1699676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0388336181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9945907592773</t>
+    <t xml:space="preserve">46.957576751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0388374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
     <t xml:space="preserve">49.429027557373</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5875244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1321830749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6977462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1869049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1659927368164</t>
+    <t xml:space="preserve">50.5875282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1321754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6977424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1659965515137</t>
   </si>
   <si>
     <t xml:space="preserve">60.1450881958008</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">60.9174156188965</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.255313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.53125</t>
+    <t xml:space="preserve">59.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6277923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2553100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5312538146973</t>
   </si>
   <si>
     <t xml:space="preserve">60.2899017333984</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">58.021183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0694580078125</t>
+    <t xml:space="preserve">58.0694541931152</t>
   </si>
   <si>
     <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8490104675293</t>
+    <t xml:space="preserve">55.849006652832</t>
   </si>
   <si>
     <t xml:space="preserve">56.2834434509277</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4354782104492</t>
+    <t xml:space="preserve">53.4354858398438</t>
   </si>
   <si>
     <t xml:space="preserve">54.4491653442383</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5802955627441</t>
+    <t xml:space="preserve">53.5802993774414</t>
   </si>
   <si>
     <t xml:space="preserve">54.0147323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9318733215332</t>
+    <t xml:space="preserve">54.9318695068359</t>
   </si>
   <si>
     <t xml:space="preserve">56.4282608032227</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">55.0284118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3872108459473</t>
+    <t xml:space="preserve">54.2078132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3872146606445</t>
   </si>
   <si>
     <t xml:space="preserve">51.9873657226562</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7733764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9801445007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2351760864258</t>
+    <t xml:space="preserve">53.773380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9801406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2351722717285</t>
   </si>
   <si>
     <t xml:space="preserve">57.345401763916</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5038871765137</t>
+    <t xml:space="preserve">58.5038909912109</t>
   </si>
   <si>
     <t xml:space="preserve">58.6004295349121</t>
@@ -3269,88 +3269,88 @@
     <t xml:space="preserve">60.965690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0139579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3035850524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3864402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6969757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420913696289</t>
+    <t xml:space="preserve">61.0139617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.303581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3864364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6969680786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420951843262</t>
   </si>
   <si>
     <t xml:space="preserve">58.4073524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">55.221492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0630035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2287216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.083911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1458625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4427070617676</t>
+    <t xml:space="preserve">55.2214965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2287178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0839080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1458587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
     <t xml:space="preserve">50.8288764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8908271789551</t>
+    <t xml:space="preserve">51.8908309936523</t>
   </si>
   <si>
     <t xml:space="preserve">50.0565490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2359504699707</t>
+    <t xml:space="preserve">49.2359466552734</t>
   </si>
   <si>
     <t xml:space="preserve">53.483757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8425559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6840667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1185035705566</t>
+    <t xml:space="preserve">51.8425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6840629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1184959411621</t>
   </si>
   <si>
     <t xml:space="preserve">52.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1804504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3461723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4563903808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9254150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7806053161621</t>
+    <t xml:space="preserve">52.1804466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3461685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4563941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9254188537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7806015014648</t>
   </si>
   <si>
     <t xml:space="preserve">49.7186546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0074462890625</t>
+    <t xml:space="preserve">45.0074501037598</t>
   </si>
   <si>
     <t xml:space="preserve">46.3976402282715</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">41.2423477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4893264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.555305480957</t>
+    <t xml:space="preserve">40.4893226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5553092956543</t>
   </si>
   <si>
     <t xml:space="preserve">42.1498336791992</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">45.5480766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2633094787598</t>
+    <t xml:space="preserve">46.8224182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2633056640625</t>
   </si>
   <si>
     <t xml:space="preserve">51.7942886352539</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">49.5738410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8771438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9117317199707</t>
+    <t xml:space="preserve">50.8771476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.911735534668</t>
   </si>
   <si>
     <t xml:space="preserve">46.6486473083496</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">47.5561294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9961967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4169502258301</t>
+    <t xml:space="preserve">46.9961929321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4169464111328</t>
   </si>
   <si>
     <t xml:space="preserve">44.9495239257812</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">43.6751823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6478157043457</t>
+    <t xml:space="preserve">41.647819519043</t>
   </si>
   <si>
     <t xml:space="preserve">42.8063125610352</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">44.1578903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4627952575684</t>
+    <t xml:space="preserve">43.4627914428711</t>
   </si>
   <si>
     <t xml:space="preserve">44.1254539489746</t>
@@ -3467,16 +3467,16 @@
     <t xml:space="preserve">45.528736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9380264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.645679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3923072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5092468261719</t>
+    <t xml:space="preserve">45.9380226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6456756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3923110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5092506408691</t>
   </si>
   <si>
     <t xml:space="preserve">44.3983154296875</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070457458496</t>
+    <t xml:space="preserve">41.0070495605469</t>
   </si>
   <si>
     <t xml:space="preserve">38.9995727539062</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646049499512</t>
+    <t xml:space="preserve">41.8646087646484</t>
   </si>
   <si>
     <t xml:space="preserve">42.7806434631348</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">41.9620590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8585968017578</t>
+    <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
     <t xml:space="preserve">45.0025062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3593368530273</t>
+    <t xml:space="preserve">44.3593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507789611816</t>
+    <t xml:space="preserve">45.4507751464844</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">49.1636276245117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1381340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8202857971191</t>
+    <t xml:space="preserve">50.1381301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8202819824219</t>
   </si>
   <si>
     <t xml:space="preserve">51.2100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7460594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9177284240723</t>
+    <t xml:space="preserve">51.7460556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9177322387695</t>
   </si>
   <si>
     <t xml:space="preserve">51.5511589050293</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">53.7437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1335906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1080932617188</t>
+    <t xml:space="preserve">54.1335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1080894470215</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4004364013672</t>
+    <t xml:space="preserve">55.4004402160645</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5466156005859</t>
+    <t xml:space="preserve">55.5466194152832</t>
   </si>
   <si>
     <t xml:space="preserve">54.474666595459</t>
@@ -3632,46 +3632,46 @@
     <t xml:space="preserve">52.5256614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4792060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7970542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.356258392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.869010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.771556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0151786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384063720703</t>
+    <t xml:space="preserve">50.4792098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7970504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3562622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8690071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7715530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0151824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384140014648</t>
   </si>
   <si>
     <t xml:space="preserve">51.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5998878479004</t>
+    <t xml:space="preserve">51.5998802185059</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3817558288574</t>
+    <t xml:space="preserve">50.3817596435547</t>
   </si>
   <si>
     <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8015937805176</t>
+    <t xml:space="preserve">45.8015975952148</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3689,16 +3689,16 @@
     <t xml:space="preserve">47.7311096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9919509887695</t>
+    <t xml:space="preserve">49.9919548034668</t>
   </si>
   <si>
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4522438049316</t>
+    <t xml:space="preserve">49.7483291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4522399902344</t>
   </si>
   <si>
     <t xml:space="preserve">48.871280670166</t>
@@ -3710,28 +3710,28 @@
     <t xml:space="preserve">49.3585319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4559783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3029937744141</t>
+    <t xml:space="preserve">49.455982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3029899597168</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242279052734</t>
+    <t xml:space="preserve">60.2242240905762</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4468994140625</t>
+    <t xml:space="preserve">57.4468955993652</t>
   </si>
   <si>
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494491577148</t>
+    <t xml:space="preserve">57.3494415283203</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">55.1568145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6927947998047</t>
+    <t xml:space="preserve">55.6927909851074</t>
   </si>
   <si>
     <t xml:space="preserve">56.5698432922363</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1522750854492</t>
+    <t xml:space="preserve">59.152271270752</t>
   </si>
   <si>
     <t xml:space="preserve">60.8576545715332</t>
@@ -3761,16 +3761,16 @@
     <t xml:space="preserve">59.6395263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8599243164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2497253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9828720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4214019775391</t>
+    <t xml:space="preserve">58.8599281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2497215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9828758239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4213981628418</t>
   </si>
   <si>
     <t xml:space="preserve">59.6882514953613</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">61.2961807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2684020996094</t>
+    <t xml:space="preserve">64.2684097290039</t>
   </si>
   <si>
     <t xml:space="preserve">62.319408416748</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">67.4842681884766</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1176986694336</t>
+    <t xml:space="preserve">68.1176910400391</t>
   </si>
   <si>
     <t xml:space="preserve">69.8230743408203</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">68.9460220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4100341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8740768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3125839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.1919174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8972930908203</t>
+    <t xml:space="preserve">68.410041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8740692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3125915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.1919097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8973007202148</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
@@ -3833,40 +3833,40 @@
     <t xml:space="preserve">65.4865341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5817108154297</t>
+    <t xml:space="preserve">67.5817184448242</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">69.6769027709961</t>
+    <t xml:space="preserve">69.6768951416016</t>
   </si>
   <si>
     <t xml:space="preserve">69.1409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5097579956055</t>
+    <t xml:space="preserve">66.509765625</t>
   </si>
   <si>
     <t xml:space="preserve">66.1199569702148</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8995666503906</t>
+    <t xml:space="preserve">66.8995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584869384766</t>
+    <t xml:space="preserve">66.5584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">68.6536712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0434722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6513977050781</t>
+    <t xml:space="preserve">69.0434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">71.7233505249023</t>
@@ -3875,10 +3875,10 @@
     <t xml:space="preserve">71.4309997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5284576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6978530883789</t>
+    <t xml:space="preserve">71.528450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6978607177734</t>
   </si>
   <si>
     <t xml:space="preserve">75.6700897216797</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.305778503418</t>
+    <t xml:space="preserve">74.3057861328125</t>
   </si>
   <si>
     <t xml:space="preserve">74.4032363891602</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7188034057617</t>
+    <t xml:space="preserve">75.7188110351562</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
@@ -3917,13 +3917,13 @@
     <t xml:space="preserve">77.8627166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">79.3244781494141</t>
+    <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
     <t xml:space="preserve">78.8859405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">77.5703582763672</t>
+    <t xml:space="preserve">77.5703659057617</t>
   </si>
   <si>
     <t xml:space="preserve">77.1805572509766</t>
@@ -3941,10 +3941,10 @@
     <t xml:space="preserve">77.424186706543</t>
   </si>
   <si>
-    <t xml:space="preserve">77.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6678085327148</t>
+    <t xml:space="preserve">77.0831069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6678161621094</t>
   </si>
   <si>
     <t xml:space="preserve">78.2525177001953</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">79.032112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4474182128906</t>
+    <t xml:space="preserve">78.4474105834961</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
@@ -3974,76 +3974,76 @@
     <t xml:space="preserve">71.82080078125</t>
   </si>
   <si>
-    <t xml:space="preserve">77.9601593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8162612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7165374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3964233398438</t>
+    <t xml:space="preserve">77.9601669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8162689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7165451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3964157104492</t>
   </si>
   <si>
     <t xml:space="preserve">80.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7119903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.468376159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8581695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7607192993164</t>
+    <t xml:space="preserve">81.7119979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4683685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8581771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7607269287109</t>
   </si>
   <si>
     <t xml:space="preserve">85.268928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1924438476562</t>
+    <t xml:space="preserve">88.1924285888672</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488143920898</t>
+    <t xml:space="preserve">87.9488067626953</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6796798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9000854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7051849365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2876205444336</t>
+    <t xml:space="preserve">88.6796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9000778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3408737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434234619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.705192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2876129150391</t>
   </si>
   <si>
     <t xml:space="preserve">87.8513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3618316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0972595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.972038269043</t>
+    <t xml:space="preserve">89.3618392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0972518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
     <t xml:space="preserve">88.4360580444336</t>
@@ -4058,49 +4058,49 @@
     <t xml:space="preserve">82.1017990112305</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1250305175781</t>
+    <t xml:space="preserve">83.1250228881836</t>
   </si>
   <si>
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559036254883</t>
+    <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0043411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4196548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2270278930664</t>
+    <t xml:space="preserve">82.0043563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4196472167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2270202636719</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5299377441406</t>
+    <t xml:space="preserve">79.9091720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5299453735352</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096420288086</t>
+    <t xml:space="preserve">77.1096496582031</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6322021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830764770508</t>
+    <t xml:space="preserve">78.632194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830841064453</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618255615234</t>
+    <t xml:space="preserve">79.7618179321289</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370315551758</t>
+    <t xml:space="preserve">81.1370239257812</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909790039062</t>
+    <t xml:space="preserve">83.6909713745117</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6281661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317092895508</t>
+    <t xml:space="preserve">81.628173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317169189453</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0742263793945</t>
+    <t xml:space="preserve">79.07421875</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.926872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326721191406</t>
+    <t xml:space="preserve">78.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0959548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326644897461</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853332519531</t>
+    <t xml:space="preserve">75.6853256225586</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928894042969</t>
+    <t xml:space="preserve">72.4928970336914</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870971679688</t>
+    <t xml:space="preserve">75.5870895385742</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402359008789</t>
+    <t xml:space="preserve">72.6402282714844</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176834106445</t>
+    <t xml:space="preserve">71.1176910400391</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597152709961</t>
+    <t xml:space="preserve">71.5597076416016</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4253,19 +4253,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3946533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022171020508</t>
+    <t xml:space="preserve">72.394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022247314453</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212188720703</t>
+    <t xml:space="preserve">70.9212265014648</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5420074462891</t>
+    <t xml:space="preserve">72.5419998168945</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389419555664</t>
+    <t xml:space="preserve">73.4260635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389343261719</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8270263671875</t>
+    <t xml:space="preserve">67.827018737793</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247772216797</t>
+    <t xml:space="preserve">70.7247695922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.546028137207</t>
+    <t xml:space="preserve">69.5460205078125</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698669433594</t>
+    <t xml:space="preserve">73.7698593139648</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4364,19 +4364,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065765380859</t>
+    <t xml:space="preserve">77.6007843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481384277344</t>
+    <t xml:space="preserve">77.7481307983398</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4397,25 +4397,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273498535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238067626953</t>
+    <t xml:space="preserve">75.9309005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238143920898</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344436645508</t>
+    <t xml:space="preserve">75.7344360351562</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4445,19 +4445,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9051513671875</t>
+    <t xml:space="preserve">82.905143737793</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046661376953</t>
+    <t xml:space="preserve">85.7046737670898</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851867675781</t>
+    <t xml:space="preserve">86.7851791381836</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4469,13 +4469,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542617797852</t>
+    <t xml:space="preserve">82.9542541503906</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489547729492</t>
+    <t xml:space="preserve">83.2489471435547</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4487,16 +4487,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312316894531</t>
+    <t xml:space="preserve">84.2312393188477</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507263183594</t>
+    <t xml:space="preserve">82.5613555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507186889648</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338195800781</t>
+    <t xml:space="preserve">89.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581436157227</t>
+    <t xml:space="preserve">91.0581359863281</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8576736450195</t>
+    <t xml:space="preserve">93.857666015625</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747367858887</t>
+    <t xml:space="preserve">102.845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747375488281</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.82788848877</t>
+    <t xml:space="preserve">103.827896118164</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034019470215</t>
+    <t xml:space="preserve">109.034027099609</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525161743164</t>
+    <t xml:space="preserve">109.525169372559</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.63143157959</t>
+    <t xml:space="preserve">103.631439208984</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.158004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122581481934</t>
+    <t xml:space="preserve">102.157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122573852539</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987350463867</t>
+    <t xml:space="preserve">99.8987426757812</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3625030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518737792969</t>
+    <t xml:space="preserve">96.3624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518661499023</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4670,13 +4670,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.264274597168</t>
+    <t xml:space="preserve">96.2642669677734</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.558967590332</t>
+    <t xml:space="preserve">96.5589599609375</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890686035156</t>
+    <t xml:space="preserve">94.8890609741211</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488159179688</t>
+    <t xml:space="preserve">94.7417221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488082885742</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5672,7 +5672,16 @@
     <t xml:space="preserve">87.2799987792969</t>
   </si>
   <si>
+    <t xml:space="preserve">88.7399978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3199996948242</t>
+  </si>
+  <si>
     <t xml:space="preserve">86.6399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3000030517578</t>
   </si>
 </sst>
 </file>
@@ -71115,27 +71124,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911921296</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>229308</v>
+        <v>218305</v>
       </c>
       <c r="C2505" t="n">
-        <v>88.2600021362305</v>
+        <v>89.0999984741211</v>
       </c>
       <c r="D2505" t="n">
-        <v>85.8000030517578</v>
+        <v>85.5999984741211</v>
       </c>
       <c r="E2505" t="n">
-        <v>87.0800018310547</v>
+        <v>86.7200012207031</v>
       </c>
       <c r="F2505" t="n">
-        <v>86.6399993896484</v>
+        <v>88.7399978637695</v>
       </c>
       <c r="G2505" t="s">
         <v>1886</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>254735</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>89.2799987792969</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>86.8000030517578</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>88.3199996948242</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>87.3199996948242</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1887</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>229308</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>88.2600021362305</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>85.8000030517578</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>87.0800018310547</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>86.6399993896484</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6915162037</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>308043</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>88.5400009155273</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>87.3000030517578</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>87.8199996948242</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>87.3000030517578</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="1891">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.180757522583</t>
+    <t xml:space="preserve">15.1807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">14.8537845611572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4801063537598</t>
+    <t xml:space="preserve">14.4801054000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.1718187332153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9476108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289283752441</t>
+    <t xml:space="preserve">13.9476118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289264678955</t>
   </si>
   <si>
     <t xml:space="preserve">15.0406265258789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3208866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022003173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.44273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389198303223</t>
+    <t xml:space="preserve">15.3208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022022247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4427375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389188766479</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877408981323</t>
@@ -80,49 +80,49 @@
     <t xml:space="preserve">14.0410308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3212919235229</t>
+    <t xml:space="preserve">14.3212909698486</t>
   </si>
   <si>
     <t xml:space="preserve">14.33997631073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7697086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3866853713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943227767944</t>
+    <t xml:space="preserve">14.7697076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3866844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943218231201</t>
   </si>
   <si>
     <t xml:space="preserve">14.424054145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3960266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849815368652</t>
+    <t xml:space="preserve">14.3960275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849805831909</t>
   </si>
   <si>
     <t xml:space="preserve">14.0036630630493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4155244827271</t>
+    <t xml:space="preserve">13.4338026046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051267623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4155216217041</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172292709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5459060668945</t>
+    <t xml:space="preserve">12.8172302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5459051132202</t>
   </si>
   <si>
     <t xml:space="preserve">13.1722259521484</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251096725464</t>
+    <t xml:space="preserve">13.4057779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251087188721</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195861816406</t>
@@ -146,139 +146,139 @@
     <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7607727050781</t>
+    <t xml:space="preserve">13.7607717514038</t>
   </si>
   <si>
     <t xml:space="preserve">13.8355093002319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.106427192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372140884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2558975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4143047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4797029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385145187378</t>
+    <t xml:space="preserve">14.1064252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372121810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.601149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4797010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385135650635</t>
   </si>
   <si>
     <t xml:space="preserve">15.5450925827026</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.61048412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873365402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.993914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202354431152</t>
+    <t xml:space="preserve">15.6945648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873355865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939165115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202344894409</t>
   </si>
   <si>
     <t xml:space="preserve">15.1527290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.330228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918035507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3485088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4139003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924575805664</t>
+    <t xml:space="preserve">15.3302278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253583908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017978668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3485069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4139041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924556732178</t>
   </si>
   <si>
     <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215377807617</t>
+    <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
     <t xml:space="preserve">16.2177200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3765316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3391647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325828552246</t>
+    <t xml:space="preserve">16.3765335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3391666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325866699219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6474514007568</t>
+    <t xml:space="preserve">16.6474494934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.6287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4419288635254</t>
+    <t xml:space="preserve">16.4419269561768</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889850616455</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">16.6866264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.658390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8278007507324</t>
+    <t xml:space="preserve">16.7054500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8277950286865</t>
   </si>
   <si>
     <t xml:space="preserve">16.8183879852295</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">16.2254600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6890058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407793045044</t>
+    <t xml:space="preserve">15.6890048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407783508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.583101272583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.253698348999</t>
+    <t xml:space="preserve">16.6113338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2536964416504</t>
   </si>
   <si>
     <t xml:space="preserve">16.5642795562744</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">15.5290088653564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8796157836914</t>
+    <t xml:space="preserve">14.8796148300171</t>
   </si>
   <si>
     <t xml:space="preserve">15.0678453445435</t>
@@ -359,37 +359,37 @@
     <t xml:space="preserve">15.2748985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2090167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3149242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.644326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9172601699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513605117798</t>
+    <t xml:space="preserve">15.2090177536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101861953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3149223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9172620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513586044312</t>
   </si>
   <si>
     <t xml:space="preserve">15.5195970535278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4348945617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854797363281</t>
+    <t xml:space="preserve">15.4348926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854787826538</t>
   </si>
   <si>
     <t xml:space="preserve">15.9054708480835</t>
@@ -398,73 +398,73 @@
     <t xml:space="preserve">15.8301773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9901733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.933705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701822280884</t>
+    <t xml:space="preserve">15.9901752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.792534828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.547833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337072372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.670184135437</t>
   </si>
   <si>
     <t xml:space="preserve">15.3784255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5007734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148836135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278205871582</t>
+    <t xml:space="preserve">15.5007762908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419496536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278186798096</t>
   </si>
   <si>
     <t xml:space="preserve">16.2725200653076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195762634277</t>
+    <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1595802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3760433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607486724854</t>
+    <t xml:space="preserve">16.1595821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3760452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607524871826</t>
   </si>
   <si>
     <t xml:space="preserve">16.5078086853027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6301593780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4701633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560314178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.98779296875</t>
+    <t xml:space="preserve">16.6301574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4701614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7807388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9877948760986</t>
   </si>
   <si>
     <t xml:space="preserve">17.0160293579102</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">16.9407386779785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8372116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9313278198242</t>
+    <t xml:space="preserve">16.8372097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
     <t xml:space="preserve">16.9783840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8466243743896</t>
+    <t xml:space="preserve">16.8466205596924</t>
   </si>
   <si>
     <t xml:space="preserve">16.8936805725098</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">16.912504196167</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713298797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231033325195</t>
+    <t xml:space="preserve">16.7713260650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231052398682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8842678070068</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">16.7525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9030914306641</t>
+    <t xml:space="preserve">16.9030895233154</t>
   </si>
   <si>
     <t xml:space="preserve">17.0066184997559</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0536766052246</t>
+    <t xml:space="preserve">17.0536785125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.8748569488525</t>
@@ -530,34 +530,34 @@
     <t xml:space="preserve">16.8654441833496</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0725002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007328033447</t>
+    <t xml:space="preserve">16.7619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0724983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2324962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2607307434082</t>
+    <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
     <t xml:space="preserve">17.2136726379395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3548431396484</t>
+    <t xml:space="preserve">17.3548469543457</t>
   </si>
   <si>
     <t xml:space="preserve">17.3642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3077869415283</t>
+    <t xml:space="preserve">17.307788848877</t>
   </si>
   <si>
     <t xml:space="preserve">17.2983741760254</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">17.8724784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7383365631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6818675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8042182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.143030166626</t>
+    <t xml:space="preserve">18.738338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406753540039</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183246612549</t>
+    <t xml:space="preserve">19.2183265686035</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571403503418</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">20.2724151611328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4230003356934</t>
+    <t xml:space="preserve">20.423002243042</t>
   </si>
   <si>
     <t xml:space="preserve">20.2347717285156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2535953521729</t>
+    <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982929229736</t>
@@ -623,16 +623,16 @@
     <t xml:space="preserve">20.8935775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665332794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030101776123</t>
+    <t xml:space="preserve">20.6676959991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030082702637</t>
   </si>
   <si>
     <t xml:space="preserve">19.8206634521484</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">19.7453708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">19.519495010376</t>
+    <t xml:space="preserve">19.5194931030273</t>
   </si>
   <si>
     <t xml:space="preserve">19.6889038085938</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">19.8488960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.575963973999</t>
+    <t xml:space="preserve">19.5759620666504</t>
   </si>
   <si>
     <t xml:space="preserve">19.4630260467529</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3877334594727</t>
+    <t xml:space="preserve">19.3877353668213</t>
   </si>
   <si>
     <t xml:space="preserve">19.3500862121582</t>
@@ -674,25 +674,25 @@
     <t xml:space="preserve">19.3971462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0018615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053886413574</t>
+    <t xml:space="preserve">19.0959758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.001859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053848266602</t>
   </si>
   <si>
     <t xml:space="preserve">18.9171581268311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0865669250488</t>
+    <t xml:space="preserve">19.0865650177002</t>
   </si>
   <si>
     <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4936389923096</t>
+    <t xml:space="preserve">18.4936370849609</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524646759033</t>
@@ -701,58 +701,58 @@
     <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559700012207</t>
+    <t xml:space="preserve">18.6254024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2559719085693</t>
   </si>
   <si>
     <t xml:space="preserve">19.510082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2371501922607</t>
+    <t xml:space="preserve">19.2371482849121</t>
   </si>
   <si>
     <t xml:space="preserve">19.5006694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7547855377197</t>
+    <t xml:space="preserve">19.7547779083252</t>
   </si>
   <si>
     <t xml:space="preserve">19.7924289703369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994632720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900524139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.298267364502</t>
+    <t xml:space="preserve">19.5947895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1853351593018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0159244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029884338379</t>
+    <t xml:space="preserve">21.015926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029865264893</t>
   </si>
   <si>
     <t xml:space="preserve">21.0253391265869</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112071990967</t>
+    <t xml:space="preserve">21.1100444793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112091064453</t>
   </si>
   <si>
     <t xml:space="preserve">21.608850479126</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135696411133</t>
+    <t xml:space="preserve">21.213565826416</t>
   </si>
   <si>
     <t xml:space="preserve">21.3829746246338</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8064937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.041784286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2582473754883</t>
+    <t xml:space="preserve">21.8064956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0417804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2582454681396</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817646026611</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7476482391357</t>
+    <t xml:space="preserve">22.7476463317871</t>
   </si>
   <si>
     <t xml:space="preserve">22.6252975463867</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5876522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9194316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.787670135498</t>
+    <t xml:space="preserve">22.5876483917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3711853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9194355010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7876682281494</t>
   </si>
   <si>
     <t xml:space="preserve">21.3076820373535</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0981254577637</t>
+    <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1549777984619</t>
+    <t xml:space="preserve">22.1549758911133</t>
   </si>
   <si>
     <t xml:space="preserve">22.2686920166016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0507431030273</t>
+    <t xml:space="preserve">22.0507411956787</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0886459350586</t>
+    <t xml:space="preserve">22.08864402771</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569847106934</t>
@@ -872,58 +872,58 @@
     <t xml:space="preserve">21.6811752319336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5769424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7285556793213</t>
+    <t xml:space="preserve">21.576940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7285594940186</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200824737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1315650939941</t>
+    <t xml:space="preserve">21.5579872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1315670013428</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612194061279</t>
+    <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
     <t xml:space="preserve">21.4632263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">21.662223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674648284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5624465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529708862305</t>
+    <t xml:space="preserve">21.6622257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5624485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529727935791</t>
   </si>
   <si>
     <t xml:space="preserve">22.5813999176025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6761608123779</t>
+    <t xml:space="preserve">22.6761589050293</t>
   </si>
   <si>
     <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7948894500732</t>
+    <t xml:space="preserve">21.7948875427246</t>
   </si>
   <si>
     <t xml:space="preserve">21.8138427734375</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">21.6717014312744</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5958938598633</t>
+    <t xml:space="preserve">21.5958957672119</t>
   </si>
   <si>
     <t xml:space="preserve">22.4676876068115</t>
@@ -944,49 +944,49 @@
     <t xml:space="preserve">22.3255481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951160430908</t>
+    <t xml:space="preserve">22.5055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0362510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2068176269531</t>
+    <t xml:space="preserve">23.0362491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2068195343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9983463287354</t>
+    <t xml:space="preserve">22.998348236084</t>
   </si>
   <si>
     <t xml:space="preserve">23.131010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5005760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4531955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7709197998047</t>
+    <t xml:space="preserve">23.5005741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404838562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4058170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.453197479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
     <t xml:space="preserve">22.9509658813477</t>
@@ -995,40 +995,40 @@
     <t xml:space="preserve">23.0646781921387</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7519721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.723539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9793949127197</t>
+    <t xml:space="preserve">22.7519683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7235412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9793930053711</t>
   </si>
   <si>
     <t xml:space="preserve">22.6477317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4771633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1834049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8796195983887</t>
+    <t xml:space="preserve">22.477165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.183406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.87961769104</t>
   </si>
   <si>
     <t xml:space="preserve">24.1165180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6616668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.90358543396</t>
+    <t xml:space="preserve">23.6616687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9035873413086</t>
   </si>
   <si>
     <t xml:space="preserve">24.0217590332031</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377010345459</t>
+    <t xml:space="preserve">24.6377029418945</t>
   </si>
   <si>
     <t xml:space="preserve">24.6850814819336</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8082695007324</t>
+    <t xml:space="preserve">24.8082714080811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7229843139648</t>
+    <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">24.5429401397705</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651275634766</t>
+    <t xml:space="preserve">24.8651237487793</t>
   </si>
   <si>
     <t xml:space="preserve">25.7558727264404</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5474014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915477752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052600860596</t>
+    <t xml:space="preserve">25.547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052581787109</t>
   </si>
   <si>
     <t xml:space="preserve">25.4431648254395</t>
@@ -1100,31 +1100,31 @@
     <t xml:space="preserve">25.3294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0830745697021</t>
+    <t xml:space="preserve">25.0830726623535</t>
   </si>
   <si>
     <t xml:space="preserve">25.727445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6611137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643459320068</t>
+    <t xml:space="preserve">25.6611099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643440246582</t>
   </si>
   <si>
     <t xml:space="preserve">26.3054847717285</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8645725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.309944152832</t>
+    <t xml:space="preserve">26.8645706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3099422454834</t>
   </si>
   <si>
     <t xml:space="preserve">26.9119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0635662078857</t>
+    <t xml:space="preserve">27.0635681152344</t>
   </si>
   <si>
     <t xml:space="preserve">26.675048828125</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">25.1778335571289</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1967887878418</t>
+    <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
     <t xml:space="preserve">25.5189743041992</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">25.5379219055176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1588821411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3010234832764</t>
+    <t xml:space="preserve">25.935920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1588840484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3010215759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.2631187438965</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">24.9219818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">25.206262588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8601112365723</t>
+    <t xml:space="preserve">25.2062644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8601093292236</t>
   </si>
   <si>
     <t xml:space="preserve">26.333911895752</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">26.2486305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4381484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7987957000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3673572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3578815460205</t>
+    <t xml:space="preserve">26.4381465911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7987937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3673553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3578796386719</t>
   </si>
   <si>
     <t xml:space="preserve">25.6800670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232089996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5947799682617</t>
+    <t xml:space="preserve">25.6232109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.594783782959</t>
   </si>
   <si>
     <t xml:space="preserve">25.7084903717041</t>
@@ -1229,25 +1229,25 @@
     <t xml:space="preserve">26.1064872741699</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8171863555908</t>
+    <t xml:space="preserve">26.8171901702881</t>
   </si>
   <si>
     <t xml:space="preserve">27.0540904998779</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3857517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9169673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.632682800293</t>
+    <t xml:space="preserve">27.3857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9169654846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7324600219727</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8272247314453</t>
+    <t xml:space="preserve">24.0691394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.827220916748</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2586612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641250610352</t>
+    <t xml:space="preserve">24.258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641212463379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0167407989502</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">23.9269981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433876037598</t>
+    <t xml:space="preserve">26.3433895111084</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0117282867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">26.0117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5329055786133</t>
+    <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593315124512</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">26.7698097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9492988586426</t>
+    <t xml:space="preserve">28.9492969512939</t>
   </si>
   <si>
     <t xml:space="preserve">28.617639541626</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">29.3283405303955</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2335815429688</t>
+    <t xml:space="preserve">29.2335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">29.5394916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0652770996094</t>
+    <t xml:space="preserve">30.2086734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0652751922607</t>
   </si>
   <si>
     <t xml:space="preserve">30.3042678833008</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602386474609</t>
+    <t xml:space="preserve">31.2602367401123</t>
   </si>
   <si>
     <t xml:space="preserve">32.7419967651367</t>
@@ -1355,37 +1355,37 @@
     <t xml:space="preserve">33.6501655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0803565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797142028809</t>
+    <t xml:space="preserve">34.0803527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797218322754</t>
   </si>
   <si>
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149475097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.936954498291</t>
+    <t xml:space="preserve">34.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9369583129883</t>
   </si>
   <si>
     <t xml:space="preserve">34.1759490966797</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9885177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.753303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2275123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0841255187988</t>
+    <t xml:space="preserve">34.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7532958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2275161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0841217041016</t>
   </si>
   <si>
     <t xml:space="preserve">35.6576995849609</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3746795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268814086914</t>
+    <t xml:space="preserve">36.374683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268852233887</t>
   </si>
   <si>
     <t xml:space="preserve">35.4187088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5658721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8526649475098</t>
+    <t xml:space="preserve">36.5658760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8526611328125</t>
   </si>
   <si>
     <t xml:space="preserve">30.7822551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168422698975</t>
+    <t xml:space="preserve">31.1168403625488</t>
   </si>
   <si>
     <t xml:space="preserve">31.4036331176758</t>
@@ -1427,28 +1427,28 @@
     <t xml:space="preserve">31.3558349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">31.212438583374</t>
+    <t xml:space="preserve">31.2124404907227</t>
   </si>
   <si>
     <t xml:space="preserve">33.0287818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7935562133789</t>
+    <t xml:space="preserve">33.7935600280762</t>
   </si>
   <si>
     <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7973289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671417236328</t>
+    <t xml:space="preserve">34.7973251342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671455383301</t>
   </si>
   <si>
     <t xml:space="preserve">34.6539344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0363273620605</t>
+    <t xml:space="preserve">35.0363235473633</t>
   </si>
   <si>
     <t xml:space="preserve">34.6061363220215</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413619995117</t>
+    <t xml:space="preserve">33.8413581848145</t>
   </si>
   <si>
     <t xml:space="preserve">34.7495307922363</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0400886535645</t>
+    <t xml:space="preserve">36.0400924682617</t>
   </si>
   <si>
     <t xml:space="preserve">35.8966941833496</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">39.0035972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3306465148926</t>
+    <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180778503418</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">37.2350540161133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8929290771484</t>
+    <t xml:space="preserve">34.8929214477539</t>
   </si>
   <si>
     <t xml:space="preserve">34.5583381652832</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">32.9809875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3633766174316</t>
+    <t xml:space="preserve">33.3633728027344</t>
   </si>
   <si>
     <t xml:space="preserve">32.7897911071777</t>
@@ -1532,49 +1532,49 @@
     <t xml:space="preserve">32.5029983520508</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2199821472168</t>
+    <t xml:space="preserve">33.2199745178223</t>
   </si>
   <si>
     <t xml:space="preserve">32.6463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3596038818359</t>
+    <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
     <t xml:space="preserve">32.072811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7860202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338184356689</t>
+    <t xml:space="preserve">31.7860221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338203430176</t>
   </si>
   <si>
     <t xml:space="preserve">31.0690422058105</t>
   </si>
   <si>
-    <t xml:space="preserve">32.025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0212459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703136444092</t>
+    <t xml:space="preserve">32.0250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703117370605</t>
   </si>
   <si>
     <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2011318206787</t>
+    <t xml:space="preserve">28.2011299133301</t>
   </si>
   <si>
     <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401226043701</t>
+    <t xml:space="preserve">28.4401264190674</t>
   </si>
   <si>
     <t xml:space="preserve">28.248929977417</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">27.2451610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9621391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3445262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0137062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2049026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4954605102539</t>
+    <t xml:space="preserve">27.9621410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3445281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.013708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2048988342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4954586029053</t>
   </si>
   <si>
     <t xml:space="preserve">29.5872917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344551086426</t>
+    <t xml:space="preserve">30.7344570159912</t>
   </si>
   <si>
     <t xml:space="preserve">30.0174751281738</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">29.6828861236572</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.384786605835</t>
+    <t xml:space="preserve">28.5835189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3847885131836</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929592132568</t>
@@ -1637,43 +1637,43 @@
     <t xml:space="preserve">27.4363574981689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8187408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231483459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6313209533691</t>
+    <t xml:space="preserve">27.8187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231464385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6313190460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017665863037</t>
+    <t xml:space="preserve">27.1017684936523</t>
   </si>
   <si>
     <t xml:space="preserve">26.8627738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.48415184021</t>
+    <t xml:space="preserve">27.4841556549072</t>
   </si>
   <si>
     <t xml:space="preserve">27.0061683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0979957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1935939788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156066894531</t>
+    <t xml:space="preserve">26.0979976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1935901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
     <t xml:space="preserve">26.2891902923584</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659080505371</t>
+    <t xml:space="preserve">28.9659099578857</t>
   </si>
   <si>
     <t xml:space="preserve">28.6791172027588</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">26.6715793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8149757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4803886413574</t>
+    <t xml:space="preserve">26.8149719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4803867340088</t>
   </si>
   <si>
     <t xml:space="preserve">27.3885555267334</t>
@@ -1718,10 +1718,10 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.45143699646</t>
+    <t xml:space="preserve">31.3080348968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4514331817627</t>
   </si>
   <si>
     <t xml:space="preserve">32.4552001953125</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">33.602367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1721801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5545654296875</t>
+    <t xml:space="preserve">33.172176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5545692443848</t>
   </si>
   <si>
     <t xml:space="preserve">30.2564697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6388549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004989624023</t>
+    <t xml:space="preserve">30.6388568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910606384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004970550537</t>
   </si>
   <si>
     <t xml:space="preserve">29.9409999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6484203338623</t>
+    <t xml:space="preserve">30.648416519165</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">30.2851486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0748329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4763412475586</t>
+    <t xml:space="preserve">30.0748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.47633934021</t>
   </si>
   <si>
     <t xml:space="preserve">30.2277889251709</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">29.9983558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8262844085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.667537689209</t>
+    <t xml:space="preserve">29.8262825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6675357818604</t>
   </si>
   <si>
     <t xml:space="preserve">30.438102722168</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">29.7498054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7115650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8129539489746</t>
+    <t xml:space="preserve">29.7115669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.812952041626</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203704833984</t>
   </si>
   <si>
-    <t xml:space="preserve">28.487922668457</t>
+    <t xml:space="preserve">28.4879245758057</t>
   </si>
   <si>
     <t xml:space="preserve">28.717357635498</t>
@@ -1817,16 +1817,16 @@
     <t xml:space="preserve">29.4821319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1762218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3291778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9237060546875</t>
+    <t xml:space="preserve">29.1762237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3291797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9237041473389</t>
   </si>
   <si>
     <t xml:space="preserve">28.6533908843994</t>
@@ -1835,34 +1835,34 @@
     <t xml:space="preserve">28.3058414459229</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3637657165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5182323455811</t>
+    <t xml:space="preserve">28.3637676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5182342529297</t>
   </si>
   <si>
     <t xml:space="preserve">27.8038291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0741443634033</t>
+    <t xml:space="preserve">28.0741424560547</t>
   </si>
   <si>
     <t xml:space="preserve">27.1859664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2245845794678</t>
+    <t xml:space="preserve">27.2245826721191</t>
   </si>
   <si>
     <t xml:space="preserve">27.2052745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3211212158203</t>
+    <t xml:space="preserve">27.3211231231689</t>
   </si>
   <si>
     <t xml:space="preserve">27.5335140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6493606567383</t>
+    <t xml:space="preserve">27.6493625640869</t>
   </si>
   <si>
     <t xml:space="preserve">27.9776020050049</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">28.4989242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2479190826416</t>
+    <t xml:space="preserve">28.247917175293</t>
   </si>
   <si>
     <t xml:space="preserve">28.3251514434814</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.900369644165</t>
+    <t xml:space="preserve">27.9003677368164</t>
   </si>
   <si>
     <t xml:space="preserve">28.0934505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6340808868408</t>
+    <t xml:space="preserve">28.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">29.1167888641357</t>
@@ -1913,37 +1913,37 @@
     <t xml:space="preserve">29.2712535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8311920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9084243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2173557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9856567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6807518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3677959442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4836444854736</t>
+    <t xml:space="preserve">29.8311901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9084224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2173538208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6807537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3677940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4836463928223</t>
   </si>
   <si>
     <t xml:space="preserve">29.174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4257202148438</t>
+    <t xml:space="preserve">29.4257164001465</t>
   </si>
   <si>
     <t xml:space="preserve">29.2519454956055</t>
@@ -1952,55 +1952,55 @@
     <t xml:space="preserve">29.4643363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0202465057373</t>
+    <t xml:space="preserve">29.0202445983887</t>
   </si>
   <si>
     <t xml:space="preserve">28.9043979644775</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6920051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4796161651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7652111053467</t>
+    <t xml:space="preserve">28.6920070648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4796180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7652130126953</t>
   </si>
   <si>
     <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542694091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1473503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2825088500977</t>
+    <t xml:space="preserve">26.9542675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1473522186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.282506942749</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6839542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101795196533</t>
+    <t xml:space="preserve">26.683952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101776123047</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1899929046631</t>
+    <t xml:space="preserve">28.1899948120117</t>
   </si>
   <si>
     <t xml:space="preserve">28.3444595336914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.938985824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4369716644287</t>
+    <t xml:space="preserve">27.9389877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4369735717773</t>
   </si>
   <si>
     <t xml:space="preserve">27.2631988525391</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">27.0314998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6260299682617</t>
+    <t xml:space="preserve">26.6260280609131</t>
   </si>
   <si>
     <t xml:space="preserve">27.4176635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0355281829834</t>
+    <t xml:space="preserve">28.035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">27.0894241333008</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">26.992883682251</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755878448486</t>
+    <t xml:space="preserve">27.0508079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755897521973</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">27.591438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">27.610746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6879806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3557109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9309329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8536987304688</t>
+    <t xml:space="preserve">27.6107482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6879787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8537006378174</t>
   </si>
   <si>
     <t xml:space="preserve">25.8730068206787</t>
@@ -2057,25 +2057,25 @@
     <t xml:space="preserve">27.3018169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4562835693359</t>
+    <t xml:space="preserve">27.4562816619873</t>
   </si>
   <si>
     <t xml:space="preserve">26.8577251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7957725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9116249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7032623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7459049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1087322235107</t>
+    <t xml:space="preserve">25.7957744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9116230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7032604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7459030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1087341308594</t>
   </si>
   <si>
     <t xml:space="preserve">28.1320686340332</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">28.8078575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.981632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1360969543457</t>
+    <t xml:space="preserve">28.9816303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1360950469971</t>
   </si>
   <si>
     <t xml:space="preserve">28.7499313354492</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">28.6147727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2133312225342</t>
+    <t xml:space="preserve">29.2133293151855</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.935791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026428222656</t>
+    <t xml:space="preserve">31.9357872009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026466369629</t>
   </si>
   <si>
     <t xml:space="preserve">32.4571075439453</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">31.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">31.182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6654720306396</t>
+    <t xml:space="preserve">31.1827659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.665470123291</t>
   </si>
   <si>
     <t xml:space="preserve">32.1674842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2600021362305</t>
+    <t xml:space="preserve">31.2599983215332</t>
   </si>
   <si>
     <t xml:space="preserve">31.5882396697998</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">30.9510707855225</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1248455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.356538772583</t>
+    <t xml:space="preserve">31.1248435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3565406799316</t>
   </si>
   <si>
     <t xml:space="preserve">30.8545246124268</t>
@@ -2168,16 +2168,16 @@
     <t xml:space="preserve">30.8931427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8159084320068</t>
+    <t xml:space="preserve">30.8159122467041</t>
   </si>
   <si>
     <t xml:space="preserve">31.3372325897217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4683609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0089912414551</t>
+    <t xml:space="preserve">30.4683628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0089931488037</t>
   </si>
   <si>
     <t xml:space="preserve">30.7000598907471</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">33.8859176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8899421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0251045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9711990356445</t>
+    <t xml:space="preserve">34.8899459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0250968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9712028503418</t>
   </si>
   <si>
     <t xml:space="preserve">36.5311431884766</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">36.9559211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2069320678711</t>
+    <t xml:space="preserve">37.2069282531738</t>
   </si>
   <si>
     <t xml:space="preserve">35.7008895874023</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">35.8167343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9864883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2873611450195</t>
+    <t xml:space="preserve">34.9864807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2873573303223</t>
   </si>
   <si>
     <t xml:space="preserve">33.0363578796387</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9937114715576</t>
+    <t xml:space="preserve">31.993709564209</t>
   </si>
   <si>
     <t xml:space="preserve">31.6847801208496</t>
@@ -2246,46 +2246,46 @@
     <t xml:space="preserve">33.383903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8432769775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7427062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8239631652832</t>
+    <t xml:space="preserve">32.8432693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7427082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8239669799805</t>
   </si>
   <si>
     <t xml:space="preserve">32.901195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2447166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5343437194824</t>
+    <t xml:space="preserve">32.2447204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5343399047852</t>
   </si>
   <si>
     <t xml:space="preserve">32.4764137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6928367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081146240234</t>
+    <t xml:space="preserve">33.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081184387207</t>
   </si>
   <si>
     <t xml:space="preserve">29.3871021270752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.811882019043</t>
+    <t xml:space="preserve">29.8118839263916</t>
   </si>
   <si>
     <t xml:space="preserve">28.9623222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8698101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7732677459717</t>
+    <t xml:space="preserve">29.8698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.773265838623</t>
   </si>
   <si>
     <t xml:space="preserve">30.0049648284912</t>
@@ -2294,28 +2294,28 @@
     <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784786224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2937622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5407428741455</t>
+    <t xml:space="preserve">26.2784805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2937641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1240158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5407390594482</t>
   </si>
   <si>
     <t xml:space="preserve">24.1931934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9767742156982</t>
+    <t xml:space="preserve">22.9767761230469</t>
   </si>
   <si>
     <t xml:space="preserve">25.2744541168213</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7378482818604</t>
+    <t xml:space="preserve">25.737850189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150825500488</t>
@@ -2324,40 +2324,40 @@
     <t xml:space="preserve">25.100679397583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7225704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8384189605713</t>
+    <t xml:space="preserve">26.7225685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8384170532227</t>
   </si>
   <si>
     <t xml:space="preserve">24.791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8263339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.019416809082</t>
+    <t xml:space="preserve">23.8263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0194187164307</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4441986083984</t>
+    <t xml:space="preserve">24.4442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075946807861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0427570343018</t>
+    <t xml:space="preserve">25.0427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">25.6220016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300563812256</t>
+    <t xml:space="preserve">26.3943271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300582885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.8231372833252</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">25.718542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4482269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5833854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5487957000732</t>
+    <t xml:space="preserve">25.4482288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5833835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5487937927246</t>
   </si>
   <si>
     <t xml:space="preserve">26.9349594116211</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">25.8923149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.066089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.973575592041</t>
+    <t xml:space="preserve">26.0660877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
     <t xml:space="preserve">26.375020980835</t>
@@ -2405,34 +2405,34 @@
     <t xml:space="preserve">28.0162200927734</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0242729187012</t>
+    <t xml:space="preserve">30.0242748260498</t>
   </si>
   <si>
     <t xml:space="preserve">32.283332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4104385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5994930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5721302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5681056976318</t>
+    <t xml:space="preserve">30.410436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5994911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5721282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5681037902832</t>
   </si>
   <si>
     <t xml:space="preserve">25.5061511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903026580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5254592895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4055843353271</t>
+    <t xml:space="preserve">25.3903007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5254611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4055824279785</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">24.2511196136475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2897357940674</t>
+    <t xml:space="preserve">24.2897338867188</t>
   </si>
   <si>
     <t xml:space="preserve">24.5793571472168</t>
@@ -2453,49 +2453,49 @@
     <t xml:space="preserve">24.8496723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3283519744873</t>
+    <t xml:space="preserve">24.3283500671387</t>
   </si>
   <si>
     <t xml:space="preserve">24.8303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3862762451172</t>
+    <t xml:space="preserve">24.3862743377686</t>
   </si>
   <si>
     <t xml:space="preserve">23.8842601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9421844482422</t>
+    <t xml:space="preserve">23.9421863555908</t>
   </si>
   <si>
     <t xml:space="preserve">24.1352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1545753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0387268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1505470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3822460174561</t>
+    <t xml:space="preserve">24.154577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0387287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1505508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3822479248047</t>
   </si>
   <si>
     <t xml:space="preserve">23.0733165740967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7684116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7877197265625</t>
+    <t xml:space="preserve">23.7684135437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5946407318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7877216339111</t>
   </si>
   <si>
     <t xml:space="preserve">24.2704257965088</t>
@@ -2504,19 +2504,19 @@
     <t xml:space="preserve">24.6372833251953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.081371307373</t>
+    <t xml:space="preserve">25.0813732147217</t>
   </si>
   <si>
     <t xml:space="preserve">24.3476581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5447673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1047058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0853977203369</t>
+    <t xml:space="preserve">25.5447654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1047077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0853996276855</t>
   </si>
   <si>
     <t xml:space="preserve">25.119987487793</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.5986671447754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7338237762451</t>
+    <t xml:space="preserve">24.7338218688965</t>
   </si>
   <si>
     <t xml:space="preserve">24.9848289489746</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">24.9269065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7611846923828</t>
+    <t xml:space="preserve">26.7611865997314</t>
   </si>
   <si>
     <t xml:space="preserve">26.2205543518066</t>
@@ -2552,22 +2552,22 @@
     <t xml:space="preserve">24.463508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358341217041</t>
+    <t xml:space="preserve">25.2358360290527</t>
   </si>
   <si>
     <t xml:space="preserve">25.1392955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6413078308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3130683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7804927825928</t>
+    <t xml:space="preserve">25.6413097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3130702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7804946899414</t>
   </si>
   <si>
     <t xml:space="preserve">26.6067199707031</t>
@@ -2576,37 +2576,37 @@
     <t xml:space="preserve">26.046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2591724395752</t>
+    <t xml:space="preserve">26.2591743469238</t>
   </si>
   <si>
     <t xml:space="preserve">26.4136371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8343925476074</t>
+    <t xml:space="preserve">25.8343906402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.7571582794189</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4675331115723</t>
+    <t xml:space="preserve">25.4675350189209</t>
   </si>
   <si>
     <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689823150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.772439956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1401214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7620182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1481742858887</t>
+    <t xml:space="preserve">24.8689804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7724380493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1401233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7620124816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1481781005859</t>
   </si>
   <si>
     <t xml:space="preserve">32.2061042785645</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">31.8392467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9744033813477</t>
+    <t xml:space="preserve">31.9744052886963</t>
   </si>
   <si>
     <t xml:space="preserve">31.9550952911377</t>
@@ -2627,28 +2627,28 @@
     <t xml:space="preserve">33.2680549621582</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1755409240723</t>
+    <t xml:space="preserve">34.175537109375</t>
   </si>
   <si>
     <t xml:space="preserve">34.1562309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1795692443848</t>
+    <t xml:space="preserve">33.9245376586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1795654296875</t>
   </si>
   <si>
     <t xml:space="preserve">35.3726501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3879280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5810127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2761077880859</t>
+    <t xml:space="preserve">34.3879318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5810089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2761116027832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">34.8706359863281</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7547912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0444068908691</t>
+    <t xml:space="preserve">34.7547874450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6429595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0444107055664</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
@@ -2672,22 +2672,22 @@
     <t xml:space="preserve">34.4651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6003227233887</t>
+    <t xml:space="preserve">34.6003189086914</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4957237243652</t>
+    <t xml:space="preserve">32.495719909668</t>
   </si>
   <si>
     <t xml:space="preserve">33.0556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.059684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5383720397949</t>
+    <t xml:space="preserve">34.0596923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5383682250977</t>
   </si>
   <si>
     <t xml:space="preserve">34.291389465332</t>
@@ -2696,13 +2696,13 @@
     <t xml:space="preserve">33.6542205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9977416992188</t>
+    <t xml:space="preserve">32.9977378845215</t>
   </si>
   <si>
     <t xml:space="preserve">33.7314491271973</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3066711425781</t>
+    <t xml:space="preserve">33.3066673278809</t>
   </si>
   <si>
     <t xml:space="preserve">33.6349105834961</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">32.9591217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8971710205078</t>
+    <t xml:space="preserve">31.8971748352051</t>
   </si>
   <si>
     <t xml:space="preserve">32.0709419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">32.437801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3452911376953</t>
+    <t xml:space="preserve">32.4377975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.345287322998</t>
   </si>
   <si>
     <t xml:space="preserve">33.210132598877</t>
@@ -2735,19 +2735,19 @@
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824562072754</t>
+    <t xml:space="preserve">33.9824600219727</t>
   </si>
   <si>
     <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4458541870117</t>
+    <t xml:space="preserve">34.445858001709</t>
   </si>
   <si>
     <t xml:space="preserve">34.0983085632324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5962905883789</t>
+    <t xml:space="preserve">33.5962944030762</t>
   </si>
   <si>
     <t xml:space="preserve">33.0749702453613</t>
@@ -2759,22 +2759,22 @@
     <t xml:space="preserve">33.4418296813965</t>
   </si>
   <si>
-    <t xml:space="preserve">32.881893157959</t>
+    <t xml:space="preserve">32.8818893432617</t>
   </si>
   <si>
     <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6775550842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5351676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8360481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4000129699707</t>
+    <t xml:space="preserve">34.677547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5351715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8360443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.400016784668</t>
   </si>
   <si>
     <t xml:space="preserve">36.4925270080566</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">37.1490058898926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2994422912598</t>
+    <t xml:space="preserve">36.2994384765625</t>
   </si>
   <si>
     <t xml:space="preserve">36.2801361083984</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043472290039</t>
+    <t xml:space="preserve">35.6043510437012</t>
   </si>
   <si>
     <t xml:space="preserve">35.565731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3919563293457</t>
+    <t xml:space="preserve">35.3919525146484</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
@@ -2810,13 +2810,13 @@
     <t xml:space="preserve">37.0331573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3807067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5158615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5198936462402</t>
+    <t xml:space="preserve">37.3807029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5158576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">39.581844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9100761413574</t>
+    <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
     <t xml:space="preserve">40.2383193969727</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">39.2149810791016</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9527206420898</t>
+    <t xml:space="preserve">40.9527244567871</t>
   </si>
   <si>
     <t xml:space="preserve">41.1458015441895</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">41.7057418823242</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4587669372559</t>
+    <t xml:space="preserve">42.4587631225586</t>
   </si>
   <si>
     <t xml:space="preserve">41.9567489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5319747924805</t>
+    <t xml:space="preserve">41.5319671630859</t>
   </si>
   <si>
     <t xml:space="preserve">41.3388862609863</t>
@@ -2870,43 +2870,43 @@
     <t xml:space="preserve">40.5665550231934</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3429183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878868103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2809600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3236045837402</t>
+    <t xml:space="preserve">42.3429145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2809638977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3236083984375</t>
   </si>
   <si>
     <t xml:space="preserve">42.4008369445801</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6711578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256149291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8875694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5786437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9841156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8489532470703</t>
+    <t xml:space="preserve">42.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.887565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5786361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9841117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8489570617676</t>
   </si>
   <si>
     <t xml:space="preserve">45.3743057250977</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">47.3244361877441</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7669219970703</t>
+    <t xml:space="preserve">49.7669258117676</t>
   </si>
   <si>
     <t xml:space="preserve">49.9600067138672</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">47.4982109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4748725891113</t>
+    <t xml:space="preserve">46.4748687744141</t>
   </si>
   <si>
     <t xml:space="preserve">45.8183898925781</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">47.4016647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">48.01953125</t>
+    <t xml:space="preserve">48.0195350646973</t>
   </si>
   <si>
     <t xml:space="preserve">48.3188056945801</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.691291809082</t>
+    <t xml:space="preserve">47.6912879943848</t>
   </si>
   <si>
     <t xml:space="preserve">47.7878303527832</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">47.3051223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6140556335449</t>
+    <t xml:space="preserve">47.6140594482422</t>
   </si>
   <si>
     <t xml:space="preserve">48.2705345153809</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.539249420166</t>
+    <t xml:space="preserve">50.5392532348633</t>
   </si>
   <si>
     <t xml:space="preserve">47.8457565307617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2842140197754</t>
+    <t xml:space="preserve">49.2842178344727</t>
   </si>
   <si>
     <t xml:space="preserve">49.6221122741699</t>
@@ -3005,28 +3005,28 @@
     <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9422988891602</t>
+    <t xml:space="preserve">47.4209747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9422950744629</t>
   </si>
   <si>
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3807601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2978973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4909782409668</t>
+    <t xml:space="preserve">47.9809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3807563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0082778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2978935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4909820556641</t>
   </si>
   <si>
     <t xml:space="preserve">54.4974365234375</t>
@@ -3044,34 +3044,34 @@
     <t xml:space="preserve">52.9045066833496</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6768379211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0975914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0010528564453</t>
+    <t xml:space="preserve">53.6768341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0975875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
     <t xml:space="preserve">52.8562393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0356369018555</t>
+    <t xml:space="preserve">52.0356407165527</t>
   </si>
   <si>
     <t xml:space="preserve">51.601203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7105979919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0774536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.173999786377</t>
+    <t xml:space="preserve">47.7105941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6567001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0774574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1739959716797</t>
   </si>
   <si>
     <t xml:space="preserve">47.9616050720215</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4402847290039</t>
+    <t xml:space="preserve">47.4402809143066</t>
   </si>
   <si>
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996543884277</t>
+    <t xml:space="preserve">46.8996505737305</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590278625488</t>
@@ -3095,43 +3095,43 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3010940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5907249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8031120300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8071365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6446151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.895622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1659469604492</t>
+    <t xml:space="preserve">45.5287742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5907173156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8071403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6446189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8956298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1659393310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3163757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4129219055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4322280883789</t>
+    <t xml:space="preserve">45.9149360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3163795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4129180908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4322319030762</t>
   </si>
   <si>
     <t xml:space="preserve">46.0887107849121</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">47.1699714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0388336181641</t>
+    <t xml:space="preserve">48.0388374328613</t>
   </si>
   <si>
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4290351867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5875244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1321792602539</t>
+    <t xml:space="preserve">49.429027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5875282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1321754455566</t>
   </si>
   <si>
     <t xml:space="preserve">51.6977424621582</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">56.1869010925293</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1659927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.145092010498</t>
+    <t xml:space="preserve">58.1659965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1450881958008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7106552124023</t>
+    <t xml:space="preserve">59.7106513977051</t>
   </si>
   <si>
     <t xml:space="preserve">60.6277923583984</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">58.021183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0694580078125</t>
+    <t xml:space="preserve">58.0694541931152</t>
   </si>
   <si>
     <t xml:space="preserve">56.6213417053223</t>
@@ -3203,16 +3203,16 @@
     <t xml:space="preserve">55.849006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">56.283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4354782104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4491691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9664573669434</t>
+    <t xml:space="preserve">56.2834434509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4354858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4491653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9664611816406</t>
   </si>
   <si>
     <t xml:space="preserve">54.7870597839355</t>
@@ -3221,22 +3221,22 @@
     <t xml:space="preserve">53.5802993774414</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0147285461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9318733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4282569885254</t>
+    <t xml:space="preserve">54.0147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9318695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4282608032227</t>
   </si>
   <si>
     <t xml:space="preserve">55.0284118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3872108459473</t>
+    <t xml:space="preserve">54.2078132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3872146606445</t>
   </si>
   <si>
     <t xml:space="preserve">51.9873657226562</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7733764648438</t>
+    <t xml:space="preserve">53.773380279541</t>
   </si>
   <si>
     <t xml:space="preserve">54.9801406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2351760864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3453979492188</t>
+    <t xml:space="preserve">56.2351722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.345401763916</t>
   </si>
   <si>
     <t xml:space="preserve">58.5038909912109</t>
@@ -3263,28 +3263,28 @@
     <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9656867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0139579772949</t>
+    <t xml:space="preserve">60.965690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0139617919922</t>
   </si>
   <si>
     <t xml:space="preserve">61.303581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3864402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6969718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420913696289</t>
+    <t xml:space="preserve">60.3864364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6969680786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420951843262</t>
   </si>
   <si>
     <t xml:space="preserve">58.4073524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">55.221492767334</t>
+    <t xml:space="preserve">55.2214965820312</t>
   </si>
   <si>
     <t xml:space="preserve">54.0629997253418</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">50.8288764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8908271789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0565452575684</t>
+    <t xml:space="preserve">51.8908309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0565490722656</t>
   </si>
   <si>
     <t xml:space="preserve">49.2359466552734</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4837608337402</t>
+    <t xml:space="preserve">53.483757019043</t>
   </si>
   <si>
     <t xml:space="preserve">51.8425598144531</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1184997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.37353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1804504394531</t>
+    <t xml:space="preserve">51.1184959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1804466247559</t>
   </si>
   <si>
     <t xml:space="preserve">50.3461685180664</t>
@@ -3338,46 +3338,46 @@
     <t xml:space="preserve">51.4563941955566</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9254150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7186508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0074462890625</t>
+    <t xml:space="preserve">50.9254188537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7806015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7186546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0074501037598</t>
   </si>
   <si>
     <t xml:space="preserve">46.3976402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763160705566</t>
+    <t xml:space="preserve">45.8763198852539</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423439025879</t>
+    <t xml:space="preserve">41.2423477172852</t>
   </si>
   <si>
     <t xml:space="preserve">40.4893226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">42.555305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.149829864502</t>
+    <t xml:space="preserve">42.5553092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1498336791992</t>
   </si>
   <si>
     <t xml:space="preserve">45.5480766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8224220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2633094787598</t>
+    <t xml:space="preserve">46.8224182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2633056640625</t>
   </si>
   <si>
     <t xml:space="preserve">51.7942886352539</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">50.8771476745605</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0219535827637</t>
+    <t xml:space="preserve">51.0219612121582</t>
   </si>
   <si>
     <t xml:space="preserve">49.911735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6486434936523</t>
+    <t xml:space="preserve">46.6486473083496</t>
   </si>
   <si>
     <t xml:space="preserve">45.2970695495605</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">46.9961929321289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4169502258301</t>
+    <t xml:space="preserve">46.4169464111328</t>
   </si>
   <si>
     <t xml:space="preserve">44.9495239257812</t>
@@ -3419,28 +3419,28 @@
     <t xml:space="preserve">41.647819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8063087463379</t>
+    <t xml:space="preserve">42.8063125610352</t>
   </si>
   <si>
     <t xml:space="preserve">44.119270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0348129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.157886505127</t>
+    <t xml:space="preserve">45.6253089904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0348091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.837703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1578903198242</t>
   </si>
   <si>
     <t xml:space="preserve">43.4627914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1254501342773</t>
+    <t xml:space="preserve">44.1254539489746</t>
   </si>
   <si>
     <t xml:space="preserve">42.3908386230469</t>
@@ -3452,28 +3452,28 @@
     <t xml:space="preserve">43.4043235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">44.827091217041</t>
+    <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
     <t xml:space="preserve">46.444766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">45.431282043457</t>
+    <t xml:space="preserve">45.4312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9380264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.645679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3923072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5092468261719</t>
+    <t xml:space="preserve">45.9380226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6456756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3923110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5092506408691</t>
   </si>
   <si>
     <t xml:space="preserve">44.3983154296875</t>
@@ -3506,40 +3506,40 @@
     <t xml:space="preserve">40.3248977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8706130981445</t>
+    <t xml:space="preserve">40.8706169128418</t>
   </si>
   <si>
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7806396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0924797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8841018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9620628356934</t>
+    <t xml:space="preserve">41.8646087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7806434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8840980529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9620590209961</t>
   </si>
   <si>
     <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0025024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3593368530273</t>
+    <t xml:space="preserve">45.0025062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507789611816</t>
+    <t xml:space="preserve">45.4507751464844</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">49.1636276245117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1381340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8202857971191</t>
+    <t xml:space="preserve">50.1381301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8202819824219</t>
   </si>
   <si>
     <t xml:space="preserve">51.2100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7460594177246</t>
+    <t xml:space="preserve">51.7460556030273</t>
   </si>
   <si>
     <t xml:space="preserve">50.9177322387695</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517112731934</t>
+    <t xml:space="preserve">55.3517150878906</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">54.1335868835449</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1080932617188</t>
+    <t xml:space="preserve">55.1080894470215</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
@@ -3608,16 +3608,16 @@
     <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4004364013672</t>
+    <t xml:space="preserve">55.4004402160645</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5466156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4746704101562</t>
+    <t xml:space="preserve">55.5466194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.474666595459</t>
   </si>
   <si>
     <t xml:space="preserve">53.0616416931152</t>
@@ -3626,49 +3626,49 @@
     <t xml:space="preserve">52.5743865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5256576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4792022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7970542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.356258392334</t>
+    <t xml:space="preserve">52.5256614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4792098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7970504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3562622070312</t>
   </si>
   <si>
     <t xml:space="preserve">50.8690071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.771556854248</t>
+    <t xml:space="preserve">50.7715530395508</t>
   </si>
   <si>
     <t xml:space="preserve">51.0151824951172</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5024299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384101867676</t>
+    <t xml:space="preserve">51.5024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384140014648</t>
   </si>
   <si>
     <t xml:space="preserve">51.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5998878479004</t>
+    <t xml:space="preserve">51.5998802185059</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3817558288574</t>
+    <t xml:space="preserve">50.3817596435547</t>
   </si>
   <si>
     <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8015937805176</t>
+    <t xml:space="preserve">45.8015975952148</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">46.8345718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5362129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7738304138184</t>
+    <t xml:space="preserve">47.5362091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7738265991211</t>
   </si>
   <si>
     <t xml:space="preserve">47.7311096191406</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">49.7483291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4522438049316</t>
+    <t xml:space="preserve">48.4522399902344</t>
   </si>
   <si>
     <t xml:space="preserve">48.871280670166</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">49.3585319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4559783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3029937744141</t>
+    <t xml:space="preserve">49.455982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3029899597168</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242279052734</t>
+    <t xml:space="preserve">60.2242240905762</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4468994140625</t>
+    <t xml:space="preserve">57.4468955993652</t>
   </si>
   <si>
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494491577148</t>
+    <t xml:space="preserve">57.3494415283203</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3737,40 +3737,40 @@
     <t xml:space="preserve">55.1568145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6927947998047</t>
+    <t xml:space="preserve">55.6927909851074</t>
   </si>
   <si>
     <t xml:space="preserve">56.5698432922363</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1522750854492</t>
+    <t xml:space="preserve">59.152271270752</t>
   </si>
   <si>
     <t xml:space="preserve">60.8576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0038299560547</t>
+    <t xml:space="preserve">61.0038261413574</t>
   </si>
   <si>
     <t xml:space="preserve">58.8111991882324</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6395225524902</t>
+    <t xml:space="preserve">59.6395263671875</t>
   </si>
   <si>
     <t xml:space="preserve">58.8599281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2497253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9828720092773</t>
+    <t xml:space="preserve">59.2497215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9828758239746</t>
   </si>
   <si>
     <t xml:space="preserve">58.4213981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6882476806641</t>
+    <t xml:space="preserve">59.6882514953613</t>
   </si>
   <si>
     <t xml:space="preserve">61.2961807250977</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">62.319408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0502815246582</t>
+    <t xml:space="preserve">63.0502853393555</t>
   </si>
   <si>
     <t xml:space="preserve">61.3936309814453</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.484260559082</t>
+    <t xml:space="preserve">67.4842681884766</t>
   </si>
   <si>
     <t xml:space="preserve">68.1176910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8230819702148</t>
+    <t xml:space="preserve">69.8230743408203</t>
   </si>
   <si>
     <t xml:space="preserve">70.3590469360352</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">67.1919097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8972930908203</t>
+    <t xml:space="preserve">68.8973007202148</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">65.4865341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5817108154297</t>
+    <t xml:space="preserve">67.5817184448242</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">66.509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1199645996094</t>
+    <t xml:space="preserve">66.1199569702148</t>
   </si>
   <si>
     <t xml:space="preserve">66.8995742797852</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6536636352539</t>
+    <t xml:space="preserve">66.5584945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6536712646484</t>
   </si>
   <si>
     <t xml:space="preserve">69.0434646606445</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">71.4309997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5284576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6978530883789</t>
+    <t xml:space="preserve">71.528450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6978607177734</t>
   </si>
   <si>
     <t xml:space="preserve">75.6700897216797</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.305778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4032287597656</t>
+    <t xml:space="preserve">74.3057861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4032363891602</t>
   </si>
   <si>
     <t xml:space="preserve">75.7188110351562</t>
@@ -3899,25 +3899,25 @@
     <t xml:space="preserve">76.839485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">77.2780227661133</t>
+    <t xml:space="preserve">77.2780151367188</t>
   </si>
   <si>
     <t xml:space="preserve">77.3754653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9879302978516</t>
+    <t xml:space="preserve">74.987922668457</t>
   </si>
   <si>
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627090454102</t>
+    <t xml:space="preserve">77.8627166748047</t>
   </si>
   <si>
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859329223633</t>
+    <t xml:space="preserve">78.8859405517578</t>
   </si>
   <si>
     <t xml:space="preserve">77.5703659057617</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012466430664</t>
+    <t xml:space="preserve">78.3012390136719</t>
   </si>
   <si>
     <t xml:space="preserve">79.032112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4474182128906</t>
+    <t xml:space="preserve">78.4474105834961</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
@@ -3971,28 +3971,28 @@
     <t xml:space="preserve">71.82080078125</t>
   </si>
   <si>
-    <t xml:space="preserve">77.9601593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8162612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.7165374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3964233398438</t>
+    <t xml:space="preserve">77.9601669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8162689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.7165451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3964157104492</t>
   </si>
   <si>
     <t xml:space="preserve">80.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7119903564453</t>
+    <t xml:space="preserve">81.7119979858398</t>
   </si>
   <si>
     <t xml:space="preserve">81.4683685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8581695556641</t>
+    <t xml:space="preserve">81.8581771850586</t>
   </si>
   <si>
     <t xml:space="preserve">81.7607269287109</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">85.268928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1924362182617</t>
+    <t xml:space="preserve">88.1924285888672</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488143920898</t>
+    <t xml:space="preserve">87.9488067626953</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
@@ -4016,16 +4016,16 @@
     <t xml:space="preserve">88.6796875</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9000854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7051849365234</t>
+    <t xml:space="preserve">87.9000778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3408737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434234619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.705192565918</t>
   </si>
   <si>
     <t xml:space="preserve">90.2876129150391</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">87.8513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3618316650391</t>
+    <t xml:space="preserve">89.3618392944336</t>
   </si>
   <si>
     <t xml:space="preserve">86.0972518920898</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360656738281</t>
+    <t xml:space="preserve">88.4360580444336</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
@@ -4055,31 +4055,31 @@
     <t xml:space="preserve">82.1017990112305</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1250305175781</t>
+    <t xml:space="preserve">83.1250228881836</t>
   </si>
   <si>
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559036254883</t>
+    <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0043487548828</t>
+    <t xml:space="preserve">82.0043563842773</t>
   </si>
   <si>
     <t xml:space="preserve">81.4196472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2270278930664</t>
+    <t xml:space="preserve">79.2270202636719</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091644287109</t>
+    <t xml:space="preserve">79.9091720581055</t>
   </si>
   <si>
     <t xml:space="preserve">81.5299453735352</t>
@@ -5682,6 +5682,9 @@
   </si>
   <si>
     <t xml:space="preserve">91.9599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6399993896484</t>
   </si>
 </sst>
 </file>
@@ -71228,7 +71231,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6944212963</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>649330</v>
@@ -71249,6 +71252,32 @@
         <v>1889</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6910532407</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>547435</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>93.7600021362305</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>91.3600006103516</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>92.8199996948242</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>93.6399993896484</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="1895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="1896">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807565689087</t>
+    <t xml:space="preserve">15.1807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">14.171820640564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9476118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208847045898</t>
+    <t xml:space="preserve">13.9476108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289274215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406274795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208875656128</t>
   </si>
   <si>
     <t xml:space="preserve">15.3022022247314</t>
@@ -74,49 +74,49 @@
     <t xml:space="preserve">14.6389198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.087742805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0410299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3212919235229</t>
+    <t xml:space="preserve">14.0877418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0410308837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3212928771973</t>
   </si>
   <si>
     <t xml:space="preserve">14.33997631073</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7697086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3866863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240522384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338026046753</t>
+    <t xml:space="preserve">14.7697095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3866853713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240531921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036649703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433801651001</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155225753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4061813354492</t>
+    <t xml:space="preserve">12.4155235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4061803817749</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172292709351</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">14.1251096725464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9195861816406</t>
+    <t xml:space="preserve">13.9195852279663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0316905975342</t>
@@ -149,55 +149,55 @@
     <t xml:space="preserve">13.7607717514038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8355073928833</t>
+    <t xml:space="preserve">13.8355083465576</t>
   </si>
   <si>
     <t xml:space="preserve">14.1064262390137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2372131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2558975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4143056869507</t>
+    <t xml:space="preserve">14.2372140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.255898475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.414306640625</t>
   </si>
   <si>
     <t xml:space="preserve">15.6011457443237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.246150970459</t>
+    <t xml:space="preserve">15.2461490631104</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060190200806</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3769378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5450925827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104879379272</t>
+    <t xml:space="preserve">15.3769388198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4797010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.545093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104898452759</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983835220337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873355865479</t>
+    <t xml:space="preserve">15.0873346328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.9939155578613</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">14.6202363967896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1527290344238</t>
+    <t xml:space="preserve">15.1527299880981</t>
   </si>
   <si>
     <t xml:space="preserve">15.3302268981934</t>
@@ -215,37 +215,37 @@
     <t xml:space="preserve">15.5918045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7225904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253545761108</t>
+    <t xml:space="preserve">15.7225933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412767410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253536224365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3017978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3952178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3485088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2550868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4139022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924575805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671894073486</t>
+    <t xml:space="preserve">16.3952159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3485069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4139003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215377807617</t>
@@ -260,19 +260,19 @@
     <t xml:space="preserve">16.3391628265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325828552246</t>
+    <t xml:space="preserve">16.114953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325866699219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100826263428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6474514007568</t>
+    <t xml:space="preserve">16.6474494934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.6287670135498</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">16.4419288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889831542969</t>
+    <t xml:space="preserve">16.4889850616455</t>
   </si>
   <si>
     <t xml:space="preserve">16.6489810943604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5548648834229</t>
+    <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207447052002</t>
@@ -299,67 +299,67 @@
     <t xml:space="preserve">16.6866264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583938598633</t>
+    <t xml:space="preserve">16.7054481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
   </si>
   <si>
     <t xml:space="preserve">16.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183898925781</t>
+    <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.689003944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4725399017334</t>
+    <t xml:space="preserve">15.6890068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.472541809082</t>
   </si>
   <si>
     <t xml:space="preserve">15.7078285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3407773971558</t>
+    <t xml:space="preserve">15.3407783508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.583101272583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.253698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.564281463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090187072754</t>
+    <t xml:space="preserve">16.6113357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2536964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290098190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678453445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748975753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090167999268</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101861953735</t>
@@ -368,46 +368,46 @@
     <t xml:space="preserve">14.7854986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3149242401123</t>
+    <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
     <t xml:space="preserve">14.644326210022</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9172611236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195960998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348936080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854768753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301792144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337043762207</t>
+    <t xml:space="preserve">14.9172601699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301773071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.547833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.933705329895</t>
   </si>
   <si>
     <t xml:space="preserve">15.6701812744141</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">15.5007743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6419486999512</t>
+    <t xml:space="preserve">15.6419506072998</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148836135864</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">16.0278186798096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2725200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3195781707764</t>
+    <t xml:space="preserve">16.2725219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3195762634277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819309234619</t>
@@ -440,52 +440,52 @@
     <t xml:space="preserve">16.1595802307129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.460750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078086853027</t>
+    <t xml:space="preserve">16.3760433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078067779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301593780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4701633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7807426452637</t>
+    <t xml:space="preserve">16.4701614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7807388305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.8560333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.98779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9313259124756</t>
+    <t xml:space="preserve">16.9877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0160274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.931324005127</t>
   </si>
   <si>
     <t xml:space="preserve">16.9783840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.846622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936786651611</t>
+    <t xml:space="preserve">16.8466205596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936824798584</t>
   </si>
   <si>
     <t xml:space="preserve">16.6960391998291</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">16.7713298797607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8089752197266</t>
+    <t xml:space="preserve">16.8089790344238</t>
   </si>
   <si>
     <t xml:space="preserve">16.4231052398682</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">16.8842697143555</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7525062561035</t>
+    <t xml:space="preserve">16.7525081634521</t>
   </si>
   <si>
     <t xml:space="preserve">16.9030914306641</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972076416016</t>
+    <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
     <t xml:space="preserve">17.0536766052246</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">16.8748588562012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0348529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654460906982</t>
+    <t xml:space="preserve">17.0348510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654441833496</t>
   </si>
   <si>
     <t xml:space="preserve">16.7619171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0724964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007347106934</t>
+    <t xml:space="preserve">17.0724983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2324924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2607288360596</t>
+    <t xml:space="preserve">17.2607307434082</t>
   </si>
   <si>
     <t xml:space="preserve">17.2136726379395</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">17.3548450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3642559051514</t>
+    <t xml:space="preserve">17.3642539978027</t>
   </si>
   <si>
     <t xml:space="preserve">17.3077869415283</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.804220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430358886719</t>
+    <t xml:space="preserve">18.8042163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406753540039</t>
@@ -590,73 +590,73 @@
     <t xml:space="preserve">19.3783206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9359817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2183265686035</t>
+    <t xml:space="preserve">18.9359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2183246612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159679412842</t>
+    <t xml:space="preserve">19.4159641265869</t>
   </si>
   <si>
     <t xml:space="preserve">20.2724170684814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4230003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.234769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535953521729</t>
+    <t xml:space="preserve">20.423002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2347717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982929229736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3571186065674</t>
+    <t xml:space="preserve">20.357120513916</t>
   </si>
   <si>
     <t xml:space="preserve">20.893575668335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7453689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.519495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6889019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171363830566</t>
+    <t xml:space="preserve">20.6676979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7453708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5194931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6889038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.717134475708</t>
   </si>
   <si>
     <t xml:space="preserve">19.84889793396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.575963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630241394043</t>
+    <t xml:space="preserve">19.5759620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630260467529</t>
   </si>
   <si>
     <t xml:space="preserve">19.2747936248779</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3877372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3500900268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0018615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053886413574</t>
+    <t xml:space="preserve">19.3877334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3500862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3971462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.001859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053867340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.9171581268311</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">19.0865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8701000213623</t>
+    <t xml:space="preserve">18.8700981140137</t>
   </si>
   <si>
     <t xml:space="preserve">18.4936389923096</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">18.2865867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559719085693</t>
+    <t xml:space="preserve">18.6254024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">19.510082244873</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">19.7547836303711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7924289703369</t>
+    <t xml:space="preserve">19.7924308776855</t>
   </si>
   <si>
     <t xml:space="preserve">19.5947875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6018199920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.298267364502</t>
+    <t xml:space="preserve">20.6018180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1853351593018</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">21.0159244537354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253372192383</t>
+    <t xml:space="preserve">20.9029846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253391265869</t>
   </si>
   <si>
     <t xml:space="preserve">20.9876918792725</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100406646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112071990967</t>
+    <t xml:space="preserve">21.1100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112091064453</t>
   </si>
   <si>
     <t xml:space="preserve">21.608850479126</t>
@@ -779,37 +779,37 @@
     <t xml:space="preserve">21.2135696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3829746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429668426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8347301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0229606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8064975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0417823791504</t>
+    <t xml:space="preserve">21.3829765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429706573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8347320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0229625701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8064918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.041784286499</t>
   </si>
   <si>
     <t xml:space="preserve">22.2582473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476463317871</t>
+    <t xml:space="preserve">22.6817665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
   </si>
   <si>
     <t xml:space="preserve">22.6252975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0394058227539</t>
+    <t xml:space="preserve">23.0394020080566</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288227081299</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">21.6464977264404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.91943359375</t>
+    <t xml:space="preserve">21.9194316864014</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">21.3076820373535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1170749664307</t>
+    <t xml:space="preserve">22.117073059082</t>
   </si>
   <si>
     <t xml:space="preserve">22.098123550415</t>
@@ -857,61 +857,61 @@
     <t xml:space="preserve">22.0507411956787</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190837860107</t>
+    <t xml:space="preserve">21.7190780639648</t>
   </si>
   <si>
     <t xml:space="preserve">22.0886459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.756986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6811771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5769386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7285556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200843811035</t>
+    <t xml:space="preserve">21.7569847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327960968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6811752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5769424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7285594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200805664062</t>
   </si>
   <si>
     <t xml:space="preserve">21.1315650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4158458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8612232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4632263183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6622257232666</t>
+    <t xml:space="preserve">21.4158496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8612194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4632244110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.662223815918</t>
   </si>
   <si>
     <t xml:space="preserve">21.5674648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5624465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4013557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529727935791</t>
+    <t xml:space="preserve">22.5624485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
     <t xml:space="preserve">22.5813999176025</t>
@@ -920,79 +920,79 @@
     <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5908756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7948894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6717014312744</t>
+    <t xml:space="preserve">22.5908794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7948875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.671703338623</t>
   </si>
   <si>
     <t xml:space="preserve">21.5958919525146</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4676876068115</t>
+    <t xml:space="preserve">22.4676856994629</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5055904388428</t>
+    <t xml:space="preserve">22.5055923461914</t>
   </si>
   <si>
     <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8277759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0362510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2068176269531</t>
+    <t xml:space="preserve">22.8277797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0362491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2068157196045</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9983463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1310138702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5005741119385</t>
+    <t xml:space="preserve">22.998348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.131010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5005760192871</t>
   </si>
   <si>
     <t xml:space="preserve">23.6900978088379</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2731513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404838562012</t>
+    <t xml:space="preserve">23.2731494903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404895782471</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.453197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7709217071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.950963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0646781921387</t>
+    <t xml:space="preserve">23.4531955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7709197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9509658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.06467628479</t>
   </si>
   <si>
     <t xml:space="preserve">22.7519702911377</t>
@@ -1001,34 +1001,34 @@
     <t xml:space="preserve">22.7235412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9793930053711</t>
+    <t xml:space="preserve">22.9793968200684</t>
   </si>
   <si>
     <t xml:space="preserve">22.6477317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4771633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1834087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8796195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1165180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6616668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9035873413086</t>
+    <t xml:space="preserve">22.477165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1834049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.87961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6616687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783924102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.90358543396</t>
   </si>
   <si>
     <t xml:space="preserve">24.0217590332031</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">24.4955615997314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6377010345459</t>
+    <t xml:space="preserve">24.5145111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6377029418945</t>
   </si>
   <si>
     <t xml:space="preserve">24.6850814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5903205871582</t>
+    <t xml:space="preserve">24.5903224945068</t>
   </si>
   <si>
     <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8082714080811</t>
+    <t xml:space="preserve">24.8082695007324</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7229824066162</t>
+    <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">24.5429401397705</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651256561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.547399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915496826172</t>
+    <t xml:space="preserve">24.8651275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5474033355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
   </si>
   <si>
     <t xml:space="preserve">25.4052600860596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4431667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4905414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3863086700439</t>
+    <t xml:space="preserve">25.4431648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4905452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3863105773926</t>
   </si>
   <si>
     <t xml:space="preserve">25.3484039306641</t>
@@ -1100,40 +1100,40 @@
     <t xml:space="preserve">25.3294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0830745697021</t>
+    <t xml:space="preserve">25.0830726623535</t>
   </si>
   <si>
     <t xml:space="preserve">25.727445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">25.661111831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054847717285</t>
+    <t xml:space="preserve">25.6611137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054866790771</t>
   </si>
   <si>
     <t xml:space="preserve">26.8645706176758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.309944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0635643005371</t>
+    <t xml:space="preserve">27.3099460601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
     <t xml:space="preserve">26.6750469207764</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9972343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678028106689</t>
+    <t xml:space="preserve">26.9972362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678047180176</t>
   </si>
   <si>
     <t xml:space="preserve">26.4665775299072</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">26.0591087341309</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0451717376709</t>
+    <t xml:space="preserve">25.0451698303223</t>
   </si>
   <si>
     <t xml:space="preserve">25.1778335571289</t>
@@ -1154,40 +1154,40 @@
     <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1115036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5379238128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9359188079834</t>
+    <t xml:space="preserve">25.1115016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5379219055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9359169006348</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010215759277</t>
+    <t xml:space="preserve">25.301025390625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2631187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1683578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9219799041748</t>
+    <t xml:space="preserve">25.1683597564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9219818115234</t>
   </si>
   <si>
     <t xml:space="preserve">25.206262588501</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042594909668</t>
+    <t xml:space="preserve">25.1020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042575836182</t>
   </si>
   <si>
     <t xml:space="preserve">25.8601112365723</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">26.4381465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">24.798791885376</t>
+    <t xml:space="preserve">24.7987957000732</t>
   </si>
   <si>
     <t xml:space="preserve">25.3673572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3578777313232</t>
+    <t xml:space="preserve">25.3578796386719</t>
   </si>
   <si>
     <t xml:space="preserve">25.6800651550293</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">25.7748241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5947818756104</t>
+    <t xml:space="preserve">25.5947799682617</t>
   </si>
   <si>
     <t xml:space="preserve">25.7084903717041</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">26.8171882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0540904998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3857498168945</t>
+    <t xml:space="preserve">27.0540924072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3857517242432</t>
   </si>
   <si>
     <t xml:space="preserve">25.8695831298828</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">25.8222064971924</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9169654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6326847076416</t>
+    <t xml:space="preserve">25.9169673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.632682800293</t>
   </si>
   <si>
     <t xml:space="preserve">24.7324600219727</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">23.9743785858154</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4007987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0691394805908</t>
+    <t xml:space="preserve">24.4008007049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0691375732422</t>
   </si>
   <si>
     <t xml:space="preserve">24.4481792449951</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7848567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641250610352</t>
+    <t xml:space="preserve">23.7848587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2586574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
     <t xml:space="preserve">25.0167407989502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9693641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9269981384277</t>
+    <t xml:space="preserve">24.9693622589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9269943237305</t>
   </si>
   <si>
     <t xml:space="preserve">26.3433876037598</t>
@@ -1292,34 +1292,34 @@
     <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0117282867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">26.0117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5329074859619</t>
+    <t xml:space="preserve">26.5329055786133</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7698078155518</t>
+    <t xml:space="preserve">26.7698097229004</t>
   </si>
   <si>
     <t xml:space="preserve">28.9492969512939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6176414489746</t>
+    <t xml:space="preserve">28.617639541626</t>
   </si>
   <si>
     <t xml:space="preserve">28.8071594238281</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6650161743164</t>
+    <t xml:space="preserve">28.665018081665</t>
   </si>
   <si>
     <t xml:space="preserve">29.3283405303955</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">30.2086696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.065279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042659759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9696788787842</t>
+    <t xml:space="preserve">30.0652770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042678833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9696769714355</t>
   </si>
   <si>
     <t xml:space="preserve">30.113073348999</t>
@@ -1349,31 +1349,31 @@
     <t xml:space="preserve">31.2602386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7419929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.135684967041</t>
+    <t xml:space="preserve">32.7419967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797142028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
     <t xml:space="preserve">34.4149475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9369583129883</t>
+    <t xml:space="preserve">33.936954498291</t>
   </si>
   <si>
     <t xml:space="preserve">34.1759490966797</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9885215759277</t>
+    <t xml:space="preserve">34.9885177612305</t>
   </si>
   <si>
     <t xml:space="preserve">35.753303527832</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">35.2275123596191</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0841217041016</t>
+    <t xml:space="preserve">35.0841255187988</t>
   </si>
   <si>
     <t xml:space="preserve">35.6576995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2753143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4224739074707</t>
+    <t xml:space="preserve">35.275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
     <t xml:space="preserve">36.3746795654297</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">35.4187088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5658760070801</t>
+    <t xml:space="preserve">36.5658721923828</t>
   </si>
   <si>
     <t xml:space="preserve">36.8526649475098</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">30.7822551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168403625488</t>
+    <t xml:space="preserve">31.1168422698975</t>
   </si>
   <si>
     <t xml:space="preserve">31.4036331176758</t>
@@ -1427,19 +1427,19 @@
     <t xml:space="preserve">31.3558349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2124366760254</t>
+    <t xml:space="preserve">31.212438583374</t>
   </si>
   <si>
     <t xml:space="preserve">33.0287818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7935600280762</t>
+    <t xml:space="preserve">33.7935562133789</t>
   </si>
   <si>
     <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7973327636719</t>
+    <t xml:space="preserve">34.7973289489746</t>
   </si>
   <si>
     <t xml:space="preserve">34.3671417236328</t>
@@ -1448,37 +1448,37 @@
     <t xml:space="preserve">34.6539344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">35.036319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6061401367188</t>
+    <t xml:space="preserve">35.0363273620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6061363220215</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7495269775391</t>
+    <t xml:space="preserve">33.8413619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7495307922363</t>
   </si>
   <si>
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0400924682617</t>
+    <t xml:space="preserve">36.0400886535645</t>
   </si>
   <si>
     <t xml:space="preserve">35.8966941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6614685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306503295898</t>
+    <t xml:space="preserve">36.6614646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306465148926</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180778503418</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">37.8564300537109</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2790832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.235050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8929214477539</t>
+    <t xml:space="preserve">36.2790870666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2350540161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8929290771484</t>
   </si>
   <si>
     <t xml:space="preserve">34.5583381652832</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">33.6979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.506763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2677764892578</t>
+    <t xml:space="preserve">33.5067672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2677726745605</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640075683594</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">32.3596038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690441131592</t>
+    <t xml:space="preserve">32.072811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7860202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690422058105</t>
   </si>
   <si>
     <t xml:space="preserve">32.025016784668</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">31.0212459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8816165924072</t>
+    <t xml:space="preserve">31.8816146850586</t>
   </si>
   <si>
     <t xml:space="preserve">28.8703136444092</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2489280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5797519683838</t>
+    <t xml:space="preserve">28.4401226043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.248929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5797500610352</t>
   </si>
   <si>
     <t xml:space="preserve">28.1055335998535</t>
@@ -1592,34 +1592,34 @@
     <t xml:space="preserve">27.9621391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3445281982422</t>
+    <t xml:space="preserve">28.3445262908936</t>
   </si>
   <si>
     <t xml:space="preserve">29.0137062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9181098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2049007415771</t>
+    <t xml:space="preserve">28.9181118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2049026489258</t>
   </si>
   <si>
     <t xml:space="preserve">30.4954605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5872898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344570159912</t>
+    <t xml:space="preserve">29.5872917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344551086426</t>
   </si>
   <si>
     <t xml:space="preserve">30.0174751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4438934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6828842163086</t>
+    <t xml:space="preserve">29.4438915252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6828861236572</t>
   </si>
   <si>
     <t xml:space="preserve">28.5835208892822</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">26.5759830474854</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3847885131836</t>
+    <t xml:space="preserve">26.384786605835</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929592132568</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">27.4363574981689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8187446594238</t>
+    <t xml:space="preserve">27.8187408447266</t>
   </si>
   <si>
     <t xml:space="preserve">27.7231483459473</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">26.8627738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4841556549072</t>
+    <t xml:space="preserve">27.48415184021</t>
   </si>
   <si>
     <t xml:space="preserve">27.0061683654785</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">26.0979957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6200103759766</t>
+    <t xml:space="preserve">25.6200122833252</t>
   </si>
   <si>
     <t xml:space="preserve">26.1935939788818</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">25.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2891941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671756744385</t>
+    <t xml:space="preserve">26.2891902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671737670898</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">28.9659080505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6791191101074</t>
+    <t xml:space="preserve">28.6791172027588</t>
   </si>
   <si>
     <t xml:space="preserve">29.1093044281006</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">26.6715793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8149738311768</t>
+    <t xml:space="preserve">26.8149757385254</t>
   </si>
   <si>
     <t xml:space="preserve">26.4803886413574</t>
   </si>
   <si>
-    <t xml:space="preserve">27.388557434082</t>
+    <t xml:space="preserve">27.3885555267334</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8740825653076</t>
+    <t xml:space="preserve">29.874080657959</t>
   </si>
   <si>
     <t xml:space="preserve">30.1608715057373</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080387115479</t>
+    <t xml:space="preserve">31.3080368041992</t>
   </si>
   <si>
     <t xml:space="preserve">31.45143699646</t>
@@ -1751,28 +1751,28 @@
     <t xml:space="preserve">30.5910587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3004970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409980773926</t>
+    <t xml:space="preserve">29.3004989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409999847412</t>
   </si>
   <si>
     <t xml:space="preserve">30.6484203338623</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8204956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9734516143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2851467132568</t>
+    <t xml:space="preserve">30.8204936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9734497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2851486206055</t>
   </si>
   <si>
     <t xml:space="preserve">30.0748329162598</t>
   </si>
   <si>
-    <t xml:space="preserve">30.47633934021</t>
+    <t xml:space="preserve">30.4763412475586</t>
   </si>
   <si>
     <t xml:space="preserve">30.2277889251709</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">29.7115650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">28.812952041626</t>
+    <t xml:space="preserve">28.8129539489746</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203704833984</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">29.4821319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1762237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3291797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761566162109</t>
+    <t xml:space="preserve">29.1762218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761585235596</t>
   </si>
   <si>
     <t xml:space="preserve">28.9237060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6533889770508</t>
+    <t xml:space="preserve">28.6533908843994</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058414459229</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">28.3637657165527</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5182342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8038272857666</t>
+    <t xml:space="preserve">28.5182323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8038291931152</t>
   </si>
   <si>
     <t xml:space="preserve">28.0741443634033</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">27.2245845794678</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2052764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3211231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6493625640869</t>
+    <t xml:space="preserve">27.2052745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3211212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5335140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6493606567383</t>
   </si>
   <si>
     <t xml:space="preserve">27.9776020050049</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">27.8617534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7845211029053</t>
+    <t xml:space="preserve">27.7845230102539</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548343658447</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">27.9969120025635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4989261627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.247917175293</t>
+    <t xml:space="preserve">28.4989242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2479190826416</t>
   </si>
   <si>
     <t xml:space="preserve">28.3251514434814</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9003677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0934524536133</t>
+    <t xml:space="preserve">27.900369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0934505462646</t>
   </si>
   <si>
     <t xml:space="preserve">28.6340808868408</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">29.7539596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2173538208008</t>
+    <t xml:space="preserve">30.2173557281494</t>
   </si>
   <si>
     <t xml:space="preserve">29.9856567382812</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">29.4836444854736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1747131347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4257183074951</t>
+    <t xml:space="preserve">29.174711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4257202148438</t>
   </si>
   <si>
     <t xml:space="preserve">29.2519454956055</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">28.4796161651611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7652130126953</t>
+    <t xml:space="preserve">27.7652111053467</t>
   </si>
   <si>
     <t xml:space="preserve">27.1666584014893</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.683952331543</t>
+    <t xml:space="preserve">26.6839542388916</t>
   </si>
   <si>
     <t xml:space="preserve">26.5101795196533</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">27.0314998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6260280609131</t>
+    <t xml:space="preserve">26.6260299682617</t>
   </si>
   <si>
     <t xml:space="preserve">27.4176635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.035530090332</t>
+    <t xml:space="preserve">28.0355281829834</t>
   </si>
   <si>
     <t xml:space="preserve">27.0894241333008</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">27.4755878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7072906494141</t>
+    <t xml:space="preserve">27.7072887420654</t>
   </si>
   <si>
     <t xml:space="preserve">27.591438293457</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">27.3018169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4562816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8577270507812</t>
+    <t xml:space="preserve">27.4562835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8577251434326</t>
   </si>
   <si>
     <t xml:space="preserve">25.7957725524902</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">28.3830738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9430141448975</t>
+    <t xml:space="preserve">28.9430122375488</t>
   </si>
   <si>
     <t xml:space="preserve">29.4064102172852</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">28.8078575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9816303253174</t>
+    <t xml:space="preserve">28.981632232666</t>
   </si>
   <si>
     <t xml:space="preserve">29.1360969543457</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">28.7499313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8271675109863</t>
+    <t xml:space="preserve">28.8271656036377</t>
   </si>
   <si>
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954647064209</t>
+    <t xml:space="preserve">28.5954666137695</t>
   </si>
   <si>
     <t xml:space="preserve">28.6147727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2133293151855</t>
+    <t xml:space="preserve">29.2133312225342</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">32.3026428222656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4571113586426</t>
+    <t xml:space="preserve">32.4571075439453</t>
   </si>
   <si>
     <t xml:space="preserve">31.8585548400879</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">32.1674842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2600002288818</t>
+    <t xml:space="preserve">31.2600021362305</t>
   </si>
   <si>
     <t xml:space="preserve">31.5882396697998</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">31.1248455047607</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3565425872803</t>
+    <t xml:space="preserve">31.356538772583</t>
   </si>
   <si>
     <t xml:space="preserve">30.8545246124268</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">31.3372325897217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4683628082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0089893341064</t>
+    <t xml:space="preserve">30.4683609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0089912414551</t>
   </si>
   <si>
     <t xml:space="preserve">30.7000598907471</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">33.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">33.885913848877</t>
+    <t xml:space="preserve">33.8859176635742</t>
   </si>
   <si>
     <t xml:space="preserve">34.8899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0251007080078</t>
+    <t xml:space="preserve">35.0251045227051</t>
   </si>
   <si>
     <t xml:space="preserve">35.9711990356445</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">35.8167343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9864845275879</t>
+    <t xml:space="preserve">34.9864883422852</t>
   </si>
   <si>
     <t xml:space="preserve">33.2873611450195</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9937076568604</t>
+    <t xml:space="preserve">31.9937114715576</t>
   </si>
   <si>
     <t xml:space="preserve">31.6847801208496</t>
@@ -2243,22 +2243,22 @@
     <t xml:space="preserve">32.3605690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3839073181152</t>
+    <t xml:space="preserve">33.383903503418</t>
   </si>
   <si>
     <t xml:space="preserve">32.8432769775391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7427024841309</t>
+    <t xml:space="preserve">31.7427062988281</t>
   </si>
   <si>
     <t xml:space="preserve">32.8239631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9011993408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2447204589844</t>
+    <t xml:space="preserve">32.901195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2447166442871</t>
   </si>
   <si>
     <t xml:space="preserve">32.5343437194824</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">29.811882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9623241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.773265838623</t>
+    <t xml:space="preserve">28.9623222351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8698101043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7732677459717</t>
   </si>
   <si>
     <t xml:space="preserve">30.0049648284912</t>
@@ -2294,31 +2294,31 @@
     <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784767150879</t>
+    <t xml:space="preserve">26.2784786224365</t>
   </si>
   <si>
     <t xml:space="preserve">25.2937622070312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1240139007568</t>
+    <t xml:space="preserve">26.1240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">24.5407428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1931915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9767761230469</t>
+    <t xml:space="preserve">24.1931934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9767742156982</t>
   </si>
   <si>
     <t xml:space="preserve">25.2744541168213</t>
   </si>
   <si>
-    <t xml:space="preserve">25.737850189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150806427002</t>
+    <t xml:space="preserve">25.7378482818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150825500488</t>
   </si>
   <si>
     <t xml:space="preserve">25.100679397583</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">26.8384189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7917499542236</t>
+    <t xml:space="preserve">24.791748046875</t>
   </si>
   <si>
     <t xml:space="preserve">23.8263339996338</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4442005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9075965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0427551269531</t>
+    <t xml:space="preserve">24.4441986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9075946807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0427570343018</t>
   </si>
   <si>
     <t xml:space="preserve">25.6220016479492</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">25.718542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4482250213623</t>
+    <t xml:space="preserve">25.4482269287109</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5487976074219</t>
+    <t xml:space="preserve">26.5487957000732</t>
   </si>
   <si>
     <t xml:space="preserve">26.9349594116211</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">30.0242729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2833366394043</t>
+    <t xml:space="preserve">32.283332824707</t>
   </si>
   <si>
     <t xml:space="preserve">30.4104385375977</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">29.5994930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5721282958984</t>
+    <t xml:space="preserve">27.5721302032471</t>
   </si>
   <si>
     <t xml:space="preserve">26.5681056976318</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">25.5061511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3903007507324</t>
+    <t xml:space="preserve">25.3903026580811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5254592895508</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565895080566</t>
+    <t xml:space="preserve">24.6565914154053</t>
   </si>
   <si>
     <t xml:space="preserve">24.2511196136475</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">23.9421844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1352691650391</t>
+    <t xml:space="preserve">24.1352672576904</t>
   </si>
   <si>
     <t xml:space="preserve">24.1545753479004</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">23.9035682678223</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1505489349365</t>
+    <t xml:space="preserve">23.1505470275879</t>
   </si>
   <si>
     <t xml:space="preserve">23.3822460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.073314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7684135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5946388244629</t>
+    <t xml:space="preserve">23.0733165740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7684116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5946369171143</t>
   </si>
   <si>
     <t xml:space="preserve">23.7877197265625</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">24.2704257965088</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6372814178467</t>
+    <t xml:space="preserve">24.6372833251953</t>
   </si>
   <si>
     <t xml:space="preserve">25.081371307373</t>
@@ -2516,25 +2516,25 @@
     <t xml:space="preserve">26.1047058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0853996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1199893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9462146759033</t>
+    <t xml:space="preserve">26.0853977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.119987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9462127685547</t>
   </si>
   <si>
     <t xml:space="preserve">24.811056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5986652374268</t>
+    <t xml:space="preserve">24.5986671447754</t>
   </si>
   <si>
     <t xml:space="preserve">24.7338237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.984827041626</t>
+    <t xml:space="preserve">24.9848289489746</t>
   </si>
   <si>
     <t xml:space="preserve">24.9269065856934</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">24.6179733276367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4635105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358360290527</t>
+    <t xml:space="preserve">24.463508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358341217041</t>
   </si>
   <si>
     <t xml:space="preserve">25.1392955780029</t>
@@ -2570,28 +2570,28 @@
     <t xml:space="preserve">26.7804927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6067180633545</t>
+    <t xml:space="preserve">26.6067199707031</t>
   </si>
   <si>
     <t xml:space="preserve">26.046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2591705322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4136390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8343906402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7571601867676</t>
+    <t xml:space="preserve">26.2591724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4136371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8343925476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7571582794189</t>
   </si>
   <si>
     <t xml:space="preserve">25.4675331115723</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5600509643555</t>
+    <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689823150635</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">24.772439956665</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1401233673096</t>
+    <t xml:space="preserve">30.1401214599609</t>
   </si>
   <si>
     <t xml:space="preserve">31.7620182037354</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5810089111328</t>
+    <t xml:space="preserve">34.5810127258301</t>
   </si>
   <si>
     <t xml:space="preserve">35.2761077880859</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">34.7547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6429595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0444107055664</t>
+    <t xml:space="preserve">35.6429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0444068908691</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">34.4651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6003265380859</t>
+    <t xml:space="preserve">34.6003227233887</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4957275390625</t>
+    <t xml:space="preserve">32.4957237243652</t>
   </si>
   <si>
     <t xml:space="preserve">33.0556640625</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6542167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9977378845215</t>
+    <t xml:space="preserve">33.6542205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9977416992188</t>
   </si>
   <si>
     <t xml:space="preserve">33.7314491271973</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">32.0709419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4377975463867</t>
+    <t xml:space="preserve">32.437801361084</t>
   </si>
   <si>
     <t xml:space="preserve">33.3452911376953</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2101287841797</t>
+    <t xml:space="preserve">33.210132598877</t>
   </si>
   <si>
     <t xml:space="preserve">33.7893753051758</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824523925781</t>
+    <t xml:space="preserve">33.9824562072754</t>
   </si>
   <si>
     <t xml:space="preserve">33.9631500244141</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">34.4458541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0983047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5962944030762</t>
+    <t xml:space="preserve">34.0983085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5962905883789</t>
   </si>
   <si>
     <t xml:space="preserve">33.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9398155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4418258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8818893432617</t>
+    <t xml:space="preserve">32.939811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4418296813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.881893157959</t>
   </si>
   <si>
     <t xml:space="preserve">32.6115760803223</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">34.6775550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5351715087891</t>
+    <t xml:space="preserve">37.5351676940918</t>
   </si>
   <si>
     <t xml:space="preserve">35.8360481262207</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">37.4000129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4925231933594</t>
+    <t xml:space="preserve">36.4925270080566</t>
   </si>
   <si>
     <t xml:space="preserve">37.1490058898926</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043510437012</t>
+    <t xml:space="preserve">35.6043472290039</t>
   </si>
   <si>
     <t xml:space="preserve">35.565731048584</t>
@@ -2810,13 +2810,13 @@
     <t xml:space="preserve">37.0331573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3807029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5158653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.519889831543</t>
+    <t xml:space="preserve">37.3807067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198936462402</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9100799560547</t>
+    <t xml:space="preserve">39.581844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9100761413574</t>
   </si>
   <si>
     <t xml:space="preserve">40.2383193969727</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">41.1458015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7057456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4587631225586</t>
+    <t xml:space="preserve">41.7057418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4587669372559</t>
   </si>
   <si>
     <t xml:space="preserve">41.9567489624023</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">40.6244850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5665588378906</t>
+    <t xml:space="preserve">40.5665550231934</t>
   </si>
   <si>
     <t xml:space="preserve">42.3429183959961</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">42.8256149291992</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8875732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5786399841309</t>
+    <t xml:space="preserve">43.8875694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5786437988281</t>
   </si>
   <si>
     <t xml:space="preserve">43.9841156005859</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">43.6172561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8489570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3743019104004</t>
+    <t xml:space="preserve">43.8489532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3743057250977</t>
   </si>
   <si>
     <t xml:space="preserve">47.3244361877441</t>
@@ -2969,19 +2969,19 @@
     <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6912879943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7878341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051261901855</t>
+    <t xml:space="preserve">47.691291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051223754883</t>
   </si>
   <si>
     <t xml:space="preserve">47.6140556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2705383300781</t>
+    <t xml:space="preserve">48.2705345153809</t>
   </si>
   <si>
     <t xml:space="preserve">48.8980560302734</t>
@@ -2993,19 +2993,19 @@
     <t xml:space="preserve">47.8457565307617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2842178344727</t>
+    <t xml:space="preserve">49.2842140197754</t>
   </si>
   <si>
     <t xml:space="preserve">49.6221122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6703872680664</t>
+    <t xml:space="preserve">49.6703834533691</t>
   </si>
   <si>
     <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4209747314453</t>
+    <t xml:space="preserve">47.420970916748</t>
   </si>
   <si>
     <t xml:space="preserve">47.9422988891602</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">50.4909782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4974403381348</t>
+    <t xml:space="preserve">54.4974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">53.8699188232422</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">53.6768379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0975952148438</t>
+    <t xml:space="preserve">53.0975914001465</t>
   </si>
   <si>
     <t xml:space="preserve">53.0010528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8562355041504</t>
+    <t xml:space="preserve">52.8562393188477</t>
   </si>
   <si>
     <t xml:space="preserve">52.0356369018555</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">48.0774536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1739959716797</t>
+    <t xml:space="preserve">48.173999786377</t>
   </si>
   <si>
     <t xml:space="preserve">47.9616050720215</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">46.8996543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3590240478516</t>
+    <t xml:space="preserve">46.3590278625488</t>
   </si>
   <si>
     <t xml:space="preserve">45.1426048278809</t>
@@ -3098,19 +3098,19 @@
     <t xml:space="preserve">45.5287704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">46.301097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5907211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.803108215332</t>
+    <t xml:space="preserve">46.3010940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5907249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031120300293</t>
   </si>
   <si>
     <t xml:space="preserve">47.8071365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6446189880371</t>
+    <t xml:space="preserve">45.6446151733398</t>
   </si>
   <si>
     <t xml:space="preserve">45.895622253418</t>
@@ -3131,16 +3131,16 @@
     <t xml:space="preserve">45.4129219055176</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4322319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0887145996094</t>
+    <t xml:space="preserve">45.4322280883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0887107849121</t>
   </si>
   <si>
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699676513672</t>
+    <t xml:space="preserve">47.1699714660645</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388336181641</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4290313720703</t>
+    <t xml:space="preserve">49.4290351867676</t>
   </si>
   <si>
     <t xml:space="preserve">50.5875244140625</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">52.1321792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6977462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1869049072266</t>
+    <t xml:space="preserve">51.6977424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1869010925293</t>
   </si>
   <si>
     <t xml:space="preserve">58.1659927368164</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8490104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2834434509277</t>
+    <t xml:space="preserve">55.849006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.283447265625</t>
   </si>
   <si>
     <t xml:space="preserve">53.4354782104492</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">54.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9664611816406</t>
+    <t xml:space="preserve">53.9664573669434</t>
   </si>
   <si>
     <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5802955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0147323608398</t>
+    <t xml:space="preserve">53.5802993774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0147285461426</t>
   </si>
   <si>
     <t xml:space="preserve">54.9318733215332</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">55.0284118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2078132629395</t>
+    <t xml:space="preserve">54.2078170776367</t>
   </si>
   <si>
     <t xml:space="preserve">53.3872108459473</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">51.9873657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4145812988281</t>
+    <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
     <t xml:space="preserve">53.7733764648438</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">54.9801406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2351722717285</t>
+    <t xml:space="preserve">56.2351760864258</t>
   </si>
   <si>
     <t xml:space="preserve">57.3453979492188</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">60.3864402770996</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6969757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420951843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4073486328125</t>
+    <t xml:space="preserve">58.6969718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4073524475098</t>
   </si>
   <si>
     <t xml:space="preserve">55.221492767334</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">52.2287178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">52.083911895752</t>
+    <t xml:space="preserve">52.0839080810547</t>
   </si>
   <si>
     <t xml:space="preserve">53.1458587646484</t>
@@ -3320,28 +3320,28 @@
     <t xml:space="preserve">51.8425598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6840667724609</t>
+    <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
     <t xml:space="preserve">51.1184997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3735313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1804466247559</t>
+    <t xml:space="preserve">52.37353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1804504394531</t>
   </si>
   <si>
     <t xml:space="preserve">50.3461685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4563903808594</t>
+    <t xml:space="preserve">51.4563941955566</t>
   </si>
   <si>
     <t xml:space="preserve">50.9254150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7806015014648</t>
+    <t xml:space="preserve">50.7806053161621</t>
   </si>
   <si>
     <t xml:space="preserve">49.7186508178711</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">46.3976402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763198852539</t>
+    <t xml:space="preserve">45.8763160705566</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">42.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1498336791992</t>
+    <t xml:space="preserve">42.149829864502</t>
   </si>
   <si>
     <t xml:space="preserve">45.5480766296387</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">51.7942886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5738372802734</t>
+    <t xml:space="preserve">49.5738410949707</t>
   </si>
   <si>
     <t xml:space="preserve">50.8771476745605</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">49.911735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6486473083496</t>
+    <t xml:space="preserve">46.6486434936523</t>
   </si>
   <si>
     <t xml:space="preserve">45.2970695495605</t>
@@ -3410,16 +3410,16 @@
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9495277404785</t>
+    <t xml:space="preserve">44.9495239257812</t>
   </si>
   <si>
     <t xml:space="preserve">43.6751823425293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6478157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8063125610352</t>
+    <t xml:space="preserve">41.647819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8063087463379</t>
   </si>
   <si>
     <t xml:space="preserve">44.119270324707</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">45.6253051757812</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0348091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.837703704834</t>
+    <t xml:space="preserve">47.0348129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
     <t xml:space="preserve">44.157886505127</t>
@@ -5697,6 +5697,9 @@
   </si>
   <si>
     <t xml:space="preserve">85.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9199981689453</t>
   </si>
 </sst>
 </file>
@@ -71373,7 +71376,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6927083333</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>410191</v>
@@ -71394,6 +71397,32 @@
         <v>1894</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6911921296</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>214715</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>87.0400009155273</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>85.3399963378906</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>86.9199981689453</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="1898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1899">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807565689087</t>
+    <t xml:space="preserve">15.1807546615601</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
@@ -47,70 +47,70 @@
     <t xml:space="preserve">14.8537864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4801054000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1718187332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289274215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406274795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208875656128</t>
+    <t xml:space="preserve">14.4801063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.171820640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476127624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208866119385</t>
   </si>
   <si>
     <t xml:space="preserve">15.3022012710571</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.087742805481</t>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0877418518066</t>
   </si>
   <si>
     <t xml:space="preserve">14.0410318374634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3212909698486</t>
+    <t xml:space="preserve">14.3212928771973</t>
   </si>
   <si>
     <t xml:space="preserve">14.3399772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7697086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3866844177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240531921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849805831909</t>
+    <t xml:space="preserve">14.7697095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3866863250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.424054145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849815368652</t>
   </si>
   <si>
     <t xml:space="preserve">14.0036640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.433801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051258087158</t>
+    <t xml:space="preserve">13.4337997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051267623901</t>
   </si>
   <si>
     <t xml:space="preserve">12.4155235290527</t>
@@ -119,25 +119,25 @@
     <t xml:space="preserve">12.4061803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172302246094</t>
+    <t xml:space="preserve">12.8172283172607</t>
   </si>
   <si>
     <t xml:space="preserve">13.5459060668945</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1722269058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645895004272</t>
+    <t xml:space="preserve">13.1722259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
     <t xml:space="preserve">13.4057760238647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251096725464</t>
+    <t xml:space="preserve">13.3777484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251087188721</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195861816406</t>
@@ -149,25 +149,25 @@
     <t xml:space="preserve">13.7607717514038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.835506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.106424331665</t>
+    <t xml:space="preserve">13.8355073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1064252853394</t>
   </si>
   <si>
     <t xml:space="preserve">14.2372140884399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4520807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2558975219727</t>
+    <t xml:space="preserve">14.4520797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558994293213</t>
   </si>
   <si>
     <t xml:space="preserve">15.4143056869507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011457443237</t>
+    <t xml:space="preserve">15.6011447906494</t>
   </si>
   <si>
     <t xml:space="preserve">15.2461500167847</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">15.1060190200806</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3769369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385164260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5450954437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873355865479</t>
+    <t xml:space="preserve">15.3769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4797010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385145187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.545093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4983835220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873365402222</t>
   </si>
   <si>
     <t xml:space="preserve">14.9939155578613</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">14.6202344894409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1527299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.330228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412757873535</t>
+    <t xml:space="preserve">15.1527290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412776947021</t>
   </si>
   <si>
     <t xml:space="preserve">15.8253545761108</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">16.3017997741699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3952140808105</t>
+    <t xml:space="preserve">16.3952178955078</t>
   </si>
   <si>
     <t xml:space="preserve">16.3858757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3485050201416</t>
+    <t xml:space="preserve">16.3485069274902</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550868988037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4139003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924575805664</t>
+    <t xml:space="preserve">16.4139022827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924537658691</t>
   </si>
   <si>
     <t xml:space="preserve">16.3671894073486</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2177200317383</t>
+    <t xml:space="preserve">16.2177181243896</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325847625732</t>
+    <t xml:space="preserve">16.3391628265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325866699219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6474514007568</t>
+    <t xml:space="preserve">16.6474494934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.6287670135498</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">16.4889831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6489810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548648834229</t>
+    <t xml:space="preserve">16.6489791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207466125488</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">16.6866264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054481506348</t>
+    <t xml:space="preserve">16.705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995643615723</t>
@@ -308,19 +308,19 @@
     <t xml:space="preserve">16.5454540252686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6583919525146</t>
+    <t xml:space="preserve">16.6583938598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.8278007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183898925781</t>
+    <t xml:space="preserve">16.8183860778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6890058517456</t>
+    <t xml:space="preserve">15.6890048980713</t>
   </si>
   <si>
     <t xml:space="preserve">15.472541809082</t>
@@ -332,37 +332,37 @@
     <t xml:space="preserve">15.3407793045044</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5830993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2536964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642776489258</t>
+    <t xml:space="preserve">16.583101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113319396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.253698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642757415771</t>
   </si>
   <si>
     <t xml:space="preserve">15.5290088653564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8796148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678453445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2090158462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101842880249</t>
+    <t xml:space="preserve">14.8796157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748994827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2090167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101852416992</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854995727539</t>
@@ -386,67 +386,67 @@
     <t xml:space="preserve">15.5195980072021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4348955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.792534828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.933705329895</t>
+    <t xml:space="preserve">15.4348945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854768753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925300598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478353500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337043762207</t>
   </si>
   <si>
     <t xml:space="preserve">15.6701831817627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3784246444702</t>
+    <t xml:space="preserve">15.3784255981445</t>
   </si>
   <si>
     <t xml:space="preserve">15.5007743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6419467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148836135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2725219726562</t>
+    <t xml:space="preserve">15.6419458389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278186798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2725200653076</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2819309234619</t>
+    <t xml:space="preserve">16.2819290161133</t>
   </si>
   <si>
     <t xml:space="preserve">16.1595802307129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607524871826</t>
+    <t xml:space="preserve">16.3760471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607486724854</t>
   </si>
   <si>
     <t xml:space="preserve">16.5078086853027</t>
@@ -458,55 +458,55 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7807426452637</t>
+    <t xml:space="preserve">16.780740737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.8560352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9877967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0160274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372097015381</t>
+    <t xml:space="preserve">16.9877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.978385925293</t>
+    <t xml:space="preserve">16.9783840179443</t>
   </si>
   <si>
     <t xml:space="preserve">16.846622467041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8936786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960372924805</t>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960353851318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525062561035</t>
+    <t xml:space="preserve">16.7713298797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842678070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525081634521</t>
   </si>
   <si>
     <t xml:space="preserve">16.9030914306641</t>
@@ -515,37 +515,37 @@
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0536766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8748588562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.034854888916</t>
+    <t xml:space="preserve">16.9972057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0536785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0348529815674</t>
   </si>
   <si>
     <t xml:space="preserve">16.8654460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7619209289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0724964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2324962615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2607307434082</t>
+    <t xml:space="preserve">16.7619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0724983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2324924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
     <t xml:space="preserve">17.2136726379395</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">17.3077850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2983779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724784851074</t>
+    <t xml:space="preserve">17.298376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724765777588</t>
   </si>
   <si>
     <t xml:space="preserve">18.7383365631104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8230419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6818695068359</t>
+    <t xml:space="preserve">18.8230438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6818714141846</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042163848877</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3406715393066</t>
+    <t xml:space="preserve">19.1430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
     <t xml:space="preserve">19.3783206939697</t>
@@ -593,49 +593,49 @@
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5571403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4159679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724151611328</t>
+    <t xml:space="preserve">19.2183246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5571422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4159660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724170684814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4230003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2347717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535934448242</t>
+    <t xml:space="preserve">20.234769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982929229736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3571186065674</t>
+    <t xml:space="preserve">20.357120513916</t>
   </si>
   <si>
     <t xml:space="preserve">20.8935775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206615447998</t>
+    <t xml:space="preserve">20.6677017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
     <t xml:space="preserve">19.7453727722168</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">19.5194931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6888999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171363830566</t>
+    <t xml:space="preserve">19.6889019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171382904053</t>
   </si>
   <si>
     <t xml:space="preserve">19.84889793396</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">19.5759620666504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4630241394043</t>
+    <t xml:space="preserve">19.4630279541016</t>
   </si>
   <si>
     <t xml:space="preserve">19.2747917175293</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">19.3877353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3500881195068</t>
+    <t xml:space="preserve">19.3500843048096</t>
   </si>
   <si>
     <t xml:space="preserve">19.3971462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959777832031</t>
+    <t xml:space="preserve">19.0959796905518</t>
   </si>
   <si>
     <t xml:space="preserve">19.0018615722656</t>
@@ -683,31 +683,31 @@
     <t xml:space="preserve">19.1053867340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8700981140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4936370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.352466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6253986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.510082244873</t>
+    <t xml:space="preserve">18.9171581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8701000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2865829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6254005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5100860595703</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371482849121</t>
@@ -716,133 +716,133 @@
     <t xml:space="preserve">19.5006713867188</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7547798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335834503174</t>
+    <t xml:space="preserve">19.7547836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7900505065918</t>
+    <t xml:space="preserve">20.7900543212891</t>
   </si>
   <si>
     <t xml:space="preserve">20.9218120574951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3641510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.298267364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853351593018</t>
+    <t xml:space="preserve">21.3641529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2982692718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">21.015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947441101074</t>
+    <t xml:space="preserve">20.9029884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947422027588</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112091064453</t>
+    <t xml:space="preserve">21.1100406646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112071990967</t>
   </si>
   <si>
     <t xml:space="preserve">21.6088485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8347282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0229587554932</t>
+    <t xml:space="preserve">21.2135715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0229568481445</t>
   </si>
   <si>
     <t xml:space="preserve">21.8064937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0417804718018</t>
+    <t xml:space="preserve">22.0417823791504</t>
   </si>
   <si>
     <t xml:space="preserve">22.2582454681396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817626953125</t>
+    <t xml:space="preserve">22.6817665100098</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6252975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0394058227539</t>
+    <t xml:space="preserve">22.6252994537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0394039154053</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0582256317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9194316864014</t>
+    <t xml:space="preserve">23.0582275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3711833953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135478973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3076858520508</t>
+    <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0981254577637</t>
+    <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455020904541</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">22.2686920166016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0507431030273</t>
+    <t xml:space="preserve">22.050745010376</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190799713135</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">21.7569828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8327922821045</t>
+    <t xml:space="preserve">21.8327941894531</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811752319336</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285575866699</t>
+    <t xml:space="preserve">21.7285556793213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380332946777</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">21.5579872131348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5200824737549</t>
+    <t xml:space="preserve">21.5200805664062</t>
   </si>
   <si>
     <t xml:space="preserve">21.1315650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4158496856689</t>
+    <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
     <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.463228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.662223815918</t>
+    <t xml:space="preserve">21.4632301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6622257232666</t>
   </si>
   <si>
     <t xml:space="preserve">21.5674667358398</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5813999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6761608123779</t>
+    <t xml:space="preserve">22.4013557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5813980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6761646270752</t>
   </si>
   <si>
     <t xml:space="preserve">22.5908756256104</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">21.7948894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8138427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6717014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958957672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4676856994629</t>
+    <t xml:space="preserve">21.8138408660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6717052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4676895141602</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255481719971</t>
@@ -950,40 +950,40 @@
     <t xml:space="preserve">22.6951122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8277759552002</t>
+    <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.0362491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2068176269531</t>
+    <t xml:space="preserve">23.2068195343018</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.998348236084</t>
+    <t xml:space="preserve">22.9983444213867</t>
   </si>
   <si>
     <t xml:space="preserve">23.131010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5005760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731475830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404838562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4058170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4531955718994</t>
+    <t xml:space="preserve">23.5005741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.405818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.453197479248</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
@@ -992,70 +992,70 @@
     <t xml:space="preserve">22.950963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0646781921387</t>
+    <t xml:space="preserve">23.0646800994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.7519721984863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.723539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9793968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6477317810059</t>
+    <t xml:space="preserve">22.7235374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9793949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6477336883545</t>
   </si>
   <si>
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1834087371826</t>
+    <t xml:space="preserve">22.183406829834</t>
   </si>
   <si>
     <t xml:space="preserve">23.8796195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1165180206299</t>
+    <t xml:space="preserve">24.1165161132812</t>
   </si>
   <si>
     <t xml:space="preserve">23.6616687774658</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3868637084961</t>
+    <t xml:space="preserve">23.3868618011475</t>
   </si>
   <si>
     <t xml:space="preserve">23.1783905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9035873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0217571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955615997314</t>
+    <t xml:space="preserve">22.90358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0217590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955635070801</t>
   </si>
   <si>
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6850833892822</t>
+    <t xml:space="preserve">24.6376991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6850814819336</t>
   </si>
   <si>
     <t xml:space="preserve">24.5903224945068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7040328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8082714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7798404693604</t>
+    <t xml:space="preserve">24.7040348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8082733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7798385620117</t>
   </si>
   <si>
     <t xml:space="preserve">24.7229862213135</t>
@@ -1070,28 +1070,28 @@
     <t xml:space="preserve">24.8651256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7558765411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.547399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4431667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4905433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3863067626953</t>
+    <t xml:space="preserve">25.7558727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5473976135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4431648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4905452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">25.3484039306641</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">25.7274436950684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6611137390137</t>
+    <t xml:space="preserve">25.6611156463623</t>
   </si>
   <si>
     <t xml:space="preserve">25.9643440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3054847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645687103271</t>
+    <t xml:space="preserve">26.3054866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645706176758</t>
   </si>
   <si>
     <t xml:space="preserve">27.309944152832</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">26.9119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0635681152344</t>
+    <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
     <t xml:space="preserve">26.6750469207764</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">26.0591068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0451717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1778354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1967849731445</t>
+    <t xml:space="preserve">25.0451698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1778335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
     <t xml:space="preserve">25.518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1115016937256</t>
+    <t xml:space="preserve">25.1115036010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.5379238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.935920715332</t>
+    <t xml:space="preserve">25.9359169006348</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631187438965</t>
+    <t xml:space="preserve">25.3010234832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.1683578491211</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">25.5853042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6042556762695</t>
+    <t xml:space="preserve">25.6042575836182</t>
   </si>
   <si>
     <t xml:space="preserve">25.8601093292236</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4381504058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.798791885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3673553466797</t>
+    <t xml:space="preserve">26.2486267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4381484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7987957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3673572540283</t>
   </si>
   <si>
     <t xml:space="preserve">25.3578796386719</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">25.6800670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232109069824</t>
+    <t xml:space="preserve">25.6232070922852</t>
   </si>
   <si>
     <t xml:space="preserve">25.7748279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5947818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7084922790527</t>
+    <t xml:space="preserve">25.5947799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7084941864014</t>
   </si>
   <si>
     <t xml:space="preserve">26.1064853668213</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">27.3857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8695888519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9169635772705</t>
+    <t xml:space="preserve">25.8695869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
     <t xml:space="preserve">25.6326847076416</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">23.9743766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008007049561</t>
+    <t xml:space="preserve">24.4007987976074</t>
   </si>
   <si>
     <t xml:space="preserve">24.0691394805908</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">24.2586612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0641250610352</t>
+    <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
     <t xml:space="preserve">25.0167427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9693622589111</t>
+    <t xml:space="preserve">24.9693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">23.9269981384277</t>
@@ -1289,43 +1289,43 @@
     <t xml:space="preserve">26.3433876037598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2012481689453</t>
+    <t xml:space="preserve">26.2012500762939</t>
   </si>
   <si>
     <t xml:space="preserve">26.0117263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5329093933105</t>
+    <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593296051025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7698078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9492969512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6176376342773</t>
+    <t xml:space="preserve">26.7698097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9492988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6176357269287</t>
   </si>
   <si>
     <t xml:space="preserve">28.8071575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">28.665018081665</t>
+    <t xml:space="preserve">28.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">29.3283424377441</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2335796356201</t>
+    <t xml:space="preserve">29.2335815429688</t>
   </si>
   <si>
     <t xml:space="preserve">29.5394897460938</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">30.3042678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9696788787842</t>
+    <t xml:space="preserve">29.9696769714355</t>
   </si>
   <si>
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602386474609</t>
+    <t xml:space="preserve">31.2602367401123</t>
   </si>
   <si>
     <t xml:space="preserve">32.7419967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6501655578613</t>
+    <t xml:space="preserve">33.6501617431641</t>
   </si>
   <si>
     <t xml:space="preserve">34.0803527832031</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">34.4149436950684</t>
   </si>
   <si>
-    <t xml:space="preserve">33.936954498291</t>
+    <t xml:space="preserve">33.9369583129883</t>
   </si>
   <si>
     <t xml:space="preserve">34.1759452819824</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7532997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922904968262</t>
+    <t xml:space="preserve">35.753303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922943115234</t>
   </si>
   <si>
     <t xml:space="preserve">35.2275123596191</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">35.0841217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6576957702637</t>
+    <t xml:space="preserve">35.6576995849609</t>
   </si>
   <si>
     <t xml:space="preserve">35.275318145752</t>
@@ -1397,37 +1397,37 @@
     <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.374683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4187126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5658721923828</t>
+    <t xml:space="preserve">36.3746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4187088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5658760070801</t>
   </si>
   <si>
     <t xml:space="preserve">36.8526611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7822551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036312103271</t>
+    <t xml:space="preserve">30.7822532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036331176758</t>
   </si>
   <si>
     <t xml:space="preserve">31.5948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3558387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2124423980713</t>
+    <t xml:space="preserve">31.3558368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2124404907227</t>
   </si>
   <si>
     <t xml:space="preserve">33.0287857055664</t>
@@ -1436,37 +1436,37 @@
     <t xml:space="preserve">33.7935600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">33.984748840332</t>
+    <t xml:space="preserve">33.9847526550293</t>
   </si>
   <si>
     <t xml:space="preserve">34.7973251342773</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3671455383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6539344787598</t>
+    <t xml:space="preserve">34.3671493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6539306640625</t>
   </si>
   <si>
     <t xml:space="preserve">35.0363235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6061401367188</t>
+    <t xml:space="preserve">34.6061363220215</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413581848145</t>
+    <t xml:space="preserve">33.8413619995117</t>
   </si>
   <si>
     <t xml:space="preserve">34.7495307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0400886535645</t>
+    <t xml:space="preserve">35.5621109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0400924682617</t>
   </si>
   <si>
     <t xml:space="preserve">35.8966941833496</t>
@@ -1478,31 +1478,31 @@
     <t xml:space="preserve">39.0036010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3306465148926</t>
+    <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180740356445</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4262466430664</t>
+    <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
     <t xml:space="preserve">37.8564338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2790870666504</t>
+    <t xml:space="preserve">36.2790832519531</t>
   </si>
   <si>
     <t xml:space="preserve">37.2350540161133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8929252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5583419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6979637145996</t>
+    <t xml:space="preserve">34.8929290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5583381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6979598999023</t>
   </si>
   <si>
     <t xml:space="preserve">33.5067710876465</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">33.2677726745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640037536621</t>
+    <t xml:space="preserve">32.2640075683594</t>
   </si>
   <si>
     <t xml:space="preserve">32.9809837341309</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">33.3633766174316</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7897911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.837589263916</t>
+    <t xml:space="preserve">32.7897872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8375854492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.5985946655273</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">33.2199783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6463966369629</t>
+    <t xml:space="preserve">32.6464004516602</t>
   </si>
   <si>
     <t xml:space="preserve">32.3596000671387</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">31.0690422058105</t>
   </si>
   <si>
-    <t xml:space="preserve">32.025016784668</t>
+    <t xml:space="preserve">32.0250129699707</t>
   </si>
   <si>
     <t xml:space="preserve">31.0212440490723</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">28.5357227325439</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2011318206787</t>
+    <t xml:space="preserve">28.2011299133301</t>
   </si>
   <si>
     <t xml:space="preserve">27.7709465026855</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.248929977417</t>
+    <t xml:space="preserve">28.2489280700684</t>
   </si>
   <si>
     <t xml:space="preserve">27.5797500610352</t>
@@ -1592,16 +1592,16 @@
     <t xml:space="preserve">27.9621391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3445262908936</t>
+    <t xml:space="preserve">28.3445281982422</t>
   </si>
   <si>
     <t xml:space="preserve">29.0137062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9181098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2048988342285</t>
+    <t xml:space="preserve">28.9181118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2049007415771</t>
   </si>
   <si>
     <t xml:space="preserve">30.4954605102539</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">29.5872917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344551086426</t>
+    <t xml:space="preserve">30.7344532012939</t>
   </si>
   <si>
     <t xml:space="preserve">30.0174770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4438915252686</t>
+    <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
     <t xml:space="preserve">29.6828842163086</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">26.5759811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">26.384786605835</t>
+    <t xml:space="preserve">26.3847885131836</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929611206055</t>
@@ -1655,19 +1655,19 @@
     <t xml:space="preserve">26.8627738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4841537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0061664581299</t>
+    <t xml:space="preserve">27.4841556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0061683654785</t>
   </si>
   <si>
     <t xml:space="preserve">26.0979976654053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1935901641846</t>
+    <t xml:space="preserve">25.6200103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1935920715332</t>
   </si>
   <si>
     <t xml:space="preserve">26.623779296875</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">28.6791172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1093063354492</t>
+    <t xml:space="preserve">29.1093044281006</t>
   </si>
   <si>
     <t xml:space="preserve">26.6715793609619</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3885555267334</t>
+    <t xml:space="preserve">26.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3885536193848</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080387115479</t>
+    <t xml:space="preserve">31.3080368041992</t>
   </si>
   <si>
     <t xml:space="preserve">31.4514331817627</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">32.4552001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3118057250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2162055969238</t>
+    <t xml:space="preserve">32.3118095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2162094116211</t>
   </si>
   <si>
     <t xml:space="preserve">33.6023635864258</t>
@@ -1748,28 +1748,28 @@
     <t xml:space="preserve">30.6388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5910568237305</t>
+    <t xml:space="preserve">30.5910587310791</t>
   </si>
   <si>
     <t xml:space="preserve">29.3004970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9409980773926</t>
+    <t xml:space="preserve">29.9409999847412</t>
   </si>
   <si>
     <t xml:space="preserve">30.6484184265137</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8204956054688</t>
+    <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
     <t xml:space="preserve">30.9734497070312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2851486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748329162598</t>
+    <t xml:space="preserve">30.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">30.4763412475586</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.438102722168</t>
+    <t xml:space="preserve">30.4381046295166</t>
   </si>
   <si>
     <t xml:space="preserve">30.7631359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9352111816406</t>
+    <t xml:space="preserve">30.935209274292</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">29.7115650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">28.812952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5203704833984</t>
+    <t xml:space="preserve">28.8129539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5203723907471</t>
   </si>
   <si>
     <t xml:space="preserve">28.487922668457</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">29.1762237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291778564453</t>
+    <t xml:space="preserve">29.3291759490967</t>
   </si>
   <si>
     <t xml:space="preserve">28.5761585235596</t>
@@ -5706,6 +5706,9 @@
   </si>
   <si>
     <t xml:space="preserve">87.4000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -71434,7 +71437,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6910185185</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>284456</v>
@@ -71455,6 +71458,32 @@
         <v>1897</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6912268518</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>271900</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>89.120002746582</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>86.3399963378906</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>86.620002746582</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>88.5999984741211</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1900" uniqueCount="1900">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807556152344</t>
+    <t xml:space="preserve">15.1807546615601</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537855148315</t>
+    <t xml:space="preserve">14.8537845611572</t>
   </si>
   <si>
     <t xml:space="preserve">14.4801054000854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1718187332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476108551025</t>
+    <t xml:space="preserve">14.1718196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
     <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0406265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208856582642</t>
+    <t xml:space="preserve">15.0406274795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">15.3022022247314</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389198303223</t>
+    <t xml:space="preserve">14.4427366256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389207839966</t>
   </si>
   <si>
     <t xml:space="preserve">14.087742805481</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">14.0410318374634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3212909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.33997631073</t>
+    <t xml:space="preserve">14.3212919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3399753570557</t>
   </si>
   <si>
     <t xml:space="preserve">14.7697086334229</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">13.9943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240531921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960285186768</t>
+    <t xml:space="preserve">14.424054145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960266113281</t>
   </si>
   <si>
     <t xml:space="preserve">13.9849815368652</t>
@@ -107,52 +107,52 @@
     <t xml:space="preserve">14.003662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338026046753</t>
+    <t xml:space="preserve">13.433801651001</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155235290527</t>
+    <t xml:space="preserve">12.4155225753784</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172292709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5459051132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645895004272</t>
+    <t xml:space="preserve">12.8172302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5459060668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722269058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645885467529</t>
   </si>
   <si>
     <t xml:space="preserve">13.4057750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195852279663</t>
+    <t xml:space="preserve">13.3777484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7607717514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8355083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1064252853394</t>
+    <t xml:space="preserve">13.7607727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8355093002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">14.2372140884399</t>
@@ -161,64 +161,64 @@
     <t xml:space="preserve">14.4520807266235</t>
   </si>
   <si>
-    <t xml:space="preserve">14.255898475647</t>
+    <t xml:space="preserve">14.2558975219727</t>
   </si>
   <si>
     <t xml:space="preserve">15.414306640625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.601146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060199737549</t>
+    <t xml:space="preserve">15.6011457443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060190200806</t>
   </si>
   <si>
     <t xml:space="preserve">15.3769359588623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.479700088501</t>
+    <t xml:space="preserve">15.4797019958496</t>
   </si>
   <si>
     <t xml:space="preserve">15.6385164260864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5450925827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104869842529</t>
+    <t xml:space="preserve">15.545093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104879379272</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983854293823</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939165115356</t>
+    <t xml:space="preserve">15.0873374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939155578613</t>
   </si>
   <si>
     <t xml:space="preserve">14.6202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1527290344238</t>
+    <t xml:space="preserve">15.1527309417725</t>
   </si>
   <si>
     <t xml:space="preserve">15.3302278518677</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5918035507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412757873535</t>
+    <t xml:space="preserve">15.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412767410278</t>
   </si>
   <si>
     <t xml:space="preserve">15.8253526687622</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">16.3858776092529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3485088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2550868988037</t>
+    <t xml:space="preserve">16.3485069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
     <t xml:space="preserve">16.4139003753662</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215339660645</t>
+    <t xml:space="preserve">16.0215377807617</t>
   </si>
   <si>
     <t xml:space="preserve">16.2177200317383</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">16.3391647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1149559020996</t>
+    <t xml:space="preserve">16.1149578094482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2737731933594</t>
@@ -269,64 +269,64 @@
     <t xml:space="preserve">16.4325847625732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6100845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287631988525</t>
+    <t xml:space="preserve">16.6100826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287651062012</t>
   </si>
   <si>
     <t xml:space="preserve">16.4419269561768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489791870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548648834229</t>
+    <t xml:space="preserve">16.4889850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648983001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.601921081543</t>
+    <t xml:space="preserve">16.6019191741943</t>
   </si>
   <si>
     <t xml:space="preserve">16.6866264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.658390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8278007507324</t>
+    <t xml:space="preserve">16.7054481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8277988433838</t>
   </si>
   <si>
     <t xml:space="preserve">16.8183860778809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078266143799</t>
+    <t xml:space="preserve">16.2254619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890077590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725408554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078285217285</t>
   </si>
   <si>
     <t xml:space="preserve">15.3407793045044</t>
@@ -335,28 +335,28 @@
     <t xml:space="preserve">16.583101272583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325160980225</t>
+    <t xml:space="preserve">16.6113338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325141906738</t>
   </si>
   <si>
     <t xml:space="preserve">16.2537002563477</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5642795562744</t>
+    <t xml:space="preserve">16.5642776489258</t>
   </si>
   <si>
     <t xml:space="preserve">15.5290088653564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8796157836914</t>
+    <t xml:space="preserve">14.8796138763428</t>
   </si>
   <si>
     <t xml:space="preserve">15.0678453445435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2748975753784</t>
+    <t xml:space="preserve">15.2748994827271</t>
   </si>
   <si>
     <t xml:space="preserve">15.2090167999268</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">15.5101852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7854995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3149223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443271636963</t>
+    <t xml:space="preserve">14.7855005264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.314923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.644326210022</t>
   </si>
   <si>
     <t xml:space="preserve">14.9172601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513614654541</t>
+    <t xml:space="preserve">15.5384216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513595581055</t>
   </si>
   <si>
     <t xml:space="preserve">15.5195970535278</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">15.4348936080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854797363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054708480835</t>
+    <t xml:space="preserve">15.5854787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054698944092</t>
   </si>
   <si>
     <t xml:space="preserve">15.8301773071289</t>
@@ -401,43 +401,43 @@
     <t xml:space="preserve">15.9901733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.547833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3784255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148836135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.272518157959</t>
+    <t xml:space="preserve">15.792534828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337024688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701803207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3784265518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2725219726562</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195762634277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2819271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1595802307129</t>
+    <t xml:space="preserve">16.2819309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1595821380615</t>
   </si>
   <si>
     <t xml:space="preserve">16.3760452270508</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">16.4983959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078086853027</t>
+    <t xml:space="preserve">16.460750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078105926514</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301574707031</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560352325439</t>
+    <t xml:space="preserve">16.7807426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
@@ -470,43 +470,43 @@
     <t xml:space="preserve">17.0160312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9407367706299</t>
+    <t xml:space="preserve">16.9407386779785</t>
   </si>
   <si>
     <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9313259124756</t>
+    <t xml:space="preserve">16.9313278198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.9783840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8466243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936805725098</t>
+    <t xml:space="preserve">16.846622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936786651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.6960353851318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.912504196167</t>
+    <t xml:space="preserve">16.9125003814697</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713298797607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8089752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231033325195</t>
+    <t xml:space="preserve">16.8089733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231052398682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8842697143555</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7525043487549</t>
+    <t xml:space="preserve">16.7525062561035</t>
   </si>
   <si>
     <t xml:space="preserve">16.9030914306641</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0536766052246</t>
+    <t xml:space="preserve">17.0536785125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.8748569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0348529815674</t>
+    <t xml:space="preserve">17.0348567962646</t>
   </si>
   <si>
     <t xml:space="preserve">16.8654441833496</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">16.7619171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0724983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2324924468994</t>
+    <t xml:space="preserve">17.0725002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.232494354248</t>
   </si>
   <si>
     <t xml:space="preserve">17.1007328033447</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">17.2607307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136707305908</t>
+    <t xml:space="preserve">17.2136726379395</t>
   </si>
   <si>
     <t xml:space="preserve">17.3548431396484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3077869415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.298376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936569213867</t>
+    <t xml:space="preserve">17.3642559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936588287354</t>
   </si>
   <si>
     <t xml:space="preserve">17.8724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738338470459</t>
+    <t xml:space="preserve">18.7383346557617</t>
   </si>
   <si>
     <t xml:space="preserve">18.8230419158936</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042163848877</t>
+    <t xml:space="preserve">18.8042182922363</t>
   </si>
   <si>
     <t xml:space="preserve">19.1430358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3406734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3783206939697</t>
+    <t xml:space="preserve">19.3406753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.378324508667</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359798431396</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">20.4230003356934</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2347679138184</t>
+    <t xml:space="preserve">20.234769821167</t>
   </si>
   <si>
     <t xml:space="preserve">20.2535953521729</t>
@@ -623,121 +623,121 @@
     <t xml:space="preserve">20.893575668335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6677017211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665332794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7453708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5194931030273</t>
+    <t xml:space="preserve">20.6676998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7453727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.519495010376</t>
   </si>
   <si>
     <t xml:space="preserve">19.6888999938965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171363830566</t>
+    <t xml:space="preserve">19.7171382904053</t>
   </si>
   <si>
     <t xml:space="preserve">19.84889793396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5759601593018</t>
+    <t xml:space="preserve">19.5759620666504</t>
   </si>
   <si>
     <t xml:space="preserve">19.4630241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2747898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4442043304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3877353668213</t>
+    <t xml:space="preserve">19.2747936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4442024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.387731552124</t>
   </si>
   <si>
     <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959758758545</t>
+    <t xml:space="preserve">19.3971462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959777832031</t>
   </si>
   <si>
     <t xml:space="preserve">19.001859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1053848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8701000213623</t>
+    <t xml:space="preserve">19.1053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8700981140137</t>
   </si>
   <si>
     <t xml:space="preserve">18.4936389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">18.352466583252</t>
+    <t xml:space="preserve">18.3524646759033</t>
   </si>
   <si>
     <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6253967285156</t>
+    <t xml:space="preserve">18.6253986358643</t>
   </si>
   <si>
     <t xml:space="preserve">19.2559700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.510082244873</t>
+    <t xml:space="preserve">19.5100841522217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5006713867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547817230225</t>
+    <t xml:space="preserve">19.5006694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547836303711</t>
   </si>
   <si>
     <t xml:space="preserve">19.7924289703369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5947875976562</t>
+    <t xml:space="preserve">19.5947856903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6018199920654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7335815429688</t>
+    <t xml:space="preserve">20.7335834503174</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994632720947</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7900505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218082427979</t>
+    <t xml:space="preserve">20.7900524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218101501465</t>
   </si>
   <si>
     <t xml:space="preserve">21.3641529083252</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">21.2982711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853332519531</t>
+    <t xml:space="preserve">21.1853351593018</t>
   </si>
   <si>
     <t xml:space="preserve">21.0159282684326</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">20.9029884338379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0253391265869</t>
+    <t xml:space="preserve">21.0253372192383</t>
   </si>
   <si>
     <t xml:space="preserve">20.9876918792725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1947441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1100406646729</t>
+    <t xml:space="preserve">21.1947422027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1100425720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.4112071990967</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">21.608850479126</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829746246338</t>
+    <t xml:space="preserve">21.2135677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829765319824</t>
   </si>
   <si>
     <t xml:space="preserve">21.5429706573486</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">21.8347301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0229568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8064918518066</t>
+    <t xml:space="preserve">22.0229587554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.806489944458</t>
   </si>
   <si>
     <t xml:space="preserve">22.0417804718018</t>
@@ -800,25 +800,25 @@
     <t xml:space="preserve">22.2582454681396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252994537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0394020080566</t>
+    <t xml:space="preserve">22.6817665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0394039154053</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0582237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876522064209</t>
+    <t xml:space="preserve">23.0582256317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876502990723</t>
   </si>
   <si>
     <t xml:space="preserve">22.3711853027344</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.787670135498</t>
+    <t xml:space="preserve">21.7876720428467</t>
   </si>
   <si>
     <t xml:space="preserve">21.3076820373535</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0981254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1455039978027</t>
+    <t xml:space="preserve">22.098123550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1455020904541</t>
   </si>
   <si>
     <t xml:space="preserve">22.1549777984619</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0886459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7569828033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327922821045</t>
+    <t xml:space="preserve">22.08864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327941894531</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811771392822</t>
@@ -875,34 +875,34 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285537719727</t>
+    <t xml:space="preserve">21.7285556793213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380332946777</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200843811035</t>
+    <t xml:space="preserve">21.5579853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200824737549</t>
   </si>
   <si>
     <t xml:space="preserve">21.1315670013428</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4158458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.463228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6622257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674629211426</t>
+    <t xml:space="preserve">21.4158477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8612194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4632263183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674648284912</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624485015869</t>
@@ -914,67 +914,67 @@
     <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5814018249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6761608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.590877532959</t>
+    <t xml:space="preserve">22.5813999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6761627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5908756256104</t>
   </si>
   <si>
     <t xml:space="preserve">21.7948894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8138408660889</t>
+    <t xml:space="preserve">21.8138427734375</t>
   </si>
   <si>
     <t xml:space="preserve">21.8422679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717014312744</t>
+    <t xml:space="preserve">21.6716995239258</t>
   </si>
   <si>
     <t xml:space="preserve">21.5958938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4676876068115</t>
+    <t xml:space="preserve">22.4676895141602</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5055923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951122283936</t>
+    <t xml:space="preserve">22.5055904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277759552002</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0362491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2068195343018</t>
+    <t xml:space="preserve">23.0362510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2068176269531</t>
   </si>
   <si>
     <t xml:space="preserve">23.2162933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9983463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1310119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5005760192871</t>
+    <t xml:space="preserve">22.9983444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.131010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5005741119385</t>
   </si>
   <si>
     <t xml:space="preserve">23.6900959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2731475830078</t>
+    <t xml:space="preserve">23.2731494903564</t>
   </si>
   <si>
     <t xml:space="preserve">23.1404876708984</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950963973999</t>
+    <t xml:space="preserve">22.9509658813477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0646781921387</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.723539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9793968200684</t>
+    <t xml:space="preserve">22.7519721984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7235374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
     <t xml:space="preserve">22.6477336883545</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.183406829834</t>
+    <t xml:space="preserve">22.1834087371826</t>
   </si>
   <si>
     <t xml:space="preserve">23.87961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1165180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6616668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783905029297</t>
+    <t xml:space="preserve">24.1165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6616687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783924102783</t>
   </si>
   <si>
     <t xml:space="preserve">22.90358543396</t>
@@ -1040,40 +1040,40 @@
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6376991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6850833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040328979492</t>
+    <t xml:space="preserve">24.6377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6850814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040309906006</t>
   </si>
   <si>
     <t xml:space="preserve">24.8082714080811</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7798404693604</t>
+    <t xml:space="preserve">24.7798385620117</t>
   </si>
   <si>
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429401397705</t>
+    <t xml:space="preserve">24.5429382324219</t>
   </si>
   <si>
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651256561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653522491455</t>
+    <t xml:space="preserve">24.8651275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
     <t xml:space="preserve">25.547399520874</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">25.2915496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4052600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4431648254395</t>
+    <t xml:space="preserve">25.4052581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4431667327881</t>
   </si>
   <si>
     <t xml:space="preserve">25.4905433654785</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484039306641</t>
+    <t xml:space="preserve">25.3484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">25.3294506072998</t>
@@ -1115,49 +1115,49 @@
     <t xml:space="preserve">26.3054828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8645725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.309944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119472503662</t>
+    <t xml:space="preserve">26.8645706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3099422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6750469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4665775299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0591049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0451698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1778335571289</t>
+    <t xml:space="preserve">26.675048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4665756225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0591087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0451679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1778354644775</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.518970489502</t>
+    <t xml:space="preserve">25.5189723968506</t>
   </si>
   <si>
     <t xml:space="preserve">25.1115036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5379219055176</t>
+    <t xml:space="preserve">25.5379238128662</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359188079834</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">25.1588840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010272979736</t>
+    <t xml:space="preserve">25.3010234832764</t>
   </si>
   <si>
     <t xml:space="preserve">25.2631187438965</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">25.1683597564697</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9219837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.206262588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020259857178</t>
+    <t xml:space="preserve">24.9219818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2062606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020240783691</t>
   </si>
   <si>
     <t xml:space="preserve">25.5853061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6042575836182</t>
+    <t xml:space="preserve">25.6042556762695</t>
   </si>
   <si>
     <t xml:space="preserve">25.8601112365723</t>
@@ -1196,46 +1196,46 @@
     <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2486305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4381465911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7987937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3673553466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3578796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6800670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748279571533</t>
+    <t xml:space="preserve">26.248628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4381484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7987957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3673572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3578815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6232070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748260498047</t>
   </si>
   <si>
     <t xml:space="preserve">25.5947799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7084903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1064872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8171863555908</t>
+    <t xml:space="preserve">25.7084922790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1064853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8171882629395</t>
   </si>
   <si>
     <t xml:space="preserve">27.0540904998779</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3857517242432</t>
+    <t xml:space="preserve">27.3857536315918</t>
   </si>
   <si>
     <t xml:space="preserve">25.8695850372314</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7324600219727</t>
+    <t xml:space="preserve">25.6326866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7324619293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.9743766784668</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4481773376465</t>
+    <t xml:space="preserve">24.0691375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4481792449951</t>
   </si>
   <si>
     <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7848567962646</t>
+    <t xml:space="preserve">23.784854888916</t>
   </si>
   <si>
     <t xml:space="preserve">24.258659362793</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">23.9270000457764</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433876037598</t>
+    <t xml:space="preserve">26.3433895111084</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012462615967</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">26.0117263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5329093933105</t>
+    <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593315124512</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">26.7698097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9492969512939</t>
+    <t xml:space="preserve">28.9492988586426</t>
   </si>
   <si>
     <t xml:space="preserve">28.6176376342773</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">28.8071575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">28.665018081665</t>
+    <t xml:space="preserve">28.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">29.3283424377441</t>
@@ -5709,6 +5709,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.3199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.6800003051758</t>
   </si>
 </sst>
 </file>
@@ -71489,7 +71492,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6913194444</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>152139</v>
@@ -71510,6 +71513,32 @@
         <v>1898</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6912962963</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>241858</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>88.7600021362305</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>87.1600036621094</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>88.3199996948242</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>88.6800003051758</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="1901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1902">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,82 +44,82 @@
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537845611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801054000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1718196868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289274215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3021993637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.087742805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0410308837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3212909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.33997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7697076797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3866853713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240531921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338006973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051248550415</t>
+    <t xml:space="preserve">14.8537864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.171820640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476127624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406274795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208875656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022012710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0877418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0410318374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3212919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7697095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3866863250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.424054145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4337997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051267623901</t>
   </si>
   <si>
     <t xml:space="preserve">12.4155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4061794281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172302246094</t>
+    <t xml:space="preserve">12.4061813354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172283172607</t>
   </si>
   <si>
     <t xml:space="preserve">13.5459060668945</t>
@@ -137,25 +137,25 @@
     <t xml:space="preserve">13.3777484893799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251096725464</t>
+    <t xml:space="preserve">14.1251087188721</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195852279663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0316915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7607717514038</t>
+    <t xml:space="preserve">14.0316905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
     <t xml:space="preserve">13.8355083465576</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372131347656</t>
+    <t xml:space="preserve">14.1064252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372140884399</t>
   </si>
   <si>
     <t xml:space="preserve">14.4520797729492</t>
@@ -164,28 +164,28 @@
     <t xml:space="preserve">14.255898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4143056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060199737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.545093536377</t>
+    <t xml:space="preserve">15.4143047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011447906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060190200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5450944900513</t>
   </si>
   <si>
     <t xml:space="preserve">15.6945657730103</t>
@@ -197,64 +197,64 @@
     <t xml:space="preserve">15.4983835220337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939155578613</t>
+    <t xml:space="preserve">15.0873355865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">14.6202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1527299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.330228805542</t>
+    <t xml:space="preserve">15.1527290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302297592163</t>
   </si>
   <si>
     <t xml:space="preserve">15.5918054580688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7225914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412786483765</t>
+    <t xml:space="preserve">15.7225894927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412776947021</t>
   </si>
   <si>
     <t xml:space="preserve">15.8253555297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3017959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858757019043</t>
+    <t xml:space="preserve">16.3017978668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">16.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550868988037</t>
+    <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
     <t xml:space="preserve">16.4139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924556732178</t>
+    <t xml:space="preserve">16.2924537658691</t>
   </si>
   <si>
     <t xml:space="preserve">16.3671894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2177200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3765316009521</t>
+    <t xml:space="preserve">16.0215358734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.217716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3765335083008</t>
   </si>
   <si>
     <t xml:space="preserve">16.3391647338867</t>
@@ -263,94 +263,94 @@
     <t xml:space="preserve">16.1149578094482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2737712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325828552246</t>
+    <t xml:space="preserve">16.2737731933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325847625732</t>
   </si>
   <si>
     <t xml:space="preserve">16.6100845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6474514007568</t>
+    <t xml:space="preserve">16.6474475860596</t>
   </si>
   <si>
     <t xml:space="preserve">16.6287651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4419250488281</t>
+    <t xml:space="preserve">16.4419269561768</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6489849090576</t>
+    <t xml:space="preserve">16.6489791870117</t>
   </si>
   <si>
     <t xml:space="preserve">16.5548648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207466125488</t>
+    <t xml:space="preserve">16.6207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6866245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054481506348</t>
+    <t xml:space="preserve">16.6866264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054500579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995643615723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5454559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8277988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8183898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890058517456</t>
+    <t xml:space="preserve">16.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8278007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8183860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890048980713</t>
   </si>
   <si>
     <t xml:space="preserve">15.472541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7078275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407802581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5830993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2536964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642757415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796148300171</t>
+    <t xml:space="preserve">15.7078294754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407793045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.583101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.253698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796157836914</t>
   </si>
   <si>
     <t xml:space="preserve">15.0678453445435</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">14.7854995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.314923286438</t>
+    <t xml:space="preserve">14.3149223327637</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443271636963</t>
@@ -377,34 +377,34 @@
     <t xml:space="preserve">14.9172611236572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384197235107</t>
+    <t xml:space="preserve">15.5384206771851</t>
   </si>
   <si>
     <t xml:space="preserve">15.6513595581055</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5195999145508</t>
+    <t xml:space="preserve">15.5195980072021</t>
   </si>
   <si>
     <t xml:space="preserve">15.4348955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054670333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301773071289</t>
+    <t xml:space="preserve">15.5854768753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054727554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301792144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.9901733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478324890137</t>
+    <t xml:space="preserve">15.7925310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478353500366</t>
   </si>
   <si>
     <t xml:space="preserve">15.933705329895</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">15.670184135437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3784246444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419477462769</t>
+    <t xml:space="preserve">15.3784255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419458389282</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148817062378</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">16.2819309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1595821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3760471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983959197998</t>
+    <t xml:space="preserve">16.1595802307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3760452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
   </si>
   <si>
     <t xml:space="preserve">16.460750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078086853027</t>
+    <t xml:space="preserve">16.5078067779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301593780518</t>
@@ -461,31 +461,31 @@
     <t xml:space="preserve">16.780740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8560333251953</t>
+    <t xml:space="preserve">16.8560352325439</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0160293579102</t>
+    <t xml:space="preserve">17.0160312652588</t>
   </si>
   <si>
     <t xml:space="preserve">16.9407405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8372077941895</t>
+    <t xml:space="preserve">16.8372097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.978385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8466205596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936824798584</t>
+    <t xml:space="preserve">16.9783840179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.846622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936805725098</t>
   </si>
   <si>
     <t xml:space="preserve">16.6960372924805</t>
@@ -494,34 +494,34 @@
     <t xml:space="preserve">16.9125022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713298797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9030914306641</t>
+    <t xml:space="preserve">16.7713279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231052398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9030933380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0536766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8748588562012</t>
+    <t xml:space="preserve">16.9972038269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0536785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">17.034854888916</t>
@@ -533,49 +533,49 @@
     <t xml:space="preserve">16.7619190216064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0725002288818</t>
+    <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
     <t xml:space="preserve">17.232494354248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1007328033447</t>
+    <t xml:space="preserve">17.1007308959961</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2607307434082</t>
+    <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
     <t xml:space="preserve">17.2136707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3548431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.307788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936569213867</t>
+    <t xml:space="preserve">17.3548469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642597198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077850341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.298376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936588287354</t>
   </si>
   <si>
     <t xml:space="preserve">17.8724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6818695068359</t>
+    <t xml:space="preserve">18.7383365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230457305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6818714141846</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042163848877</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3783206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2183265686035</t>
+    <t xml:space="preserve">19.3783187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2183246612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571422576904</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">19.4159660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2724151611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4230003356934</t>
+    <t xml:space="preserve">20.2724170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4229984283447</t>
   </si>
   <si>
     <t xml:space="preserve">20.2347717285156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2535934448242</t>
+    <t xml:space="preserve">20.2535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982929229736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3571186065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8935775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665313720703</t>
+    <t xml:space="preserve">20.357120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8935794830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6677017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665332794189</t>
   </si>
   <si>
     <t xml:space="preserve">20.1030101776123</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7453708648682</t>
+    <t xml:space="preserve">19.7453727722168</t>
   </si>
   <si>
     <t xml:space="preserve">19.5194931030273</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">19.7171382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8488960266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5759601593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2747936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4442043304443</t>
+    <t xml:space="preserve">19.84889793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5759620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2747917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">19.3877353668213</t>
@@ -674,31 +674,31 @@
     <t xml:space="preserve">19.3971462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959796905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001859664917</t>
+    <t xml:space="preserve">19.0959777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0018615722656</t>
   </si>
   <si>
     <t xml:space="preserve">19.1053867340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8701019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4936370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865829467773</t>
+    <t xml:space="preserve">18.9171581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8701000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4936351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.352466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
     <t xml:space="preserve">18.6254005432129</t>
@@ -710,31 +710,31 @@
     <t xml:space="preserve">19.5100841522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2371482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7547836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7924289703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335834503174</t>
+    <t xml:space="preserve">19.2371501922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006713867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7547817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7924327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7900505065918</t>
+    <t xml:space="preserve">20.7900524139404</t>
   </si>
   <si>
     <t xml:space="preserve">20.9218120574951</t>
@@ -743,43 +743,43 @@
     <t xml:space="preserve">21.3641529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2982692718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0159282684326</t>
+    <t xml:space="preserve">21.298267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.015926361084</t>
   </si>
   <si>
     <t xml:space="preserve">20.9029884338379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0253372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947441101074</t>
+    <t xml:space="preserve">21.0253391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947422027588</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100406646729</t>
+    <t xml:space="preserve">21.1100425720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.4112071990967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2135677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3829746246338</t>
+    <t xml:space="preserve">21.6088485717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2135696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3829765319824</t>
   </si>
   <si>
     <t xml:space="preserve">21.5429706573486</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">21.8347282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0229606628418</t>
+    <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
     <t xml:space="preserve">21.8064937591553</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">22.6252975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0394039154053</t>
+    <t xml:space="preserve">23.0394058227539</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0582256317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
+    <t xml:space="preserve">23.0582275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3711853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135478973389</t>
   </si>
   <si>
     <t xml:space="preserve">21.6464977264404</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">21.787670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3076858520508</t>
+    <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0981254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1455039978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1549758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0507411956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7190799713135</t>
+    <t xml:space="preserve">22.098123550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1455020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1549797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0507431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
     <t xml:space="preserve">22.08864402771</t>
@@ -866,25 +866,25 @@
     <t xml:space="preserve">21.7569828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8327941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6811771392822</t>
+    <t xml:space="preserve">21.8327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6811752319336</t>
   </si>
   <si>
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380352020264</t>
+    <t xml:space="preserve">21.7285556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380332946777</t>
   </si>
   <si>
     <t xml:space="preserve">21.5579853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5200824737549</t>
+    <t xml:space="preserve">21.5200805664062</t>
   </si>
   <si>
     <t xml:space="preserve">21.1315650939941</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">21.8612194061279</t>
   </si>
   <si>
-    <t xml:space="preserve">21.463228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.662223815918</t>
+    <t xml:space="preserve">21.4632301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6622257232666</t>
   </si>
   <si>
     <t xml:space="preserve">21.5674667358398</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529708862305</t>
+    <t xml:space="preserve">22.4013538360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529727935791</t>
   </si>
   <si>
     <t xml:space="preserve">22.5813980102539</t>
@@ -923,31 +923,31 @@
     <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7948875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6717014312744</t>
+    <t xml:space="preserve">21.7948894500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6717052459717</t>
   </si>
   <si>
     <t xml:space="preserve">21.5958938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4676876068115</t>
+    <t xml:space="preserve">22.4676895141602</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5055904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951141357422</t>
+    <t xml:space="preserve">22.5055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951122283936</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277759552002</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">23.2068195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2162952423096</t>
+    <t xml:space="preserve">23.2162971496582</t>
   </si>
   <si>
     <t xml:space="preserve">22.9983463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.131010055542</t>
+    <t xml:space="preserve">23.1310119628906</t>
   </si>
   <si>
     <t xml:space="preserve">23.5005760192871</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">23.1404857635498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4058151245117</t>
+    <t xml:space="preserve">23.405818939209</t>
   </si>
   <si>
     <t xml:space="preserve">23.4531955718994</t>
@@ -992,91 +992,91 @@
     <t xml:space="preserve">22.950963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0646781921387</t>
+    <t xml:space="preserve">23.0646800994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.7519721984863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7235412597656</t>
+    <t xml:space="preserve">22.723539352417</t>
   </si>
   <si>
     <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6477317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4771633148193</t>
+    <t xml:space="preserve">22.6477336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4771614074707</t>
   </si>
   <si>
     <t xml:space="preserve">22.183406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1165199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6616687774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783924102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.90358543396</t>
+    <t xml:space="preserve">23.87961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1165161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6616668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9035873413086</t>
   </si>
   <si>
     <t xml:space="preserve">24.0217571258545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955615997314</t>
+    <t xml:space="preserve">24.4955635070801</t>
   </si>
   <si>
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377010345459</t>
+    <t xml:space="preserve">24.6376991271973</t>
   </si>
   <si>
     <t xml:space="preserve">24.6850814819336</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5903205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8082695007324</t>
+    <t xml:space="preserve">24.5903224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8082733154297</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7229843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5429420471191</t>
+    <t xml:space="preserve">24.7229862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5429382324219</t>
   </si>
   <si>
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651256561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558765411377</t>
+    <t xml:space="preserve">24.8651237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558746337891</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5474014282227</t>
+    <t xml:space="preserve">25.5473976135254</t>
   </si>
   <si>
     <t xml:space="preserve">25.2915477752686</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">25.4431648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4905452728271</t>
+    <t xml:space="preserve">25.4905433654785</t>
   </si>
   <si>
     <t xml:space="preserve">25.3863086700439</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">25.7274436950684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.661111831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645725250244</t>
+    <t xml:space="preserve">25.6611156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645687103271</t>
   </si>
   <si>
     <t xml:space="preserve">27.309944152832</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">26.9119472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0635681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.675048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.46657371521</t>
+    <t xml:space="preserve">27.0635662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6750469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4665775299072</t>
   </si>
   <si>
     <t xml:space="preserve">26.0591068267822</t>
@@ -1145,19 +1145,19 @@
     <t xml:space="preserve">25.0451698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1778354644775</t>
+    <t xml:space="preserve">25.1778335571289</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5189723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1115016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5379238128662</t>
+    <t xml:space="preserve">25.518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1115036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5379257202148</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359188079834</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">25.1588821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3010234832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683559417725</t>
+    <t xml:space="preserve">25.3010215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683578491211</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">25.206262588501</t>
+    <t xml:space="preserve">25.2062606811523</t>
   </si>
   <si>
     <t xml:space="preserve">25.1020259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5853061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8601093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3339099884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.248628616333</t>
+    <t xml:space="preserve">25.5853042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.860107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.333911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2486267089844</t>
   </si>
   <si>
     <t xml:space="preserve">26.4381484985352</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">25.3673553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3578815460205</t>
+    <t xml:space="preserve">25.3578796386719</t>
   </si>
   <si>
     <t xml:space="preserve">25.6800670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5947818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7084941864014</t>
+    <t xml:space="preserve">25.6232089996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5947799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7084922790527</t>
   </si>
   <si>
     <t xml:space="preserve">26.1064853668213</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">26.8171882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0540904998779</t>
+    <t xml:space="preserve">27.0540924072266</t>
   </si>
   <si>
     <t xml:space="preserve">27.3857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8695850372314</t>
+    <t xml:space="preserve">25.8695869445801</t>
   </si>
   <si>
     <t xml:space="preserve">25.8222045898438</t>
@@ -1247,13 +1247,13 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7324619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9743785858154</t>
+    <t xml:space="preserve">25.632682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7324600219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9743766784668</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008007049561</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">23.7848587036133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.258659362793</t>
+    <t xml:space="preserve">24.2586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167427062988</t>
+    <t xml:space="preserve">25.0167407989502</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693622589111</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">23.9269981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433895111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0117282867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">26.3433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2012481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538696289062</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855270385742</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">26.9593296051025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7698078155518</t>
+    <t xml:space="preserve">26.7698097229004</t>
   </si>
   <si>
     <t xml:space="preserve">28.9492988586426</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">28.6176357269287</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8071594238281</t>
+    <t xml:space="preserve">28.8071575164795</t>
   </si>
   <si>
     <t xml:space="preserve">28.665018081665</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">29.3283405303955</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2335815429688</t>
+    <t xml:space="preserve">29.2335796356201</t>
   </si>
   <si>
     <t xml:space="preserve">29.5394897460938</t>
@@ -1346,31 +1346,31 @@
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501655578613</t>
+    <t xml:space="preserve">31.2602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501617431641</t>
   </si>
   <si>
     <t xml:space="preserve">34.0803527832031</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1797142028809</t>
+    <t xml:space="preserve">35.1797180175781</t>
   </si>
   <si>
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149475097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.936954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759490966797</t>
+    <t xml:space="preserve">34.4149436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9369583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759452819824</t>
   </si>
   <si>
     <t xml:space="preserve">34.9885215759277</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">35.753303527832</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9922904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2275161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0841255187988</t>
+    <t xml:space="preserve">35.9922943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2275123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0841217041016</t>
   </si>
   <si>
     <t xml:space="preserve">35.6576995849609</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">35.4187088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5658721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8526649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7822551727295</t>
+    <t xml:space="preserve">36.5658760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7822532653809</t>
   </si>
   <si>
     <t xml:space="preserve">31.1168422698975</t>
@@ -1430,28 +1430,28 @@
     <t xml:space="preserve">31.2124404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0287818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.984748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7973289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671455383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6539344787598</t>
+    <t xml:space="preserve">33.0287857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9847526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7973251342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6539306640625</t>
   </si>
   <si>
     <t xml:space="preserve">35.0363235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6061401367188</t>
+    <t xml:space="preserve">34.6061363220215</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627380371094</t>
@@ -1463,34 +1463,34 @@
     <t xml:space="preserve">34.7495307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0400886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966903686523</t>
+    <t xml:space="preserve">35.5621109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0400924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966941833496</t>
   </si>
   <si>
     <t xml:space="preserve">36.6614685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0035972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5180778503418</t>
+    <t xml:space="preserve">39.0036010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5180740356445</t>
   </si>
   <si>
     <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8564300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2790870666504</t>
+    <t xml:space="preserve">37.8564338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2790832519531</t>
   </si>
   <si>
     <t xml:space="preserve">37.2350540161133</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">34.8929290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5583419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6979675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5067672729492</t>
+    <t xml:space="preserve">34.5583381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6979598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5067710876465</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677726745605</t>
@@ -1514,70 +1514,70 @@
     <t xml:space="preserve">32.2640075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9809875488281</t>
+    <t xml:space="preserve">32.9809837341309</t>
   </si>
   <si>
     <t xml:space="preserve">33.3633766174316</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7897911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.837589263916</t>
+    <t xml:space="preserve">32.7897872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8375854492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.5985946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">32.503002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6463966369629</t>
+    <t xml:space="preserve">32.5029983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6464004516602</t>
   </si>
   <si>
     <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.072811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7860202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.025016784668</t>
+    <t xml:space="preserve">32.0728073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7860221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0250129699707</t>
   </si>
   <si>
     <t xml:space="preserve">31.0212440490723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8816146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2011318206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7709445953369</t>
+    <t xml:space="preserve">31.8816165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357227325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2011299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7709465026855</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.248929977417</t>
+    <t xml:space="preserve">28.2489280700684</t>
   </si>
   <si>
     <t xml:space="preserve">27.5797500610352</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">28.1055355072021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2451610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.96213722229</t>
+    <t xml:space="preserve">27.2451629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9621391296387</t>
   </si>
   <si>
     <t xml:space="preserve">28.3445281982422</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">29.0137062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9181098937988</t>
+    <t xml:space="preserve">28.9181118011475</t>
   </si>
   <si>
     <t xml:space="preserve">29.2049007415771</t>
@@ -1610,31 +1610,31 @@
     <t xml:space="preserve">29.5872917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344551086426</t>
+    <t xml:space="preserve">30.7344532012939</t>
   </si>
   <si>
     <t xml:space="preserve">30.0174770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4438915252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6828861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.583517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3847846984863</t>
+    <t xml:space="preserve">29.4438934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6828842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3847885131836</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4363574981689</t>
+    <t xml:space="preserve">27.4363555908203</t>
   </si>
   <si>
     <t xml:space="preserve">27.8187427520752</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">27.7231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6350860595703</t>
+    <t xml:space="preserve">28.6313190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
     <t xml:space="preserve">27.1017665863037</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">26.8627738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4841537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0061664581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0979957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200122833252</t>
+    <t xml:space="preserve">27.4841556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0061683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0979976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200103759766</t>
   </si>
   <si>
     <t xml:space="preserve">26.1935920715332</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2891883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7671775817871</t>
+    <t xml:space="preserve">26.2891902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7671756744385</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.388557434082</t>
+    <t xml:space="preserve">26.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3885536193848</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
@@ -1721,43 +1721,43 @@
     <t xml:space="preserve">31.3080368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4514350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4552040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3118019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2162055969238</t>
+    <t xml:space="preserve">31.4514331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3118095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2162094116211</t>
   </si>
   <si>
     <t xml:space="preserve">33.6023635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1721839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5545654296875</t>
+    <t xml:space="preserve">33.1721801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5545692443848</t>
   </si>
   <si>
     <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6388568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6484203338623</t>
+    <t xml:space="preserve">30.6388549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6484184265137</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
@@ -1766,31 +1766,31 @@
     <t xml:space="preserve">30.9734497070312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2851505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748329162598</t>
+    <t xml:space="preserve">30.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">30.4763412475586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2277889251709</t>
+    <t xml:space="preserve">30.2277908325195</t>
   </si>
   <si>
     <t xml:space="preserve">29.9983558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.826286315918</t>
+    <t xml:space="preserve">29.8262825012207</t>
   </si>
   <si>
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.438102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631340026855</t>
+    <t xml:space="preserve">30.4381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631359100342</t>
   </si>
   <si>
     <t xml:space="preserve">30.935209274292</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">29.7498054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7115669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.812952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5203704833984</t>
+    <t xml:space="preserve">29.7115650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8129539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5203723907471</t>
   </si>
   <si>
     <t xml:space="preserve">28.487922668457</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">28.717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1762218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3291797637939</t>
+    <t xml:space="preserve">29.4821338653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1762237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3291759490967</t>
   </si>
   <si>
     <t xml:space="preserve">28.5761585235596</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9237060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6533908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058414459229</t>
+    <t xml:space="preserve">28.9237041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.653392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058433532715</t>
   </si>
   <si>
     <t xml:space="preserve">28.3637657165527</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">28.0741443634033</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1859664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2245845794678</t>
+    <t xml:space="preserve">27.1859645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2245826721191</t>
   </si>
   <si>
     <t xml:space="preserve">27.2052745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3211212158203</t>
+    <t xml:space="preserve">27.3211231231689</t>
   </si>
   <si>
     <t xml:space="preserve">27.5335140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6493606567383</t>
+    <t xml:space="preserve">27.6493625640869</t>
   </si>
   <si>
     <t xml:space="preserve">27.9776020050049</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">28.0548343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9969120025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4989242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2479190826416</t>
+    <t xml:space="preserve">27.9969139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4989261627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.247917175293</t>
   </si>
   <si>
     <t xml:space="preserve">28.3251514434814</t>
@@ -1913,28 +1913,28 @@
     <t xml:space="preserve">29.2712535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8311920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9084243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2173557281494</t>
+    <t xml:space="preserve">29.8311901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9084224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2173538208008</t>
   </si>
   <si>
     <t xml:space="preserve">29.9856567382812</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6807518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3677959442139</t>
+    <t xml:space="preserve">30.6807556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3677940368652</t>
   </si>
   <si>
     <t xml:space="preserve">29.4836444854736</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">29.174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4257202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2519454956055</t>
+    <t xml:space="preserve">29.4257183074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2519435882568</t>
   </si>
   <si>
     <t xml:space="preserve">29.4643363952637</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">28.9043979644775</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6920051574707</t>
+    <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
     <t xml:space="preserve">28.4796161651611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7652111053467</t>
+    <t xml:space="preserve">27.7652130126953</t>
   </si>
   <si>
     <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542694091797</t>
+    <t xml:space="preserve">26.9542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1473503112793</t>
@@ -1982,25 +1982,25 @@
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6839542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101795196533</t>
+    <t xml:space="preserve">26.683952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101776123047</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1899929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3444595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.938985824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4369716644287</t>
+    <t xml:space="preserve">28.1899948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.34446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9389877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4369735717773</t>
   </si>
   <si>
     <t xml:space="preserve">27.2631988525391</t>
@@ -2009,25 +2009,25 @@
     <t xml:space="preserve">27.0314998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6260299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4176635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0355281829834</t>
+    <t xml:space="preserve">26.6260280609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4176616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">27.0894241333008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.992883682251</t>
+    <t xml:space="preserve">26.9928817749023</t>
   </si>
   <si>
     <t xml:space="preserve">27.0508098602295</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4755878448486</t>
+    <t xml:space="preserve">27.4755897521973</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2036,28 +2036,28 @@
     <t xml:space="preserve">27.591438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">27.610746383667</t>
+    <t xml:space="preserve">27.6107482910156</t>
   </si>
   <si>
     <t xml:space="preserve">27.6879806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3557109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9309329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8536987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8730068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3018169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4562835693359</t>
+    <t xml:space="preserve">26.355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8537006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8730049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4562816619873</t>
   </si>
   <si>
     <t xml:space="preserve">26.8577251434326</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">25.7957725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9116249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7032623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7459049224854</t>
+    <t xml:space="preserve">25.9116230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7032604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7459030151367</t>
   </si>
   <si>
     <t xml:space="preserve">27.1087322235107</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">28.1320686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3830738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9430122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4064102172852</t>
+    <t xml:space="preserve">28.3830757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9430141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4064083099365</t>
   </si>
   <si>
     <t xml:space="preserve">28.8078575134277</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">29.1360969543457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7499313354492</t>
+    <t xml:space="preserve">28.7499294281006</t>
   </si>
   <si>
     <t xml:space="preserve">28.8271656036377</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6147727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6228275299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.935791015625</t>
+    <t xml:space="preserve">28.5954647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6147747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6228294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9357872009277</t>
   </si>
   <si>
     <t xml:space="preserve">32.3026428222656</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">32.4571075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8585548400879</t>
+    <t xml:space="preserve">31.8585510253906</t>
   </si>
   <si>
     <t xml:space="preserve">31.2213821411133</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">31.182767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6654720306396</t>
+    <t xml:space="preserve">31.6654739379883</t>
   </si>
   <si>
     <t xml:space="preserve">32.1674842834473</t>
@@ -2153,28 +2153,28 @@
     <t xml:space="preserve">31.047607421875</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9510707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1248455047607</t>
+    <t xml:space="preserve">30.9510726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1248435974121</t>
   </si>
   <si>
     <t xml:space="preserve">31.356538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8545246124268</t>
+    <t xml:space="preserve">30.8545265197754</t>
   </si>
   <si>
     <t xml:space="preserve">30.8931427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8159084320068</t>
+    <t xml:space="preserve">30.8159103393555</t>
   </si>
   <si>
     <t xml:space="preserve">31.3372325897217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4683609008789</t>
+    <t xml:space="preserve">30.4683628082275</t>
   </si>
   <si>
     <t xml:space="preserve">31.0089912414551</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">33.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8859176635742</t>
+    <t xml:space="preserve">33.8859214782715</t>
   </si>
   <si>
     <t xml:space="preserve">34.8899421691895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0251045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9711990356445</t>
+    <t xml:space="preserve">35.0250968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9712028503418</t>
   </si>
   <si>
     <t xml:space="preserve">36.5311431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9559211730957</t>
+    <t xml:space="preserve">36.955924987793</t>
   </si>
   <si>
     <t xml:space="preserve">37.2069320678711</t>
@@ -2225,19 +2225,19 @@
     <t xml:space="preserve">33.2873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0363578796387</t>
+    <t xml:space="preserve">33.0363540649414</t>
   </si>
   <si>
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6847801208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8778629302979</t>
+    <t xml:space="preserve">31.9937133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6847839355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8778591156006</t>
   </si>
   <si>
     <t xml:space="preserve">32.3605690002441</t>
@@ -2246,25 +2246,25 @@
     <t xml:space="preserve">33.383903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8432769775391</t>
+    <t xml:space="preserve">32.8432731628418</t>
   </si>
   <si>
     <t xml:space="preserve">31.7427062988281</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8239631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.901195526123</t>
+    <t xml:space="preserve">32.8239669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9011993408203</t>
   </si>
   <si>
     <t xml:space="preserve">32.2447166442871</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5343437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4764137268066</t>
+    <t xml:space="preserve">32.5343399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4764175415039</t>
   </si>
   <si>
     <t xml:space="preserve">33.6928367614746</t>
@@ -2276,64 +2276,64 @@
     <t xml:space="preserve">29.3871021270752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.811882019043</t>
+    <t xml:space="preserve">29.8118839263916</t>
   </si>
   <si>
     <t xml:space="preserve">28.9623222351074</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8698101043701</t>
+    <t xml:space="preserve">29.8698081970215</t>
   </si>
   <si>
     <t xml:space="preserve">29.7732677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0049648284912</t>
+    <t xml:space="preserve">30.0049667358398</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2784786224365</t>
+    <t xml:space="preserve">26.2784805297852</t>
   </si>
   <si>
     <t xml:space="preserve">25.2937622070312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1240119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5407428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9767742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2744541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378482818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150825500488</t>
+    <t xml:space="preserve">26.1240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5407409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1931915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9767761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2744560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.737850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150844573975</t>
   </si>
   <si>
     <t xml:space="preserve">25.100679397583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7225704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8384189605713</t>
+    <t xml:space="preserve">26.7225685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8384170532227</t>
   </si>
   <si>
     <t xml:space="preserve">24.791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8263339996338</t>
+    <t xml:space="preserve">23.8263359069824</t>
   </si>
   <si>
     <t xml:space="preserve">24.019416809082</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4441986083984</t>
+    <t xml:space="preserve">24.4442005157471</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075946807861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0427570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6220016479492</t>
+    <t xml:space="preserve">25.0427551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6220035552979</t>
   </si>
   <si>
     <t xml:space="preserve">26.3943290710449</t>
@@ -2363,25 +2363,25 @@
     <t xml:space="preserve">27.8231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6646461486816</t>
+    <t xml:space="preserve">26.664644241333</t>
   </si>
   <si>
     <t xml:space="preserve">26.645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2398624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.718542098999</t>
+    <t xml:space="preserve">26.2398643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7185401916504</t>
   </si>
   <si>
     <t xml:space="preserve">25.4482269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5833854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5487957000732</t>
+    <t xml:space="preserve">25.5833873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5487937927246</t>
   </si>
   <si>
     <t xml:space="preserve">26.9349594116211</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">25.8923149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.066089630127</t>
+    <t xml:space="preserve">26.0660877227783</t>
   </si>
   <si>
     <t xml:space="preserve">26.973575592041</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">32.283332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4104385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5994930267334</t>
+    <t xml:space="preserve">30.410436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5994911193848</t>
   </si>
   <si>
     <t xml:space="preserve">27.5721302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5681056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5061511993408</t>
+    <t xml:space="preserve">26.5681037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5061531066895</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903026580811</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">24.6565914154053</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2511196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2897357940674</t>
+    <t xml:space="preserve">24.2511177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2897338867188</t>
   </si>
   <si>
     <t xml:space="preserve">24.5793571472168</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">24.8303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3862762451172</t>
+    <t xml:space="preserve">24.3862743377686</t>
   </si>
   <si>
     <t xml:space="preserve">23.8842601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9421844482422</t>
+    <t xml:space="preserve">23.9421863555908</t>
   </si>
   <si>
     <t xml:space="preserve">24.1352672576904</t>
@@ -2474,25 +2474,25 @@
     <t xml:space="preserve">24.1545753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0387268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035682678223</t>
+    <t xml:space="preserve">24.038724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035701751709</t>
   </si>
   <si>
     <t xml:space="preserve">23.1505470275879</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3822460174561</t>
+    <t xml:space="preserve">23.3822441101074</t>
   </si>
   <si>
     <t xml:space="preserve">23.0733165740967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7684116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5946369171143</t>
+    <t xml:space="preserve">23.7684135437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5946388244629</t>
   </si>
   <si>
     <t xml:space="preserve">23.7877197265625</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">25.081371307373</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3476581573486</t>
+    <t xml:space="preserve">24.34765625</t>
   </si>
   <si>
     <t xml:space="preserve">25.5447673797607</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">26.1047058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0853977203369</t>
+    <t xml:space="preserve">26.0853996276855</t>
   </si>
   <si>
     <t xml:space="preserve">25.119987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9462127685547</t>
+    <t xml:space="preserve">24.9462146759033</t>
   </si>
   <si>
     <t xml:space="preserve">24.811056137085</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">26.2205543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6179733276367</t>
+    <t xml:space="preserve">24.6179752349854</t>
   </si>
   <si>
     <t xml:space="preserve">24.463508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358341217041</t>
+    <t xml:space="preserve">25.2358360290527</t>
   </si>
   <si>
     <t xml:space="preserve">25.1392955780029</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">25.6413078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3130683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977867126465</t>
+    <t xml:space="preserve">25.3130702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977886199951</t>
   </si>
   <si>
     <t xml:space="preserve">26.7804927825928</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">26.046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2591724395752</t>
+    <t xml:space="preserve">26.2591743469238</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012462615967</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">26.4136371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8343925476074</t>
+    <t xml:space="preserve">25.8343906402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.7571582794189</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4675331115723</t>
+    <t xml:space="preserve">25.4675350189209</t>
   </si>
   <si>
     <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689823150635</t>
+    <t xml:space="preserve">24.8689804077148</t>
   </si>
   <si>
     <t xml:space="preserve">24.772439956665</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">30.1401214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7620182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1481742858887</t>
+    <t xml:space="preserve">31.7620162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1481781005859</t>
   </si>
   <si>
     <t xml:space="preserve">32.2061042785645</t>
@@ -2618,16 +2618,16 @@
     <t xml:space="preserve">31.8392467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9744033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9550952911377</t>
+    <t xml:space="preserve">31.9744052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9550933837891</t>
   </si>
   <si>
     <t xml:space="preserve">32.3798789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2680549621582</t>
+    <t xml:space="preserve">33.2680511474609</t>
   </si>
   <si>
     <t xml:space="preserve">34.1755409240723</t>
@@ -2639,61 +2639,61 @@
     <t xml:space="preserve">33.9245338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1795692443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3726501464844</t>
+    <t xml:space="preserve">35.1795654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3726463317871</t>
   </si>
   <si>
     <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5810127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2761077880859</t>
+    <t xml:space="preserve">34.5810165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2761116027832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8706359863281</t>
+    <t xml:space="preserve">34.8706321716309</t>
   </si>
   <si>
     <t xml:space="preserve">34.7547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0444068908691</t>
+    <t xml:space="preserve">35.6429595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0444107055664</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4651641845703</t>
+    <t xml:space="preserve">34.465160369873</t>
   </si>
   <si>
     <t xml:space="preserve">34.6003227233887</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4957237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.059684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5383720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.291389465332</t>
+    <t xml:space="preserve">32.2640228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.495719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0556678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0596885681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5383682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2913932800293</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542205810547</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">32.9977416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7314491271973</t>
+    <t xml:space="preserve">33.7314529418945</t>
   </si>
   <si>
     <t xml:space="preserve">33.3066711425781</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8971710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0709419250488</t>
+    <t xml:space="preserve">33.1908149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8971748352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0709457397461</t>
   </si>
   <si>
     <t xml:space="preserve">32.437801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3452911376953</t>
+    <t xml:space="preserve">33.345287322998</t>
   </si>
   <si>
     <t xml:space="preserve">33.210132598877</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">33.9824562072754</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4458541870117</t>
+    <t xml:space="preserve">33.9631538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.445858001709</t>
   </si>
   <si>
     <t xml:space="preserve">34.0983085632324</t>
@@ -2762,13 +2762,13 @@
     <t xml:space="preserve">33.4418296813965</t>
   </si>
   <si>
-    <t xml:space="preserve">32.881893157959</t>
+    <t xml:space="preserve">32.8818893432617</t>
   </si>
   <si>
     <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6775550842285</t>
+    <t xml:space="preserve">34.6775512695312</t>
   </si>
   <si>
     <t xml:space="preserve">37.5351676940918</t>
@@ -2789,37 +2789,37 @@
     <t xml:space="preserve">36.2994422912598</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2801361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7201957702637</t>
+    <t xml:space="preserve">36.2801399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7201919555664</t>
   </si>
   <si>
     <t xml:space="preserve">35.6043472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">35.565731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3919563293457</t>
+    <t xml:space="preserve">35.5657272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.391960144043</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510162353516</t>
+    <t xml:space="preserve">37.6510200500488</t>
   </si>
   <si>
     <t xml:space="preserve">37.0331573486328</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3807067871094</t>
+    <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
     <t xml:space="preserve">37.5158615112305</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5198936462402</t>
+    <t xml:space="preserve">38.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.581844329834</t>
+    <t xml:space="preserve">39.5818405151367</t>
   </si>
   <si>
     <t xml:space="preserve">39.9100761413574</t>
@@ -2840,46 +2840,46 @@
     <t xml:space="preserve">39.2149810791016</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9527206420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1458015441895</t>
+    <t xml:space="preserve">40.9527244567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1458053588867</t>
   </si>
   <si>
     <t xml:space="preserve">41.7057418823242</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4587669372559</t>
+    <t xml:space="preserve">42.4587631225586</t>
   </si>
   <si>
     <t xml:space="preserve">41.9567489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5319747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3388862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8947982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.701717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5665550231934</t>
+    <t xml:space="preserve">41.5319709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3388900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8948020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7017135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6244812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5665588378906</t>
   </si>
   <si>
     <t xml:space="preserve">42.3429183959961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4780693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878868103027</t>
+    <t xml:space="preserve">42.4780731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878791809082</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
@@ -2891,16 +2891,16 @@
     <t xml:space="preserve">42.4008369445801</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6711578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256149291992</t>
+    <t xml:space="preserve">42.6711540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256187438965</t>
   </si>
   <si>
     <t xml:space="preserve">43.8875694274902</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5786437988281</t>
+    <t xml:space="preserve">43.5786399841309</t>
   </si>
   <si>
     <t xml:space="preserve">43.9841156005859</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">43.6172561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8489532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3743057250977</t>
+    <t xml:space="preserve">43.848949432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3743019104004</t>
   </si>
   <si>
     <t xml:space="preserve">47.3244361877441</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7669219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9600067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5601577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4636192321777</t>
+    <t xml:space="preserve">49.7669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9600028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5601615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4636154174805</t>
   </si>
   <si>
     <t xml:space="preserve">47.2665100097656</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">47.4016647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">48.01953125</t>
+    <t xml:space="preserve">48.0195350646973</t>
   </si>
   <si>
     <t xml:space="preserve">48.3188056945801</t>
@@ -2975,10 +2975,10 @@
     <t xml:space="preserve">47.691291809082</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7878303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051223754883</t>
+    <t xml:space="preserve">47.7878341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051261901855</t>
   </si>
   <si>
     <t xml:space="preserve">47.6140556335449</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">47.8457565307617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2842140197754</t>
+    <t xml:space="preserve">49.2842178344727</t>
   </si>
   <si>
     <t xml:space="preserve">49.6221122741699</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809112548828</t>
+    <t xml:space="preserve">47.9809150695801</t>
   </si>
   <si>
     <t xml:space="preserve">49.3807601928711</t>
@@ -3047,31 +3047,31 @@
     <t xml:space="preserve">52.9045066833496</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6768379211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0975914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0010528564453</t>
+    <t xml:space="preserve">53.6768341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0975875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
     <t xml:space="preserve">52.8562393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0356369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.601203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7105979919434</t>
+    <t xml:space="preserve">52.0356407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7106018066406</t>
   </si>
   <si>
     <t xml:space="preserve">48.6567039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0774536132812</t>
+    <t xml:space="preserve">48.077449798584</t>
   </si>
   <si>
     <t xml:space="preserve">48.173999786377</t>
@@ -3104,31 +3104,31 @@
     <t xml:space="preserve">46.3010940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5907249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8031120300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8071365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6446151733398</t>
+    <t xml:space="preserve">46.5907211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8071403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
     <t xml:space="preserve">45.895622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1659469604492</t>
+    <t xml:space="preserve">46.165943145752</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3163757324219</t>
+    <t xml:space="preserve">45.9149360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3163795471191</t>
   </si>
   <si>
     <t xml:space="preserve">45.4129219055176</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699714660645</t>
+    <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388336181641</t>
@@ -3152,22 +3152,22 @@
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4290351867676</t>
+    <t xml:space="preserve">49.4290313720703</t>
   </si>
   <si>
     <t xml:space="preserve">50.5875244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1321792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6977424621582</t>
+    <t xml:space="preserve">52.1321754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6977386474609</t>
   </si>
   <si>
     <t xml:space="preserve">56.1869010925293</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1659927368164</t>
+    <t xml:space="preserve">58.1659965515137</t>
   </si>
   <si>
     <t xml:space="preserve">60.145092010498</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">59.7106552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">60.6277923583984</t>
+    <t xml:space="preserve">60.6277961730957</t>
   </si>
   <si>
     <t xml:space="preserve">61.2553100585938</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">60.2899017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7589263916016</t>
+    <t xml:space="preserve">59.7589302062988</t>
   </si>
   <si>
     <t xml:space="preserve">58.021183013916</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">55.849006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">56.283447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4354782104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4491691589355</t>
+    <t xml:space="preserve">56.2834434509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4354820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4491653442383</t>
   </si>
   <si>
     <t xml:space="preserve">53.9664573669434</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5802993774414</t>
+    <t xml:space="preserve">53.5802955627441</t>
   </si>
   <si>
     <t xml:space="preserve">54.0147285461426</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">54.9318733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4282569885254</t>
+    <t xml:space="preserve">56.4282608032227</t>
   </si>
   <si>
     <t xml:space="preserve">55.0284118652344</t>
@@ -3239,34 +3239,34 @@
     <t xml:space="preserve">54.2078170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3872108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9873657226562</t>
+    <t xml:space="preserve">53.3872184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9873695373535</t>
   </si>
   <si>
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7733764648438</t>
+    <t xml:space="preserve">53.773380279541</t>
   </si>
   <si>
     <t xml:space="preserve">54.9801406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2351760864258</t>
+    <t xml:space="preserve">56.2351722717285</t>
   </si>
   <si>
     <t xml:space="preserve">57.3453979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5038909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6004295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9656867980957</t>
+    <t xml:space="preserve">58.5038871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6004333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.965690612793</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">61.303581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3864402770996</t>
+    <t xml:space="preserve">60.3864364624023</t>
   </si>
   <si>
     <t xml:space="preserve">58.6969718933105</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">58.4073524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">55.221492767334</t>
+    <t xml:space="preserve">55.2214965820312</t>
   </si>
   <si>
     <t xml:space="preserve">54.0629997253418</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8288764953613</t>
+    <t xml:space="preserve">50.8288726806641</t>
   </si>
   <si>
     <t xml:space="preserve">51.8908271789551</t>
@@ -3314,31 +3314,31 @@
     <t xml:space="preserve">50.0565452575684</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2359466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4837608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8425598144531</t>
+    <t xml:space="preserve">49.2359504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4837532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8425559997559</t>
   </si>
   <si>
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1184997558594</t>
+    <t xml:space="preserve">51.1185035705566</t>
   </si>
   <si>
     <t xml:space="preserve">52.37353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1804504394531</t>
+    <t xml:space="preserve">52.1804466247559</t>
   </si>
   <si>
     <t xml:space="preserve">50.3461685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4563941955566</t>
+    <t xml:space="preserve">51.4563903808594</t>
   </si>
   <si>
     <t xml:space="preserve">50.9254150390625</t>
@@ -3347,25 +3347,25 @@
     <t xml:space="preserve">50.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7186508178711</t>
+    <t xml:space="preserve">49.7186546325684</t>
   </si>
   <si>
     <t xml:space="preserve">45.0074462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3976402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0919075012207</t>
+    <t xml:space="preserve">46.3976440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8763198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0919036865234</t>
   </si>
   <si>
     <t xml:space="preserve">41.2423439025879</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4893226623535</t>
+    <t xml:space="preserve">40.4893264770508</t>
   </si>
   <si>
     <t xml:space="preserve">42.555305480957</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">46.8224220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2633094787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7942886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5738410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8771476745605</t>
+    <t xml:space="preserve">51.2633056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7942848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5738372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8771438598633</t>
   </si>
   <si>
     <t xml:space="preserve">51.0219535827637</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">49.911735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6486434936523</t>
+    <t xml:space="preserve">46.6486473083496</t>
   </si>
   <si>
     <t xml:space="preserve">45.2970695495605</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">41.647819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8063087463379</t>
+    <t xml:space="preserve">42.8063125610352</t>
   </si>
   <si>
     <t xml:space="preserve">44.119270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6253051757812</t>
+    <t xml:space="preserve">45.6253089904785</t>
   </si>
   <si>
     <t xml:space="preserve">47.0348129272461</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">45.8376998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">44.157886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4627914428711</t>
+    <t xml:space="preserve">44.1578903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4627876281738</t>
   </si>
   <si>
     <t xml:space="preserve">44.1254501342773</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">43.4043235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">44.827091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.444766998291</t>
+    <t xml:space="preserve">44.8270950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4447708129883</t>
   </si>
   <si>
     <t xml:space="preserve">45.431282043457</t>
@@ -3470,13 +3470,13 @@
     <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.645679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3923072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5092468261719</t>
+    <t xml:space="preserve">45.6456756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3923110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5092506408691</t>
   </si>
   <si>
     <t xml:space="preserve">44.3983154296875</t>
@@ -3485,22 +3485,22 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9995727539062</t>
+    <t xml:space="preserve">41.0070457458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9995765686035</t>
   </si>
   <si>
     <t xml:space="preserve">40.3054046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1360054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7012176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766250610352</t>
+    <t xml:space="preserve">39.1360015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7012138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766212463379</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3509,40 +3509,40 @@
     <t xml:space="preserve">40.3248977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8706130981445</t>
+    <t xml:space="preserve">40.8706169128418</t>
   </si>
   <si>
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7806396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0924797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8841018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9620628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8586006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0025024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3593368530273</t>
+    <t xml:space="preserve">41.8646087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7806434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8840980529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9620590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8586044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0025062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507789611816</t>
+    <t xml:space="preserve">45.4507751464844</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3557,28 +3557,28 @@
     <t xml:space="preserve">50.1381340026855</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8202857971191</t>
+    <t xml:space="preserve">50.8202819824219</t>
   </si>
   <si>
     <t xml:space="preserve">51.2100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7460594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9177322387695</t>
+    <t xml:space="preserve">51.7460556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9177284240723</t>
   </si>
   <si>
     <t xml:space="preserve">51.5511589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5488891601562</t>
+    <t xml:space="preserve">53.548885345459</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517112731934</t>
+    <t xml:space="preserve">55.3517189025879</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">55.8389663696289</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0338706970215</t>
+    <t xml:space="preserve">56.0338668823242</t>
   </si>
   <si>
     <t xml:space="preserve">54.3772125244141</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">54.1335868835449</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1080932617188</t>
+    <t xml:space="preserve">55.1080894470215</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
@@ -3611,16 +3611,16 @@
     <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4004364013672</t>
+    <t xml:space="preserve">55.4004440307617</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5466156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4746704101562</t>
+    <t xml:space="preserve">55.5466194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.474666595459</t>
   </si>
   <si>
     <t xml:space="preserve">53.0616416931152</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">52.5743865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5256576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4792022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7970542907715</t>
+    <t xml:space="preserve">52.5256614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4792098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7970504760742</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
@@ -3644,10 +3644,10 @@
     <t xml:space="preserve">50.8690071105957</t>
   </si>
   <si>
-    <t xml:space="preserve">50.771556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0151824951172</t>
+    <t xml:space="preserve">50.7715530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0151786804199</t>
   </si>
   <si>
     <t xml:space="preserve">51.5024299621582</t>
@@ -3659,16 +3659,16 @@
     <t xml:space="preserve">51.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5998878479004</t>
+    <t xml:space="preserve">51.5998840332031</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3817558288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8480491638184</t>
+    <t xml:space="preserve">50.3817596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8480529785156</t>
   </si>
   <si>
     <t xml:space="preserve">45.8015937805176</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">46.8345718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5362129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7311096191406</t>
+    <t xml:space="preserve">47.5362091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7738265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7311134338379</t>
   </si>
   <si>
     <t xml:space="preserve">49.9919548034668</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4522438049316</t>
+    <t xml:space="preserve">49.7483329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4522399902344</t>
   </si>
   <si>
     <t xml:space="preserve">48.871280670166</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">58.5188484191895</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4468994140625</t>
+    <t xml:space="preserve">57.4468955993652</t>
   </si>
   <si>
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494491577148</t>
+    <t xml:space="preserve">57.3494415283203</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698432922363</t>
+    <t xml:space="preserve">56.5698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3755,25 +3755,25 @@
     <t xml:space="preserve">61.0038299560547</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8111991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6395225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8599281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2497253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9828720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4213981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6882476806641</t>
+    <t xml:space="preserve">58.8111953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6395263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8599243164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2497215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9828758239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4214019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6882514953613</t>
   </si>
   <si>
     <t xml:space="preserve">61.2961807250977</t>
@@ -3797,16 +3797,16 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.484260559082</t>
+    <t xml:space="preserve">67.4842758178711</t>
   </si>
   <si>
     <t xml:space="preserve">68.1176910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8230819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3590469360352</t>
+    <t xml:space="preserve">69.8230743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3590393066406</t>
   </si>
   <si>
     <t xml:space="preserve">68.9460220336914</t>
@@ -3815,13 +3815,13 @@
     <t xml:space="preserve">68.410041809082</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8740692138672</t>
+    <t xml:space="preserve">67.8740615844727</t>
   </si>
   <si>
     <t xml:space="preserve">68.3125915527344</t>
   </si>
   <si>
-    <t xml:space="preserve">67.1919097900391</t>
+    <t xml:space="preserve">67.1919174194336</t>
   </si>
   <si>
     <t xml:space="preserve">68.8972930908203</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">65.4865341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5817108154297</t>
+    <t xml:space="preserve">67.5817260742188</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8995742797852</t>
+    <t xml:space="preserve">66.8995666503906</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0434646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6514053344727</t>
+    <t xml:space="preserve">69.0434722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6513977050781</t>
   </si>
   <si>
     <t xml:space="preserve">71.7233505249023</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">71.4309997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5284576416016</t>
+    <t xml:space="preserve">71.528450012207</t>
   </si>
   <si>
     <t xml:space="preserve">72.6978530883789</t>
@@ -3884,16 +3884,16 @@
     <t xml:space="preserve">75.6700897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">75.0366516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.305778503418</t>
+    <t xml:space="preserve">75.0366592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.3057861328125</t>
   </si>
   <si>
     <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7188110351562</t>
+    <t xml:space="preserve">75.7188034057617</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">76.839485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">77.2780227661133</t>
+    <t xml:space="preserve">77.2780151367188</t>
   </si>
   <si>
     <t xml:space="preserve">77.3754653930664</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859329223633</t>
+    <t xml:space="preserve">78.8859405517578</t>
   </si>
   <si>
     <t xml:space="preserve">77.5703659057617</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295623779297</t>
+    <t xml:space="preserve">78.0088958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295700073242</t>
   </si>
   <si>
     <t xml:space="preserve">77.424186706543</t>
@@ -3950,10 +3950,10 @@
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.032112121582</t>
+    <t xml:space="preserve">78.3012313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0321197509766</t>
   </si>
   <si>
     <t xml:space="preserve">78.4474182128906</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">77.4729156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9647064208984</t>
+    <t xml:space="preserve">73.964714050293</t>
   </si>
   <si>
     <t xml:space="preserve">74.4519653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">71.82080078125</t>
+    <t xml:space="preserve">71.8207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">77.9601593017578</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">75.8162612915039</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7165374755859</t>
+    <t xml:space="preserve">77.7165451049805</t>
   </si>
   <si>
     <t xml:space="preserve">80.3964233398438</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">80.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7119903564453</t>
+    <t xml:space="preserve">81.7119979858398</t>
   </si>
   <si>
     <t xml:space="preserve">81.4683685302734</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">81.8581695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.268928527832</t>
+    <t xml:space="preserve">81.7607192993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2689361572266</t>
   </si>
   <si>
     <t xml:space="preserve">88.1924362182617</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488143920898</t>
+    <t xml:space="preserve">87.9488067626953</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
@@ -4019,13 +4019,13 @@
     <t xml:space="preserve">88.6796875</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9000854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434387207031</t>
+    <t xml:space="preserve">87.9000778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3408737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434234619141</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">87.8513641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3618316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0972518920898</t>
+    <t xml:space="preserve">89.3618392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">87.3153839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">84.4893264770508</t>
+    <t xml:space="preserve">84.4893341064453</t>
   </si>
   <si>
     <t xml:space="preserve">82.1017990112305</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1250305175781</t>
+    <t xml:space="preserve">83.1250228881836</t>
   </si>
   <si>
     <t xml:space="preserve">85.6100082397461</t>
@@ -4082,25 +4082,25 @@
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5299453735352</t>
+    <t xml:space="preserve">79.9091720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096496582031</t>
+    <t xml:space="preserve">77.1096420288086</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.632194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830841064453</t>
+    <t xml:space="preserve">78.6322021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618179321289</t>
+    <t xml:space="preserve">79.7618255615234</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370239257812</t>
+    <t xml:space="preserve">81.1370315551758</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909713745117</t>
+    <t xml:space="preserve">83.6909790039062</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.628173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317169189453</t>
+    <t xml:space="preserve">81.6281661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317092895508</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.07421875</t>
+    <t xml:space="preserve">79.0742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9268798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0959548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326644897461</t>
+    <t xml:space="preserve">78.926872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326721191406</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853256225586</t>
+    <t xml:space="preserve">75.6853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928970336914</t>
+    <t xml:space="preserve">72.4928894042969</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870895385742</t>
+    <t xml:space="preserve">75.5870971679688</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402282714844</t>
+    <t xml:space="preserve">72.6402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176910400391</t>
+    <t xml:space="preserve">71.1176834106445</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597076416016</t>
+    <t xml:space="preserve">71.5597152709961</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4253,19 +4253,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022247314453</t>
+    <t xml:space="preserve">72.3946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022171020508</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212265014648</t>
+    <t xml:space="preserve">70.9212188720703</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5419998168945</t>
+    <t xml:space="preserve">72.5420074462891</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389343261719</t>
+    <t xml:space="preserve">73.4260711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.827018737793</t>
+    <t xml:space="preserve">67.8270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247695922852</t>
+    <t xml:space="preserve">70.7247772216797</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.5460205078125</t>
+    <t xml:space="preserve">69.546028137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698593139648</t>
+    <t xml:space="preserve">73.7698669433594</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4364,19 +4364,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065841674805</t>
+    <t xml:space="preserve">77.6007919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065765380859</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481307983398</t>
+    <t xml:space="preserve">77.7481384277344</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4397,25 +4397,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.9309005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238143920898</t>
+    <t xml:space="preserve">75.930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238067626953</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344360351562</t>
+    <t xml:space="preserve">75.7344436645508</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4445,19 +4445,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.905143737793</t>
+    <t xml:space="preserve">82.9051513671875</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046737670898</t>
+    <t xml:space="preserve">85.7046661376953</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851791381836</t>
+    <t xml:space="preserve">86.7851867675781</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4469,13 +4469,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542541503906</t>
+    <t xml:space="preserve">82.9542617797852</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489471435547</t>
+    <t xml:space="preserve">83.2489547729492</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4487,16 +4487,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312393188477</t>
+    <t xml:space="preserve">84.2312316894531</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507186889648</t>
+    <t xml:space="preserve">82.5613479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507263183594</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338272094727</t>
+    <t xml:space="preserve">89.6338195800781</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581359863281</t>
+    <t xml:space="preserve">91.0581436157227</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.857666015625</t>
+    <t xml:space="preserve">93.8576736450195</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747375488281</t>
+    <t xml:space="preserve">102.845596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.827896118164</t>
+    <t xml:space="preserve">103.82788848877</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034027099609</t>
+    <t xml:space="preserve">109.034019470215</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525169372559</t>
+    <t xml:space="preserve">109.525161743164</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.631439208984</t>
+    <t xml:space="preserve">103.63143157959</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122573852539</t>
+    <t xml:space="preserve">102.158004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122581481934</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987426757812</t>
+    <t xml:space="preserve">99.8987350463867</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518661499023</t>
+    <t xml:space="preserve">96.3625030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518737792969</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4670,13 +4670,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2642669677734</t>
+    <t xml:space="preserve">96.264274597168</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5589599609375</t>
+    <t xml:space="preserve">96.558967590332</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890609741211</t>
+    <t xml:space="preserve">94.8890686035156</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488082885742</t>
+    <t xml:space="preserve">94.7417144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488159179688</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5715,6 +5715,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.6800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0800018310547</t>
   </si>
 </sst>
 </file>
@@ -71547,7 +71550,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912962963</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>245783</v>
@@ -71568,6 +71571,32 @@
         <v>1872</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6910185185</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>168571</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>90.5999984741211</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>89.620002746582</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>90.2600021362305</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>90.0800018310547</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1901</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="1903">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,100 +44,100 @@
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.171820640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0406274795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208875656128</t>
+    <t xml:space="preserve">14.8537855148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1718196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289274215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0406265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208856582642</t>
   </si>
   <si>
     <t xml:space="preserve">15.3022012710571</t>
   </si>
   <si>
-    <t xml:space="preserve">14.44273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389188766479</t>
+    <t xml:space="preserve">14.4427366256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389207839966</t>
   </si>
   <si>
     <t xml:space="preserve">14.0877418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0410318374634</t>
+    <t xml:space="preserve">14.0410308837891</t>
   </si>
   <si>
     <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3399772644043</t>
+    <t xml:space="preserve">14.33997631073</t>
   </si>
   <si>
     <t xml:space="preserve">14.7697095870972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3866863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943218231201</t>
+    <t xml:space="preserve">14.3866853713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943208694458</t>
   </si>
   <si>
     <t xml:space="preserve">14.424054145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3960275650024</t>
+    <t xml:space="preserve">14.3960266113281</t>
   </si>
   <si>
     <t xml:space="preserve">13.9849805831909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0036640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4337997436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051267623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4155235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4061813354492</t>
+    <t xml:space="preserve">14.003662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4155225753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4061822891235</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722269058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251087188721</t>
+    <t xml:space="preserve">13.5459051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645914077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251096725464</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195852279663</t>
@@ -146,154 +146,154 @@
     <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7607707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8355083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1064252853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372140884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.255898475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4143047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011447906494</t>
+    <t xml:space="preserve">13.7607727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8355093002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1064262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372121810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011486053467</t>
   </si>
   <si>
     <t xml:space="preserve">15.2461500167847</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1060190200806</t>
+    <t xml:space="preserve">15.1060199737549</t>
   </si>
   <si>
     <t xml:space="preserve">15.3769359588623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4797019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
+    <t xml:space="preserve">15.479700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385116577148</t>
   </si>
   <si>
     <t xml:space="preserve">15.5450944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945657730103</t>
+    <t xml:space="preserve">15.6945638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.6104869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4983835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939165115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412776947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253555297852</t>
+    <t xml:space="preserve">15.4983854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873365402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253545761108</t>
   </si>
   <si>
     <t xml:space="preserve">16.3017978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3952178955078</t>
+    <t xml:space="preserve">16.3952159881592</t>
   </si>
   <si>
     <t xml:space="preserve">16.3858737945557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3485069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4139003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924537658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671894073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0215358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.217716217041</t>
+    <t xml:space="preserve">16.3485050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4139022827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0215396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2177200317383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4419269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889831542969</t>
+    <t xml:space="preserve">16.3391666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.61008644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4419288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889869689941</t>
   </si>
   <si>
     <t xml:space="preserve">16.6489791870117</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5548648834229</t>
+    <t xml:space="preserve">16.5548667907715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.601921081543</t>
+    <t xml:space="preserve">16.6019229888916</t>
   </si>
   <si>
     <t xml:space="preserve">16.6866264343262</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">16.7995643615723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5454540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8278007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8183860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254600524902</t>
+    <t xml:space="preserve">16.5454521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8277988433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8183879852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254619598389</t>
   </si>
   <si>
     <t xml:space="preserve">15.6890048980713</t>
   </si>
   <si>
-    <t xml:space="preserve">15.472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407793045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.583101272583</t>
+    <t xml:space="preserve">15.4725427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407783508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5830993652344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4325141906738</t>
+    <t xml:space="preserve">16.4325122833252</t>
   </si>
   <si>
     <t xml:space="preserve">16.253698348999</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">16.5642776489258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5290079116821</t>
+    <t xml:space="preserve">15.5290098190308</t>
   </si>
   <si>
     <t xml:space="preserve">14.8796157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0678453445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748985290527</t>
+    <t xml:space="preserve">15.0678472518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748994827271</t>
   </si>
   <si>
     <t xml:space="preserve">15.2090167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101852416992</t>
+    <t xml:space="preserve">15.5101871490479</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3149223327637</t>
+    <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443271636963</t>
@@ -377,70 +377,70 @@
     <t xml:space="preserve">14.9172611236572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6513595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195980072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854768753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054727554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301792144775</t>
+    <t xml:space="preserve">15.5384216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6513586044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195970535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854787826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301753997803</t>
   </si>
   <si>
     <t xml:space="preserve">15.9901733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7925310134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478353500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.933705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.670184135437</t>
+    <t xml:space="preserve">15.7925319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701822280884</t>
   </si>
   <si>
     <t xml:space="preserve">15.3784255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5007753372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419458389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148817062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0278205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2725200653076</t>
+    <t xml:space="preserve">15.5007743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148836135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0278186798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2725219726562</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2819309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1595802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3760452270508</t>
+    <t xml:space="preserve">16.2819271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1595821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.376049041748</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983978271484</t>
@@ -449,31 +449,31 @@
     <t xml:space="preserve">16.460750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301593780518</t>
+    <t xml:space="preserve">16.5078086853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301574707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9877948760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372097015381</t>
+    <t xml:space="preserve">16.7807388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560314178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.98779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0160293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
@@ -488,43 +488,43 @@
     <t xml:space="preserve">16.8936805725098</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6960372924805</t>
+    <t xml:space="preserve">16.6960353851318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842658996582</t>
+    <t xml:space="preserve">16.7713317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842697143555</t>
   </si>
   <si>
     <t xml:space="preserve">16.7525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9030933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0066184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9972038269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0536785125732</t>
+    <t xml:space="preserve">16.9030895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0066223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9972076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0536766052246</t>
   </si>
   <si>
     <t xml:space="preserve">16.8748569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.034854888916</t>
+    <t xml:space="preserve">17.0348529815674</t>
   </si>
   <si>
     <t xml:space="preserve">16.8654460906982</t>
@@ -536,58 +536,58 @@
     <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289672851562</t>
+    <t xml:space="preserve">17.2324962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289691925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136707305908</t>
+    <t xml:space="preserve">17.2136726379395</t>
   </si>
   <si>
     <t xml:space="preserve">17.3548469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3642597198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3077850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.298376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7383365631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230457305908</t>
+    <t xml:space="preserve">17.3642559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3077869415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.738338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230419158936</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818714141846</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430320739746</t>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3783187866211</t>
+    <t xml:space="preserve">19.3783206939697</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359798431396</t>
@@ -596,58 +596,58 @@
     <t xml:space="preserve">19.2183246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5571422576904</t>
+    <t xml:space="preserve">19.5571403503418</t>
   </si>
   <si>
     <t xml:space="preserve">19.4159660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2724170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4229984283447</t>
+    <t xml:space="preserve">20.2724189758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.423002243042</t>
   </si>
   <si>
     <t xml:space="preserve">20.2347717285156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2535953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4982929229736</t>
+    <t xml:space="preserve">20.2535934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.498291015625</t>
   </si>
   <si>
     <t xml:space="preserve">20.357120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8935794830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6677017211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665332794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1030101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5194931030273</t>
+    <t xml:space="preserve">20.893575668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6676998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1030082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8206615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7453708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.519495010376</t>
   </si>
   <si>
     <t xml:space="preserve">19.6889019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171382904053</t>
+    <t xml:space="preserve">19.7171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">19.84889793396</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">19.4630279541016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2747917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3877353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3500862121582</t>
+    <t xml:space="preserve">19.2747936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4442043304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3877334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3500843048096</t>
   </si>
   <si>
     <t xml:space="preserve">19.3971462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959777832031</t>
+    <t xml:space="preserve">19.0959796905518</t>
   </si>
   <si>
     <t xml:space="preserve">19.0018615722656</t>
@@ -689,40 +689,40 @@
     <t xml:space="preserve">19.0865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8701000213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4936351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.352466583252</t>
+    <t xml:space="preserve">18.870096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4936370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524646759033</t>
   </si>
   <si>
     <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2371501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006713867188</t>
+    <t xml:space="preserve">18.6254043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.255973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.510082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2371463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006694793701</t>
   </si>
   <si>
     <t xml:space="preserve">19.7547817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7924327850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5947875976562</t>
+    <t xml:space="preserve">19.7924289703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947895050049</t>
   </si>
   <si>
     <t xml:space="preserve">20.6018161773682</t>
@@ -731,61 +731,61 @@
     <t xml:space="preserve">20.7335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994613647461</t>
+    <t xml:space="preserve">20.7994594573975</t>
   </si>
   <si>
     <t xml:space="preserve">20.7900524139404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9218120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.298267364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.015926361084</t>
+    <t xml:space="preserve">20.9218101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2982730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0159282684326</t>
   </si>
   <si>
     <t xml:space="preserve">20.9029884338379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0253391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947422027588</t>
+    <t xml:space="preserve">21.0253372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947441101074</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6088485717773</t>
+    <t xml:space="preserve">21.1100406646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.608850479126</t>
   </si>
   <si>
     <t xml:space="preserve">21.2135696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3829765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8347282409668</t>
+    <t xml:space="preserve">21.3829784393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8347301483154</t>
   </si>
   <si>
     <t xml:space="preserve">22.0229587554932</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">22.0417823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2582454681396</t>
+    <t xml:space="preserve">22.258243560791</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817665100098</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">22.6252975463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0394058227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7288246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0582275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876522064209</t>
+    <t xml:space="preserve">23.0394039154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7288208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0582256317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876502990723</t>
   </si>
   <si>
     <t xml:space="preserve">22.3711853027344</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">22.0135478973389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9194316864014</t>
+    <t xml:space="preserve">21.6464996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.098123550415</t>
+    <t xml:space="preserve">22.0981197357178</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1549797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686901092529</t>
+    <t xml:space="preserve">22.1549777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686939239502</t>
   </si>
   <si>
     <t xml:space="preserve">22.0507431030273</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190818786621</t>
+    <t xml:space="preserve">21.7190799713135</t>
   </si>
   <si>
     <t xml:space="preserve">22.08864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7569828033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327922821045</t>
+    <t xml:space="preserve">21.7569847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327941894531</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811752319336</t>
@@ -875,64 +875,64 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1315650939941</t>
+    <t xml:space="preserve">21.7285575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1315670013428</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4632301330566</t>
+    <t xml:space="preserve">21.8612213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4632263183594</t>
   </si>
   <si>
     <t xml:space="preserve">21.6622257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5674667358398</t>
+    <t xml:space="preserve">21.5674648284912</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013538360596</t>
+    <t xml:space="preserve">22.4013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">22.5529727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5813980102539</t>
+    <t xml:space="preserve">22.5813999176025</t>
   </si>
   <si>
     <t xml:space="preserve">22.6761627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">22.590877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7948894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138427734375</t>
+    <t xml:space="preserve">22.5908737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7948913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138408660889</t>
   </si>
   <si>
     <t xml:space="preserve">21.8422698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717052459717</t>
+    <t xml:space="preserve">21.6717014312744</t>
   </si>
   <si>
     <t xml:space="preserve">21.5958938598633</t>
@@ -947,55 +947,55 @@
     <t xml:space="preserve">22.5055923461914</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6951122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0362491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2068195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2162971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9983463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1310119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5005760192871</t>
+    <t xml:space="preserve">22.6951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0362510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2068176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2162933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.998348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.131010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5005741119385</t>
   </si>
   <si>
     <t xml:space="preserve">23.6900978088379</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2731494903564</t>
+    <t xml:space="preserve">23.2731533050537</t>
   </si>
   <si>
     <t xml:space="preserve">23.1404857635498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.405818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4531955718994</t>
+    <t xml:space="preserve">23.4058170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.453197479248</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950963973999</t>
+    <t xml:space="preserve">22.9509658813477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0646800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7519721984863</t>
+    <t xml:space="preserve">22.7519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.723539352417</t>
@@ -1004,55 +1004,55 @@
     <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6477336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4771614074707</t>
+    <t xml:space="preserve">22.6477317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.477165222168</t>
   </si>
   <si>
     <t xml:space="preserve">22.183406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">23.87961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1165161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6616668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1783885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9035873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0217571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955635070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145130157471</t>
+    <t xml:space="preserve">23.8796195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1165199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6616687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3868637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1783905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.90358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0217590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145111083984</t>
   </si>
   <si>
     <t xml:space="preserve">24.6376991271973</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6850814819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8082733154297</t>
+    <t xml:space="preserve">24.685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8082714080811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7798404693604</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429382324219</t>
+    <t xml:space="preserve">24.5429420471191</t>
   </si>
   <si>
     <t xml:space="preserve">24.1638984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8651237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7558746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5473976135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915477752686</t>
+    <t xml:space="preserve">24.8651256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7558727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915496826172</t>
   </si>
   <si>
     <t xml:space="preserve">25.4052581787109</t>
@@ -1088,49 +1088,49 @@
     <t xml:space="preserve">25.4431648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4905433654785</t>
+    <t xml:space="preserve">25.4905471801758</t>
   </si>
   <si>
     <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484058380127</t>
+    <t xml:space="preserve">25.3484039306641</t>
   </si>
   <si>
     <t xml:space="preserve">25.3294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0830726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7274436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6611156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9643459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3054866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645687103271</t>
+    <t xml:space="preserve">25.0830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.727445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6611137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9643440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3054847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645725250244</t>
   </si>
   <si>
     <t xml:space="preserve">27.309944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119472503662</t>
+    <t xml:space="preserve">26.9119510650635</t>
   </si>
   <si>
     <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6750469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972343444824</t>
+    <t xml:space="preserve">26.675048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972362518311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1678028106689</t>
@@ -1142,61 +1142,61 @@
     <t xml:space="preserve">26.0591068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0451698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1778335571289</t>
+    <t xml:space="preserve">25.0451717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1778354644775</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.518970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1115036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5379257202148</t>
+    <t xml:space="preserve">25.5189723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.111499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5379238128662</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1588821411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3010215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9219818115234</t>
+    <t xml:space="preserve">25.1588802337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3010272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683597564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9219799041748</t>
   </si>
   <si>
     <t xml:space="preserve">25.2062606811523</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1020259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.860107421875</t>
+    <t xml:space="preserve">25.1020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8601112365723</t>
   </si>
   <si>
     <t xml:space="preserve">26.333911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2486267089844</t>
+    <t xml:space="preserve">26.248628616333</t>
   </si>
   <si>
     <t xml:space="preserve">26.4381484985352</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">24.7987937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3673553466797</t>
+    <t xml:space="preserve">25.3673572540283</t>
   </si>
   <si>
     <t xml:space="preserve">25.3578796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6800670623779</t>
+    <t xml:space="preserve">25.6800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.6232089996338</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">25.7748279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5947799682617</t>
+    <t xml:space="preserve">25.5947818756104</t>
   </si>
   <si>
     <t xml:space="preserve">25.7084922790527</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">26.8171882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0540924072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3857517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8695869445801</t>
+    <t xml:space="preserve">27.0540885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3857498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8695850372314</t>
   </si>
   <si>
     <t xml:space="preserve">25.8222045898438</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.632682800293</t>
+    <t xml:space="preserve">25.6326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7324600219727</t>
@@ -1256,52 +1256,52 @@
     <t xml:space="preserve">23.9743766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008007049561</t>
+    <t xml:space="preserve">24.4007987976074</t>
   </si>
   <si>
     <t xml:space="preserve">24.0691394805908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4481773376465</t>
+    <t xml:space="preserve">24.4481811523438</t>
   </si>
   <si>
     <t xml:space="preserve">24.8272228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7848587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2586612701416</t>
+    <t xml:space="preserve">23.7848567962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167407989502</t>
+    <t xml:space="preserve">25.0167446136475</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693622589111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9269981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433876037598</t>
+    <t xml:space="preserve">23.9269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433856964111</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0117263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1538696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4855270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5329093933105</t>
+    <t xml:space="preserve">26.0117282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4855308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593296051025</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">28.9492988586426</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6176357269287</t>
+    <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
     <t xml:space="preserve">28.8071575164795</t>
@@ -1331,64 +1331,64 @@
     <t xml:space="preserve">29.5394897460938</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0652751922607</t>
+    <t xml:space="preserve">30.2086734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0652732849121</t>
   </si>
   <si>
     <t xml:space="preserve">30.3042678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9696769714355</t>
+    <t xml:space="preserve">29.9696788787842</t>
   </si>
   <si>
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602367401123</t>
+    <t xml:space="preserve">31.2602386474609</t>
   </si>
   <si>
     <t xml:space="preserve">32.7419967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6501617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797180175781</t>
+    <t xml:space="preserve">33.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797218322754</t>
   </si>
   <si>
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9369583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9885215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.753303527832</t>
+    <t xml:space="preserve">34.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.936954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9885177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7532997131348</t>
   </si>
   <si>
     <t xml:space="preserve">35.9922943115234</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2275123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0841217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6576995849609</t>
+    <t xml:space="preserve">35.2275161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0841178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6577033996582</t>
   </si>
   <si>
     <t xml:space="preserve">35.275318145752</t>
@@ -1415,40 +1415,40 @@
     <t xml:space="preserve">30.7822532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036331176758</t>
+    <t xml:space="preserve">31.1168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036312103271</t>
   </si>
   <si>
     <t xml:space="preserve">31.5948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3558368682861</t>
+    <t xml:space="preserve">31.3558330535889</t>
   </si>
   <si>
     <t xml:space="preserve">31.2124404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0287857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9847526550293</t>
+    <t xml:space="preserve">33.0287818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.984748840332</t>
   </si>
   <si>
     <t xml:space="preserve">34.7973251342773</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3671493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6539306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0363235473633</t>
+    <t xml:space="preserve">34.3671455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.653938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.036319732666</t>
   </si>
   <si>
     <t xml:space="preserve">34.6061363220215</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7495307922363</t>
+    <t xml:space="preserve">33.8413581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7495346069336</t>
   </si>
   <si>
     <t xml:space="preserve">35.5621109008789</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">36.6614685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3306503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5180740356445</t>
+    <t xml:space="preserve">39.0035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3306465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5180778503418</t>
   </si>
   <si>
     <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8564338684082</t>
+    <t xml:space="preserve">37.8564300537109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2790832519531</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">37.2350540161133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8929290771484</t>
+    <t xml:space="preserve">34.8929214477539</t>
   </si>
   <si>
     <t xml:space="preserve">34.5583381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6979598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5067710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2677726745605</t>
+    <t xml:space="preserve">33.6979675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5067672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2677764892578</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640075683594</t>
@@ -1517,13 +1517,13 @@
     <t xml:space="preserve">32.9809837341309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3633766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7897872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8375854492188</t>
+    <t xml:space="preserve">33.3633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.789794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.837589263916</t>
   </si>
   <si>
     <t xml:space="preserve">32.5985946655273</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">32.5029983520508</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2199783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6464004516602</t>
+    <t xml:space="preserve">33.2199745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6463966369629</t>
   </si>
   <si>
     <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0728073120117</t>
+    <t xml:space="preserve">32.072811126709</t>
   </si>
   <si>
     <t xml:space="preserve">31.7860221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8338241577148</t>
+    <t xml:space="preserve">31.8338203430176</t>
   </si>
   <si>
     <t xml:space="preserve">31.0690422058105</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">32.0250129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0212440490723</t>
+    <t xml:space="preserve">31.0212478637695</t>
   </si>
   <si>
     <t xml:space="preserve">31.8816165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8703098297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5357227325439</t>
+    <t xml:space="preserve">28.8703117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5357208251953</t>
   </si>
   <si>
     <t xml:space="preserve">28.2011299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709465026855</t>
+    <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2489280700684</t>
+    <t xml:space="preserve">28.2489318847656</t>
   </si>
   <si>
     <t xml:space="preserve">27.5797500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1055355072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2451629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9621391296387</t>
+    <t xml:space="preserve">28.1055335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2451610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9621410369873</t>
   </si>
   <si>
     <t xml:space="preserve">28.3445281982422</t>
@@ -1598,49 +1598,49 @@
     <t xml:space="preserve">29.0137062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9181118011475</t>
+    <t xml:space="preserve">28.9181098937988</t>
   </si>
   <si>
     <t xml:space="preserve">29.2049007415771</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4954605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5872917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174770355225</t>
+    <t xml:space="preserve">30.4954586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5872898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174732208252</t>
   </si>
   <si>
     <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6828842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759811401367</t>
+    <t xml:space="preserve">29.6828861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5835189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759792327881</t>
   </si>
   <si>
     <t xml:space="preserve">26.3847885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2929611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4363555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8187427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231483459473</t>
+    <t xml:space="preserve">27.2929573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4363574981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231464385986</t>
   </si>
   <si>
     <t xml:space="preserve">28.6313190460205</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017665863037</t>
+    <t xml:space="preserve">27.1017684936523</t>
   </si>
   <si>
     <t xml:space="preserve">26.8627738952637</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">27.0061683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0979976654053</t>
+    <t xml:space="preserve">26.0979957580566</t>
   </si>
   <si>
     <t xml:space="preserve">25.6200103759766</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">26.1935920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156085968018</t>
+    <t xml:space="preserve">26.6237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156105041504</t>
   </si>
   <si>
     <t xml:space="preserve">26.2891902923584</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">26.7671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7269153594971</t>
+    <t xml:space="preserve">28.7269172668457</t>
   </si>
   <si>
     <t xml:space="preserve">28.9659099578857</t>
@@ -1697,25 +1697,25 @@
     <t xml:space="preserve">26.6715793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8149738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4803848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3885536193848</t>
+    <t xml:space="preserve">26.8149719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4803867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3885555267334</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.874080657959</t>
+    <t xml:space="preserve">29.8740825653076</t>
   </si>
   <si>
     <t xml:space="preserve">30.1608715057373</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3520660400391</t>
+    <t xml:space="preserve">30.3520679473877</t>
   </si>
   <si>
     <t xml:space="preserve">31.3080368041992</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">32.2162094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6023635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1721801757812</t>
+    <t xml:space="preserve">33.602367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.172176361084</t>
   </si>
   <si>
     <t xml:space="preserve">33.5545692443848</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6388549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910587310791</t>
+    <t xml:space="preserve">30.6388568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910606384277</t>
   </si>
   <si>
     <t xml:space="preserve">29.3004970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9409999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6484184265137</t>
+    <t xml:space="preserve">29.9409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.648416519165</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
@@ -1766,16 +1766,16 @@
     <t xml:space="preserve">30.9734497070312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2851467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0748310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4763412475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2277908325195</t>
+    <t xml:space="preserve">30.2851486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0748348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.47633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2277889251709</t>
   </si>
   <si>
     <t xml:space="preserve">29.9983558654785</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631359100342</t>
+    <t xml:space="preserve">30.438102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631340026855</t>
   </si>
   <si>
     <t xml:space="preserve">30.935209274292</t>
@@ -1799,55 +1799,55 @@
     <t xml:space="preserve">29.7498054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7115650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8129539489746</t>
+    <t xml:space="preserve">29.7115669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8129501342773</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203723907471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.487922668457</t>
+    <t xml:space="preserve">28.4879245758057</t>
   </si>
   <si>
     <t xml:space="preserve">28.717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821338653564</t>
+    <t xml:space="preserve">29.4821319580078</t>
   </si>
   <si>
     <t xml:space="preserve">29.1762237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761585235596</t>
+    <t xml:space="preserve">29.3291797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761566162109</t>
   </si>
   <si>
     <t xml:space="preserve">28.9237041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">28.653392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637657165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5182323455811</t>
+    <t xml:space="preserve">28.6533908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5182342529297</t>
   </si>
   <si>
     <t xml:space="preserve">27.8038291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0741443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1859645843506</t>
+    <t xml:space="preserve">28.0741424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1859664916992</t>
   </si>
   <si>
     <t xml:space="preserve">27.2245826721191</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">28.0548343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9969139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4989261627197</t>
+    <t xml:space="preserve">27.9969120025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4989242553711</t>
   </si>
   <si>
     <t xml:space="preserve">28.247917175293</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.900369644165</t>
+    <t xml:space="preserve">27.9003677368164</t>
   </si>
   <si>
     <t xml:space="preserve">28.0934505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6340808868408</t>
+    <t xml:space="preserve">28.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">29.1167888641357</t>
@@ -1928,31 +1928,31 @@
     <t xml:space="preserve">30.2173538208008</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9856567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6807556152344</t>
+    <t xml:space="preserve">29.9856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6807537078857</t>
   </si>
   <si>
     <t xml:space="preserve">29.3677940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4836444854736</t>
+    <t xml:space="preserve">29.4836463928223</t>
   </si>
   <si>
     <t xml:space="preserve">29.174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4257183074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2519435882568</t>
+    <t xml:space="preserve">29.4257164001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2519454956055</t>
   </si>
   <si>
     <t xml:space="preserve">29.4643363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0202465057373</t>
+    <t xml:space="preserve">29.0202445983887</t>
   </si>
   <si>
     <t xml:space="preserve">28.9043979644775</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">28.6920070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4796161651611</t>
+    <t xml:space="preserve">28.4796180725098</t>
   </si>
   <si>
     <t xml:space="preserve">27.7652130126953</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">26.9542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1473503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2825088500977</t>
+    <t xml:space="preserve">27.1473522186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.282506942749</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">28.1899948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">28.34446144104</t>
+    <t xml:space="preserve">28.3444595336914</t>
   </si>
   <si>
     <t xml:space="preserve">27.9389877319336</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">26.6260280609131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4176616668701</t>
+    <t xml:space="preserve">27.4176635742188</t>
   </si>
   <si>
     <t xml:space="preserve">28.035530090332</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">27.0894241333008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9928817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0508098602295</t>
+    <t xml:space="preserve">26.992883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0508079528809</t>
   </si>
   <si>
     <t xml:space="preserve">27.4755897521973</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">27.6107482910156</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6879806518555</t>
+    <t xml:space="preserve">27.6879787445068</t>
   </si>
   <si>
     <t xml:space="preserve">26.355712890625</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">25.8537006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8730049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.301815032959</t>
+    <t xml:space="preserve">25.8730068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3018169403076</t>
   </si>
   <si>
     <t xml:space="preserve">27.4562816619873</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">26.8577251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7957725524902</t>
+    <t xml:space="preserve">25.7957744598389</t>
   </si>
   <si>
     <t xml:space="preserve">25.9116230010986</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">27.7459030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1087322235107</t>
+    <t xml:space="preserve">27.1087341308594</t>
   </si>
   <si>
     <t xml:space="preserve">28.1320686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3830757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9430141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4064083099365</t>
+    <t xml:space="preserve">28.3830738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9430122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4064102172852</t>
   </si>
   <si>
     <t xml:space="preserve">28.8078575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.981632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1360969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7499294281006</t>
+    <t xml:space="preserve">28.9816303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1360950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7499313354492</t>
   </si>
   <si>
     <t xml:space="preserve">28.8271656036377</t>
@@ -2108,43 +2108,43 @@
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6147747039795</t>
+    <t xml:space="preserve">28.5954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6147727966309</t>
   </si>
   <si>
     <t xml:space="preserve">29.2133293151855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6228294372559</t>
+    <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
     <t xml:space="preserve">31.9357872009277</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3026428222656</t>
+    <t xml:space="preserve">32.3026466369629</t>
   </si>
   <si>
     <t xml:space="preserve">32.4571075439453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8585510253906</t>
+    <t xml:space="preserve">31.8585548400879</t>
   </si>
   <si>
     <t xml:space="preserve">31.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">31.182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6654739379883</t>
+    <t xml:space="preserve">31.1827659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.665470123291</t>
   </si>
   <si>
     <t xml:space="preserve">32.1674842834473</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2600021362305</t>
+    <t xml:space="preserve">31.2599983215332</t>
   </si>
   <si>
     <t xml:space="preserve">31.5882396697998</t>
@@ -2153,22 +2153,22 @@
     <t xml:space="preserve">31.047607421875</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9510726928711</t>
+    <t xml:space="preserve">30.9510707855225</t>
   </si>
   <si>
     <t xml:space="preserve">31.1248435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8545265197754</t>
+    <t xml:space="preserve">31.3565406799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8545246124268</t>
   </si>
   <si>
     <t xml:space="preserve">30.8931427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8159103393555</t>
+    <t xml:space="preserve">30.8159122467041</t>
   </si>
   <si>
     <t xml:space="preserve">31.3372325897217</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">30.4683628082275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0089912414551</t>
+    <t xml:space="preserve">31.0089931488037</t>
   </si>
   <si>
     <t xml:space="preserve">30.7000598907471</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">33.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8859214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8899421691895</t>
+    <t xml:space="preserve">33.8859176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8899459838867</t>
   </si>
   <si>
     <t xml:space="preserve">35.0250968933105</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">36.5311431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.955924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2069320678711</t>
+    <t xml:space="preserve">36.9559211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2069282531738</t>
   </si>
   <si>
     <t xml:space="preserve">35.7008895874023</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">35.8167343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9864883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2873611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0363540649414</t>
+    <t xml:space="preserve">34.9864807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2873573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0363578796387</t>
   </si>
   <si>
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9937133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6847839355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8778591156006</t>
+    <t xml:space="preserve">31.993709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6847801208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8778629302979</t>
   </si>
   <si>
     <t xml:space="preserve">32.3605690002441</t>
@@ -2246,31 +2246,31 @@
     <t xml:space="preserve">33.383903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8432731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7427062988281</t>
+    <t xml:space="preserve">32.8432693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7427082061768</t>
   </si>
   <si>
     <t xml:space="preserve">32.8239669799805</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9011993408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2447166442871</t>
+    <t xml:space="preserve">32.901195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2447204589844</t>
   </si>
   <si>
     <t xml:space="preserve">32.5343399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4764175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6928367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081146240234</t>
+    <t xml:space="preserve">32.4764137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081184387207</t>
   </si>
   <si>
     <t xml:space="preserve">29.3871021270752</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">29.8698081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7732677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0049667358398</t>
+    <t xml:space="preserve">29.773265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0049648284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274715423584</t>
@@ -2297,28 +2297,28 @@
     <t xml:space="preserve">26.2784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2937622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5407409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1931915283203</t>
+    <t xml:space="preserve">25.2937641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1240158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5407390594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1931934356689</t>
   </si>
   <si>
     <t xml:space="preserve">22.9767761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2744560241699</t>
+    <t xml:space="preserve">25.2744541168213</t>
   </si>
   <si>
     <t xml:space="preserve">25.737850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150844573975</t>
+    <t xml:space="preserve">25.8150825500488</t>
   </si>
   <si>
     <t xml:space="preserve">25.100679397583</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">24.791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8263359069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.019416809082</t>
+    <t xml:space="preserve">23.8263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0194187164307</t>
   </si>
   <si>
     <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4442005157471</t>
+    <t xml:space="preserve">24.4442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075946807861</t>
@@ -2351,34 +2351,34 @@
     <t xml:space="preserve">25.0427551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6220035552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300563812256</t>
+    <t xml:space="preserve">25.6220016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3943271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300582885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.8231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">26.664644241333</t>
+    <t xml:space="preserve">26.6646461486816</t>
   </si>
   <si>
     <t xml:space="preserve">26.645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2398643493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7185401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4482269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5833873748779</t>
+    <t xml:space="preserve">26.2398624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.718542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4482288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5833835601807</t>
   </si>
   <si>
     <t xml:space="preserve">26.5487937927246</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">26.0660877227783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.973575592041</t>
+    <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
     <t xml:space="preserve">26.375020980835</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">28.0162200927734</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0242729187012</t>
+    <t xml:space="preserve">30.0242748260498</t>
   </si>
   <si>
     <t xml:space="preserve">32.283332824707</t>
@@ -2417,22 +2417,22 @@
     <t xml:space="preserve">29.5994911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5721302032471</t>
+    <t xml:space="preserve">27.5721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">26.5681037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5061531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3903026580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5254592895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4055843353271</t>
+    <t xml:space="preserve">25.5061511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3903007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5254611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4055824279785</t>
   </si>
   <si>
     <t xml:space="preserve">24.482816696167</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">24.6565914154053</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2511177062988</t>
+    <t xml:space="preserve">24.2511196136475</t>
   </si>
   <si>
     <t xml:space="preserve">24.2897338867188</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">24.8496723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3283519744873</t>
+    <t xml:space="preserve">24.3283500671387</t>
   </si>
   <si>
     <t xml:space="preserve">24.8303642272949</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">24.1352672576904</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1545753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.038724899292</t>
+    <t xml:space="preserve">24.154577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0387287139893</t>
   </si>
   <si>
     <t xml:space="preserve">23.9035701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1505470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3822441101074</t>
+    <t xml:space="preserve">23.1505508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3822479248047</t>
   </si>
   <si>
     <t xml:space="preserve">23.0733165740967</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">23.7684135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5946388244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7877197265625</t>
+    <t xml:space="preserve">23.5946407318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7877216339111</t>
   </si>
   <si>
     <t xml:space="preserve">24.2704257965088</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">24.6372833251953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.081371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.34765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5447673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1047058105469</t>
+    <t xml:space="preserve">25.0813732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3476581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5447654724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1047077178955</t>
   </si>
   <si>
     <t xml:space="preserve">26.0853996276855</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">25.119987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9462146759033</t>
+    <t xml:space="preserve">24.9462127685547</t>
   </si>
   <si>
     <t xml:space="preserve">24.811056137085</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.5986671447754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7338237762451</t>
+    <t xml:space="preserve">24.7338218688965</t>
   </si>
   <si>
     <t xml:space="preserve">24.9848289489746</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">24.9269065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7611846923828</t>
+    <t xml:space="preserve">26.7611865997314</t>
   </si>
   <si>
     <t xml:space="preserve">26.2205543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6179752349854</t>
+    <t xml:space="preserve">24.6179733276367</t>
   </si>
   <si>
     <t xml:space="preserve">24.463508605957</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">25.1392955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6413078308105</t>
+    <t xml:space="preserve">25.6413097381592</t>
   </si>
   <si>
     <t xml:space="preserve">25.3130702972412</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">26.2977886199951</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7804927825928</t>
+    <t xml:space="preserve">26.7804946899414</t>
   </si>
   <si>
     <t xml:space="preserve">26.6067199707031</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">24.8689804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.772439956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1401214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7620162963867</t>
+    <t xml:space="preserve">24.7724380493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1401233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7620124816895</t>
   </si>
   <si>
     <t xml:space="preserve">32.1481781005859</t>
@@ -2621,34 +2621,34 @@
     <t xml:space="preserve">31.9744052886963</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9550933837891</t>
+    <t xml:space="preserve">31.9550952911377</t>
   </si>
   <si>
     <t xml:space="preserve">32.3798789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2680511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1755409240723</t>
+    <t xml:space="preserve">33.2680549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.175537109375</t>
   </si>
   <si>
     <t xml:space="preserve">34.1562309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245338439941</t>
+    <t xml:space="preserve">33.9245376586914</t>
   </si>
   <si>
     <t xml:space="preserve">35.1795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3726463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3879280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5810165405273</t>
+    <t xml:space="preserve">35.3726501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3879318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5810089111328</t>
   </si>
   <si>
     <t xml:space="preserve">35.2761116027832</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">35.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8706321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7547912597656</t>
+    <t xml:space="preserve">34.8706359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7547874450684</t>
   </si>
   <si>
     <t xml:space="preserve">35.6429595947266</t>
@@ -2672,58 +2672,58 @@
     <t xml:space="preserve">35.2181854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">34.465160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6003227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640228271484</t>
+    <t xml:space="preserve">34.4651641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6003189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640266418457</t>
   </si>
   <si>
     <t xml:space="preserve">32.495719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0556678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0596885681152</t>
+    <t xml:space="preserve">33.0556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0596923828125</t>
   </si>
   <si>
     <t xml:space="preserve">33.5383682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2913932800293</t>
+    <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7314529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3066711425781</t>
+    <t xml:space="preserve">32.9977378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7314491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3066673278809</t>
   </si>
   <si>
     <t xml:space="preserve">33.6349105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1908149719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9591178894043</t>
+    <t xml:space="preserve">33.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9591217041016</t>
   </si>
   <si>
     <t xml:space="preserve">31.8971748352051</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0709457397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.437801361084</t>
+    <t xml:space="preserve">32.0709419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4377975463867</t>
   </si>
   <si>
     <t xml:space="preserve">33.345287322998</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824562072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9631538391113</t>
+    <t xml:space="preserve">33.9824600219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9631500244141</t>
   </si>
   <si>
     <t xml:space="preserve">34.445858001709</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">34.0983085632324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5962905883789</t>
+    <t xml:space="preserve">33.5962944030762</t>
   </si>
   <si>
     <t xml:space="preserve">33.0749702453613</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6775512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5351676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8360481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4000129699707</t>
+    <t xml:space="preserve">34.677547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5351715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8360443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.400016784668</t>
   </si>
   <si>
     <t xml:space="preserve">36.4925270080566</t>
@@ -2786,28 +2786,28 @@
     <t xml:space="preserve">37.1490058898926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2801399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7201919555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6043472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5657272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.391960144043</t>
+    <t xml:space="preserve">36.2994384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2801361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7201957702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6043510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.565731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3919525146484</t>
   </si>
   <si>
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510200500488</t>
+    <t xml:space="preserve">37.6510162353516</t>
   </si>
   <si>
     <t xml:space="preserve">37.0331573486328</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5158615112305</t>
+    <t xml:space="preserve">37.5158576965332</t>
   </si>
   <si>
     <t xml:space="preserve">38.519889831543</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9100761413574</t>
+    <t xml:space="preserve">39.581844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
     <t xml:space="preserve">40.2383193969727</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">40.9527244567871</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1458053588867</t>
+    <t xml:space="preserve">41.1458015441895</t>
   </si>
   <si>
     <t xml:space="preserve">41.7057418823242</t>
@@ -2855,64 +2855,64 @@
     <t xml:space="preserve">41.9567489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3388900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8948020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7017135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6244812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5665588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3429183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780731201172</t>
+    <t xml:space="preserve">41.5319671630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3388862609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8947982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.701717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6244850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5665550231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3429145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780769348145</t>
   </si>
   <si>
     <t xml:space="preserve">41.0878791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2809600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3236045837402</t>
+    <t xml:space="preserve">41.2809638977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3236083984375</t>
   </si>
   <si>
     <t xml:space="preserve">42.4008369445801</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6711540222168</t>
+    <t xml:space="preserve">42.6711502075195</t>
   </si>
   <si>
     <t xml:space="preserve">42.8256187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8875694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5786399841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9841156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.848949432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3743019104004</t>
+    <t xml:space="preserve">43.887565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5786361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9841117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8489570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3743057250977</t>
   </si>
   <si>
     <t xml:space="preserve">47.3244361877441</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">49.7669258117676</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9600028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5601615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4636154174805</t>
+    <t xml:space="preserve">49.9600067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5601577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4636192321777</t>
   </si>
   <si>
     <t xml:space="preserve">47.2665100097656</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">47.4982109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4748725891113</t>
+    <t xml:space="preserve">46.4748687744141</t>
   </si>
   <si>
     <t xml:space="preserve">45.8183898925781</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7878341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6140556335449</t>
+    <t xml:space="preserve">47.6912879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7878303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6140594482422</t>
   </si>
   <si>
     <t xml:space="preserve">48.2705345153809</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.539249420166</t>
+    <t xml:space="preserve">50.5392532348633</t>
   </si>
   <si>
     <t xml:space="preserve">47.8457565307617</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9422988891602</t>
+    <t xml:space="preserve">47.4209747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9422950744629</t>
   </si>
   <si>
     <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9809150695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3807601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2978973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4909782409668</t>
+    <t xml:space="preserve">47.9809188842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3807563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0082778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2978935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4909820556641</t>
   </si>
   <si>
     <t xml:space="preserve">54.4974365234375</t>
@@ -3062,19 +3062,19 @@
     <t xml:space="preserve">52.0356407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6012077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7106018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.077449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.173999786377</t>
+    <t xml:space="preserve">51.601203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7105941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6567001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0774574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1739959716797</t>
   </si>
   <si>
     <t xml:space="preserve">47.9616050720215</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4402847290039</t>
+    <t xml:space="preserve">47.4402809143066</t>
   </si>
   <si>
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996543884277</t>
+    <t xml:space="preserve">46.8996505737305</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590278625488</t>
@@ -3098,13 +3098,13 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3010940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5907211303711</t>
+    <t xml:space="preserve">45.5287742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5907173156738</t>
   </si>
   <si>
     <t xml:space="preserve">46.8031158447266</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">45.895622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.165943145752</t>
+    <t xml:space="preserve">45.8956298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1659393310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">45.3163795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4129219055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4322280883789</t>
+    <t xml:space="preserve">45.4129180908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4322319030762</t>
   </si>
   <si>
     <t xml:space="preserve">46.0887107849121</t>
@@ -3143,25 +3143,25 @@
     <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0388336181641</t>
+    <t xml:space="preserve">47.1699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0388374328613</t>
   </si>
   <si>
     <t xml:space="preserve">48.9945945739746</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4290313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5875244140625</t>
+    <t xml:space="preserve">49.429027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5875282287598</t>
   </si>
   <si>
     <t xml:space="preserve">52.1321754455566</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6977386474609</t>
+    <t xml:space="preserve">51.6977424621582</t>
   </si>
   <si>
     <t xml:space="preserve">56.1869010925293</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">58.1659965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">60.145092010498</t>
+    <t xml:space="preserve">60.1450881958008</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6277961730957</t>
+    <t xml:space="preserve">59.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6277923583984</t>
   </si>
   <si>
     <t xml:space="preserve">61.2553100585938</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">60.2899017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7589302062988</t>
+    <t xml:space="preserve">59.7589263916016</t>
   </si>
   <si>
     <t xml:space="preserve">58.021183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0694580078125</t>
+    <t xml:space="preserve">58.0694541931152</t>
   </si>
   <si>
     <t xml:space="preserve">56.6213417053223</t>
@@ -3209,25 +3209,25 @@
     <t xml:space="preserve">56.2834434509277</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4354820251465</t>
+    <t xml:space="preserve">53.4354858398438</t>
   </si>
   <si>
     <t xml:space="preserve">54.4491653442383</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9664573669434</t>
+    <t xml:space="preserve">53.9664611816406</t>
   </si>
   <si>
     <t xml:space="preserve">54.7870597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5802955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0147285461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9318733215332</t>
+    <t xml:space="preserve">53.5802993774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9318695068359</t>
   </si>
   <si>
     <t xml:space="preserve">56.4282608032227</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">55.0284118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3872184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9873695373535</t>
+    <t xml:space="preserve">54.2078132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3872146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9873657226562</t>
   </si>
   <si>
     <t xml:space="preserve">55.4145774841309</t>
@@ -3257,19 +3257,19 @@
     <t xml:space="preserve">56.2351722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3453979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5038871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6004333496094</t>
+    <t xml:space="preserve">57.345401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5038909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
     <t xml:space="preserve">60.965690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0139579772949</t>
+    <t xml:space="preserve">61.0139617919922</t>
   </si>
   <si>
     <t xml:space="preserve">61.303581237793</t>
@@ -3278,10 +3278,10 @@
     <t xml:space="preserve">60.3864364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6969718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420913696289</t>
+    <t xml:space="preserve">58.6969680786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420951843262</t>
   </si>
   <si>
     <t xml:space="preserve">58.4073524475098</t>
@@ -3305,31 +3305,31 @@
     <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8288726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8908271789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0565452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2359504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4837532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8425559997559</t>
+    <t xml:space="preserve">50.8288764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8908309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0565490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2359466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.483757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8425598144531</t>
   </si>
   <si>
     <t xml:space="preserve">50.6840629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1185035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.37353515625</t>
+    <t xml:space="preserve">51.1184959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">52.1804466247559</t>
@@ -3338,61 +3338,61 @@
     <t xml:space="preserve">50.3461685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4563903808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9254150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7806053161621</t>
+    <t xml:space="preserve">51.4563941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9254188537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7806015014648</t>
   </si>
   <si>
     <t xml:space="preserve">49.7186546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0074462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3976440429688</t>
+    <t xml:space="preserve">45.0074501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3976402282715</t>
   </si>
   <si>
     <t xml:space="preserve">45.8763198852539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2423439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4893264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.555305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.149829864502</t>
+    <t xml:space="preserve">42.0919075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2423477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4893226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5553092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1498336791992</t>
   </si>
   <si>
     <t xml:space="preserve">45.5480766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8224220275879</t>
+    <t xml:space="preserve">46.8224182128906</t>
   </si>
   <si>
     <t xml:space="preserve">51.2633056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5738372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8771438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219535827637</t>
+    <t xml:space="preserve">51.7942886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5738410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8771476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219612121582</t>
   </si>
   <si>
     <t xml:space="preserve">49.911735534668</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">46.9961929321289</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4169502258301</t>
+    <t xml:space="preserve">46.4169464111328</t>
   </si>
   <si>
     <t xml:space="preserve">44.9495239257812</t>
@@ -3431,19 +3431,19 @@
     <t xml:space="preserve">45.6253089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0348129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376998901367</t>
+    <t xml:space="preserve">47.0348091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.837703704834</t>
   </si>
   <si>
     <t xml:space="preserve">44.1578903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4627876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1254501342773</t>
+    <t xml:space="preserve">43.4627914428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1254539489746</t>
   </si>
   <si>
     <t xml:space="preserve">42.3908386230469</t>
@@ -3458,16 +3458,16 @@
     <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.431282043457</t>
+    <t xml:space="preserve">46.444766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4312858581543</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9380264282227</t>
+    <t xml:space="preserve">45.9380226135254</t>
   </si>
   <si>
     <t xml:space="preserve">45.6456756591797</t>
@@ -3485,22 +3485,22 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070457458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9995765686035</t>
+    <t xml:space="preserve">41.0070495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
     <t xml:space="preserve">40.3054046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1360015869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7012138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766212463379</t>
+    <t xml:space="preserve">39.1360054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7012176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766250610352</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">41.9620590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8586044311523</t>
+    <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
     <t xml:space="preserve">45.0025062561035</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">49.1636276245117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1381340026855</t>
+    <t xml:space="preserve">50.1381301879883</t>
   </si>
   <si>
     <t xml:space="preserve">50.8202819824219</t>
@@ -3566,19 +3566,19 @@
     <t xml:space="preserve">51.7460556030273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9177284240723</t>
+    <t xml:space="preserve">50.9177322387695</t>
   </si>
   <si>
     <t xml:space="preserve">51.5511589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">53.548885345459</t>
+    <t xml:space="preserve">53.5488891601562</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517189025879</t>
+    <t xml:space="preserve">55.3517150878906</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">55.8389663696289</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0338668823242</t>
+    <t xml:space="preserve">56.0338706970215</t>
   </si>
   <si>
     <t xml:space="preserve">54.3772125244141</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">55.4491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4004440307617</t>
+    <t xml:space="preserve">55.4004402160645</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">49.7970504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">51.356258392334</t>
+    <t xml:space="preserve">51.3562622070312</t>
   </si>
   <si>
     <t xml:space="preserve">50.8690071105957</t>
@@ -3647,19 +3647,19 @@
     <t xml:space="preserve">50.7715530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0151786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384101867676</t>
+    <t xml:space="preserve">51.0151824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384140014648</t>
   </si>
   <si>
     <t xml:space="preserve">51.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5998840332031</t>
+    <t xml:space="preserve">51.5998802185059</t>
   </si>
   <si>
     <t xml:space="preserve">49.0174522399902</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">50.3817596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8480529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8015937805176</t>
+    <t xml:space="preserve">47.8480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8015975952148</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">48.7738265991211</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7311134338379</t>
+    <t xml:space="preserve">47.7311096191406</t>
   </si>
   <si>
     <t xml:space="preserve">49.9919548034668</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483329772949</t>
+    <t xml:space="preserve">49.7483291625977</t>
   </si>
   <si>
     <t xml:space="preserve">48.4522399902344</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">49.3585319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4559783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3029937744141</t>
+    <t xml:space="preserve">49.455982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3029899597168</t>
   </si>
   <si>
     <t xml:space="preserve">59.4446258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2242279052734</t>
+    <t xml:space="preserve">60.2242240905762</t>
   </si>
   <si>
     <t xml:space="preserve">58.5188484191895</t>
@@ -3740,28 +3740,28 @@
     <t xml:space="preserve">55.1568145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6927947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1522750854492</t>
+    <t xml:space="preserve">55.6927909851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5698432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.152271270752</t>
   </si>
   <si>
     <t xml:space="preserve">60.8576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0038299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8111953735352</t>
+    <t xml:space="preserve">61.0038261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8111991882324</t>
   </si>
   <si>
     <t xml:space="preserve">59.6395263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8599243164062</t>
+    <t xml:space="preserve">58.8599281311035</t>
   </si>
   <si>
     <t xml:space="preserve">59.2497215270996</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">57.9828758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4214019775391</t>
+    <t xml:space="preserve">58.4213981628418</t>
   </si>
   <si>
     <t xml:space="preserve">59.6882514953613</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">62.319408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0502815246582</t>
+    <t xml:space="preserve">63.0502853393555</t>
   </si>
   <si>
     <t xml:space="preserve">61.3936309814453</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4842758178711</t>
+    <t xml:space="preserve">67.4842681884766</t>
   </si>
   <si>
     <t xml:space="preserve">68.1176910400391</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">69.8230743408203</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3590393066406</t>
+    <t xml:space="preserve">70.3590469360352</t>
   </si>
   <si>
     <t xml:space="preserve">68.9460220336914</t>
@@ -3815,16 +3815,16 @@
     <t xml:space="preserve">68.410041809082</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8740615844727</t>
+    <t xml:space="preserve">67.8740692138672</t>
   </si>
   <si>
     <t xml:space="preserve">68.3125915527344</t>
   </si>
   <si>
-    <t xml:space="preserve">67.1919174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8972930908203</t>
+    <t xml:space="preserve">67.1919097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8973007202148</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">65.4865341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5817260742188</t>
+    <t xml:space="preserve">67.5817184448242</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3848,25 +3848,25 @@
     <t xml:space="preserve">66.509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1199645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8995666503906</t>
+    <t xml:space="preserve">66.1199569702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5584869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6536636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0434722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6513977050781</t>
+    <t xml:space="preserve">66.5584945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6536712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">71.7233505249023</t>
@@ -3878,22 +3878,22 @@
     <t xml:space="preserve">71.528450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6978530883789</t>
+    <t xml:space="preserve">72.6978607177734</t>
   </si>
   <si>
     <t xml:space="preserve">75.6700897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">75.0366592407227</t>
+    <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
     <t xml:space="preserve">74.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4032287597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.7188034057617</t>
+    <t xml:space="preserve">74.4032363891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.7188110351562</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
@@ -3908,13 +3908,13 @@
     <t xml:space="preserve">77.3754653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9879302978516</t>
+    <t xml:space="preserve">74.987922668457</t>
   </si>
   <si>
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627090454102</t>
+    <t xml:space="preserve">77.8627166748047</t>
   </si>
   <si>
     <t xml:space="preserve">79.3244705200195</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295700073242</t>
+    <t xml:space="preserve">78.0088882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295623779297</t>
   </si>
   <si>
     <t xml:space="preserve">77.424186706543</t>
@@ -3950,13 +3950,13 @@
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0321197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4474182128906</t>
+    <t xml:space="preserve">78.3012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.032112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4474105834961</t>
   </si>
   <si>
     <t xml:space="preserve">77.8139877319336</t>
@@ -3965,25 +3965,25 @@
     <t xml:space="preserve">77.4729156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">73.964714050293</t>
+    <t xml:space="preserve">73.9647064208984</t>
   </si>
   <si>
     <t xml:space="preserve">74.4519653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">71.8207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.9601593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8162612915039</t>
+    <t xml:space="preserve">71.82080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.9601669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8162689208984</t>
   </si>
   <si>
     <t xml:space="preserve">77.7165451049805</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964233398438</t>
+    <t xml:space="preserve">80.3964157104492</t>
   </si>
   <si>
     <t xml:space="preserve">80.2989730834961</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">81.4683685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8581695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7607192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2689361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1924362182617</t>
+    <t xml:space="preserve">81.8581771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.268928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1924285888672</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">86.2434234619141</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7051849365234</t>
+    <t xml:space="preserve">87.705192565918</t>
   </si>
   <si>
     <t xml:space="preserve">90.2876129150391</t>
@@ -4040,19 +4040,19 @@
     <t xml:space="preserve">89.3618392944336</t>
   </si>
   <si>
-    <t xml:space="preserve">86.0972595214844</t>
+    <t xml:space="preserve">86.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360656738281</t>
+    <t xml:space="preserve">88.4360580444336</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">84.4893341064453</t>
+    <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
     <t xml:space="preserve">82.1017990112305</t>
@@ -4064,19 +4064,19 @@
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559036254883</t>
+    <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0043487548828</t>
+    <t xml:space="preserve">82.0043563842773</t>
   </si>
   <si>
     <t xml:space="preserve">81.4196472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2270278930664</t>
+    <t xml:space="preserve">79.2270202636719</t>
   </si>
   <si>
     <t xml:space="preserve">78.7397689819336</t>
@@ -4085,22 +4085,22 @@
     <t xml:space="preserve">79.9091720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5299377441406</t>
+    <t xml:space="preserve">81.5299453735352</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096420288086</t>
+    <t xml:space="preserve">77.1096496582031</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6322021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830764770508</t>
+    <t xml:space="preserve">78.632194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830841064453</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618255615234</t>
+    <t xml:space="preserve">79.7618179321289</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370315551758</t>
+    <t xml:space="preserve">81.1370239257812</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909790039062</t>
+    <t xml:space="preserve">83.6909713745117</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6281661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317092895508</t>
+    <t xml:space="preserve">81.628173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317169189453</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0742263793945</t>
+    <t xml:space="preserve">79.07421875</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.926872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326721191406</t>
+    <t xml:space="preserve">78.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0959548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326644897461</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853332519531</t>
+    <t xml:space="preserve">75.6853256225586</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928894042969</t>
+    <t xml:space="preserve">72.4928970336914</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870971679688</t>
+    <t xml:space="preserve">75.5870895385742</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402359008789</t>
+    <t xml:space="preserve">72.6402282714844</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4232,13 +4232,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176834106445</t>
+    <t xml:space="preserve">71.1176910400391</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597152709961</t>
+    <t xml:space="preserve">71.5597076416016</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4253,19 +4253,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3946533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022171020508</t>
+    <t xml:space="preserve">72.394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022247314453</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212188720703</t>
+    <t xml:space="preserve">70.9212265014648</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5420074462891</t>
+    <t xml:space="preserve">72.5419998168945</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389419555664</t>
+    <t xml:space="preserve">73.4260635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389343261719</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8270263671875</t>
+    <t xml:space="preserve">67.827018737793</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247772216797</t>
+    <t xml:space="preserve">70.7247695922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.546028137207</t>
+    <t xml:space="preserve">69.5460205078125</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698669433594</t>
+    <t xml:space="preserve">73.7698593139648</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4364,19 +4364,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065765380859</t>
+    <t xml:space="preserve">77.6007843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481384277344</t>
+    <t xml:space="preserve">77.7481307983398</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4397,25 +4397,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273498535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238067626953</t>
+    <t xml:space="preserve">75.9309005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238143920898</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344436645508</t>
+    <t xml:space="preserve">75.7344360351562</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4445,19 +4445,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9051513671875</t>
+    <t xml:space="preserve">82.905143737793</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046661376953</t>
+    <t xml:space="preserve">85.7046737670898</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851867675781</t>
+    <t xml:space="preserve">86.7851791381836</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4469,13 +4469,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542617797852</t>
+    <t xml:space="preserve">82.9542541503906</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489547729492</t>
+    <t xml:space="preserve">83.2489471435547</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4487,16 +4487,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312316894531</t>
+    <t xml:space="preserve">84.2312393188477</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507263183594</t>
+    <t xml:space="preserve">82.5613555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507186889648</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338195800781</t>
+    <t xml:space="preserve">89.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581436157227</t>
+    <t xml:space="preserve">91.0581359863281</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8576736450195</t>
+    <t xml:space="preserve">93.857666015625</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747367858887</t>
+    <t xml:space="preserve">102.845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747375488281</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.82788848877</t>
+    <t xml:space="preserve">103.827896118164</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034019470215</t>
+    <t xml:space="preserve">109.034027099609</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525161743164</t>
+    <t xml:space="preserve">109.525169372559</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.63143157959</t>
+    <t xml:space="preserve">103.631439208984</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.158004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122581481934</t>
+    <t xml:space="preserve">102.157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122573852539</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987350463867</t>
+    <t xml:space="preserve">99.8987426757812</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3625030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518737792969</t>
+    <t xml:space="preserve">96.3624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518661499023</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4670,13 +4670,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.264274597168</t>
+    <t xml:space="preserve">96.2642669677734</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.558967590332</t>
+    <t xml:space="preserve">96.5589599609375</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890686035156</t>
+    <t xml:space="preserve">94.8890609741211</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488159179688</t>
+    <t xml:space="preserve">94.7417221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488082885742</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5718,6 +5718,9 @@
   </si>
   <si>
     <t xml:space="preserve">90.0800018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6600036621094</t>
   </si>
 </sst>
 </file>
@@ -71576,7 +71579,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6910185185</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>168571</v>
@@ -71597,6 +71600,32 @@
         <v>1901</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6915625</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>516037</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>93.120002746582</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>90.3000030517578</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>90.4199981689453</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>91.6600036621094</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1902</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="1903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="1904">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537855148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801063537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1718196868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289274215698</t>
+    <t xml:space="preserve">14.8537864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1718187332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476127624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289293289185</t>
   </si>
   <si>
     <t xml:space="preserve">15.0406265258789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3208866119385</t>
+    <t xml:space="preserve">15.3208856582642</t>
   </si>
   <si>
     <t xml:space="preserve">15.3022012710571</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4427366256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0877418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0410308837891</t>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0877408981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0410318374634</t>
   </si>
   <si>
     <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.33997631073</t>
+    <t xml:space="preserve">14.3399772644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.7697086334229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3866844177246</t>
+    <t xml:space="preserve">14.3866853713989</t>
   </si>
   <si>
     <t xml:space="preserve">13.9943218231201</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">14.424054145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3960285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9849805831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338006973267</t>
+    <t xml:space="preserve">14.3960275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9849796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433801651001</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155225753784</t>
+    <t xml:space="preserve">12.4155244827271</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061813354492</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">12.8172292709351</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645895004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4057760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251096725464</t>
+    <t xml:space="preserve">13.5459051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722269058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4057750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251106262207</t>
   </si>
   <si>
     <t xml:space="preserve">13.9195852279663</t>
@@ -146,97 +146,97 @@
     <t xml:space="preserve">14.0316896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7607698440552</t>
+    <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
     <t xml:space="preserve">13.8355083465576</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372140884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.255898475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.414306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060199737549</t>
+    <t xml:space="preserve">14.1064252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372121810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2558994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4143047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.601146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060190200806</t>
   </si>
   <si>
     <t xml:space="preserve">15.3769378662109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4797010421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.545093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104860305786</t>
+    <t xml:space="preserve">15.4796991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5450944900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104869842529</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983835220337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873365402222</t>
+    <t xml:space="preserve">15.0873355865479</t>
   </si>
   <si>
     <t xml:space="preserve">14.9939155578613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6202354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527290344238</t>
+    <t xml:space="preserve">14.6202363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527299880981</t>
   </si>
   <si>
     <t xml:space="preserve">15.3302278518677</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3952178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3858776092529</t>
+    <t xml:space="preserve">15.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3952159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">16.3485088348389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550830841064</t>
+    <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
     <t xml:space="preserve">16.4138984680176</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">16.2924556732178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3671894073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0215358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2177181243896</t>
+    <t xml:space="preserve">16.3671913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0215377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2177200317383</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765316009521</t>
@@ -266,61 +266,61 @@
     <t xml:space="preserve">16.2737731933594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4325847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.61008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4419269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889812469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548667907715</t>
+    <t xml:space="preserve">16.4325828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6287651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4419288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6489791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548686981201</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.601921081543</t>
+    <t xml:space="preserve">16.6019229888916</t>
   </si>
   <si>
     <t xml:space="preserve">16.6866264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995643615723</t>
+    <t xml:space="preserve">16.7054500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995681762695</t>
   </si>
   <si>
     <t xml:space="preserve">16.5454540252686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6583919525146</t>
+    <t xml:space="preserve">16.6583938598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183879852295</t>
+    <t xml:space="preserve">16.8183898925781</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6890068054199</t>
+    <t xml:space="preserve">15.6890077590942</t>
   </si>
   <si>
     <t xml:space="preserve">15.472541809082</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">15.7078275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3407793045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.583101272583</t>
+    <t xml:space="preserve">15.3407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5830993652344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113338470459</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">16.253698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5642776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678443908691</t>
+    <t xml:space="preserve">16.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678453445435</t>
   </si>
   <si>
     <t xml:space="preserve">15.2748985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2090158462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101861953735</t>
+    <t xml:space="preserve">15.2090177536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101871490479</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854995727539</t>
@@ -371,67 +371,67 @@
     <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.644326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9172601699829</t>
+    <t xml:space="preserve">14.6443271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9172611236572</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6513595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348936080933</t>
+    <t xml:space="preserve">15.6513576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195989608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348945617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.5854787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9054708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301773071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9901752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9337024688721</t>
+    <t xml:space="preserve">15.9054698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9901723861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478315353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.933705329895</t>
   </si>
   <si>
     <t xml:space="preserve">15.6701812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3784265518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148836135864</t>
+    <t xml:space="preserve">15.3784246444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419496536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148826599121</t>
   </si>
   <si>
     <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2725200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3195762634277</t>
+    <t xml:space="preserve">16.272518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819309234619</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">16.3760452270508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4983978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607524871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078105926514</t>
+    <t xml:space="preserve">16.4983997344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078086853027</t>
   </si>
   <si>
     <t xml:space="preserve">16.6301574707031</t>
@@ -458,79 +458,79 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7807426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560352325439</t>
+    <t xml:space="preserve">16.780740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560333251953</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372116088867</t>
+    <t xml:space="preserve">17.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372077941895</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9783840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8466243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960353851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.912504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8842678070068</t>
+    <t xml:space="preserve">16.978385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8466186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9125022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8842716217041</t>
   </si>
   <si>
     <t xml:space="preserve">16.7525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9030895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0066165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9972057342529</t>
+    <t xml:space="preserve">16.9030914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0066184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9972076416016</t>
   </si>
   <si>
     <t xml:space="preserve">17.0536766052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.034854888916</t>
+    <t xml:space="preserve">16.8748588562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0348510742188</t>
   </si>
   <si>
     <t xml:space="preserve">16.8654460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7619171142578</t>
+    <t xml:space="preserve">16.7619209289551</t>
   </si>
   <si>
     <t xml:space="preserve">17.0724983215332</t>
@@ -539,40 +539,40 @@
     <t xml:space="preserve">17.232494354248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1007308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289710998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2136726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642578125</t>
+    <t xml:space="preserve">17.1007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2607288360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2136745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642559051514</t>
   </si>
   <si>
     <t xml:space="preserve">17.3077869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2983741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936588287354</t>
+    <t xml:space="preserve">17.298376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936569213867</t>
   </si>
   <si>
     <t xml:space="preserve">17.8724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7383365631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230400085449</t>
+    <t xml:space="preserve">18.738338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230438232422</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818695068359</t>
@@ -587,49 +587,49 @@
     <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3783206939697</t>
+    <t xml:space="preserve">19.3783226013184</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183246612549</t>
+    <t xml:space="preserve">19.2183265686035</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4230003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2347679138184</t>
+    <t xml:space="preserve">19.4159660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724189758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4230041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.234769821167</t>
   </si>
   <si>
     <t xml:space="preserve">20.2535934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4982948303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.357120513916</t>
+    <t xml:space="preserve">20.4982929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3571224212646</t>
   </si>
   <si>
     <t xml:space="preserve">20.8935775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6676998138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665313720703</t>
+    <t xml:space="preserve">20.6676979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665294647217</t>
   </si>
   <si>
     <t xml:space="preserve">20.1030082702637</t>
@@ -638,61 +638,61 @@
     <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7453708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.519495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6888999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.84889793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5759601593018</t>
+    <t xml:space="preserve">19.7453689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5194969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6889019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7171382904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8488960266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5759620666504</t>
   </si>
   <si>
     <t xml:space="preserve">19.4630260467529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2747917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4442005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3877353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3500881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.397144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053867340088</t>
+    <t xml:space="preserve">19.2747936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.444206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3877334594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3500862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3971462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0018615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053886413574</t>
   </si>
   <si>
     <t xml:space="preserve">18.9171562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0865650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8701000213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4936408996582</t>
+    <t xml:space="preserve">19.0865631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8700981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4936389923096</t>
   </si>
   <si>
     <t xml:space="preserve">18.352466583252</t>
@@ -701,19 +701,19 @@
     <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6253986358643</t>
+    <t xml:space="preserve">18.6254024505615</t>
   </si>
   <si>
     <t xml:space="preserve">19.2559719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.510082244873</t>
+    <t xml:space="preserve">19.5100841522217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5006694793701</t>
+    <t xml:space="preserve">19.5006713867188</t>
   </si>
   <si>
     <t xml:space="preserve">19.7547836303711</t>
@@ -722,58 +722,58 @@
     <t xml:space="preserve">19.7924270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5947875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335815429688</t>
+    <t xml:space="preserve">19.594783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335834503174</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994632720947</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7900505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3641529083252</t>
+    <t xml:space="preserve">20.7900524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3641548156738</t>
   </si>
   <si>
     <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0159282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029903411865</t>
+    <t xml:space="preserve">21.1853332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.015926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029865264893</t>
   </si>
   <si>
     <t xml:space="preserve">21.0253372192383</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9876899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947441101074</t>
+    <t xml:space="preserve">20.9876880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947422027588</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6088485717773</t>
+    <t xml:space="preserve">21.1100444793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.608850479126</t>
   </si>
   <si>
     <t xml:space="preserve">21.2135696411133</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">21.3829746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5429706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8347282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0229568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8064937591553</t>
+    <t xml:space="preserve">21.5429725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0229606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8064918518066</t>
   </si>
   <si>
     <t xml:space="preserve">22.0417823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2582454681396</t>
+    <t xml:space="preserve">22.2582473754883</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817646026611</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7476463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252975463867</t>
+    <t xml:space="preserve">22.7476444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252956390381</t>
   </si>
   <si>
     <t xml:space="preserve">23.0394039154053</t>
@@ -818,55 +818,55 @@
     <t xml:space="preserve">23.0582256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5876522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3711814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464996337891</t>
+    <t xml:space="preserve">22.5876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3711853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135478973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464977264404</t>
   </si>
   <si>
     <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7876682281494</t>
+    <t xml:space="preserve">21.787670135498</t>
   </si>
   <si>
     <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1170768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.098123550415</t>
+    <t xml:space="preserve">22.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1455039978027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1549777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0507431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7190818786621</t>
+    <t xml:space="preserve">22.1549758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0507411956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7190799713135</t>
   </si>
   <si>
     <t xml:space="preserve">22.0886459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7569828033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327922821045</t>
+    <t xml:space="preserve">21.7569847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327941894531</t>
   </si>
   <si>
     <t xml:space="preserve">21.6811771392822</t>
@@ -875,43 +875,43 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285537719727</t>
+    <t xml:space="preserve">21.7285575866699</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380332946777</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5579853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200824737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1315670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4158458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8612194061279</t>
+    <t xml:space="preserve">21.5579891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1315631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4158477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8612213134766</t>
   </si>
   <si>
     <t xml:space="preserve">21.463228225708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.662223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674629211426</t>
+    <t xml:space="preserve">21.6622257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674667358398</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529727935791</t>
+    <t xml:space="preserve">22.4013557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529689788818</t>
   </si>
   <si>
     <t xml:space="preserve">22.5813999176025</t>
@@ -926,64 +926,64 @@
     <t xml:space="preserve">21.7948894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8138427734375</t>
+    <t xml:space="preserve">21.8138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">21.8422679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958938598633</t>
+    <t xml:space="preserve">21.671703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958919525146</t>
   </si>
   <si>
     <t xml:space="preserve">22.4676876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3255481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5055923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8277759552002</t>
+    <t xml:space="preserve">22.3255462646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.50559425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
     <t xml:space="preserve">23.0362510681152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2068195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2162933349609</t>
+    <t xml:space="preserve">23.2068157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2162952423096</t>
   </si>
   <si>
     <t xml:space="preserve">22.9983463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1310119628906</t>
+    <t xml:space="preserve">23.131010055542</t>
   </si>
   <si>
     <t xml:space="preserve">23.5005741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6900959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1404876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4058170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4531955718994</t>
+    <t xml:space="preserve">23.6900978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1404857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.405818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4531936645508</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">22.950963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0646781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.723539352417</t>
+    <t xml:space="preserve">23.0646800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7519721984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7235412597656</t>
   </si>
   <si>
     <t xml:space="preserve">22.9793949127197</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8796157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1165180206299</t>
+    <t xml:space="preserve">22.1834087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.87961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1165199279785</t>
   </si>
   <si>
     <t xml:space="preserve">23.6616668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3868618011475</t>
+    <t xml:space="preserve">23.3868656158447</t>
   </si>
   <si>
     <t xml:space="preserve">23.1783905029297</t>
@@ -1040,16 +1040,16 @@
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6850833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040328979492</t>
+    <t xml:space="preserve">24.6377029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040348052979</t>
   </si>
   <si>
     <t xml:space="preserve">24.8082714080811</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">24.7798404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7229843139648</t>
+    <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">24.5429401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1638984680176</t>
+    <t xml:space="preserve">24.1639003753662</t>
   </si>
   <si>
     <t xml:space="preserve">24.8651256561279</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">25.7558746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653522491455</t>
+    <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
     <t xml:space="preserve">25.547399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2915496826172</t>
+    <t xml:space="preserve">25.2915458679199</t>
   </si>
   <si>
     <t xml:space="preserve">25.4052581787109</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">25.4905433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3863086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3294506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0830745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7274436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6611137390137</t>
+    <t xml:space="preserve">25.3863105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3484039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3294525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0830726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7274475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.661111831665</t>
   </si>
   <si>
     <t xml:space="preserve">25.9643459320068</t>
@@ -1118,40 +1118,40 @@
     <t xml:space="preserve">26.8645706176758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.309944152832</t>
+    <t xml:space="preserve">27.3099460601807</t>
   </si>
   <si>
     <t xml:space="preserve">26.9119472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0635662078857</t>
+    <t xml:space="preserve">27.0635681152344</t>
   </si>
   <si>
     <t xml:space="preserve">26.6750469207764</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9972362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678047180176</t>
+    <t xml:space="preserve">26.9972343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678028106689</t>
   </si>
   <si>
     <t xml:space="preserve">26.4665756225586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0591049194336</t>
+    <t xml:space="preserve">26.0591087341309</t>
   </si>
   <si>
     <t xml:space="preserve">25.0451698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1778354644775</t>
+    <t xml:space="preserve">25.1778335571289</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5189723968506</t>
+    <t xml:space="preserve">25.5189743041992</t>
   </si>
   <si>
     <t xml:space="preserve">25.1115036010742</t>
@@ -1163,25 +1163,25 @@
     <t xml:space="preserve">25.935920715332</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1588840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.301025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2631187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1683597564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9219818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2062606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020240783691</t>
+    <t xml:space="preserve">25.1588821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3010234832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2631206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1683578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9219799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2062644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020278930664</t>
   </si>
   <si>
     <t xml:space="preserve">25.5853042602539</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">25.6042575836182</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8601112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.333911895752</t>
+    <t xml:space="preserve">25.860107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3339138031006</t>
   </si>
   <si>
     <t xml:space="preserve">26.2486305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4381465911865</t>
+    <t xml:space="preserve">26.4381484985352</t>
   </si>
   <si>
     <t xml:space="preserve">24.7987937927246</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">25.3673553466797</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3578815460205</t>
+    <t xml:space="preserve">25.3578796386719</t>
   </si>
   <si>
     <t xml:space="preserve">25.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5947799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7084903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1064872741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8171882629395</t>
+    <t xml:space="preserve">25.6232089996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5947818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7084922790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1064834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8171901702881</t>
   </si>
   <si>
     <t xml:space="preserve">27.0540904998779</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">27.3857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8695850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222026824951</t>
+    <t xml:space="preserve">25.8695831298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222045898438</t>
   </si>
   <si>
     <t xml:space="preserve">25.9169673919678</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">25.6326866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7324600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9743766784668</t>
+    <t xml:space="preserve">24.7324619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0691394805908</t>
+    <t xml:space="preserve">24.0691375732422</t>
   </si>
   <si>
     <t xml:space="preserve">24.4481773376465</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8272228240967</t>
+    <t xml:space="preserve">24.8272247314453</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2586612701416</t>
+    <t xml:space="preserve">24.258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
@@ -1280,76 +1280,76 @@
     <t xml:space="preserve">25.0167427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9693622589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9270000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0117263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.153865814209</t>
+    <t xml:space="preserve">24.9693641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9269981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2012481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0117282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
     <t xml:space="preserve">26.4855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5329093933105</t>
+    <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">26.9593315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7698078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9492969512939</t>
+    <t xml:space="preserve">26.7698097229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9492950439453</t>
   </si>
   <si>
     <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8071556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.665018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3283424377441</t>
+    <t xml:space="preserve">28.8071575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6650161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3283386230469</t>
   </si>
   <si>
     <t xml:space="preserve">29.2335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5394897460938</t>
+    <t xml:space="preserve">29.5394916534424</t>
   </si>
   <si>
     <t xml:space="preserve">30.2086696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0652770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3042659759521</t>
+    <t xml:space="preserve">30.0652751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3042697906494</t>
   </si>
   <si>
     <t xml:space="preserve">29.9696788787842</t>
   </si>
   <si>
-    <t xml:space="preserve">30.113073348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2602367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419929504395</t>
+    <t xml:space="preserve">30.1130714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2602405548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419891357422</t>
   </si>
   <si>
     <t xml:space="preserve">33.6501655578613</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">35.1797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1356925964355</t>
+    <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
     <t xml:space="preserve">34.4149436950684</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9369506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.988525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.753303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2275123596191</t>
+    <t xml:space="preserve">33.9369583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7532997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2275161743164</t>
   </si>
   <si>
     <t xml:space="preserve">35.0841217041016</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">35.6576995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2753143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3746757507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268775939941</t>
+    <t xml:space="preserve">35.275318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4224739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268814086914</t>
   </si>
   <si>
     <t xml:space="preserve">35.4187088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5658760070801</t>
+    <t xml:space="preserve">36.5658721923828</t>
   </si>
   <si>
     <t xml:space="preserve">36.8526649475098</t>
@@ -1415,64 +1415,64 @@
     <t xml:space="preserve">30.7822532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5948295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2124366760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0287857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9847526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7973327636719</t>
+    <t xml:space="preserve">31.1168422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5948276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2124404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0287818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9847564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7973289489746</t>
   </si>
   <si>
     <t xml:space="preserve">34.3671417236328</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6539306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0363235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6061401367188</t>
+    <t xml:space="preserve">34.6539344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.036319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6061363220215</t>
   </si>
   <si>
     <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8413581848145</t>
+    <t xml:space="preserve">33.8413619995117</t>
   </si>
   <si>
     <t xml:space="preserve">34.7495307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5621109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0400924682617</t>
+    <t xml:space="preserve">35.5621070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0400886535645</t>
   </si>
   <si>
     <t xml:space="preserve">35.8966941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6614685058594</t>
+    <t xml:space="preserve">36.6614723205566</t>
   </si>
   <si>
     <t xml:space="preserve">39.0036010742188</t>
@@ -1484,37 +1484,37 @@
     <t xml:space="preserve">36.5180740356445</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4262466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8564300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2790870666504</t>
+    <t xml:space="preserve">37.4262504577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8564376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2790832519531</t>
   </si>
   <si>
     <t xml:space="preserve">37.2350540161133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8929252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5583381652832</t>
+    <t xml:space="preserve">34.8929214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5583343505859</t>
   </si>
   <si>
     <t xml:space="preserve">33.6979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5067710876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2677726745605</t>
+    <t xml:space="preserve">33.5067672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2677764892578</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9809875488281</t>
+    <t xml:space="preserve">32.9809837341309</t>
   </si>
   <si>
     <t xml:space="preserve">33.3633728027344</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">32.7897872924805</t>
   </si>
   <si>
-    <t xml:space="preserve">32.837589263916</t>
+    <t xml:space="preserve">32.8375854492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.5985908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">32.503002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6463966369629</t>
+    <t xml:space="preserve">32.5029983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6463928222656</t>
   </si>
   <si>
     <t xml:space="preserve">32.3596038818359</t>
@@ -1544,34 +1544,34 @@
     <t xml:space="preserve">32.0728149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7860221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8338165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0250129699707</t>
+    <t xml:space="preserve">31.7860240936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8338184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.025016784668</t>
   </si>
   <si>
     <t xml:space="preserve">31.0212440490723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.88161277771</t>
+    <t xml:space="preserve">31.8816146850586</t>
   </si>
   <si>
     <t xml:space="preserve">28.8703117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5357227325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2011337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7709426879883</t>
+    <t xml:space="preserve">28.5357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">27.5797519683838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1055355072021</t>
+    <t xml:space="preserve">28.1055335998535</t>
   </si>
   <si>
     <t xml:space="preserve">27.2451610565186</t>
@@ -1595,40 +1595,40 @@
     <t xml:space="preserve">28.3445281982422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0137062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181118011475</t>
+    <t xml:space="preserve">29.013708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181098937988</t>
   </si>
   <si>
     <t xml:space="preserve">29.2049007415771</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4954586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5872917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7344551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4438915252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6828861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5835189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3847885131836</t>
+    <t xml:space="preserve">30.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5872898101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7344570159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4438934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6828842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.384786605835</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929592132568</t>
@@ -1640,28 +1640,28 @@
     <t xml:space="preserve">27.8187446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7231483459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6313209533691</t>
+    <t xml:space="preserve">27.7231464385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6313190460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.6350879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1017665863037</t>
+    <t xml:space="preserve">27.1017646789551</t>
   </si>
   <si>
     <t xml:space="preserve">26.8627758026123</t>
   </si>
   <si>
-    <t xml:space="preserve">27.48415184021</t>
+    <t xml:space="preserve">27.4841537475586</t>
   </si>
   <si>
     <t xml:space="preserve">27.0061683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0979957580566</t>
+    <t xml:space="preserve">26.0979976654053</t>
   </si>
   <si>
     <t xml:space="preserve">25.6200103759766</t>
@@ -1670,31 +1670,31 @@
     <t xml:space="preserve">26.1935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">26.623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7156066894531</t>
+    <t xml:space="preserve">26.6237812042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7156085968018</t>
   </si>
   <si>
     <t xml:space="preserve">26.289192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7671756744385</t>
+    <t xml:space="preserve">26.7671775817871</t>
   </si>
   <si>
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659061431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6791152954102</t>
+    <t xml:space="preserve">28.9659080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6791172027588</t>
   </si>
   <si>
     <t xml:space="preserve">29.1093044281006</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6715793609619</t>
+    <t xml:space="preserve">26.6715774536133</t>
   </si>
   <si>
     <t xml:space="preserve">26.8149738311768</t>
@@ -1706,31 +1706,31 @@
     <t xml:space="preserve">27.3885555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8225135803223</t>
+    <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
     <t xml:space="preserve">29.8740825653076</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1608715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3520679473877</t>
+    <t xml:space="preserve">30.1608695983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
     <t xml:space="preserve">31.3080348968506</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4514331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4552040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3118057250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2162055969238</t>
+    <t xml:space="preserve">31.4514350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4552001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3118019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2162094116211</t>
   </si>
   <si>
     <t xml:space="preserve">33.602367401123</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">33.5545692443848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2564697265625</t>
+    <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
     <t xml:space="preserve">30.6388568878174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5910606384277</t>
+    <t xml:space="preserve">30.5910587310791</t>
   </si>
   <si>
     <t xml:space="preserve">29.3004970550537</t>
@@ -1757,49 +1757,49 @@
     <t xml:space="preserve">29.9409961700439</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6484203338623</t>
+    <t xml:space="preserve">30.6484184265137</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9734497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2851467132568</t>
+    <t xml:space="preserve">30.9734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2851486206055</t>
   </si>
   <si>
     <t xml:space="preserve">30.0748329162598</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4763412475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2277889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9983558654785</t>
+    <t xml:space="preserve">30.4763431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2277908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9983577728271</t>
   </si>
   <si>
     <t xml:space="preserve">29.8262825012207</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6675395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.438102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352130889893</t>
+    <t xml:space="preserve">30.667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4381046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935209274292</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498035430908</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7115650177002</t>
+    <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
     <t xml:space="preserve">28.8129539489746</t>
@@ -1808,28 +1808,28 @@
     <t xml:space="preserve">29.5203704833984</t>
   </si>
   <si>
-    <t xml:space="preserve">28.487922668457</t>
+    <t xml:space="preserve">28.4879207611084</t>
   </si>
   <si>
     <t xml:space="preserve">28.717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4821357727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1762237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3291759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761585235596</t>
+    <t xml:space="preserve">29.4821338653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1762199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761547088623</t>
   </si>
   <si>
     <t xml:space="preserve">28.9237041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">28.653392791748</t>
+    <t xml:space="preserve">28.6533908843994</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058433532715</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">27.8038291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0741424560547</t>
+    <t xml:space="preserve">28.0741443634033</t>
   </si>
   <si>
     <t xml:space="preserve">27.1859664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2245845794678</t>
+    <t xml:space="preserve">27.2245826721191</t>
   </si>
   <si>
     <t xml:space="preserve">27.2052745819092</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">27.3211231231689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5335140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6493606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9776020050049</t>
+    <t xml:space="preserve">27.5335159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6493625640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9776039123535</t>
   </si>
   <si>
     <t xml:space="preserve">27.5142059326172</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">27.7845211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548343658447</t>
+    <t xml:space="preserve">28.0548362731934</t>
   </si>
   <si>
     <t xml:space="preserve">27.9969120025635</t>
@@ -1889,46 +1889,46 @@
     <t xml:space="preserve">28.2479190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3251514434814</t>
+    <t xml:space="preserve">28.3251495361328</t>
   </si>
   <si>
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9003715515137</t>
+    <t xml:space="preserve">27.900369644165</t>
   </si>
   <si>
     <t xml:space="preserve">28.0934524536133</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1167869567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8850898742676</t>
+    <t xml:space="preserve">28.6340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1167888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8850917816162</t>
   </si>
   <si>
     <t xml:space="preserve">29.2712535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8311901092529</t>
+    <t xml:space="preserve">29.8311920166016</t>
   </si>
   <si>
     <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539596557617</t>
+    <t xml:space="preserve">29.8505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539577484131</t>
   </si>
   <si>
     <t xml:space="preserve">30.2173557281494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9856586456299</t>
+    <t xml:space="preserve">29.9856567382812</t>
   </si>
   <si>
     <t xml:space="preserve">30.6807537078857</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">29.3677959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4836444854736</t>
+    <t xml:space="preserve">29.483642578125</t>
   </si>
   <si>
     <t xml:space="preserve">29.174711227417</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">29.4257202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2519435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4643363952637</t>
+    <t xml:space="preserve">29.2519454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.464334487915</t>
   </si>
   <si>
     <t xml:space="preserve">29.0202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9043979644775</t>
+    <t xml:space="preserve">28.9043960571289</t>
   </si>
   <si>
     <t xml:space="preserve">28.6920070648193</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">27.7652111053467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1666564941406</t>
+    <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
     <t xml:space="preserve">26.9542675018311</t>
@@ -1982,10 +1982,10 @@
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101795196533</t>
+    <t xml:space="preserve">26.6839504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101776123047</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
@@ -2000,34 +2000,34 @@
     <t xml:space="preserve">27.938985824585</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4369716644287</t>
+    <t xml:space="preserve">27.4369735717773</t>
   </si>
   <si>
     <t xml:space="preserve">27.2631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0314998626709</t>
+    <t xml:space="preserve">27.0315017700195</t>
   </si>
   <si>
     <t xml:space="preserve">26.6260299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4176635742188</t>
+    <t xml:space="preserve">27.4176654815674</t>
   </si>
   <si>
     <t xml:space="preserve">28.0355281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0894222259521</t>
+    <t xml:space="preserve">27.0894241333008</t>
   </si>
   <si>
     <t xml:space="preserve">26.9928817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755878448486</t>
+    <t xml:space="preserve">27.0508079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755897521973</t>
   </si>
   <si>
     <t xml:space="preserve">27.7072887420654</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">27.6107482910156</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6879825592041</t>
+    <t xml:space="preserve">27.6879787445068</t>
   </si>
   <si>
     <t xml:space="preserve">26.355712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9309349060059</t>
+    <t xml:space="preserve">25.9309329986572</t>
   </si>
   <si>
     <t xml:space="preserve">25.8537006378174</t>
@@ -2054,52 +2054,52 @@
     <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3018169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4562816619873</t>
+    <t xml:space="preserve">27.301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4562797546387</t>
   </si>
   <si>
     <t xml:space="preserve">26.8577251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7957725524902</t>
+    <t xml:space="preserve">25.7957744598389</t>
   </si>
   <si>
     <t xml:space="preserve">25.9116230010986</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7032604217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7459049224854</t>
+    <t xml:space="preserve">26.7032623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.745906829834</t>
   </si>
   <si>
     <t xml:space="preserve">27.1087341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1320686340332</t>
+    <t xml:space="preserve">28.1320667266846</t>
   </si>
   <si>
     <t xml:space="preserve">28.3830757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9430122375488</t>
+    <t xml:space="preserve">28.9430141448975</t>
   </si>
   <si>
     <t xml:space="preserve">29.4064083099365</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8078575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.981632232666</t>
+    <t xml:space="preserve">28.8078556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9816303253174</t>
   </si>
   <si>
     <t xml:space="preserve">29.1360950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7499313354492</t>
+    <t xml:space="preserve">28.7499332427979</t>
   </si>
   <si>
     <t xml:space="preserve">28.8271636962891</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6147727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133312225342</t>
+    <t xml:space="preserve">28.5954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6147747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133274078369</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">31.8585529327393</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2213802337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.182767868042</t>
+    <t xml:space="preserve">31.2213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1827659606934</t>
   </si>
   <si>
     <t xml:space="preserve">31.6654720306396</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">31.2600021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5882396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0476093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9510707855225</t>
+    <t xml:space="preserve">31.5882434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0476112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9510688781738</t>
   </si>
   <si>
     <t xml:space="preserve">31.1248435974121</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">30.8159103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3372325897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4683628082275</t>
+    <t xml:space="preserve">31.337230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4683647155762</t>
   </si>
   <si>
     <t xml:space="preserve">31.0089912414551</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7000598907471</t>
+    <t xml:space="preserve">30.7000617980957</t>
   </si>
   <si>
     <t xml:space="preserve">33.0170478820801</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">33.3645935058594</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9052238464355</t>
+    <t xml:space="preserve">33.9052200317383</t>
   </si>
   <si>
     <t xml:space="preserve">33.8859176635742</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">35.0251007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9712028503418</t>
+    <t xml:space="preserve">35.9712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">36.5311431884766</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">37.2069282531738</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7008895874023</t>
+    <t xml:space="preserve">35.7008934020996</t>
   </si>
   <si>
     <t xml:space="preserve">35.8167343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9864883422852</t>
+    <t xml:space="preserve">34.9864845275879</t>
   </si>
   <si>
     <t xml:space="preserve">33.2873611450195</t>
@@ -2228,19 +2228,19 @@
     <t xml:space="preserve">33.0363578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9205017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9937133789062</t>
+    <t xml:space="preserve">32.9205055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.993709564209</t>
   </si>
   <si>
     <t xml:space="preserve">31.6847801208496</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8778629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3605690002441</t>
+    <t xml:space="preserve">31.8778667449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3605651855469</t>
   </si>
   <si>
     <t xml:space="preserve">33.383903503418</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">32.8432731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7427062988281</t>
+    <t xml:space="preserve">31.7427024841309</t>
   </si>
   <si>
     <t xml:space="preserve">32.8239669799805</t>
@@ -2261,34 +2261,34 @@
     <t xml:space="preserve">32.2447166442871</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5343399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4764137268066</t>
+    <t xml:space="preserve">32.5343437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4764175415039</t>
   </si>
   <si>
     <t xml:space="preserve">33.6928329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7081146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3871021270752</t>
+    <t xml:space="preserve">32.7081184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3871040344238</t>
   </si>
   <si>
     <t xml:space="preserve">29.811882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9623203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8698101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7732696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0049648284912</t>
+    <t xml:space="preserve">28.9623222351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7732677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0049667358398</t>
   </si>
   <si>
     <t xml:space="preserve">26.027473449707</t>
@@ -2300,19 +2300,19 @@
     <t xml:space="preserve">25.2937622070312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1240119934082</t>
+    <t xml:space="preserve">26.1240139007568</t>
   </si>
   <si>
     <t xml:space="preserve">24.5407428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1931934356689</t>
+    <t xml:space="preserve">24.1931915283203</t>
   </si>
   <si>
     <t xml:space="preserve">22.9767742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2744541168213</t>
+    <t xml:space="preserve">25.274450302124</t>
   </si>
   <si>
     <t xml:space="preserve">25.737850189209</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">25.100679397583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7225704193115</t>
+    <t xml:space="preserve">26.7225685119629</t>
   </si>
   <si>
     <t xml:space="preserve">26.8384189605713</t>
@@ -2339,37 +2339,37 @@
     <t xml:space="preserve">24.019416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9614963531494</t>
+    <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
     <t xml:space="preserve">24.4441986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9075946807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0427570343018</t>
+    <t xml:space="preserve">24.9075965881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">25.6220016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3943290710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6300563812256</t>
+    <t xml:space="preserve">26.3943309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.630054473877</t>
   </si>
   <si>
     <t xml:space="preserve">27.8231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">26.664644241333</t>
+    <t xml:space="preserve">26.6646461486816</t>
   </si>
   <si>
     <t xml:space="preserve">26.645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2398643493652</t>
+    <t xml:space="preserve">26.2398624420166</t>
   </si>
   <si>
     <t xml:space="preserve">25.718542098999</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">25.4482288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5833854675293</t>
+    <t xml:space="preserve">25.5833873748779</t>
   </si>
   <si>
     <t xml:space="preserve">26.5487957000732</t>
@@ -2390,19 +2390,19 @@
     <t xml:space="preserve">26.4522533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8923149108887</t>
+    <t xml:space="preserve">25.8923168182373</t>
   </si>
   <si>
     <t xml:space="preserve">26.0660915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.973575592041</t>
+    <t xml:space="preserve">26.9735774993896</t>
   </si>
   <si>
     <t xml:space="preserve">26.375020980835</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0162200927734</t>
+    <t xml:space="preserve">28.0162181854248</t>
   </si>
   <si>
     <t xml:space="preserve">30.0242729187012</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">32.283332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4104385375977</t>
+    <t xml:space="preserve">30.4104404449463</t>
   </si>
   <si>
     <t xml:space="preserve">29.5994930267334</t>
@@ -2420,16 +2420,16 @@
     <t xml:space="preserve">27.5721302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5681056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5061511993408</t>
+    <t xml:space="preserve">26.5681037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5061531066895</t>
   </si>
   <si>
     <t xml:space="preserve">25.3903026580811</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5254611968994</t>
+    <t xml:space="preserve">25.5254592895508</t>
   </si>
   <si>
     <t xml:space="preserve">24.4055843353271</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">24.482816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6565914154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2511196136475</t>
+    <t xml:space="preserve">24.6565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2511177062988</t>
   </si>
   <si>
     <t xml:space="preserve">24.2897338867188</t>
@@ -2468,31 +2468,31 @@
     <t xml:space="preserve">23.9421844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1352672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.154577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0387268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1505470275879</t>
+    <t xml:space="preserve">24.1352691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1545753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0387287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1505489349365</t>
   </si>
   <si>
     <t xml:space="preserve">23.3822460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0733184814453</t>
+    <t xml:space="preserve">23.0733165740967</t>
   </si>
   <si>
     <t xml:space="preserve">23.7684135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5946369171143</t>
+    <t xml:space="preserve">23.5946388244629</t>
   </si>
   <si>
     <t xml:space="preserve">23.7877197265625</t>
@@ -2510,25 +2510,25 @@
     <t xml:space="preserve">24.3476581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5447673797607</t>
+    <t xml:space="preserve">25.5447654724121</t>
   </si>
   <si>
     <t xml:space="preserve">26.1047058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0853977203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1199855804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9462146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.811056137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5986671447754</t>
+    <t xml:space="preserve">26.0853996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.119987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.946216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8110580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5986652374268</t>
   </si>
   <si>
     <t xml:space="preserve">24.7338237762451</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">24.9269046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7611846923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2205562591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6179733276367</t>
+    <t xml:space="preserve">26.7611865997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2205581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6179752349854</t>
   </si>
   <si>
     <t xml:space="preserve">24.463508605957</t>
@@ -2561,28 +2561,28 @@
     <t xml:space="preserve">25.6413097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3130683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7804927825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6067199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.046781539917</t>
+    <t xml:space="preserve">25.3130702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7804946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6067180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0467796325684</t>
   </si>
   <si>
     <t xml:space="preserve">26.2591724395752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4136390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8343925476074</t>
+    <t xml:space="preserve">26.4136371612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8343906402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.7571582794189</t>
@@ -2594,19 +2594,19 @@
     <t xml:space="preserve">24.5600490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689804077148</t>
+    <t xml:space="preserve">24.8689785003662</t>
   </si>
   <si>
     <t xml:space="preserve">24.772439956665</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1401214599609</t>
+    <t xml:space="preserve">30.1401233673096</t>
   </si>
   <si>
     <t xml:space="preserve">31.7620143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1481742858887</t>
+    <t xml:space="preserve">32.1481781005859</t>
   </si>
   <si>
     <t xml:space="preserve">32.2061042785645</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">31.8392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9744052886963</t>
+    <t xml:space="preserve">31.974401473999</t>
   </si>
   <si>
     <t xml:space="preserve">31.9550933837891</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">33.2680511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1755409240723</t>
+    <t xml:space="preserve">34.175537109375</t>
   </si>
   <si>
     <t xml:space="preserve">34.1562347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9245300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1795654296875</t>
+    <t xml:space="preserve">33.9245338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1795616149902</t>
   </si>
   <si>
     <t xml:space="preserve">35.3726501464844</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5810165405273</t>
+    <t xml:space="preserve">34.5810127258301</t>
   </si>
   <si>
     <t xml:space="preserve">35.2761077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1216468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8706321716309</t>
+    <t xml:space="preserve">35.1216430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8706359863281</t>
   </si>
   <si>
     <t xml:space="preserve">34.7547874450684</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">35.6429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0444068908691</t>
+    <t xml:space="preserve">35.0444107055664</t>
   </si>
   <si>
     <t xml:space="preserve">35.2181854248047</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">34.4651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6003189086914</t>
+    <t xml:space="preserve">34.6003227233887</t>
   </si>
   <si>
     <t xml:space="preserve">32.2640228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4957237243652</t>
+    <t xml:space="preserve">32.4957275390625</t>
   </si>
   <si>
     <t xml:space="preserve">33.0556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.059684753418</t>
+    <t xml:space="preserve">34.0596885681152</t>
   </si>
   <si>
     <t xml:space="preserve">33.5383682250977</t>
@@ -2696,25 +2696,25 @@
     <t xml:space="preserve">33.6542205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9977416992188</t>
+    <t xml:space="preserve">32.9977378845215</t>
   </si>
   <si>
     <t xml:space="preserve">33.7314491271973</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3066711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6349105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1908226013184</t>
+    <t xml:space="preserve">33.3066749572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6349067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1908187866211</t>
   </si>
   <si>
     <t xml:space="preserve">32.9591217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8971710205078</t>
+    <t xml:space="preserve">31.8971748352051</t>
   </si>
   <si>
     <t xml:space="preserve">32.0709457397461</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">32.437801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3452911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.210132598877</t>
+    <t xml:space="preserve">33.345287322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2101287841797</t>
   </si>
   <si>
     <t xml:space="preserve">33.7893753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5576782226562</t>
+    <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
     <t xml:space="preserve">33.9824600219727</t>
@@ -2747,16 +2747,16 @@
     <t xml:space="preserve">34.0983085632324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5962905883789</t>
+    <t xml:space="preserve">33.5962944030762</t>
   </si>
   <si>
     <t xml:space="preserve">33.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9398078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4418296813965</t>
+    <t xml:space="preserve">32.939811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4418258666992</t>
   </si>
   <si>
     <t xml:space="preserve">32.881893157959</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">37.4000129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4925308227539</t>
+    <t xml:space="preserve">36.4925270080566</t>
   </si>
   <si>
     <t xml:space="preserve">37.1490097045898</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2994422912598</t>
+    <t xml:space="preserve">36.2994384765625</t>
   </si>
   <si>
     <t xml:space="preserve">36.2801361083984</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043434143066</t>
+    <t xml:space="preserve">35.6043472290039</t>
   </si>
   <si>
     <t xml:space="preserve">35.565731048584</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0331573486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3807067871094</t>
+    <t xml:space="preserve">37.6510200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0331611633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
     <t xml:space="preserve">37.5158615112305</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5198936462402</t>
+    <t xml:space="preserve">38.519889831543</t>
   </si>
   <si>
     <t xml:space="preserve">38.8481292724609</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9100799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2383232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9527206420898</t>
+    <t xml:space="preserve">39.581844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.910083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2383193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2149848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9527168273926</t>
   </si>
   <si>
     <t xml:space="preserve">41.1458053588867</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5665550231934</t>
+    <t xml:space="preserve">40.6244812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5665588378906</t>
   </si>
   <si>
     <t xml:space="preserve">42.3429145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4780731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878868103027</t>
+    <t xml:space="preserve">42.4780769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
@@ -2885,22 +2885,22 @@
     <t xml:space="preserve">42.3236045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4008407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6711578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256187438965</t>
+    <t xml:space="preserve">42.4008331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6711502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256225585938</t>
   </si>
   <si>
     <t xml:space="preserve">43.8875694274902</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5786437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9841156005859</t>
+    <t xml:space="preserve">43.5786399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9841117858887</t>
   </si>
   <si>
     <t xml:space="preserve">43.6172561645508</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4982070922852</t>
+    <t xml:space="preserve">47.4982032775879</t>
   </si>
   <si>
     <t xml:space="preserve">46.4748725891113</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">45.8183937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0693969726562</t>
+    <t xml:space="preserve">46.0694007873535</t>
   </si>
   <si>
     <t xml:space="preserve">46.5521049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1120452880859</t>
+    <t xml:space="preserve">47.1120414733887</t>
   </si>
   <si>
     <t xml:space="preserve">47.4016647338867</t>
@@ -2966,52 +2966,52 @@
     <t xml:space="preserve">49.1876792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9229927062988</t>
+    <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
     <t xml:space="preserve">47.691291809082</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7878303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3051223754883</t>
+    <t xml:space="preserve">47.7878341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3051261901855</t>
   </si>
   <si>
     <t xml:space="preserve">47.6140556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2705345153809</t>
+    <t xml:space="preserve">48.2705383300781</t>
   </si>
   <si>
     <t xml:space="preserve">48.8980560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5392456054688</t>
+    <t xml:space="preserve">50.539249420166</t>
   </si>
   <si>
     <t xml:space="preserve">47.8457565307617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2842140197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6221122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6703834533691</t>
+    <t xml:space="preserve">49.2842178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6703872680664</t>
   </si>
   <si>
     <t xml:space="preserve">49.5255699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">47.420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9422988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0734214782715</t>
+    <t xml:space="preserve">47.4209747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9422950744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0734252929688</t>
   </si>
   <si>
     <t xml:space="preserve">47.9809112548828</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">49.3807601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0082702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2979011535645</t>
+    <t xml:space="preserve">50.0082740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2978973388672</t>
   </si>
   <si>
     <t xml:space="preserve">50.4909782409668</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">53.8699188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3252639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9527778625488</t>
+    <t xml:space="preserve">52.3252601623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9527740478516</t>
   </si>
   <si>
     <t xml:space="preserve">52.9045066833496</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">53.001049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8562393188477</t>
+    <t xml:space="preserve">52.8562355041504</t>
   </si>
   <si>
     <t xml:space="preserve">52.0356369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6012077331543</t>
+    <t xml:space="preserve">51.601203918457</t>
   </si>
   <si>
     <t xml:space="preserve">47.7105979919434</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">48.6567001342773</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0774536132812</t>
+    <t xml:space="preserve">48.0774574279785</t>
   </si>
   <si>
     <t xml:space="preserve">48.173999786377</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8996543884277</t>
+    <t xml:space="preserve">46.899658203125</t>
   </si>
   <si>
     <t xml:space="preserve">46.3590278625488</t>
@@ -3095,28 +3095,28 @@
     <t xml:space="preserve">45.1426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5287666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3010940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5907211303711</t>
+    <t xml:space="preserve">45.5287704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.301097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5907173156738</t>
   </si>
   <si>
     <t xml:space="preserve">46.8031158447266</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8071403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6446151733398</t>
+    <t xml:space="preserve">47.8071441650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
     <t xml:space="preserve">45.8956260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">46.165943145752</t>
+    <t xml:space="preserve">46.1659393310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
@@ -3134,22 +3134,22 @@
     <t xml:space="preserve">45.4322280883789</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0887069702148</t>
+    <t xml:space="preserve">46.0887107849121</t>
   </si>
   <si>
     <t xml:space="preserve">46.9575805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1699714660645</t>
+    <t xml:space="preserve">47.1699676513672</t>
   </si>
   <si>
     <t xml:space="preserve">48.0388336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9945945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4290313720703</t>
+    <t xml:space="preserve">48.9945907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.429027557373</t>
   </si>
   <si>
     <t xml:space="preserve">50.5875244140625</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">56.1869049072266</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1659927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1450881958008</t>
+    <t xml:space="preserve">58.1659965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1450843811035</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">61.255313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5312538146973</t>
+    <t xml:space="preserve">60.53125</t>
   </si>
   <si>
     <t xml:space="preserve">60.2899017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7589302062988</t>
+    <t xml:space="preserve">59.7589263916016</t>
   </si>
   <si>
     <t xml:space="preserve">58.021183013916</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">58.0694580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">56.621337890625</t>
+    <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
     <t xml:space="preserve">55.849006652832</t>
@@ -3209,10 +3209,10 @@
     <t xml:space="preserve">53.4354782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4491691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9664573669434</t>
+    <t xml:space="preserve">54.4491653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9664611816406</t>
   </si>
   <si>
     <t xml:space="preserve">54.7870597839355</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">53.5802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0147285461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9318733215332</t>
+    <t xml:space="preserve">54.0147323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9318695068359</t>
   </si>
   <si>
     <t xml:space="preserve">56.4282569885254</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">54.2078170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3872108459473</t>
+    <t xml:space="preserve">53.3872146606445</t>
   </si>
   <si>
     <t xml:space="preserve">51.9873657226562</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">55.4145774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7733764648438</t>
+    <t xml:space="preserve">53.773380279541</t>
   </si>
   <si>
     <t xml:space="preserve">54.9801406860352</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">56.2351760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">57.345401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5038871765137</t>
+    <t xml:space="preserve">57.3453979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5038909912109</t>
   </si>
   <si>
     <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9656867980957</t>
+    <t xml:space="preserve">60.965690612793</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
@@ -3287,55 +3287,55 @@
     <t xml:space="preserve">55.2214965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0629997253418</t>
+    <t xml:space="preserve">54.0630035400391</t>
   </si>
   <si>
     <t xml:space="preserve">52.2287216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0839080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1458625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4427108764648</t>
+    <t xml:space="preserve">52.083911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1458587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4427070617676</t>
   </si>
   <si>
     <t xml:space="preserve">50.8288764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8908233642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0565452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2359466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.483757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8425598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6840629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1184997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.37353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1804542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3461685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4563941955566</t>
+    <t xml:space="preserve">51.8908271789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0565490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2359504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4837532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8425559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1185035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1804504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3461723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4563903808594</t>
   </si>
   <si>
     <t xml:space="preserve">50.9254150390625</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">46.3976402282715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8763160705566</t>
+    <t xml:space="preserve">45.8763198852539</t>
   </si>
   <si>
     <t xml:space="preserve">42.0919075012207</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">42.555305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">42.149829864502</t>
+    <t xml:space="preserve">42.1498336791992</t>
   </si>
   <si>
     <t xml:space="preserve">45.5480804443359</t>
@@ -3386,16 +3386,16 @@
     <t xml:space="preserve">49.573844909668</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8771476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.911735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6486434936523</t>
+    <t xml:space="preserve">50.8771438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9117317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6486473083496</t>
   </si>
   <si>
     <t xml:space="preserve">45.2970695495605</t>
@@ -3404,49 +3404,49 @@
     <t xml:space="preserve">47.5561294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9961929321289</t>
+    <t xml:space="preserve">46.9961967468262</t>
   </si>
   <si>
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9495239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6751823425293</t>
+    <t xml:space="preserve">44.949520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.675178527832</t>
   </si>
   <si>
     <t xml:space="preserve">41.647819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8063087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.119270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6253089904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0348129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376998901367</t>
+    <t xml:space="preserve">42.8063125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1192665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6253128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0348091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.837703704834</t>
   </si>
   <si>
     <t xml:space="preserve">44.157886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4627914428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1254539489746</t>
+    <t xml:space="preserve">43.4627952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1254501342773</t>
   </si>
   <si>
     <t xml:space="preserve">42.3908386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0400161743164</t>
+    <t xml:space="preserve">42.0400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">43.4043235778809</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">44.8270950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.444766998291</t>
+    <t xml:space="preserve">46.4447708129883</t>
   </si>
   <si>
     <t xml:space="preserve">45.4312858581543</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.645679473877</t>
+    <t xml:space="preserve">45.6456756591797</t>
   </si>
   <si>
     <t xml:space="preserve">45.3923072814941</t>
@@ -3488,16 +3488,16 @@
     <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3054046630859</t>
+    <t xml:space="preserve">40.3054084777832</t>
   </si>
   <si>
     <t xml:space="preserve">39.1360054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7012176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766250610352</t>
+    <t xml:space="preserve">39.7012138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766212463379</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646049499512</t>
+    <t xml:space="preserve">41.8646087646484</t>
   </si>
   <si>
     <t xml:space="preserve">42.7806434631348</t>
@@ -3524,22 +3524,22 @@
     <t xml:space="preserve">41.8840980529785</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9620590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8585968017578</t>
+    <t xml:space="preserve">41.9620628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
     <t xml:space="preserve">45.0025062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3593368530273</t>
+    <t xml:space="preserve">44.3593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507789611816</t>
+    <t xml:space="preserve">45.4507751464844</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">50.9177284240723</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5511589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5488891601562</t>
+    <t xml:space="preserve">51.5511627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.548885345459</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517150878906</t>
+    <t xml:space="preserve">55.3517189025879</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">54.1335906982422</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1080932617188</t>
+    <t xml:space="preserve">55.1080894470215</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4491691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4004364013672</t>
+    <t xml:space="preserve">55.4491653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4004402160645</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">50.4792060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7970542907715</t>
+    <t xml:space="preserve">49.7970504760742</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">51.0151786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5024299621582</t>
+    <t xml:space="preserve">51.5024337768555</t>
   </si>
   <si>
     <t xml:space="preserve">52.0384063720703</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8015937805176</t>
+    <t xml:space="preserve">45.8015975952148</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">47.7311096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9919509887695</t>
+    <t xml:space="preserve">49.9919548034668</t>
   </si>
   <si>
     <t xml:space="preserve">49.8945045471191</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494491577148</t>
+    <t xml:space="preserve">57.3494453430176</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698432922363</t>
+    <t xml:space="preserve">56.5698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">61.0038261413574</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8111991882324</t>
+    <t xml:space="preserve">58.8111953735352</t>
   </si>
   <si>
     <t xml:space="preserve">59.6395263671875</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">58.8599243164062</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2497253417969</t>
+    <t xml:space="preserve">59.2497215270996</t>
   </si>
   <si>
     <t xml:space="preserve">57.9828720092773</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">64.2684020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">62.319408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0502853393555</t>
+    <t xml:space="preserve">62.3194046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0502815246582</t>
   </si>
   <si>
     <t xml:space="preserve">61.3936309814453</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">68.1176986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8230743408203</t>
+    <t xml:space="preserve">69.8230819702148</t>
   </si>
   <si>
     <t xml:space="preserve">70.3590469360352</t>
@@ -3809,43 +3809,43 @@
     <t xml:space="preserve">68.9460220336914</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4100341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8740768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3125839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.1919174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8972930908203</t>
+    <t xml:space="preserve">68.410041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8740692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3125915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.1919097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8972854614258</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4865341186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5817108154297</t>
+    <t xml:space="preserve">65.4865417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5817184448242</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">69.6769027709961</t>
+    <t xml:space="preserve">69.6768951416016</t>
   </si>
   <si>
     <t xml:space="preserve">69.1409149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5097579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1199569702148</t>
+    <t xml:space="preserve">66.509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
     <t xml:space="preserve">66.8995666503906</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">66.5584869384766</t>
   </si>
   <si>
-    <t xml:space="preserve">68.6536712646484</t>
+    <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
     <t xml:space="preserve">69.0434722900391</t>
@@ -3869,10 +3869,10 @@
     <t xml:space="preserve">71.7233505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4309997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5284576416016</t>
+    <t xml:space="preserve">71.4310073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.528450012207</t>
   </si>
   <si>
     <t xml:space="preserve">72.6978530883789</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.305778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4032363891602</t>
+    <t xml:space="preserve">74.3057861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
     <t xml:space="preserve">75.7188034057617</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">77.2780151367188</t>
   </si>
   <si>
-    <t xml:space="preserve">77.3754653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.987922668457</t>
+    <t xml:space="preserve">77.3754577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9879302978516</t>
   </si>
   <si>
     <t xml:space="preserve">76.9369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">77.8627166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3244781494141</t>
+    <t xml:space="preserve">77.8627090454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
     <t xml:space="preserve">78.8859405517578</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.424186706543</t>
+    <t xml:space="preserve">78.0088958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.4241790771484</t>
   </si>
   <si>
     <t xml:space="preserve">77.0831146240234</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">78.3012390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">79.032112121582</t>
+    <t xml:space="preserve">79.0321197509766</t>
   </si>
   <si>
     <t xml:space="preserve">78.4474182128906</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">77.8139877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">77.4729156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9647064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4519653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.82080078125</t>
+    <t xml:space="preserve">77.4729080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.964714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">77.9601593017578</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">77.7165374755859</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2989730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7119903564453</t>
+    <t xml:space="preserve">80.3964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2989654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7119979858398</t>
   </si>
   <si>
     <t xml:space="preserve">81.468376159668</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">81.7607192993164</t>
   </si>
   <si>
-    <t xml:space="preserve">85.268928527832</t>
+    <t xml:space="preserve">85.2689361572266</t>
   </si>
   <si>
     <t xml:space="preserve">88.1924438476562</t>
@@ -4007,22 +4007,22 @@
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488143920898</t>
+    <t xml:space="preserve">87.9488067626953</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6796798706055</t>
+    <t xml:space="preserve">88.6796875</t>
   </si>
   <si>
     <t xml:space="preserve">87.9000854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">86.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434310913086</t>
+    <t xml:space="preserve">86.3408737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434234619141</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">86.0972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">88.972038269043</t>
+    <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
     <t xml:space="preserve">88.4360580444336</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1017990112305</t>
+    <t xml:space="preserve">82.1017913818359</t>
   </si>
   <si>
     <t xml:space="preserve">83.1250305175781</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559036254883</t>
+    <t xml:space="preserve">83.8559112548828</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091644287109</t>
+    <t xml:space="preserve">79.9091720581055</t>
   </si>
   <si>
     <t xml:space="preserve">81.5299377441406</t>
@@ -5721,6 +5721,9 @@
   </si>
   <si>
     <t xml:space="preserve">92.0800018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.879997253418</t>
   </si>
 </sst>
 </file>
@@ -71631,7 +71634,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6916782407</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>224914</v>
@@ -71652,6 +71655,32 @@
         <v>1902</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6924768519</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>326851</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>93.4199981689453</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>91.2600021362305</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>92.879997253418</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1903</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="1904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="1905">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,145 +38,145 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807556152344</t>
+    <t xml:space="preserve">15.1807565689087</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8537864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4801054000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1718187332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9476127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9289293289185</t>
+    <t xml:space="preserve">14.8537855148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4801073074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1718196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9476108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
     <t xml:space="preserve">15.0406265258789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3208856582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022012710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.44273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389188766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0877408981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0410318374634</t>
+    <t xml:space="preserve">15.3208866119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4427375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0877418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0410327911377</t>
   </si>
   <si>
     <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3399772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7697086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3866853713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.424054145813</t>
+    <t xml:space="preserve">14.33997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7697095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3866844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9943208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240531921387</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7051258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4155244827271</t>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0036640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338006973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7051248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4155216217041</t>
   </si>
   <si>
     <t xml:space="preserve">12.4061813354492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172292709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5459051132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722269058228</t>
+    <t xml:space="preserve">12.8172302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5459060668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722249984741</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0316896438599</t>
+    <t xml:space="preserve">13.4057769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0316915512085</t>
   </si>
   <si>
     <t xml:space="preserve">13.7607707977295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8355083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1064252853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372121810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2558994293213</t>
+    <t xml:space="preserve">13.8355093002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.106427192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.255898475647</t>
   </si>
   <si>
     <t xml:space="preserve">15.4143047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.601146697998</t>
+    <t xml:space="preserve">15.601149559021</t>
   </si>
   <si>
     <t xml:space="preserve">15.2461500167847</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1060190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3769378662109</t>
+    <t xml:space="preserve">15.1060199737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3769369125366</t>
   </si>
   <si>
     <t xml:space="preserve">15.4796991348267</t>
@@ -188,43 +188,43 @@
     <t xml:space="preserve">15.5450944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4983835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0873355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9939155578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302278518677</t>
+    <t xml:space="preserve">15.6945638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0873374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9939136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202344894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330228805542</t>
   </si>
   <si>
     <t xml:space="preserve">15.5918054580688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7225933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017997741699</t>
+    <t xml:space="preserve">15.7225923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253517150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017959594727</t>
   </si>
   <si>
     <t xml:space="preserve">16.3952159881592</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4138984680176</t>
+    <t xml:space="preserve">16.4139022827148</t>
   </si>
   <si>
     <t xml:space="preserve">16.2924556732178</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">16.3671913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0215377807617</t>
+    <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
     <t xml:space="preserve">16.2177200317383</t>
@@ -260,40 +260,40 @@
     <t xml:space="preserve">16.3391647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1149559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325828552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100845336914</t>
+    <t xml:space="preserve">16.1149597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.432580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100826263428</t>
   </si>
   <si>
     <t xml:space="preserve">16.6474494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6287651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4419288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489791870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548686981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6019229888916</t>
+    <t xml:space="preserve">16.6287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4419269561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6489810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6866264343262</t>
@@ -302,76 +302,76 @@
     <t xml:space="preserve">16.7054500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7995681762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5454540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6583938598633</t>
+    <t xml:space="preserve">16.7995662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5454521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6583919525146</t>
   </si>
   <si>
     <t xml:space="preserve">16.8277988433838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6890077590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7078275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407802581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5830993652344</t>
+    <t xml:space="preserve">16.8183879852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6890048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4725408554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7078285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407783508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.583101272583</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4325141906738</t>
+    <t xml:space="preserve">16.4325160980225</t>
   </si>
   <si>
     <t xml:space="preserve">16.253698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678453445435</t>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290098190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678472518921</t>
   </si>
   <si>
     <t xml:space="preserve">15.2748985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2090177536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854995727539</t>
+    <t xml:space="preserve">15.2090187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854986190796</t>
   </si>
   <si>
     <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443271636963</t>
+    <t xml:space="preserve">14.644326210022</t>
   </si>
   <si>
     <t xml:space="preserve">14.9172611236572</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">15.4348945617676</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854787826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054698944092</t>
+    <t xml:space="preserve">15.5854778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054708480835</t>
   </si>
   <si>
     <t xml:space="preserve">15.8301782608032</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9901723861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7925319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5478315353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.933705329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701812744141</t>
+    <t xml:space="preserve">15.9901752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5478343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9337034225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701822280884</t>
   </si>
   <si>
     <t xml:space="preserve">15.3784246444702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5007734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419496536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9148826599121</t>
+    <t xml:space="preserve">15.5007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9148817062378</t>
   </si>
   <si>
     <t xml:space="preserve">16.0278205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.272518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3195781707764</t>
+    <t xml:space="preserve">16.2725200653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3195762634277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2819309234619</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">16.1595821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983997344971</t>
+    <t xml:space="preserve">16.3760471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983978271484</t>
   </si>
   <si>
     <t xml:space="preserve">16.4607486724854</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.780740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560333251953</t>
+    <t xml:space="preserve">16.7807445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560314178467</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">17.0160312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9407367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372077941895</t>
+    <t xml:space="preserve">16.9407386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.978385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8466186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960391998291</t>
+    <t xml:space="preserve">16.9783840179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.846622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960372924805</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
@@ -503,43 +503,43 @@
     <t xml:space="preserve">16.4231033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8842716217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9030914306641</t>
+    <t xml:space="preserve">16.8842697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7525043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9030895233154</t>
   </si>
   <si>
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972076416016</t>
+    <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
     <t xml:space="preserve">17.0536766052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748588562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0348510742188</t>
+    <t xml:space="preserve">16.8748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.034854888916</t>
   </si>
   <si>
     <t xml:space="preserve">16.8654460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7619209289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0724983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007347106934</t>
+    <t xml:space="preserve">16.7619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0725002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2324924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289691925049</t>
@@ -548,91 +548,91 @@
     <t xml:space="preserve">17.2607288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2136745452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642559051514</t>
+    <t xml:space="preserve">17.2136726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642578125</t>
   </si>
   <si>
     <t xml:space="preserve">17.3077869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.298376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6936569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724765777588</t>
+    <t xml:space="preserve">17.2983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6936588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724784851074</t>
   </si>
   <si>
     <t xml:space="preserve">18.738338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8230438232422</t>
+    <t xml:space="preserve">18.8230419158936</t>
   </si>
   <si>
     <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.804220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430339813232</t>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3783226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2183265686035</t>
+    <t xml:space="preserve">19.3783206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2183246612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159660339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724189758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4230041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.234769821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535934448242</t>
+    <t xml:space="preserve">19.4159679412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4229984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2347717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982929229736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3571224212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8935775756836</t>
+    <t xml:space="preserve">20.3571186065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.893575668335</t>
   </si>
   <si>
     <t xml:space="preserve">20.6676979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6959342956543</t>
+    <t xml:space="preserve">20.6959362030029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3665294647217</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1030082702637</t>
+    <t xml:space="preserve">20.1030120849609</t>
   </si>
   <si>
     <t xml:space="preserve">19.8206634521484</t>
@@ -641,28 +641,28 @@
     <t xml:space="preserve">19.7453689575195</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5194969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6889019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7171382904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8488960266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5759620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630260467529</t>
+    <t xml:space="preserve">19.519495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6888999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.717134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.84889793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.575963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630279541016</t>
   </si>
   <si>
     <t xml:space="preserve">19.2747936248779</t>
   </si>
   <si>
-    <t xml:space="preserve">19.444206237793</t>
+    <t xml:space="preserve">19.4442043304443</t>
   </si>
   <si>
     <t xml:space="preserve">19.3877334594727</t>
@@ -671,25 +671,25 @@
     <t xml:space="preserve">19.3500862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3971462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0959758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0018615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1053886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0865631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8700981140137</t>
+    <t xml:space="preserve">19.397144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0959777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.001859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8701000213623</t>
   </si>
   <si>
     <t xml:space="preserve">18.4936389923096</t>
@@ -698,46 +698,46 @@
     <t xml:space="preserve">18.352466583252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.286584854126</t>
+    <t xml:space="preserve">18.2865867614746</t>
   </si>
   <si>
     <t xml:space="preserve">18.6254024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100841522217</t>
+    <t xml:space="preserve">19.2559680938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.510082244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2371501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5006713867188</t>
+    <t xml:space="preserve">19.5006694793701</t>
   </si>
   <si>
     <t xml:space="preserve">19.7547836303711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7924270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.594783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018218994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7335834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994632720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900524139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9218139648438</t>
+    <t xml:space="preserve">19.7924308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5947856903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7335796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9218120574951</t>
   </si>
   <si>
     <t xml:space="preserve">21.3641548156738</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">21.2982692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.015926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9029865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9876880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1947422027588</t>
+    <t xml:space="preserve">21.1853370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0159244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9029884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9876899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1947441101074</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100444793701</t>
+    <t xml:space="preserve">21.1100406646729</t>
   </si>
   <si>
     <t xml:space="preserve">21.4112091064453</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608850479126</t>
+    <t xml:space="preserve">21.6088485717773</t>
   </si>
   <si>
     <t xml:space="preserve">21.2135696411133</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">21.3829746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5429725646973</t>
+    <t xml:space="preserve">21.54296875</t>
   </si>
   <si>
     <t xml:space="preserve">21.8347301483154</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">22.0229606628418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8064918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0417823791504</t>
+    <t xml:space="preserve">21.8064956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0417804718018</t>
   </si>
   <si>
     <t xml:space="preserve">22.2582473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6252956390381</t>
+    <t xml:space="preserve">22.6817665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6252994537354</t>
   </si>
   <si>
     <t xml:space="preserve">23.0394039154053</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">22.3711853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0135478973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.91943359375</t>
+    <t xml:space="preserve">22.0135459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9194297790527</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">21.3076839447021</t>
   </si>
   <si>
-    <t xml:space="preserve">22.117073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0981216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1455039978027</t>
+    <t xml:space="preserve">22.1170749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.098123550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1455020904541</t>
   </si>
   <si>
     <t xml:space="preserve">22.1549758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2686901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0507411956787</t>
+    <t xml:space="preserve">22.2686920166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0507431030273</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0886459350586</t>
+    <t xml:space="preserve">22.08864402771</t>
   </si>
   <si>
     <t xml:space="preserve">21.7569847106934</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">21.6811771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">21.576940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7285575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7380332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579891204834</t>
+    <t xml:space="preserve">21.5769386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7285537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7380352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579872131348</t>
   </si>
   <si>
     <t xml:space="preserve">21.5200843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1315631866455</t>
+    <t xml:space="preserve">21.1315650939941</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612213134766</t>
+    <t xml:space="preserve">21.8612194061279</t>
   </si>
   <si>
     <t xml:space="preserve">21.463228225708</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">22.4013557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5529689788818</t>
+    <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
     <t xml:space="preserve">22.5813999176025</t>
@@ -923,31 +923,31 @@
     <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7948894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422679901123</t>
+    <t xml:space="preserve">21.7948875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422698974609</t>
   </si>
   <si>
     <t xml:space="preserve">21.671703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5958919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4676876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3255462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.50559425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951122283936</t>
+    <t xml:space="preserve">21.5958938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3255481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5055923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277778625488</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">23.2068157196045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2162952423096</t>
+    <t xml:space="preserve">23.2162971496582</t>
   </si>
   <si>
     <t xml:space="preserve">22.9983463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.131010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5005741119385</t>
+    <t xml:space="preserve">23.1310119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5005760192871</t>
   </si>
   <si>
     <t xml:space="preserve">23.6900978088379</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">23.1404857635498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.405818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4531936645508</t>
+    <t xml:space="preserve">23.4058170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0646800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7519721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7235412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9793949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6477336883545</t>
+    <t xml:space="preserve">22.9509658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7519683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.723539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9793930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6477298736572</t>
   </si>
   <si>
     <t xml:space="preserve">22.4771633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1834087371826</t>
+    <t xml:space="preserve">22.1834049224854</t>
   </si>
   <si>
     <t xml:space="preserve">23.87961769104</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">23.6616668701172</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3868656158447</t>
+    <t xml:space="preserve">23.3868618011475</t>
   </si>
   <si>
     <t xml:space="preserve">23.1783905029297</t>
@@ -1031,79 +1031,79 @@
     <t xml:space="preserve">22.90358543396</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0217590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955615997314</t>
+    <t xml:space="preserve">24.0217571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955635070801</t>
   </si>
   <si>
     <t xml:space="preserve">24.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6377029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.685079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5903205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7040348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8082714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7798404693604</t>
+    <t xml:space="preserve">24.6377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6850814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5903186798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7040328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8082675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.779842376709</t>
   </si>
   <si>
     <t xml:space="preserve">24.7229862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5429401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1639003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8651256561279</t>
+    <t xml:space="preserve">24.5429439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1638965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8651275634766</t>
   </si>
   <si>
     <t xml:space="preserve">25.7558746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.547399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915458679199</t>
+    <t xml:space="preserve">25.7653484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5474014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915496826172</t>
   </si>
   <si>
     <t xml:space="preserve">25.4052581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4431648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4905433654785</t>
+    <t xml:space="preserve">25.4431629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4905452728271</t>
   </si>
   <si>
     <t xml:space="preserve">25.3863105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3294525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0830726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7274475097656</t>
+    <t xml:space="preserve">25.3484020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3294506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.727445602417</t>
   </si>
   <si>
     <t xml:space="preserve">25.661111831665</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">25.9643459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3054828643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8645706176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3099460601807</t>
+    <t xml:space="preserve">26.3054847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8645687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.309944152832</t>
   </si>
   <si>
     <t xml:space="preserve">26.9119472503662</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">27.0635681152344</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6750469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972343444824</t>
+    <t xml:space="preserve">26.675048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972362518311</t>
   </si>
   <si>
     <t xml:space="preserve">27.1678028106689</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4665756225586</t>
+    <t xml:space="preserve">26.4665775299072</t>
   </si>
   <si>
     <t xml:space="preserve">26.0591087341309</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">25.0451698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1778335571289</t>
+    <t xml:space="preserve">25.1778316497803</t>
   </si>
   <si>
     <t xml:space="preserve">25.1967868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5189743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1115036010742</t>
+    <t xml:space="preserve">25.5189723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1115016937256</t>
   </si>
   <si>
     <t xml:space="preserve">25.5379238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.935920715332</t>
+    <t xml:space="preserve">25.9359188079834</t>
   </si>
   <si>
     <t xml:space="preserve">25.1588821411133</t>
@@ -1175,37 +1175,37 @@
     <t xml:space="preserve">25.1683578491211</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9219799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2062644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5853042602539</t>
+    <t xml:space="preserve">24.9219818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.206262588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1020259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5853023529053</t>
   </si>
   <si>
     <t xml:space="preserve">25.6042575836182</t>
   </si>
   <si>
-    <t xml:space="preserve">25.860107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3339138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2486305236816</t>
+    <t xml:space="preserve">25.8601112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.333911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.248628616333</t>
   </si>
   <si>
     <t xml:space="preserve">26.4381484985352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7987937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3673553466797</t>
+    <t xml:space="preserve">24.7987957000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3673572540283</t>
   </si>
   <si>
     <t xml:space="preserve">25.3578796386719</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">25.6800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6232089996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7748260498047</t>
+    <t xml:space="preserve">25.6232109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7748279571533</t>
   </si>
   <si>
     <t xml:space="preserve">25.5947818756104</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">25.7084922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1064834594727</t>
+    <t xml:space="preserve">26.1064872741699</t>
   </si>
   <si>
     <t xml:space="preserve">26.8171901702881</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">25.8695831298828</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8222045898438</t>
+    <t xml:space="preserve">25.8222064971924</t>
   </si>
   <si>
     <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6326866149902</t>
+    <t xml:space="preserve">25.632682800293</t>
   </si>
   <si>
     <t xml:space="preserve">24.7324619293213</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">24.0691375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4481773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8272247314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7848567962646</t>
+    <t xml:space="preserve">24.4481792449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8272228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7848587036133</t>
   </si>
   <si>
     <t xml:space="preserve">24.258659362793</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9693641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9269981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012481689453</t>
+    <t xml:space="preserve">25.0167407989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9693622589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2012462615967</t>
   </si>
   <si>
     <t xml:space="preserve">26.0117282867432</t>
@@ -1298,88 +1298,88 @@
     <t xml:space="preserve">26.1538677215576</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4855270385742</t>
+    <t xml:space="preserve">26.4855289459229</t>
   </si>
   <si>
     <t xml:space="preserve">26.5329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9593315124512</t>
+    <t xml:space="preserve">26.9593296051025</t>
   </si>
   <si>
     <t xml:space="preserve">26.7698097229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9492950439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6176376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8071575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6650161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3283386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2335796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5394916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0652751922607</t>
+    <t xml:space="preserve">28.9492988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.617639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8071594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.665018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3283405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2335815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5394897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2086715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0652770996094</t>
   </si>
   <si>
     <t xml:space="preserve">30.3042697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9696788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1130714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2602405548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0803565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1797180175781</t>
+    <t xml:space="preserve">29.9696750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.113073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2602424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6501693725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0803527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1797142028809</t>
   </si>
   <si>
     <t xml:space="preserve">36.1356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4149436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9369583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1759414672852</t>
+    <t xml:space="preserve">34.4149475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.936954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1759490966797</t>
   </si>
   <si>
     <t xml:space="preserve">34.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7532997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9922981262207</t>
+    <t xml:space="preserve">35.753303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9922904968262</t>
   </si>
   <si>
     <t xml:space="preserve">35.2275161743164</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">35.275318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4224739074707</t>
+    <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
     <t xml:space="preserve">36.3746795654297</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">30.7822532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168422698975</t>
+    <t xml:space="preserve">31.1168403625488</t>
   </si>
   <si>
     <t xml:space="preserve">31.4036312103271</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">31.3558330535889</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2124404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0287818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7935600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9847564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7973289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3671417236328</t>
+    <t xml:space="preserve">31.2124423980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0287780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7935562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9847526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7973327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3671455383301</t>
   </si>
   <si>
     <t xml:space="preserve">34.6539344787598</t>
@@ -1454,22 +1454,22 @@
     <t xml:space="preserve">34.6061363220215</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4627380371094</t>
+    <t xml:space="preserve">34.4627342224121</t>
   </si>
   <si>
     <t xml:space="preserve">33.8413619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7495307922363</t>
+    <t xml:space="preserve">34.7495269775391</t>
   </si>
   <si>
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0400886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8966941833496</t>
+    <t xml:space="preserve">36.0400924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8966903686523</t>
   </si>
   <si>
     <t xml:space="preserve">36.6614723205566</t>
@@ -1478,28 +1478,28 @@
     <t xml:space="preserve">39.0036010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3306503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5180740356445</t>
+    <t xml:space="preserve">37.3306465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5180778503418</t>
   </si>
   <si>
     <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8564376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2790832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2350540161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8929214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5583343505859</t>
+    <t xml:space="preserve">37.8564338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2790870666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2350578308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8929290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5583381652832</t>
   </si>
   <si>
     <t xml:space="preserve">33.6979637145996</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">32.2640075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9809837341309</t>
+    <t xml:space="preserve">32.9809875488281</t>
   </si>
   <si>
     <t xml:space="preserve">33.3633728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7897872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5985908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5029983520508</t>
+    <t xml:space="preserve">32.7897911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.837589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5985946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.503002166748</t>
   </si>
   <si>
     <t xml:space="preserve">33.2199821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6463928222656</t>
+    <t xml:space="preserve">32.6463966369629</t>
   </si>
   <si>
     <t xml:space="preserve">32.3596038818359</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">32.0728149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7860240936279</t>
+    <t xml:space="preserve">31.7860202789307</t>
   </si>
   <si>
     <t xml:space="preserve">31.8338184356689</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0690422058105</t>
+    <t xml:space="preserve">31.0690441131592</t>
   </si>
   <si>
     <t xml:space="preserve">32.025016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0212440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8816146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8703117370605</t>
+    <t xml:space="preserve">31.0212459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8816108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8703136444092</t>
   </si>
   <si>
     <t xml:space="preserve">28.5357208251953</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709445953369</t>
+    <t xml:space="preserve">27.7709465026855</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2489280700684</t>
+    <t xml:space="preserve">28.248929977417</t>
   </si>
   <si>
     <t xml:space="preserve">27.5797519683838</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">28.1055335998535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2451610565186</t>
+    <t xml:space="preserve">27.2451591491699</t>
   </si>
   <si>
     <t xml:space="preserve">27.9621391296387</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">28.3445281982422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.013708114624</t>
+    <t xml:space="preserve">29.0137062072754</t>
   </si>
   <si>
     <t xml:space="preserve">28.9181098937988</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">29.5872898101807</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7344570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0174732208252</t>
+    <t xml:space="preserve">30.7344551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0174770355225</t>
   </si>
   <si>
     <t xml:space="preserve">29.4438934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6828842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5759792327881</t>
+    <t xml:space="preserve">29.6828861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5835189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5759830474854</t>
   </si>
   <si>
     <t xml:space="preserve">26.384786605835</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">27.4363555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8187446594238</t>
+    <t xml:space="preserve">27.8187427520752</t>
   </si>
   <si>
     <t xml:space="preserve">27.7231464385986</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6313190460205</t>
+    <t xml:space="preserve">28.6313209533691</t>
   </si>
   <si>
     <t xml:space="preserve">29.6350879669189</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">27.1017646789551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8627758026123</t>
+    <t xml:space="preserve">26.862771987915</t>
   </si>
   <si>
     <t xml:space="preserve">27.4841537475586</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">27.0061683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0979976654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200103759766</t>
+    <t xml:space="preserve">26.097993850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200122833252</t>
   </si>
   <si>
     <t xml:space="preserve">26.1935939788818</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">26.6237812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7156085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.289192199707</t>
+    <t xml:space="preserve">25.7156066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2891883850098</t>
   </si>
   <si>
     <t xml:space="preserve">26.7671775817871</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3885555267334</t>
+    <t xml:space="preserve">26.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.388557434082</t>
   </si>
   <si>
     <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8740825653076</t>
+    <t xml:space="preserve">29.874080657959</t>
   </si>
   <si>
     <t xml:space="preserve">30.1608695983887</t>
@@ -1718,82 +1718,82 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080348968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4514350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4552001953125</t>
+    <t xml:space="preserve">31.308032989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4514312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4552040100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.3118019104004</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2162094116211</t>
+    <t xml:space="preserve">32.2162055969238</t>
   </si>
   <si>
     <t xml:space="preserve">33.602367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1721801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5545692443848</t>
+    <t xml:space="preserve">33.1721839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5545654296875</t>
   </si>
   <si>
     <t xml:space="preserve">30.2564678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6388568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5910587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3004970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9409961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6484184265137</t>
+    <t xml:space="preserve">30.638858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5910568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3004989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6484203338623</t>
   </si>
   <si>
     <t xml:space="preserve">30.8204936981201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2851486206055</t>
+    <t xml:space="preserve">30.9734497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2851505279541</t>
   </si>
   <si>
     <t xml:space="preserve">30.0748329162598</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4763431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2277908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9983577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8262825012207</t>
+    <t xml:space="preserve">30.4763412475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2277889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9983558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8262844085693</t>
   </si>
   <si>
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4381046295166</t>
+    <t xml:space="preserve">30.438102722168</t>
   </si>
   <si>
     <t xml:space="preserve">30.7631340026855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.935209274292</t>
+    <t xml:space="preserve">30.9352073669434</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498035430908</t>
@@ -1802,37 +1802,37 @@
     <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8129539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5203704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4879207611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.717357635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4821338653564</t>
+    <t xml:space="preserve">28.812952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5203723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.487922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7173557281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4821319580078</t>
   </si>
   <si>
     <t xml:space="preserve">29.1762199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9237041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6533908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058433532715</t>
+    <t xml:space="preserve">29.3291797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9237060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6533889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058414459229</t>
   </si>
   <si>
     <t xml:space="preserve">28.3637657165527</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">28.5182342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8038291931152</t>
+    <t xml:space="preserve">27.8038272857666</t>
   </si>
   <si>
     <t xml:space="preserve">28.0741443634033</t>
@@ -1850,10 +1850,10 @@
     <t xml:space="preserve">27.1859664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2245826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2052745819092</t>
+    <t xml:space="preserve">27.2245845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2052764892578</t>
   </si>
   <si>
     <t xml:space="preserve">27.3211231231689</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">27.6493625640869</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9776039123535</t>
+    <t xml:space="preserve">27.9776020050049</t>
   </si>
   <si>
     <t xml:space="preserve">27.5142059326172</t>
@@ -1877,37 +1877,37 @@
     <t xml:space="preserve">27.7845211029053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548362731934</t>
+    <t xml:space="preserve">28.0548343658447</t>
   </si>
   <si>
     <t xml:space="preserve">27.9969120025635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4989242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2479190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3251495361328</t>
+    <t xml:space="preserve">28.4989261627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.247917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3251514434814</t>
   </si>
   <si>
     <t xml:space="preserve">27.8424453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.900369644165</t>
+    <t xml:space="preserve">27.9003677368164</t>
   </si>
   <si>
     <t xml:space="preserve">28.0934524536133</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6340827941895</t>
+    <t xml:space="preserve">28.6340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">29.1167888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8850917816162</t>
+    <t xml:space="preserve">28.8850898742676</t>
   </si>
   <si>
     <t xml:space="preserve">29.2712535858154</t>
@@ -1919,79 +1919,79 @@
     <t xml:space="preserve">29.9084243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8505001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7539577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2173557281494</t>
+    <t xml:space="preserve">29.8504981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7539596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2173538208008</t>
   </si>
   <si>
     <t xml:space="preserve">29.9856567382812</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6807537078857</t>
+    <t xml:space="preserve">30.6807518005371</t>
   </si>
   <si>
     <t xml:space="preserve">29.3677959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">29.483642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.174711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4257202148438</t>
+    <t xml:space="preserve">29.4836444854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1747131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4257183074951</t>
   </si>
   <si>
     <t xml:space="preserve">29.2519454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.464334487915</t>
+    <t xml:space="preserve">29.4643363952637</t>
   </si>
   <si>
     <t xml:space="preserve">29.0202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9043960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6920070648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4796180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7652111053467</t>
+    <t xml:space="preserve">28.9043979644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6920051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4796161651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7652130126953</t>
   </si>
   <si>
     <t xml:space="preserve">27.1666584014893</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9542675018311</t>
+    <t xml:space="preserve">26.9542694091797</t>
   </si>
   <si>
     <t xml:space="preserve">27.1473503112793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.282506942749</t>
+    <t xml:space="preserve">27.2825088500977</t>
   </si>
   <si>
     <t xml:space="preserve">27.5528240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6839504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5101776123047</t>
+    <t xml:space="preserve">26.683952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5101795196533</t>
   </si>
   <si>
     <t xml:space="preserve">27.8810615539551</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1899948120117</t>
+    <t xml:space="preserve">28.1899929046631</t>
   </si>
   <si>
     <t xml:space="preserve">28.3444595336914</t>
@@ -2000,187 +2000,187 @@
     <t xml:space="preserve">27.938985824585</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4369735717773</t>
+    <t xml:space="preserve">27.4369716644287</t>
   </si>
   <si>
     <t xml:space="preserve">27.2631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0315017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6260299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4176654815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0355281829834</t>
+    <t xml:space="preserve">27.0314998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6260280609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4176635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.035530090332</t>
   </si>
   <si>
     <t xml:space="preserve">27.0894241333008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9928817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0508079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4755897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7072887420654</t>
+    <t xml:space="preserve">26.992883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0508098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4755878448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7072906494141</t>
   </si>
   <si>
     <t xml:space="preserve">27.591438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6107482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6879787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.355712890625</t>
+    <t xml:space="preserve">27.610746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6879806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3557109832764</t>
   </si>
   <si>
     <t xml:space="preserve">25.9309329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8537006378174</t>
+    <t xml:space="preserve">25.8536987304688</t>
   </si>
   <si>
     <t xml:space="preserve">25.8730068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.301815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4562797546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8577251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7957744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9116230010986</t>
+    <t xml:space="preserve">27.3018169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4562816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8577270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7957725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9116249084473</t>
   </si>
   <si>
     <t xml:space="preserve">26.7032623291016</t>
   </si>
   <si>
-    <t xml:space="preserve">27.745906829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1087341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1320667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3830757141113</t>
+    <t xml:space="preserve">27.7459049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1087322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1320686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3830738067627</t>
   </si>
   <si>
     <t xml:space="preserve">28.9430141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4064083099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8078556060791</t>
+    <t xml:space="preserve">29.4064102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8078575134277</t>
   </si>
   <si>
     <t xml:space="preserve">28.9816303253174</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1360950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7499332427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8271636962891</t>
+    <t xml:space="preserve">29.1360969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7499313354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8271675109863</t>
   </si>
   <si>
     <t xml:space="preserve">29.000940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6147747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2133274078369</t>
+    <t xml:space="preserve">28.5954647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6147727966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2133293151855</t>
   </si>
   <si>
     <t xml:space="preserve">30.6228275299072</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9357872009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.457103729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8585529327393</t>
+    <t xml:space="preserve">31.935791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3026428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4571113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8585548400879</t>
   </si>
   <si>
     <t xml:space="preserve">31.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1827659606934</t>
+    <t xml:space="preserve">31.182767868042</t>
   </si>
   <si>
     <t xml:space="preserve">31.6654720306396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1674880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2600021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5882434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0476112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9510688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1248435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8545265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8931446075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8159103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.337230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4683647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0089912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7000617980957</t>
+    <t xml:space="preserve">32.1674842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5882396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.047607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9510707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1248455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3565425872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8545246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8931427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8159084320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3372325897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4683628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0089893341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7000598907471</t>
   </si>
   <si>
     <t xml:space="preserve">33.0170478820801</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">33.3645935058594</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9052200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8859176635742</t>
+    <t xml:space="preserve">33.9052238464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.885913848877</t>
   </si>
   <si>
     <t xml:space="preserve">34.8899421691895</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">35.0251007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9712066650391</t>
+    <t xml:space="preserve">35.9711990356445</t>
   </si>
   <si>
     <t xml:space="preserve">36.5311431884766</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">36.9559211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7008934020996</t>
+    <t xml:space="preserve">37.2069320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7008895874023</t>
   </si>
   <si>
     <t xml:space="preserve">35.8167343139648</t>
@@ -2231,70 +2231,70 @@
     <t xml:space="preserve">32.9205055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">31.993709564209</t>
+    <t xml:space="preserve">31.9937076568604</t>
   </si>
   <si>
     <t xml:space="preserve">31.6847801208496</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8778667449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3605651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.383903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8432731628418</t>
+    <t xml:space="preserve">31.8778629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3605690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3839073181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8432769775391</t>
   </si>
   <si>
     <t xml:space="preserve">31.7427024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8239669799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.901195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2447166442871</t>
+    <t xml:space="preserve">32.8239631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9011993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2447204589844</t>
   </si>
   <si>
     <t xml:space="preserve">32.5343437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4764175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6928329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3871040344238</t>
+    <t xml:space="preserve">32.4764137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6928367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3871021270752</t>
   </si>
   <si>
     <t xml:space="preserve">29.811882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9623222351074</t>
+    <t xml:space="preserve">28.9623241424561</t>
   </si>
   <si>
     <t xml:space="preserve">29.8698081970215</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7732677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0049667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.027473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2784805297852</t>
+    <t xml:space="preserve">29.773265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0049648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0274715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2784767150879</t>
   </si>
   <si>
     <t xml:space="preserve">25.2937622070312</t>
@@ -2309,31 +2309,31 @@
     <t xml:space="preserve">24.1931915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9767742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.274450302124</t>
+    <t xml:space="preserve">22.9767761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2744541168213</t>
   </si>
   <si>
     <t xml:space="preserve">25.737850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8150825500488</t>
+    <t xml:space="preserve">25.8150806427002</t>
   </si>
   <si>
     <t xml:space="preserve">25.100679397583</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7225685119629</t>
+    <t xml:space="preserve">26.7225704193115</t>
   </si>
   <si>
     <t xml:space="preserve">26.8384189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7917461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8263359069824</t>
+    <t xml:space="preserve">24.7917499542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8263339996338</t>
   </si>
   <si>
     <t xml:space="preserve">24.019416809082</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">23.9614944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4441986083984</t>
+    <t xml:space="preserve">24.4442005157471</t>
   </si>
   <si>
     <t xml:space="preserve">24.9075965881348</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">25.6220016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.630054473877</t>
+    <t xml:space="preserve">26.3943290710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6300563812256</t>
   </si>
   <si>
     <t xml:space="preserve">27.8231372833252</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">25.718542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4482288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5833873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5487957000732</t>
+    <t xml:space="preserve">25.4482250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5833854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5487976074219</t>
   </si>
   <si>
     <t xml:space="preserve">26.9349594116211</t>
@@ -2390,43 +2390,43 @@
     <t xml:space="preserve">26.4522533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8923168182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0660915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735774993896</t>
+    <t xml:space="preserve">25.8923149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.066089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.973575592041</t>
   </si>
   <si>
     <t xml:space="preserve">26.375020980835</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0162181854248</t>
+    <t xml:space="preserve">28.0162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">30.0242729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">32.283332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4104404449463</t>
+    <t xml:space="preserve">32.2833366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4104385375977</t>
   </si>
   <si>
     <t xml:space="preserve">29.5994930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5721302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5681037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5061531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3903026580811</t>
+    <t xml:space="preserve">27.5721282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5681056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5061511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3903007507324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5254592895508</t>
@@ -2441,22 +2441,22 @@
     <t xml:space="preserve">24.6565895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2511177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2897338867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5793552398682</t>
+    <t xml:space="preserve">24.2511196136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2897357940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5793571472168</t>
   </si>
   <si>
     <t xml:space="preserve">24.8496723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3283500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8303623199463</t>
+    <t xml:space="preserve">24.3283519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8303642272949</t>
   </si>
   <si>
     <t xml:space="preserve">24.3862762451172</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">24.1545753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0387287139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9035720825195</t>
+    <t xml:space="preserve">24.0387268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9035682678223</t>
   </si>
   <si>
     <t xml:space="preserve">23.1505489349365</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">23.3822460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0733165740967</t>
+    <t xml:space="preserve">23.073314666748</t>
   </si>
   <si>
     <t xml:space="preserve">23.7684135437012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">24.3476581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5447654724121</t>
+    <t xml:space="preserve">25.5447673797607</t>
   </si>
   <si>
     <t xml:space="preserve">26.1047058105469</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">26.0853996276855</t>
   </si>
   <si>
-    <t xml:space="preserve">25.119987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.946216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8110580444336</t>
+    <t xml:space="preserve">25.1199893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9462146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.811056137085</t>
   </si>
   <si>
     <t xml:space="preserve">24.5986652374268</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">24.7338237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9848289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9269046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7611865997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2205581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6179752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.463508605957</t>
+    <t xml:space="preserve">24.984827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9269065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7611846923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2205543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4635105133057</t>
   </si>
   <si>
     <t xml:space="preserve">25.2358360290527</t>
@@ -2558,43 +2558,43 @@
     <t xml:space="preserve">25.1392955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6413097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3130702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2977886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7804946899414</t>
+    <t xml:space="preserve">25.6413078308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3130683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2977867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7804927825928</t>
   </si>
   <si>
     <t xml:space="preserve">26.6067180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0467796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2591724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4136371612549</t>
+    <t xml:space="preserve">26.046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2591705322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4136390686035</t>
   </si>
   <si>
     <t xml:space="preserve">25.8343906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7571582794189</t>
+    <t xml:space="preserve">25.7571601867676</t>
   </si>
   <si>
     <t xml:space="preserve">25.4675331115723</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5600490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689785003662</t>
+    <t xml:space="preserve">24.5600509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689823150635</t>
   </si>
   <si>
     <t xml:space="preserve">24.772439956665</t>
@@ -2603,40 +2603,40 @@
     <t xml:space="preserve">30.1401233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7620143890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1481781005859</t>
+    <t xml:space="preserve">31.7620182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1481742858887</t>
   </si>
   <si>
     <t xml:space="preserve">32.2061042785645</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8392448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.974401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9550933837891</t>
+    <t xml:space="preserve">31.8392467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9744033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9550952911377</t>
   </si>
   <si>
     <t xml:space="preserve">32.3798789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2680511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.175537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1562347412109</t>
+    <t xml:space="preserve">33.2680549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1755409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1562309265137</t>
   </si>
   <si>
     <t xml:space="preserve">33.9245338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1795616149902</t>
+    <t xml:space="preserve">35.1795692443848</t>
   </si>
   <si>
     <t xml:space="preserve">35.3726501464844</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">34.3879280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5810127258301</t>
+    <t xml:space="preserve">34.5810089111328</t>
   </si>
   <si>
     <t xml:space="preserve">35.2761077880859</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">34.8706359863281</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7547874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6429634094238</t>
+    <t xml:space="preserve">34.7547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6429595947266</t>
   </si>
   <si>
     <t xml:space="preserve">35.0444107055664</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">34.4651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6003227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2640228271484</t>
+    <t xml:space="preserve">34.6003265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2640266418457</t>
   </si>
   <si>
     <t xml:space="preserve">32.4957275390625</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">33.0556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0596885681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5383682250977</t>
+    <t xml:space="preserve">34.059684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5383720397949</t>
   </si>
   <si>
     <t xml:space="preserve">34.291389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6542205810547</t>
+    <t xml:space="preserve">33.6542167663574</t>
   </si>
   <si>
     <t xml:space="preserve">32.9977378845215</t>
@@ -2702,28 +2702,28 @@
     <t xml:space="preserve">33.7314491271973</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3066749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6349067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1908187866211</t>
+    <t xml:space="preserve">33.3066711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6349105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1908226013184</t>
   </si>
   <si>
     <t xml:space="preserve">32.9591217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8971748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0709457397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.437801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.345287322998</t>
+    <t xml:space="preserve">31.8971710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0709419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4377975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3452911376953</t>
   </si>
   <si>
     <t xml:space="preserve">33.2101287841797</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">33.557674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9824600219727</t>
+    <t xml:space="preserve">33.9824523925781</t>
   </si>
   <si>
     <t xml:space="preserve">33.9631500244141</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">34.4458541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0983085632324</t>
+    <t xml:space="preserve">34.0983047485352</t>
   </si>
   <si>
     <t xml:space="preserve">33.5962944030762</t>
@@ -2753,37 +2753,37 @@
     <t xml:space="preserve">33.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">32.939811706543</t>
+    <t xml:space="preserve">32.9398155212402</t>
   </si>
   <si>
     <t xml:space="preserve">33.4418258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">32.881893157959</t>
+    <t xml:space="preserve">32.8818893432617</t>
   </si>
   <si>
     <t xml:space="preserve">32.6115760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6775512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5351676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8360443115234</t>
+    <t xml:space="preserve">34.6775550842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5351715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8360481262207</t>
   </si>
   <si>
     <t xml:space="preserve">37.4000129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4925270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1490097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2994384765625</t>
+    <t xml:space="preserve">36.4925231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1490058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2994422912598</t>
   </si>
   <si>
     <t xml:space="preserve">36.2801361083984</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">35.7201957702637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6043472290039</t>
+    <t xml:space="preserve">35.6043510437012</t>
   </si>
   <si>
     <t xml:space="preserve">35.565731048584</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">36.4346008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6510200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0331611633301</t>
+    <t xml:space="preserve">37.6510162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0331573486328</t>
   </si>
   <si>
     <t xml:space="preserve">37.3807029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5158615112305</t>
+    <t xml:space="preserve">37.5158653259277</t>
   </si>
   <si>
     <t xml:space="preserve">38.519889831543</t>
@@ -2825,34 +2825,34 @@
     <t xml:space="preserve">39.5625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">39.581844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.910083770752</t>
+    <t xml:space="preserve">39.5818405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9100799560547</t>
   </si>
   <si>
     <t xml:space="preserve">40.2383193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2149848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9527168273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1458053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7057418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4587669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9567451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5319709777832</t>
+    <t xml:space="preserve">39.2149810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9527206420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1458015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7057456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4587631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9567489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5319747924805</t>
   </si>
   <si>
     <t xml:space="preserve">41.3388862609863</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">40.701717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6244812011719</t>
+    <t xml:space="preserve">40.6244850158691</t>
   </si>
   <si>
     <t xml:space="preserve">40.5665588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3429145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4780769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0878829956055</t>
+    <t xml:space="preserve">42.3429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4780693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0878868103027</t>
   </si>
   <si>
     <t xml:space="preserve">41.2809600830078</t>
@@ -2885,31 +2885,31 @@
     <t xml:space="preserve">42.3236045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4008331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6711502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8256225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8875694274902</t>
+    <t xml:space="preserve">42.4008369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6711578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8256149291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8875732421875</t>
   </si>
   <si>
     <t xml:space="preserve">43.5786399841309</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9841117858887</t>
+    <t xml:space="preserve">43.9841156005859</t>
   </si>
   <si>
     <t xml:space="preserve">43.6172561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8489532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3743057250977</t>
+    <t xml:space="preserve">43.8489570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3743019104004</t>
   </si>
   <si>
     <t xml:space="preserve">47.3244361877441</t>
@@ -2918,13 +2918,13 @@
     <t xml:space="preserve">49.7669219970703</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9600028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5601615905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4636154174805</t>
+    <t xml:space="preserve">49.9600067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5601577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4636192321777</t>
   </si>
   <si>
     <t xml:space="preserve">47.2665100097656</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">48.3670768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4982032775879</t>
+    <t xml:space="preserve">47.4982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">46.4748725891113</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8183937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0694007873535</t>
+    <t xml:space="preserve">45.8183898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0693969726562</t>
   </si>
   <si>
     <t xml:space="preserve">46.5521049499512</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">48.3188056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1876792907715</t>
+    <t xml:space="preserve">49.1876754760742</t>
   </si>
   <si>
     <t xml:space="preserve">47.9229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">47.691291809082</t>
+    <t xml:space="preserve">47.6912879943848</t>
   </si>
   <si>
     <t xml:space="preserve">47.7878341674805</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">49.2842178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6221160888672</t>
+    <t xml:space="preserve">49.6221122741699</t>
   </si>
   <si>
     <t xml:space="preserve">49.6703872680664</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">47.4209747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9422950744629</t>
+    <t xml:space="preserve">47.9422988891602</t>
   </si>
   <si>
     <t xml:space="preserve">47.0734252929688</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">50.4909782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4974365234375</t>
+    <t xml:space="preserve">54.4974403381348</t>
   </si>
   <si>
     <t xml:space="preserve">53.8699188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3252601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9527740478516</t>
+    <t xml:space="preserve">52.3252639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9527778625488</t>
   </si>
   <si>
     <t xml:space="preserve">52.9045066833496</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">53.6768379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0975914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.001049041748</t>
+    <t xml:space="preserve">53.0975952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0010528564453</t>
   </si>
   <si>
     <t xml:space="preserve">52.8562355041504</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">47.7105979919434</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6567001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0774574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.173999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9616088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9036827087402</t>
+    <t xml:space="preserve">48.6567039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1739959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9616050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.903678894043</t>
   </si>
   <si>
     <t xml:space="preserve">47.4402847290039</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">47.7685203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">46.899658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3590278625488</t>
+    <t xml:space="preserve">46.8996543884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3590240478516</t>
   </si>
   <si>
     <t xml:space="preserve">45.1426048278809</t>
@@ -3101,28 +3101,28 @@
     <t xml:space="preserve">46.301097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5907173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8031158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8071441650391</t>
+    <t xml:space="preserve">46.5907211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.803108215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8071365356445</t>
   </si>
   <si>
     <t xml:space="preserve">45.6446189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8956260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1659393310547</t>
+    <t xml:space="preserve">45.895622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1659469604492</t>
   </si>
   <si>
     <t xml:space="preserve">45.6639251708984</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9149360656738</t>
+    <t xml:space="preserve">45.9149398803711</t>
   </si>
   <si>
     <t xml:space="preserve">45.3163757324219</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">45.4129219055176</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4322280883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0887107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9575805664062</t>
+    <t xml:space="preserve">45.4322319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0887145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.957576751709</t>
   </si>
   <si>
     <t xml:space="preserve">47.1699676513672</t>
@@ -3146,28 +3146,28 @@
     <t xml:space="preserve">48.0388336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9945907592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.429027557373</t>
+    <t xml:space="preserve">48.9945945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4290313720703</t>
   </si>
   <si>
     <t xml:space="preserve">50.5875244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1321830749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6977424621582</t>
+    <t xml:space="preserve">52.1321792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6977462768555</t>
   </si>
   <si>
     <t xml:space="preserve">56.1869049072266</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1659965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1450843811035</t>
+    <t xml:space="preserve">58.1659927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.145092010498</t>
   </si>
   <si>
     <t xml:space="preserve">60.9174156188965</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">60.6277923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">61.255313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.53125</t>
+    <t xml:space="preserve">61.2553100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5312538146973</t>
   </si>
   <si>
     <t xml:space="preserve">60.2899017333984</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">56.6213417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">55.849006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.283447265625</t>
+    <t xml:space="preserve">55.8490104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2834434509277</t>
   </si>
   <si>
     <t xml:space="preserve">53.4354782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4491653442383</t>
+    <t xml:space="preserve">54.4491691589355</t>
   </si>
   <si>
     <t xml:space="preserve">53.9664611816406</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">54.0147323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9318695068359</t>
+    <t xml:space="preserve">54.9318733215332</t>
   </si>
   <si>
     <t xml:space="preserve">56.4282569885254</t>
@@ -3233,25 +3233,25 @@
     <t xml:space="preserve">55.0284118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3872146606445</t>
+    <t xml:space="preserve">54.2078132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3872108459473</t>
   </si>
   <si>
     <t xml:space="preserve">51.9873657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4145774841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.773380279541</t>
+    <t xml:space="preserve">55.4145812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7733764648438</t>
   </si>
   <si>
     <t xml:space="preserve">54.9801406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2351760864258</t>
+    <t xml:space="preserve">56.2351722717285</t>
   </si>
   <si>
     <t xml:space="preserve">57.3453979492188</t>
@@ -3263,34 +3263,34 @@
     <t xml:space="preserve">58.6004295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">60.965690612793</t>
+    <t xml:space="preserve">60.9656867980957</t>
   </si>
   <si>
     <t xml:space="preserve">61.0139579772949</t>
   </si>
   <si>
-    <t xml:space="preserve">61.3035850524902</t>
+    <t xml:space="preserve">61.303581237793</t>
   </si>
   <si>
     <t xml:space="preserve">60.3864402770996</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6969718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0420875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4073524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2214965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0630035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2287216186523</t>
+    <t xml:space="preserve">58.6969757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0420951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4073486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.221492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2287178039551</t>
   </si>
   <si>
     <t xml:space="preserve">52.083911895752</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">53.1458587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4427070617676</t>
+    <t xml:space="preserve">50.4427108764648</t>
   </si>
   <si>
     <t xml:space="preserve">50.8288764953613</t>
@@ -3308,31 +3308,31 @@
     <t xml:space="preserve">51.8908271789551</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2359504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4837532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8425559997559</t>
+    <t xml:space="preserve">50.0565452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2359466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4837608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8425598144531</t>
   </si>
   <si>
     <t xml:space="preserve">50.6840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1185035705566</t>
+    <t xml:space="preserve">51.1184997558594</t>
   </si>
   <si>
     <t xml:space="preserve">52.3735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1804504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3461723327637</t>
+    <t xml:space="preserve">52.1804466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3461685180664</t>
   </si>
   <si>
     <t xml:space="preserve">51.4563903808594</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">50.9254150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7186546325684</t>
+    <t xml:space="preserve">50.7806015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7186508178711</t>
   </si>
   <si>
     <t xml:space="preserve">45.0074462890625</t>
@@ -3359,10 +3359,10 @@
     <t xml:space="preserve">42.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2423477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4893264770508</t>
+    <t xml:space="preserve">41.2423439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4893226623535</t>
   </si>
   <si>
     <t xml:space="preserve">42.555305480957</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">42.1498336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5480804443359</t>
+    <t xml:space="preserve">45.5480766296387</t>
   </si>
   <si>
     <t xml:space="preserve">46.8224220275879</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">51.7942886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">49.573844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8771438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0219573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9117317199707</t>
+    <t xml:space="preserve">49.5738372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8771476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0219535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.911735534668</t>
   </si>
   <si>
     <t xml:space="preserve">46.6486473083496</t>
@@ -3404,28 +3404,28 @@
     <t xml:space="preserve">47.5561294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9961967468262</t>
+    <t xml:space="preserve">46.9961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">46.4169502258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.949520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.675178527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.647819519043</t>
+    <t xml:space="preserve">44.9495277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6751823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6478157043457</t>
   </si>
   <si>
     <t xml:space="preserve">42.8063125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1192665100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6253128051758</t>
+    <t xml:space="preserve">44.119270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6253051757812</t>
   </si>
   <si>
     <t xml:space="preserve">47.0348091125488</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">44.157886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4627952575684</t>
+    <t xml:space="preserve">43.4627914428711</t>
   </si>
   <si>
     <t xml:space="preserve">44.1254501342773</t>
@@ -3446,19 +3446,19 @@
     <t xml:space="preserve">42.3908386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0400199890137</t>
+    <t xml:space="preserve">42.0400161743164</t>
   </si>
   <si>
     <t xml:space="preserve">43.4043235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8270950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4312858581543</t>
+    <t xml:space="preserve">44.827091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.444766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.431282043457</t>
   </si>
   <si>
     <t xml:space="preserve">45.528736114502</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">45.9380264282227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6456756591797</t>
+    <t xml:space="preserve">45.645679473877</t>
   </si>
   <si>
     <t xml:space="preserve">45.3923072814941</t>
@@ -3482,22 +3482,22 @@
     <t xml:space="preserve">42.9560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0070457458496</t>
+    <t xml:space="preserve">41.0070495605469</t>
   </si>
   <si>
     <t xml:space="preserve">38.9995727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3054084777832</t>
+    <t xml:space="preserve">40.3054046630859</t>
   </si>
   <si>
     <t xml:space="preserve">39.1360054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7012138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8766212463379</t>
+    <t xml:space="preserve">39.7012176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8766250610352</t>
   </si>
   <si>
     <t xml:space="preserve">40.0325469970703</t>
@@ -3506,22 +3506,22 @@
     <t xml:space="preserve">40.3248977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8706169128418</t>
+    <t xml:space="preserve">40.8706130981445</t>
   </si>
   <si>
     <t xml:space="preserve">42.3713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8646087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7806434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0924835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8840980529785</t>
+    <t xml:space="preserve">41.8646049499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7806396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8841018676758</t>
   </si>
   <si>
     <t xml:space="preserve">41.9620628356934</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">42.8586006164551</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0025062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3593330383301</t>
+    <t xml:space="preserve">45.0025024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3593368530273</t>
   </si>
   <si>
     <t xml:space="preserve">46.2303771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4507751464844</t>
+    <t xml:space="preserve">45.4507789611816</t>
   </si>
   <si>
     <t xml:space="preserve">46.2693557739258</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">51.7460594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9177284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5511627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.548885345459</t>
+    <t xml:space="preserve">50.9177322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5511589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5488891601562</t>
   </si>
   <si>
     <t xml:space="preserve">55.0106430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3517189025879</t>
+    <t xml:space="preserve">55.3517112731934</t>
   </si>
   <si>
     <t xml:space="preserve">54.669563293457</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">53.7437896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1335906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1080894470215</t>
+    <t xml:space="preserve">54.1335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1080932617188</t>
   </si>
   <si>
     <t xml:space="preserve">55.2055435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4491653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4004402160645</t>
+    <t xml:space="preserve">55.4491691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4004364013672</t>
   </si>
   <si>
     <t xml:space="preserve">56.3262176513672</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">55.5466156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">54.474666595459</t>
+    <t xml:space="preserve">54.4746704101562</t>
   </si>
   <si>
     <t xml:space="preserve">53.0616416931152</t>
@@ -3626,31 +3626,31 @@
     <t xml:space="preserve">52.5743865966797</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5256614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4792060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7970504760742</t>
+    <t xml:space="preserve">52.5256576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4792022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">51.356258392334</t>
   </si>
   <si>
-    <t xml:space="preserve">50.869010925293</t>
+    <t xml:space="preserve">50.8690071105957</t>
   </si>
   <si>
     <t xml:space="preserve">50.771556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0151786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0384063720703</t>
+    <t xml:space="preserve">51.0151824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0384101867676</t>
   </si>
   <si>
     <t xml:space="preserve">51.4537086486816</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">47.8480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8015975952148</t>
+    <t xml:space="preserve">45.8015937805176</t>
   </si>
   <si>
     <t xml:space="preserve">46.7955894470215</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">46.8345718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5362091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7738265991211</t>
+    <t xml:space="preserve">47.5362129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7738304138184</t>
   </si>
   <si>
     <t xml:space="preserve">47.7311096191406</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">49.8945045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7483329772949</t>
+    <t xml:space="preserve">49.7483291625977</t>
   </si>
   <si>
     <t xml:space="preserve">48.4522438049316</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">57.1545486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3494453430176</t>
+    <t xml:space="preserve">57.3494491577148</t>
   </si>
   <si>
     <t xml:space="preserve">56.9109230041504</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">55.6927947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5698394775391</t>
+    <t xml:space="preserve">56.5698432922363</t>
   </si>
   <si>
     <t xml:space="preserve">59.1522750854492</t>
@@ -3749,37 +3749,37 @@
     <t xml:space="preserve">60.8576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0038261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8111953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6395263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8599243164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2497215270996</t>
+    <t xml:space="preserve">61.0038299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8111991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6395225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8599281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2497253417969</t>
   </si>
   <si>
     <t xml:space="preserve">57.9828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4214019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6882514953613</t>
+    <t xml:space="preserve">58.4213981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6882476806641</t>
   </si>
   <si>
     <t xml:space="preserve">61.2961807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2684020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3194046020508</t>
+    <t xml:space="preserve">64.2684097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.319408416748</t>
   </si>
   <si>
     <t xml:space="preserve">63.0502815246582</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">67.0457458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4842681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1176986694336</t>
+    <t xml:space="preserve">67.484260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1176910400391</t>
   </si>
   <si>
     <t xml:space="preserve">69.8230819702148</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">67.1919097900391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8972854614258</t>
+    <t xml:space="preserve">68.8972930908203</t>
   </si>
   <si>
     <t xml:space="preserve">67.3380889892578</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4865417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5817184448242</t>
+    <t xml:space="preserve">65.4865341186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5817108154297</t>
   </si>
   <si>
     <t xml:space="preserve">68.2638702392578</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">66.1199645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8995666503906</t>
+    <t xml:space="preserve">66.8995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">67.0944671630859</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">68.6536636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0434722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6513977050781</t>
+    <t xml:space="preserve">69.0434646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6514053344727</t>
   </si>
   <si>
     <t xml:space="preserve">71.7233505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4310073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.528450012207</t>
+    <t xml:space="preserve">71.4309997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5284576416016</t>
   </si>
   <si>
     <t xml:space="preserve">72.6978530883789</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">75.0366516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.3057861328125</t>
+    <t xml:space="preserve">74.305778503418</t>
   </si>
   <si>
     <t xml:space="preserve">74.4032287597656</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7188034057617</t>
+    <t xml:space="preserve">75.7188110351562</t>
   </si>
   <si>
     <t xml:space="preserve">78.8372192382812</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">76.839485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">77.2780151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.3754577636719</t>
+    <t xml:space="preserve">77.2780227661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.3754653930664</t>
   </si>
   <si>
     <t xml:space="preserve">74.9879302978516</t>
@@ -3917,10 +3917,10 @@
     <t xml:space="preserve">79.3244705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">78.8859405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.5703582763672</t>
+    <t xml:space="preserve">78.8859329223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.5703659057617</t>
   </si>
   <si>
     <t xml:space="preserve">77.1805572509766</t>
@@ -3929,28 +3929,28 @@
     <t xml:space="preserve">78.1550598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0088958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1295700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.4241790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6678085327148</t>
+    <t xml:space="preserve">78.0088882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.1295623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.424186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.0831069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6678161621094</t>
   </si>
   <si>
     <t xml:space="preserve">78.2525177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.3012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0321197509766</t>
+    <t xml:space="preserve">78.3012466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.032112121582</t>
   </si>
   <si>
     <t xml:space="preserve">78.4474182128906</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">77.8139877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">77.4729080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.964714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8207931518555</t>
+    <t xml:space="preserve">77.4729156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9647064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.82080078125</t>
   </si>
   <si>
     <t xml:space="preserve">77.9601593017578</t>
@@ -3980,34 +3980,34 @@
     <t xml:space="preserve">77.7165374755859</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7119979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.468376159668</t>
+    <t xml:space="preserve">80.3964233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2989730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7119903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4683685302734</t>
   </si>
   <si>
     <t xml:space="preserve">81.8581695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7607192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2689361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1924438476562</t>
+    <t xml:space="preserve">81.7607269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.268928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1924362182617</t>
   </si>
   <si>
     <t xml:space="preserve">89.1182098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9488067626953</t>
+    <t xml:space="preserve">87.9488143920898</t>
   </si>
   <si>
     <t xml:space="preserve">86.6819534301758</t>
@@ -4019,16 +4019,16 @@
     <t xml:space="preserve">87.9000854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">86.3408737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2434234619141</t>
+    <t xml:space="preserve">86.3408813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2434387207031</t>
   </si>
   <si>
     <t xml:space="preserve">87.7051849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2876205444336</t>
+    <t xml:space="preserve">90.2876129150391</t>
   </si>
   <si>
     <t xml:space="preserve">87.8513641357422</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">89.3618316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">86.0972595214844</t>
+    <t xml:space="preserve">86.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">88.9720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4360580444336</t>
+    <t xml:space="preserve">88.4360656738281</t>
   </si>
   <si>
     <t xml:space="preserve">87.3153839111328</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">84.4893264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">82.1017913818359</t>
+    <t xml:space="preserve">82.1017990112305</t>
   </si>
   <si>
     <t xml:space="preserve">83.1250305175781</t>
@@ -4061,16 +4061,16 @@
     <t xml:space="preserve">85.6100082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8559112548828</t>
+    <t xml:space="preserve">83.8559036254883</t>
   </si>
   <si>
     <t xml:space="preserve">80.6887741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0043411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4196548461914</t>
+    <t xml:space="preserve">82.0043487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4196472167969</t>
   </si>
   <si>
     <t xml:space="preserve">79.2270278930664</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">78.7397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9091720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5299377441406</t>
+    <t xml:space="preserve">79.9091644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5299453735352</t>
   </si>
   <si>
     <t xml:space="preserve">78.3375091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">77.1096420288086</t>
+    <t xml:space="preserve">77.1096496582031</t>
   </si>
   <si>
     <t xml:space="preserve">77.5516738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6322021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5830764770508</t>
+    <t xml:space="preserve">78.632194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5830841064453</t>
   </si>
   <si>
     <t xml:space="preserve">78.3866271972656</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">80.056510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7618255615234</t>
+    <t xml:space="preserve">79.7618179321289</t>
   </si>
   <si>
     <t xml:space="preserve">80.5476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1370315551758</t>
+    <t xml:space="preserve">81.1370239257812</t>
   </si>
   <si>
     <t xml:space="preserve">82.7578048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6909790039062</t>
+    <t xml:space="preserve">83.6909713745117</t>
   </si>
   <si>
     <t xml:space="preserve">83.6418685913086</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">83.8874359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6281661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4317092895508</t>
+    <t xml:space="preserve">81.628173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4317169189453</t>
   </si>
   <si>
     <t xml:space="preserve">80.351203918457</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">79.4180221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0742263793945</t>
+    <t xml:space="preserve">79.07421875</t>
   </si>
   <si>
     <t xml:space="preserve">79.1724472045898</t>
@@ -4184,22 +4184,22 @@
     <t xml:space="preserve">81.8737411499023</t>
   </si>
   <si>
-    <t xml:space="preserve">78.926872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6362152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8326721191406</t>
+    <t xml:space="preserve">78.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6362075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0959548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8326644897461</t>
   </si>
   <si>
     <t xml:space="preserve">75.0468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6853332519531</t>
+    <t xml:space="preserve">75.6853256225586</t>
   </si>
   <si>
     <t xml:space="preserve">75.1450729370117</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">74.7030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4928894042969</t>
+    <t xml:space="preserve">72.4928970336914</t>
   </si>
   <si>
     <t xml:space="preserve">74.0154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">75.5870971679688</t>
+    <t xml:space="preserve">75.5870895385742</t>
   </si>
   <si>
     <t xml:space="preserve">73.7207489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6402359008789</t>
+    <t xml:space="preserve">72.6402282714844</t>
   </si>
   <si>
     <t xml:space="preserve">73.0331497192383</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">72.9349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1176834106445</t>
+    <t xml:space="preserve">71.1176910400391</t>
   </si>
   <si>
     <t xml:space="preserve">70.7738876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5597152709961</t>
+    <t xml:space="preserve">71.5597076416016</t>
   </si>
   <si>
     <t xml:space="preserve">74.4574737548828</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">73.6225128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3946533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7424850463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3181610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2022171020508</t>
+    <t xml:space="preserve">72.394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7424774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3181686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2022247314453</t>
   </si>
   <si>
     <t xml:space="preserve">68.8584213256836</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">69.2513427734375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9212188720703</t>
+    <t xml:space="preserve">70.9212265014648</t>
   </si>
   <si>
     <t xml:space="preserve">74.1136627197266</t>
@@ -4295,16 +4295,16 @@
     <t xml:space="preserve">72.1490859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5420074462891</t>
+    <t xml:space="preserve">72.5419998168945</t>
   </si>
   <si>
     <t xml:space="preserve">72.4437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4260711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9389419555664</t>
+    <t xml:space="preserve">73.4260635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9389343261719</t>
   </si>
   <si>
     <t xml:space="preserve">70.380973815918</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">68.7601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8270263671875</t>
+    <t xml:space="preserve">67.827018737793</t>
   </si>
   <si>
     <t xml:space="preserve">67.6305618286133</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">68.2690505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7247772216797</t>
+    <t xml:space="preserve">70.7247695922852</t>
   </si>
   <si>
     <t xml:space="preserve">70.675651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">69.546028137207</t>
+    <t xml:space="preserve">69.5460205078125</t>
   </si>
   <si>
     <t xml:space="preserve">70.1353988647461</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">70.2827453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">73.7698669433594</t>
+    <t xml:space="preserve">73.7698593139648</t>
   </si>
   <si>
     <t xml:space="preserve">74.7521514892578</t>
@@ -4361,19 +4361,19 @@
     <t xml:space="preserve">76.7167282104492</t>
   </si>
   <si>
-    <t xml:space="preserve">77.6007919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1804885864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5065765380859</t>
+    <t xml:space="preserve">77.6007843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1804962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5065841674805</t>
   </si>
   <si>
     <t xml:space="preserve">73.9172058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">77.7481384277344</t>
+    <t xml:space="preserve">77.7481307983398</t>
   </si>
   <si>
     <t xml:space="preserve">78.0428161621094</t>
@@ -4394,25 +4394,25 @@
     <t xml:space="preserve">77.3060989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">75.930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2255783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1273498535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9131851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.3238067626953</t>
+    <t xml:space="preserve">75.9309005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9131927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3238143920898</t>
   </si>
   <si>
     <t xml:space="preserve">76.372932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7344436645508</t>
+    <t xml:space="preserve">75.7344360351562</t>
   </si>
   <si>
     <t xml:space="preserve">73.1313781738281</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">83.9856643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9051513671875</t>
+    <t xml:space="preserve">82.905143737793</t>
   </si>
   <si>
     <t xml:space="preserve">85.0170669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7046661376953</t>
+    <t xml:space="preserve">85.7046737670898</t>
   </si>
   <si>
     <t xml:space="preserve">86.1466979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7851867675781</t>
+    <t xml:space="preserve">86.7851791381836</t>
   </si>
   <si>
     <t xml:space="preserve">86.7360687255859</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">86.048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9542617797852</t>
+    <t xml:space="preserve">82.9542541503906</t>
   </si>
   <si>
     <t xml:space="preserve">81.7263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2489547729492</t>
+    <t xml:space="preserve">83.2489471435547</t>
   </si>
   <si>
     <t xml:space="preserve">83.0033721923828</t>
@@ -4484,16 +4484,16 @@
     <t xml:space="preserve">84.3785858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2312316894531</t>
+    <t xml:space="preserve">84.2312393188477</t>
   </si>
   <si>
     <t xml:space="preserve">84.034782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5613479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1507263183594</t>
+    <t xml:space="preserve">82.5613555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1507186889648</t>
   </si>
   <si>
     <t xml:space="preserve">83.4454040527344</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">89.4864807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6338195800781</t>
+    <t xml:space="preserve">89.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">91.0090255737305</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">90.6652297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0581436157227</t>
+    <t xml:space="preserve">91.0581359863281</t>
   </si>
   <si>
     <t xml:space="preserve">91.9421997070312</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">92.286003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8576736450195</t>
+    <t xml:space="preserve">93.857666015625</t>
   </si>
   <si>
     <t xml:space="preserve">94.2014694213867</t>
@@ -4547,16 +4547,16 @@
     <t xml:space="preserve">100.88102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">102.845596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.747367858887</t>
+    <t xml:space="preserve">102.845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.747375488281</t>
   </si>
   <si>
     <t xml:space="preserve">104.613723754883</t>
   </si>
   <si>
-    <t xml:space="preserve">103.82788848877</t>
+    <t xml:space="preserve">103.827896118164</t>
   </si>
   <si>
     <t xml:space="preserve">104.515495300293</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">111.78443145752</t>
   </si>
   <si>
-    <t xml:space="preserve">109.034019470215</t>
+    <t xml:space="preserve">109.034027099609</t>
   </si>
   <si>
     <t xml:space="preserve">110.802146911621</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">109.721618652344</t>
   </si>
   <si>
-    <t xml:space="preserve">109.525161743164</t>
+    <t xml:space="preserve">109.525169372559</t>
   </si>
   <si>
     <t xml:space="preserve">109.918083190918</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">103.140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">103.63143157959</t>
+    <t xml:space="preserve">103.631439208984</t>
   </si>
   <si>
     <t xml:space="preserve">104.417266845703</t>
@@ -4625,16 +4625,16 @@
     <t xml:space="preserve">99.5058288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">102.158004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.122581481934</t>
+    <t xml:space="preserve">102.157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.122573852539</t>
   </si>
   <si>
     <t xml:space="preserve">99.9969711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8987350463867</t>
+    <t xml:space="preserve">99.8987426757812</t>
   </si>
   <si>
     <t xml:space="preserve">99.4075927734375</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">96.4116134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3625030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9518737792969</t>
+    <t xml:space="preserve">96.3624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9518661499023</t>
   </si>
   <si>
     <t xml:space="preserve">98.6217651367188</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">98.0815048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">96.264274597168</t>
+    <t xml:space="preserve">96.2642669677734</t>
   </si>
   <si>
     <t xml:space="preserve">95.429328918457</t>
   </si>
   <si>
-    <t xml:space="preserve">96.558967590332</t>
+    <t xml:space="preserve">96.5589599609375</t>
   </si>
   <si>
     <t xml:space="preserve">94.8399505615234</t>
@@ -4697,16 +4697,16 @@
     <t xml:space="preserve">96.3133850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8890686035156</t>
+    <t xml:space="preserve">94.8890609741211</t>
   </si>
   <si>
     <t xml:space="preserve">95.2328643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7417144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3488159179688</t>
+    <t xml:space="preserve">94.7417221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3488082885742</t>
   </si>
   <si>
     <t xml:space="preserve">93.4647521972656</t>
@@ -5724,6 +5724,9 @@
   </si>
   <si>
     <t xml:space="preserve">92.879997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3199996948242</t>
   </si>
 </sst>
 </file>
@@ -71660,7 +71663,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6924768519</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>326851</v>
@@ -71681,6 +71684,32 @@
         <v>1903</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6912847222</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>386685</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>94</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>92.4599990844727</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>93.3199996948242</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="1907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="1908">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1807565689087</t>
+    <t xml:space="preserve">15.1807556152344</t>
   </si>
   <si>
     <t xml:space="preserve">BC.MI</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0406265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3208866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3022012710571</t>
+    <t xml:space="preserve">15.0406255722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3208856582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3022022247314</t>
   </si>
   <si>
     <t xml:space="preserve">14.4427375793457</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">14.6389198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.087742805481</t>
+    <t xml:space="preserve">14.0877418518066</t>
   </si>
   <si>
     <t xml:space="preserve">14.0410308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3212919235229</t>
+    <t xml:space="preserve">14.3212909698486</t>
   </si>
   <si>
     <t xml:space="preserve">14.3399782180786</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">14.3866844177246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240531921387</t>
+    <t xml:space="preserve">13.9943227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240522384644</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9849796295166</t>
+    <t xml:space="preserve">13.9849805831909</t>
   </si>
   <si>
     <t xml:space="preserve">14.0036630630493</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">13.5459051132202</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1722259521484</t>
+    <t xml:space="preserve">13.1722269058228</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645904541016</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">13.4057760238647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0316905975342</t>
+    <t xml:space="preserve">13.3777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0316896438599</t>
   </si>
   <si>
     <t xml:space="preserve">13.7607717514038</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">13.8355073928833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372140884399</t>
+    <t xml:space="preserve">14.1064252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372150421143</t>
   </si>
   <si>
     <t xml:space="preserve">14.4520807266235</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">14.2558975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">15.414306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011447906494</t>
+    <t xml:space="preserve">15.4143056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011457443237</t>
   </si>
   <si>
     <t xml:space="preserve">15.2461490631104</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">15.1060180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3769378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
+    <t xml:space="preserve">15.3769369125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.479700088501</t>
   </si>
   <si>
     <t xml:space="preserve">15.6385164260864</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">15.5450963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6945657730103</t>
+    <t xml:space="preserve">15.6945648193359</t>
   </si>
   <si>
     <t xml:space="preserve">15.6104860305786</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">15.498384475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0873365402222</t>
+    <t xml:space="preserve">15.0873374938965</t>
   </si>
   <si>
     <t xml:space="preserve">14.9939155578613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6202354431152</t>
+    <t xml:space="preserve">14.6202363967896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1527299880981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.330228805542</t>
+    <t xml:space="preserve">15.3302297592163</t>
   </si>
   <si>
     <t xml:space="preserve">15.5918035507202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7225923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7412786483765</t>
+    <t xml:space="preserve">15.7225904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7412767410278</t>
   </si>
   <si>
     <t xml:space="preserve">15.8253564834595</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">16.4139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2924556732178</t>
+    <t xml:space="preserve">16.2924575805664</t>
   </si>
   <si>
     <t xml:space="preserve">16.3671913146973</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">16.2177181243896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3765316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3391647338867</t>
+    <t xml:space="preserve">16.3765296936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3391666412354</t>
   </si>
   <si>
     <t xml:space="preserve">16.1149559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2737712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4325866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6100845336914</t>
+    <t xml:space="preserve">16.2737731933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4325847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6100826263428</t>
   </si>
   <si>
     <t xml:space="preserve">16.6474514007568</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">16.5548648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6207466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6019191741943</t>
+    <t xml:space="preserve">16.6207485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.601921081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6866245269775</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">16.6583938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8278007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8183879852295</t>
+    <t xml:space="preserve">16.8278026580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8183898925781</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6890048980713</t>
+    <t xml:space="preserve">15.6890058517456</t>
   </si>
   <si>
     <t xml:space="preserve">15.472541809082</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">15.7078285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3407793045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.583101272583</t>
+    <t xml:space="preserve">15.3407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5831031799316</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113357543945</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">16.253698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290079116821</t>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290088653564</t>
   </si>
   <si>
     <t xml:space="preserve">14.8796148300171</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">15.2748985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2090167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101852416992</t>
+    <t xml:space="preserve">15.2090177536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101861953735</t>
   </si>
   <si>
     <t xml:space="preserve">14.7855005264282</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">14.314923286438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443281173706</t>
+    <t xml:space="preserve">14.6443271636963</t>
   </si>
   <si>
     <t xml:space="preserve">14.9172620773315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384197235107</t>
+    <t xml:space="preserve">15.5384206771851</t>
   </si>
   <si>
     <t xml:space="preserve">15.6513595581055</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5195960998535</t>
+    <t xml:space="preserve">15.5195970535278</t>
   </si>
   <si>
     <t xml:space="preserve">15.4348936080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854759216309</t>
+    <t xml:space="preserve">15.5854768753052</t>
   </si>
   <si>
     <t xml:space="preserve">15.9054689407349</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">15.933705329895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6701822280884</t>
+    <t xml:space="preserve">15.6701831817627</t>
   </si>
   <si>
     <t xml:space="preserve">15.3784246444702</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">15.5007753372192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6419458389282</t>
+    <t xml:space="preserve">15.6419467926025</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148836135864</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">16.3195781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2819290161133</t>
+    <t xml:space="preserve">16.2819309234619</t>
   </si>
   <si>
     <t xml:space="preserve">16.1595802307129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3760433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4607524871826</t>
+    <t xml:space="preserve">16.3760452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4607543945312</t>
   </si>
   <si>
     <t xml:space="preserve">16.5078105926514</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">16.4701614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7807388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560333251953</t>
+    <t xml:space="preserve">16.780740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560352325439</t>
   </si>
   <si>
     <t xml:space="preserve">16.9877948760986</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">17.0160293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9407386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8372097015381</t>
+    <t xml:space="preserve">16.9407405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8372116088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.9313278198242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9783840179443</t>
+    <t xml:space="preserve">16.978385925293</t>
   </si>
   <si>
     <t xml:space="preserve">16.846622467041</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">16.8936824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6960391998291</t>
+    <t xml:space="preserve">16.6960411071777</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125003814697</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">16.8089752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4231033325195</t>
+    <t xml:space="preserve">16.4231052398682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8842678070068</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9972038269043</t>
+    <t xml:space="preserve">16.9972057342529</t>
   </si>
   <si>
     <t xml:space="preserve">17.0536785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748569488525</t>
+    <t xml:space="preserve">16.8748588562012</t>
   </si>
   <si>
     <t xml:space="preserve">17.034854888916</t>
@@ -530,52 +530,52 @@
     <t xml:space="preserve">16.8654460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0724983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2324924468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1007328033447</t>
+    <t xml:space="preserve">16.7619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0725002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.232494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2607288360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2136726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3548412322998</t>
+    <t xml:space="preserve">17.2607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2136745452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3548431396484</t>
   </si>
   <si>
     <t xml:space="preserve">17.3642597198486</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3077850341797</t>
+    <t xml:space="preserve">17.3077869415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.2983741760254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6936588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8724784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.738338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8230438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6818714141846</t>
+    <t xml:space="preserve">17.693660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8724765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7383365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8230419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6818695068359</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042182922363</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">19.1430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3406753540039</t>
+    <t xml:space="preserve">19.3406734466553</t>
   </si>
   <si>
     <t xml:space="preserve">19.3783206939697</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5571422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4159698486328</t>
+    <t xml:space="preserve">19.2183246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5571403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4159679412842</t>
   </si>
   <si>
     <t xml:space="preserve">20.2724170684814</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">20.3571186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8935813903809</t>
+    <t xml:space="preserve">20.8935794830322</t>
   </si>
   <si>
     <t xml:space="preserve">20.6676979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6959362030029</t>
+    <t xml:space="preserve">20.6959342956543</t>
   </si>
   <si>
     <t xml:space="preserve">20.3665332794189</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">20.1030101776123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8206653594971</t>
+    <t xml:space="preserve">19.8206634521484</t>
   </si>
   <si>
     <t xml:space="preserve">19.7453727722168</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">19.6888999938965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7171382904053</t>
+    <t xml:space="preserve">19.7171363830566</t>
   </si>
   <si>
     <t xml:space="preserve">19.8488960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5759601593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630260467529</t>
+    <t xml:space="preserve">19.5759582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630241394043</t>
   </si>
   <si>
     <t xml:space="preserve">19.2747936248779</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">19.0018615722656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1053886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9171581268311</t>
+    <t xml:space="preserve">19.1053867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9171562194824</t>
   </si>
   <si>
     <t xml:space="preserve">19.0865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8701000213623</t>
+    <t xml:space="preserve">18.8700981140137</t>
   </si>
   <si>
     <t xml:space="preserve">18.4936351776123</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">18.286584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254005432129</t>
+    <t xml:space="preserve">18.6253986358643</t>
   </si>
   <si>
     <t xml:space="preserve">19.2559700012207</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">19.510082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2371520996094</t>
+    <t xml:space="preserve">19.2371501922607</t>
   </si>
   <si>
     <t xml:space="preserve">19.5006713867188</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">19.7924289703369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5947875976562</t>
+    <t xml:space="preserve">19.5947856903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6018199920654</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">21.3641510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2982692718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1853332519531</t>
+    <t xml:space="preserve">21.298267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1853351593018</t>
   </si>
   <si>
     <t xml:space="preserve">21.015926361084</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">21.2794494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1100406646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4112091064453</t>
+    <t xml:space="preserve">21.1100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4112071990967</t>
   </si>
   <si>
     <t xml:space="preserve">21.6088485717773</t>
@@ -791,25 +791,25 @@
     <t xml:space="preserve">22.0229587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.806489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0417804718018</t>
+    <t xml:space="preserve">21.8064918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0417823791504</t>
   </si>
   <si>
     <t xml:space="preserve">22.2582454681396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6817646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476482391357</t>
+    <t xml:space="preserve">22.6817665100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476463317871</t>
   </si>
   <si>
     <t xml:space="preserve">22.6252956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0394039154053</t>
+    <t xml:space="preserve">23.0394058227539</t>
   </si>
   <si>
     <t xml:space="preserve">22.7288246154785</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">21.6464996337891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9194297790527</t>
+    <t xml:space="preserve">21.9194316864014</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3076839447021</t>
+    <t xml:space="preserve">21.3076858520508</t>
   </si>
   <si>
     <t xml:space="preserve">22.1170711517334</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">21.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7285575866699</t>
+    <t xml:space="preserve">21.7285556793213</t>
   </si>
   <si>
     <t xml:space="preserve">21.7380332946777</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">21.4632263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6622257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5674648284912</t>
+    <t xml:space="preserve">21.662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5674667358398</t>
   </si>
   <si>
     <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013538360596</t>
+    <t xml:space="preserve">22.4013557434082</t>
   </si>
   <si>
     <t xml:space="preserve">22.5529708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5813980102539</t>
+    <t xml:space="preserve">22.5813999176025</t>
   </si>
   <si>
     <t xml:space="preserve">22.6761608123779</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">22.590877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7948894500732</t>
+    <t xml:space="preserve">21.7948913574219</t>
   </si>
   <si>
     <t xml:space="preserve">21.8138427734375</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8277778625488</t>
+    <t xml:space="preserve">22.8277759552002</t>
   </si>
   <si>
     <t xml:space="preserve">23.0362510681152</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">23.2162952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9983463287354</t>
+    <t xml:space="preserve">22.998348236084</t>
   </si>
   <si>
     <t xml:space="preserve">23.131010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5005779266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6900959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2731494903564</t>
+    <t xml:space="preserve">23.5005798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6900978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2731513977051</t>
   </si>
   <si>
     <t xml:space="preserve">23.1404857635498</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">23.4058170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">23.453197479248</t>
+    <t xml:space="preserve">23.4531955718994</t>
   </si>
   <si>
     <t xml:space="preserve">22.7709217071533</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">22.9793949127197</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6477317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4771633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.183406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8796195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1165199279785</t>
+    <t xml:space="preserve">22.6477336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.477165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1834049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.87961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1165180206299</t>
   </si>
   <si>
     <t xml:space="preserve">23.6616687774658</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">23.3868637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1783905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9035873413086</t>
+    <t xml:space="preserve">23.1783885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.90358543396</t>
   </si>
   <si>
     <t xml:space="preserve">24.0217571258545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6377010345459</t>
+    <t xml:space="preserve">24.4955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5145149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6376991271973</t>
   </si>
   <si>
     <t xml:space="preserve">24.6850814819336</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">24.5903244018555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7040309906006</t>
+    <t xml:space="preserve">24.7040328979492</t>
   </si>
   <si>
     <t xml:space="preserve">24.8082714080811</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">25.7653503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5474014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2915458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4052600860596</t>
+    <t xml:space="preserve">25.547399520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2915477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4052581787109</t>
   </si>
   <si>
     <t xml:space="preserve">25.4431648254395</t>
@@ -1094,28 +1094,28 @@
     <t xml:space="preserve">25.3863086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3484039306641</t>
+    <t xml:space="preserve">25.3484058380127</t>
   </si>
   <si>
     <t xml:space="preserve">25.3294506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0830707550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7274436950684</t>
+    <t xml:space="preserve">25.0830726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.727445602417</t>
   </si>
   <si>
     <t xml:space="preserve">25.661111831665</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9643459320068</t>
+    <t xml:space="preserve">25.9643440246582</t>
   </si>
   <si>
     <t xml:space="preserve">26.3054847717285</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8645706176758</t>
+    <t xml:space="preserve">26.8645687103271</t>
   </si>
   <si>
     <t xml:space="preserve">27.309944152832</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">27.0635662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">26.675048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9972343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1678028106689</t>
+    <t xml:space="preserve">26.6750469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9972362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1678009033203</t>
   </si>
   <si>
     <t xml:space="preserve">26.4665775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0591068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0451698303223</t>
+    <t xml:space="preserve">26.0591087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0451717376709</t>
   </si>
   <si>
     <t xml:space="preserve">25.1778335571289</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">25.1967887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5189723968506</t>
+    <t xml:space="preserve">25.518970489502</t>
   </si>
   <si>
     <t xml:space="preserve">25.1115036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5379238128662</t>
+    <t xml:space="preserve">25.5379257202148</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359188079834</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">25.2631187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1683597564697</t>
+    <t xml:space="preserve">25.1683578491211</t>
   </si>
   <si>
     <t xml:space="preserve">24.9219818115234</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">26.2486305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4381484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7987937927246</t>
+    <t xml:space="preserve">26.4381504058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7987957000732</t>
   </si>
   <si>
     <t xml:space="preserve">25.3673553466797</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">25.7084903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1064872741699</t>
+    <t xml:space="preserve">26.1064853668213</t>
   </si>
   <si>
     <t xml:space="preserve">26.8171882629395</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">27.3857536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8695850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8222064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9169654846191</t>
+    <t xml:space="preserve">25.8695869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8222045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9169673919678</t>
   </si>
   <si>
     <t xml:space="preserve">25.632682800293</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">24.0691375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4481792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.827220916748</t>
+    <t xml:space="preserve">24.4481773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8272190093994</t>
   </si>
   <si>
     <t xml:space="preserve">23.7848567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2586612701416</t>
+    <t xml:space="preserve">24.258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">25.0641231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0167407989502</t>
+    <t xml:space="preserve">25.0167427062988</t>
   </si>
   <si>
     <t xml:space="preserve">24.9693641662598</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">23.9269981384277</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433876037598</t>
+    <t xml:space="preserve">26.3433856964111</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012481689453</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">26.153865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4855270385742</t>
+    <t xml:space="preserve">26.4855251312256</t>
   </si>
   <si>
     <t xml:space="preserve">26.5329093933105</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">28.6176376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8071556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6650161743164</t>
+    <t xml:space="preserve">28.8071575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.665018081665</t>
   </si>
   <si>
     <t xml:space="preserve">29.3283405303955</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">29.2335796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5394916534424</t>
+    <t xml:space="preserve">29.5394897460938</t>
   </si>
   <si>
     <t xml:space="preserve">30.2086715698242</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">30.113073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2602367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7419929504395</t>
+    <t xml:space="preserve">31.2602386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7419967651367</t>
   </si>
   <si>
     <t xml:space="preserve">33.6501617431641</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">33.936954498291</t>
   </si>
   <si>
-    <t xml:space="preserve">34.175952911377</t>
+    <t xml:space="preserve">34.1759490966797</t>
   </si>
   <si>
     <t xml:space="preserve">34.9885215759277</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">35.0841255187988</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6576995849609</t>
+    <t xml:space="preserve">35.6576957702637</t>
   </si>
   <si>
     <t xml:space="preserve">35.275318145752</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">36.422477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3746795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3268814086914</t>
+    <t xml:space="preserve">36.374683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3268852233887</t>
   </si>
   <si>
     <t xml:space="preserve">35.4187088012695</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">30.7822551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1168422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4036312103271</t>
+    <t xml:space="preserve">31.1168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4036331176758</t>
   </si>
   <si>
     <t xml:space="preserve">31.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2124404907227</t>
+    <t xml:space="preserve">31.3558368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2124423980713</t>
   </si>
   <si>
     <t xml:space="preserve">33.0287857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7935600280762</t>
+    <t xml:space="preserve">33.7935562133789</t>
   </si>
   <si>
     <t xml:space="preserve">33.9847526550293</t>
@@ -1442,31 +1442,31 @@
     <t xml:space="preserve">34.7973289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3671455383301</t>
+    <t xml:space="preserve">34.3671417236328</t>
   </si>
   <si>
     <t xml:space="preserve">34.6539344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0363273620605</t>
+    <t xml:space="preserve">35.0363235473633</t>
   </si>
   <si>
     <t xml:space="preserve">34.6061401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4627342224121</t>
+    <t xml:space="preserve">34.4627380371094</t>
   </si>
   <si>
     <t xml:space="preserve">33.8413619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7495307922363</t>
+    <t xml:space="preserve">34.7495346069336</t>
   </si>
   <si>
     <t xml:space="preserve">35.5621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0400924682617</t>
+    <t xml:space="preserve">36.0400886535645</t>
   </si>
   <si>
     <t xml:space="preserve">35.8966941833496</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">39.0035972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3306541442871</t>
+    <t xml:space="preserve">37.3306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">36.5180740356445</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">37.4262504577637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8564300537109</t>
+    <t xml:space="preserve">37.8564338684082</t>
   </si>
   <si>
     <t xml:space="preserve">36.2790870666504</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">34.8929252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5583343505859</t>
+    <t xml:space="preserve">34.5583381652832</t>
   </si>
   <si>
     <t xml:space="preserve">33.6979637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5067672729492</t>
+    <t xml:space="preserve">33.5067710876465</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677726745605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2640037536621</t>
+    <t xml:space="preserve">32.2640075683594</t>
   </si>
   <si>
     <t xml:space="preserve">32.9809875488281</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">32.5985946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">32.503002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2199745178223</t>
+    <t xml:space="preserve">32.5029983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2199783325195</t>
   </si>
   <si>
     <t xml:space="preserve">32.6463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3596038818359</t>
+    <t xml:space="preserve">32.3596000671387</t>
   </si>
   <si>
     <t xml:space="preserve">32.0728073120117</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">31.7860221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8338203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690402984619</t>
+    <t xml:space="preserve">31.8338241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0690422058105</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250129699707</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">31.8816165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8703117370605</t>
+    <t xml:space="preserve">28.8703098297119</t>
   </si>
   <si>
     <t xml:space="preserve">28.5357227325439</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">28.2011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7709465026855</t>
+    <t xml:space="preserve">27.7709445953369</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401245117188</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">27.5797500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1055355072021</t>
+    <t xml:space="preserve">28.1055374145508</t>
   </si>
   <si>
     <t xml:space="preserve">27.2451610565186</t>
@@ -1592,19 +1592,19 @@
     <t xml:space="preserve">27.9621410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3445262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0137042999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9181118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2048988342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4954605102539</t>
+    <t xml:space="preserve">28.3445281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0137062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9181098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2049007415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4954586029053</t>
   </si>
   <si>
     <t xml:space="preserve">29.5872917175293</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">29.6828861236572</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5835189819336</t>
+    <t xml:space="preserve">28.5835208892822</t>
   </si>
   <si>
     <t xml:space="preserve">26.5759811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">26.384786605835</t>
+    <t xml:space="preserve">26.3847846984863</t>
   </si>
   <si>
     <t xml:space="preserve">27.2929611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4363555908203</t>
+    <t xml:space="preserve">27.4363574981689</t>
   </si>
   <si>
     <t xml:space="preserve">27.8187427520752</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">27.7231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6313209533691</t>
+    <t xml:space="preserve">28.6313190460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.6350860595703</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">27.0061664581299</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0979957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6200103759766</t>
+    <t xml:space="preserve">26.0979976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6200122833252</t>
   </si>
   <si>
     <t xml:space="preserve">26.1935920715332</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">28.7269153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9659080505371</t>
+    <t xml:space="preserve">28.9659099578857</t>
   </si>
   <si>
     <t xml:space="preserve">28.6791172027588</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">26.8149738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4803848266602</t>
+    <t xml:space="preserve">26.4803867340088</t>
   </si>
   <si>
     <t xml:space="preserve">27.3885555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8225135803223</t>
+    <t xml:space="preserve">28.8225116729736</t>
   </si>
   <si>
     <t xml:space="preserve">29.8740787506104</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">30.3520660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3080368041992</t>
+    <t xml:space="preserve">31.3080387115479</t>
   </si>
   <si>
     <t xml:space="preserve">31.4514350891113</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">30.0748329162598</t>
   </si>
   <si>
-    <t xml:space="preserve">30.47633934021</t>
+    <t xml:space="preserve">30.4763412475586</t>
   </si>
   <si>
     <t xml:space="preserve">30.2277889251709</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">29.9983577728271</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8262825012207</t>
+    <t xml:space="preserve">29.8262844085693</t>
   </si>
   <si>
     <t xml:space="preserve">30.667537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4381046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352111816406</t>
+    <t xml:space="preserve">30.438102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7631340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935209274292</t>
   </si>
   <si>
     <t xml:space="preserve">29.7498054504395</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">29.7115669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8129539489746</t>
+    <t xml:space="preserve">28.812952041626</t>
   </si>
   <si>
     <t xml:space="preserve">29.5203704833984</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">29.1762237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3291759490967</t>
+    <t xml:space="preserve">29.3291778564453</t>
   </si>
   <si>
     <t xml:space="preserve">28.5761566162109</t>
@@ -5733,6 +5733,9 @@
   </si>
   <si>
     <t xml:space="preserve">92.9400024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -71721,7 +71724,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6917939815</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>245216</v>
@@ -71742,6 +71745,32 @@
         <v>1906</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6925231481</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>408795</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>95.1800003051758</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>92.8399963378906</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>94.8199996948242</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>1907</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="1908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="1909">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">14.8537864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4801063537598</t>
+    <t xml:space="preserve">14.4801054000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.1718196868896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9476127624512</t>
+    <t xml:space="preserve">13.9476118087769</t>
   </si>
   <si>
     <t xml:space="preserve">13.9289274215698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0406265258789</t>
+    <t xml:space="preserve">15.0406274795532</t>
   </si>
   <si>
     <t xml:space="preserve">15.3208856582642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3022022247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0877418518066</t>
+    <t xml:space="preserve">15.3022003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.44273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.087742805481</t>
   </si>
   <si>
     <t xml:space="preserve">14.0410308837891</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">14.3212919235229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.33997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7697076797485</t>
+    <t xml:space="preserve">14.3399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7697086334229</t>
   </si>
   <si>
     <t xml:space="preserve">14.3866844177246</t>
@@ -95,103 +95,103 @@
     <t xml:space="preserve">13.9943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240522384644</t>
+    <t xml:space="preserve">14.4240531921387</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9849796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0036640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433801651001</t>
+    <t xml:space="preserve">13.9849805831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.003662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338006973267</t>
   </si>
   <si>
     <t xml:space="preserve">12.7051248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4155235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4061813354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172292709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1722269058228</t>
+    <t xml:space="preserve">12.4155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5459051132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1722249984741</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4057750701904</t>
+    <t xml:space="preserve">13.4057760238647</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777494430542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9195852279663</t>
+    <t xml:space="preserve">14.1251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0316905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7607717514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.835506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2372150421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4520797729492</t>
+    <t xml:space="preserve">13.7607707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8355073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1064252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2372140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4520807266235</t>
   </si>
   <si>
     <t xml:space="preserve">14.255898475647</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4143056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011457443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2461500167847</t>
+    <t xml:space="preserve">15.414306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2461490631104</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060190200806</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3769388198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4796991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6385135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5450925827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6104879379272</t>
+    <t xml:space="preserve">15.3769369125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.479700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6385145187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.545093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6945648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6104888916016</t>
   </si>
   <si>
     <t xml:space="preserve">15.4983835220337</t>
@@ -200,37 +200,37 @@
     <t xml:space="preserve">15.0873355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9939165115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6202354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1527280807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3302278518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5918045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7225952148438</t>
+    <t xml:space="preserve">14.99391746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6202335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1527290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3302297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5918035507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7225942611694</t>
   </si>
   <si>
     <t xml:space="preserve">15.7412757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8253536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3017978668213</t>
+    <t xml:space="preserve">15.8253593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3017997741699</t>
   </si>
   <si>
     <t xml:space="preserve">16.3952159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3858757019043</t>
+    <t xml:space="preserve">16.3858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">16.3485088348389</t>
@@ -239,70 +239,70 @@
     <t xml:space="preserve">16.2550849914551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4138965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2924575805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3671913146973</t>
+    <t xml:space="preserve">16.4139003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2924556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3671894073486</t>
   </si>
   <si>
     <t xml:space="preserve">16.0215358734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2177181243896</t>
+    <t xml:space="preserve">16.2177219390869</t>
   </si>
   <si>
     <t xml:space="preserve">16.3765354156494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3391628265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1149559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2737712860107</t>
+    <t xml:space="preserve">16.3391647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1149578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2737731933594</t>
   </si>
   <si>
     <t xml:space="preserve">16.4325866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6100826263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6474494934082</t>
+    <t xml:space="preserve">16.6100845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6474475860596</t>
   </si>
   <si>
     <t xml:space="preserve">16.6287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4419288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889850616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6489810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5548667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207427978516</t>
+    <t xml:space="preserve">16.4419250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6489791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5548648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">16.6019229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6866245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995662689209</t>
+    <t xml:space="preserve">16.6866283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995624542236</t>
   </si>
   <si>
     <t xml:space="preserve">16.5454540252686</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">16.8183879852295</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254638671875</t>
+    <t xml:space="preserve">16.2254600524902</t>
   </si>
   <si>
     <t xml:space="preserve">15.6890048980713</t>
@@ -326,52 +326,52 @@
     <t xml:space="preserve">15.4725408554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7078275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3407793045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.583101272583</t>
+    <t xml:space="preserve">15.7078285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3407783508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5830993652344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4325141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.253698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5290088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8796138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0678443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2748975753784</t>
+    <t xml:space="preserve">16.4325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2536964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5642776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5290098190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8796157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0678453445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2748994827271</t>
   </si>
   <si>
     <t xml:space="preserve">15.2090177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854986190796</t>
+    <t xml:space="preserve">15.5101852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7855005264282</t>
   </si>
   <si>
     <t xml:space="preserve">14.3149223327637</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443252563477</t>
+    <t xml:space="preserve">14.6443271636963</t>
   </si>
   <si>
     <t xml:space="preserve">14.9172611236572</t>
@@ -380,46 +380,46 @@
     <t xml:space="preserve">15.5384206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6513614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5195970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4348936080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9054708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8301792144775</t>
+    <t xml:space="preserve">15.6513586044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5195980072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4348945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9054689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8301773071289</t>
   </si>
   <si>
     <t xml:space="preserve">15.9901752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7925310134888</t>
+    <t xml:space="preserve">15.7925329208374</t>
   </si>
   <si>
     <t xml:space="preserve">15.5478343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9337043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6701803207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3784236907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5007743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6419496536255</t>
+    <t xml:space="preserve">15.933705329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6701822280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3784255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5007753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6419467926025</t>
   </si>
   <si>
     <t xml:space="preserve">15.9148836135864</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">16.2725200653076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2819309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1595802307129</t>
+    <t xml:space="preserve">16.3195762634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2819290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1595840454102</t>
   </si>
   <si>
     <t xml:space="preserve">16.3760452270508</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">16.4983997344971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4607486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5078086853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4701633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7807426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8560352325439</t>
+    <t xml:space="preserve">16.4607524871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5078067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4701614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7807388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8560333251953</t>
   </si>
   <si>
     <t xml:space="preserve">16.98779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9407367706299</t>
+    <t xml:space="preserve">17.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9407386779785</t>
   </si>
   <si>
     <t xml:space="preserve">16.8372097015381</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">16.931324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.978385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.846622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8936824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6960372924805</t>
+    <t xml:space="preserve">16.9783821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8466205596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8936805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6960391998291</t>
   </si>
   <si>
     <t xml:space="preserve">16.9125022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713298797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8089790344238</t>
+    <t xml:space="preserve">16.7713279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8089771270752</t>
   </si>
   <si>
     <t xml:space="preserve">16.4231052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8842716217041</t>
+    <t xml:space="preserve">16.8842678070068</t>
   </si>
   <si>
     <t xml:space="preserve">16.7525062561035</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">16.9030914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0066146850586</t>
+    <t xml:space="preserve">17.0066184997559</t>
   </si>
   <si>
     <t xml:space="preserve">16.9972057342529</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">17.0536785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8748588562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0348529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8654441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7619171142578</t>
+    <t xml:space="preserve">16.8748550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.034854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8654460906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7619190216064</t>
   </si>
   <si>
     <t xml:space="preserve">17.0724983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.232494354248</t>
+    <t xml:space="preserve">17.2324981689453</t>
   </si>
   <si>
     <t xml:space="preserve">17.1007328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289710998535</t>
+    <t xml:space="preserve">17.1289691925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2607307434082</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">17.2136707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3642539978027</t>
+    <t xml:space="preserve">17.3548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3642578125</t>
   </si>
   <si>
     <t xml:space="preserve">17.3077869415283</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">17.2983741760254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6936569213867</t>
+    <t xml:space="preserve">17.693660736084</t>
   </si>
   <si>
     <t xml:space="preserve">17.8724784851074</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738338470459</t>
+    <t xml:space="preserve">18.7383365631104</t>
   </si>
   <si>
     <t xml:space="preserve">18.8230419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8042163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430358886719</t>
+    <t xml:space="preserve">18.6818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">19.3406734466553</t>
@@ -593,43 +593,43 @@
     <t xml:space="preserve">18.9359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2183246612549</t>
+    <t xml:space="preserve">19.2183265686035</t>
   </si>
   <si>
     <t xml:space="preserve">19.5571422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4159641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2724170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.423002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2347679138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2535934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4982929229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.357120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.893575668335</t>
+    <t xml:space="preserve">19.4159679412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2724189758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4230003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2347736358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2535953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.498291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3571186065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8935775756836</t>
   </si>
   <si>
     <t xml:space="preserve">20.6676998138428</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6959362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3665332794189</t>
+    <t xml:space="preserve">20.6959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3665294647217</t>
   </si>
   <si>
     <t xml:space="preserve">20.1030082702637</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">19.8206615447998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7453689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5194931030273</t>
+    <t xml:space="preserve">19.7453708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.519495010376</t>
   </si>
   <si>
     <t xml:space="preserve">19.6889019012451</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">19.7171363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.84889793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5759601593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4630241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2747917175293</t>
+    <t xml:space="preserve">19.8488960266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.575963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4630279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2747936248779</t>
   </si>
   <si>
     <t xml:space="preserve">19.4442024230957</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">19.3971462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0959758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.001859664917</t>
+    <t xml:space="preserve">19.0959777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0018615722656</t>
   </si>
   <si>
     <t xml:space="preserve">19.1053867340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9171581268311</t>
+    <t xml:space="preserve">18.9171600341797</t>
   </si>
   <si>
     <t xml:space="preserve">19.0865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8701019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4936408996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524646759033</t>
+    <t xml:space="preserve">18.8700981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4936370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524684906006</t>
   </si>
   <si>
     <t xml:space="preserve">18.2865867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6254005432129</t>
+    <t xml:space="preserve">18.6254024505615</t>
   </si>
   <si>
     <t xml:space="preserve">19.2559719085693</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">19.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2371501922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5006713867188</t>
+    <t xml:space="preserve">19.2371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5006694793701</t>
   </si>
   <si>
     <t xml:space="preserve">19.7547798156738</t>
@@ -722,61 +722,61 @@
     <t xml:space="preserve">19.7924289703369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5947875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6018199920654</t>
+    <t xml:space="preserve">19.5947895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6018180847168</t>
   </si>
   <si>
     <t xml:space="preserve">20.7335815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994632720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7900485992432</t>
+    <t xml:space="preserve">20.7994613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7900505065918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9218101501465</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3641529083252</t>
+    <t xml:space="preserve">21.3641510009766</t>
   </si>
   <si>
     <t xml:space="preserve">21.2982711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1853351593018</t>
+    <t xml:space="preserve">21.1853332519531</t>
   </si>
   <si>
     <t xml:space="preserve">21.015926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9029865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0253391265869</t>
+    <t xml:space="preserve">20.9029884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0253372192383</t>
   </si>
   <si>
     <t xml:space="preserve">20.9876899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1947460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794494628906</t>
+    <t xml:space="preserve">21.1947441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794513702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.1100425720215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4112091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6088542938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2135715484619</t>
+    <t xml:space="preserve">21.4112110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.608850479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.213565826416</t>
   </si>
   <si>
     <t xml:space="preserve">21.3829765319824</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">21.54296875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8347301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0229587554932</t>
+    <t xml:space="preserve">21.8347282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0229606628418</t>
   </si>
   <si>
     <t xml:space="preserve">21.8064937591553</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">22.0417823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2582473754883</t>
+    <t xml:space="preserve">22.2582454681396</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817646026611</t>
@@ -806,70 +806,70 @@
     <t xml:space="preserve">22.7476463317871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6252994537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0394020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7288246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0582237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0135459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6464958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9194316864014</t>
+    <t xml:space="preserve">22.6252975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0394039154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7288208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0582256317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5876522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3711853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0135478973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6464996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.91943359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.787670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3076820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.117073059082</t>
+    <t xml:space="preserve">21.3076839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1170749664307</t>
   </si>
   <si>
     <t xml:space="preserve">22.0981216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1455059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1549777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2686901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0507431030273</t>
+    <t xml:space="preserve">22.1455020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1549797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2686920166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0507411956787</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0886459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.756986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8327960968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6811752319336</t>
+    <t xml:space="preserve">22.08864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7569847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6811771392822</t>
   </si>
   <si>
     <t xml:space="preserve">21.576940536499</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">21.7285575866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7380332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5579891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5200843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1315650939941</t>
+    <t xml:space="preserve">21.7380313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5579872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5200824737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1315670013428</t>
   </si>
   <si>
     <t xml:space="preserve">21.4158477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8612232208252</t>
+    <t xml:space="preserve">21.8612194061279</t>
   </si>
   <si>
     <t xml:space="preserve">21.4632263183594</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6622276306152</t>
+    <t xml:space="preserve">21.6622257232666</t>
   </si>
   <si>
     <t xml:space="preserve">21.5674648284912</t>
@@ -908,70 +908,70 @@
     <t xml:space="preserve">22.5624485015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4013538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5529689788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5814018249512</t>
+    <t xml:space="preserve">22.4013557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5529727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5813999176025</t>
   </si>
   <si>
     <t xml:space="preserve">22.6761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5908794403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7948875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8138446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8422679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.671703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4676856994629</t>
+    <t xml:space="preserve">22.5908756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7948913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8138427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8422698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6717014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958957672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4676895141602</t>
   </si>
   <si>
     <t xml:space="preserve">22.3255481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5055923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6951122283936</t>
+    <t xml:space="preserve">22.50559425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">22.8277778625488</t>
   </si>
   <si>
-    <t